--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92A427E5-0D68-401F-9CE6-2EFB3B589B9B}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9161CB68-41B6-4FBC-AC40-042C07F253AD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="81">
   <si>
     <t>POD</t>
   </si>
@@ -267,6 +267,24 @@
   </si>
   <si>
     <t>17 DIAS</t>
+  </si>
+  <si>
+    <t>KAOHSIUNG</t>
+  </si>
+  <si>
+    <t>8 al 15 de marzo</t>
+  </si>
+  <si>
+    <t>KEELUNG</t>
+  </si>
+  <si>
+    <t>TAIPEI</t>
+  </si>
+  <si>
+    <t>TAICHUNG</t>
+  </si>
+  <si>
+    <t>TAOYUAN</t>
   </si>
 </sst>
 </file>
@@ -274,8 +292,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="168" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -376,7 +394,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -390,7 +408,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -764,13 +782,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I175"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>2</v>
       </c>
@@ -799,7 +819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
@@ -828,7 +848,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>20</v>
       </c>
@@ -857,7 +877,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>19</v>
       </c>
@@ -886,7 +906,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -915,7 +935,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -944,7 +964,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
@@ -973,7 +993,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>4</v>
       </c>
@@ -1002,7 +1022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>25</v>
       </c>
@@ -1031,7 +1051,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>26</v>
       </c>
@@ -1060,7 +1080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>27</v>
       </c>
@@ -1089,7 +1109,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>28</v>
       </c>
@@ -1118,7 +1138,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>29</v>
       </c>
@@ -1147,7 +1167,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>57</v>
       </c>
@@ -1176,7 +1196,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>58</v>
       </c>
@@ -1205,7 +1225,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>30</v>
       </c>
@@ -1234,7 +1254,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>59</v>
       </c>
@@ -1263,7 +1283,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>60</v>
       </c>
@@ -1292,7 +1312,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>61</v>
       </c>
@@ -1321,7 +1341,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>31</v>
       </c>
@@ -1350,7 +1370,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>32</v>
       </c>
@@ -1379,7 +1399,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>33</v>
       </c>
@@ -1408,7 +1428,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>34</v>
       </c>
@@ -1437,7 +1457,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>35</v>
       </c>
@@ -1466,7 +1486,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
         <v>36</v>
       </c>
@@ -1495,7 +1515,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>62</v>
       </c>
@@ -1524,7 +1544,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>63</v>
       </c>
@@ -1553,7 +1573,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>37</v>
       </c>
@@ -1582,7 +1602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>38</v>
       </c>
@@ -1611,7 +1631,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>64</v>
       </c>
@@ -1640,7 +1660,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>65</v>
       </c>
@@ -1669,7 +1689,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>66</v>
       </c>
@@ -1698,7 +1718,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>67</v>
       </c>
@@ -1727,7 +1747,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>68</v>
       </c>
@@ -1756,7 +1776,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>69</v>
       </c>
@@ -1785,7 +1805,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>70</v>
       </c>
@@ -1814,7 +1834,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>71</v>
       </c>
@@ -1843,7 +1863,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>39</v>
       </c>
@@ -1872,7 +1892,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>40</v>
       </c>
@@ -1901,7 +1921,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>72</v>
       </c>
@@ -1930,7 +1950,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>73</v>
       </c>
@@ -1959,7 +1979,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>41</v>
       </c>
@@ -1988,7 +2008,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>21</v>
       </c>
@@ -2017,7 +2037,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>20</v>
       </c>
@@ -2046,7 +2066,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>19</v>
       </c>
@@ -2075,7 +2095,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>16</v>
       </c>
@@ -2104,7 +2124,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>13</v>
       </c>
@@ -2133,7 +2153,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>5</v>
       </c>
@@ -2162,7 +2182,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>4</v>
       </c>
@@ -2191,7 +2211,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>25</v>
       </c>
@@ -2220,7 +2240,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>26</v>
       </c>
@@ -2249,7 +2269,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>27</v>
       </c>
@@ -2278,7 +2298,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>28</v>
       </c>
@@ -2307,7 +2327,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>29</v>
       </c>
@@ -2336,7 +2356,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>57</v>
       </c>
@@ -2365,7 +2385,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>58</v>
       </c>
@@ -2394,7 +2414,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>30</v>
       </c>
@@ -2423,7 +2443,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>59</v>
       </c>
@@ -2452,7 +2472,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>60</v>
       </c>
@@ -2481,7 +2501,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>61</v>
       </c>
@@ -2510,7 +2530,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>31</v>
       </c>
@@ -2539,7 +2559,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>32</v>
       </c>
@@ -2568,7 +2588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>33</v>
       </c>
@@ -2597,7 +2617,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>34</v>
       </c>
@@ -2626,7 +2646,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>35</v>
       </c>
@@ -2655,7 +2675,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="8" t="s">
         <v>36</v>
       </c>
@@ -2684,7 +2704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>62</v>
       </c>
@@ -2713,7 +2733,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>63</v>
       </c>
@@ -2742,7 +2762,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>37</v>
       </c>
@@ -2771,7 +2791,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>38</v>
       </c>
@@ -2800,7 +2820,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>64</v>
       </c>
@@ -2829,7 +2849,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>65</v>
       </c>
@@ -2858,7 +2878,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>66</v>
       </c>
@@ -2887,7 +2907,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>67</v>
       </c>
@@ -2916,7 +2936,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>68</v>
       </c>
@@ -2945,7 +2965,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>69</v>
       </c>
@@ -2974,7 +2994,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>70</v>
       </c>
@@ -3003,7 +3023,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>71</v>
       </c>
@@ -3032,7 +3052,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>39</v>
       </c>
@@ -3061,7 +3081,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
         <v>40</v>
       </c>
@@ -3090,7 +3110,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>72</v>
       </c>
@@ -3119,7 +3139,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>73</v>
       </c>
@@ -3148,7 +3168,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>41</v>
       </c>
@@ -3174,6 +3194,2674 @@
         <v>23</v>
       </c>
       <c r="I83" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D84" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E84" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G84" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D85" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E85" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G85" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H85" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D86" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E86" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G86" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H86" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D87" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E87" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G87" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H87" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D88" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E88" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G88" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D89" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E89" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G89" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H89" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="8">
+        <v>2720</v>
+      </c>
+      <c r="D90" s="8">
+        <v>3200</v>
+      </c>
+      <c r="E90" s="8">
+        <v>3350</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G90" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H90" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D91" s="8">
+        <v>3300</v>
+      </c>
+      <c r="E91" s="8">
+        <v>3560</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G91" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I91" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="8">
+        <v>3300</v>
+      </c>
+      <c r="E92" s="8">
+        <v>3560</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G92" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H92" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D93" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E93" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G93" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D94" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E94" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G94" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H94" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D95" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E95" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G95" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D96" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E96" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G96" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H96" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D97" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E97" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G97" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D98" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E98" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G98" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H98" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D99" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E99" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G99" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I99" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D100" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E100" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G100" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H100" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I100" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="8">
+        <v>2930</v>
+      </c>
+      <c r="D101" s="8">
+        <v>3250</v>
+      </c>
+      <c r="E101" s="8">
+        <v>3460</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G101" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="8">
+        <v>3300</v>
+      </c>
+      <c r="E102" s="8">
+        <v>3560</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G102" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H102" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I102" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="8">
+        <v>3300</v>
+      </c>
+      <c r="E103" s="8">
+        <v>3560</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G103" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="8">
+        <v>3300</v>
+      </c>
+      <c r="E104" s="8">
+        <v>3560</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G104" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H104" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I104" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="8">
+        <v>3300</v>
+      </c>
+      <c r="E105" s="8">
+        <v>3510</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G105" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I105" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="8">
+        <v>3460</v>
+      </c>
+      <c r="E106" s="8">
+        <v>3830</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G106" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H106" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E107" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G107" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I107" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" s="8">
+        <v>3510</v>
+      </c>
+      <c r="E108" s="8">
+        <v>3880</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G108" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H108" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I108" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="8">
+        <v>3510</v>
+      </c>
+      <c r="E109" s="8">
+        <v>3880</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G109" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I109" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C110" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E110" s="8">
+        <v>3560</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G110" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H110" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C111" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E111" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G111" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E112" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E113" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G113" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E114" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G114" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H114" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E115" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G115" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H115" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E116" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G116" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H116" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E117" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G117" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E118" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G118" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H118" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E119" s="8">
+        <v>3670</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G119" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H119" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" s="8">
+        <v>3460</v>
+      </c>
+      <c r="E120" s="8">
+        <v>3830</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G120" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I120" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="8">
+        <v>3510</v>
+      </c>
+      <c r="E121" s="8">
+        <v>3880</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G121" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H121" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I121" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" s="8">
+        <v>3560</v>
+      </c>
+      <c r="E122" s="8">
+        <v>3980</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G122" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H122" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I122" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="8">
+        <v>3560</v>
+      </c>
+      <c r="E123" s="8">
+        <v>3980</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G123" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H123" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I123" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="8">
+        <v>3720</v>
+      </c>
+      <c r="E124" s="8">
+        <v>4190</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G124" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H124" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I124" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E125" s="8">
+        <v>3510</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G125" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H125" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I125" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E126" s="8">
+        <v>3510</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G126" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H126" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I126" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E127" s="8">
+        <v>3510</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G127" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I127" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E128" s="8">
+        <v>3510</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G128" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I128" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E129" s="8">
+        <v>3510</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G129" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="I129" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B130" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E130" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G130" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H130" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I130" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E131" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G131" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I131" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E132" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G132" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E133" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G133" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I133" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E134" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G134" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I134" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E135" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G135" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H135" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I135" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B136" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E136" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G136" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I136" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E137" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G137" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H137" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I137" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B138" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="8">
+        <v>3160</v>
+      </c>
+      <c r="E138" s="8">
+        <v>3370</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G138" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H138" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I138" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="8">
+        <v>3230</v>
+      </c>
+      <c r="E139" s="8">
+        <v>3520</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G139" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H139" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I139" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E140" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I140" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E141" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H141" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I141" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B142" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E142" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I142" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E143" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I143" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B144" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E144" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H144" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I144" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E145" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H145" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I145" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B146" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E146" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I146" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E147" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H147" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I147" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B148" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E148" s="8">
+        <v>3780</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H148" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I148" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="8">
+        <v>3210</v>
+      </c>
+      <c r="E149" s="8">
+        <v>3470</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H149" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B150" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="8">
+        <v>3260</v>
+      </c>
+      <c r="E150" s="8">
+        <v>3520</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="8">
+        <v>3380</v>
+      </c>
+      <c r="E151" s="8">
+        <v>3680</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" s="8">
+        <v>3310</v>
+      </c>
+      <c r="E152" s="8">
+        <v>3680</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I152" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="8">
+        <v>3380</v>
+      </c>
+      <c r="E153" s="8">
+        <v>3720</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H153" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I153" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B154" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E154" s="8">
+        <v>3810</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I154" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="8">
+        <v>3410</v>
+      </c>
+      <c r="E155" s="8">
+        <v>3810</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H155" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I155" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" s="8">
+        <v>3350</v>
+      </c>
+      <c r="E156" s="8">
+        <v>3680</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H156" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I156" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" s="8">
+        <v>3370</v>
+      </c>
+      <c r="E157" s="8">
+        <v>3700</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H157" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I157" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="B158" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E158" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I158" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E159" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H159" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I159" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B160" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E160" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I160" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C161" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E161" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H161" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I161" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B162" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E162" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I162" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E163" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H163" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I163" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B164" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E164" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I164" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="8">
+        <v>3280</v>
+      </c>
+      <c r="E165" s="8">
+        <v>3590</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H165" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I165" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B166" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166" s="8">
+        <v>3400</v>
+      </c>
+      <c r="E166" s="8">
+        <v>3800</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H166" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I166" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167" s="8">
+        <v>3400</v>
+      </c>
+      <c r="E167" s="8">
+        <v>3770</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H167" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I167" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B168" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168" s="8">
+        <v>3400</v>
+      </c>
+      <c r="E168" s="8">
+        <v>3840</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H168" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I168" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="8">
+        <v>3400</v>
+      </c>
+      <c r="E169" s="8">
+        <v>3840</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H169" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I169" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B170" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="8">
+        <v>3590</v>
+      </c>
+      <c r="E170" s="8">
+        <v>4190</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H170" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I170" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171" s="8">
+        <v>3260</v>
+      </c>
+      <c r="E171" s="8">
+        <v>3520</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I171" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="B172" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" s="8">
+        <v>3370</v>
+      </c>
+      <c r="E172" s="8">
+        <v>3680</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H172" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I172" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="8">
+        <v>3370</v>
+      </c>
+      <c r="E173" s="8">
+        <v>3680</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H173" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="B174" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" s="8">
+        <v>3420</v>
+      </c>
+      <c r="E174" s="8">
+        <v>3730</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H174" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D175" s="8">
+        <v>3420</v>
+      </c>
+      <c r="E175" s="8">
+        <v>3730</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="H175" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" s="8" t="s">
         <v>24</v>
       </c>
     </row>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9161CB68-41B6-4FBC-AC40-042C07F253AD}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73B71079-A96C-4D9B-BBD5-7D854AECB877}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1215" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="96">
   <si>
     <t>POD</t>
   </si>
@@ -285,15 +285,63 @@
   </si>
   <si>
     <t>TAOYUAN</t>
+  </si>
+  <si>
+    <t>CALLAO</t>
+  </si>
+  <si>
+    <t>SAN ANTONIO</t>
+  </si>
+  <si>
+    <t>BARCELONA</t>
+  </si>
+  <si>
+    <t>POSORJA</t>
+  </si>
+  <si>
+    <t>CMA-CGM</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>31 de marzo</t>
+  </si>
+  <si>
+    <t>VALENCIA</t>
+  </si>
+  <si>
+    <t>LIVORNO</t>
+  </si>
+  <si>
+    <t>GENOA</t>
+  </si>
+  <si>
+    <t>HAMBURG</t>
+  </si>
+  <si>
+    <t>ANTWERP</t>
+  </si>
+  <si>
+    <t>ROTTERDAM</t>
+  </si>
+  <si>
+    <t>LE HAVRE</t>
+  </si>
+  <si>
+    <t>LONDON GATEWAY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="169" formatCode="0\ &quot;DÍAS&quot;"/>
+    <numFmt numFmtId="175" formatCode="[$EUR]\ #,##0"/>
+    <numFmt numFmtId="176" formatCode="[$USD]\ #,##0.00"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -402,7 +450,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -424,6 +472,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -782,10 +835,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I175"/>
+  <dimension ref="A1:I413"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.42578125" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
@@ -826,13 +880,13 @@
       <c r="B2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="11">
         <v>2510</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2" s="11">
         <v>2670</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2" s="11">
         <v>2830</v>
       </c>
       <c r="F2" s="8" t="s">
@@ -855,13 +909,13 @@
       <c r="B3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="11">
         <v>2510</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="11">
         <v>2670</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="11">
         <v>2830</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -884,13 +938,13 @@
       <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="11">
         <v>2510</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="11">
         <v>2670</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="11">
         <v>2830</v>
       </c>
       <c r="F4" s="8" t="s">
@@ -913,13 +967,13 @@
       <c r="B5" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="11">
         <v>2510</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="11">
         <v>2670</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="11">
         <v>2830</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -942,13 +996,13 @@
       <c r="B6" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="11">
         <v>2510</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="11">
         <v>2670</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="11">
         <v>2830</v>
       </c>
       <c r="F6" s="8" t="s">
@@ -971,13 +1025,13 @@
       <c r="B7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="11">
         <v>2510</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="11">
         <v>2670</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="11">
         <v>2830</v>
       </c>
       <c r="F7" s="8" t="s">
@@ -1000,13 +1054,13 @@
       <c r="B8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="11">
         <v>2510</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="11">
         <v>2670</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="11">
         <v>2830</v>
       </c>
       <c r="F8" s="8" t="s">
@@ -1029,13 +1083,13 @@
       <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="11">
         <v>2720</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="11">
         <v>2780</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="11">
         <v>3040</v>
       </c>
       <c r="F9" s="8" t="s">
@@ -1058,13 +1112,13 @@
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="8">
+      <c r="C10" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="11">
         <v>2780</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="11">
         <v>3040</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -1087,13 +1141,13 @@
       <c r="B11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="11">
         <v>2720</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="11">
         <v>2720</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="11">
         <v>2930</v>
       </c>
       <c r="F11" s="8" t="s">
@@ -1116,13 +1170,13 @@
       <c r="B12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12" s="11">
         <v>2720</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="11">
         <v>2720</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="11">
         <v>2930</v>
       </c>
       <c r="F12" s="8" t="s">
@@ -1145,13 +1199,13 @@
       <c r="B13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="11">
         <v>2720</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="11">
         <v>2720</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="11">
         <v>2930</v>
       </c>
       <c r="F13" s="8" t="s">
@@ -1174,13 +1228,13 @@
       <c r="B14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="11">
         <v>2720</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="11">
         <v>2720</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="11">
         <v>2930</v>
       </c>
       <c r="F14" s="8" t="s">
@@ -1203,13 +1257,13 @@
       <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="11">
         <v>2720</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="11">
         <v>2720</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="11">
         <v>2930</v>
       </c>
       <c r="F15" s="8" t="s">
@@ -1232,13 +1286,13 @@
       <c r="B16" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="11">
         <v>2720</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="11">
         <v>2720</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="11">
         <v>2930</v>
       </c>
       <c r="F16" s="8" t="s">
@@ -1261,13 +1315,13 @@
       <c r="B17" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="11">
         <v>2720</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="11">
         <v>2720</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="11">
         <v>2930</v>
       </c>
       <c r="F17" s="8" t="s">
@@ -1290,13 +1344,13 @@
       <c r="B18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="11">
         <v>2720</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="11">
         <v>2720</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="11">
         <v>2930</v>
       </c>
       <c r="F18" s="8" t="s">
@@ -1319,13 +1373,13 @@
       <c r="B19" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="11">
         <v>2720</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="11">
         <v>2720</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="11">
         <v>2930</v>
       </c>
       <c r="F19" s="8" t="s">
@@ -1348,13 +1402,13 @@
       <c r="B20" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="8">
+      <c r="C20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="11">
         <v>2780</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="11">
         <v>3040</v>
       </c>
       <c r="F20" s="8" t="s">
@@ -1377,13 +1431,13 @@
       <c r="B21" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="8">
+      <c r="C21" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="11">
         <v>2780</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="11">
         <v>3040</v>
       </c>
       <c r="F21" s="8" t="s">
@@ -1406,13 +1460,13 @@
       <c r="B22" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8">
+      <c r="C22" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="11">
         <v>2780</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="11">
         <v>3040</v>
       </c>
       <c r="F22" s="8" t="s">
@@ -1435,13 +1489,13 @@
       <c r="B23" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8">
+      <c r="C23" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="11">
         <v>2780</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="11">
         <v>2990</v>
       </c>
       <c r="F23" s="8" t="s">
@@ -1464,13 +1518,13 @@
       <c r="B24" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="8">
+      <c r="C24" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="11">
         <v>2930</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="11">
         <v>3300</v>
       </c>
       <c r="F24" s="8" t="s">
@@ -1493,13 +1547,13 @@
       <c r="B25" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="8">
+      <c r="C25" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="11">
         <v>2880</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="11">
         <v>3140</v>
       </c>
       <c r="F25" s="8" t="s">
@@ -1522,13 +1576,13 @@
       <c r="B26" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="8">
+      <c r="C26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="11">
         <v>2990</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="11">
         <v>3350</v>
       </c>
       <c r="F26" s="8" t="s">
@@ -1551,13 +1605,13 @@
       <c r="B27" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D27" s="8">
+      <c r="C27" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="11">
         <v>2990</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="11">
         <v>3350</v>
       </c>
       <c r="F27" s="8" t="s">
@@ -1580,13 +1634,13 @@
       <c r="B28" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="8">
+      <c r="C28" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="11">
         <v>2830</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="11">
         <v>3040</v>
       </c>
       <c r="F28" s="8" t="s">
@@ -1609,13 +1663,13 @@
       <c r="B29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="8">
+      <c r="C29" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D29" s="11">
         <v>2880</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="11">
         <v>3140</v>
       </c>
       <c r="F29" s="8" t="s">
@@ -1638,13 +1692,13 @@
       <c r="B30" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D30" s="8">
+      <c r="C30" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" s="11">
         <v>2880</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="11">
         <v>3140</v>
       </c>
       <c r="F30" s="8" t="s">
@@ -1667,13 +1721,13 @@
       <c r="B31" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C31" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D31" s="8">
+      <c r="C31" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="11">
         <v>2880</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="11">
         <v>3140</v>
       </c>
       <c r="F31" s="8" t="s">
@@ -1696,13 +1750,13 @@
       <c r="B32" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C32" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D32" s="8">
+      <c r="C32" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="11">
         <v>2880</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="11">
         <v>3140</v>
       </c>
       <c r="F32" s="8" t="s">
@@ -1725,13 +1779,13 @@
       <c r="B33" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C33" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D33" s="8">
+      <c r="C33" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="11">
         <v>2880</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="11">
         <v>3140</v>
       </c>
       <c r="F33" s="8" t="s">
@@ -1754,13 +1808,13 @@
       <c r="B34" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C34" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D34" s="8">
+      <c r="C34" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="11">
         <v>2880</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="11">
         <v>3140</v>
       </c>
       <c r="F34" s="8" t="s">
@@ -1783,13 +1837,13 @@
       <c r="B35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C35" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D35" s="8">
+      <c r="C35" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="11">
         <v>2880</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="11">
         <v>3140</v>
       </c>
       <c r="F35" s="8" t="s">
@@ -1812,13 +1866,13 @@
       <c r="B36" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D36" s="8">
+      <c r="C36" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="11">
         <v>2880</v>
       </c>
-      <c r="E36" s="8">
+      <c r="E36" s="11">
         <v>3140</v>
       </c>
       <c r="F36" s="8" t="s">
@@ -1841,13 +1895,13 @@
       <c r="B37" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="8">
+      <c r="C37" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="11">
         <v>2880</v>
       </c>
-      <c r="E37" s="8">
+      <c r="E37" s="11">
         <v>3140</v>
       </c>
       <c r="F37" s="8" t="s">
@@ -1870,13 +1924,13 @@
       <c r="B38" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C38" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="8">
+      <c r="C38" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="11">
         <v>2930</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="11">
         <v>3300</v>
       </c>
       <c r="F38" s="8" t="s">
@@ -1899,13 +1953,13 @@
       <c r="B39" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C39" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D39" s="8">
+      <c r="C39" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="11">
         <v>2990</v>
       </c>
-      <c r="E39" s="8">
+      <c r="E39" s="11">
         <v>3350</v>
       </c>
       <c r="F39" s="8" t="s">
@@ -1928,13 +1982,13 @@
       <c r="B40" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D40" s="8">
+      <c r="C40" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="11">
         <v>3040</v>
       </c>
-      <c r="E40" s="8">
+      <c r="E40" s="11">
         <v>3460</v>
       </c>
       <c r="F40" s="8" t="s">
@@ -1957,13 +2011,13 @@
       <c r="B41" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C41" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D41" s="8">
+      <c r="C41" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="11">
         <v>3040</v>
       </c>
-      <c r="E41" s="8">
+      <c r="E41" s="11">
         <v>3460</v>
       </c>
       <c r="F41" s="8" t="s">
@@ -1986,13 +2040,13 @@
       <c r="B42" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D42" s="8">
+      <c r="C42" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="11">
         <v>3200</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="11">
         <v>3670</v>
       </c>
       <c r="F42" s="8" t="s">
@@ -2015,13 +2069,13 @@
       <c r="B43" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D43" s="8">
+      <c r="C43" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="11">
         <v>2630</v>
       </c>
-      <c r="E43" s="8">
+      <c r="E43" s="11">
         <v>2840</v>
       </c>
       <c r="F43" s="8" t="s">
@@ -2044,13 +2098,13 @@
       <c r="B44" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C44" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D44" s="8">
+      <c r="C44" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="11">
         <v>2630</v>
       </c>
-      <c r="E44" s="8">
+      <c r="E44" s="11">
         <v>2840</v>
       </c>
       <c r="F44" s="8" t="s">
@@ -2073,13 +2127,13 @@
       <c r="B45" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C45" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D45" s="8">
+      <c r="C45" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="11">
         <v>2630</v>
       </c>
-      <c r="E45" s="8">
+      <c r="E45" s="11">
         <v>2840</v>
       </c>
       <c r="F45" s="8" t="s">
@@ -2102,13 +2156,13 @@
       <c r="B46" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D46" s="8">
+      <c r="C46" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="11">
         <v>2630</v>
       </c>
-      <c r="E46" s="8">
+      <c r="E46" s="11">
         <v>2840</v>
       </c>
       <c r="F46" s="8" t="s">
@@ -2131,13 +2185,13 @@
       <c r="B47" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C47" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D47" s="8">
+      <c r="C47" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D47" s="11">
         <v>2630</v>
       </c>
-      <c r="E47" s="8">
+      <c r="E47" s="11">
         <v>2840</v>
       </c>
       <c r="F47" s="8" t="s">
@@ -2160,13 +2214,13 @@
       <c r="B48" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D48" s="8">
+      <c r="C48" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="11">
         <v>2630</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="11">
         <v>2840</v>
       </c>
       <c r="F48" s="8" t="s">
@@ -2189,13 +2243,13 @@
       <c r="B49" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C49" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D49" s="8">
+      <c r="C49" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D49" s="11">
         <v>2630</v>
       </c>
-      <c r="E49" s="8">
+      <c r="E49" s="11">
         <v>2840</v>
       </c>
       <c r="F49" s="8" t="s">
@@ -2218,13 +2272,13 @@
       <c r="B50" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D50" s="8">
+      <c r="C50" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" s="11">
         <v>2630</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="11">
         <v>2840</v>
       </c>
       <c r="F50" s="8" t="s">
@@ -2247,13 +2301,13 @@
       <c r="B51" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D51" s="8">
+      <c r="C51" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" s="11">
         <v>2630</v>
       </c>
-      <c r="E51" s="8">
+      <c r="E51" s="11">
         <v>2840</v>
       </c>
       <c r="F51" s="8" t="s">
@@ -2276,13 +2330,13 @@
       <c r="B52" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C52" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D52" s="8">
+      <c r="C52" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" s="11">
         <v>2710</v>
       </c>
-      <c r="E52" s="8">
+      <c r="E52" s="11">
         <v>3000</v>
       </c>
       <c r="F52" s="8" t="s">
@@ -2305,13 +2359,13 @@
       <c r="B53" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C53" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D53" s="8">
+      <c r="C53" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D53" s="11">
         <v>2680</v>
       </c>
-      <c r="E53" s="8">
+      <c r="E53" s="11">
         <v>2950</v>
       </c>
       <c r="F53" s="8" t="s">
@@ -2334,13 +2388,13 @@
       <c r="B54" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C54" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D54" s="8">
+      <c r="C54" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" s="11">
         <v>2680</v>
       </c>
-      <c r="E54" s="8">
+      <c r="E54" s="11">
         <v>2950</v>
       </c>
       <c r="F54" s="8" t="s">
@@ -2363,13 +2417,13 @@
       <c r="B55" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C55" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" s="8">
+      <c r="C55" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D55" s="11">
         <v>2680</v>
       </c>
-      <c r="E55" s="8">
+      <c r="E55" s="11">
         <v>2950</v>
       </c>
       <c r="F55" s="8" t="s">
@@ -2392,13 +2446,13 @@
       <c r="B56" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C56" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" s="8">
+      <c r="C56" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D56" s="11">
         <v>2680</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="11">
         <v>2950</v>
       </c>
       <c r="F56" s="8" t="s">
@@ -2421,13 +2475,13 @@
       <c r="B57" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C57" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D57" s="8">
+      <c r="C57" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D57" s="11">
         <v>2680</v>
       </c>
-      <c r="E57" s="8">
+      <c r="E57" s="11">
         <v>2950</v>
       </c>
       <c r="F57" s="8" t="s">
@@ -2450,13 +2504,13 @@
       <c r="B58" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58" s="8">
+      <c r="C58" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" s="11">
         <v>2680</v>
       </c>
-      <c r="E58" s="8">
+      <c r="E58" s="11">
         <v>2950</v>
       </c>
       <c r="F58" s="8" t="s">
@@ -2479,13 +2533,13 @@
       <c r="B59" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" s="8">
+      <c r="C59" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59" s="11">
         <v>2680</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="11">
         <v>2950</v>
       </c>
       <c r="F59" s="8" t="s">
@@ -2508,13 +2562,13 @@
       <c r="B60" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D60" s="8">
+      <c r="C60" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" s="11">
         <v>2680</v>
       </c>
-      <c r="E60" s="8">
+      <c r="E60" s="11">
         <v>2950</v>
       </c>
       <c r="F60" s="8" t="s">
@@ -2537,13 +2591,13 @@
       <c r="B61" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D61" s="8">
+      <c r="C61" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D61" s="11">
         <v>2880</v>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="11">
         <v>3250</v>
       </c>
       <c r="F61" s="8" t="s">
@@ -2566,13 +2620,13 @@
       <c r="B62" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D62" s="8">
+      <c r="C62" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" s="11">
         <v>2680</v>
       </c>
-      <c r="E62" s="8">
+      <c r="E62" s="11">
         <v>2950</v>
       </c>
       <c r="F62" s="8" t="s">
@@ -2595,13 +2649,13 @@
       <c r="B63" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D63" s="8">
+      <c r="C63" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" s="11">
         <v>2740</v>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="11">
         <v>3000</v>
       </c>
       <c r="F63" s="8" t="s">
@@ -2624,13 +2678,13 @@
       <c r="B64" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D64" s="8">
+      <c r="C64" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" s="11">
         <v>2850</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="11">
         <v>3160</v>
       </c>
       <c r="F64" s="8" t="s">
@@ -2653,13 +2707,13 @@
       <c r="B65" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D65" s="8">
+      <c r="C65" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D65" s="11">
         <v>2790</v>
       </c>
-      <c r="E65" s="8">
+      <c r="E65" s="11">
         <v>3160</v>
       </c>
       <c r="F65" s="8" t="s">
@@ -2682,13 +2736,13 @@
       <c r="B66" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D66" s="8">
+      <c r="C66" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D66" s="11">
         <v>2850</v>
       </c>
-      <c r="E66" s="8">
+      <c r="E66" s="11">
         <v>3190</v>
       </c>
       <c r="F66" s="8" t="s">
@@ -2711,13 +2765,13 @@
       <c r="B67" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D67" s="8">
+      <c r="C67" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="11">
         <v>2890</v>
       </c>
-      <c r="E67" s="8">
+      <c r="E67" s="11">
         <v>3290</v>
       </c>
       <c r="F67" s="8" t="s">
@@ -2740,13 +2794,13 @@
       <c r="B68" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C68" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D68" s="8">
+      <c r="C68" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" s="11">
         <v>2890</v>
       </c>
-      <c r="E68" s="8">
+      <c r="E68" s="11">
         <v>3290</v>
       </c>
       <c r="F68" s="8" t="s">
@@ -2769,13 +2823,13 @@
       <c r="B69" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D69" s="8">
+      <c r="C69" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D69" s="11">
         <v>2820</v>
       </c>
-      <c r="E69" s="8">
+      <c r="E69" s="11">
         <v>3160</v>
       </c>
       <c r="F69" s="8" t="s">
@@ -2798,13 +2852,13 @@
       <c r="B70" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C70" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D70" s="8">
+      <c r="C70" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" s="11">
         <v>2840</v>
       </c>
-      <c r="E70" s="8">
+      <c r="E70" s="11">
         <v>3180</v>
       </c>
       <c r="F70" s="8" t="s">
@@ -2827,13 +2881,13 @@
       <c r="B71" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D71" s="8">
+      <c r="C71" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="11">
         <v>2760</v>
       </c>
-      <c r="E71" s="8">
+      <c r="E71" s="11">
         <v>3060</v>
       </c>
       <c r="F71" s="8" t="s">
@@ -2856,13 +2910,13 @@
       <c r="B72" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D72" s="8">
+      <c r="C72" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="11">
         <v>2760</v>
       </c>
-      <c r="E72" s="8">
+      <c r="E72" s="11">
         <v>3060</v>
       </c>
       <c r="F72" s="8" t="s">
@@ -2885,13 +2939,13 @@
       <c r="B73" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D73" s="8">
+      <c r="C73" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D73" s="11">
         <v>2760</v>
       </c>
-      <c r="E73" s="8">
+      <c r="E73" s="11">
         <v>3060</v>
       </c>
       <c r="F73" s="8" t="s">
@@ -2914,13 +2968,13 @@
       <c r="B74" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D74" s="8">
+      <c r="C74" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D74" s="11">
         <v>2760</v>
       </c>
-      <c r="E74" s="8">
+      <c r="E74" s="11">
         <v>3060</v>
       </c>
       <c r="F74" s="8" t="s">
@@ -2943,13 +2997,13 @@
       <c r="B75" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D75" s="8">
+      <c r="C75" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D75" s="11">
         <v>2760</v>
       </c>
-      <c r="E75" s="8">
+      <c r="E75" s="11">
         <v>3060</v>
       </c>
       <c r="F75" s="8" t="s">
@@ -2972,13 +3026,13 @@
       <c r="B76" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D76" s="8">
+      <c r="C76" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" s="11">
         <v>2760</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="11">
         <v>3060</v>
       </c>
       <c r="F76" s="8" t="s">
@@ -3001,13 +3055,13 @@
       <c r="B77" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D77" s="8">
+      <c r="C77" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D77" s="11">
         <v>2760</v>
       </c>
-      <c r="E77" s="8">
+      <c r="E77" s="11">
         <v>3060</v>
       </c>
       <c r="F77" s="8" t="s">
@@ -3030,13 +3084,13 @@
       <c r="B78" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D78" s="8">
+      <c r="C78" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" s="11">
         <v>2760</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="11">
         <v>3060</v>
       </c>
       <c r="F78" s="8" t="s">
@@ -3059,13 +3113,13 @@
       <c r="B79" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C79" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D79" s="8">
+      <c r="C79" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D79" s="11">
         <v>2880</v>
       </c>
-      <c r="E79" s="8">
+      <c r="E79" s="11">
         <v>3280</v>
       </c>
       <c r="F79" s="8" t="s">
@@ -3088,13 +3142,13 @@
       <c r="B80" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C80" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" s="8">
+      <c r="C80" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" s="11">
         <v>2870</v>
       </c>
-      <c r="E80" s="8">
+      <c r="E80" s="11">
         <v>3250</v>
       </c>
       <c r="F80" s="8" t="s">
@@ -3117,13 +3171,13 @@
       <c r="B81" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C81" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D81" s="8">
+      <c r="C81" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D81" s="11">
         <v>2870</v>
       </c>
-      <c r="E81" s="8">
+      <c r="E81" s="11">
         <v>3310</v>
       </c>
       <c r="F81" s="8" t="s">
@@ -3146,13 +3200,13 @@
       <c r="B82" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C82" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D82" s="8">
+      <c r="C82" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="11">
         <v>2870</v>
       </c>
-      <c r="E82" s="8">
+      <c r="E82" s="11">
         <v>3310</v>
       </c>
       <c r="F82" s="8" t="s">
@@ -3175,13 +3229,13 @@
       <c r="B83" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C83" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D83" s="8">
+      <c r="C83" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="11">
         <v>3060</v>
       </c>
-      <c r="E83" s="8">
+      <c r="E83" s="11">
         <v>3670</v>
       </c>
       <c r="F83" s="8" t="s">
@@ -3204,13 +3258,13 @@
       <c r="B84" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C84" s="8">
+      <c r="C84" s="11">
         <v>2720</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="11">
         <v>3200</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="11">
         <v>3350</v>
       </c>
       <c r="F84" s="8" t="s">
@@ -3233,13 +3287,13 @@
       <c r="B85" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C85" s="8">
+      <c r="C85" s="11">
         <v>2720</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="11">
         <v>3200</v>
       </c>
-      <c r="E85" s="8">
+      <c r="E85" s="11">
         <v>3350</v>
       </c>
       <c r="F85" s="8" t="s">
@@ -3262,13 +3316,13 @@
       <c r="B86" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C86" s="8">
+      <c r="C86" s="11">
         <v>2720</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="11">
         <v>3200</v>
       </c>
-      <c r="E86" s="8">
+      <c r="E86" s="11">
         <v>3350</v>
       </c>
       <c r="F86" s="8" t="s">
@@ -3291,13 +3345,13 @@
       <c r="B87" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="8">
+      <c r="C87" s="11">
         <v>2720</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="11">
         <v>3200</v>
       </c>
-      <c r="E87" s="8">
+      <c r="E87" s="11">
         <v>3350</v>
       </c>
       <c r="F87" s="8" t="s">
@@ -3320,13 +3374,13 @@
       <c r="B88" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C88" s="8">
+      <c r="C88" s="11">
         <v>2720</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="11">
         <v>3200</v>
       </c>
-      <c r="E88" s="8">
+      <c r="E88" s="11">
         <v>3350</v>
       </c>
       <c r="F88" s="8" t="s">
@@ -3349,13 +3403,13 @@
       <c r="B89" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C89" s="8">
+      <c r="C89" s="11">
         <v>2720</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="11">
         <v>3200</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="11">
         <v>3350</v>
       </c>
       <c r="F89" s="8" t="s">
@@ -3378,13 +3432,13 @@
       <c r="B90" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C90" s="8">
+      <c r="C90" s="11">
         <v>2720</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="11">
         <v>3200</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="11">
         <v>3350</v>
       </c>
       <c r="F90" s="8" t="s">
@@ -3407,13 +3461,13 @@
       <c r="B91" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C91" s="8">
+      <c r="C91" s="11">
         <v>2930</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="11">
         <v>3300</v>
       </c>
-      <c r="E91" s="8">
+      <c r="E91" s="11">
         <v>3560</v>
       </c>
       <c r="F91" s="8" t="s">
@@ -3436,13 +3490,13 @@
       <c r="B92" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D92" s="8">
+      <c r="C92" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D92" s="11">
         <v>3300</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="11">
         <v>3560</v>
       </c>
       <c r="F92" s="8" t="s">
@@ -3465,13 +3519,13 @@
       <c r="B93" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C93" s="8">
+      <c r="C93" s="11">
         <v>2930</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="11">
         <v>3250</v>
       </c>
-      <c r="E93" s="8">
+      <c r="E93" s="11">
         <v>3460</v>
       </c>
       <c r="F93" s="8" t="s">
@@ -3494,13 +3548,13 @@
       <c r="B94" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C94" s="8">
+      <c r="C94" s="11">
         <v>2930</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="11">
         <v>3250</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E94" s="11">
         <v>3460</v>
       </c>
       <c r="F94" s="8" t="s">
@@ -3523,13 +3577,13 @@
       <c r="B95" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C95" s="8">
+      <c r="C95" s="11">
         <v>2930</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="11">
         <v>3250</v>
       </c>
-      <c r="E95" s="8">
+      <c r="E95" s="11">
         <v>3460</v>
       </c>
       <c r="F95" s="8" t="s">
@@ -3552,13 +3606,13 @@
       <c r="B96" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C96" s="8">
+      <c r="C96" s="11">
         <v>2930</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="11">
         <v>3250</v>
       </c>
-      <c r="E96" s="8">
+      <c r="E96" s="11">
         <v>3460</v>
       </c>
       <c r="F96" s="8" t="s">
@@ -3581,13 +3635,13 @@
       <c r="B97" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C97" s="8">
+      <c r="C97" s="11">
         <v>2930</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="11">
         <v>3250</v>
       </c>
-      <c r="E97" s="8">
+      <c r="E97" s="11">
         <v>3460</v>
       </c>
       <c r="F97" s="8" t="s">
@@ -3610,13 +3664,13 @@
       <c r="B98" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C98" s="8">
+      <c r="C98" s="11">
         <v>2930</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="11">
         <v>3250</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="11">
         <v>3460</v>
       </c>
       <c r="F98" s="8" t="s">
@@ -3639,13 +3693,13 @@
       <c r="B99" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C99" s="8">
+      <c r="C99" s="11">
         <v>2930</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="11">
         <v>3250</v>
       </c>
-      <c r="E99" s="8">
+      <c r="E99" s="11">
         <v>3460</v>
       </c>
       <c r="F99" s="8" t="s">
@@ -3668,13 +3722,13 @@
       <c r="B100" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C100" s="8">
+      <c r="C100" s="11">
         <v>2930</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="11">
         <v>3250</v>
       </c>
-      <c r="E100" s="8">
+      <c r="E100" s="11">
         <v>3460</v>
       </c>
       <c r="F100" s="8" t="s">
@@ -3697,13 +3751,13 @@
       <c r="B101" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C101" s="8">
+      <c r="C101" s="11">
         <v>2930</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="11">
         <v>3250</v>
       </c>
-      <c r="E101" s="8">
+      <c r="E101" s="11">
         <v>3460</v>
       </c>
       <c r="F101" s="8" t="s">
@@ -3726,13 +3780,13 @@
       <c r="B102" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C102" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D102" s="8">
+      <c r="C102" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D102" s="11">
         <v>3300</v>
       </c>
-      <c r="E102" s="8">
+      <c r="E102" s="11">
         <v>3560</v>
       </c>
       <c r="F102" s="8" t="s">
@@ -3755,13 +3809,13 @@
       <c r="B103" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C103" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D103" s="8">
+      <c r="C103" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D103" s="11">
         <v>3300</v>
       </c>
-      <c r="E103" s="8">
+      <c r="E103" s="11">
         <v>3560</v>
       </c>
       <c r="F103" s="8" t="s">
@@ -3784,13 +3838,13 @@
       <c r="B104" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C104" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D104" s="8">
+      <c r="C104" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D104" s="11">
         <v>3300</v>
       </c>
-      <c r="E104" s="8">
+      <c r="E104" s="11">
         <v>3560</v>
       </c>
       <c r="F104" s="8" t="s">
@@ -3813,13 +3867,13 @@
       <c r="B105" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C105" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D105" s="8">
+      <c r="C105" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D105" s="11">
         <v>3300</v>
       </c>
-      <c r="E105" s="8">
+      <c r="E105" s="11">
         <v>3510</v>
       </c>
       <c r="F105" s="8" t="s">
@@ -3842,13 +3896,13 @@
       <c r="B106" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C106" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D106" s="8">
+      <c r="C106" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D106" s="11">
         <v>3460</v>
       </c>
-      <c r="E106" s="8">
+      <c r="E106" s="11">
         <v>3830</v>
       </c>
       <c r="F106" s="8" t="s">
@@ -3871,13 +3925,13 @@
       <c r="B107" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C107" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D107" s="8">
+      <c r="C107" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D107" s="11">
         <v>3410</v>
       </c>
-      <c r="E107" s="8">
+      <c r="E107" s="11">
         <v>3670</v>
       </c>
       <c r="F107" s="8" t="s">
@@ -3900,13 +3954,13 @@
       <c r="B108" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C108" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D108" s="8">
+      <c r="C108" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D108" s="11">
         <v>3510</v>
       </c>
-      <c r="E108" s="8">
+      <c r="E108" s="11">
         <v>3880</v>
       </c>
       <c r="F108" s="8" t="s">
@@ -3929,13 +3983,13 @@
       <c r="B109" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C109" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D109" s="8">
+      <c r="C109" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D109" s="11">
         <v>3510</v>
       </c>
-      <c r="E109" s="8">
+      <c r="E109" s="11">
         <v>3880</v>
       </c>
       <c r="F109" s="8" t="s">
@@ -3958,13 +4012,13 @@
       <c r="B110" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C110" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D110" s="8">
+      <c r="C110" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D110" s="11">
         <v>3350</v>
       </c>
-      <c r="E110" s="8">
+      <c r="E110" s="11">
         <v>3560</v>
       </c>
       <c r="F110" s="8" t="s">
@@ -3987,13 +4041,13 @@
       <c r="B111" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C111" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D111" s="8">
+      <c r="C111" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D111" s="11">
         <v>3410</v>
       </c>
-      <c r="E111" s="8">
+      <c r="E111" s="11">
         <v>3670</v>
       </c>
       <c r="F111" s="8" t="s">
@@ -4016,13 +4070,13 @@
       <c r="B112" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C112" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D112" s="8">
+      <c r="C112" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D112" s="11">
         <v>3410</v>
       </c>
-      <c r="E112" s="8">
+      <c r="E112" s="11">
         <v>3670</v>
       </c>
       <c r="F112" s="8" t="s">
@@ -4045,13 +4099,13 @@
       <c r="B113" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C113" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D113" s="8">
+      <c r="C113" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D113" s="11">
         <v>3410</v>
       </c>
-      <c r="E113" s="8">
+      <c r="E113" s="11">
         <v>3670</v>
       </c>
       <c r="F113" s="8" t="s">
@@ -4074,13 +4128,13 @@
       <c r="B114" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C114" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D114" s="8">
+      <c r="C114" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="11">
         <v>3410</v>
       </c>
-      <c r="E114" s="8">
+      <c r="E114" s="11">
         <v>3670</v>
       </c>
       <c r="F114" s="8" t="s">
@@ -4103,13 +4157,13 @@
       <c r="B115" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C115" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D115" s="8">
+      <c r="C115" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D115" s="11">
         <v>3410</v>
       </c>
-      <c r="E115" s="8">
+      <c r="E115" s="11">
         <v>3670</v>
       </c>
       <c r="F115" s="8" t="s">
@@ -4132,13 +4186,13 @@
       <c r="B116" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C116" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D116" s="8">
+      <c r="C116" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D116" s="11">
         <v>3410</v>
       </c>
-      <c r="E116" s="8">
+      <c r="E116" s="11">
         <v>3670</v>
       </c>
       <c r="F116" s="8" t="s">
@@ -4161,13 +4215,13 @@
       <c r="B117" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C117" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D117" s="8">
+      <c r="C117" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D117" s="11">
         <v>3410</v>
       </c>
-      <c r="E117" s="8">
+      <c r="E117" s="11">
         <v>3670</v>
       </c>
       <c r="F117" s="8" t="s">
@@ -4190,13 +4244,13 @@
       <c r="B118" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C118" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D118" s="8">
+      <c r="C118" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D118" s="11">
         <v>3410</v>
       </c>
-      <c r="E118" s="8">
+      <c r="E118" s="11">
         <v>3670</v>
       </c>
       <c r="F118" s="8" t="s">
@@ -4219,13 +4273,13 @@
       <c r="B119" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C119" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D119" s="8">
+      <c r="C119" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D119" s="11">
         <v>3410</v>
       </c>
-      <c r="E119" s="8">
+      <c r="E119" s="11">
         <v>3670</v>
       </c>
       <c r="F119" s="8" t="s">
@@ -4248,13 +4302,13 @@
       <c r="B120" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C120" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D120" s="8">
+      <c r="C120" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D120" s="11">
         <v>3460</v>
       </c>
-      <c r="E120" s="8">
+      <c r="E120" s="11">
         <v>3830</v>
       </c>
       <c r="F120" s="8" t="s">
@@ -4277,13 +4331,13 @@
       <c r="B121" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C121" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D121" s="8">
+      <c r="C121" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D121" s="11">
         <v>3510</v>
       </c>
-      <c r="E121" s="8">
+      <c r="E121" s="11">
         <v>3880</v>
       </c>
       <c r="F121" s="8" t="s">
@@ -4306,13 +4360,13 @@
       <c r="B122" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C122" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D122" s="8">
+      <c r="C122" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D122" s="11">
         <v>3560</v>
       </c>
-      <c r="E122" s="8">
+      <c r="E122" s="11">
         <v>3980</v>
       </c>
       <c r="F122" s="8" t="s">
@@ -4335,13 +4389,13 @@
       <c r="B123" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C123" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D123" s="8">
+      <c r="C123" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D123" s="11">
         <v>3560</v>
       </c>
-      <c r="E123" s="8">
+      <c r="E123" s="11">
         <v>3980</v>
       </c>
       <c r="F123" s="8" t="s">
@@ -4364,13 +4418,13 @@
       <c r="B124" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C124" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D124" s="8">
+      <c r="C124" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D124" s="11">
         <v>3720</v>
       </c>
-      <c r="E124" s="8">
+      <c r="E124" s="11">
         <v>4190</v>
       </c>
       <c r="F124" s="8" t="s">
@@ -4393,13 +4447,13 @@
       <c r="B125" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C125" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D125" s="8">
+      <c r="C125" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D125" s="11">
         <v>3350</v>
       </c>
-      <c r="E125" s="8">
+      <c r="E125" s="11">
         <v>3510</v>
       </c>
       <c r="F125" s="8" t="s">
@@ -4422,13 +4476,13 @@
       <c r="B126" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C126" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D126" s="8">
+      <c r="C126" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D126" s="11">
         <v>3350</v>
       </c>
-      <c r="E126" s="8">
+      <c r="E126" s="11">
         <v>3510</v>
       </c>
       <c r="F126" s="8" t="s">
@@ -4451,13 +4505,13 @@
       <c r="B127" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C127" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D127" s="8">
+      <c r="C127" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D127" s="11">
         <v>3350</v>
       </c>
-      <c r="E127" s="8">
+      <c r="E127" s="11">
         <v>3510</v>
       </c>
       <c r="F127" s="8" t="s">
@@ -4480,13 +4534,13 @@
       <c r="B128" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C128" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D128" s="8">
+      <c r="C128" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D128" s="11">
         <v>3350</v>
       </c>
-      <c r="E128" s="8">
+      <c r="E128" s="11">
         <v>3510</v>
       </c>
       <c r="F128" s="8" t="s">
@@ -4509,13 +4563,13 @@
       <c r="B129" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C129" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D129" s="8">
+      <c r="C129" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D129" s="11">
         <v>3350</v>
       </c>
-      <c r="E129" s="8">
+      <c r="E129" s="11">
         <v>3510</v>
       </c>
       <c r="F129" s="8" t="s">
@@ -4538,13 +4592,13 @@
       <c r="B130" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C130" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D130" s="8">
+      <c r="C130" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D130" s="11">
         <v>3160</v>
       </c>
-      <c r="E130" s="8">
+      <c r="E130" s="11">
         <v>3370</v>
       </c>
       <c r="F130" s="8" t="s">
@@ -4567,13 +4621,13 @@
       <c r="B131" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C131" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D131" s="8">
+      <c r="C131" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="11">
         <v>3160</v>
       </c>
-      <c r="E131" s="8">
+      <c r="E131" s="11">
         <v>3370</v>
       </c>
       <c r="F131" s="8" t="s">
@@ -4596,13 +4650,13 @@
       <c r="B132" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C132" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D132" s="8">
+      <c r="C132" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D132" s="11">
         <v>3160</v>
       </c>
-      <c r="E132" s="8">
+      <c r="E132" s="11">
         <v>3370</v>
       </c>
       <c r="F132" s="8" t="s">
@@ -4625,13 +4679,13 @@
       <c r="B133" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C133" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D133" s="8">
+      <c r="C133" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D133" s="11">
         <v>3160</v>
       </c>
-      <c r="E133" s="8">
+      <c r="E133" s="11">
         <v>3370</v>
       </c>
       <c r="F133" s="8" t="s">
@@ -4654,13 +4708,13 @@
       <c r="B134" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C134" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D134" s="8">
+      <c r="C134" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D134" s="11">
         <v>3160</v>
       </c>
-      <c r="E134" s="8">
+      <c r="E134" s="11">
         <v>3370</v>
       </c>
       <c r="F134" s="8" t="s">
@@ -4683,13 +4737,13 @@
       <c r="B135" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C135" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D135" s="8">
+      <c r="C135" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D135" s="11">
         <v>3160</v>
       </c>
-      <c r="E135" s="8">
+      <c r="E135" s="11">
         <v>3370</v>
       </c>
       <c r="F135" s="8" t="s">
@@ -4712,13 +4766,13 @@
       <c r="B136" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C136" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D136" s="8">
+      <c r="C136" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D136" s="11">
         <v>3160</v>
       </c>
-      <c r="E136" s="8">
+      <c r="E136" s="11">
         <v>3370</v>
       </c>
       <c r="F136" s="8" t="s">
@@ -4741,13 +4795,13 @@
       <c r="B137" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C137" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D137" s="8">
+      <c r="C137" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D137" s="11">
         <v>3160</v>
       </c>
-      <c r="E137" s="8">
+      <c r="E137" s="11">
         <v>3370</v>
       </c>
       <c r="F137" s="8" t="s">
@@ -4770,13 +4824,13 @@
       <c r="B138" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C138" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D138" s="8">
+      <c r="C138" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D138" s="11">
         <v>3160</v>
       </c>
-      <c r="E138" s="8">
+      <c r="E138" s="11">
         <v>3370</v>
       </c>
       <c r="F138" s="8" t="s">
@@ -4799,13 +4853,13 @@
       <c r="B139" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C139" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D139" s="8">
+      <c r="C139" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D139" s="11">
         <v>3230</v>
       </c>
-      <c r="E139" s="8">
+      <c r="E139" s="11">
         <v>3520</v>
       </c>
       <c r="F139" s="8" t="s">
@@ -4828,13 +4882,13 @@
       <c r="B140" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C140" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D140" s="8">
+      <c r="C140" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D140" s="11">
         <v>3210</v>
       </c>
-      <c r="E140" s="8">
+      <c r="E140" s="11">
         <v>3470</v>
       </c>
       <c r="F140" s="8" t="s">
@@ -4857,13 +4911,13 @@
       <c r="B141" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C141" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D141" s="8">
+      <c r="C141" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D141" s="11">
         <v>3210</v>
       </c>
-      <c r="E141" s="8">
+      <c r="E141" s="11">
         <v>3470</v>
       </c>
       <c r="F141" s="8" t="s">
@@ -4886,13 +4940,13 @@
       <c r="B142" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C142" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D142" s="8">
+      <c r="C142" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D142" s="11">
         <v>3210</v>
       </c>
-      <c r="E142" s="8">
+      <c r="E142" s="11">
         <v>3470</v>
       </c>
       <c r="F142" s="8" t="s">
@@ -4915,13 +4969,13 @@
       <c r="B143" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C143" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D143" s="8">
+      <c r="C143" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D143" s="11">
         <v>3210</v>
       </c>
-      <c r="E143" s="8">
+      <c r="E143" s="11">
         <v>3470</v>
       </c>
       <c r="F143" s="8" t="s">
@@ -4944,13 +4998,13 @@
       <c r="B144" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C144" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D144" s="8">
+      <c r="C144" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D144" s="11">
         <v>3210</v>
       </c>
-      <c r="E144" s="8">
+      <c r="E144" s="11">
         <v>3470</v>
       </c>
       <c r="F144" s="8" t="s">
@@ -4973,13 +5027,13 @@
       <c r="B145" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C145" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D145" s="8">
+      <c r="C145" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D145" s="11">
         <v>3210</v>
       </c>
-      <c r="E145" s="8">
+      <c r="E145" s="11">
         <v>3470</v>
       </c>
       <c r="F145" s="8" t="s">
@@ -5002,13 +5056,13 @@
       <c r="B146" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C146" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D146" s="8">
+      <c r="C146" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D146" s="11">
         <v>3210</v>
       </c>
-      <c r="E146" s="8">
+      <c r="E146" s="11">
         <v>3470</v>
       </c>
       <c r="F146" s="8" t="s">
@@ -5031,13 +5085,13 @@
       <c r="B147" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C147" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D147" s="8">
+      <c r="C147" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D147" s="11">
         <v>3210</v>
       </c>
-      <c r="E147" s="8">
+      <c r="E147" s="11">
         <v>3470</v>
       </c>
       <c r="F147" s="8" t="s">
@@ -5060,13 +5114,13 @@
       <c r="B148" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C148" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D148" s="8">
+      <c r="C148" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D148" s="11">
         <v>3410</v>
       </c>
-      <c r="E148" s="8">
+      <c r="E148" s="11">
         <v>3780</v>
       </c>
       <c r="F148" s="8" t="s">
@@ -5089,13 +5143,13 @@
       <c r="B149" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C149" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D149" s="8">
+      <c r="C149" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D149" s="11">
         <v>3210</v>
       </c>
-      <c r="E149" s="8">
+      <c r="E149" s="11">
         <v>3470</v>
       </c>
       <c r="F149" s="8" t="s">
@@ -5118,13 +5172,13 @@
       <c r="B150" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C150" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D150" s="8">
+      <c r="C150" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="11">
         <v>3260</v>
       </c>
-      <c r="E150" s="8">
+      <c r="E150" s="11">
         <v>3520</v>
       </c>
       <c r="F150" s="8" t="s">
@@ -5147,13 +5201,13 @@
       <c r="B151" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C151" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D151" s="8">
+      <c r="C151" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D151" s="11">
         <v>3380</v>
       </c>
-      <c r="E151" s="8">
+      <c r="E151" s="11">
         <v>3680</v>
       </c>
       <c r="F151" s="8" t="s">
@@ -5176,13 +5230,13 @@
       <c r="B152" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C152" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D152" s="8">
+      <c r="C152" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D152" s="11">
         <v>3310</v>
       </c>
-      <c r="E152" s="8">
+      <c r="E152" s="11">
         <v>3680</v>
       </c>
       <c r="F152" s="8" t="s">
@@ -5205,13 +5259,13 @@
       <c r="B153" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C153" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D153" s="8">
+      <c r="C153" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D153" s="11">
         <v>3380</v>
       </c>
-      <c r="E153" s="8">
+      <c r="E153" s="11">
         <v>3720</v>
       </c>
       <c r="F153" s="8" t="s">
@@ -5234,13 +5288,13 @@
       <c r="B154" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C154" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D154" s="8">
+      <c r="C154" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D154" s="11">
         <v>3410</v>
       </c>
-      <c r="E154" s="8">
+      <c r="E154" s="11">
         <v>3810</v>
       </c>
       <c r="F154" s="8" t="s">
@@ -5263,13 +5317,13 @@
       <c r="B155" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C155" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D155" s="8">
+      <c r="C155" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D155" s="11">
         <v>3410</v>
       </c>
-      <c r="E155" s="8">
+      <c r="E155" s="11">
         <v>3810</v>
       </c>
       <c r="F155" s="8" t="s">
@@ -5292,13 +5346,13 @@
       <c r="B156" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C156" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D156" s="8">
+      <c r="C156" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D156" s="11">
         <v>3350</v>
       </c>
-      <c r="E156" s="8">
+      <c r="E156" s="11">
         <v>3680</v>
       </c>
       <c r="F156" s="8" t="s">
@@ -5321,13 +5375,13 @@
       <c r="B157" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C157" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D157" s="8">
+      <c r="C157" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D157" s="11">
         <v>3370</v>
       </c>
-      <c r="E157" s="8">
+      <c r="E157" s="11">
         <v>3700</v>
       </c>
       <c r="F157" s="8" t="s">
@@ -5350,13 +5404,13 @@
       <c r="B158" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C158" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D158" s="8">
+      <c r="C158" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D158" s="11">
         <v>3280</v>
       </c>
-      <c r="E158" s="8">
+      <c r="E158" s="11">
         <v>3590</v>
       </c>
       <c r="F158" s="8" t="s">
@@ -5379,13 +5433,13 @@
       <c r="B159" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C159" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D159" s="8">
+      <c r="C159" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D159" s="11">
         <v>3280</v>
       </c>
-      <c r="E159" s="8">
+      <c r="E159" s="11">
         <v>3590</v>
       </c>
       <c r="F159" s="8" t="s">
@@ -5408,13 +5462,13 @@
       <c r="B160" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C160" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D160" s="8">
+      <c r="C160" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D160" s="11">
         <v>3280</v>
       </c>
-      <c r="E160" s="8">
+      <c r="E160" s="11">
         <v>3590</v>
       </c>
       <c r="F160" s="8" t="s">
@@ -5437,13 +5491,13 @@
       <c r="B161" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C161" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D161" s="8">
+      <c r="C161" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D161" s="11">
         <v>3280</v>
       </c>
-      <c r="E161" s="8">
+      <c r="E161" s="11">
         <v>3590</v>
       </c>
       <c r="F161" s="8" t="s">
@@ -5466,13 +5520,13 @@
       <c r="B162" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C162" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D162" s="8">
+      <c r="C162" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D162" s="11">
         <v>3280</v>
       </c>
-      <c r="E162" s="8">
+      <c r="E162" s="11">
         <v>3590</v>
       </c>
       <c r="F162" s="8" t="s">
@@ -5495,13 +5549,13 @@
       <c r="B163" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C163" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D163" s="8">
+      <c r="C163" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D163" s="11">
         <v>3280</v>
       </c>
-      <c r="E163" s="8">
+      <c r="E163" s="11">
         <v>3590</v>
       </c>
       <c r="F163" s="8" t="s">
@@ -5524,13 +5578,13 @@
       <c r="B164" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C164" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D164" s="8">
+      <c r="C164" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D164" s="11">
         <v>3280</v>
       </c>
-      <c r="E164" s="8">
+      <c r="E164" s="11">
         <v>3590</v>
       </c>
       <c r="F164" s="8" t="s">
@@ -5553,13 +5607,13 @@
       <c r="B165" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C165" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D165" s="8">
+      <c r="C165" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D165" s="11">
         <v>3280</v>
       </c>
-      <c r="E165" s="8">
+      <c r="E165" s="11">
         <v>3590</v>
       </c>
       <c r="F165" s="8" t="s">
@@ -5582,13 +5636,13 @@
       <c r="B166" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C166" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D166" s="8">
+      <c r="C166" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D166" s="11">
         <v>3400</v>
       </c>
-      <c r="E166" s="8">
+      <c r="E166" s="11">
         <v>3800</v>
       </c>
       <c r="F166" s="8" t="s">
@@ -5611,13 +5665,13 @@
       <c r="B167" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C167" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D167" s="8">
+      <c r="C167" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D167" s="11">
         <v>3400</v>
       </c>
-      <c r="E167" s="8">
+      <c r="E167" s="11">
         <v>3770</v>
       </c>
       <c r="F167" s="8" t="s">
@@ -5640,13 +5694,13 @@
       <c r="B168" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C168" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D168" s="8">
+      <c r="C168" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D168" s="11">
         <v>3400</v>
       </c>
-      <c r="E168" s="8">
+      <c r="E168" s="11">
         <v>3840</v>
       </c>
       <c r="F168" s="8" t="s">
@@ -5669,13 +5723,13 @@
       <c r="B169" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C169" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D169" s="8">
+      <c r="C169" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="11">
         <v>3400</v>
       </c>
-      <c r="E169" s="8">
+      <c r="E169" s="11">
         <v>3840</v>
       </c>
       <c r="F169" s="8" t="s">
@@ -5698,13 +5752,13 @@
       <c r="B170" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C170" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D170" s="8">
+      <c r="C170" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D170" s="11">
         <v>3590</v>
       </c>
-      <c r="E170" s="8">
+      <c r="E170" s="11">
         <v>4190</v>
       </c>
       <c r="F170" s="8" t="s">
@@ -5727,13 +5781,13 @@
       <c r="B171" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C171" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D171" s="8">
+      <c r="C171" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D171" s="11">
         <v>3260</v>
       </c>
-      <c r="E171" s="8">
+      <c r="E171" s="11">
         <v>3520</v>
       </c>
       <c r="F171" s="8" t="s">
@@ -5756,13 +5810,13 @@
       <c r="B172" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C172" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D172" s="8">
+      <c r="C172" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D172" s="11">
         <v>3370</v>
       </c>
-      <c r="E172" s="8">
+      <c r="E172" s="11">
         <v>3680</v>
       </c>
       <c r="F172" s="8" t="s">
@@ -5785,13 +5839,13 @@
       <c r="B173" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C173" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D173" s="8">
+      <c r="C173" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D173" s="11">
         <v>3370</v>
       </c>
-      <c r="E173" s="8">
+      <c r="E173" s="11">
         <v>3680</v>
       </c>
       <c r="F173" s="8" t="s">
@@ -5814,13 +5868,13 @@
       <c r="B174" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C174" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D174" s="8">
+      <c r="C174" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D174" s="11">
         <v>3420</v>
       </c>
-      <c r="E174" s="8">
+      <c r="E174" s="11">
         <v>3730</v>
       </c>
       <c r="F174" s="8" t="s">
@@ -5843,13 +5897,13 @@
       <c r="B175" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C175" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D175" s="8">
+      <c r="C175" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D175" s="11">
         <v>3420</v>
       </c>
-      <c r="E175" s="8">
+      <c r="E175" s="11">
         <v>3730</v>
       </c>
       <c r="F175" s="8" t="s">
@@ -5864,9 +5918,1192 @@
       <c r="I175" s="8" t="s">
         <v>24</v>
       </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>81</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D176" s="10">
+        <v>50</v>
+      </c>
+      <c r="E176" s="10">
+        <v>90</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G176" s="9">
+        <v>14</v>
+      </c>
+      <c r="H176" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I176" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>82</v>
+      </c>
+      <c r="B177" t="s">
+        <v>84</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D177" s="10">
+        <v>140</v>
+      </c>
+      <c r="E177" s="10">
+        <v>260</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G177" s="9">
+        <v>14</v>
+      </c>
+      <c r="H177" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I177" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>82</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D178" s="10">
+        <v>180</v>
+      </c>
+      <c r="E178" s="10">
+        <v>410</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G178" s="9">
+        <v>14</v>
+      </c>
+      <c r="H178" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I178" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>81</v>
+      </c>
+      <c r="B179" t="s">
+        <v>84</v>
+      </c>
+      <c r="C179" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D179" s="10">
+        <v>130</v>
+      </c>
+      <c r="E179" s="10">
+        <v>150</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G179" s="9">
+        <v>14</v>
+      </c>
+      <c r="H179" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I179" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>83</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D180" s="10">
+        <v>1570</v>
+      </c>
+      <c r="E180" s="10">
+        <v>2470</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G180" s="9">
+        <v>14</v>
+      </c>
+      <c r="H180" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I180" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>88</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D181" s="10">
+        <v>1570</v>
+      </c>
+      <c r="E181" s="10">
+        <v>2470</v>
+      </c>
+      <c r="F181" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G181" s="9">
+        <v>14</v>
+      </c>
+      <c r="H181" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I181" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>89</v>
+      </c>
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D182" s="10">
+        <v>1470</v>
+      </c>
+      <c r="E182" s="10">
+        <v>2780</v>
+      </c>
+      <c r="F182" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G182" s="9">
+        <v>14</v>
+      </c>
+      <c r="H182" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I182" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>90</v>
+      </c>
+      <c r="B183" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D183" s="10">
+        <v>1470</v>
+      </c>
+      <c r="E183" s="10">
+        <v>2780</v>
+      </c>
+      <c r="F183" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G183" s="9">
+        <v>14</v>
+      </c>
+      <c r="H183" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I183" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>91</v>
+      </c>
+      <c r="B184" t="s">
+        <v>84</v>
+      </c>
+      <c r="C184" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D184" s="10">
+        <v>1230</v>
+      </c>
+      <c r="E184" s="10">
+        <v>2030</v>
+      </c>
+      <c r="F184" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G184" s="9">
+        <v>14</v>
+      </c>
+      <c r="H184" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I184" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>92</v>
+      </c>
+      <c r="B185" t="s">
+        <v>84</v>
+      </c>
+      <c r="C185" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D185" s="10">
+        <v>1230</v>
+      </c>
+      <c r="E185" s="10">
+        <v>2030</v>
+      </c>
+      <c r="F185" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G185" s="9">
+        <v>14</v>
+      </c>
+      <c r="H185" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I185" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>93</v>
+      </c>
+      <c r="B186" t="s">
+        <v>84</v>
+      </c>
+      <c r="C186" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D186" s="10">
+        <v>1230</v>
+      </c>
+      <c r="E186" s="10">
+        <v>2030</v>
+      </c>
+      <c r="F186" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G186" s="9">
+        <v>14</v>
+      </c>
+      <c r="H186" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I186" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>91</v>
+      </c>
+      <c r="B187" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D187" s="10">
+        <v>1550</v>
+      </c>
+      <c r="E187" s="10">
+        <v>2490</v>
+      </c>
+      <c r="F187" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G187" s="9">
+        <v>14</v>
+      </c>
+      <c r="H187" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I187" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>95</v>
+      </c>
+      <c r="B188" t="s">
+        <v>84</v>
+      </c>
+      <c r="C188" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D188" s="10">
+        <v>1230</v>
+      </c>
+      <c r="E188" s="10">
+        <v>2030</v>
+      </c>
+      <c r="F188" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G188" s="9">
+        <v>14</v>
+      </c>
+      <c r="H188" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I188" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>94</v>
+      </c>
+      <c r="B189" t="s">
+        <v>84</v>
+      </c>
+      <c r="C189" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D189" s="10">
+        <v>1510</v>
+      </c>
+      <c r="E189" s="10">
+        <v>2350</v>
+      </c>
+      <c r="F189" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G189" s="9">
+        <v>14</v>
+      </c>
+      <c r="H189" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I189" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>93</v>
+      </c>
+      <c r="B190" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D190" s="10">
+        <v>1550</v>
+      </c>
+      <c r="E190" s="10">
+        <v>2490</v>
+      </c>
+      <c r="F190" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G190" s="9">
+        <v>14</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I190" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>94</v>
+      </c>
+      <c r="B191" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D191" s="10">
+        <v>1830</v>
+      </c>
+      <c r="E191" s="10">
+        <v>2810</v>
+      </c>
+      <c r="F191" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G191" s="9">
+        <v>14</v>
+      </c>
+      <c r="H191" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I191" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>95</v>
+      </c>
+      <c r="B192" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D192" s="10">
+        <v>1550</v>
+      </c>
+      <c r="E192" s="10">
+        <v>2490</v>
+      </c>
+      <c r="F192" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G192" s="9">
+        <v>14</v>
+      </c>
+      <c r="H192" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I192" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>92</v>
+      </c>
+      <c r="B193" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D193" s="10">
+        <v>1550</v>
+      </c>
+      <c r="E193" s="10">
+        <v>2490</v>
+      </c>
+      <c r="F193" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G193" s="9">
+        <v>14</v>
+      </c>
+      <c r="H193" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I193" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G194" s="9"/>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G195" s="9"/>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G196" s="9"/>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G197" s="9"/>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G198" s="9"/>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G199" s="9"/>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G200" s="9"/>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G201" s="9"/>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G202" s="9"/>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G203" s="9"/>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G204" s="9"/>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G205" s="9"/>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G206" s="9"/>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G207" s="9"/>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G208" s="9"/>
+    </row>
+    <row r="209" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G209" s="9"/>
+    </row>
+    <row r="210" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G210" s="9"/>
+    </row>
+    <row r="211" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G211" s="9"/>
+    </row>
+    <row r="212" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G212" s="9"/>
+    </row>
+    <row r="213" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G213" s="9"/>
+    </row>
+    <row r="214" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G214" s="9"/>
+    </row>
+    <row r="215" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G215" s="9"/>
+    </row>
+    <row r="216" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G216" s="9"/>
+    </row>
+    <row r="217" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G217" s="9"/>
+    </row>
+    <row r="218" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G218" s="9"/>
+    </row>
+    <row r="219" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G219" s="9"/>
+    </row>
+    <row r="220" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G220" s="9"/>
+    </row>
+    <row r="221" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G221" s="9"/>
+    </row>
+    <row r="222" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G222" s="9"/>
+    </row>
+    <row r="223" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G223" s="9"/>
+    </row>
+    <row r="224" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G224" s="9"/>
+    </row>
+    <row r="225" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G225" s="9"/>
+    </row>
+    <row r="226" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G226" s="9"/>
+    </row>
+    <row r="227" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G227" s="9"/>
+    </row>
+    <row r="228" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G228" s="9"/>
+    </row>
+    <row r="229" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G229" s="9"/>
+    </row>
+    <row r="230" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G230" s="9"/>
+    </row>
+    <row r="231" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G231" s="9"/>
+    </row>
+    <row r="232" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G232" s="9"/>
+    </row>
+    <row r="233" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G233" s="9"/>
+    </row>
+    <row r="234" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G234" s="9"/>
+    </row>
+    <row r="235" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G235" s="9"/>
+    </row>
+    <row r="236" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G236" s="9"/>
+    </row>
+    <row r="237" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G237" s="9"/>
+    </row>
+    <row r="238" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G238" s="9"/>
+    </row>
+    <row r="239" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G239" s="9"/>
+    </row>
+    <row r="240" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G240" s="9"/>
+    </row>
+    <row r="241" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G241" s="9"/>
+    </row>
+    <row r="242" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G242" s="9"/>
+    </row>
+    <row r="243" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G243" s="9"/>
+    </row>
+    <row r="244" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G244" s="9"/>
+    </row>
+    <row r="245" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G245" s="9"/>
+    </row>
+    <row r="246" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G246" s="9"/>
+    </row>
+    <row r="247" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G247" s="9"/>
+    </row>
+    <row r="248" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G248" s="9"/>
+    </row>
+    <row r="249" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G249" s="9"/>
+    </row>
+    <row r="250" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G250" s="9"/>
+    </row>
+    <row r="251" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G251" s="9"/>
+    </row>
+    <row r="252" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G252" s="9"/>
+    </row>
+    <row r="253" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G253" s="9"/>
+    </row>
+    <row r="254" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G254" s="9"/>
+    </row>
+    <row r="255" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G255" s="9"/>
+    </row>
+    <row r="256" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G256" s="9"/>
+    </row>
+    <row r="257" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G257" s="9"/>
+    </row>
+    <row r="258" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G258" s="9"/>
+    </row>
+    <row r="259" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G259" s="9"/>
+    </row>
+    <row r="260" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G260" s="9"/>
+    </row>
+    <row r="261" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G261" s="9"/>
+    </row>
+    <row r="262" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G262" s="9"/>
+    </row>
+    <row r="263" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G263" s="9"/>
+    </row>
+    <row r="264" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G264" s="9"/>
+    </row>
+    <row r="265" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G265" s="9"/>
+    </row>
+    <row r="266" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G266" s="9"/>
+    </row>
+    <row r="267" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G267" s="9"/>
+    </row>
+    <row r="268" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G268" s="9"/>
+    </row>
+    <row r="269" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G269" s="9"/>
+    </row>
+    <row r="270" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G270" s="9"/>
+    </row>
+    <row r="271" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G271" s="9"/>
+    </row>
+    <row r="272" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G272" s="9"/>
+    </row>
+    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G273" s="9"/>
+    </row>
+    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G274" s="9"/>
+    </row>
+    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G275" s="9"/>
+    </row>
+    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G276" s="9"/>
+    </row>
+    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G277" s="9"/>
+    </row>
+    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G278" s="9"/>
+    </row>
+    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G279" s="9"/>
+    </row>
+    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G280" s="9"/>
+    </row>
+    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G281" s="9"/>
+    </row>
+    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G282" s="9"/>
+    </row>
+    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G283" s="9"/>
+    </row>
+    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G284" s="9"/>
+    </row>
+    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G285" s="9"/>
+    </row>
+    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G286" s="9"/>
+    </row>
+    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G287" s="9"/>
+    </row>
+    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G288" s="9"/>
+    </row>
+    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G289" s="9"/>
+    </row>
+    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G290" s="9"/>
+    </row>
+    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G291" s="9"/>
+    </row>
+    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G292" s="9"/>
+    </row>
+    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G293" s="9"/>
+    </row>
+    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G294" s="9"/>
+    </row>
+    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G295" s="9"/>
+    </row>
+    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G296" s="9"/>
+    </row>
+    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G297" s="9"/>
+    </row>
+    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G298" s="9"/>
+    </row>
+    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G299" s="9"/>
+    </row>
+    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G300" s="9"/>
+    </row>
+    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G301" s="9"/>
+    </row>
+    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G302" s="9"/>
+    </row>
+    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G303" s="9"/>
+    </row>
+    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G304" s="9"/>
+    </row>
+    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G305" s="9"/>
+    </row>
+    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G306" s="9"/>
+    </row>
+    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G307" s="9"/>
+    </row>
+    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G308" s="9"/>
+    </row>
+    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G309" s="9"/>
+    </row>
+    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G310" s="9"/>
+    </row>
+    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G311" s="9"/>
+    </row>
+    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G312" s="9"/>
+    </row>
+    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G313" s="9"/>
+    </row>
+    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G314" s="9"/>
+    </row>
+    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G315" s="9"/>
+    </row>
+    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G316" s="9"/>
+    </row>
+    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G317" s="9"/>
+    </row>
+    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G318" s="9"/>
+    </row>
+    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G319" s="9"/>
+    </row>
+    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G320" s="9"/>
+    </row>
+    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G321" s="9"/>
+    </row>
+    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G322" s="9"/>
+    </row>
+    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G323" s="9"/>
+    </row>
+    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G324" s="9"/>
+    </row>
+    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G325" s="9"/>
+    </row>
+    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G326" s="9"/>
+    </row>
+    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G327" s="9"/>
+    </row>
+    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G328" s="9"/>
+    </row>
+    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G329" s="9"/>
+    </row>
+    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G330" s="9"/>
+    </row>
+    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G331" s="9"/>
+    </row>
+    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G332" s="9"/>
+    </row>
+    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G333" s="9"/>
+    </row>
+    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G334" s="9"/>
+    </row>
+    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G335" s="9"/>
+    </row>
+    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G336" s="9"/>
+    </row>
+    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G337" s="9"/>
+    </row>
+    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G338" s="9"/>
+    </row>
+    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G339" s="9"/>
+    </row>
+    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G340" s="9"/>
+    </row>
+    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G341" s="9"/>
+    </row>
+    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G342" s="9"/>
+    </row>
+    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G343" s="9"/>
+    </row>
+    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G344" s="9"/>
+    </row>
+    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G345" s="9"/>
+    </row>
+    <row r="346" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G346" s="9"/>
+    </row>
+    <row r="347" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G347" s="9"/>
+    </row>
+    <row r="348" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G348" s="9"/>
+    </row>
+    <row r="349" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G349" s="9"/>
+    </row>
+    <row r="350" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G350" s="9"/>
+    </row>
+    <row r="351" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G351" s="9"/>
+    </row>
+    <row r="352" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G352" s="9"/>
+    </row>
+    <row r="353" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G353" s="9"/>
+    </row>
+    <row r="354" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G354" s="9"/>
+    </row>
+    <row r="355" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G355" s="9"/>
+    </row>
+    <row r="356" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G356" s="9"/>
+    </row>
+    <row r="357" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G357" s="9"/>
+    </row>
+    <row r="358" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G358" s="9"/>
+    </row>
+    <row r="359" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G359" s="9"/>
+    </row>
+    <row r="360" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G360" s="9"/>
+    </row>
+    <row r="361" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G361" s="9"/>
+    </row>
+    <row r="362" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G362" s="9"/>
+    </row>
+    <row r="363" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G363" s="9"/>
+    </row>
+    <row r="364" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G364" s="9"/>
+    </row>
+    <row r="365" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G365" s="9"/>
+    </row>
+    <row r="366" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G366" s="9"/>
+    </row>
+    <row r="367" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G367" s="9"/>
+    </row>
+    <row r="368" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G368" s="9"/>
+    </row>
+    <row r="369" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G369" s="9"/>
+    </row>
+    <row r="370" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G370" s="9"/>
+    </row>
+    <row r="371" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G371" s="9"/>
+    </row>
+    <row r="372" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G372" s="9"/>
+    </row>
+    <row r="373" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G373" s="9"/>
+    </row>
+    <row r="374" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G374" s="9"/>
+    </row>
+    <row r="375" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G375" s="9"/>
+    </row>
+    <row r="376" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G376" s="9"/>
+    </row>
+    <row r="377" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G377" s="9"/>
+    </row>
+    <row r="378" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G378" s="9"/>
+    </row>
+    <row r="379" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G379" s="9"/>
+    </row>
+    <row r="380" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G380" s="9"/>
+    </row>
+    <row r="381" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G381" s="9"/>
+    </row>
+    <row r="382" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G382" s="9"/>
+    </row>
+    <row r="383" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G383" s="9"/>
+    </row>
+    <row r="384" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G384" s="9"/>
+    </row>
+    <row r="385" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G385" s="9"/>
+    </row>
+    <row r="386" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G386" s="9"/>
+    </row>
+    <row r="387" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G387" s="9"/>
+    </row>
+    <row r="388" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G388" s="9"/>
+    </row>
+    <row r="389" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G389" s="9"/>
+    </row>
+    <row r="390" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G390" s="9"/>
+    </row>
+    <row r="391" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G391" s="9"/>
+    </row>
+    <row r="392" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G392" s="9"/>
+    </row>
+    <row r="393" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G393" s="9"/>
+    </row>
+    <row r="394" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G394" s="9"/>
+    </row>
+    <row r="395" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G395" s="9"/>
+    </row>
+    <row r="396" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G396" s="9"/>
+    </row>
+    <row r="397" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G397" s="9"/>
+    </row>
+    <row r="398" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G398" s="9"/>
+    </row>
+    <row r="399" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G399" s="9"/>
+    </row>
+    <row r="400" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G400" s="9"/>
+    </row>
+    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G401" s="9"/>
+    </row>
+    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G402" s="9"/>
+    </row>
+    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G403" s="9"/>
+    </row>
+    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G404" s="9"/>
+    </row>
+    <row r="405" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G405" s="9"/>
+    </row>
+    <row r="406" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G406" s="9"/>
+    </row>
+    <row r="407" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G407" s="9"/>
+    </row>
+    <row r="408" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G408" s="9"/>
+    </row>
+    <row r="409" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G409" s="9"/>
+    </row>
+    <row r="410" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G410" s="9"/>
+    </row>
+    <row r="411" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G411" s="9"/>
+    </row>
+    <row r="412" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G412" s="9"/>
+    </row>
+    <row r="413" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G413" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73B71079-A96C-4D9B-BBD5-7D854AECB877}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4FE0E50-9D0A-4015-91E8-36F496D2CF99}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -336,12 +336,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+  <numFmts count="4">
     <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
-    <numFmt numFmtId="169" formatCode="0\ &quot;DÍAS&quot;"/>
-    <numFmt numFmtId="175" formatCode="[$EUR]\ #,##0"/>
-    <numFmt numFmtId="176" formatCode="[$USD]\ #,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0\ &quot;DÍAS&quot;"/>
+    <numFmt numFmtId="167" formatCode="[$EUR]\ #,##0"/>
+    <numFmt numFmtId="172" formatCode="[$USD]\ #,##0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -450,14 +449,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -474,11 +470,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="172" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -845,39 +845,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="11">
@@ -889,24 +889,24 @@
       <c r="E2" s="11">
         <v>2830</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="F2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="8" t="s">
+      <c r="H2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="11">
@@ -918,24 +918,24 @@
       <c r="E3" s="11">
         <v>2830</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="8" t="s">
+      <c r="H3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="11">
@@ -947,24 +947,24 @@
       <c r="E4" s="11">
         <v>2830</v>
       </c>
-      <c r="F4" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="8" t="s">
+      <c r="F4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I4" s="8" t="s">
+      <c r="H4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C5" s="11">
@@ -976,24 +976,24 @@
       <c r="E5" s="11">
         <v>2830</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C6" s="11">
@@ -1005,24 +1005,24 @@
       <c r="E6" s="11">
         <v>2830</v>
       </c>
-      <c r="F6" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="11">
@@ -1034,24 +1034,24 @@
       <c r="E7" s="11">
         <v>2830</v>
       </c>
-      <c r="F7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="8" t="s">
+      <c r="F7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I7" s="8" t="s">
+      <c r="H7" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+      <c r="A8" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="11">
@@ -1063,24 +1063,24 @@
       <c r="E8" s="11">
         <v>2830</v>
       </c>
-      <c r="F8" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="F8" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I8" s="8" t="s">
+      <c r="H8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="11">
@@ -1092,24 +1092,24 @@
       <c r="E9" s="11">
         <v>3040</v>
       </c>
-      <c r="F9" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="11" t="s">
@@ -1121,24 +1121,24 @@
       <c r="E10" s="11">
         <v>3040</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="8" t="s">
+      <c r="H10" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="11">
@@ -1150,24 +1150,24 @@
       <c r="E11" s="11">
         <v>2930</v>
       </c>
-      <c r="F11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="8" t="s">
+      <c r="H11" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C12" s="11">
@@ -1179,24 +1179,24 @@
       <c r="E12" s="11">
         <v>2930</v>
       </c>
-      <c r="F12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="8" t="s">
+      <c r="F12" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="8" t="s">
+      <c r="H12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="11">
@@ -1208,24 +1208,24 @@
       <c r="E13" s="11">
         <v>2930</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" s="8" t="s">
+      <c r="F13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="8" t="s">
+      <c r="H13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="11">
@@ -1237,24 +1237,24 @@
       <c r="E14" s="11">
         <v>2930</v>
       </c>
-      <c r="F14" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" s="8" t="s">
+      <c r="F14" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="8" t="s">
+      <c r="H14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="11">
@@ -1266,24 +1266,24 @@
       <c r="E15" s="11">
         <v>2930</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="8" t="s">
+      <c r="H15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="11">
@@ -1295,24 +1295,24 @@
       <c r="E16" s="11">
         <v>2930</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="8" t="s">
+      <c r="H16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="11">
@@ -1324,24 +1324,24 @@
       <c r="E17" s="11">
         <v>2930</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="F17" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="8" t="s">
+      <c r="H17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="11">
@@ -1353,24 +1353,24 @@
       <c r="E18" s="11">
         <v>2930</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="F18" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="8" t="s">
+      <c r="H18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="11">
@@ -1382,24 +1382,24 @@
       <c r="E19" s="11">
         <v>2930</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="8" t="s">
+      <c r="H19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="11" t="s">
@@ -1411,24 +1411,24 @@
       <c r="E20" s="11">
         <v>3040</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="8" t="s">
+      <c r="H20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="11" t="s">
@@ -1440,24 +1440,24 @@
       <c r="E21" s="11">
         <v>3040</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="8" t="s">
+      <c r="H21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="11" t="s">
@@ -1469,24 +1469,24 @@
       <c r="E22" s="11">
         <v>3040</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="F22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I22" s="8" t="s">
+      <c r="H22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -1498,24 +1498,24 @@
       <c r="E23" s="11">
         <v>2990</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="F23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I23" s="8" t="s">
+      <c r="H23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="11" t="s">
@@ -1527,24 +1527,24 @@
       <c r="E24" s="11">
         <v>3300</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="F24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H24" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="8" t="s">
+      <c r="H24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="11" t="s">
@@ -1556,24 +1556,24 @@
       <c r="E25" s="11">
         <v>3140</v>
       </c>
-      <c r="F25" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" s="8" t="s">
+      <c r="F25" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H25" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I25" s="8" t="s">
+      <c r="H25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="11" t="s">
@@ -1585,24 +1585,24 @@
       <c r="E26" s="11">
         <v>3350</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="F26" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I26" s="8" t="s">
+      <c r="H26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="8" t="s">
+      <c r="B27" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="11" t="s">
@@ -1614,24 +1614,24 @@
       <c r="E27" s="11">
         <v>3350</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="F27" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I27" s="8" t="s">
+      <c r="H27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
+      <c r="A28" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="11" t="s">
@@ -1643,24 +1643,24 @@
       <c r="E28" s="11">
         <v>3040</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="F28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="8" t="s">
+      <c r="H28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
+      <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C29" s="11" t="s">
@@ -1672,24 +1672,24 @@
       <c r="E29" s="11">
         <v>3140</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="F29" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I29" s="8" t="s">
+      <c r="H29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="A30" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -1701,24 +1701,24 @@
       <c r="E30" s="11">
         <v>3140</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="F30" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I30" s="8" t="s">
+      <c r="H30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C31" s="11" t="s">
@@ -1730,24 +1730,24 @@
       <c r="E31" s="11">
         <v>3140</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="F31" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I31" s="8" t="s">
+      <c r="H31" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="11" t="s">
@@ -1759,24 +1759,24 @@
       <c r="E32" s="11">
         <v>3140</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="F32" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I32" s="8" t="s">
+      <c r="H32" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C33" s="11" t="s">
@@ -1788,24 +1788,24 @@
       <c r="E33" s="11">
         <v>3140</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G33" s="8" t="s">
+      <c r="F33" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I33" s="8" t="s">
+      <c r="H33" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="11" t="s">
@@ -1817,24 +1817,24 @@
       <c r="E34" s="11">
         <v>3140</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G34" s="8" t="s">
+      <c r="F34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H34" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I34" s="8" t="s">
+      <c r="H34" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C35" s="11" t="s">
@@ -1846,24 +1846,24 @@
       <c r="E35" s="11">
         <v>3140</v>
       </c>
-      <c r="F35" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G35" s="8" t="s">
+      <c r="F35" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H35" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I35" s="8" t="s">
+      <c r="H35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="11" t="s">
@@ -1875,24 +1875,24 @@
       <c r="E36" s="11">
         <v>3140</v>
       </c>
-      <c r="F36" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G36" s="8" t="s">
+      <c r="F36" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G36" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H36" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I36" s="8" t="s">
+      <c r="H36" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C37" s="11" t="s">
@@ -1904,24 +1904,24 @@
       <c r="E37" s="11">
         <v>3140</v>
       </c>
-      <c r="F37" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G37" s="8" t="s">
+      <c r="F37" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G37" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H37" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I37" s="8" t="s">
+      <c r="H37" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="11" t="s">
@@ -1933,24 +1933,24 @@
       <c r="E38" s="11">
         <v>3300</v>
       </c>
-      <c r="F38" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G38" s="8" t="s">
+      <c r="F38" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H38" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I38" s="8" t="s">
+      <c r="H38" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="11" t="s">
@@ -1962,24 +1962,24 @@
       <c r="E39" s="11">
         <v>3350</v>
       </c>
-      <c r="F39" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G39" s="8" t="s">
+      <c r="F39" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G39" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H39" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I39" s="8" t="s">
+      <c r="H39" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C40" s="11" t="s">
@@ -1991,24 +1991,24 @@
       <c r="E40" s="11">
         <v>3460</v>
       </c>
-      <c r="F40" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G40" s="8" t="s">
+      <c r="F40" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G40" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H40" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I40" s="8" t="s">
+      <c r="H40" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="11" t="s">
@@ -2020,24 +2020,24 @@
       <c r="E41" s="11">
         <v>3460</v>
       </c>
-      <c r="F41" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G41" s="8" t="s">
+      <c r="F41" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G41" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H41" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I41" s="8" t="s">
+      <c r="H41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="11" t="s">
@@ -2049,24 +2049,24 @@
       <c r="E42" s="11">
         <v>3670</v>
       </c>
-      <c r="F42" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G42" s="8" t="s">
+      <c r="F42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H42" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I42" s="8" t="s">
+      <c r="H42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B43" s="8" t="s">
+      <c r="B43" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="11" t="s">
@@ -2078,24 +2078,24 @@
       <c r="E43" s="11">
         <v>2840</v>
       </c>
-      <c r="F43" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G43" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I43" s="8" t="s">
+      <c r="F43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I43" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B44" s="8" t="s">
+      <c r="B44" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2107,24 +2107,24 @@
       <c r="E44" s="11">
         <v>2840</v>
       </c>
-      <c r="F44" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G44" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I44" s="8" t="s">
+      <c r="F44" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H44" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I44" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B45" s="8" t="s">
+      <c r="B45" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="11" t="s">
@@ -2136,24 +2136,24 @@
       <c r="E45" s="11">
         <v>2840</v>
       </c>
-      <c r="F45" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I45" s="8" t="s">
+      <c r="F45" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I45" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="A46" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="8" t="s">
+      <c r="B46" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="11" t="s">
@@ -2165,24 +2165,24 @@
       <c r="E46" s="11">
         <v>2840</v>
       </c>
-      <c r="F46" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G46" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I46" s="8" t="s">
+      <c r="F46" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H46" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I46" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="A47" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B47" s="8" t="s">
+      <c r="B47" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="11" t="s">
@@ -2194,24 +2194,24 @@
       <c r="E47" s="11">
         <v>2840</v>
       </c>
-      <c r="F47" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G47" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I47" s="8" t="s">
+      <c r="F47" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H47" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
+      <c r="A48" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="8" t="s">
+      <c r="B48" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="11" t="s">
@@ -2223,24 +2223,24 @@
       <c r="E48" s="11">
         <v>2840</v>
       </c>
-      <c r="F48" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G48" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I48" s="8" t="s">
+      <c r="F48" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I48" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
+      <c r="A49" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="8" t="s">
+      <c r="B49" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="11" t="s">
@@ -2252,24 +2252,24 @@
       <c r="E49" s="11">
         <v>2840</v>
       </c>
-      <c r="F49" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H49" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I49" s="8" t="s">
+      <c r="F49" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I49" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+      <c r="A50" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C50" s="11" t="s">
@@ -2281,24 +2281,24 @@
       <c r="E50" s="11">
         <v>2840</v>
       </c>
-      <c r="F50" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G50" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I50" s="8" t="s">
+      <c r="F50" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I50" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
+      <c r="A51" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B51" s="8" t="s">
+      <c r="B51" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="11" t="s">
@@ -2310,24 +2310,24 @@
       <c r="E51" s="11">
         <v>2840</v>
       </c>
-      <c r="F51" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G51" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I51" s="8" t="s">
+      <c r="F51" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I51" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
+      <c r="A52" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C52" s="11" t="s">
@@ -2339,24 +2339,24 @@
       <c r="E52" s="11">
         <v>3000</v>
       </c>
-      <c r="F52" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I52" s="8" t="s">
+      <c r="F52" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I52" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
+      <c r="A53" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B53" s="8" t="s">
+      <c r="B53" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="11" t="s">
@@ -2368,24 +2368,24 @@
       <c r="E53" s="11">
         <v>2950</v>
       </c>
-      <c r="F53" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G53" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I53" s="8" t="s">
+      <c r="F53" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I53" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
+      <c r="A54" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B54" s="8" t="s">
+      <c r="B54" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="11" t="s">
@@ -2397,24 +2397,24 @@
       <c r="E54" s="11">
         <v>2950</v>
       </c>
-      <c r="F54" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I54" s="8" t="s">
+      <c r="F54" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H54" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I54" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
+      <c r="A55" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="8" t="s">
+      <c r="B55" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="11" t="s">
@@ -2426,24 +2426,24 @@
       <c r="E55" s="11">
         <v>2950</v>
       </c>
-      <c r="F55" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H55" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I55" s="8" t="s">
+      <c r="F55" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H55" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I55" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="8" t="s">
+      <c r="A56" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="8" t="s">
+      <c r="B56" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C56" s="11" t="s">
@@ -2455,24 +2455,24 @@
       <c r="E56" s="11">
         <v>2950</v>
       </c>
-      <c r="F56" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G56" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I56" s="8" t="s">
+      <c r="F56" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H56" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I56" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B57" s="8" t="s">
+      <c r="B57" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="11" t="s">
@@ -2484,24 +2484,24 @@
       <c r="E57" s="11">
         <v>2950</v>
       </c>
-      <c r="F57" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G57" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H57" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I57" s="8" t="s">
+      <c r="F57" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I57" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C58" s="11" t="s">
@@ -2513,24 +2513,24 @@
       <c r="E58" s="11">
         <v>2950</v>
       </c>
-      <c r="F58" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G58" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H58" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I58" s="8" t="s">
+      <c r="F58" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I58" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B59" s="8" t="s">
+      <c r="B59" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C59" s="11" t="s">
@@ -2542,24 +2542,24 @@
       <c r="E59" s="11">
         <v>2950</v>
       </c>
-      <c r="F59" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H59" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I59" s="8" t="s">
+      <c r="F59" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="11" t="s">
@@ -2571,24 +2571,24 @@
       <c r="E60" s="11">
         <v>2950</v>
       </c>
-      <c r="F60" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I60" s="8" t="s">
+      <c r="F60" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="11" t="s">
@@ -2600,24 +2600,24 @@
       <c r="E61" s="11">
         <v>3250</v>
       </c>
-      <c r="F61" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H61" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I61" s="8" t="s">
+      <c r="F61" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I61" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C62" s="11" t="s">
@@ -2629,24 +2629,24 @@
       <c r="E62" s="11">
         <v>2950</v>
       </c>
-      <c r="F62" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H62" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I62" s="8" t="s">
+      <c r="F62" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I62" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="11" t="s">
@@ -2658,24 +2658,24 @@
       <c r="E63" s="11">
         <v>3000</v>
       </c>
-      <c r="F63" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H63" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" s="8" t="s">
+      <c r="F63" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C64" s="11" t="s">
@@ -2687,24 +2687,24 @@
       <c r="E64" s="11">
         <v>3160</v>
       </c>
-      <c r="F64" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H64" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I64" s="8" t="s">
+      <c r="F64" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I64" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C65" s="11" t="s">
@@ -2716,24 +2716,24 @@
       <c r="E65" s="11">
         <v>3160</v>
       </c>
-      <c r="F65" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H65" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I65" s="8" t="s">
+      <c r="F65" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I65" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C66" s="11" t="s">
@@ -2745,24 +2745,24 @@
       <c r="E66" s="11">
         <v>3190</v>
       </c>
-      <c r="F66" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I66" s="8" t="s">
+      <c r="F66" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I66" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C67" s="11" t="s">
@@ -2774,24 +2774,24 @@
       <c r="E67" s="11">
         <v>3290</v>
       </c>
-      <c r="F67" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H67" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I67" s="8" t="s">
+      <c r="F67" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I67" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C68" s="11" t="s">
@@ -2803,24 +2803,24 @@
       <c r="E68" s="11">
         <v>3290</v>
       </c>
-      <c r="F68" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G68" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I68" s="8" t="s">
+      <c r="F68" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I68" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C69" s="11" t="s">
@@ -2832,24 +2832,24 @@
       <c r="E69" s="11">
         <v>3160</v>
       </c>
-      <c r="F69" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G69" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I69" s="8" t="s">
+      <c r="F69" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H69" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I69" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C70" s="11" t="s">
@@ -2861,24 +2861,24 @@
       <c r="E70" s="11">
         <v>3180</v>
       </c>
-      <c r="F70" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G70" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I70" s="8" t="s">
+      <c r="F70" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I70" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="11" t="s">
@@ -2890,24 +2890,24 @@
       <c r="E71" s="11">
         <v>3060</v>
       </c>
-      <c r="F71" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G71" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H71" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I71" s="8" t="s">
+      <c r="F71" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I71" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C72" s="11" t="s">
@@ -2919,24 +2919,24 @@
       <c r="E72" s="11">
         <v>3060</v>
       </c>
-      <c r="F72" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G72" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I72" s="8" t="s">
+      <c r="F72" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I72" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="8" t="s">
+      <c r="A73" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B73" s="8" t="s">
+      <c r="B73" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="11" t="s">
@@ -2948,24 +2948,24 @@
       <c r="E73" s="11">
         <v>3060</v>
       </c>
-      <c r="F73" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G73" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H73" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I73" s="8" t="s">
+      <c r="F73" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H73" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I73" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="8" t="s">
+      <c r="A74" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B74" s="8" t="s">
+      <c r="B74" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C74" s="11" t="s">
@@ -2977,24 +2977,24 @@
       <c r="E74" s="11">
         <v>3060</v>
       </c>
-      <c r="F74" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G74" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I74" s="8" t="s">
+      <c r="F74" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I74" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="8" t="s">
+      <c r="A75" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B75" s="8" t="s">
+      <c r="B75" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="11" t="s">
@@ -3006,24 +3006,24 @@
       <c r="E75" s="11">
         <v>3060</v>
       </c>
-      <c r="F75" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H75" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I75" s="8" t="s">
+      <c r="F75" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H75" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I75" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="8" t="s">
+      <c r="A76" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B76" s="8" t="s">
+      <c r="B76" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C76" s="11" t="s">
@@ -3035,24 +3035,24 @@
       <c r="E76" s="11">
         <v>3060</v>
       </c>
-      <c r="F76" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G76" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I76" s="8" t="s">
+      <c r="F76" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H76" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I76" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="8" t="s">
+      <c r="A77" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B77" s="8" t="s">
+      <c r="B77" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="11" t="s">
@@ -3064,24 +3064,24 @@
       <c r="E77" s="11">
         <v>3060</v>
       </c>
-      <c r="F77" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G77" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H77" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I77" s="8" t="s">
+      <c r="F77" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H77" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I77" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="8" t="s">
+      <c r="A78" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C78" s="11" t="s">
@@ -3093,24 +3093,24 @@
       <c r="E78" s="11">
         <v>3060</v>
       </c>
-      <c r="F78" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G78" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I78" s="8" t="s">
+      <c r="F78" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H78" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I78" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="8" t="s">
+      <c r="A79" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B79" s="8" t="s">
+      <c r="B79" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="11" t="s">
@@ -3122,24 +3122,24 @@
       <c r="E79" s="11">
         <v>3280</v>
       </c>
-      <c r="F79" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G79" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H79" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I79" s="8" t="s">
+      <c r="F79" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I79" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="8" t="s">
+      <c r="A80" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B80" s="8" t="s">
+      <c r="B80" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C80" s="11" t="s">
@@ -3151,24 +3151,24 @@
       <c r="E80" s="11">
         <v>3250</v>
       </c>
-      <c r="F80" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G80" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I80" s="8" t="s">
+      <c r="F80" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H80" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I80" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="8" t="s">
+      <c r="A81" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B81" s="8" t="s">
+      <c r="B81" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C81" s="11" t="s">
@@ -3180,24 +3180,24 @@
       <c r="E81" s="11">
         <v>3310</v>
       </c>
-      <c r="F81" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G81" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H81" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I81" s="8" t="s">
+      <c r="F81" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I81" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8" t="s">
+      <c r="A82" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B82" s="8" t="s">
+      <c r="B82" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C82" s="11" t="s">
@@ -3209,24 +3209,24 @@
       <c r="E82" s="11">
         <v>3310</v>
       </c>
-      <c r="F82" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G82" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H82" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I82" s="8" t="s">
+      <c r="F82" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H82" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I82" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="8" t="s">
+      <c r="A83" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B83" s="8" t="s">
+      <c r="B83" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C83" s="11" t="s">
@@ -3238,24 +3238,24 @@
       <c r="E83" s="11">
         <v>3670</v>
       </c>
-      <c r="F83" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G83" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I83" s="8" t="s">
+      <c r="F83" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H83" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I83" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="8" t="s">
+      <c r="A84" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="8" t="s">
+      <c r="B84" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="11">
@@ -3267,24 +3267,24 @@
       <c r="E84" s="11">
         <v>3350</v>
       </c>
-      <c r="F84" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G84" s="8" t="s">
+      <c r="F84" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G84" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H84" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I84" s="8" t="s">
+      <c r="H84" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I84" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="8" t="s">
+      <c r="A85" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B85" s="8" t="s">
+      <c r="B85" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="11">
@@ -3296,24 +3296,24 @@
       <c r="E85" s="11">
         <v>3350</v>
       </c>
-      <c r="F85" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G85" s="8" t="s">
+      <c r="F85" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G85" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H85" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I85" s="8" t="s">
+      <c r="H85" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I85" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="11">
@@ -3325,24 +3325,24 @@
       <c r="E86" s="11">
         <v>3350</v>
       </c>
-      <c r="F86" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G86" s="8" t="s">
+      <c r="F86" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G86" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H86" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I86" s="8" t="s">
+      <c r="H86" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I86" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="11">
@@ -3354,24 +3354,24 @@
       <c r="E87" s="11">
         <v>3350</v>
       </c>
-      <c r="F87" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G87" s="8" t="s">
+      <c r="F87" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G87" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H87" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I87" s="8" t="s">
+      <c r="H87" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I87" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="11">
@@ -3383,24 +3383,24 @@
       <c r="E88" s="11">
         <v>3350</v>
       </c>
-      <c r="F88" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G88" s="8" t="s">
+      <c r="F88" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G88" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H88" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I88" s="8" t="s">
+      <c r="H88" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I88" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C89" s="11">
@@ -3412,24 +3412,24 @@
       <c r="E89" s="11">
         <v>3350</v>
       </c>
-      <c r="F89" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G89" s="8" t="s">
+      <c r="F89" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G89" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H89" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I89" s="8" t="s">
+      <c r="H89" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I89" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C90" s="11">
@@ -3441,24 +3441,24 @@
       <c r="E90" s="11">
         <v>3350</v>
       </c>
-      <c r="F90" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G90" s="8" t="s">
+      <c r="F90" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G90" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H90" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I90" s="8" t="s">
+      <c r="H90" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I90" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C91" s="11">
@@ -3470,24 +3470,24 @@
       <c r="E91" s="11">
         <v>3560</v>
       </c>
-      <c r="F91" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G91" s="8" t="s">
+      <c r="F91" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G91" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H91" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I91" s="8" t="s">
+      <c r="H91" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I91" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C92" s="11" t="s">
@@ -3499,24 +3499,24 @@
       <c r="E92" s="11">
         <v>3560</v>
       </c>
-      <c r="F92" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G92" s="8" t="s">
+      <c r="F92" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G92" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H92" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I92" s="8" t="s">
+      <c r="H92" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I92" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B93" s="8" t="s">
+      <c r="B93" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C93" s="11">
@@ -3528,24 +3528,24 @@
       <c r="E93" s="11">
         <v>3460</v>
       </c>
-      <c r="F93" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G93" s="8" t="s">
+      <c r="F93" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G93" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H93" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I93" s="8" t="s">
+      <c r="H93" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I93" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B94" s="8" t="s">
+      <c r="B94" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C94" s="11">
@@ -3557,24 +3557,24 @@
       <c r="E94" s="11">
         <v>3460</v>
       </c>
-      <c r="F94" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G94" s="8" t="s">
+      <c r="F94" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G94" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H94" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I94" s="8" t="s">
+      <c r="H94" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I94" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B95" s="8" t="s">
+      <c r="B95" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C95" s="11">
@@ -3586,24 +3586,24 @@
       <c r="E95" s="11">
         <v>3460</v>
       </c>
-      <c r="F95" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G95" s="8" t="s">
+      <c r="F95" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G95" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H95" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I95" s="8" t="s">
+      <c r="H95" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I95" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B96" s="8" t="s">
+      <c r="B96" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C96" s="11">
@@ -3615,24 +3615,24 @@
       <c r="E96" s="11">
         <v>3460</v>
       </c>
-      <c r="F96" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G96" s="8" t="s">
+      <c r="F96" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G96" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H96" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I96" s="8" t="s">
+      <c r="H96" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I96" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C97" s="11">
@@ -3644,24 +3644,24 @@
       <c r="E97" s="11">
         <v>3460</v>
       </c>
-      <c r="F97" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G97" s="8" t="s">
+      <c r="F97" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G97" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H97" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I97" s="8" t="s">
+      <c r="H97" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I97" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C98" s="11">
@@ -3673,24 +3673,24 @@
       <c r="E98" s="11">
         <v>3460</v>
       </c>
-      <c r="F98" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G98" s="8" t="s">
+      <c r="F98" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G98" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H98" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I98" s="8" t="s">
+      <c r="H98" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I98" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="11">
@@ -3702,24 +3702,24 @@
       <c r="E99" s="11">
         <v>3460</v>
       </c>
-      <c r="F99" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G99" s="8" t="s">
+      <c r="F99" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G99" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H99" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I99" s="8" t="s">
+      <c r="H99" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I99" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C100" s="11">
@@ -3731,24 +3731,24 @@
       <c r="E100" s="11">
         <v>3460</v>
       </c>
-      <c r="F100" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G100" s="8" t="s">
+      <c r="F100" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G100" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H100" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I100" s="8" t="s">
+      <c r="H100" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I100" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C101" s="11">
@@ -3760,24 +3760,24 @@
       <c r="E101" s="11">
         <v>3460</v>
       </c>
-      <c r="F101" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G101" s="8" t="s">
+      <c r="F101" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G101" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="H101" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I101" s="8" t="s">
+      <c r="H101" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I101" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C102" s="11" t="s">
@@ -3789,24 +3789,24 @@
       <c r="E102" s="11">
         <v>3560</v>
       </c>
-      <c r="F102" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G102" s="8" t="s">
+      <c r="F102" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G102" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H102" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I102" s="8" t="s">
+      <c r="H102" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I102" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C103" s="11" t="s">
@@ -3818,24 +3818,24 @@
       <c r="E103" s="11">
         <v>3560</v>
       </c>
-      <c r="F103" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G103" s="8" t="s">
+      <c r="F103" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G103" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H103" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I103" s="8" t="s">
+      <c r="H103" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I103" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B104" s="8" t="s">
+      <c r="B104" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="11" t="s">
@@ -3847,24 +3847,24 @@
       <c r="E104" s="11">
         <v>3560</v>
       </c>
-      <c r="F104" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G104" s="8" t="s">
+      <c r="F104" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G104" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H104" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I104" s="8" t="s">
+      <c r="H104" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I104" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="8" t="s">
+      <c r="A105" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B105" s="8" t="s">
+      <c r="B105" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C105" s="11" t="s">
@@ -3876,24 +3876,24 @@
       <c r="E105" s="11">
         <v>3510</v>
       </c>
-      <c r="F105" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G105" s="8" t="s">
+      <c r="F105" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G105" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H105" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I105" s="8" t="s">
+      <c r="H105" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I105" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="8" t="s">
+      <c r="A106" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B106" s="8" t="s">
+      <c r="B106" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C106" s="11" t="s">
@@ -3905,24 +3905,24 @@
       <c r="E106" s="11">
         <v>3830</v>
       </c>
-      <c r="F106" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G106" s="8" t="s">
+      <c r="F106" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G106" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H106" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I106" s="8" t="s">
+      <c r="H106" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I106" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="8" t="s">
+      <c r="A107" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B107" s="8" t="s">
+      <c r="B107" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C107" s="11" t="s">
@@ -3934,24 +3934,24 @@
       <c r="E107" s="11">
         <v>3670</v>
       </c>
-      <c r="F107" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G107" s="8" t="s">
+      <c r="F107" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G107" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H107" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I107" s="8" t="s">
+      <c r="H107" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I107" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="8" t="s">
+      <c r="A108" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B108" s="8" t="s">
+      <c r="B108" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C108" s="11" t="s">
@@ -3963,24 +3963,24 @@
       <c r="E108" s="11">
         <v>3880</v>
       </c>
-      <c r="F108" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G108" s="8" t="s">
+      <c r="F108" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G108" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H108" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I108" s="8" t="s">
+      <c r="H108" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I108" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="8" t="s">
+      <c r="A109" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B109" s="8" t="s">
+      <c r="B109" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C109" s="11" t="s">
@@ -3992,24 +3992,24 @@
       <c r="E109" s="11">
         <v>3880</v>
       </c>
-      <c r="F109" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G109" s="8" t="s">
+      <c r="F109" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G109" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H109" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I109" s="8" t="s">
+      <c r="H109" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I109" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="8" t="s">
+      <c r="A110" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B110" s="8" t="s">
+      <c r="B110" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C110" s="11" t="s">
@@ -4021,24 +4021,24 @@
       <c r="E110" s="11">
         <v>3560</v>
       </c>
-      <c r="F110" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G110" s="8" t="s">
+      <c r="F110" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G110" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H110" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I110" s="8" t="s">
+      <c r="H110" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I110" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="8" t="s">
+      <c r="A111" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B111" s="8" t="s">
+      <c r="B111" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C111" s="11" t="s">
@@ -4050,24 +4050,24 @@
       <c r="E111" s="11">
         <v>3670</v>
       </c>
-      <c r="F111" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G111" s="8" t="s">
+      <c r="F111" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G111" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H111" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I111" s="8" t="s">
+      <c r="H111" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I111" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="8" t="s">
+      <c r="A112" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B112" s="8" t="s">
+      <c r="B112" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C112" s="11" t="s">
@@ -4079,24 +4079,24 @@
       <c r="E112" s="11">
         <v>3670</v>
       </c>
-      <c r="F112" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G112" s="8" t="s">
+      <c r="F112" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G112" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H112" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I112" s="8" t="s">
+      <c r="H112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="8" t="s">
+      <c r="A113" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B113" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C113" s="11" t="s">
@@ -4108,24 +4108,24 @@
       <c r="E113" s="11">
         <v>3670</v>
       </c>
-      <c r="F113" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G113" s="8" t="s">
+      <c r="F113" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G113" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H113" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I113" s="8" t="s">
+      <c r="H113" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="8" t="s">
+      <c r="A114" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B114" s="8" t="s">
+      <c r="B114" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C114" s="11" t="s">
@@ -4137,24 +4137,24 @@
       <c r="E114" s="11">
         <v>3670</v>
       </c>
-      <c r="F114" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G114" s="8" t="s">
+      <c r="F114" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G114" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H114" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I114" s="8" t="s">
+      <c r="H114" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="8" t="s">
+      <c r="A115" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B115" s="8" t="s">
+      <c r="B115" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C115" s="11" t="s">
@@ -4166,24 +4166,24 @@
       <c r="E115" s="11">
         <v>3670</v>
       </c>
-      <c r="F115" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G115" s="8" t="s">
+      <c r="F115" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G115" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H115" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I115" s="8" t="s">
+      <c r="H115" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="8" t="s">
+      <c r="A116" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B116" s="8" t="s">
+      <c r="B116" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C116" s="11" t="s">
@@ -4195,24 +4195,24 @@
       <c r="E116" s="11">
         <v>3670</v>
       </c>
-      <c r="F116" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G116" s="8" t="s">
+      <c r="F116" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G116" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H116" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I116" s="8" t="s">
+      <c r="H116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="8" t="s">
+      <c r="A117" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B117" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C117" s="11" t="s">
@@ -4224,24 +4224,24 @@
       <c r="E117" s="11">
         <v>3670</v>
       </c>
-      <c r="F117" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G117" s="8" t="s">
+      <c r="F117" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G117" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H117" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I117" s="8" t="s">
+      <c r="H117" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="8" t="s">
+      <c r="A118" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B118" s="8" t="s">
+      <c r="B118" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C118" s="11" t="s">
@@ -4253,24 +4253,24 @@
       <c r="E118" s="11">
         <v>3670</v>
       </c>
-      <c r="F118" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G118" s="8" t="s">
+      <c r="F118" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G118" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H118" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I118" s="8" t="s">
+      <c r="H118" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="8" t="s">
+      <c r="A119" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B119" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C119" s="11" t="s">
@@ -4282,24 +4282,24 @@
       <c r="E119" s="11">
         <v>3670</v>
       </c>
-      <c r="F119" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G119" s="8" t="s">
+      <c r="F119" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G119" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H119" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I119" s="8" t="s">
+      <c r="H119" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="8" t="s">
+      <c r="A120" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B120" s="8" t="s">
+      <c r="B120" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C120" s="11" t="s">
@@ -4311,24 +4311,24 @@
       <c r="E120" s="11">
         <v>3830</v>
       </c>
-      <c r="F120" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G120" s="8" t="s">
+      <c r="F120" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G120" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H120" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I120" s="8" t="s">
+      <c r="H120" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I120" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
+      <c r="A121" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B121" s="8" t="s">
+      <c r="B121" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C121" s="11" t="s">
@@ -4340,24 +4340,24 @@
       <c r="E121" s="11">
         <v>3880</v>
       </c>
-      <c r="F121" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G121" s="8" t="s">
+      <c r="F121" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G121" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H121" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I121" s="8" t="s">
+      <c r="H121" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I121" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="8" t="s">
+      <c r="A122" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B122" s="8" t="s">
+      <c r="B122" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C122" s="11" t="s">
@@ -4369,24 +4369,24 @@
       <c r="E122" s="11">
         <v>3980</v>
       </c>
-      <c r="F122" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G122" s="8" t="s">
+      <c r="F122" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G122" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H122" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I122" s="8" t="s">
+      <c r="H122" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I122" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="8" t="s">
+      <c r="A123" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B123" s="8" t="s">
+      <c r="B123" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C123" s="11" t="s">
@@ -4398,24 +4398,24 @@
       <c r="E123" s="11">
         <v>3980</v>
       </c>
-      <c r="F123" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G123" s="8" t="s">
+      <c r="F123" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G123" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H123" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I123" s="8" t="s">
+      <c r="H123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I123" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="8" t="s">
+      <c r="A124" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B124" s="8" t="s">
+      <c r="B124" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C124" s="11" t="s">
@@ -4427,24 +4427,24 @@
       <c r="E124" s="11">
         <v>4190</v>
       </c>
-      <c r="F124" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G124" s="8" t="s">
+      <c r="F124" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G124" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H124" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I124" s="8" t="s">
+      <c r="H124" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I124" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="8" t="s">
+      <c r="A125" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B125" s="8" t="s">
+      <c r="B125" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C125" s="11" t="s">
@@ -4456,24 +4456,24 @@
       <c r="E125" s="11">
         <v>3510</v>
       </c>
-      <c r="F125" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G125" s="8" t="s">
+      <c r="F125" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G125" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H125" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I125" s="8" t="s">
+      <c r="H125" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I125" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A126" s="8" t="s">
+      <c r="A126" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B126" s="8" t="s">
+      <c r="B126" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C126" s="11" t="s">
@@ -4485,24 +4485,24 @@
       <c r="E126" s="11">
         <v>3510</v>
       </c>
-      <c r="F126" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G126" s="8" t="s">
+      <c r="F126" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G126" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H126" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I126" s="8" t="s">
+      <c r="H126" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I126" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A127" s="8" t="s">
+      <c r="A127" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B127" s="8" t="s">
+      <c r="B127" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C127" s="11" t="s">
@@ -4514,24 +4514,24 @@
       <c r="E127" s="11">
         <v>3510</v>
       </c>
-      <c r="F127" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G127" s="8" t="s">
+      <c r="F127" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G127" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H127" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I127" s="8" t="s">
+      <c r="H127" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I127" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A128" s="8" t="s">
+      <c r="A128" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B128" s="8" t="s">
+      <c r="B128" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C128" s="11" t="s">
@@ -4543,24 +4543,24 @@
       <c r="E128" s="11">
         <v>3510</v>
       </c>
-      <c r="F128" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G128" s="8" t="s">
+      <c r="F128" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G128" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H128" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I128" s="8" t="s">
+      <c r="H128" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I128" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A129" s="8" t="s">
+      <c r="A129" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B129" s="8" t="s">
+      <c r="B129" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C129" s="11" t="s">
@@ -4572,24 +4572,24 @@
       <c r="E129" s="11">
         <v>3510</v>
       </c>
-      <c r="F129" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G129" s="8" t="s">
+      <c r="F129" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G129" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H129" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="I129" s="8" t="s">
+      <c r="H129" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I129" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A130" s="8" t="s">
+      <c r="A130" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B130" s="8" t="s">
+      <c r="B130" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C130" s="11" t="s">
@@ -4601,24 +4601,24 @@
       <c r="E130" s="11">
         <v>3370</v>
       </c>
-      <c r="F130" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G130" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H130" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I130" s="8" t="s">
+      <c r="F130" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I130" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A131" s="8" t="s">
+      <c r="A131" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B131" s="8" t="s">
+      <c r="B131" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C131" s="11" t="s">
@@ -4630,24 +4630,24 @@
       <c r="E131" s="11">
         <v>3370</v>
       </c>
-      <c r="F131" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G131" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H131" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I131" s="8" t="s">
+      <c r="F131" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I131" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A132" s="8" t="s">
+      <c r="A132" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B132" s="8" t="s">
+      <c r="B132" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C132" s="11" t="s">
@@ -4659,24 +4659,24 @@
       <c r="E132" s="11">
         <v>3370</v>
       </c>
-      <c r="F132" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G132" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H132" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I132" s="8" t="s">
+      <c r="F132" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I132" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B133" s="8" t="s">
+      <c r="B133" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C133" s="11" t="s">
@@ -4688,24 +4688,24 @@
       <c r="E133" s="11">
         <v>3370</v>
       </c>
-      <c r="F133" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G133" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H133" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I133" s="8" t="s">
+      <c r="F133" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I133" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A134" s="8" t="s">
+      <c r="A134" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C134" s="11" t="s">
@@ -4717,24 +4717,24 @@
       <c r="E134" s="11">
         <v>3370</v>
       </c>
-      <c r="F134" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G134" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H134" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I134" s="8" t="s">
+      <c r="F134" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I134" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A135" s="8" t="s">
+      <c r="A135" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B135" s="8" t="s">
+      <c r="B135" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C135" s="11" t="s">
@@ -4746,24 +4746,24 @@
       <c r="E135" s="11">
         <v>3370</v>
       </c>
-      <c r="F135" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G135" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H135" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I135" s="8" t="s">
+      <c r="F135" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I135" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A136" s="8" t="s">
+      <c r="A136" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B136" s="8" t="s">
+      <c r="B136" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C136" s="11" t="s">
@@ -4775,24 +4775,24 @@
       <c r="E136" s="11">
         <v>3370</v>
       </c>
-      <c r="F136" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G136" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H136" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I136" s="8" t="s">
+      <c r="F136" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I136" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A137" s="8" t="s">
+      <c r="A137" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B137" s="8" t="s">
+      <c r="B137" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C137" s="11" t="s">
@@ -4804,24 +4804,24 @@
       <c r="E137" s="11">
         <v>3370</v>
       </c>
-      <c r="F137" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G137" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H137" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I137" s="8" t="s">
+      <c r="F137" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I137" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A138" s="8" t="s">
+      <c r="A138" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B138" s="8" t="s">
+      <c r="B138" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C138" s="11" t="s">
@@ -4833,24 +4833,24 @@
       <c r="E138" s="11">
         <v>3370</v>
       </c>
-      <c r="F138" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G138" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H138" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I138" s="8" t="s">
+      <c r="F138" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I138" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A139" s="8" t="s">
+      <c r="A139" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B139" s="8" t="s">
+      <c r="B139" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C139" s="11" t="s">
@@ -4862,24 +4862,24 @@
       <c r="E139" s="11">
         <v>3520</v>
       </c>
-      <c r="F139" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G139" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H139" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I139" s="8" t="s">
+      <c r="F139" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I139" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A140" s="8" t="s">
+      <c r="A140" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B140" s="8" t="s">
+      <c r="B140" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C140" s="11" t="s">
@@ -4891,24 +4891,24 @@
       <c r="E140" s="11">
         <v>3470</v>
       </c>
-      <c r="F140" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H140" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I140" s="8" t="s">
+      <c r="F140" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I140" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A141" s="8" t="s">
+      <c r="A141" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B141" s="8" t="s">
+      <c r="B141" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C141" s="11" t="s">
@@ -4920,24 +4920,24 @@
       <c r="E141" s="11">
         <v>3470</v>
       </c>
-      <c r="F141" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G141" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H141" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I141" s="8" t="s">
+      <c r="F141" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I141" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A142" s="8" t="s">
+      <c r="A142" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B142" s="8" t="s">
+      <c r="B142" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C142" s="11" t="s">
@@ -4949,24 +4949,24 @@
       <c r="E142" s="11">
         <v>3470</v>
       </c>
-      <c r="F142" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G142" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H142" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I142" s="8" t="s">
+      <c r="F142" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I142" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A143" s="8" t="s">
+      <c r="A143" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B143" s="8" t="s">
+      <c r="B143" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C143" s="11" t="s">
@@ -4978,24 +4978,24 @@
       <c r="E143" s="11">
         <v>3470</v>
       </c>
-      <c r="F143" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G143" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H143" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I143" s="8" t="s">
+      <c r="F143" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I143" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A144" s="8" t="s">
+      <c r="A144" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="B144" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C144" s="11" t="s">
@@ -5007,24 +5007,24 @@
       <c r="E144" s="11">
         <v>3470</v>
       </c>
-      <c r="F144" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G144" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H144" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I144" s="8" t="s">
+      <c r="F144" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I144" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A145" s="8" t="s">
+      <c r="A145" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B145" s="8" t="s">
+      <c r="B145" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C145" s="11" t="s">
@@ -5036,24 +5036,24 @@
       <c r="E145" s="11">
         <v>3470</v>
       </c>
-      <c r="F145" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G145" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H145" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I145" s="8" t="s">
+      <c r="F145" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I145" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A146" s="8" t="s">
+      <c r="A146" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B146" s="8" t="s">
+      <c r="B146" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C146" s="11" t="s">
@@ -5065,24 +5065,24 @@
       <c r="E146" s="11">
         <v>3470</v>
       </c>
-      <c r="F146" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G146" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H146" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I146" s="8" t="s">
+      <c r="F146" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I146" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A147" s="8" t="s">
+      <c r="A147" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B147" s="8" t="s">
+      <c r="B147" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C147" s="11" t="s">
@@ -5094,24 +5094,24 @@
       <c r="E147" s="11">
         <v>3470</v>
       </c>
-      <c r="F147" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G147" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H147" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I147" s="8" t="s">
+      <c r="F147" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A148" s="8" t="s">
+      <c r="A148" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B148" s="8" t="s">
+      <c r="B148" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C148" s="11" t="s">
@@ -5123,24 +5123,24 @@
       <c r="E148" s="11">
         <v>3780</v>
       </c>
-      <c r="F148" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G148" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H148" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I148" s="8" t="s">
+      <c r="F148" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I148" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A149" s="8" t="s">
+      <c r="A149" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B149" s="8" t="s">
+      <c r="B149" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C149" s="11" t="s">
@@ -5152,24 +5152,24 @@
       <c r="E149" s="11">
         <v>3470</v>
       </c>
-      <c r="F149" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G149" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H149" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I149" s="8" t="s">
+      <c r="F149" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A150" s="8" t="s">
+      <c r="A150" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B150" s="8" t="s">
+      <c r="B150" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C150" s="11" t="s">
@@ -5181,24 +5181,24 @@
       <c r="E150" s="11">
         <v>3520</v>
       </c>
-      <c r="F150" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G150" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H150" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I150" s="8" t="s">
+      <c r="F150" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I150" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A151" s="8" t="s">
+      <c r="A151" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B151" s="8" t="s">
+      <c r="B151" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C151" s="11" t="s">
@@ -5210,24 +5210,24 @@
       <c r="E151" s="11">
         <v>3680</v>
       </c>
-      <c r="F151" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G151" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H151" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I151" s="8" t="s">
+      <c r="F151" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I151" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A152" s="8" t="s">
+      <c r="A152" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B152" s="8" t="s">
+      <c r="B152" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C152" s="11" t="s">
@@ -5239,24 +5239,24 @@
       <c r="E152" s="11">
         <v>3680</v>
       </c>
-      <c r="F152" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G152" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H152" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I152" s="8" t="s">
+      <c r="F152" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A153" s="8" t="s">
+      <c r="A153" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B153" s="8" t="s">
+      <c r="B153" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C153" s="11" t="s">
@@ -5268,24 +5268,24 @@
       <c r="E153" s="11">
         <v>3720</v>
       </c>
-      <c r="F153" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G153" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H153" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I153" s="8" t="s">
+      <c r="F153" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I153" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A154" s="8" t="s">
+      <c r="A154" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="B154" s="8" t="s">
+      <c r="B154" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C154" s="11" t="s">
@@ -5297,24 +5297,24 @@
       <c r="E154" s="11">
         <v>3810</v>
       </c>
-      <c r="F154" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G154" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H154" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I154" s="8" t="s">
+      <c r="F154" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I154" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A155" s="8" t="s">
+      <c r="A155" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B155" s="8" t="s">
+      <c r="B155" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C155" s="11" t="s">
@@ -5326,24 +5326,24 @@
       <c r="E155" s="11">
         <v>3810</v>
       </c>
-      <c r="F155" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G155" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H155" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I155" s="8" t="s">
+      <c r="F155" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I155" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A156" s="8" t="s">
+      <c r="A156" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B156" s="8" t="s">
+      <c r="B156" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C156" s="11" t="s">
@@ -5355,24 +5355,24 @@
       <c r="E156" s="11">
         <v>3680</v>
       </c>
-      <c r="F156" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G156" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H156" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I156" s="8" t="s">
+      <c r="F156" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I156" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B157" s="8" t="s">
+      <c r="B157" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C157" s="11" t="s">
@@ -5384,24 +5384,24 @@
       <c r="E157" s="11">
         <v>3700</v>
       </c>
-      <c r="F157" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G157" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H157" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I157" s="8" t="s">
+      <c r="F157" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I157" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A158" s="8" t="s">
+      <c r="A158" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B158" s="8" t="s">
+      <c r="B158" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C158" s="11" t="s">
@@ -5413,24 +5413,24 @@
       <c r="E158" s="11">
         <v>3590</v>
       </c>
-      <c r="F158" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G158" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H158" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I158" s="8" t="s">
+      <c r="F158" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I158" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A159" s="8" t="s">
+      <c r="A159" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B159" s="8" t="s">
+      <c r="B159" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C159" s="11" t="s">
@@ -5442,24 +5442,24 @@
       <c r="E159" s="11">
         <v>3590</v>
       </c>
-      <c r="F159" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G159" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H159" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I159" s="8" t="s">
+      <c r="F159" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I159" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A160" s="8" t="s">
+      <c r="A160" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B160" s="8" t="s">
+      <c r="B160" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C160" s="11" t="s">
@@ -5471,24 +5471,24 @@
       <c r="E160" s="11">
         <v>3590</v>
       </c>
-      <c r="F160" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G160" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H160" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I160" s="8" t="s">
+      <c r="F160" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I160" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A161" s="8" t="s">
+      <c r="A161" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B161" s="8" t="s">
+      <c r="B161" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C161" s="11" t="s">
@@ -5500,24 +5500,24 @@
       <c r="E161" s="11">
         <v>3590</v>
       </c>
-      <c r="F161" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G161" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H161" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I161" s="8" t="s">
+      <c r="F161" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I161" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A162" s="8" t="s">
+      <c r="A162" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B162" s="8" t="s">
+      <c r="B162" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C162" s="11" t="s">
@@ -5529,24 +5529,24 @@
       <c r="E162" s="11">
         <v>3590</v>
       </c>
-      <c r="F162" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G162" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H162" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I162" s="8" t="s">
+      <c r="F162" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I162" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A163" s="8" t="s">
+      <c r="A163" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="B163" s="8" t="s">
+      <c r="B163" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C163" s="11" t="s">
@@ -5558,24 +5558,24 @@
       <c r="E163" s="11">
         <v>3590</v>
       </c>
-      <c r="F163" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G163" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H163" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I163" s="8" t="s">
+      <c r="F163" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I163" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A164" s="8" t="s">
+      <c r="A164" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B164" s="8" t="s">
+      <c r="B164" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C164" s="11" t="s">
@@ -5587,24 +5587,24 @@
       <c r="E164" s="11">
         <v>3590</v>
       </c>
-      <c r="F164" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G164" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H164" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I164" s="8" t="s">
+      <c r="F164" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I164" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A165" s="8" t="s">
+      <c r="A165" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B165" s="8" t="s">
+      <c r="B165" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C165" s="11" t="s">
@@ -5616,24 +5616,24 @@
       <c r="E165" s="11">
         <v>3590</v>
       </c>
-      <c r="F165" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G165" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H165" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I165" s="8" t="s">
+      <c r="F165" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I165" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A166" s="8" t="s">
+      <c r="A166" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B166" s="8" t="s">
+      <c r="B166" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C166" s="11" t="s">
@@ -5645,24 +5645,24 @@
       <c r="E166" s="11">
         <v>3800</v>
       </c>
-      <c r="F166" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G166" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H166" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I166" s="8" t="s">
+      <c r="F166" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I166" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A167" s="8" t="s">
+      <c r="A167" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B167" s="8" t="s">
+      <c r="B167" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C167" s="11" t="s">
@@ -5674,24 +5674,24 @@
       <c r="E167" s="11">
         <v>3770</v>
       </c>
-      <c r="F167" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G167" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H167" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I167" s="8" t="s">
+      <c r="F167" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H167" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I167" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A168" s="8" t="s">
+      <c r="A168" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B168" s="8" t="s">
+      <c r="B168" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C168" s="11" t="s">
@@ -5703,24 +5703,24 @@
       <c r="E168" s="11">
         <v>3840</v>
       </c>
-      <c r="F168" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G168" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H168" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I168" s="8" t="s">
+      <c r="F168" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I168" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A169" s="8" t="s">
+      <c r="A169" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B169" s="8" t="s">
+      <c r="B169" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C169" s="11" t="s">
@@ -5732,24 +5732,24 @@
       <c r="E169" s="11">
         <v>3840</v>
       </c>
-      <c r="F169" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G169" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H169" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I169" s="8" t="s">
+      <c r="F169" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G169" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H169" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I169" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A170" s="8" t="s">
+      <c r="A170" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B170" s="8" t="s">
+      <c r="B170" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C170" s="11" t="s">
@@ -5761,24 +5761,24 @@
       <c r="E170" s="11">
         <v>4190</v>
       </c>
-      <c r="F170" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G170" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H170" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I170" s="8" t="s">
+      <c r="F170" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I170" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A171" s="8" t="s">
+      <c r="A171" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B171" s="8" t="s">
+      <c r="B171" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C171" s="11" t="s">
@@ -5790,24 +5790,24 @@
       <c r="E171" s="11">
         <v>3520</v>
       </c>
-      <c r="F171" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G171" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H171" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I171" s="8" t="s">
+      <c r="F171" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I171" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A172" s="8" t="s">
+      <c r="A172" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B172" s="8" t="s">
+      <c r="B172" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C172" s="11" t="s">
@@ -5819,24 +5819,24 @@
       <c r="E172" s="11">
         <v>3680</v>
       </c>
-      <c r="F172" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G172" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H172" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I172" s="8" t="s">
+      <c r="F172" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I172" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A173" s="8" t="s">
+      <c r="A173" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B173" s="8" t="s">
+      <c r="B173" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C173" s="11" t="s">
@@ -5848,24 +5848,24 @@
       <c r="E173" s="11">
         <v>3680</v>
       </c>
-      <c r="F173" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G173" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H173" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I173" s="8" t="s">
+      <c r="F173" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A174" s="8" t="s">
+      <c r="A174" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="B174" s="8" t="s">
+      <c r="B174" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C174" s="11" t="s">
@@ -5877,24 +5877,24 @@
       <c r="E174" s="11">
         <v>3730</v>
       </c>
-      <c r="F174" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G174" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H174" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I174" s="8" t="s">
+      <c r="F174" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A175" s="8" t="s">
+      <c r="A175" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="B175" s="8" t="s">
+      <c r="B175" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C175" s="11" t="s">
@@ -5906,16 +5906,16 @@
       <c r="E175" s="11">
         <v>3730</v>
       </c>
-      <c r="F175" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G175" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="H175" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I175" s="8" t="s">
+      <c r="F175" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" s="7" t="s">
         <v>24</v>
       </c>
     </row>
@@ -5929,22 +5929,22 @@
       <c r="C176" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D176" s="10">
+      <c r="D176" s="12">
         <v>50</v>
       </c>
-      <c r="E176" s="10">
+      <c r="E176" s="12">
         <v>90</v>
       </c>
-      <c r="F176" s="8" t="s">
+      <c r="F176" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G176" s="9">
+      <c r="G176" s="8">
         <v>14</v>
       </c>
-      <c r="H176" s="8" t="s">
+      <c r="H176" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I176" s="8" t="s">
+      <c r="I176" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5958,22 +5958,22 @@
       <c r="C177" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D177" s="10">
+      <c r="D177" s="12">
         <v>140</v>
       </c>
-      <c r="E177" s="10">
+      <c r="E177" s="12">
         <v>260</v>
       </c>
-      <c r="F177" s="8" t="s">
+      <c r="F177" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G177" s="9">
+      <c r="G177" s="8">
         <v>14</v>
       </c>
-      <c r="H177" s="8" t="s">
+      <c r="H177" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I177" s="8" t="s">
+      <c r="I177" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5987,22 +5987,22 @@
       <c r="C178" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D178" s="10">
+      <c r="D178" s="12">
         <v>180</v>
       </c>
-      <c r="E178" s="10">
+      <c r="E178" s="12">
         <v>410</v>
       </c>
-      <c r="F178" s="8" t="s">
+      <c r="F178" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G178" s="9">
+      <c r="G178" s="8">
         <v>14</v>
       </c>
-      <c r="H178" s="8" t="s">
+      <c r="H178" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I178" s="8" t="s">
+      <c r="I178" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6016,22 +6016,22 @@
       <c r="C179" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D179" s="10">
+      <c r="D179" s="12">
         <v>130</v>
       </c>
-      <c r="E179" s="10">
+      <c r="E179" s="12">
         <v>150</v>
       </c>
-      <c r="F179" s="8" t="s">
+      <c r="F179" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G179" s="9">
+      <c r="G179" s="8">
         <v>14</v>
       </c>
-      <c r="H179" s="8" t="s">
+      <c r="H179" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I179" s="8" t="s">
+      <c r="I179" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6045,22 +6045,22 @@
       <c r="C180" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D180" s="10">
+      <c r="D180" s="9">
         <v>1570</v>
       </c>
-      <c r="E180" s="10">
+      <c r="E180" s="9">
         <v>2470</v>
       </c>
-      <c r="F180" s="8" t="s">
+      <c r="F180" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G180" s="9">
+      <c r="G180" s="8">
         <v>14</v>
       </c>
-      <c r="H180" s="8" t="s">
+      <c r="H180" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I180" s="8" t="s">
+      <c r="I180" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6074,22 +6074,22 @@
       <c r="C181" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D181" s="10">
+      <c r="D181" s="9">
         <v>1570</v>
       </c>
-      <c r="E181" s="10">
+      <c r="E181" s="9">
         <v>2470</v>
       </c>
-      <c r="F181" s="8" t="s">
+      <c r="F181" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G181" s="9">
+      <c r="G181" s="8">
         <v>14</v>
       </c>
-      <c r="H181" s="8" t="s">
+      <c r="H181" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I181" s="8" t="s">
+      <c r="I181" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6103,22 +6103,22 @@
       <c r="C182" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D182" s="10">
+      <c r="D182" s="9">
         <v>1470</v>
       </c>
-      <c r="E182" s="10">
+      <c r="E182" s="9">
         <v>2780</v>
       </c>
-      <c r="F182" s="8" t="s">
+      <c r="F182" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G182" s="9">
+      <c r="G182" s="8">
         <v>14</v>
       </c>
-      <c r="H182" s="8" t="s">
+      <c r="H182" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I182" s="8" t="s">
+      <c r="I182" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6132,22 +6132,22 @@
       <c r="C183" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D183" s="10">
+      <c r="D183" s="9">
         <v>1470</v>
       </c>
-      <c r="E183" s="10">
+      <c r="E183" s="9">
         <v>2780</v>
       </c>
-      <c r="F183" s="8" t="s">
+      <c r="F183" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G183" s="9">
+      <c r="G183" s="8">
         <v>14</v>
       </c>
-      <c r="H183" s="8" t="s">
+      <c r="H183" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I183" s="8" t="s">
+      <c r="I183" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6161,22 +6161,22 @@
       <c r="C184" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D184" s="10">
+      <c r="D184" s="9">
         <v>1230</v>
       </c>
-      <c r="E184" s="10">
+      <c r="E184" s="9">
         <v>2030</v>
       </c>
-      <c r="F184" s="8" t="s">
+      <c r="F184" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G184" s="9">
+      <c r="G184" s="8">
         <v>14</v>
       </c>
-      <c r="H184" s="8" t="s">
+      <c r="H184" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I184" s="8" t="s">
+      <c r="I184" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6190,22 +6190,22 @@
       <c r="C185" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D185" s="10">
+      <c r="D185" s="9">
         <v>1230</v>
       </c>
-      <c r="E185" s="10">
+      <c r="E185" s="9">
         <v>2030</v>
       </c>
-      <c r="F185" s="8" t="s">
+      <c r="F185" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G185" s="9">
+      <c r="G185" s="8">
         <v>14</v>
       </c>
-      <c r="H185" s="8" t="s">
+      <c r="H185" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I185" s="8" t="s">
+      <c r="I185" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6219,22 +6219,22 @@
       <c r="C186" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D186" s="10">
+      <c r="D186" s="9">
         <v>1230</v>
       </c>
-      <c r="E186" s="10">
+      <c r="E186" s="9">
         <v>2030</v>
       </c>
-      <c r="F186" s="8" t="s">
+      <c r="F186" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G186" s="9">
+      <c r="G186" s="8">
         <v>14</v>
       </c>
-      <c r="H186" s="8" t="s">
+      <c r="H186" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I186" s="8" t="s">
+      <c r="I186" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6248,22 +6248,22 @@
       <c r="C187" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D187" s="10">
+      <c r="D187" s="9">
         <v>1550</v>
       </c>
-      <c r="E187" s="10">
+      <c r="E187" s="9">
         <v>2490</v>
       </c>
-      <c r="F187" s="8" t="s">
+      <c r="F187" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G187" s="9">
+      <c r="G187" s="8">
         <v>14</v>
       </c>
-      <c r="H187" s="8" t="s">
+      <c r="H187" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I187" s="8" t="s">
+      <c r="I187" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6277,22 +6277,22 @@
       <c r="C188" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D188" s="10">
+      <c r="D188" s="9">
         <v>1230</v>
       </c>
-      <c r="E188" s="10">
+      <c r="E188" s="9">
         <v>2030</v>
       </c>
-      <c r="F188" s="8" t="s">
+      <c r="F188" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G188" s="9">
+      <c r="G188" s="8">
         <v>14</v>
       </c>
-      <c r="H188" s="8" t="s">
+      <c r="H188" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I188" s="8" t="s">
+      <c r="I188" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6306,22 +6306,22 @@
       <c r="C189" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D189" s="10">
+      <c r="D189" s="9">
         <v>1510</v>
       </c>
-      <c r="E189" s="10">
+      <c r="E189" s="9">
         <v>2350</v>
       </c>
-      <c r="F189" s="8" t="s">
+      <c r="F189" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G189" s="9">
+      <c r="G189" s="8">
         <v>14</v>
       </c>
-      <c r="H189" s="8" t="s">
+      <c r="H189" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I189" s="8" t="s">
+      <c r="I189" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6335,22 +6335,22 @@
       <c r="C190" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D190" s="10">
+      <c r="D190" s="9">
         <v>1550</v>
       </c>
-      <c r="E190" s="10">
+      <c r="E190" s="9">
         <v>2490</v>
       </c>
-      <c r="F190" s="8" t="s">
+      <c r="F190" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G190" s="9">
+      <c r="G190" s="8">
         <v>14</v>
       </c>
-      <c r="H190" s="8" t="s">
+      <c r="H190" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I190" s="8" t="s">
+      <c r="I190" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6364,22 +6364,22 @@
       <c r="C191" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D191" s="10">
+      <c r="D191" s="9">
         <v>1830</v>
       </c>
-      <c r="E191" s="10">
+      <c r="E191" s="9">
         <v>2810</v>
       </c>
-      <c r="F191" s="8" t="s">
+      <c r="F191" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G191" s="9">
+      <c r="G191" s="8">
         <v>14</v>
       </c>
-      <c r="H191" s="8" t="s">
+      <c r="H191" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I191" s="8" t="s">
+      <c r="I191" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6393,22 +6393,22 @@
       <c r="C192" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D192" s="10">
+      <c r="D192" s="9">
         <v>1550</v>
       </c>
-      <c r="E192" s="10">
+      <c r="E192" s="9">
         <v>2490</v>
       </c>
-      <c r="F192" s="8" t="s">
+      <c r="F192" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G192" s="9">
+      <c r="G192" s="8">
         <v>14</v>
       </c>
-      <c r="H192" s="8" t="s">
+      <c r="H192" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I192" s="8" t="s">
+      <c r="I192" s="7" t="s">
         <v>86</v>
       </c>
     </row>
@@ -6422,684 +6422,684 @@
       <c r="C193" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D193" s="10">
+      <c r="D193" s="9">
         <v>1550</v>
       </c>
-      <c r="E193" s="10">
+      <c r="E193" s="9">
         <v>2490</v>
       </c>
-      <c r="F193" s="8" t="s">
+      <c r="F193" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G193" s="9">
+      <c r="G193" s="8">
         <v>14</v>
       </c>
-      <c r="H193" s="8" t="s">
+      <c r="H193" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I193" s="8" t="s">
+      <c r="I193" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G194" s="9"/>
+      <c r="G194" s="8"/>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G195" s="9"/>
+      <c r="G195" s="8"/>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G196" s="9"/>
+      <c r="G196" s="8"/>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G197" s="9"/>
+      <c r="G197" s="8"/>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G198" s="9"/>
+      <c r="G198" s="8"/>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G199" s="9"/>
+      <c r="G199" s="8"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G200" s="9"/>
+      <c r="G200" s="8"/>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G201" s="9"/>
+      <c r="G201" s="8"/>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G202" s="9"/>
+      <c r="G202" s="8"/>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G203" s="9"/>
+      <c r="G203" s="8"/>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G204" s="9"/>
+      <c r="G204" s="8"/>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G205" s="9"/>
+      <c r="G205" s="8"/>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G206" s="9"/>
+      <c r="G206" s="8"/>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G207" s="9"/>
+      <c r="G207" s="8"/>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G208" s="9"/>
+      <c r="G208" s="8"/>
     </row>
     <row r="209" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G209" s="9"/>
+      <c r="G209" s="8"/>
     </row>
     <row r="210" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G210" s="9"/>
+      <c r="G210" s="8"/>
     </row>
     <row r="211" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G211" s="9"/>
+      <c r="G211" s="8"/>
     </row>
     <row r="212" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G212" s="9"/>
+      <c r="G212" s="8"/>
     </row>
     <row r="213" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G213" s="9"/>
+      <c r="G213" s="8"/>
     </row>
     <row r="214" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G214" s="9"/>
+      <c r="G214" s="8"/>
     </row>
     <row r="215" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G215" s="9"/>
+      <c r="G215" s="8"/>
     </row>
     <row r="216" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G216" s="9"/>
+      <c r="G216" s="8"/>
     </row>
     <row r="217" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G217" s="9"/>
+      <c r="G217" s="8"/>
     </row>
     <row r="218" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G218" s="9"/>
+      <c r="G218" s="8"/>
     </row>
     <row r="219" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G219" s="9"/>
+      <c r="G219" s="8"/>
     </row>
     <row r="220" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G220" s="9"/>
+      <c r="G220" s="8"/>
     </row>
     <row r="221" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G221" s="9"/>
+      <c r="G221" s="8"/>
     </row>
     <row r="222" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G222" s="9"/>
+      <c r="G222" s="8"/>
     </row>
     <row r="223" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G223" s="9"/>
+      <c r="G223" s="8"/>
     </row>
     <row r="224" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G224" s="9"/>
+      <c r="G224" s="8"/>
     </row>
     <row r="225" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G225" s="9"/>
+      <c r="G225" s="8"/>
     </row>
     <row r="226" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G226" s="9"/>
+      <c r="G226" s="8"/>
     </row>
     <row r="227" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G227" s="9"/>
+      <c r="G227" s="8"/>
     </row>
     <row r="228" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G228" s="9"/>
+      <c r="G228" s="8"/>
     </row>
     <row r="229" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G229" s="9"/>
+      <c r="G229" s="8"/>
     </row>
     <row r="230" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G230" s="9"/>
+      <c r="G230" s="8"/>
     </row>
     <row r="231" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G231" s="9"/>
+      <c r="G231" s="8"/>
     </row>
     <row r="232" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G232" s="9"/>
+      <c r="G232" s="8"/>
     </row>
     <row r="233" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G233" s="9"/>
+      <c r="G233" s="8"/>
     </row>
     <row r="234" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G234" s="9"/>
+      <c r="G234" s="8"/>
     </row>
     <row r="235" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G235" s="9"/>
+      <c r="G235" s="8"/>
     </row>
     <row r="236" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G236" s="9"/>
+      <c r="G236" s="8"/>
     </row>
     <row r="237" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G237" s="9"/>
+      <c r="G237" s="8"/>
     </row>
     <row r="238" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G238" s="9"/>
+      <c r="G238" s="8"/>
     </row>
     <row r="239" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G239" s="9"/>
+      <c r="G239" s="8"/>
     </row>
     <row r="240" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G240" s="9"/>
+      <c r="G240" s="8"/>
     </row>
     <row r="241" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G241" s="9"/>
+      <c r="G241" s="8"/>
     </row>
     <row r="242" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G242" s="9"/>
+      <c r="G242" s="8"/>
     </row>
     <row r="243" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G243" s="9"/>
+      <c r="G243" s="8"/>
     </row>
     <row r="244" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G244" s="9"/>
+      <c r="G244" s="8"/>
     </row>
     <row r="245" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G245" s="9"/>
+      <c r="G245" s="8"/>
     </row>
     <row r="246" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G246" s="9"/>
+      <c r="G246" s="8"/>
     </row>
     <row r="247" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G247" s="9"/>
+      <c r="G247" s="8"/>
     </row>
     <row r="248" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G248" s="9"/>
+      <c r="G248" s="8"/>
     </row>
     <row r="249" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G249" s="9"/>
+      <c r="G249" s="8"/>
     </row>
     <row r="250" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G250" s="9"/>
+      <c r="G250" s="8"/>
     </row>
     <row r="251" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G251" s="9"/>
+      <c r="G251" s="8"/>
     </row>
     <row r="252" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G252" s="9"/>
+      <c r="G252" s="8"/>
     </row>
     <row r="253" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G253" s="9"/>
+      <c r="G253" s="8"/>
     </row>
     <row r="254" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G254" s="9"/>
+      <c r="G254" s="8"/>
     </row>
     <row r="255" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G255" s="9"/>
+      <c r="G255" s="8"/>
     </row>
     <row r="256" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G256" s="9"/>
+      <c r="G256" s="8"/>
     </row>
     <row r="257" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G257" s="9"/>
+      <c r="G257" s="8"/>
     </row>
     <row r="258" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G258" s="9"/>
+      <c r="G258" s="8"/>
     </row>
     <row r="259" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G259" s="9"/>
+      <c r="G259" s="8"/>
     </row>
     <row r="260" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G260" s="9"/>
+      <c r="G260" s="8"/>
     </row>
     <row r="261" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G261" s="9"/>
+      <c r="G261" s="8"/>
     </row>
     <row r="262" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G262" s="9"/>
+      <c r="G262" s="8"/>
     </row>
     <row r="263" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G263" s="9"/>
+      <c r="G263" s="8"/>
     </row>
     <row r="264" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G264" s="9"/>
+      <c r="G264" s="8"/>
     </row>
     <row r="265" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G265" s="9"/>
+      <c r="G265" s="8"/>
     </row>
     <row r="266" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G266" s="9"/>
+      <c r="G266" s="8"/>
     </row>
     <row r="267" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G267" s="9"/>
+      <c r="G267" s="8"/>
     </row>
     <row r="268" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G268" s="9"/>
+      <c r="G268" s="8"/>
     </row>
     <row r="269" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G269" s="9"/>
+      <c r="G269" s="8"/>
     </row>
     <row r="270" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G270" s="9"/>
+      <c r="G270" s="8"/>
     </row>
     <row r="271" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G271" s="9"/>
+      <c r="G271" s="8"/>
     </row>
     <row r="272" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G272" s="9"/>
+      <c r="G272" s="8"/>
     </row>
     <row r="273" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G273" s="9"/>
+      <c r="G273" s="8"/>
     </row>
     <row r="274" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G274" s="9"/>
+      <c r="G274" s="8"/>
     </row>
     <row r="275" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G275" s="9"/>
+      <c r="G275" s="8"/>
     </row>
     <row r="276" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G276" s="9"/>
+      <c r="G276" s="8"/>
     </row>
     <row r="277" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G277" s="9"/>
+      <c r="G277" s="8"/>
     </row>
     <row r="278" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G278" s="9"/>
+      <c r="G278" s="8"/>
     </row>
     <row r="279" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G279" s="9"/>
+      <c r="G279" s="8"/>
     </row>
     <row r="280" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G280" s="9"/>
+      <c r="G280" s="8"/>
     </row>
     <row r="281" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G281" s="9"/>
+      <c r="G281" s="8"/>
     </row>
     <row r="282" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G282" s="9"/>
+      <c r="G282" s="8"/>
     </row>
     <row r="283" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G283" s="9"/>
+      <c r="G283" s="8"/>
     </row>
     <row r="284" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G284" s="9"/>
+      <c r="G284" s="8"/>
     </row>
     <row r="285" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G285" s="9"/>
+      <c r="G285" s="8"/>
     </row>
     <row r="286" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G286" s="9"/>
+      <c r="G286" s="8"/>
     </row>
     <row r="287" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G287" s="9"/>
+      <c r="G287" s="8"/>
     </row>
     <row r="288" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G288" s="9"/>
+      <c r="G288" s="8"/>
     </row>
     <row r="289" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G289" s="9"/>
+      <c r="G289" s="8"/>
     </row>
     <row r="290" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G290" s="9"/>
+      <c r="G290" s="8"/>
     </row>
     <row r="291" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G291" s="9"/>
+      <c r="G291" s="8"/>
     </row>
     <row r="292" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G292" s="9"/>
+      <c r="G292" s="8"/>
     </row>
     <row r="293" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G293" s="9"/>
+      <c r="G293" s="8"/>
     </row>
     <row r="294" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G294" s="9"/>
+      <c r="G294" s="8"/>
     </row>
     <row r="295" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G295" s="9"/>
+      <c r="G295" s="8"/>
     </row>
     <row r="296" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G296" s="9"/>
+      <c r="G296" s="8"/>
     </row>
     <row r="297" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G297" s="9"/>
+      <c r="G297" s="8"/>
     </row>
     <row r="298" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G298" s="9"/>
+      <c r="G298" s="8"/>
     </row>
     <row r="299" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G299" s="9"/>
+      <c r="G299" s="8"/>
     </row>
     <row r="300" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G300" s="9"/>
+      <c r="G300" s="8"/>
     </row>
     <row r="301" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G301" s="9"/>
+      <c r="G301" s="8"/>
     </row>
     <row r="302" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G302" s="9"/>
+      <c r="G302" s="8"/>
     </row>
     <row r="303" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G303" s="9"/>
+      <c r="G303" s="8"/>
     </row>
     <row r="304" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G304" s="9"/>
+      <c r="G304" s="8"/>
     </row>
     <row r="305" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G305" s="9"/>
+      <c r="G305" s="8"/>
     </row>
     <row r="306" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G306" s="9"/>
+      <c r="G306" s="8"/>
     </row>
     <row r="307" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G307" s="9"/>
+      <c r="G307" s="8"/>
     </row>
     <row r="308" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G308" s="9"/>
+      <c r="G308" s="8"/>
     </row>
     <row r="309" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G309" s="9"/>
+      <c r="G309" s="8"/>
     </row>
     <row r="310" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G310" s="9"/>
+      <c r="G310" s="8"/>
     </row>
     <row r="311" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G311" s="9"/>
+      <c r="G311" s="8"/>
     </row>
     <row r="312" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G312" s="9"/>
+      <c r="G312" s="8"/>
     </row>
     <row r="313" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G313" s="9"/>
+      <c r="G313" s="8"/>
     </row>
     <row r="314" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G314" s="9"/>
+      <c r="G314" s="8"/>
     </row>
     <row r="315" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G315" s="9"/>
+      <c r="G315" s="8"/>
     </row>
     <row r="316" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G316" s="9"/>
+      <c r="G316" s="8"/>
     </row>
     <row r="317" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G317" s="9"/>
+      <c r="G317" s="8"/>
     </row>
     <row r="318" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G318" s="9"/>
+      <c r="G318" s="8"/>
     </row>
     <row r="319" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G319" s="9"/>
+      <c r="G319" s="8"/>
     </row>
     <row r="320" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G320" s="9"/>
+      <c r="G320" s="8"/>
     </row>
     <row r="321" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G321" s="9"/>
+      <c r="G321" s="8"/>
     </row>
     <row r="322" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G322" s="9"/>
+      <c r="G322" s="8"/>
     </row>
     <row r="323" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G323" s="9"/>
+      <c r="G323" s="8"/>
     </row>
     <row r="324" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G324" s="9"/>
+      <c r="G324" s="8"/>
     </row>
     <row r="325" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G325" s="9"/>
+      <c r="G325" s="8"/>
     </row>
     <row r="326" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G326" s="9"/>
+      <c r="G326" s="8"/>
     </row>
     <row r="327" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G327" s="9"/>
+      <c r="G327" s="8"/>
     </row>
     <row r="328" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G328" s="9"/>
+      <c r="G328" s="8"/>
     </row>
     <row r="329" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G329" s="9"/>
+      <c r="G329" s="8"/>
     </row>
     <row r="330" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G330" s="9"/>
+      <c r="G330" s="8"/>
     </row>
     <row r="331" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G331" s="9"/>
+      <c r="G331" s="8"/>
     </row>
     <row r="332" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G332" s="9"/>
+      <c r="G332" s="8"/>
     </row>
     <row r="333" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G333" s="9"/>
+      <c r="G333" s="8"/>
     </row>
     <row r="334" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G334" s="9"/>
+      <c r="G334" s="8"/>
     </row>
     <row r="335" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G335" s="9"/>
+      <c r="G335" s="8"/>
     </row>
     <row r="336" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G336" s="9"/>
+      <c r="G336" s="8"/>
     </row>
     <row r="337" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G337" s="9"/>
+      <c r="G337" s="8"/>
     </row>
     <row r="338" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G338" s="9"/>
+      <c r="G338" s="8"/>
     </row>
     <row r="339" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G339" s="9"/>
+      <c r="G339" s="8"/>
     </row>
     <row r="340" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G340" s="9"/>
+      <c r="G340" s="8"/>
     </row>
     <row r="341" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G341" s="9"/>
+      <c r="G341" s="8"/>
     </row>
     <row r="342" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G342" s="9"/>
+      <c r="G342" s="8"/>
     </row>
     <row r="343" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G343" s="9"/>
+      <c r="G343" s="8"/>
     </row>
     <row r="344" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G344" s="9"/>
+      <c r="G344" s="8"/>
     </row>
     <row r="345" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G345" s="9"/>
+      <c r="G345" s="8"/>
     </row>
     <row r="346" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G346" s="9"/>
+      <c r="G346" s="8"/>
     </row>
     <row r="347" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G347" s="9"/>
+      <c r="G347" s="8"/>
     </row>
     <row r="348" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G348" s="9"/>
+      <c r="G348" s="8"/>
     </row>
     <row r="349" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G349" s="9"/>
+      <c r="G349" s="8"/>
     </row>
     <row r="350" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G350" s="9"/>
+      <c r="G350" s="8"/>
     </row>
     <row r="351" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G351" s="9"/>
+      <c r="G351" s="8"/>
     </row>
     <row r="352" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G352" s="9"/>
+      <c r="G352" s="8"/>
     </row>
     <row r="353" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G353" s="9"/>
+      <c r="G353" s="8"/>
     </row>
     <row r="354" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G354" s="9"/>
+      <c r="G354" s="8"/>
     </row>
     <row r="355" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G355" s="9"/>
+      <c r="G355" s="8"/>
     </row>
     <row r="356" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G356" s="9"/>
+      <c r="G356" s="8"/>
     </row>
     <row r="357" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G357" s="9"/>
+      <c r="G357" s="8"/>
     </row>
     <row r="358" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G358" s="9"/>
+      <c r="G358" s="8"/>
     </row>
     <row r="359" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G359" s="9"/>
+      <c r="G359" s="8"/>
     </row>
     <row r="360" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G360" s="9"/>
+      <c r="G360" s="8"/>
     </row>
     <row r="361" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G361" s="9"/>
+      <c r="G361" s="8"/>
     </row>
     <row r="362" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G362" s="9"/>
+      <c r="G362" s="8"/>
     </row>
     <row r="363" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G363" s="9"/>
+      <c r="G363" s="8"/>
     </row>
     <row r="364" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G364" s="9"/>
+      <c r="G364" s="8"/>
     </row>
     <row r="365" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G365" s="9"/>
+      <c r="G365" s="8"/>
     </row>
     <row r="366" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G366" s="9"/>
+      <c r="G366" s="8"/>
     </row>
     <row r="367" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G367" s="9"/>
+      <c r="G367" s="8"/>
     </row>
     <row r="368" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G368" s="9"/>
+      <c r="G368" s="8"/>
     </row>
     <row r="369" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G369" s="9"/>
+      <c r="G369" s="8"/>
     </row>
     <row r="370" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G370" s="9"/>
+      <c r="G370" s="8"/>
     </row>
     <row r="371" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G371" s="9"/>
+      <c r="G371" s="8"/>
     </row>
     <row r="372" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G372" s="9"/>
+      <c r="G372" s="8"/>
     </row>
     <row r="373" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G373" s="9"/>
+      <c r="G373" s="8"/>
     </row>
     <row r="374" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G374" s="9"/>
+      <c r="G374" s="8"/>
     </row>
     <row r="375" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G375" s="9"/>
+      <c r="G375" s="8"/>
     </row>
     <row r="376" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G376" s="9"/>
+      <c r="G376" s="8"/>
     </row>
     <row r="377" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G377" s="9"/>
+      <c r="G377" s="8"/>
     </row>
     <row r="378" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G378" s="9"/>
+      <c r="G378" s="8"/>
     </row>
     <row r="379" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G379" s="9"/>
+      <c r="G379" s="8"/>
     </row>
     <row r="380" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G380" s="9"/>
+      <c r="G380" s="8"/>
     </row>
     <row r="381" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G381" s="9"/>
+      <c r="G381" s="8"/>
     </row>
     <row r="382" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G382" s="9"/>
+      <c r="G382" s="8"/>
     </row>
     <row r="383" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G383" s="9"/>
+      <c r="G383" s="8"/>
     </row>
     <row r="384" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G384" s="9"/>
+      <c r="G384" s="8"/>
     </row>
     <row r="385" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G385" s="9"/>
+      <c r="G385" s="8"/>
     </row>
     <row r="386" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G386" s="9"/>
+      <c r="G386" s="8"/>
     </row>
     <row r="387" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G387" s="9"/>
+      <c r="G387" s="8"/>
     </row>
     <row r="388" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G388" s="9"/>
+      <c r="G388" s="8"/>
     </row>
     <row r="389" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G389" s="9"/>
+      <c r="G389" s="8"/>
     </row>
     <row r="390" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G390" s="9"/>
+      <c r="G390" s="8"/>
     </row>
     <row r="391" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G391" s="9"/>
+      <c r="G391" s="8"/>
     </row>
     <row r="392" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G392" s="9"/>
+      <c r="G392" s="8"/>
     </row>
     <row r="393" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G393" s="9"/>
+      <c r="G393" s="8"/>
     </row>
     <row r="394" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G394" s="9"/>
+      <c r="G394" s="8"/>
     </row>
     <row r="395" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G395" s="9"/>
+      <c r="G395" s="8"/>
     </row>
     <row r="396" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G396" s="9"/>
+      <c r="G396" s="8"/>
     </row>
     <row r="397" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G397" s="9"/>
+      <c r="G397" s="8"/>
     </row>
     <row r="398" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G398" s="9"/>
+      <c r="G398" s="8"/>
     </row>
     <row r="399" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G399" s="9"/>
+      <c r="G399" s="8"/>
     </row>
     <row r="400" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G400" s="9"/>
+      <c r="G400" s="8"/>
     </row>
     <row r="401" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G401" s="9"/>
+      <c r="G401" s="8"/>
     </row>
     <row r="402" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G402" s="9"/>
+      <c r="G402" s="8"/>
     </row>
     <row r="403" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G403" s="9"/>
+      <c r="G403" s="8"/>
     </row>
     <row r="404" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G404" s="9"/>
+      <c r="G404" s="8"/>
     </row>
     <row r="405" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G405" s="9"/>
+      <c r="G405" s="8"/>
     </row>
     <row r="406" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G406" s="9"/>
+      <c r="G406" s="8"/>
     </row>
     <row r="407" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G407" s="9"/>
+      <c r="G407" s="8"/>
     </row>
     <row r="408" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G408" s="9"/>
+      <c r="G408" s="8"/>
     </row>
     <row r="409" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G409" s="9"/>
+      <c r="G409" s="8"/>
     </row>
     <row r="410" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G410" s="9"/>
+      <c r="G410" s="8"/>
     </row>
     <row r="411" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G411" s="9"/>
+      <c r="G411" s="8"/>
     </row>
     <row r="412" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G412" s="9"/>
+      <c r="G412" s="8"/>
     </row>
     <row r="413" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G413" s="9"/>
+      <c r="G413" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7134,13 +7134,13 @@
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="10">
         <v>200</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -7148,13 +7148,13 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="10">
         <v>50</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7162,13 +7162,13 @@
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="10">
         <v>120</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7176,13 +7176,13 @@
       <c r="A5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="10">
         <v>300</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
     </row>
@@ -7197,17 +7197,17 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
     </row>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4FE0E50-9D0A-4015-91E8-36F496D2CF99}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{492A1C7F-ADE0-401E-B0BD-2376AC9B43E2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1323" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="97">
   <si>
     <t>POD</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>LONDON GATEWAY</t>
+  </si>
+  <si>
+    <t>14 DIAS</t>
   </si>
 </sst>
 </file>
@@ -337,10 +340,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="165" formatCode="[$-409]mmm\-yy;@"/>
-    <numFmt numFmtId="166" formatCode="0\ &quot;DÍAS&quot;"/>
-    <numFmt numFmtId="167" formatCode="[$EUR]\ #,##0"/>
-    <numFmt numFmtId="172" formatCode="[$USD]\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="[$-409]mmm\-yy;@"/>
+    <numFmt numFmtId="165" formatCode="0\ &quot;DÍAS&quot;"/>
+    <numFmt numFmtId="166" formatCode="[$EUR]\ #,##0"/>
+    <numFmt numFmtId="167" formatCode="[$USD]\ #,##0"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -441,7 +444,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -470,15 +473,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="9">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5938,8 +5941,8 @@
       <c r="F176" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G176" s="8">
-        <v>14</v>
+      <c r="G176" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H176" s="7" t="s">
         <v>85</v>
@@ -5967,8 +5970,8 @@
       <c r="F177" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G177" s="8">
-        <v>14</v>
+      <c r="G177" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H177" s="7" t="s">
         <v>85</v>
@@ -5996,8 +5999,8 @@
       <c r="F178" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G178" s="8">
-        <v>14</v>
+      <c r="G178" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H178" s="7" t="s">
         <v>85</v>
@@ -6025,8 +6028,8 @@
       <c r="F179" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G179" s="8">
-        <v>14</v>
+      <c r="G179" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H179" s="7" t="s">
         <v>85</v>
@@ -6054,8 +6057,8 @@
       <c r="F180" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G180" s="8">
-        <v>14</v>
+      <c r="G180" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H180" s="7" t="s">
         <v>85</v>
@@ -6083,8 +6086,8 @@
       <c r="F181" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G181" s="8">
-        <v>14</v>
+      <c r="G181" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H181" s="7" t="s">
         <v>85</v>
@@ -6112,8 +6115,8 @@
       <c r="F182" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G182" s="8">
-        <v>14</v>
+      <c r="G182" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H182" s="7" t="s">
         <v>85</v>
@@ -6141,8 +6144,8 @@
       <c r="F183" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G183" s="8">
-        <v>14</v>
+      <c r="G183" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H183" s="7" t="s">
         <v>85</v>
@@ -6170,8 +6173,8 @@
       <c r="F184" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G184" s="8">
-        <v>14</v>
+      <c r="G184" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H184" s="7" t="s">
         <v>85</v>
@@ -6199,8 +6202,8 @@
       <c r="F185" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G185" s="8">
-        <v>14</v>
+      <c r="G185" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H185" s="7" t="s">
         <v>85</v>
@@ -6228,8 +6231,8 @@
       <c r="F186" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G186" s="8">
-        <v>14</v>
+      <c r="G186" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H186" s="7" t="s">
         <v>85</v>
@@ -6257,8 +6260,8 @@
       <c r="F187" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G187" s="8">
-        <v>14</v>
+      <c r="G187" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H187" s="7" t="s">
         <v>85</v>
@@ -6286,8 +6289,8 @@
       <c r="F188" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G188" s="8">
-        <v>14</v>
+      <c r="G188" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H188" s="7" t="s">
         <v>85</v>
@@ -6315,8 +6318,8 @@
       <c r="F189" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G189" s="8">
-        <v>14</v>
+      <c r="G189" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H189" s="7" t="s">
         <v>85</v>
@@ -6344,8 +6347,8 @@
       <c r="F190" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G190" s="8">
-        <v>14</v>
+      <c r="G190" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H190" s="7" t="s">
         <v>85</v>
@@ -6373,8 +6376,8 @@
       <c r="F191" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G191" s="8">
-        <v>14</v>
+      <c r="G191" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H191" s="7" t="s">
         <v>85</v>
@@ -6402,8 +6405,8 @@
       <c r="F192" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G192" s="8">
-        <v>14</v>
+      <c r="G192" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H192" s="7" t="s">
         <v>85</v>
@@ -6431,8 +6434,8 @@
       <c r="F193" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="G193" s="8">
-        <v>14</v>
+      <c r="G193" s="7" t="s">
+        <v>96</v>
       </c>
       <c r="H193" s="7" t="s">
         <v>85</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="65" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A100804-CE81-4CE7-A55D-6769E90E0506}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E11E9F20-1F8C-4614-B4A3-7190B805537D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="98">
   <si>
     <t>POD</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>14 DIAS</t>
+  </si>
+  <si>
+    <t>16 al 22 de marzo</t>
+  </si>
+  <si>
+    <t>15 al 21 de marzo</t>
   </si>
 </sst>
 </file>
@@ -840,7 +846,7 @@
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4296,294 +4302,2550 @@
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G112" s="8"/>
-    </row>
-    <row r="113" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G113" s="8"/>
-    </row>
-    <row r="114" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G114" s="8"/>
-    </row>
-    <row r="115" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G115" s="8"/>
-    </row>
-    <row r="116" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G116" s="8"/>
-    </row>
-    <row r="117" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G117" s="8"/>
-    </row>
-    <row r="118" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G118" s="8"/>
-    </row>
-    <row r="119" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G119" s="8"/>
-    </row>
-    <row r="120" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G120" s="8"/>
-    </row>
-    <row r="121" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G121" s="8"/>
-    </row>
-    <row r="122" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G122" s="8"/>
-    </row>
-    <row r="123" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G123" s="8"/>
-    </row>
-    <row r="124" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G124" s="8"/>
-    </row>
-    <row r="125" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G125" s="8"/>
-    </row>
-    <row r="126" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G126" s="8"/>
-    </row>
-    <row r="127" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G127" s="8"/>
-    </row>
-    <row r="128" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G128" s="8"/>
-    </row>
-    <row r="129" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G129" s="8"/>
-    </row>
-    <row r="130" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G130" s="8"/>
-    </row>
-    <row r="131" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G131" s="8"/>
-    </row>
-    <row r="132" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G132" s="8"/>
-    </row>
-    <row r="133" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G133" s="8"/>
-    </row>
-    <row r="134" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G134" s="8"/>
-    </row>
-    <row r="135" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G135" s="8"/>
-    </row>
-    <row r="136" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G136" s="8"/>
-    </row>
-    <row r="137" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G137" s="8"/>
-    </row>
-    <row r="138" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G138" s="8"/>
-    </row>
-    <row r="139" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G139" s="8"/>
-    </row>
-    <row r="140" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G140" s="8"/>
-    </row>
-    <row r="141" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G141" s="8"/>
-    </row>
-    <row r="142" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G142" s="8"/>
-    </row>
-    <row r="143" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G143" s="8"/>
-    </row>
-    <row r="144" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G144" s="8"/>
-    </row>
-    <row r="145" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G145" s="8"/>
-    </row>
-    <row r="146" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G146" s="8"/>
-    </row>
-    <row r="147" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G147" s="8"/>
-    </row>
-    <row r="148" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G148" s="8"/>
-    </row>
-    <row r="149" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G149" s="8"/>
-    </row>
-    <row r="150" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G150" s="8"/>
-    </row>
-    <row r="151" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G151" s="8"/>
-    </row>
-    <row r="152" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G152" s="8"/>
-    </row>
-    <row r="153" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G153" s="8"/>
-    </row>
-    <row r="154" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G154" s="8"/>
-    </row>
-    <row r="155" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G155" s="8"/>
-    </row>
-    <row r="156" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G156" s="8"/>
-    </row>
-    <row r="157" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G157" s="8"/>
-    </row>
-    <row r="158" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G158" s="8"/>
-    </row>
-    <row r="159" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G159" s="8"/>
-    </row>
-    <row r="160" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G160" s="8"/>
-    </row>
-    <row r="161" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G161" s="8"/>
-    </row>
-    <row r="162" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G162" s="8"/>
-    </row>
-    <row r="163" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G163" s="8"/>
-    </row>
-    <row r="164" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G164" s="8"/>
-    </row>
-    <row r="165" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G165" s="8"/>
-    </row>
-    <row r="166" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G166" s="8"/>
-    </row>
-    <row r="167" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G167" s="8"/>
-    </row>
-    <row r="168" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G168" s="8"/>
-    </row>
-    <row r="169" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G169" s="8"/>
-    </row>
-    <row r="170" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G170" s="8"/>
-    </row>
-    <row r="171" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G171" s="8"/>
-    </row>
-    <row r="172" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G172" s="8"/>
-    </row>
-    <row r="173" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G173" s="8"/>
-    </row>
-    <row r="174" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G174" s="8"/>
-    </row>
-    <row r="175" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G175" s="8"/>
-    </row>
-    <row r="176" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G176" s="8"/>
-    </row>
-    <row r="177" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G177" s="8"/>
-    </row>
-    <row r="178" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G178" s="8"/>
-    </row>
-    <row r="179" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G179" s="8"/>
-    </row>
-    <row r="180" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G180" s="8"/>
-    </row>
-    <row r="181" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G181" s="8"/>
-    </row>
-    <row r="182" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G182" s="8"/>
-    </row>
-    <row r="183" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G183" s="8"/>
-    </row>
-    <row r="184" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G184" s="8"/>
-    </row>
-    <row r="185" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G185" s="8"/>
-    </row>
-    <row r="186" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G186" s="8"/>
-    </row>
-    <row r="187" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G187" s="8"/>
-    </row>
-    <row r="188" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G188" s="8"/>
-    </row>
-    <row r="189" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G189" s="8"/>
-    </row>
-    <row r="190" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G190" s="8"/>
-    </row>
-    <row r="191" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G191" s="8"/>
-    </row>
-    <row r="192" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G192" s="8"/>
-    </row>
-    <row r="193" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G193" s="8"/>
-    </row>
-    <row r="194" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G194" s="8"/>
-    </row>
-    <row r="195" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G195" s="8"/>
-    </row>
-    <row r="196" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G196" s="8"/>
-    </row>
-    <row r="197" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G197" s="8"/>
-    </row>
-    <row r="198" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G198" s="8"/>
-    </row>
-    <row r="199" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G199" s="8"/>
-    </row>
-    <row r="200" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G200" s="8"/>
-    </row>
-    <row r="201" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G201" s="8"/>
-    </row>
-    <row r="202" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G202" s="8"/>
-    </row>
-    <row r="203" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G203" s="8"/>
-    </row>
-    <row r="204" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="A112" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B112" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D112" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E112" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G112" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H112" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I112" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B113" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D113" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E113" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H113" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I113" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B114" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D114" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E114" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H114" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I114" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B115" t="s">
+        <v>15</v>
+      </c>
+      <c r="C115" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D115" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E115" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H115" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B116" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D116" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E116" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G116" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D117" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E117" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B118" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D118" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E118" s="11">
+        <v>2990</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H118" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I118" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B119" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D119" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E119" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G119" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I119" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E120" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G120" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H120" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I120" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D121" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E121" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G121" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H121" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I121" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B122" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D122" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E122" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H122" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I122" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B123" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D123" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E123" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G123" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I123" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D124" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E124" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G124" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I124" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B125" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D125" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E125" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G125" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I125" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B126" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D126" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E126" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G126" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H126" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I126" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B127" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D127" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E127" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G127" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H127" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I127" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B128" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D128" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E128" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G128" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H128" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I128" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B129" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="11">
+        <v>2720</v>
+      </c>
+      <c r="D129" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E129" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G129" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H129" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I129" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B130" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" s="11"/>
+      <c r="D130" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E130" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G130" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I130" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B131" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E131" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G131" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H131" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I131" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B132" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E132" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G132" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B133" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E133" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H133" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I133" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B134" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E134" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G134" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B135" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" s="11"/>
+      <c r="D135" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E135" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G135" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I135" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B136" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E136" s="11">
+        <v>3510</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G136" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B137" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E137" s="11">
+        <v>3510</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G137" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H137" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I137" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B138" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E138" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G138" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B139" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E139" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G139" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H139" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I139" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B140" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E140" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B141" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E141" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G141" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H141" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I141" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B142" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E142" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E143" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G143" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B144" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="11"/>
+      <c r="D144" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E144" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B145" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="11"/>
+      <c r="D145" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E145" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G145" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E146" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E147" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G147" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E148" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B149" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E149" s="11">
+        <v>3510</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G149" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B150" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="11"/>
+      <c r="D150" s="11">
+        <v>3200</v>
+      </c>
+      <c r="E150" s="11">
+        <v>3620</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B151" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="11"/>
+      <c r="D151" s="11">
+        <v>3200</v>
+      </c>
+      <c r="E151" s="11">
+        <v>3620</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G151" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B152" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11">
+        <v>3350</v>
+      </c>
+      <c r="E152" s="11">
+        <v>3830</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G152" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E153" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G153" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" s="11"/>
+      <c r="D154" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E154" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G154" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I154" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E155" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G155" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B156" t="s">
+        <v>15</v>
+      </c>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E156" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G156" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="11"/>
+      <c r="D157" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E157" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G157" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B158" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158" s="11">
+        <v>2630</v>
+      </c>
+      <c r="D158" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E158" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G158" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B159" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D159" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E159" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G159" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B160" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D160" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E160" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B161" t="s">
+        <v>15</v>
+      </c>
+      <c r="C161" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D161" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E161" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G161" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D162" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E162" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G162" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B163" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D163" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E163" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G163" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B164" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D164" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E164" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G164" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B165" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165" s="11"/>
+      <c r="D165" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E165" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G165" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B166" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166" s="11"/>
+      <c r="D166" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E166" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G166" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B167" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167" s="11"/>
+      <c r="D167" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E167" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G167" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H167" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I167" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B168" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="11"/>
+      <c r="D168" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E168" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G168" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B169" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" s="11"/>
+      <c r="D169" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E169" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G169" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H169" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I169" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B170" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" s="11"/>
+      <c r="D170" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E170" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G170" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I170" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B171" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="11"/>
+      <c r="D171" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E171" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G171" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I171" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" s="11"/>
+      <c r="D172" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E172" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G172" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I172" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="11"/>
+      <c r="D173" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E173" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G173" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I173" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B174" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="11"/>
+      <c r="D174" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E174" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G174" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I174" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B175" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175" s="11"/>
+      <c r="D175" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E175" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G175" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I175" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" s="11"/>
+      <c r="D176" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E176" s="11">
+        <v>3360</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G176" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H176" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I176" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177" s="11"/>
+      <c r="D177" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E177" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G177" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I177" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="11"/>
+      <c r="D178" s="11">
+        <v>2840</v>
+      </c>
+      <c r="E178" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G178" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I178" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B179" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" s="11"/>
+      <c r="D179" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E179" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G179" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H179" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="11"/>
+      <c r="D180" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E180" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G180" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" s="11"/>
+      <c r="D181" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E181" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G181" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H181" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182" s="11"/>
+      <c r="D182" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E182" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G182" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H182" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B183" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="11"/>
+      <c r="D183" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E183" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G183" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H183" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B184" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" s="11"/>
+      <c r="D184" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E184" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G184" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H184" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B185" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185" s="11"/>
+      <c r="D185" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E185" s="11">
+        <v>3280</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G185" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H185" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B186" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186" s="11"/>
+      <c r="D186" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E186" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G186" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H186" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B187" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187" s="11"/>
+      <c r="D187" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E187" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G187" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H187" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B188" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188" s="11"/>
+      <c r="D188" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E188" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G188" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H188" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B189" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="11"/>
+      <c r="D189" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E189" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G189" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H189" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B190" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="11"/>
+      <c r="D190" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E190" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G190" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H190" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B191" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="11"/>
+      <c r="D191" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E191" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G191" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B192" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192" s="11"/>
+      <c r="D192" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E192" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G192" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H192" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B193" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="11"/>
+      <c r="D193" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E193" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G193" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H193" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B194" t="s">
+        <v>15</v>
+      </c>
+      <c r="C194" s="11"/>
+      <c r="D194" s="11">
+        <v>2980</v>
+      </c>
+      <c r="E194" s="11">
+        <v>3380</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G194" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B195" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="11"/>
+      <c r="D195" s="11">
+        <v>2980</v>
+      </c>
+      <c r="E195" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G195" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H195" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B196" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196" s="11"/>
+      <c r="D196" s="11">
+        <v>2980</v>
+      </c>
+      <c r="E196" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G196" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H196" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B197" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197" s="11"/>
+      <c r="D197" s="11">
+        <v>2980</v>
+      </c>
+      <c r="E197" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G197" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H197" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B198" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="11"/>
+      <c r="D198" s="11">
+        <v>3170</v>
+      </c>
+      <c r="E198" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G198" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H198" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B199" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="11"/>
+      <c r="D199" s="11">
+        <v>2840</v>
+      </c>
+      <c r="E199" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G199" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B200" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" s="11"/>
+      <c r="D200" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E200" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G200" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B201" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="11"/>
+      <c r="D201" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E201" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G201" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B202" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" s="11"/>
+      <c r="D202" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E202" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G202" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H202" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B203" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="11"/>
+      <c r="D203" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E203" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G203" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="H203" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G204" s="8"/>
     </row>
-    <row r="205" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G205" s="8"/>
     </row>
-    <row r="206" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G206" s="8"/>
     </row>
-    <row r="207" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G207" s="8"/>
     </row>
-    <row r="208" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="G208" s="8"/>
     </row>
     <row r="209" spans="7:7" x14ac:dyDescent="0.25">

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E11E9F20-1F8C-4614-B4A3-7190B805537D}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{995CF885-3AEE-4E7C-9D72-6FD6ECF2F105}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="136">
   <si>
     <t>POD</t>
   </si>
@@ -336,6 +336,120 @@
   </si>
   <si>
     <t>15 al 21 de marzo</t>
+  </si>
+  <si>
+    <t>JAKARTA</t>
+  </si>
+  <si>
+    <t>PANJANG</t>
+  </si>
+  <si>
+    <t>SEMARANG</t>
+  </si>
+  <si>
+    <t>SURABAYA</t>
+  </si>
+  <si>
+    <t>CHENNAI</t>
+  </si>
+  <si>
+    <t>MUNDRA</t>
+  </si>
+  <si>
+    <t>NHAVA SHEVA</t>
+  </si>
+  <si>
+    <t>NAGOYA</t>
+  </si>
+  <si>
+    <t>OSAKA</t>
+  </si>
+  <si>
+    <t>TOKYO</t>
+  </si>
+  <si>
+    <t>KOBE</t>
+  </si>
+  <si>
+    <t>YOKOHAMA</t>
+  </si>
+  <si>
+    <t>BUSAN NEW PORT</t>
+  </si>
+  <si>
+    <t>KWANGYANG</t>
+  </si>
+  <si>
+    <t>PUSAN</t>
+  </si>
+  <si>
+    <t>PENANG</t>
+  </si>
+  <si>
+    <t>PASIR GUDANG,JOHOR</t>
+  </si>
+  <si>
+    <t>PORT KLANG NORTH PORT</t>
+  </si>
+  <si>
+    <t>SINGAPORE</t>
+  </si>
+  <si>
+    <t>BANGKOK</t>
+  </si>
+  <si>
+    <t>LAEM CHABANG</t>
+  </si>
+  <si>
+    <t>LAT KRABANG</t>
+  </si>
+  <si>
+    <t>CAT LAI PORT HOCHIMINH</t>
+  </si>
+  <si>
+    <t>CAI MEP TCIT</t>
+  </si>
+  <si>
+    <t>DA NANG</t>
+  </si>
+  <si>
+    <t>HAIPHONG</t>
+  </si>
+  <si>
+    <t>MANILA NORTH PORT</t>
+  </si>
+  <si>
+    <t>DAVAO</t>
+  </si>
+  <si>
+    <t>JAIPUR</t>
+  </si>
+  <si>
+    <t>COLOMBO</t>
+  </si>
+  <si>
+    <t>KARACHI</t>
+  </si>
+  <si>
+    <t>BELAWAN</t>
+  </si>
+  <si>
+    <t>LUDHIANA</t>
+  </si>
+  <si>
+    <t>JEBEL ALI</t>
+  </si>
+  <si>
+    <t>GURGAON (GARHI HARSARU)</t>
+  </si>
+  <si>
+    <t>DELHI-TUGHLAKABAD</t>
+  </si>
+  <si>
+    <t>DELHI (ICD SONIPAT)</t>
+  </si>
+  <si>
+    <t>16 al 31 de marzo</t>
   </si>
 </sst>
 </file>
@@ -6834,387 +6948,1569 @@
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G204" s="8"/>
+      <c r="A204" t="s">
+        <v>98</v>
+      </c>
+      <c r="B204" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" s="11"/>
+      <c r="D204" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E204" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G204" s="8">
+        <v>18</v>
+      </c>
+      <c r="H204" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G205" s="8"/>
+      <c r="A205" t="s">
+        <v>99</v>
+      </c>
+      <c r="B205" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="11"/>
+      <c r="D205" s="11">
+        <v>3840</v>
+      </c>
+      <c r="E205" s="11">
+        <v>3840</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G205" s="8">
+        <v>18</v>
+      </c>
+      <c r="H205" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I205" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G206" s="8"/>
+      <c r="A206" t="s">
+        <v>100</v>
+      </c>
+      <c r="B206" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="11"/>
+      <c r="D206" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E206" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G206" s="8">
+        <v>18</v>
+      </c>
+      <c r="H206" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G207" s="8"/>
+      <c r="A207" t="s">
+        <v>101</v>
+      </c>
+      <c r="B207" t="s">
+        <v>15</v>
+      </c>
+      <c r="C207" s="11"/>
+      <c r="D207" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E207" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G207" s="8">
+        <v>18</v>
+      </c>
+      <c r="H207" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="G208" s="8"/>
-    </row>
-    <row r="209" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G209" s="8"/>
-    </row>
-    <row r="210" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G210" s="8"/>
-    </row>
-    <row r="211" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G211" s="8"/>
-    </row>
-    <row r="212" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G212" s="8"/>
-    </row>
-    <row r="213" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G213" s="8"/>
-    </row>
-    <row r="214" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G214" s="8"/>
-    </row>
-    <row r="215" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G215" s="8"/>
-    </row>
-    <row r="216" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G216" s="8"/>
-    </row>
-    <row r="217" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G217" s="8"/>
-    </row>
-    <row r="218" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G218" s="8"/>
-    </row>
-    <row r="219" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G219" s="8"/>
-    </row>
-    <row r="220" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G220" s="8"/>
-    </row>
-    <row r="221" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G221" s="8"/>
-    </row>
-    <row r="222" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G222" s="8"/>
-    </row>
-    <row r="223" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G223" s="8"/>
-    </row>
-    <row r="224" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G224" s="8"/>
-    </row>
-    <row r="225" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G225" s="8"/>
-    </row>
-    <row r="226" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G226" s="8"/>
-    </row>
-    <row r="227" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G227" s="8"/>
-    </row>
-    <row r="228" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G228" s="8"/>
-    </row>
-    <row r="229" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G229" s="8"/>
-    </row>
-    <row r="230" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G230" s="8"/>
-    </row>
-    <row r="231" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G231" s="8"/>
-    </row>
-    <row r="232" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G232" s="8"/>
-    </row>
-    <row r="233" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G233" s="8"/>
-    </row>
-    <row r="234" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G234" s="8"/>
-    </row>
-    <row r="235" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G235" s="8"/>
-    </row>
-    <row r="236" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G236" s="8"/>
-    </row>
-    <row r="237" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G237" s="8"/>
-    </row>
-    <row r="238" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G238" s="8"/>
-    </row>
-    <row r="239" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G239" s="8"/>
-    </row>
-    <row r="240" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G240" s="8"/>
-    </row>
-    <row r="241" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G241" s="8"/>
-    </row>
-    <row r="242" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>102</v>
+      </c>
+      <c r="B208" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" s="11"/>
+      <c r="D208" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E208" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G208" s="8">
+        <v>18</v>
+      </c>
+      <c r="H208" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>103</v>
+      </c>
+      <c r="B209" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" s="11"/>
+      <c r="D209" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E209" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G209" s="8">
+        <v>18</v>
+      </c>
+      <c r="H209" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>104</v>
+      </c>
+      <c r="B210" t="s">
+        <v>15</v>
+      </c>
+      <c r="C210" s="11"/>
+      <c r="D210" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E210" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G210" s="8">
+        <v>18</v>
+      </c>
+      <c r="H210" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>105</v>
+      </c>
+      <c r="B211" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" s="11"/>
+      <c r="D211" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E211" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F211" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G211" s="8">
+        <v>18</v>
+      </c>
+      <c r="H211" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>106</v>
+      </c>
+      <c r="B212" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" s="11"/>
+      <c r="D212" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E212" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G212" s="8">
+        <v>18</v>
+      </c>
+      <c r="H212" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>107</v>
+      </c>
+      <c r="B213" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" s="11"/>
+      <c r="D213" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E213" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G213" s="8">
+        <v>18</v>
+      </c>
+      <c r="H213" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>108</v>
+      </c>
+      <c r="B214" t="s">
+        <v>15</v>
+      </c>
+      <c r="C214" s="11"/>
+      <c r="D214" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E214" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G214" s="8">
+        <v>18</v>
+      </c>
+      <c r="H214" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I214" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>109</v>
+      </c>
+      <c r="B215" t="s">
+        <v>15</v>
+      </c>
+      <c r="C215" s="11"/>
+      <c r="D215" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E215" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G215" s="8">
+        <v>18</v>
+      </c>
+      <c r="H215" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I215" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>110</v>
+      </c>
+      <c r="B216" t="s">
+        <v>15</v>
+      </c>
+      <c r="C216" s="11"/>
+      <c r="D216" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E216" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G216" s="8">
+        <v>18</v>
+      </c>
+      <c r="H216" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>111</v>
+      </c>
+      <c r="B217" t="s">
+        <v>15</v>
+      </c>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11">
+        <v>3470</v>
+      </c>
+      <c r="E217" s="11">
+        <v>3470</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G217" s="8">
+        <v>18</v>
+      </c>
+      <c r="H217" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>112</v>
+      </c>
+      <c r="B218" t="s">
+        <v>15</v>
+      </c>
+      <c r="C218" s="11"/>
+      <c r="D218" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E218" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G218" s="8">
+        <v>18</v>
+      </c>
+      <c r="H218" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>113</v>
+      </c>
+      <c r="B219" t="s">
+        <v>15</v>
+      </c>
+      <c r="C219" s="11"/>
+      <c r="D219" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E219" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G219" s="8">
+        <v>18</v>
+      </c>
+      <c r="H219" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>114</v>
+      </c>
+      <c r="B220" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="11"/>
+      <c r="D220" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E220" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G220" s="8">
+        <v>18</v>
+      </c>
+      <c r="H220" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>115</v>
+      </c>
+      <c r="B221" t="s">
+        <v>15</v>
+      </c>
+      <c r="C221" s="11"/>
+      <c r="D221" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E221" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G221" s="8">
+        <v>18</v>
+      </c>
+      <c r="H221" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I221" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>116</v>
+      </c>
+      <c r="B222" t="s">
+        <v>15</v>
+      </c>
+      <c r="C222" s="11"/>
+      <c r="D222" s="11">
+        <v>3730</v>
+      </c>
+      <c r="E222" s="11">
+        <v>3730</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G222" s="8">
+        <v>18</v>
+      </c>
+      <c r="H222" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>117</v>
+      </c>
+      <c r="B223" t="s">
+        <v>15</v>
+      </c>
+      <c r="C223" s="11"/>
+      <c r="D223" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E223" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G223" s="8">
+        <v>18</v>
+      </c>
+      <c r="H223" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I223" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>118</v>
+      </c>
+      <c r="B224" t="s">
+        <v>15</v>
+      </c>
+      <c r="C224" s="11"/>
+      <c r="D224" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E224" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G224" s="8">
+        <v>18</v>
+      </c>
+      <c r="H224" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I224" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>119</v>
+      </c>
+      <c r="B225" t="s">
+        <v>15</v>
+      </c>
+      <c r="C225" s="11"/>
+      <c r="D225" s="11">
+        <v>3540</v>
+      </c>
+      <c r="E225" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G225" s="8">
+        <v>18</v>
+      </c>
+      <c r="H225" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I225" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>120</v>
+      </c>
+      <c r="B226" t="s">
+        <v>15</v>
+      </c>
+      <c r="C226" s="11"/>
+      <c r="D226" s="11">
+        <v>3580</v>
+      </c>
+      <c r="E226" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G226" s="8">
+        <v>18</v>
+      </c>
+      <c r="H226" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I226" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>121</v>
+      </c>
+      <c r="B227" t="s">
+        <v>15</v>
+      </c>
+      <c r="C227" s="11"/>
+      <c r="D227" s="11">
+        <v>3580</v>
+      </c>
+      <c r="E227" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G227" s="8">
+        <v>18</v>
+      </c>
+      <c r="H227" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I227" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>122</v>
+      </c>
+      <c r="B228" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="11"/>
+      <c r="D228" s="11">
+        <v>3580</v>
+      </c>
+      <c r="E228" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G228" s="8">
+        <v>18</v>
+      </c>
+      <c r="H228" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>123</v>
+      </c>
+      <c r="B229" t="s">
+        <v>15</v>
+      </c>
+      <c r="C229" s="11"/>
+      <c r="D229" s="11">
+        <v>3580</v>
+      </c>
+      <c r="E229" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G229" s="8">
+        <v>18</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>124</v>
+      </c>
+      <c r="B230" t="s">
+        <v>15</v>
+      </c>
+      <c r="C230" s="11"/>
+      <c r="D230" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E230" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G230" s="8">
+        <v>18</v>
+      </c>
+      <c r="H230" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I230" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>125</v>
+      </c>
+      <c r="B231" t="s">
+        <v>15</v>
+      </c>
+      <c r="C231" s="11"/>
+      <c r="D231" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E231" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G231" s="8">
+        <v>18</v>
+      </c>
+      <c r="H231" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I231" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>126</v>
+      </c>
+      <c r="B232" t="s">
+        <v>15</v>
+      </c>
+      <c r="C232" s="11"/>
+      <c r="D232" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E232" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G232" s="8">
+        <v>18</v>
+      </c>
+      <c r="H232" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I232" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>127</v>
+      </c>
+      <c r="B233" t="s">
+        <v>15</v>
+      </c>
+      <c r="C233" s="11"/>
+      <c r="D233" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E233" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G233" s="8">
+        <v>18</v>
+      </c>
+      <c r="H233" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I233" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>128</v>
+      </c>
+      <c r="B234" t="s">
+        <v>15</v>
+      </c>
+      <c r="C234" s="11"/>
+      <c r="D234" s="11">
+        <v>3840</v>
+      </c>
+      <c r="E234" s="11">
+        <v>3840</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G234" s="8">
+        <v>18</v>
+      </c>
+      <c r="H234" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>129</v>
+      </c>
+      <c r="B235" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235" s="11"/>
+      <c r="D235" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E235" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G235" s="8">
+        <v>18</v>
+      </c>
+      <c r="H235" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I235" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>130</v>
+      </c>
+      <c r="B236" t="s">
+        <v>15</v>
+      </c>
+      <c r="C236" s="11"/>
+      <c r="D236" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E236" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G236" s="8">
+        <v>18</v>
+      </c>
+      <c r="H236" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>131</v>
+      </c>
+      <c r="B237" t="s">
+        <v>15</v>
+      </c>
+      <c r="C237" s="11"/>
+      <c r="D237" s="11">
+        <v>3520</v>
+      </c>
+      <c r="E237" s="11">
+        <v>3520</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G237" s="8">
+        <v>18</v>
+      </c>
+      <c r="H237" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I237" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>132</v>
+      </c>
+      <c r="B238" t="s">
+        <v>15</v>
+      </c>
+      <c r="C238" s="11"/>
+      <c r="D238" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E238" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G238" s="8">
+        <v>18</v>
+      </c>
+      <c r="H238" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I238" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>133</v>
+      </c>
+      <c r="B239" t="s">
+        <v>15</v>
+      </c>
+      <c r="C239" s="11"/>
+      <c r="D239" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E239" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G239" s="8">
+        <v>18</v>
+      </c>
+      <c r="H239" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I239" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>134</v>
+      </c>
+      <c r="B240" t="s">
+        <v>15</v>
+      </c>
+      <c r="C240" s="11"/>
+      <c r="D240" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E240" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G240" s="8">
+        <v>18</v>
+      </c>
+      <c r="H240" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>126</v>
+      </c>
+      <c r="B241" t="s">
+        <v>15</v>
+      </c>
+      <c r="C241" s="11"/>
+      <c r="D241" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E241" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G241" s="8">
+        <v>18</v>
+      </c>
+      <c r="H241" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I241" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C242" s="11"/>
+      <c r="D242" s="11"/>
+      <c r="E242" s="11"/>
       <c r="G242" s="8"/>
     </row>
-    <row r="243" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C243" s="11"/>
+      <c r="D243" s="11"/>
+      <c r="E243" s="11"/>
       <c r="G243" s="8"/>
     </row>
-    <row r="244" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C244" s="11"/>
+      <c r="D244" s="11"/>
+      <c r="E244" s="11"/>
       <c r="G244" s="8"/>
     </row>
-    <row r="245" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C245" s="11"/>
+      <c r="D245" s="11"/>
+      <c r="E245" s="11"/>
       <c r="G245" s="8"/>
     </row>
-    <row r="246" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C246" s="11"/>
+      <c r="D246" s="11"/>
+      <c r="E246" s="11"/>
       <c r="G246" s="8"/>
     </row>
-    <row r="247" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C247" s="11"/>
+      <c r="D247" s="11"/>
+      <c r="E247" s="11"/>
       <c r="G247" s="8"/>
     </row>
-    <row r="248" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C248" s="11"/>
+      <c r="D248" s="11"/>
+      <c r="E248" s="11"/>
       <c r="G248" s="8"/>
     </row>
-    <row r="249" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C249" s="11"/>
+      <c r="D249" s="11"/>
+      <c r="E249" s="11"/>
       <c r="G249" s="8"/>
     </row>
-    <row r="250" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C250" s="11"/>
+      <c r="D250" s="11"/>
+      <c r="E250" s="11"/>
       <c r="G250" s="8"/>
     </row>
-    <row r="251" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C251" s="11"/>
+      <c r="D251" s="11"/>
+      <c r="E251" s="11"/>
       <c r="G251" s="8"/>
     </row>
-    <row r="252" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C252" s="11"/>
+      <c r="D252" s="11"/>
+      <c r="E252" s="11"/>
       <c r="G252" s="8"/>
     </row>
-    <row r="253" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C253" s="11"/>
+      <c r="D253" s="11"/>
+      <c r="E253" s="11"/>
       <c r="G253" s="8"/>
     </row>
-    <row r="254" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C254" s="11"/>
+      <c r="D254" s="11"/>
+      <c r="E254" s="11"/>
       <c r="G254" s="8"/>
     </row>
-    <row r="255" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C255" s="11"/>
+      <c r="D255" s="11"/>
+      <c r="E255" s="11"/>
       <c r="G255" s="8"/>
     </row>
-    <row r="256" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C256" s="11"/>
+      <c r="D256" s="11"/>
+      <c r="E256" s="11"/>
       <c r="G256" s="8"/>
     </row>
-    <row r="257" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C257" s="11"/>
+      <c r="D257" s="11"/>
+      <c r="E257" s="11"/>
       <c r="G257" s="8"/>
     </row>
-    <row r="258" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C258" s="11"/>
+      <c r="D258" s="11"/>
+      <c r="E258" s="11"/>
       <c r="G258" s="8"/>
     </row>
-    <row r="259" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C259" s="11"/>
+      <c r="D259" s="11"/>
+      <c r="E259" s="11"/>
       <c r="G259" s="8"/>
     </row>
-    <row r="260" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C260" s="11"/>
+      <c r="D260" s="11"/>
+      <c r="E260" s="11"/>
       <c r="G260" s="8"/>
     </row>
-    <row r="261" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C261" s="11"/>
+      <c r="D261" s="11"/>
+      <c r="E261" s="11"/>
       <c r="G261" s="8"/>
     </row>
-    <row r="262" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C262" s="11"/>
+      <c r="D262" s="11"/>
+      <c r="E262" s="11"/>
       <c r="G262" s="8"/>
     </row>
-    <row r="263" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C263" s="11"/>
+      <c r="D263" s="11"/>
+      <c r="E263" s="11"/>
       <c r="G263" s="8"/>
     </row>
-    <row r="264" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C264" s="11"/>
+      <c r="D264" s="11"/>
+      <c r="E264" s="11"/>
       <c r="G264" s="8"/>
     </row>
-    <row r="265" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C265" s="11"/>
+      <c r="D265" s="11"/>
+      <c r="E265" s="11"/>
       <c r="G265" s="8"/>
     </row>
-    <row r="266" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C266" s="11"/>
+      <c r="D266" s="11"/>
+      <c r="E266" s="11"/>
       <c r="G266" s="8"/>
     </row>
-    <row r="267" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C267" s="11"/>
+      <c r="D267" s="11"/>
+      <c r="E267" s="11"/>
       <c r="G267" s="8"/>
     </row>
-    <row r="268" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C268" s="11"/>
+      <c r="D268" s="11"/>
+      <c r="E268" s="11"/>
       <c r="G268" s="8"/>
     </row>
-    <row r="269" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C269" s="11"/>
+      <c r="D269" s="11"/>
+      <c r="E269" s="11"/>
       <c r="G269" s="8"/>
     </row>
-    <row r="270" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C270" s="11"/>
+      <c r="D270" s="11"/>
+      <c r="E270" s="11"/>
       <c r="G270" s="8"/>
     </row>
-    <row r="271" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C271" s="11"/>
+      <c r="D271" s="11"/>
+      <c r="E271" s="11"/>
       <c r="G271" s="8"/>
     </row>
-    <row r="272" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C272" s="11"/>
+      <c r="D272" s="11"/>
+      <c r="E272" s="11"/>
       <c r="G272" s="8"/>
     </row>
-    <row r="273" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C273" s="11"/>
+      <c r="D273" s="11"/>
+      <c r="E273" s="11"/>
       <c r="G273" s="8"/>
     </row>
-    <row r="274" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C274" s="11"/>
+      <c r="D274" s="11"/>
+      <c r="E274" s="11"/>
       <c r="G274" s="8"/>
     </row>
-    <row r="275" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C275" s="11"/>
+      <c r="D275" s="11"/>
+      <c r="E275" s="11"/>
       <c r="G275" s="8"/>
     </row>
-    <row r="276" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C276" s="11"/>
+      <c r="D276" s="11"/>
+      <c r="E276" s="11"/>
       <c r="G276" s="8"/>
     </row>
-    <row r="277" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C277" s="11"/>
+      <c r="D277" s="11"/>
+      <c r="E277" s="11"/>
       <c r="G277" s="8"/>
     </row>
-    <row r="278" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C278" s="11"/>
+      <c r="D278" s="11"/>
+      <c r="E278" s="11"/>
       <c r="G278" s="8"/>
     </row>
-    <row r="279" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C279" s="11"/>
+      <c r="D279" s="11"/>
+      <c r="E279" s="11"/>
       <c r="G279" s="8"/>
     </row>
-    <row r="280" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C280" s="11"/>
+      <c r="D280" s="11"/>
+      <c r="E280" s="11"/>
       <c r="G280" s="8"/>
     </row>
-    <row r="281" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C281" s="11"/>
+      <c r="D281" s="11"/>
+      <c r="E281" s="11"/>
       <c r="G281" s="8"/>
     </row>
-    <row r="282" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C282" s="11"/>
+      <c r="D282" s="11"/>
+      <c r="E282" s="11"/>
       <c r="G282" s="8"/>
     </row>
-    <row r="283" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C283" s="11"/>
+      <c r="D283" s="11"/>
+      <c r="E283" s="11"/>
       <c r="G283" s="8"/>
     </row>
-    <row r="284" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C284" s="11"/>
+      <c r="D284" s="11"/>
+      <c r="E284" s="11"/>
       <c r="G284" s="8"/>
     </row>
-    <row r="285" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C285" s="11"/>
+      <c r="D285" s="11"/>
+      <c r="E285" s="11"/>
       <c r="G285" s="8"/>
     </row>
-    <row r="286" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C286" s="11"/>
+      <c r="D286" s="11"/>
+      <c r="E286" s="11"/>
       <c r="G286" s="8"/>
     </row>
-    <row r="287" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C287" s="11"/>
+      <c r="D287" s="11"/>
+      <c r="E287" s="11"/>
       <c r="G287" s="8"/>
     </row>
-    <row r="288" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C288" s="11"/>
+      <c r="D288" s="11"/>
+      <c r="E288" s="11"/>
       <c r="G288" s="8"/>
     </row>
-    <row r="289" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C289" s="11"/>
+      <c r="D289" s="11"/>
+      <c r="E289" s="11"/>
       <c r="G289" s="8"/>
     </row>
-    <row r="290" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C290" s="11"/>
+      <c r="D290" s="11"/>
+      <c r="E290" s="11"/>
       <c r="G290" s="8"/>
     </row>
-    <row r="291" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C291" s="11"/>
+      <c r="D291" s="11"/>
+      <c r="E291" s="11"/>
       <c r="G291" s="8"/>
     </row>
-    <row r="292" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C292" s="11"/>
+      <c r="D292" s="11"/>
+      <c r="E292" s="11"/>
       <c r="G292" s="8"/>
     </row>
-    <row r="293" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C293" s="11"/>
+      <c r="D293" s="11"/>
+      <c r="E293" s="11"/>
       <c r="G293" s="8"/>
     </row>
-    <row r="294" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C294" s="11"/>
+      <c r="D294" s="11"/>
+      <c r="E294" s="11"/>
       <c r="G294" s="8"/>
     </row>
-    <row r="295" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C295" s="11"/>
+      <c r="D295" s="11"/>
+      <c r="E295" s="11"/>
       <c r="G295" s="8"/>
     </row>
-    <row r="296" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C296" s="11"/>
+      <c r="D296" s="11"/>
+      <c r="E296" s="11"/>
       <c r="G296" s="8"/>
     </row>
-    <row r="297" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C297" s="11"/>
+      <c r="D297" s="11"/>
+      <c r="E297" s="11"/>
       <c r="G297" s="8"/>
     </row>
-    <row r="298" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C298" s="11"/>
+      <c r="D298" s="11"/>
+      <c r="E298" s="11"/>
       <c r="G298" s="8"/>
     </row>
-    <row r="299" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C299" s="11"/>
+      <c r="D299" s="11"/>
+      <c r="E299" s="11"/>
       <c r="G299" s="8"/>
     </row>
-    <row r="300" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C300" s="11"/>
+      <c r="D300" s="11"/>
+      <c r="E300" s="11"/>
       <c r="G300" s="8"/>
     </row>
-    <row r="301" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C301" s="11"/>
+      <c r="D301" s="11"/>
+      <c r="E301" s="11"/>
       <c r="G301" s="8"/>
     </row>
-    <row r="302" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C302" s="11"/>
+      <c r="D302" s="11"/>
+      <c r="E302" s="11"/>
       <c r="G302" s="8"/>
     </row>
-    <row r="303" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C303" s="11"/>
+      <c r="D303" s="11"/>
+      <c r="E303" s="11"/>
       <c r="G303" s="8"/>
     </row>
-    <row r="304" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C304" s="11"/>
+      <c r="D304" s="11"/>
+      <c r="E304" s="11"/>
       <c r="G304" s="8"/>
     </row>
-    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C305" s="11"/>
+      <c r="D305" s="11"/>
+      <c r="E305" s="11"/>
       <c r="G305" s="8"/>
     </row>
-    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C306" s="11"/>
+      <c r="D306" s="11"/>
+      <c r="E306" s="11"/>
       <c r="G306" s="8"/>
     </row>
-    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C307" s="11"/>
+      <c r="D307" s="11"/>
+      <c r="E307" s="11"/>
       <c r="G307" s="8"/>
     </row>
-    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C308" s="11"/>
+      <c r="D308" s="11"/>
+      <c r="E308" s="11"/>
       <c r="G308" s="8"/>
     </row>
-    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C309" s="11"/>
+      <c r="D309" s="11"/>
+      <c r="E309" s="11"/>
       <c r="G309" s="8"/>
     </row>
-    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C310" s="11"/>
+      <c r="D310" s="11"/>
+      <c r="E310" s="11"/>
       <c r="G310" s="8"/>
     </row>
-    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C311" s="11"/>
+      <c r="D311" s="11"/>
+      <c r="E311" s="11"/>
       <c r="G311" s="8"/>
     </row>
-    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C312" s="11"/>
+      <c r="D312" s="11"/>
+      <c r="E312" s="11"/>
       <c r="G312" s="8"/>
     </row>
-    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C313" s="11"/>
+      <c r="D313" s="11"/>
+      <c r="E313" s="11"/>
       <c r="G313" s="8"/>
     </row>
-    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C314" s="11"/>
+      <c r="D314" s="11"/>
+      <c r="E314" s="11"/>
       <c r="G314" s="8"/>
     </row>
-    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C315" s="11"/>
+      <c r="D315" s="11"/>
+      <c r="E315" s="11"/>
       <c r="G315" s="8"/>
     </row>
-    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C316" s="11"/>
+      <c r="D316" s="11"/>
+      <c r="E316" s="11"/>
       <c r="G316" s="8"/>
     </row>
-    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C317" s="11"/>
+      <c r="D317" s="11"/>
+      <c r="E317" s="11"/>
       <c r="G317" s="8"/>
     </row>
-    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C318" s="11"/>
+      <c r="D318" s="11"/>
+      <c r="E318" s="11"/>
       <c r="G318" s="8"/>
     </row>
-    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C319" s="11"/>
+      <c r="D319" s="11"/>
+      <c r="E319" s="11"/>
       <c r="G319" s="8"/>
     </row>
-    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C320" s="11"/>
+      <c r="D320" s="11"/>
+      <c r="E320" s="11"/>
       <c r="G320" s="8"/>
     </row>
-    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C321" s="11"/>
+      <c r="D321" s="11"/>
+      <c r="E321" s="11"/>
       <c r="G321" s="8"/>
     </row>
-    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C322" s="11"/>
+      <c r="D322" s="11"/>
+      <c r="E322" s="11"/>
       <c r="G322" s="8"/>
     </row>
-    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C323" s="11"/>
+      <c r="D323" s="11"/>
+      <c r="E323" s="11"/>
       <c r="G323" s="8"/>
     </row>
-    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C324" s="11"/>
+      <c r="D324" s="11"/>
+      <c r="E324" s="11"/>
       <c r="G324" s="8"/>
     </row>
-    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C325" s="11"/>
+      <c r="D325" s="11"/>
+      <c r="E325" s="11"/>
       <c r="G325" s="8"/>
     </row>
-    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C326" s="11"/>
+      <c r="D326" s="11"/>
+      <c r="E326" s="11"/>
       <c r="G326" s="8"/>
     </row>
-    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C327" s="11"/>
+      <c r="D327" s="11"/>
+      <c r="E327" s="11"/>
       <c r="G327" s="8"/>
     </row>
-    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C328" s="11"/>
+      <c r="D328" s="11"/>
+      <c r="E328" s="11"/>
       <c r="G328" s="8"/>
     </row>
-    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C329" s="11"/>
+      <c r="D329" s="11"/>
+      <c r="E329" s="11"/>
       <c r="G329" s="8"/>
     </row>
-    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C330" s="11"/>
+      <c r="D330" s="11"/>
+      <c r="E330" s="11"/>
       <c r="G330" s="8"/>
     </row>
-    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="C331" s="11"/>
+      <c r="D331" s="11"/>
+      <c r="E331" s="11"/>
       <c r="G331" s="8"/>
     </row>
   </sheetData>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FEF9688E-0F40-4378-8996-A329B0E5206D}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C49B2CA-D1EE-4DD2-9871-17046C2B8A45}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="151">
   <si>
     <t>POD</t>
   </si>
@@ -436,6 +436,66 @@
   </si>
   <si>
     <t>20 al 31 de marzo</t>
+  </si>
+  <si>
+    <t>TIANJIN</t>
+  </si>
+  <si>
+    <t>ZHAPU</t>
+  </si>
+  <si>
+    <t>SANRONG</t>
+  </si>
+  <si>
+    <t>QINHUANGDAO</t>
+  </si>
+  <si>
+    <t>QINZHOU</t>
+  </si>
+  <si>
+    <t>WUZHOU</t>
+  </si>
+  <si>
+    <t>JIANGYIN</t>
+  </si>
+  <si>
+    <t>TAIZHOU</t>
+  </si>
+  <si>
+    <t>CHANGSHU</t>
+  </si>
+  <si>
+    <t>CHANGZHOU</t>
+  </si>
+  <si>
+    <t>JINGZHOU</t>
+  </si>
+  <si>
+    <t>KAOHSIUNG</t>
+  </si>
+  <si>
+    <t>KEELUNG</t>
+  </si>
+  <si>
+    <t>TAIPEI</t>
+  </si>
+  <si>
+    <t>TAICHUNG</t>
+  </si>
+  <si>
+    <t>TAOYUAN</t>
+  </si>
+  <si>
+    <t>23 al 28 de marzo</t>
+  </si>
+  <si>
+    <t>18 DRY / 10 NOR</t>
+  </si>
+  <si>
+    <t>17 DRY / 15 NOR</t>
+  </si>
+  <si>
+    <t>COSCO</t>
   </si>
 </sst>
 </file>
@@ -941,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I147"/>
+  <dimension ref="A1:I1644"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -4827,34 +4887,9586 @@
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="G143" s="8"/>
+      <c r="A143" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B143" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D143" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E143" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F143" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H143" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C144" s="11"/>
-      <c r="D144" s="11"/>
-      <c r="E144" s="11"/>
-      <c r="G144" s="8"/>
-    </row>
-    <row r="145" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C145" s="11"/>
-      <c r="D145" s="11"/>
-      <c r="E145" s="11"/>
-      <c r="G145" s="8"/>
-    </row>
-    <row r="146" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="G146" s="8"/>
-    </row>
-    <row r="147" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
-      <c r="G147" s="8"/>
+      <c r="A144" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B144" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D144" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E144" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H144" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B145" t="s">
+        <v>15</v>
+      </c>
+      <c r="C145" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D145" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E145" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H145" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146" t="s">
+        <v>15</v>
+      </c>
+      <c r="C146" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D146" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E146" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H146" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B147" t="s">
+        <v>15</v>
+      </c>
+      <c r="C147" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D147" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E147" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B148" t="s">
+        <v>15</v>
+      </c>
+      <c r="C148" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D148" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E148" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H148" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B149" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" s="11">
+        <v>2300</v>
+      </c>
+      <c r="D149" s="11">
+        <v>2620</v>
+      </c>
+      <c r="E149" s="11">
+        <v>2720</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B150" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D150" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E150" s="11">
+        <v>2930</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B151" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="11"/>
+      <c r="D151" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E151" s="11">
+        <v>2930</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G151" s="8">
+        <v>18</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D152" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E152" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B153" t="s">
+        <v>15</v>
+      </c>
+      <c r="C153" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D153" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E153" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B154" t="s">
+        <v>15</v>
+      </c>
+      <c r="C154" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D154" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E154" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H154" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I154" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B155" t="s">
+        <v>15</v>
+      </c>
+      <c r="C155" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D155" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E155" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B156" t="s">
+        <v>15</v>
+      </c>
+      <c r="C156" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D156" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E156" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H156" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B157" t="s">
+        <v>15</v>
+      </c>
+      <c r="C157" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D157" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E157" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B158" t="s">
+        <v>15</v>
+      </c>
+      <c r="C158" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D158" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E158" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H158" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B159" t="s">
+        <v>15</v>
+      </c>
+      <c r="C159" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D159" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E159" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H159" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B160" t="s">
+        <v>15</v>
+      </c>
+      <c r="C160" s="11">
+        <v>2510</v>
+      </c>
+      <c r="D160" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E160" s="11">
+        <v>2830</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H160" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B161" t="s">
+        <v>15</v>
+      </c>
+      <c r="C161" s="11"/>
+      <c r="D161" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E161" s="11">
+        <v>2930</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G161" s="8">
+        <v>18</v>
+      </c>
+      <c r="H161" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B162" t="s">
+        <v>15</v>
+      </c>
+      <c r="C162" s="11"/>
+      <c r="D162" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E162" s="11">
+        <v>2930</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G162" s="8">
+        <v>18</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B163" t="s">
+        <v>15</v>
+      </c>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E163" s="11">
+        <v>2930</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G163" s="8">
+        <v>18</v>
+      </c>
+      <c r="H163" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B164" t="s">
+        <v>15</v>
+      </c>
+      <c r="C164" s="11"/>
+      <c r="D164" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E164" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G164" s="8">
+        <v>18</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B165" t="s">
+        <v>15</v>
+      </c>
+      <c r="C165" s="11"/>
+      <c r="D165" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E165" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G165" s="8">
+        <v>18</v>
+      </c>
+      <c r="H165" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B166" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166" s="11"/>
+      <c r="D166" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E166" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G166" s="8">
+        <v>18</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B167" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167" s="11"/>
+      <c r="D167" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E167" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G167" s="8">
+        <v>18</v>
+      </c>
+      <c r="H167" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I167" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B168" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="11"/>
+      <c r="D168" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E168" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G168" s="8">
+        <v>18</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B169" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" s="11"/>
+      <c r="D169" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E169" s="11">
+        <v>2930</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G169" s="8">
+        <v>18</v>
+      </c>
+      <c r="H169" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B170" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" s="11"/>
+      <c r="D170" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E170" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G170" s="8">
+        <v>18</v>
+      </c>
+      <c r="H170" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I170" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B171" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="11"/>
+      <c r="D171" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E171" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G171" s="8">
+        <v>18</v>
+      </c>
+      <c r="H171" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I171" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B172" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" s="11"/>
+      <c r="D172" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E172" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G172" s="8">
+        <v>18</v>
+      </c>
+      <c r="H172" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I172" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B173" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="11"/>
+      <c r="D173" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E173" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G173" s="8">
+        <v>18</v>
+      </c>
+      <c r="H173" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I173" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B174" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="11"/>
+      <c r="D174" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E174" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G174" s="8">
+        <v>18</v>
+      </c>
+      <c r="H174" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I174" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B175" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175" s="11"/>
+      <c r="D175" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E175" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G175" s="8">
+        <v>18</v>
+      </c>
+      <c r="H175" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I175" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B176" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" s="11"/>
+      <c r="D176" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E176" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G176" s="8">
+        <v>18</v>
+      </c>
+      <c r="H176" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I176" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B177" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177" s="11"/>
+      <c r="D177" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E177" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G177" s="8">
+        <v>18</v>
+      </c>
+      <c r="H177" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I177" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B178" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="11"/>
+      <c r="D178" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E178" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G178" s="8">
+        <v>18</v>
+      </c>
+      <c r="H178" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I178" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B179" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" s="11"/>
+      <c r="D179" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E179" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G179" s="8">
+        <v>18</v>
+      </c>
+      <c r="H179" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="11"/>
+      <c r="D180" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E180" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G180" s="8">
+        <v>18</v>
+      </c>
+      <c r="H180" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B181" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" s="11"/>
+      <c r="D181" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E181" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G181" s="8">
+        <v>18</v>
+      </c>
+      <c r="H181" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B182" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182" s="11"/>
+      <c r="D182" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E182" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G182" s="8">
+        <v>18</v>
+      </c>
+      <c r="H182" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B183" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="11"/>
+      <c r="D183" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E183" s="11">
+        <v>3560</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G183" s="8">
+        <v>18</v>
+      </c>
+      <c r="H183" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B184" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" s="11"/>
+      <c r="D184" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E184" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G184" s="8">
+        <v>18</v>
+      </c>
+      <c r="H184" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B185" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185" s="11"/>
+      <c r="D185" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E185" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G185" s="8">
+        <v>18</v>
+      </c>
+      <c r="H185" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B186" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186" s="11"/>
+      <c r="D186" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E186" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G186" s="8">
+        <v>18</v>
+      </c>
+      <c r="H186" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B187" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187" s="11"/>
+      <c r="D187" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E187" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G187" s="8">
+        <v>18</v>
+      </c>
+      <c r="H187" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B188" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188" s="11"/>
+      <c r="D188" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E188" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G188" s="8">
+        <v>18</v>
+      </c>
+      <c r="H188" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="11">
+        <v>2420</v>
+      </c>
+      <c r="D189" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E189" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H189" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>20</v>
+      </c>
+      <c r="B190" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D190" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E190" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H190" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>19</v>
+      </c>
+      <c r="B191" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D191" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E191" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>16</v>
+      </c>
+      <c r="B192" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D192" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E192" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H192" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>13</v>
+      </c>
+      <c r="B193" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D193" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E193" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H193" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>5</v>
+      </c>
+      <c r="B194" t="s">
+        <v>15</v>
+      </c>
+      <c r="C194" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D194" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E194" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H194" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>4</v>
+      </c>
+      <c r="B195" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="11">
+        <v>2840</v>
+      </c>
+      <c r="D195" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E195" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H195" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>131</v>
+      </c>
+      <c r="B196" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196" s="11"/>
+      <c r="D196" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E196" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G196" s="8">
+        <v>17</v>
+      </c>
+      <c r="H196" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>24</v>
+      </c>
+      <c r="B197" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197" s="11"/>
+      <c r="D197" s="11">
+        <v>2530</v>
+      </c>
+      <c r="E197" s="11">
+        <v>2740</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G197" s="8">
+        <v>17</v>
+      </c>
+      <c r="H197" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>25</v>
+      </c>
+      <c r="B198" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="11"/>
+      <c r="D198" s="11">
+        <v>2600</v>
+      </c>
+      <c r="E198" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G198" s="8">
+        <v>17</v>
+      </c>
+      <c r="H198" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>26</v>
+      </c>
+      <c r="B199" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="11"/>
+      <c r="D199" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E199" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G199" s="8">
+        <v>17</v>
+      </c>
+      <c r="H199" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>27</v>
+      </c>
+      <c r="B200" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" s="11"/>
+      <c r="D200" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E200" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G200" s="8">
+        <v>17</v>
+      </c>
+      <c r="H200" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>48</v>
+      </c>
+      <c r="B201" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="11"/>
+      <c r="D201" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E201" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G201" s="8">
+        <v>17</v>
+      </c>
+      <c r="H201" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>49</v>
+      </c>
+      <c r="B202" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" s="11"/>
+      <c r="D202" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E202" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G202" s="8">
+        <v>17</v>
+      </c>
+      <c r="H202" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>28</v>
+      </c>
+      <c r="B203" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="11"/>
+      <c r="D203" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E203" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G203" s="8">
+        <v>17</v>
+      </c>
+      <c r="H203" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>50</v>
+      </c>
+      <c r="B204" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" s="11"/>
+      <c r="D204" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E204" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G204" s="8">
+        <v>17</v>
+      </c>
+      <c r="H204" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>51</v>
+      </c>
+      <c r="B205" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="11"/>
+      <c r="D205" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E205" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G205" s="8">
+        <v>17</v>
+      </c>
+      <c r="H205" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I205" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>52</v>
+      </c>
+      <c r="B206" t="s">
+        <v>15</v>
+      </c>
+      <c r="C206" s="11"/>
+      <c r="D206" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E206" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G206" s="8">
+        <v>17</v>
+      </c>
+      <c r="H206" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>29</v>
+      </c>
+      <c r="B207" t="s">
+        <v>15</v>
+      </c>
+      <c r="C207" s="11"/>
+      <c r="D207" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E207" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G207" s="8">
+        <v>17</v>
+      </c>
+      <c r="H207" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>30</v>
+      </c>
+      <c r="B208" t="s">
+        <v>15</v>
+      </c>
+      <c r="C208" s="11"/>
+      <c r="D208" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E208" s="11">
+        <v>2840</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G208" s="8">
+        <v>17</v>
+      </c>
+      <c r="H208" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>132</v>
+      </c>
+      <c r="B209" t="s">
+        <v>15</v>
+      </c>
+      <c r="C209" s="11"/>
+      <c r="D209" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E209" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G209" s="8">
+        <v>17</v>
+      </c>
+      <c r="H209" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>133</v>
+      </c>
+      <c r="B210" t="s">
+        <v>15</v>
+      </c>
+      <c r="C210" s="11"/>
+      <c r="D210" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E210" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G210" s="8">
+        <v>17</v>
+      </c>
+      <c r="H210" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>134</v>
+      </c>
+      <c r="B211" t="s">
+        <v>15</v>
+      </c>
+      <c r="C211" s="11"/>
+      <c r="D211" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E211" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F211" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G211" s="8">
+        <v>17</v>
+      </c>
+      <c r="H211" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>31</v>
+      </c>
+      <c r="B212" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" s="11"/>
+      <c r="D212" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E212" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G212" s="8">
+        <v>17</v>
+      </c>
+      <c r="H212" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>135</v>
+      </c>
+      <c r="B213" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" s="11"/>
+      <c r="D213" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E213" s="11">
+        <v>3180</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G213" s="8">
+        <v>17</v>
+      </c>
+      <c r="H213" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>53</v>
+      </c>
+      <c r="B214" t="s">
+        <v>15</v>
+      </c>
+      <c r="C214" s="11"/>
+      <c r="D214" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E214" s="11">
+        <v>3180</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G214" s="8">
+        <v>17</v>
+      </c>
+      <c r="H214" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I214" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>136</v>
+      </c>
+      <c r="B215" t="s">
+        <v>15</v>
+      </c>
+      <c r="C215" s="11"/>
+      <c r="D215" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E215" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G215" s="8">
+        <v>17</v>
+      </c>
+      <c r="H215" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I215" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>32</v>
+      </c>
+      <c r="B216" t="s">
+        <v>15</v>
+      </c>
+      <c r="C216" s="11"/>
+      <c r="D216" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E216" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G216" s="8">
+        <v>17</v>
+      </c>
+      <c r="H216" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>137</v>
+      </c>
+      <c r="B217" t="s">
+        <v>15</v>
+      </c>
+      <c r="C217" s="11"/>
+      <c r="D217" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E217" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G217" s="8">
+        <v>17</v>
+      </c>
+      <c r="H217" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>138</v>
+      </c>
+      <c r="B218" t="s">
+        <v>15</v>
+      </c>
+      <c r="C218" s="11"/>
+      <c r="D218" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E218" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G218" s="8">
+        <v>17</v>
+      </c>
+      <c r="H218" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>54</v>
+      </c>
+      <c r="B219" t="s">
+        <v>15</v>
+      </c>
+      <c r="C219" s="11"/>
+      <c r="D219" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E219" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G219" s="8">
+        <v>17</v>
+      </c>
+      <c r="H219" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>55</v>
+      </c>
+      <c r="B220" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="11"/>
+      <c r="D220" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E220" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G220" s="8">
+        <v>17</v>
+      </c>
+      <c r="H220" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>56</v>
+      </c>
+      <c r="B221" t="s">
+        <v>15</v>
+      </c>
+      <c r="C221" s="11"/>
+      <c r="D221" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E221" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G221" s="8">
+        <v>17</v>
+      </c>
+      <c r="H221" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I221" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>57</v>
+      </c>
+      <c r="B222" t="s">
+        <v>15</v>
+      </c>
+      <c r="C222" s="11"/>
+      <c r="D222" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E222" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G222" s="8">
+        <v>17</v>
+      </c>
+      <c r="H222" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>139</v>
+      </c>
+      <c r="B223" t="s">
+        <v>15</v>
+      </c>
+      <c r="C223" s="11"/>
+      <c r="D223" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E223" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G223" s="8">
+        <v>17</v>
+      </c>
+      <c r="H223" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I223" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>140</v>
+      </c>
+      <c r="B224" t="s">
+        <v>15</v>
+      </c>
+      <c r="C224" s="11"/>
+      <c r="D224" s="11">
+        <v>2650</v>
+      </c>
+      <c r="E224" s="11">
+        <v>2960</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G224" s="8">
+        <v>17</v>
+      </c>
+      <c r="H224" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I224" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>33</v>
+      </c>
+      <c r="B225" t="s">
+        <v>15</v>
+      </c>
+      <c r="C225" s="11"/>
+      <c r="D225" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E225" s="11">
+        <v>3170</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G225" s="8">
+        <v>17</v>
+      </c>
+      <c r="H225" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I225" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>34</v>
+      </c>
+      <c r="B226" t="s">
+        <v>15</v>
+      </c>
+      <c r="C226" s="11"/>
+      <c r="D226" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E226" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G226" s="8">
+        <v>17</v>
+      </c>
+      <c r="H226" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I226" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>58</v>
+      </c>
+      <c r="B227" t="s">
+        <v>15</v>
+      </c>
+      <c r="C227" s="11"/>
+      <c r="D227" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E227" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G227" s="8">
+        <v>17</v>
+      </c>
+      <c r="H227" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I227" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>141</v>
+      </c>
+      <c r="B228" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="11"/>
+      <c r="D228" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E228" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G228" s="8">
+        <v>17</v>
+      </c>
+      <c r="H228" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>35</v>
+      </c>
+      <c r="B229" t="s">
+        <v>15</v>
+      </c>
+      <c r="C229" s="11"/>
+      <c r="D229" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E229" s="11">
+        <v>3560</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G229" s="8">
+        <v>17</v>
+      </c>
+      <c r="H229" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>142</v>
+      </c>
+      <c r="B230" t="s">
+        <v>15</v>
+      </c>
+      <c r="C230" s="11"/>
+      <c r="D230" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E230" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G230" s="8">
+        <v>17</v>
+      </c>
+      <c r="H230" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I230" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>143</v>
+      </c>
+      <c r="B231" t="s">
+        <v>15</v>
+      </c>
+      <c r="C231" s="11"/>
+      <c r="D231" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E231" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G231" s="8">
+        <v>17</v>
+      </c>
+      <c r="H231" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I231" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>144</v>
+      </c>
+      <c r="B232" t="s">
+        <v>15</v>
+      </c>
+      <c r="C232" s="11"/>
+      <c r="D232" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E232" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G232" s="8">
+        <v>17</v>
+      </c>
+      <c r="H232" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I232" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>145</v>
+      </c>
+      <c r="B233" t="s">
+        <v>15</v>
+      </c>
+      <c r="C233" s="11"/>
+      <c r="D233" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E233" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G233" s="8">
+        <v>17</v>
+      </c>
+      <c r="H233" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I233" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>146</v>
+      </c>
+      <c r="B234" t="s">
+        <v>15</v>
+      </c>
+      <c r="C234" s="11"/>
+      <c r="D234" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E234" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="G234" s="8">
+        <v>17</v>
+      </c>
+      <c r="H234" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C235" s="11"/>
+      <c r="D235" s="11"/>
+      <c r="E235" s="11"/>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C236" s="11"/>
+      <c r="D236" s="11"/>
+      <c r="E236" s="11"/>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C237" s="11"/>
+      <c r="D237" s="11"/>
+      <c r="E237" s="11"/>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C238" s="11"/>
+      <c r="D238" s="11"/>
+      <c r="E238" s="11"/>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C239" s="11"/>
+      <c r="D239" s="11"/>
+      <c r="E239" s="11"/>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C240" s="11"/>
+      <c r="D240" s="11"/>
+      <c r="E240" s="11"/>
+    </row>
+    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C241" s="11"/>
+      <c r="D241" s="11"/>
+      <c r="E241" s="11"/>
+    </row>
+    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C242" s="11"/>
+      <c r="D242" s="11"/>
+      <c r="E242" s="11"/>
+    </row>
+    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C243" s="11"/>
+      <c r="D243" s="11"/>
+      <c r="E243" s="11"/>
+    </row>
+    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C244" s="11"/>
+      <c r="D244" s="11"/>
+      <c r="E244" s="11"/>
+    </row>
+    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C245" s="11"/>
+      <c r="D245" s="11"/>
+      <c r="E245" s="11"/>
+    </row>
+    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C246" s="11"/>
+      <c r="D246" s="11"/>
+      <c r="E246" s="11"/>
+    </row>
+    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C247" s="11"/>
+      <c r="D247" s="11"/>
+      <c r="E247" s="11"/>
+    </row>
+    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C248" s="11"/>
+      <c r="D248" s="11"/>
+      <c r="E248" s="11"/>
+    </row>
+    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C249" s="11"/>
+      <c r="D249" s="11"/>
+      <c r="E249" s="11"/>
+    </row>
+    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C250" s="11"/>
+      <c r="D250" s="11"/>
+      <c r="E250" s="11"/>
+    </row>
+    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C251" s="11"/>
+      <c r="D251" s="11"/>
+      <c r="E251" s="11"/>
+    </row>
+    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C252" s="11"/>
+      <c r="D252" s="11"/>
+      <c r="E252" s="11"/>
+    </row>
+    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C253" s="11"/>
+      <c r="D253" s="11"/>
+      <c r="E253" s="11"/>
+    </row>
+    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C254" s="11"/>
+      <c r="D254" s="11"/>
+      <c r="E254" s="11"/>
+    </row>
+    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C255" s="11"/>
+      <c r="D255" s="11"/>
+      <c r="E255" s="11"/>
+    </row>
+    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C256" s="11"/>
+      <c r="D256" s="11"/>
+      <c r="E256" s="11"/>
+    </row>
+    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C257" s="11"/>
+      <c r="D257" s="11"/>
+      <c r="E257" s="11"/>
+    </row>
+    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C258" s="11"/>
+      <c r="D258" s="11"/>
+      <c r="E258" s="11"/>
+    </row>
+    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C259" s="11"/>
+      <c r="D259" s="11"/>
+      <c r="E259" s="11"/>
+    </row>
+    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C260" s="11"/>
+      <c r="D260" s="11"/>
+      <c r="E260" s="11"/>
+    </row>
+    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C261" s="11"/>
+      <c r="D261" s="11"/>
+      <c r="E261" s="11"/>
+    </row>
+    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C262" s="11"/>
+      <c r="D262" s="11"/>
+      <c r="E262" s="11"/>
+    </row>
+    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C263" s="11"/>
+      <c r="D263" s="11"/>
+      <c r="E263" s="11"/>
+    </row>
+    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C264" s="11"/>
+      <c r="D264" s="11"/>
+      <c r="E264" s="11"/>
+    </row>
+    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C265" s="11"/>
+      <c r="D265" s="11"/>
+      <c r="E265" s="11"/>
+    </row>
+    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C266" s="11"/>
+      <c r="D266" s="11"/>
+      <c r="E266" s="11"/>
+    </row>
+    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C267" s="11"/>
+      <c r="D267" s="11"/>
+      <c r="E267" s="11"/>
+    </row>
+    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C268" s="11"/>
+      <c r="D268" s="11"/>
+      <c r="E268" s="11"/>
+    </row>
+    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C269" s="11"/>
+      <c r="D269" s="11"/>
+      <c r="E269" s="11"/>
+    </row>
+    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C270" s="11"/>
+      <c r="D270" s="11"/>
+      <c r="E270" s="11"/>
+    </row>
+    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C271" s="11"/>
+      <c r="D271" s="11"/>
+      <c r="E271" s="11"/>
+    </row>
+    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C272" s="11"/>
+      <c r="D272" s="11"/>
+      <c r="E272" s="11"/>
+    </row>
+    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C273" s="11"/>
+      <c r="D273" s="11"/>
+      <c r="E273" s="11"/>
+    </row>
+    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C274" s="11"/>
+      <c r="D274" s="11"/>
+      <c r="E274" s="11"/>
+    </row>
+    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C275" s="11"/>
+      <c r="D275" s="11"/>
+      <c r="E275" s="11"/>
+    </row>
+    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C276" s="11"/>
+      <c r="D276" s="11"/>
+      <c r="E276" s="11"/>
+    </row>
+    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C277" s="11"/>
+      <c r="D277" s="11"/>
+      <c r="E277" s="11"/>
+    </row>
+    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C278" s="11"/>
+      <c r="D278" s="11"/>
+      <c r="E278" s="11"/>
+    </row>
+    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C279" s="11"/>
+      <c r="D279" s="11"/>
+      <c r="E279" s="11"/>
+    </row>
+    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C280" s="11"/>
+      <c r="D280" s="11"/>
+      <c r="E280" s="11"/>
+    </row>
+    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C281" s="11"/>
+      <c r="D281" s="11"/>
+      <c r="E281" s="11"/>
+    </row>
+    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C282" s="11"/>
+      <c r="D282" s="11"/>
+      <c r="E282" s="11"/>
+    </row>
+    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C283" s="11"/>
+      <c r="D283" s="11"/>
+      <c r="E283" s="11"/>
+    </row>
+    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C284" s="11"/>
+      <c r="D284" s="11"/>
+      <c r="E284" s="11"/>
+    </row>
+    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C285" s="11"/>
+      <c r="D285" s="11"/>
+      <c r="E285" s="11"/>
+    </row>
+    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C286" s="11"/>
+      <c r="D286" s="11"/>
+      <c r="E286" s="11"/>
+    </row>
+    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C287" s="11"/>
+      <c r="D287" s="11"/>
+      <c r="E287" s="11"/>
+    </row>
+    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C288" s="11"/>
+      <c r="D288" s="11"/>
+      <c r="E288" s="11"/>
+    </row>
+    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C289" s="11"/>
+      <c r="D289" s="11"/>
+      <c r="E289" s="11"/>
+    </row>
+    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C290" s="11"/>
+      <c r="D290" s="11"/>
+      <c r="E290" s="11"/>
+    </row>
+    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C291" s="11"/>
+      <c r="D291" s="11"/>
+      <c r="E291" s="11"/>
+    </row>
+    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C292" s="11"/>
+      <c r="D292" s="11"/>
+      <c r="E292" s="11"/>
+    </row>
+    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C293" s="11"/>
+      <c r="D293" s="11"/>
+      <c r="E293" s="11"/>
+    </row>
+    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C294" s="11"/>
+      <c r="D294" s="11"/>
+      <c r="E294" s="11"/>
+    </row>
+    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C295" s="11"/>
+      <c r="D295" s="11"/>
+      <c r="E295" s="11"/>
+    </row>
+    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C296" s="11"/>
+      <c r="D296" s="11"/>
+      <c r="E296" s="11"/>
+    </row>
+    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C297" s="11"/>
+      <c r="D297" s="11"/>
+      <c r="E297" s="11"/>
+    </row>
+    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C298" s="11"/>
+      <c r="D298" s="11"/>
+      <c r="E298" s="11"/>
+    </row>
+    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C299" s="11"/>
+      <c r="D299" s="11"/>
+      <c r="E299" s="11"/>
+    </row>
+    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C300" s="11"/>
+      <c r="D300" s="11"/>
+      <c r="E300" s="11"/>
+    </row>
+    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C301" s="11"/>
+      <c r="D301" s="11"/>
+      <c r="E301" s="11"/>
+    </row>
+    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C302" s="11"/>
+      <c r="D302" s="11"/>
+      <c r="E302" s="11"/>
+    </row>
+    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C303" s="11"/>
+      <c r="D303" s="11"/>
+      <c r="E303" s="11"/>
+    </row>
+    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C304" s="11"/>
+      <c r="D304" s="11"/>
+      <c r="E304" s="11"/>
+    </row>
+    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C305" s="11"/>
+      <c r="D305" s="11"/>
+      <c r="E305" s="11"/>
+    </row>
+    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C306" s="11"/>
+      <c r="D306" s="11"/>
+      <c r="E306" s="11"/>
+    </row>
+    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C307" s="11"/>
+      <c r="D307" s="11"/>
+      <c r="E307" s="11"/>
+    </row>
+    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C308" s="11"/>
+      <c r="D308" s="11"/>
+      <c r="E308" s="11"/>
+    </row>
+    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C309" s="11"/>
+      <c r="D309" s="11"/>
+      <c r="E309" s="11"/>
+    </row>
+    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C310" s="11"/>
+      <c r="D310" s="11"/>
+      <c r="E310" s="11"/>
+    </row>
+    <row r="311" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C311" s="11"/>
+      <c r="D311" s="11"/>
+      <c r="E311" s="11"/>
+    </row>
+    <row r="312" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C312" s="11"/>
+      <c r="D312" s="11"/>
+      <c r="E312" s="11"/>
+    </row>
+    <row r="313" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C313" s="11"/>
+      <c r="D313" s="11"/>
+      <c r="E313" s="11"/>
+    </row>
+    <row r="314" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C314" s="11"/>
+      <c r="D314" s="11"/>
+      <c r="E314" s="11"/>
+    </row>
+    <row r="315" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C315" s="11"/>
+      <c r="D315" s="11"/>
+      <c r="E315" s="11"/>
+    </row>
+    <row r="316" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C316" s="11"/>
+      <c r="D316" s="11"/>
+      <c r="E316" s="11"/>
+    </row>
+    <row r="317" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C317" s="11"/>
+      <c r="D317" s="11"/>
+      <c r="E317" s="11"/>
+    </row>
+    <row r="318" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C318" s="11"/>
+      <c r="D318" s="11"/>
+      <c r="E318" s="11"/>
+    </row>
+    <row r="319" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C319" s="11"/>
+      <c r="D319" s="11"/>
+      <c r="E319" s="11"/>
+    </row>
+    <row r="320" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C320" s="11"/>
+      <c r="D320" s="11"/>
+      <c r="E320" s="11"/>
+    </row>
+    <row r="321" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C321" s="11"/>
+      <c r="D321" s="11"/>
+      <c r="E321" s="11"/>
+    </row>
+    <row r="322" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C322" s="11"/>
+      <c r="D322" s="11"/>
+      <c r="E322" s="11"/>
+    </row>
+    <row r="323" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C323" s="11"/>
+      <c r="D323" s="11"/>
+      <c r="E323" s="11"/>
+    </row>
+    <row r="324" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C324" s="11"/>
+      <c r="D324" s="11"/>
+      <c r="E324" s="11"/>
+    </row>
+    <row r="325" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C325" s="11"/>
+      <c r="D325" s="11"/>
+      <c r="E325" s="11"/>
+    </row>
+    <row r="326" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C326" s="11"/>
+      <c r="D326" s="11"/>
+      <c r="E326" s="11"/>
+    </row>
+    <row r="327" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C327" s="11"/>
+      <c r="D327" s="11"/>
+      <c r="E327" s="11"/>
+    </row>
+    <row r="328" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C328" s="11"/>
+      <c r="D328" s="11"/>
+      <c r="E328" s="11"/>
+    </row>
+    <row r="329" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C329" s="11"/>
+      <c r="D329" s="11"/>
+      <c r="E329" s="11"/>
+    </row>
+    <row r="330" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C330" s="11"/>
+      <c r="D330" s="11"/>
+      <c r="E330" s="11"/>
+    </row>
+    <row r="331" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C331" s="11"/>
+      <c r="D331" s="11"/>
+      <c r="E331" s="11"/>
+    </row>
+    <row r="332" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C332" s="11"/>
+      <c r="D332" s="11"/>
+      <c r="E332" s="11"/>
+    </row>
+    <row r="333" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C333" s="11"/>
+      <c r="D333" s="11"/>
+      <c r="E333" s="11"/>
+    </row>
+    <row r="334" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C334" s="11"/>
+      <c r="D334" s="11"/>
+      <c r="E334" s="11"/>
+    </row>
+    <row r="335" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C335" s="11"/>
+      <c r="D335" s="11"/>
+      <c r="E335" s="11"/>
+    </row>
+    <row r="336" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C336" s="11"/>
+      <c r="D336" s="11"/>
+      <c r="E336" s="11"/>
+    </row>
+    <row r="337" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C337" s="11"/>
+      <c r="D337" s="11"/>
+      <c r="E337" s="11"/>
+    </row>
+    <row r="338" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C338" s="11"/>
+      <c r="D338" s="11"/>
+      <c r="E338" s="11"/>
+    </row>
+    <row r="339" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C339" s="11"/>
+      <c r="D339" s="11"/>
+      <c r="E339" s="11"/>
+    </row>
+    <row r="340" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C340" s="11"/>
+      <c r="D340" s="11"/>
+      <c r="E340" s="11"/>
+    </row>
+    <row r="341" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C341" s="11"/>
+      <c r="D341" s="11"/>
+      <c r="E341" s="11"/>
+    </row>
+    <row r="342" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C342" s="11"/>
+      <c r="D342" s="11"/>
+      <c r="E342" s="11"/>
+    </row>
+    <row r="343" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C343" s="11"/>
+      <c r="D343" s="11"/>
+      <c r="E343" s="11"/>
+    </row>
+    <row r="344" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C344" s="11"/>
+      <c r="D344" s="11"/>
+      <c r="E344" s="11"/>
+    </row>
+    <row r="345" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C345" s="11"/>
+      <c r="D345" s="11"/>
+      <c r="E345" s="11"/>
+    </row>
+    <row r="346" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C346" s="11"/>
+      <c r="D346" s="11"/>
+      <c r="E346" s="11"/>
+    </row>
+    <row r="347" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C347" s="11"/>
+      <c r="D347" s="11"/>
+      <c r="E347" s="11"/>
+    </row>
+    <row r="348" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C348" s="11"/>
+      <c r="D348" s="11"/>
+      <c r="E348" s="11"/>
+    </row>
+    <row r="349" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C349" s="11"/>
+      <c r="D349" s="11"/>
+      <c r="E349" s="11"/>
+    </row>
+    <row r="350" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C350" s="11"/>
+      <c r="D350" s="11"/>
+      <c r="E350" s="11"/>
+    </row>
+    <row r="351" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C351" s="11"/>
+      <c r="D351" s="11"/>
+      <c r="E351" s="11"/>
+    </row>
+    <row r="352" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C352" s="11"/>
+      <c r="D352" s="11"/>
+      <c r="E352" s="11"/>
+    </row>
+    <row r="353" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C353" s="11"/>
+      <c r="D353" s="11"/>
+      <c r="E353" s="11"/>
+    </row>
+    <row r="354" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C354" s="11"/>
+      <c r="D354" s="11"/>
+      <c r="E354" s="11"/>
+    </row>
+    <row r="355" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C355" s="11"/>
+      <c r="D355" s="11"/>
+      <c r="E355" s="11"/>
+    </row>
+    <row r="356" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C356" s="11"/>
+      <c r="D356" s="11"/>
+      <c r="E356" s="11"/>
+    </row>
+    <row r="357" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C357" s="11"/>
+      <c r="D357" s="11"/>
+      <c r="E357" s="11"/>
+    </row>
+    <row r="358" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C358" s="11"/>
+      <c r="D358" s="11"/>
+      <c r="E358" s="11"/>
+    </row>
+    <row r="359" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C359" s="11"/>
+      <c r="D359" s="11"/>
+      <c r="E359" s="11"/>
+    </row>
+    <row r="360" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C360" s="11"/>
+      <c r="D360" s="11"/>
+      <c r="E360" s="11"/>
+    </row>
+    <row r="361" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C361" s="11"/>
+      <c r="D361" s="11"/>
+      <c r="E361" s="11"/>
+    </row>
+    <row r="362" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C362" s="11"/>
+      <c r="D362" s="11"/>
+      <c r="E362" s="11"/>
+    </row>
+    <row r="363" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C363" s="11"/>
+      <c r="D363" s="11"/>
+      <c r="E363" s="11"/>
+    </row>
+    <row r="364" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C364" s="11"/>
+      <c r="D364" s="11"/>
+      <c r="E364" s="11"/>
+    </row>
+    <row r="365" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C365" s="11"/>
+      <c r="D365" s="11"/>
+      <c r="E365" s="11"/>
+    </row>
+    <row r="366" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C366" s="11"/>
+      <c r="D366" s="11"/>
+      <c r="E366" s="11"/>
+    </row>
+    <row r="367" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C367" s="11"/>
+      <c r="D367" s="11"/>
+      <c r="E367" s="11"/>
+    </row>
+    <row r="368" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C368" s="11"/>
+      <c r="D368" s="11"/>
+      <c r="E368" s="11"/>
+    </row>
+    <row r="369" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C369" s="11"/>
+      <c r="D369" s="11"/>
+      <c r="E369" s="11"/>
+    </row>
+    <row r="370" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C370" s="11"/>
+      <c r="D370" s="11"/>
+      <c r="E370" s="11"/>
+    </row>
+    <row r="371" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C371" s="11"/>
+      <c r="D371" s="11"/>
+      <c r="E371" s="11"/>
+    </row>
+    <row r="372" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C372" s="11"/>
+      <c r="D372" s="11"/>
+      <c r="E372" s="11"/>
+    </row>
+    <row r="373" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C373" s="11"/>
+      <c r="D373" s="11"/>
+      <c r="E373" s="11"/>
+    </row>
+    <row r="374" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C374" s="11"/>
+      <c r="D374" s="11"/>
+      <c r="E374" s="11"/>
+    </row>
+    <row r="375" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C375" s="11"/>
+      <c r="D375" s="11"/>
+      <c r="E375" s="11"/>
+    </row>
+    <row r="376" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C376" s="11"/>
+      <c r="D376" s="11"/>
+      <c r="E376" s="11"/>
+    </row>
+    <row r="377" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C377" s="11"/>
+      <c r="D377" s="11"/>
+      <c r="E377" s="11"/>
+    </row>
+    <row r="378" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C378" s="11"/>
+      <c r="D378" s="11"/>
+      <c r="E378" s="11"/>
+    </row>
+    <row r="379" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C379" s="11"/>
+      <c r="D379" s="11"/>
+      <c r="E379" s="11"/>
+    </row>
+    <row r="380" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C380" s="11"/>
+      <c r="D380" s="11"/>
+      <c r="E380" s="11"/>
+    </row>
+    <row r="381" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C381" s="11"/>
+      <c r="D381" s="11"/>
+      <c r="E381" s="11"/>
+    </row>
+    <row r="382" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C382" s="11"/>
+      <c r="D382" s="11"/>
+      <c r="E382" s="11"/>
+    </row>
+    <row r="383" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C383" s="11"/>
+      <c r="D383" s="11"/>
+      <c r="E383" s="11"/>
+    </row>
+    <row r="384" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C384" s="11"/>
+      <c r="D384" s="11"/>
+      <c r="E384" s="11"/>
+    </row>
+    <row r="385" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C385" s="11"/>
+      <c r="D385" s="11"/>
+      <c r="E385" s="11"/>
+    </row>
+    <row r="386" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C386" s="11"/>
+      <c r="D386" s="11"/>
+      <c r="E386" s="11"/>
+    </row>
+    <row r="387" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C387" s="11"/>
+      <c r="D387" s="11"/>
+      <c r="E387" s="11"/>
+    </row>
+    <row r="388" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C388" s="11"/>
+      <c r="D388" s="11"/>
+      <c r="E388" s="11"/>
+    </row>
+    <row r="389" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C389" s="11"/>
+      <c r="D389" s="11"/>
+      <c r="E389" s="11"/>
+    </row>
+    <row r="390" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C390" s="11"/>
+      <c r="D390" s="11"/>
+      <c r="E390" s="11"/>
+    </row>
+    <row r="391" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C391" s="11"/>
+      <c r="D391" s="11"/>
+      <c r="E391" s="11"/>
+    </row>
+    <row r="392" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C392" s="11"/>
+      <c r="D392" s="11"/>
+      <c r="E392" s="11"/>
+    </row>
+    <row r="393" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C393" s="11"/>
+      <c r="D393" s="11"/>
+      <c r="E393" s="11"/>
+    </row>
+    <row r="394" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C394" s="11"/>
+      <c r="D394" s="11"/>
+      <c r="E394" s="11"/>
+    </row>
+    <row r="395" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C395" s="11"/>
+      <c r="D395" s="11"/>
+      <c r="E395" s="11"/>
+    </row>
+    <row r="396" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C396" s="11"/>
+      <c r="D396" s="11"/>
+      <c r="E396" s="11"/>
+    </row>
+    <row r="397" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C397" s="11"/>
+      <c r="D397" s="11"/>
+      <c r="E397" s="11"/>
+    </row>
+    <row r="398" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C398" s="11"/>
+      <c r="D398" s="11"/>
+      <c r="E398" s="11"/>
+    </row>
+    <row r="399" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C399" s="11"/>
+      <c r="D399" s="11"/>
+      <c r="E399" s="11"/>
+    </row>
+    <row r="400" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C400" s="11"/>
+      <c r="D400" s="11"/>
+      <c r="E400" s="11"/>
+    </row>
+    <row r="401" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C401" s="11"/>
+      <c r="D401" s="11"/>
+      <c r="E401" s="11"/>
+    </row>
+    <row r="402" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C402" s="11"/>
+      <c r="D402" s="11"/>
+      <c r="E402" s="11"/>
+    </row>
+    <row r="403" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C403" s="11"/>
+      <c r="D403" s="11"/>
+      <c r="E403" s="11"/>
+    </row>
+    <row r="404" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C404" s="11"/>
+      <c r="D404" s="11"/>
+      <c r="E404" s="11"/>
+    </row>
+    <row r="405" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C405" s="11"/>
+      <c r="D405" s="11"/>
+      <c r="E405" s="11"/>
+    </row>
+    <row r="406" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C406" s="11"/>
+      <c r="D406" s="11"/>
+      <c r="E406" s="11"/>
+    </row>
+    <row r="407" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C407" s="11"/>
+      <c r="D407" s="11"/>
+      <c r="E407" s="11"/>
+    </row>
+    <row r="408" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C408" s="11"/>
+      <c r="D408" s="11"/>
+      <c r="E408" s="11"/>
+    </row>
+    <row r="409" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C409" s="11"/>
+      <c r="D409" s="11"/>
+      <c r="E409" s="11"/>
+    </row>
+    <row r="410" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C410" s="11"/>
+      <c r="D410" s="11"/>
+      <c r="E410" s="11"/>
+    </row>
+    <row r="411" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C411" s="11"/>
+      <c r="D411" s="11"/>
+      <c r="E411" s="11"/>
+    </row>
+    <row r="412" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C412" s="11"/>
+      <c r="D412" s="11"/>
+      <c r="E412" s="11"/>
+    </row>
+    <row r="413" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C413" s="11"/>
+      <c r="D413" s="11"/>
+      <c r="E413" s="11"/>
+    </row>
+    <row r="414" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C414" s="11"/>
+      <c r="D414" s="11"/>
+      <c r="E414" s="11"/>
+    </row>
+    <row r="415" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C415" s="11"/>
+      <c r="D415" s="11"/>
+      <c r="E415" s="11"/>
+    </row>
+    <row r="416" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C416" s="11"/>
+      <c r="D416" s="11"/>
+      <c r="E416" s="11"/>
+    </row>
+    <row r="417" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C417" s="11"/>
+      <c r="D417" s="11"/>
+      <c r="E417" s="11"/>
+    </row>
+    <row r="418" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C418" s="11"/>
+      <c r="D418" s="11"/>
+      <c r="E418" s="11"/>
+    </row>
+    <row r="419" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C419" s="11"/>
+      <c r="D419" s="11"/>
+      <c r="E419" s="11"/>
+    </row>
+    <row r="420" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C420" s="11"/>
+      <c r="D420" s="11"/>
+      <c r="E420" s="11"/>
+    </row>
+    <row r="421" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C421" s="11"/>
+      <c r="D421" s="11"/>
+      <c r="E421" s="11"/>
+    </row>
+    <row r="422" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C422" s="11"/>
+      <c r="D422" s="11"/>
+      <c r="E422" s="11"/>
+    </row>
+    <row r="423" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C423" s="11"/>
+      <c r="D423" s="11"/>
+      <c r="E423" s="11"/>
+    </row>
+    <row r="424" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C424" s="11"/>
+      <c r="D424" s="11"/>
+      <c r="E424" s="11"/>
+    </row>
+    <row r="425" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C425" s="11"/>
+      <c r="D425" s="11"/>
+      <c r="E425" s="11"/>
+    </row>
+    <row r="426" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C426" s="11"/>
+      <c r="D426" s="11"/>
+      <c r="E426" s="11"/>
+    </row>
+    <row r="427" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C427" s="11"/>
+      <c r="D427" s="11"/>
+      <c r="E427" s="11"/>
+    </row>
+    <row r="428" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C428" s="11"/>
+      <c r="D428" s="11"/>
+      <c r="E428" s="11"/>
+    </row>
+    <row r="429" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C429" s="11"/>
+      <c r="D429" s="11"/>
+      <c r="E429" s="11"/>
+    </row>
+    <row r="430" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C430" s="11"/>
+      <c r="D430" s="11"/>
+      <c r="E430" s="11"/>
+    </row>
+    <row r="431" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C431" s="11"/>
+      <c r="D431" s="11"/>
+      <c r="E431" s="11"/>
+    </row>
+    <row r="432" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C432" s="11"/>
+      <c r="D432" s="11"/>
+      <c r="E432" s="11"/>
+    </row>
+    <row r="433" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C433" s="11"/>
+      <c r="D433" s="11"/>
+      <c r="E433" s="11"/>
+    </row>
+    <row r="434" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C434" s="11"/>
+      <c r="D434" s="11"/>
+      <c r="E434" s="11"/>
+    </row>
+    <row r="435" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C435" s="11"/>
+      <c r="D435" s="11"/>
+      <c r="E435" s="11"/>
+    </row>
+    <row r="436" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C436" s="11"/>
+      <c r="D436" s="11"/>
+      <c r="E436" s="11"/>
+    </row>
+    <row r="437" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C437" s="11"/>
+      <c r="D437" s="11"/>
+      <c r="E437" s="11"/>
+    </row>
+    <row r="438" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C438" s="11"/>
+      <c r="D438" s="11"/>
+      <c r="E438" s="11"/>
+    </row>
+    <row r="439" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C439" s="11"/>
+      <c r="D439" s="11"/>
+      <c r="E439" s="11"/>
+    </row>
+    <row r="440" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C440" s="11"/>
+      <c r="D440" s="11"/>
+      <c r="E440" s="11"/>
+    </row>
+    <row r="441" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C441" s="11"/>
+      <c r="D441" s="11"/>
+      <c r="E441" s="11"/>
+    </row>
+    <row r="442" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C442" s="11"/>
+      <c r="D442" s="11"/>
+      <c r="E442" s="11"/>
+    </row>
+    <row r="443" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C443" s="11"/>
+      <c r="D443" s="11"/>
+      <c r="E443" s="11"/>
+    </row>
+    <row r="444" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C444" s="11"/>
+      <c r="D444" s="11"/>
+      <c r="E444" s="11"/>
+    </row>
+    <row r="445" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C445" s="11"/>
+      <c r="D445" s="11"/>
+      <c r="E445" s="11"/>
+    </row>
+    <row r="446" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C446" s="11"/>
+      <c r="D446" s="11"/>
+      <c r="E446" s="11"/>
+    </row>
+    <row r="447" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C447" s="11"/>
+      <c r="D447" s="11"/>
+      <c r="E447" s="11"/>
+    </row>
+    <row r="448" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C448" s="11"/>
+      <c r="D448" s="11"/>
+      <c r="E448" s="11"/>
+    </row>
+    <row r="449" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C449" s="11"/>
+      <c r="D449" s="11"/>
+      <c r="E449" s="11"/>
+    </row>
+    <row r="450" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C450" s="11"/>
+      <c r="D450" s="11"/>
+      <c r="E450" s="11"/>
+    </row>
+    <row r="451" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C451" s="11"/>
+      <c r="D451" s="11"/>
+      <c r="E451" s="11"/>
+    </row>
+    <row r="452" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C452" s="11"/>
+      <c r="D452" s="11"/>
+      <c r="E452" s="11"/>
+    </row>
+    <row r="453" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C453" s="11"/>
+      <c r="D453" s="11"/>
+      <c r="E453" s="11"/>
+    </row>
+    <row r="454" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C454" s="11"/>
+      <c r="D454" s="11"/>
+      <c r="E454" s="11"/>
+    </row>
+    <row r="455" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C455" s="11"/>
+      <c r="D455" s="11"/>
+      <c r="E455" s="11"/>
+    </row>
+    <row r="456" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C456" s="11"/>
+      <c r="D456" s="11"/>
+      <c r="E456" s="11"/>
+    </row>
+    <row r="457" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C457" s="11"/>
+      <c r="D457" s="11"/>
+      <c r="E457" s="11"/>
+    </row>
+    <row r="458" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C458" s="11"/>
+      <c r="D458" s="11"/>
+      <c r="E458" s="11"/>
+    </row>
+    <row r="459" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C459" s="11"/>
+      <c r="D459" s="11"/>
+      <c r="E459" s="11"/>
+    </row>
+    <row r="460" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C460" s="11"/>
+      <c r="D460" s="11"/>
+      <c r="E460" s="11"/>
+    </row>
+    <row r="461" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C461" s="11"/>
+      <c r="D461" s="11"/>
+      <c r="E461" s="11"/>
+    </row>
+    <row r="462" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C462" s="11"/>
+      <c r="D462" s="11"/>
+      <c r="E462" s="11"/>
+    </row>
+    <row r="463" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C463" s="11"/>
+      <c r="D463" s="11"/>
+      <c r="E463" s="11"/>
+    </row>
+    <row r="464" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C464" s="11"/>
+      <c r="D464" s="11"/>
+      <c r="E464" s="11"/>
+    </row>
+    <row r="465" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C465" s="11"/>
+      <c r="D465" s="11"/>
+      <c r="E465" s="11"/>
+    </row>
+    <row r="466" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C466" s="11"/>
+      <c r="D466" s="11"/>
+      <c r="E466" s="11"/>
+    </row>
+    <row r="467" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C467" s="11"/>
+      <c r="D467" s="11"/>
+      <c r="E467" s="11"/>
+    </row>
+    <row r="468" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C468" s="11"/>
+      <c r="D468" s="11"/>
+      <c r="E468" s="11"/>
+    </row>
+    <row r="469" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C469" s="11"/>
+      <c r="D469" s="11"/>
+      <c r="E469" s="11"/>
+    </row>
+    <row r="470" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C470" s="11"/>
+      <c r="D470" s="11"/>
+      <c r="E470" s="11"/>
+    </row>
+    <row r="471" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C471" s="11"/>
+      <c r="D471" s="11"/>
+      <c r="E471" s="11"/>
+    </row>
+    <row r="472" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C472" s="11"/>
+      <c r="D472" s="11"/>
+      <c r="E472" s="11"/>
+    </row>
+    <row r="473" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C473" s="11"/>
+      <c r="D473" s="11"/>
+      <c r="E473" s="11"/>
+    </row>
+    <row r="474" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C474" s="11"/>
+      <c r="D474" s="11"/>
+      <c r="E474" s="11"/>
+    </row>
+    <row r="475" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C475" s="11"/>
+      <c r="D475" s="11"/>
+      <c r="E475" s="11"/>
+    </row>
+    <row r="476" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C476" s="11"/>
+      <c r="D476" s="11"/>
+      <c r="E476" s="11"/>
+    </row>
+    <row r="477" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C477" s="11"/>
+      <c r="D477" s="11"/>
+      <c r="E477" s="11"/>
+    </row>
+    <row r="478" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C478" s="11"/>
+      <c r="D478" s="11"/>
+      <c r="E478" s="11"/>
+    </row>
+    <row r="479" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C479" s="11"/>
+      <c r="D479" s="11"/>
+      <c r="E479" s="11"/>
+    </row>
+    <row r="480" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C480" s="11"/>
+      <c r="D480" s="11"/>
+      <c r="E480" s="11"/>
+    </row>
+    <row r="481" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C481" s="11"/>
+      <c r="D481" s="11"/>
+      <c r="E481" s="11"/>
+    </row>
+    <row r="482" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C482" s="11"/>
+      <c r="D482" s="11"/>
+      <c r="E482" s="11"/>
+    </row>
+    <row r="483" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C483" s="11"/>
+      <c r="D483" s="11"/>
+      <c r="E483" s="11"/>
+    </row>
+    <row r="484" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C484" s="11"/>
+      <c r="D484" s="11"/>
+      <c r="E484" s="11"/>
+    </row>
+    <row r="485" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C485" s="11"/>
+      <c r="D485" s="11"/>
+      <c r="E485" s="11"/>
+    </row>
+    <row r="486" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C486" s="11"/>
+      <c r="D486" s="11"/>
+      <c r="E486" s="11"/>
+    </row>
+    <row r="487" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C487" s="11"/>
+      <c r="D487" s="11"/>
+      <c r="E487" s="11"/>
+    </row>
+    <row r="488" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C488" s="11"/>
+      <c r="D488" s="11"/>
+      <c r="E488" s="11"/>
+    </row>
+    <row r="489" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C489" s="11"/>
+      <c r="D489" s="11"/>
+      <c r="E489" s="11"/>
+    </row>
+    <row r="490" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C490" s="11"/>
+      <c r="D490" s="11"/>
+      <c r="E490" s="11"/>
+    </row>
+    <row r="491" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C491" s="11"/>
+      <c r="D491" s="11"/>
+      <c r="E491" s="11"/>
+    </row>
+    <row r="492" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C492" s="11"/>
+      <c r="D492" s="11"/>
+      <c r="E492" s="11"/>
+    </row>
+    <row r="493" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C493" s="11"/>
+      <c r="D493" s="11"/>
+      <c r="E493" s="11"/>
+    </row>
+    <row r="494" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C494" s="11"/>
+      <c r="D494" s="11"/>
+      <c r="E494" s="11"/>
+    </row>
+    <row r="495" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C495" s="11"/>
+      <c r="D495" s="11"/>
+      <c r="E495" s="11"/>
+    </row>
+    <row r="496" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C496" s="11"/>
+      <c r="D496" s="11"/>
+      <c r="E496" s="11"/>
+    </row>
+    <row r="497" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C497" s="11"/>
+      <c r="D497" s="11"/>
+      <c r="E497" s="11"/>
+    </row>
+    <row r="498" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C498" s="11"/>
+      <c r="D498" s="11"/>
+      <c r="E498" s="11"/>
+    </row>
+    <row r="499" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C499" s="11"/>
+      <c r="D499" s="11"/>
+      <c r="E499" s="11"/>
+    </row>
+    <row r="500" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C500" s="11"/>
+      <c r="D500" s="11"/>
+      <c r="E500" s="11"/>
+    </row>
+    <row r="501" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C501" s="11"/>
+      <c r="D501" s="11"/>
+      <c r="E501" s="11"/>
+    </row>
+    <row r="502" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C502" s="11"/>
+      <c r="D502" s="11"/>
+      <c r="E502" s="11"/>
+    </row>
+    <row r="503" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C503" s="11"/>
+      <c r="D503" s="11"/>
+      <c r="E503" s="11"/>
+    </row>
+    <row r="504" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C504" s="11"/>
+      <c r="D504" s="11"/>
+      <c r="E504" s="11"/>
+    </row>
+    <row r="505" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C505" s="11"/>
+      <c r="D505" s="11"/>
+      <c r="E505" s="11"/>
+    </row>
+    <row r="506" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C506" s="11"/>
+      <c r="D506" s="11"/>
+      <c r="E506" s="11"/>
+    </row>
+    <row r="507" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C507" s="11"/>
+      <c r="D507" s="11"/>
+      <c r="E507" s="11"/>
+    </row>
+    <row r="508" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C508" s="11"/>
+      <c r="D508" s="11"/>
+      <c r="E508" s="11"/>
+    </row>
+    <row r="509" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C509" s="11"/>
+      <c r="D509" s="11"/>
+      <c r="E509" s="11"/>
+    </row>
+    <row r="510" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C510" s="11"/>
+      <c r="D510" s="11"/>
+      <c r="E510" s="11"/>
+    </row>
+    <row r="511" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C511" s="11"/>
+      <c r="D511" s="11"/>
+      <c r="E511" s="11"/>
+    </row>
+    <row r="512" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C512" s="11"/>
+      <c r="D512" s="11"/>
+      <c r="E512" s="11"/>
+    </row>
+    <row r="513" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C513" s="11"/>
+      <c r="D513" s="11"/>
+      <c r="E513" s="11"/>
+    </row>
+    <row r="514" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C514" s="11"/>
+      <c r="D514" s="11"/>
+      <c r="E514" s="11"/>
+    </row>
+    <row r="515" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C515" s="11"/>
+      <c r="D515" s="11"/>
+      <c r="E515" s="11"/>
+    </row>
+    <row r="516" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C516" s="11"/>
+      <c r="D516" s="11"/>
+      <c r="E516" s="11"/>
+    </row>
+    <row r="517" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C517" s="11"/>
+      <c r="D517" s="11"/>
+      <c r="E517" s="11"/>
+    </row>
+    <row r="518" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C518" s="11"/>
+      <c r="D518" s="11"/>
+      <c r="E518" s="11"/>
+    </row>
+    <row r="519" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C519" s="11"/>
+      <c r="D519" s="11"/>
+      <c r="E519" s="11"/>
+    </row>
+    <row r="520" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C520" s="11"/>
+      <c r="D520" s="11"/>
+      <c r="E520" s="11"/>
+    </row>
+    <row r="521" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C521" s="11"/>
+      <c r="D521" s="11"/>
+      <c r="E521" s="11"/>
+    </row>
+    <row r="522" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C522" s="11"/>
+      <c r="D522" s="11"/>
+      <c r="E522" s="11"/>
+    </row>
+    <row r="523" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C523" s="11"/>
+      <c r="D523" s="11"/>
+      <c r="E523" s="11"/>
+    </row>
+    <row r="524" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C524" s="11"/>
+      <c r="D524" s="11"/>
+      <c r="E524" s="11"/>
+    </row>
+    <row r="525" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C525" s="11"/>
+      <c r="D525" s="11"/>
+      <c r="E525" s="11"/>
+    </row>
+    <row r="526" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C526" s="11"/>
+      <c r="D526" s="11"/>
+      <c r="E526" s="11"/>
+    </row>
+    <row r="527" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C527" s="11"/>
+      <c r="D527" s="11"/>
+      <c r="E527" s="11"/>
+    </row>
+    <row r="528" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C528" s="11"/>
+      <c r="D528" s="11"/>
+      <c r="E528" s="11"/>
+    </row>
+    <row r="529" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C529" s="11"/>
+      <c r="D529" s="11"/>
+      <c r="E529" s="11"/>
+    </row>
+    <row r="530" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C530" s="11"/>
+      <c r="D530" s="11"/>
+      <c r="E530" s="11"/>
+    </row>
+    <row r="531" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C531" s="11"/>
+      <c r="D531" s="11"/>
+      <c r="E531" s="11"/>
+    </row>
+    <row r="532" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C532" s="11"/>
+      <c r="D532" s="11"/>
+      <c r="E532" s="11"/>
+    </row>
+    <row r="533" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C533" s="11"/>
+      <c r="D533" s="11"/>
+      <c r="E533" s="11"/>
+    </row>
+    <row r="534" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C534" s="11"/>
+      <c r="D534" s="11"/>
+      <c r="E534" s="11"/>
+    </row>
+    <row r="535" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C535" s="11"/>
+      <c r="D535" s="11"/>
+      <c r="E535" s="11"/>
+    </row>
+    <row r="536" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C536" s="11"/>
+      <c r="D536" s="11"/>
+      <c r="E536" s="11"/>
+    </row>
+    <row r="537" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C537" s="11"/>
+      <c r="D537" s="11"/>
+      <c r="E537" s="11"/>
+    </row>
+    <row r="538" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C538" s="11"/>
+      <c r="D538" s="11"/>
+      <c r="E538" s="11"/>
+    </row>
+    <row r="539" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C539" s="11"/>
+      <c r="D539" s="11"/>
+      <c r="E539" s="11"/>
+    </row>
+    <row r="540" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C540" s="11"/>
+      <c r="D540" s="11"/>
+      <c r="E540" s="11"/>
+    </row>
+    <row r="541" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C541" s="11"/>
+      <c r="D541" s="11"/>
+      <c r="E541" s="11"/>
+    </row>
+    <row r="542" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C542" s="11"/>
+      <c r="D542" s="11"/>
+      <c r="E542" s="11"/>
+    </row>
+    <row r="543" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C543" s="11"/>
+      <c r="D543" s="11"/>
+      <c r="E543" s="11"/>
+    </row>
+    <row r="544" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C544" s="11"/>
+      <c r="D544" s="11"/>
+      <c r="E544" s="11"/>
+    </row>
+    <row r="545" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C545" s="11"/>
+      <c r="D545" s="11"/>
+      <c r="E545" s="11"/>
+    </row>
+    <row r="546" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C546" s="11"/>
+      <c r="D546" s="11"/>
+      <c r="E546" s="11"/>
+    </row>
+    <row r="547" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C547" s="11"/>
+      <c r="D547" s="11"/>
+      <c r="E547" s="11"/>
+    </row>
+    <row r="548" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C548" s="11"/>
+      <c r="D548" s="11"/>
+      <c r="E548" s="11"/>
+    </row>
+    <row r="549" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C549" s="11"/>
+      <c r="D549" s="11"/>
+      <c r="E549" s="11"/>
+    </row>
+    <row r="550" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C550" s="11"/>
+      <c r="D550" s="11"/>
+      <c r="E550" s="11"/>
+    </row>
+    <row r="551" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C551" s="11"/>
+      <c r="D551" s="11"/>
+      <c r="E551" s="11"/>
+    </row>
+    <row r="552" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C552" s="11"/>
+      <c r="D552" s="11"/>
+      <c r="E552" s="11"/>
+    </row>
+    <row r="553" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C553" s="11"/>
+      <c r="D553" s="11"/>
+      <c r="E553" s="11"/>
+    </row>
+    <row r="554" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C554" s="11"/>
+      <c r="D554" s="11"/>
+      <c r="E554" s="11"/>
+    </row>
+    <row r="555" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C555" s="11"/>
+      <c r="D555" s="11"/>
+      <c r="E555" s="11"/>
+    </row>
+    <row r="556" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C556" s="11"/>
+      <c r="D556" s="11"/>
+      <c r="E556" s="11"/>
+    </row>
+    <row r="557" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C557" s="11"/>
+      <c r="D557" s="11"/>
+      <c r="E557" s="11"/>
+    </row>
+    <row r="558" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C558" s="11"/>
+      <c r="D558" s="11"/>
+      <c r="E558" s="11"/>
+    </row>
+    <row r="559" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C559" s="11"/>
+      <c r="D559" s="11"/>
+      <c r="E559" s="11"/>
+    </row>
+    <row r="560" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C560" s="11"/>
+      <c r="D560" s="11"/>
+      <c r="E560" s="11"/>
+    </row>
+    <row r="561" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C561" s="11"/>
+      <c r="D561" s="11"/>
+      <c r="E561" s="11"/>
+    </row>
+    <row r="562" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C562" s="11"/>
+      <c r="D562" s="11"/>
+      <c r="E562" s="11"/>
+    </row>
+    <row r="563" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C563" s="11"/>
+      <c r="D563" s="11"/>
+      <c r="E563" s="11"/>
+    </row>
+    <row r="564" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C564" s="11"/>
+      <c r="D564" s="11"/>
+      <c r="E564" s="11"/>
+    </row>
+    <row r="565" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C565" s="11"/>
+      <c r="D565" s="11"/>
+      <c r="E565" s="11"/>
+    </row>
+    <row r="566" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C566" s="11"/>
+      <c r="D566" s="11"/>
+      <c r="E566" s="11"/>
+    </row>
+    <row r="567" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C567" s="11"/>
+      <c r="D567" s="11"/>
+      <c r="E567" s="11"/>
+    </row>
+    <row r="568" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C568" s="11"/>
+      <c r="D568" s="11"/>
+      <c r="E568" s="11"/>
+    </row>
+    <row r="569" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C569" s="11"/>
+      <c r="D569" s="11"/>
+      <c r="E569" s="11"/>
+    </row>
+    <row r="570" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C570" s="11"/>
+      <c r="D570" s="11"/>
+      <c r="E570" s="11"/>
+    </row>
+    <row r="571" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C571" s="11"/>
+      <c r="D571" s="11"/>
+      <c r="E571" s="11"/>
+    </row>
+    <row r="572" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C572" s="11"/>
+      <c r="D572" s="11"/>
+      <c r="E572" s="11"/>
+    </row>
+    <row r="573" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C573" s="11"/>
+      <c r="D573" s="11"/>
+      <c r="E573" s="11"/>
+    </row>
+    <row r="574" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C574" s="11"/>
+      <c r="D574" s="11"/>
+      <c r="E574" s="11"/>
+    </row>
+    <row r="575" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C575" s="11"/>
+      <c r="D575" s="11"/>
+      <c r="E575" s="11"/>
+    </row>
+    <row r="576" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C576" s="11"/>
+      <c r="D576" s="11"/>
+      <c r="E576" s="11"/>
+    </row>
+    <row r="577" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C577" s="11"/>
+      <c r="D577" s="11"/>
+      <c r="E577" s="11"/>
+    </row>
+    <row r="578" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C578" s="11"/>
+      <c r="D578" s="11"/>
+      <c r="E578" s="11"/>
+    </row>
+    <row r="579" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C579" s="11"/>
+      <c r="D579" s="11"/>
+      <c r="E579" s="11"/>
+    </row>
+    <row r="580" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C580" s="11"/>
+      <c r="D580" s="11"/>
+      <c r="E580" s="11"/>
+    </row>
+    <row r="581" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C581" s="11"/>
+      <c r="D581" s="11"/>
+      <c r="E581" s="11"/>
+    </row>
+    <row r="582" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C582" s="11"/>
+      <c r="D582" s="11"/>
+      <c r="E582" s="11"/>
+    </row>
+    <row r="583" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C583" s="11"/>
+      <c r="D583" s="11"/>
+      <c r="E583" s="11"/>
+    </row>
+    <row r="584" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C584" s="11"/>
+      <c r="D584" s="11"/>
+      <c r="E584" s="11"/>
+    </row>
+    <row r="585" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C585" s="11"/>
+      <c r="D585" s="11"/>
+      <c r="E585" s="11"/>
+    </row>
+    <row r="586" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C586" s="11"/>
+      <c r="D586" s="11"/>
+      <c r="E586" s="11"/>
+    </row>
+    <row r="587" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C587" s="11"/>
+      <c r="D587" s="11"/>
+      <c r="E587" s="11"/>
+    </row>
+    <row r="588" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C588" s="11"/>
+      <c r="D588" s="11"/>
+      <c r="E588" s="11"/>
+    </row>
+    <row r="589" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C589" s="11"/>
+      <c r="D589" s="11"/>
+      <c r="E589" s="11"/>
+    </row>
+    <row r="590" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C590" s="11"/>
+      <c r="D590" s="11"/>
+      <c r="E590" s="11"/>
+    </row>
+    <row r="591" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C591" s="11"/>
+      <c r="D591" s="11"/>
+      <c r="E591" s="11"/>
+    </row>
+    <row r="592" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C592" s="11"/>
+      <c r="D592" s="11"/>
+      <c r="E592" s="11"/>
+    </row>
+    <row r="593" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C593" s="11"/>
+      <c r="D593" s="11"/>
+      <c r="E593" s="11"/>
+    </row>
+    <row r="594" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C594" s="11"/>
+      <c r="D594" s="11"/>
+      <c r="E594" s="11"/>
+    </row>
+    <row r="595" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C595" s="11"/>
+      <c r="D595" s="11"/>
+      <c r="E595" s="11"/>
+    </row>
+    <row r="596" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C596" s="11"/>
+      <c r="D596" s="11"/>
+      <c r="E596" s="11"/>
+    </row>
+    <row r="597" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C597" s="11"/>
+      <c r="D597" s="11"/>
+      <c r="E597" s="11"/>
+    </row>
+    <row r="598" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C598" s="11"/>
+      <c r="D598" s="11"/>
+      <c r="E598" s="11"/>
+    </row>
+    <row r="599" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C599" s="11"/>
+      <c r="D599" s="11"/>
+      <c r="E599" s="11"/>
+    </row>
+    <row r="600" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C600" s="11"/>
+      <c r="D600" s="11"/>
+      <c r="E600" s="11"/>
+    </row>
+    <row r="601" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C601" s="11"/>
+      <c r="D601" s="11"/>
+      <c r="E601" s="11"/>
+    </row>
+    <row r="602" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C602" s="11"/>
+      <c r="D602" s="11"/>
+      <c r="E602" s="11"/>
+    </row>
+    <row r="603" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C603" s="11"/>
+      <c r="D603" s="11"/>
+      <c r="E603" s="11"/>
+    </row>
+    <row r="604" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C604" s="11"/>
+      <c r="D604" s="11"/>
+      <c r="E604" s="11"/>
+    </row>
+    <row r="605" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C605" s="11"/>
+      <c r="D605" s="11"/>
+      <c r="E605" s="11"/>
+    </row>
+    <row r="606" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C606" s="11"/>
+      <c r="D606" s="11"/>
+      <c r="E606" s="11"/>
+    </row>
+    <row r="607" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C607" s="11"/>
+      <c r="D607" s="11"/>
+      <c r="E607" s="11"/>
+    </row>
+    <row r="608" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C608" s="11"/>
+      <c r="D608" s="11"/>
+      <c r="E608" s="11"/>
+    </row>
+    <row r="609" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C609" s="11"/>
+      <c r="D609" s="11"/>
+      <c r="E609" s="11"/>
+    </row>
+    <row r="610" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C610" s="11"/>
+      <c r="D610" s="11"/>
+      <c r="E610" s="11"/>
+    </row>
+    <row r="611" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C611" s="11"/>
+      <c r="D611" s="11"/>
+      <c r="E611" s="11"/>
+    </row>
+    <row r="612" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C612" s="11"/>
+      <c r="D612" s="11"/>
+      <c r="E612" s="11"/>
+    </row>
+    <row r="613" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C613" s="11"/>
+      <c r="D613" s="11"/>
+      <c r="E613" s="11"/>
+    </row>
+    <row r="614" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C614" s="11"/>
+      <c r="D614" s="11"/>
+      <c r="E614" s="11"/>
+    </row>
+    <row r="615" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C615" s="11"/>
+      <c r="D615" s="11"/>
+      <c r="E615" s="11"/>
+    </row>
+    <row r="616" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C616" s="11"/>
+      <c r="D616" s="11"/>
+      <c r="E616" s="11"/>
+    </row>
+    <row r="617" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C617" s="11"/>
+      <c r="D617" s="11"/>
+      <c r="E617" s="11"/>
+    </row>
+    <row r="618" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C618" s="11"/>
+      <c r="D618" s="11"/>
+      <c r="E618" s="11"/>
+    </row>
+    <row r="619" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C619" s="11"/>
+      <c r="D619" s="11"/>
+      <c r="E619" s="11"/>
+    </row>
+    <row r="620" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C620" s="11"/>
+      <c r="D620" s="11"/>
+      <c r="E620" s="11"/>
+    </row>
+    <row r="621" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C621" s="11"/>
+      <c r="D621" s="11"/>
+      <c r="E621" s="11"/>
+    </row>
+    <row r="622" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C622" s="11"/>
+      <c r="D622" s="11"/>
+      <c r="E622" s="11"/>
+    </row>
+    <row r="623" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C623" s="11"/>
+      <c r="D623" s="11"/>
+      <c r="E623" s="11"/>
+    </row>
+    <row r="624" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C624" s="11"/>
+      <c r="D624" s="11"/>
+      <c r="E624" s="11"/>
+    </row>
+    <row r="625" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C625" s="11"/>
+      <c r="D625" s="11"/>
+      <c r="E625" s="11"/>
+    </row>
+    <row r="626" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C626" s="11"/>
+      <c r="D626" s="11"/>
+      <c r="E626" s="11"/>
+    </row>
+    <row r="627" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C627" s="11"/>
+      <c r="D627" s="11"/>
+      <c r="E627" s="11"/>
+    </row>
+    <row r="628" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C628" s="11"/>
+      <c r="D628" s="11"/>
+      <c r="E628" s="11"/>
+    </row>
+    <row r="629" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C629" s="11"/>
+      <c r="D629" s="11"/>
+      <c r="E629" s="11"/>
+    </row>
+    <row r="630" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C630" s="11"/>
+      <c r="D630" s="11"/>
+      <c r="E630" s="11"/>
+    </row>
+    <row r="631" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C631" s="11"/>
+      <c r="D631" s="11"/>
+      <c r="E631" s="11"/>
+    </row>
+    <row r="632" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C632" s="11"/>
+      <c r="D632" s="11"/>
+      <c r="E632" s="11"/>
+    </row>
+    <row r="633" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C633" s="11"/>
+      <c r="D633" s="11"/>
+      <c r="E633" s="11"/>
+    </row>
+    <row r="634" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C634" s="11"/>
+      <c r="D634" s="11"/>
+      <c r="E634" s="11"/>
+    </row>
+    <row r="635" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C635" s="11"/>
+      <c r="D635" s="11"/>
+      <c r="E635" s="11"/>
+    </row>
+    <row r="636" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C636" s="11"/>
+      <c r="D636" s="11"/>
+      <c r="E636" s="11"/>
+    </row>
+    <row r="637" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C637" s="11"/>
+      <c r="D637" s="11"/>
+      <c r="E637" s="11"/>
+    </row>
+    <row r="638" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C638" s="11"/>
+      <c r="D638" s="11"/>
+      <c r="E638" s="11"/>
+    </row>
+    <row r="639" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C639" s="11"/>
+      <c r="D639" s="11"/>
+      <c r="E639" s="11"/>
+    </row>
+    <row r="640" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C640" s="11"/>
+      <c r="D640" s="11"/>
+      <c r="E640" s="11"/>
+    </row>
+    <row r="641" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C641" s="11"/>
+      <c r="D641" s="11"/>
+      <c r="E641" s="11"/>
+    </row>
+    <row r="642" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C642" s="11"/>
+      <c r="D642" s="11"/>
+      <c r="E642" s="11"/>
+    </row>
+    <row r="643" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C643" s="11"/>
+      <c r="D643" s="11"/>
+      <c r="E643" s="11"/>
+    </row>
+    <row r="644" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C644" s="11"/>
+      <c r="D644" s="11"/>
+      <c r="E644" s="11"/>
+    </row>
+    <row r="645" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C645" s="11"/>
+      <c r="D645" s="11"/>
+      <c r="E645" s="11"/>
+    </row>
+    <row r="646" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C646" s="11"/>
+      <c r="D646" s="11"/>
+      <c r="E646" s="11"/>
+    </row>
+    <row r="647" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C647" s="11"/>
+      <c r="D647" s="11"/>
+      <c r="E647" s="11"/>
+    </row>
+    <row r="648" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C648" s="11"/>
+      <c r="D648" s="11"/>
+      <c r="E648" s="11"/>
+    </row>
+    <row r="649" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C649" s="11"/>
+      <c r="D649" s="11"/>
+      <c r="E649" s="11"/>
+    </row>
+    <row r="650" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C650" s="11"/>
+      <c r="D650" s="11"/>
+      <c r="E650" s="11"/>
+    </row>
+    <row r="651" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C651" s="11"/>
+      <c r="D651" s="11"/>
+      <c r="E651" s="11"/>
+    </row>
+    <row r="652" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C652" s="11"/>
+      <c r="D652" s="11"/>
+      <c r="E652" s="11"/>
+    </row>
+    <row r="653" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C653" s="11"/>
+      <c r="D653" s="11"/>
+      <c r="E653" s="11"/>
+    </row>
+    <row r="654" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C654" s="11"/>
+      <c r="D654" s="11"/>
+      <c r="E654" s="11"/>
+    </row>
+    <row r="655" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C655" s="11"/>
+      <c r="D655" s="11"/>
+      <c r="E655" s="11"/>
+    </row>
+    <row r="656" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C656" s="11"/>
+      <c r="D656" s="11"/>
+      <c r="E656" s="11"/>
+    </row>
+    <row r="657" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C657" s="11"/>
+      <c r="D657" s="11"/>
+      <c r="E657" s="11"/>
+    </row>
+    <row r="658" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C658" s="11"/>
+      <c r="D658" s="11"/>
+      <c r="E658" s="11"/>
+    </row>
+    <row r="659" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C659" s="11"/>
+      <c r="D659" s="11"/>
+      <c r="E659" s="11"/>
+    </row>
+    <row r="660" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C660" s="11"/>
+      <c r="D660" s="11"/>
+      <c r="E660" s="11"/>
+    </row>
+    <row r="661" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C661" s="11"/>
+      <c r="D661" s="11"/>
+      <c r="E661" s="11"/>
+    </row>
+    <row r="662" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C662" s="11"/>
+      <c r="D662" s="11"/>
+      <c r="E662" s="11"/>
+    </row>
+    <row r="663" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C663" s="11"/>
+      <c r="D663" s="11"/>
+      <c r="E663" s="11"/>
+    </row>
+    <row r="664" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C664" s="11"/>
+      <c r="D664" s="11"/>
+      <c r="E664" s="11"/>
+    </row>
+    <row r="665" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C665" s="11"/>
+      <c r="D665" s="11"/>
+      <c r="E665" s="11"/>
+    </row>
+    <row r="666" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C666" s="11"/>
+      <c r="D666" s="11"/>
+      <c r="E666" s="11"/>
+    </row>
+    <row r="667" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C667" s="11"/>
+      <c r="D667" s="11"/>
+      <c r="E667" s="11"/>
+    </row>
+    <row r="668" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C668" s="11"/>
+      <c r="D668" s="11"/>
+      <c r="E668" s="11"/>
+    </row>
+    <row r="669" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C669" s="11"/>
+      <c r="D669" s="11"/>
+      <c r="E669" s="11"/>
+    </row>
+    <row r="670" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C670" s="11"/>
+      <c r="D670" s="11"/>
+      <c r="E670" s="11"/>
+    </row>
+    <row r="671" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C671" s="11"/>
+      <c r="D671" s="11"/>
+      <c r="E671" s="11"/>
+    </row>
+    <row r="672" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C672" s="11"/>
+      <c r="D672" s="11"/>
+      <c r="E672" s="11"/>
+    </row>
+    <row r="673" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C673" s="11"/>
+      <c r="D673" s="11"/>
+      <c r="E673" s="11"/>
+    </row>
+    <row r="674" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C674" s="11"/>
+      <c r="D674" s="11"/>
+      <c r="E674" s="11"/>
+    </row>
+    <row r="675" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C675" s="11"/>
+      <c r="D675" s="11"/>
+      <c r="E675" s="11"/>
+    </row>
+    <row r="676" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C676" s="11"/>
+      <c r="D676" s="11"/>
+      <c r="E676" s="11"/>
+    </row>
+    <row r="677" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C677" s="11"/>
+      <c r="D677" s="11"/>
+      <c r="E677" s="11"/>
+    </row>
+    <row r="678" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C678" s="11"/>
+      <c r="D678" s="11"/>
+      <c r="E678" s="11"/>
+    </row>
+    <row r="679" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C679" s="11"/>
+      <c r="D679" s="11"/>
+      <c r="E679" s="11"/>
+    </row>
+    <row r="680" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C680" s="11"/>
+      <c r="D680" s="11"/>
+      <c r="E680" s="11"/>
+    </row>
+    <row r="681" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C681" s="11"/>
+      <c r="D681" s="11"/>
+      <c r="E681" s="11"/>
+    </row>
+    <row r="682" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C682" s="11"/>
+      <c r="D682" s="11"/>
+      <c r="E682" s="11"/>
+    </row>
+    <row r="683" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C683" s="11"/>
+      <c r="D683" s="11"/>
+      <c r="E683" s="11"/>
+    </row>
+    <row r="684" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C684" s="11"/>
+      <c r="D684" s="11"/>
+      <c r="E684" s="11"/>
+    </row>
+    <row r="685" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C685" s="11"/>
+      <c r="D685" s="11"/>
+      <c r="E685" s="11"/>
+    </row>
+    <row r="686" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C686" s="11"/>
+      <c r="D686" s="11"/>
+      <c r="E686" s="11"/>
+    </row>
+    <row r="687" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C687" s="11"/>
+      <c r="D687" s="11"/>
+      <c r="E687" s="11"/>
+    </row>
+    <row r="688" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C688" s="11"/>
+      <c r="D688" s="11"/>
+      <c r="E688" s="11"/>
+    </row>
+    <row r="689" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C689" s="11"/>
+      <c r="D689" s="11"/>
+      <c r="E689" s="11"/>
+    </row>
+    <row r="690" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C690" s="11"/>
+      <c r="D690" s="11"/>
+      <c r="E690" s="11"/>
+    </row>
+    <row r="691" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C691" s="11"/>
+      <c r="D691" s="11"/>
+      <c r="E691" s="11"/>
+    </row>
+    <row r="692" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C692" s="11"/>
+      <c r="D692" s="11"/>
+      <c r="E692" s="11"/>
+    </row>
+    <row r="693" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C693" s="11"/>
+      <c r="D693" s="11"/>
+      <c r="E693" s="11"/>
+    </row>
+    <row r="694" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C694" s="11"/>
+      <c r="D694" s="11"/>
+      <c r="E694" s="11"/>
+    </row>
+    <row r="695" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C695" s="11"/>
+      <c r="D695" s="11"/>
+      <c r="E695" s="11"/>
+    </row>
+    <row r="696" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C696" s="11"/>
+      <c r="D696" s="11"/>
+      <c r="E696" s="11"/>
+    </row>
+    <row r="697" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C697" s="11"/>
+      <c r="D697" s="11"/>
+      <c r="E697" s="11"/>
+    </row>
+    <row r="698" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C698" s="11"/>
+      <c r="D698" s="11"/>
+      <c r="E698" s="11"/>
+    </row>
+    <row r="699" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C699" s="11"/>
+      <c r="D699" s="11"/>
+      <c r="E699" s="11"/>
+    </row>
+    <row r="700" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C700" s="11"/>
+      <c r="D700" s="11"/>
+      <c r="E700" s="11"/>
+    </row>
+    <row r="701" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C701" s="11"/>
+      <c r="D701" s="11"/>
+      <c r="E701" s="11"/>
+    </row>
+    <row r="702" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C702" s="11"/>
+      <c r="D702" s="11"/>
+      <c r="E702" s="11"/>
+    </row>
+    <row r="703" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C703" s="11"/>
+      <c r="D703" s="11"/>
+      <c r="E703" s="11"/>
+    </row>
+    <row r="704" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C704" s="11"/>
+      <c r="D704" s="11"/>
+      <c r="E704" s="11"/>
+    </row>
+    <row r="705" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C705" s="11"/>
+      <c r="D705" s="11"/>
+      <c r="E705" s="11"/>
+    </row>
+    <row r="706" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C706" s="11"/>
+      <c r="D706" s="11"/>
+      <c r="E706" s="11"/>
+    </row>
+    <row r="707" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C707" s="11"/>
+      <c r="D707" s="11"/>
+      <c r="E707" s="11"/>
+    </row>
+    <row r="708" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C708" s="11"/>
+      <c r="D708" s="11"/>
+      <c r="E708" s="11"/>
+    </row>
+    <row r="709" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C709" s="11"/>
+      <c r="D709" s="11"/>
+      <c r="E709" s="11"/>
+    </row>
+    <row r="710" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C710" s="11"/>
+      <c r="D710" s="11"/>
+      <c r="E710" s="11"/>
+    </row>
+    <row r="711" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C711" s="11"/>
+      <c r="D711" s="11"/>
+      <c r="E711" s="11"/>
+    </row>
+    <row r="712" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C712" s="11"/>
+      <c r="D712" s="11"/>
+      <c r="E712" s="11"/>
+    </row>
+    <row r="713" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C713" s="11"/>
+      <c r="D713" s="11"/>
+      <c r="E713" s="11"/>
+    </row>
+    <row r="714" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C714" s="11"/>
+      <c r="D714" s="11"/>
+      <c r="E714" s="11"/>
+    </row>
+    <row r="715" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C715" s="11"/>
+      <c r="D715" s="11"/>
+      <c r="E715" s="11"/>
+    </row>
+    <row r="716" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C716" s="11"/>
+      <c r="D716" s="11"/>
+      <c r="E716" s="11"/>
+    </row>
+    <row r="717" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C717" s="11"/>
+      <c r="D717" s="11"/>
+      <c r="E717" s="11"/>
+    </row>
+    <row r="718" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C718" s="11"/>
+      <c r="D718" s="11"/>
+      <c r="E718" s="11"/>
+    </row>
+    <row r="719" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C719" s="11"/>
+      <c r="D719" s="11"/>
+      <c r="E719" s="11"/>
+    </row>
+    <row r="720" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C720" s="11"/>
+      <c r="D720" s="11"/>
+      <c r="E720" s="11"/>
+    </row>
+    <row r="721" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C721" s="11"/>
+      <c r="D721" s="11"/>
+      <c r="E721" s="11"/>
+    </row>
+    <row r="722" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C722" s="11"/>
+      <c r="D722" s="11"/>
+      <c r="E722" s="11"/>
+    </row>
+    <row r="723" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C723" s="11"/>
+      <c r="D723" s="11"/>
+      <c r="E723" s="11"/>
+    </row>
+    <row r="724" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C724" s="11"/>
+      <c r="D724" s="11"/>
+      <c r="E724" s="11"/>
+    </row>
+    <row r="725" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C725" s="11"/>
+      <c r="D725" s="11"/>
+      <c r="E725" s="11"/>
+    </row>
+    <row r="726" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C726" s="11"/>
+      <c r="D726" s="11"/>
+      <c r="E726" s="11"/>
+    </row>
+    <row r="727" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C727" s="11"/>
+      <c r="D727" s="11"/>
+      <c r="E727" s="11"/>
+    </row>
+    <row r="728" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C728" s="11"/>
+      <c r="D728" s="11"/>
+      <c r="E728" s="11"/>
+    </row>
+    <row r="729" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C729" s="11"/>
+      <c r="D729" s="11"/>
+      <c r="E729" s="11"/>
+    </row>
+    <row r="730" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C730" s="11"/>
+      <c r="D730" s="11"/>
+      <c r="E730" s="11"/>
+    </row>
+    <row r="731" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C731" s="11"/>
+      <c r="D731" s="11"/>
+      <c r="E731" s="11"/>
+    </row>
+    <row r="732" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C732" s="11"/>
+      <c r="D732" s="11"/>
+      <c r="E732" s="11"/>
+    </row>
+    <row r="733" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C733" s="11"/>
+      <c r="D733" s="11"/>
+      <c r="E733" s="11"/>
+    </row>
+    <row r="734" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C734" s="11"/>
+      <c r="D734" s="11"/>
+      <c r="E734" s="11"/>
+    </row>
+    <row r="735" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C735" s="11"/>
+      <c r="D735" s="11"/>
+      <c r="E735" s="11"/>
+    </row>
+    <row r="736" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C736" s="11"/>
+      <c r="D736" s="11"/>
+      <c r="E736" s="11"/>
+    </row>
+    <row r="737" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C737" s="11"/>
+      <c r="D737" s="11"/>
+      <c r="E737" s="11"/>
+    </row>
+    <row r="738" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C738" s="11"/>
+      <c r="D738" s="11"/>
+      <c r="E738" s="11"/>
+    </row>
+    <row r="739" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C739" s="11"/>
+      <c r="D739" s="11"/>
+      <c r="E739" s="11"/>
+    </row>
+    <row r="740" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C740" s="11"/>
+      <c r="D740" s="11"/>
+      <c r="E740" s="11"/>
+    </row>
+    <row r="741" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C741" s="11"/>
+      <c r="D741" s="11"/>
+      <c r="E741" s="11"/>
+    </row>
+    <row r="742" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C742" s="11"/>
+      <c r="D742" s="11"/>
+      <c r="E742" s="11"/>
+    </row>
+    <row r="743" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C743" s="11"/>
+      <c r="D743" s="11"/>
+      <c r="E743" s="11"/>
+    </row>
+    <row r="744" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C744" s="11"/>
+      <c r="D744" s="11"/>
+      <c r="E744" s="11"/>
+    </row>
+    <row r="745" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C745" s="11"/>
+      <c r="D745" s="11"/>
+      <c r="E745" s="11"/>
+    </row>
+    <row r="746" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C746" s="11"/>
+      <c r="D746" s="11"/>
+      <c r="E746" s="11"/>
+    </row>
+    <row r="747" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C747" s="11"/>
+      <c r="D747" s="11"/>
+      <c r="E747" s="11"/>
+    </row>
+    <row r="748" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C748" s="11"/>
+      <c r="D748" s="11"/>
+      <c r="E748" s="11"/>
+    </row>
+    <row r="749" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C749" s="11"/>
+      <c r="D749" s="11"/>
+      <c r="E749" s="11"/>
+    </row>
+    <row r="750" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C750" s="11"/>
+      <c r="D750" s="11"/>
+      <c r="E750" s="11"/>
+    </row>
+    <row r="751" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C751" s="11"/>
+      <c r="D751" s="11"/>
+      <c r="E751" s="11"/>
+    </row>
+    <row r="752" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C752" s="11"/>
+      <c r="D752" s="11"/>
+      <c r="E752" s="11"/>
+    </row>
+    <row r="753" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C753" s="11"/>
+      <c r="D753" s="11"/>
+      <c r="E753" s="11"/>
+    </row>
+    <row r="754" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C754" s="11"/>
+      <c r="D754" s="11"/>
+      <c r="E754" s="11"/>
+    </row>
+    <row r="755" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C755" s="11"/>
+      <c r="D755" s="11"/>
+      <c r="E755" s="11"/>
+    </row>
+    <row r="756" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C756" s="11"/>
+      <c r="D756" s="11"/>
+      <c r="E756" s="11"/>
+    </row>
+    <row r="757" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C757" s="11"/>
+      <c r="D757" s="11"/>
+      <c r="E757" s="11"/>
+    </row>
+    <row r="758" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C758" s="11"/>
+      <c r="D758" s="11"/>
+      <c r="E758" s="11"/>
+    </row>
+    <row r="759" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C759" s="11"/>
+      <c r="D759" s="11"/>
+      <c r="E759" s="11"/>
+    </row>
+    <row r="760" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C760" s="11"/>
+      <c r="D760" s="11"/>
+      <c r="E760" s="11"/>
+    </row>
+    <row r="761" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C761" s="11"/>
+      <c r="D761" s="11"/>
+      <c r="E761" s="11"/>
+    </row>
+    <row r="762" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C762" s="11"/>
+      <c r="D762" s="11"/>
+      <c r="E762" s="11"/>
+    </row>
+    <row r="763" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C763" s="11"/>
+      <c r="D763" s="11"/>
+      <c r="E763" s="11"/>
+    </row>
+    <row r="764" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C764" s="11"/>
+      <c r="D764" s="11"/>
+      <c r="E764" s="11"/>
+    </row>
+    <row r="765" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C765" s="11"/>
+      <c r="D765" s="11"/>
+      <c r="E765" s="11"/>
+    </row>
+    <row r="766" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C766" s="11"/>
+      <c r="D766" s="11"/>
+      <c r="E766" s="11"/>
+    </row>
+    <row r="767" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C767" s="11"/>
+      <c r="D767" s="11"/>
+      <c r="E767" s="11"/>
+    </row>
+    <row r="768" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C768" s="11"/>
+      <c r="D768" s="11"/>
+      <c r="E768" s="11"/>
+    </row>
+    <row r="769" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C769" s="11"/>
+      <c r="D769" s="11"/>
+      <c r="E769" s="11"/>
+    </row>
+    <row r="770" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C770" s="11"/>
+      <c r="D770" s="11"/>
+      <c r="E770" s="11"/>
+    </row>
+    <row r="771" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C771" s="11"/>
+      <c r="D771" s="11"/>
+      <c r="E771" s="11"/>
+    </row>
+    <row r="772" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C772" s="11"/>
+      <c r="D772" s="11"/>
+      <c r="E772" s="11"/>
+    </row>
+    <row r="773" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C773" s="11"/>
+      <c r="D773" s="11"/>
+      <c r="E773" s="11"/>
+    </row>
+    <row r="774" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C774" s="11"/>
+      <c r="D774" s="11"/>
+      <c r="E774" s="11"/>
+    </row>
+    <row r="775" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C775" s="11"/>
+      <c r="D775" s="11"/>
+      <c r="E775" s="11"/>
+    </row>
+    <row r="776" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C776" s="11"/>
+      <c r="D776" s="11"/>
+      <c r="E776" s="11"/>
+    </row>
+    <row r="777" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C777" s="11"/>
+      <c r="D777" s="11"/>
+      <c r="E777" s="11"/>
+    </row>
+    <row r="778" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C778" s="11"/>
+      <c r="D778" s="11"/>
+      <c r="E778" s="11"/>
+    </row>
+    <row r="779" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C779" s="11"/>
+      <c r="D779" s="11"/>
+      <c r="E779" s="11"/>
+    </row>
+    <row r="780" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C780" s="11"/>
+      <c r="D780" s="11"/>
+      <c r="E780" s="11"/>
+    </row>
+    <row r="781" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C781" s="11"/>
+      <c r="D781" s="11"/>
+      <c r="E781" s="11"/>
+    </row>
+    <row r="782" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C782" s="11"/>
+      <c r="D782" s="11"/>
+      <c r="E782" s="11"/>
+    </row>
+    <row r="783" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C783" s="11"/>
+      <c r="D783" s="11"/>
+      <c r="E783" s="11"/>
+    </row>
+    <row r="784" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C784" s="11"/>
+      <c r="D784" s="11"/>
+      <c r="E784" s="11"/>
+    </row>
+    <row r="785" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C785" s="11"/>
+      <c r="D785" s="11"/>
+      <c r="E785" s="11"/>
+    </row>
+    <row r="786" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C786" s="11"/>
+      <c r="D786" s="11"/>
+      <c r="E786" s="11"/>
+    </row>
+    <row r="787" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C787" s="11"/>
+      <c r="D787" s="11"/>
+      <c r="E787" s="11"/>
+    </row>
+    <row r="788" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C788" s="11"/>
+      <c r="D788" s="11"/>
+      <c r="E788" s="11"/>
+    </row>
+    <row r="789" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C789" s="11"/>
+      <c r="D789" s="11"/>
+      <c r="E789" s="11"/>
+    </row>
+    <row r="790" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C790" s="11"/>
+      <c r="D790" s="11"/>
+      <c r="E790" s="11"/>
+    </row>
+    <row r="791" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C791" s="11"/>
+      <c r="D791" s="11"/>
+      <c r="E791" s="11"/>
+    </row>
+    <row r="792" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C792" s="11"/>
+      <c r="D792" s="11"/>
+      <c r="E792" s="11"/>
+    </row>
+    <row r="793" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C793" s="11"/>
+      <c r="D793" s="11"/>
+      <c r="E793" s="11"/>
+    </row>
+    <row r="794" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C794" s="11"/>
+      <c r="D794" s="11"/>
+      <c r="E794" s="11"/>
+    </row>
+    <row r="795" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C795" s="11"/>
+      <c r="D795" s="11"/>
+      <c r="E795" s="11"/>
+    </row>
+    <row r="796" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C796" s="11"/>
+      <c r="D796" s="11"/>
+      <c r="E796" s="11"/>
+    </row>
+    <row r="797" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C797" s="11"/>
+      <c r="D797" s="11"/>
+      <c r="E797" s="11"/>
+    </row>
+    <row r="798" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C798" s="11"/>
+      <c r="D798" s="11"/>
+      <c r="E798" s="11"/>
+    </row>
+    <row r="799" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C799" s="11"/>
+      <c r="D799" s="11"/>
+      <c r="E799" s="11"/>
+    </row>
+    <row r="800" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C800" s="11"/>
+      <c r="D800" s="11"/>
+      <c r="E800" s="11"/>
+    </row>
+    <row r="801" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C801" s="11"/>
+      <c r="D801" s="11"/>
+      <c r="E801" s="11"/>
+    </row>
+    <row r="802" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C802" s="11"/>
+      <c r="D802" s="11"/>
+      <c r="E802" s="11"/>
+    </row>
+    <row r="803" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C803" s="11"/>
+      <c r="D803" s="11"/>
+      <c r="E803" s="11"/>
+    </row>
+    <row r="804" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C804" s="11"/>
+      <c r="D804" s="11"/>
+      <c r="E804" s="11"/>
+    </row>
+    <row r="805" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C805" s="11"/>
+      <c r="D805" s="11"/>
+      <c r="E805" s="11"/>
+    </row>
+    <row r="806" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C806" s="11"/>
+      <c r="D806" s="11"/>
+      <c r="E806" s="11"/>
+    </row>
+    <row r="807" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C807" s="11"/>
+      <c r="D807" s="11"/>
+      <c r="E807" s="11"/>
+    </row>
+    <row r="808" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C808" s="11"/>
+      <c r="D808" s="11"/>
+      <c r="E808" s="11"/>
+    </row>
+    <row r="809" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C809" s="11"/>
+      <c r="D809" s="11"/>
+      <c r="E809" s="11"/>
+    </row>
+    <row r="810" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C810" s="11"/>
+      <c r="D810" s="11"/>
+      <c r="E810" s="11"/>
+    </row>
+    <row r="811" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C811" s="11"/>
+      <c r="D811" s="11"/>
+      <c r="E811" s="11"/>
+    </row>
+    <row r="812" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C812" s="11"/>
+      <c r="D812" s="11"/>
+      <c r="E812" s="11"/>
+    </row>
+    <row r="813" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C813" s="11"/>
+      <c r="D813" s="11"/>
+      <c r="E813" s="11"/>
+    </row>
+    <row r="814" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C814" s="11"/>
+      <c r="D814" s="11"/>
+      <c r="E814" s="11"/>
+    </row>
+    <row r="815" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C815" s="11"/>
+      <c r="D815" s="11"/>
+      <c r="E815" s="11"/>
+    </row>
+    <row r="816" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C816" s="11"/>
+      <c r="D816" s="11"/>
+      <c r="E816" s="11"/>
+    </row>
+    <row r="817" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C817" s="11"/>
+      <c r="D817" s="11"/>
+      <c r="E817" s="11"/>
+    </row>
+    <row r="818" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C818" s="11"/>
+      <c r="D818" s="11"/>
+      <c r="E818" s="11"/>
+    </row>
+    <row r="819" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C819" s="11"/>
+      <c r="D819" s="11"/>
+      <c r="E819" s="11"/>
+    </row>
+    <row r="820" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C820" s="11"/>
+      <c r="D820" s="11"/>
+      <c r="E820" s="11"/>
+    </row>
+    <row r="821" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C821" s="11"/>
+      <c r="D821" s="11"/>
+      <c r="E821" s="11"/>
+    </row>
+    <row r="822" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C822" s="11"/>
+      <c r="D822" s="11"/>
+      <c r="E822" s="11"/>
+    </row>
+    <row r="823" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C823" s="11"/>
+      <c r="D823" s="11"/>
+      <c r="E823" s="11"/>
+    </row>
+    <row r="824" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C824" s="11"/>
+      <c r="D824" s="11"/>
+      <c r="E824" s="11"/>
+    </row>
+    <row r="825" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C825" s="11"/>
+      <c r="D825" s="11"/>
+      <c r="E825" s="11"/>
+    </row>
+    <row r="826" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C826" s="11"/>
+      <c r="D826" s="11"/>
+      <c r="E826" s="11"/>
+    </row>
+    <row r="827" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C827" s="11"/>
+      <c r="D827" s="11"/>
+      <c r="E827" s="11"/>
+    </row>
+    <row r="828" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C828" s="11"/>
+      <c r="D828" s="11"/>
+      <c r="E828" s="11"/>
+    </row>
+    <row r="829" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C829" s="11"/>
+      <c r="D829" s="11"/>
+      <c r="E829" s="11"/>
+    </row>
+    <row r="830" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C830" s="11"/>
+      <c r="D830" s="11"/>
+      <c r="E830" s="11"/>
+    </row>
+    <row r="831" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C831" s="11"/>
+      <c r="D831" s="11"/>
+      <c r="E831" s="11"/>
+    </row>
+    <row r="832" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C832" s="11"/>
+      <c r="D832" s="11"/>
+      <c r="E832" s="11"/>
+    </row>
+    <row r="833" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C833" s="11"/>
+      <c r="D833" s="11"/>
+      <c r="E833" s="11"/>
+    </row>
+    <row r="834" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C834" s="11"/>
+      <c r="D834" s="11"/>
+      <c r="E834" s="11"/>
+    </row>
+    <row r="835" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C835" s="11"/>
+      <c r="D835" s="11"/>
+      <c r="E835" s="11"/>
+    </row>
+    <row r="836" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C836" s="11"/>
+      <c r="D836" s="11"/>
+      <c r="E836" s="11"/>
+    </row>
+    <row r="837" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C837" s="11"/>
+      <c r="D837" s="11"/>
+      <c r="E837" s="11"/>
+    </row>
+    <row r="838" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C838" s="11"/>
+      <c r="D838" s="11"/>
+      <c r="E838" s="11"/>
+    </row>
+    <row r="839" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C839" s="11"/>
+      <c r="D839" s="11"/>
+      <c r="E839" s="11"/>
+    </row>
+    <row r="840" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C840" s="11"/>
+      <c r="D840" s="11"/>
+      <c r="E840" s="11"/>
+    </row>
+    <row r="841" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C841" s="11"/>
+      <c r="D841" s="11"/>
+      <c r="E841" s="11"/>
+    </row>
+    <row r="842" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C842" s="11"/>
+      <c r="D842" s="11"/>
+      <c r="E842" s="11"/>
+    </row>
+    <row r="843" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C843" s="11"/>
+      <c r="D843" s="11"/>
+      <c r="E843" s="11"/>
+    </row>
+    <row r="844" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C844" s="11"/>
+      <c r="D844" s="11"/>
+      <c r="E844" s="11"/>
+    </row>
+    <row r="845" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C845" s="11"/>
+      <c r="D845" s="11"/>
+      <c r="E845" s="11"/>
+    </row>
+    <row r="846" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C846" s="11"/>
+      <c r="D846" s="11"/>
+      <c r="E846" s="11"/>
+    </row>
+    <row r="847" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C847" s="11"/>
+      <c r="D847" s="11"/>
+      <c r="E847" s="11"/>
+    </row>
+    <row r="848" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C848" s="11"/>
+      <c r="D848" s="11"/>
+      <c r="E848" s="11"/>
+    </row>
+    <row r="849" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C849" s="11"/>
+      <c r="D849" s="11"/>
+      <c r="E849" s="11"/>
+    </row>
+    <row r="850" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C850" s="11"/>
+      <c r="D850" s="11"/>
+      <c r="E850" s="11"/>
+    </row>
+    <row r="851" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C851" s="11"/>
+      <c r="D851" s="11"/>
+      <c r="E851" s="11"/>
+    </row>
+    <row r="852" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C852" s="11"/>
+      <c r="D852" s="11"/>
+      <c r="E852" s="11"/>
+    </row>
+    <row r="853" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C853" s="11"/>
+      <c r="D853" s="11"/>
+      <c r="E853" s="11"/>
+    </row>
+    <row r="854" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C854" s="11"/>
+      <c r="D854" s="11"/>
+      <c r="E854" s="11"/>
+    </row>
+    <row r="855" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C855" s="11"/>
+      <c r="D855" s="11"/>
+      <c r="E855" s="11"/>
+    </row>
+    <row r="856" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C856" s="11"/>
+      <c r="D856" s="11"/>
+      <c r="E856" s="11"/>
+    </row>
+    <row r="857" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C857" s="11"/>
+      <c r="D857" s="11"/>
+      <c r="E857" s="11"/>
+    </row>
+    <row r="858" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C858" s="11"/>
+      <c r="D858" s="11"/>
+      <c r="E858" s="11"/>
+    </row>
+    <row r="859" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C859" s="11"/>
+      <c r="D859" s="11"/>
+      <c r="E859" s="11"/>
+    </row>
+    <row r="860" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C860" s="11"/>
+      <c r="D860" s="11"/>
+      <c r="E860" s="11"/>
+    </row>
+    <row r="861" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C861" s="11"/>
+      <c r="D861" s="11"/>
+      <c r="E861" s="11"/>
+    </row>
+    <row r="862" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C862" s="11"/>
+      <c r="D862" s="11"/>
+      <c r="E862" s="11"/>
+    </row>
+    <row r="863" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C863" s="11"/>
+      <c r="D863" s="11"/>
+      <c r="E863" s="11"/>
+    </row>
+    <row r="864" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C864" s="11"/>
+      <c r="D864" s="11"/>
+      <c r="E864" s="11"/>
+    </row>
+    <row r="865" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C865" s="11"/>
+      <c r="D865" s="11"/>
+      <c r="E865" s="11"/>
+    </row>
+    <row r="866" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C866" s="11"/>
+      <c r="D866" s="11"/>
+      <c r="E866" s="11"/>
+    </row>
+    <row r="867" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C867" s="11"/>
+      <c r="D867" s="11"/>
+      <c r="E867" s="11"/>
+    </row>
+    <row r="868" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C868" s="11"/>
+      <c r="D868" s="11"/>
+      <c r="E868" s="11"/>
+    </row>
+    <row r="869" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C869" s="11"/>
+      <c r="D869" s="11"/>
+      <c r="E869" s="11"/>
+    </row>
+    <row r="870" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C870" s="11"/>
+      <c r="D870" s="11"/>
+      <c r="E870" s="11"/>
+    </row>
+    <row r="871" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C871" s="11"/>
+      <c r="D871" s="11"/>
+      <c r="E871" s="11"/>
+    </row>
+    <row r="872" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C872" s="11"/>
+      <c r="D872" s="11"/>
+      <c r="E872" s="11"/>
+    </row>
+    <row r="873" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C873" s="11"/>
+      <c r="D873" s="11"/>
+      <c r="E873" s="11"/>
+    </row>
+    <row r="874" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C874" s="11"/>
+      <c r="D874" s="11"/>
+      <c r="E874" s="11"/>
+    </row>
+    <row r="875" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C875" s="11"/>
+      <c r="D875" s="11"/>
+      <c r="E875" s="11"/>
+    </row>
+    <row r="876" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C876" s="11"/>
+      <c r="D876" s="11"/>
+      <c r="E876" s="11"/>
+    </row>
+    <row r="877" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C877" s="11"/>
+      <c r="D877" s="11"/>
+      <c r="E877" s="11"/>
+    </row>
+    <row r="878" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C878" s="11"/>
+      <c r="D878" s="11"/>
+      <c r="E878" s="11"/>
+    </row>
+    <row r="879" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C879" s="11"/>
+      <c r="D879" s="11"/>
+      <c r="E879" s="11"/>
+    </row>
+    <row r="880" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C880" s="11"/>
+      <c r="D880" s="11"/>
+      <c r="E880" s="11"/>
+    </row>
+    <row r="881" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C881" s="11"/>
+      <c r="D881" s="11"/>
+      <c r="E881" s="11"/>
+    </row>
+    <row r="882" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C882" s="11"/>
+      <c r="D882" s="11"/>
+      <c r="E882" s="11"/>
+    </row>
+    <row r="883" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C883" s="11"/>
+      <c r="D883" s="11"/>
+      <c r="E883" s="11"/>
+    </row>
+    <row r="884" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C884" s="11"/>
+      <c r="D884" s="11"/>
+      <c r="E884" s="11"/>
+    </row>
+    <row r="885" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C885" s="11"/>
+      <c r="D885" s="11"/>
+      <c r="E885" s="11"/>
+    </row>
+    <row r="886" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C886" s="11"/>
+      <c r="D886" s="11"/>
+      <c r="E886" s="11"/>
+    </row>
+    <row r="887" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C887" s="11"/>
+      <c r="D887" s="11"/>
+      <c r="E887" s="11"/>
+    </row>
+    <row r="888" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C888" s="11"/>
+      <c r="D888" s="11"/>
+      <c r="E888" s="11"/>
+    </row>
+    <row r="889" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C889" s="11"/>
+      <c r="D889" s="11"/>
+      <c r="E889" s="11"/>
+    </row>
+    <row r="890" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C890" s="11"/>
+      <c r="D890" s="11"/>
+      <c r="E890" s="11"/>
+    </row>
+    <row r="891" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C891" s="11"/>
+      <c r="D891" s="11"/>
+      <c r="E891" s="11"/>
+    </row>
+    <row r="892" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C892" s="11"/>
+      <c r="D892" s="11"/>
+      <c r="E892" s="11"/>
+    </row>
+    <row r="893" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C893" s="11"/>
+      <c r="D893" s="11"/>
+      <c r="E893" s="11"/>
+    </row>
+    <row r="894" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C894" s="11"/>
+      <c r="D894" s="11"/>
+      <c r="E894" s="11"/>
+    </row>
+    <row r="895" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C895" s="11"/>
+      <c r="D895" s="11"/>
+      <c r="E895" s="11"/>
+    </row>
+    <row r="896" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C896" s="11"/>
+      <c r="D896" s="11"/>
+      <c r="E896" s="11"/>
+    </row>
+    <row r="897" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C897" s="11"/>
+      <c r="D897" s="11"/>
+      <c r="E897" s="11"/>
+    </row>
+    <row r="898" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C898" s="11"/>
+      <c r="D898" s="11"/>
+      <c r="E898" s="11"/>
+    </row>
+    <row r="899" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C899" s="11"/>
+      <c r="D899" s="11"/>
+      <c r="E899" s="11"/>
+    </row>
+    <row r="900" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C900" s="11"/>
+      <c r="D900" s="11"/>
+      <c r="E900" s="11"/>
+    </row>
+    <row r="901" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C901" s="11"/>
+      <c r="D901" s="11"/>
+      <c r="E901" s="11"/>
+    </row>
+    <row r="902" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C902" s="11"/>
+      <c r="D902" s="11"/>
+      <c r="E902" s="11"/>
+    </row>
+    <row r="903" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C903" s="11"/>
+      <c r="D903" s="11"/>
+      <c r="E903" s="11"/>
+    </row>
+    <row r="904" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C904" s="11"/>
+      <c r="D904" s="11"/>
+      <c r="E904" s="11"/>
+    </row>
+    <row r="905" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C905" s="11"/>
+      <c r="D905" s="11"/>
+      <c r="E905" s="11"/>
+    </row>
+    <row r="906" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C906" s="11"/>
+      <c r="D906" s="11"/>
+      <c r="E906" s="11"/>
+    </row>
+    <row r="907" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C907" s="11"/>
+      <c r="D907" s="11"/>
+      <c r="E907" s="11"/>
+    </row>
+    <row r="908" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C908" s="11"/>
+      <c r="D908" s="11"/>
+      <c r="E908" s="11"/>
+    </row>
+    <row r="909" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C909" s="11"/>
+      <c r="D909" s="11"/>
+      <c r="E909" s="11"/>
+    </row>
+    <row r="910" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C910" s="11"/>
+      <c r="D910" s="11"/>
+      <c r="E910" s="11"/>
+    </row>
+    <row r="911" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C911" s="11"/>
+      <c r="D911" s="11"/>
+      <c r="E911" s="11"/>
+    </row>
+    <row r="912" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C912" s="11"/>
+      <c r="D912" s="11"/>
+      <c r="E912" s="11"/>
+    </row>
+    <row r="913" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C913" s="11"/>
+      <c r="D913" s="11"/>
+      <c r="E913" s="11"/>
+    </row>
+    <row r="914" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C914" s="11"/>
+      <c r="D914" s="11"/>
+      <c r="E914" s="11"/>
+    </row>
+    <row r="915" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C915" s="11"/>
+      <c r="D915" s="11"/>
+      <c r="E915" s="11"/>
+    </row>
+    <row r="916" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C916" s="11"/>
+      <c r="D916" s="11"/>
+      <c r="E916" s="11"/>
+    </row>
+    <row r="917" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C917" s="11"/>
+      <c r="D917" s="11"/>
+      <c r="E917" s="11"/>
+    </row>
+    <row r="918" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C918" s="11"/>
+      <c r="D918" s="11"/>
+      <c r="E918" s="11"/>
+    </row>
+    <row r="919" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C919" s="11"/>
+      <c r="D919" s="11"/>
+      <c r="E919" s="11"/>
+    </row>
+    <row r="920" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C920" s="11"/>
+      <c r="D920" s="11"/>
+      <c r="E920" s="11"/>
+    </row>
+    <row r="921" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C921" s="11"/>
+      <c r="D921" s="11"/>
+      <c r="E921" s="11"/>
+    </row>
+    <row r="922" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C922" s="11"/>
+      <c r="D922" s="11"/>
+      <c r="E922" s="11"/>
+    </row>
+    <row r="923" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C923" s="11"/>
+      <c r="D923" s="11"/>
+      <c r="E923" s="11"/>
+    </row>
+    <row r="924" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C924" s="11"/>
+      <c r="D924" s="11"/>
+      <c r="E924" s="11"/>
+    </row>
+    <row r="925" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C925" s="11"/>
+      <c r="D925" s="11"/>
+      <c r="E925" s="11"/>
+    </row>
+    <row r="926" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C926" s="11"/>
+      <c r="D926" s="11"/>
+      <c r="E926" s="11"/>
+    </row>
+    <row r="927" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C927" s="11"/>
+      <c r="D927" s="11"/>
+      <c r="E927" s="11"/>
+    </row>
+    <row r="928" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C928" s="11"/>
+      <c r="D928" s="11"/>
+      <c r="E928" s="11"/>
+    </row>
+    <row r="929" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C929" s="11"/>
+      <c r="D929" s="11"/>
+      <c r="E929" s="11"/>
+    </row>
+    <row r="930" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C930" s="11"/>
+      <c r="D930" s="11"/>
+      <c r="E930" s="11"/>
+    </row>
+    <row r="931" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C931" s="11"/>
+      <c r="D931" s="11"/>
+      <c r="E931" s="11"/>
+    </row>
+    <row r="932" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C932" s="11"/>
+      <c r="D932" s="11"/>
+      <c r="E932" s="11"/>
+    </row>
+    <row r="933" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C933" s="11"/>
+      <c r="D933" s="11"/>
+      <c r="E933" s="11"/>
+    </row>
+    <row r="934" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C934" s="11"/>
+      <c r="D934" s="11"/>
+      <c r="E934" s="11"/>
+    </row>
+    <row r="935" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C935" s="11"/>
+      <c r="D935" s="11"/>
+      <c r="E935" s="11"/>
+    </row>
+    <row r="936" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C936" s="11"/>
+      <c r="D936" s="11"/>
+      <c r="E936" s="11"/>
+    </row>
+    <row r="937" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C937" s="11"/>
+      <c r="D937" s="11"/>
+      <c r="E937" s="11"/>
+    </row>
+    <row r="938" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C938" s="11"/>
+      <c r="D938" s="11"/>
+      <c r="E938" s="11"/>
+    </row>
+    <row r="939" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C939" s="11"/>
+      <c r="D939" s="11"/>
+      <c r="E939" s="11"/>
+    </row>
+    <row r="940" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C940" s="11"/>
+      <c r="D940" s="11"/>
+      <c r="E940" s="11"/>
+    </row>
+    <row r="941" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C941" s="11"/>
+      <c r="D941" s="11"/>
+      <c r="E941" s="11"/>
+    </row>
+    <row r="942" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C942" s="11"/>
+      <c r="D942" s="11"/>
+      <c r="E942" s="11"/>
+    </row>
+    <row r="943" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C943" s="11"/>
+      <c r="D943" s="11"/>
+      <c r="E943" s="11"/>
+    </row>
+    <row r="944" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C944" s="11"/>
+      <c r="D944" s="11"/>
+      <c r="E944" s="11"/>
+    </row>
+    <row r="945" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C945" s="11"/>
+      <c r="D945" s="11"/>
+      <c r="E945" s="11"/>
+    </row>
+    <row r="946" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C946" s="11"/>
+      <c r="D946" s="11"/>
+      <c r="E946" s="11"/>
+    </row>
+    <row r="947" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C947" s="11"/>
+      <c r="D947" s="11"/>
+      <c r="E947" s="11"/>
+    </row>
+    <row r="948" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C948" s="11"/>
+      <c r="D948" s="11"/>
+      <c r="E948" s="11"/>
+    </row>
+    <row r="949" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C949" s="11"/>
+      <c r="D949" s="11"/>
+      <c r="E949" s="11"/>
+    </row>
+    <row r="950" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C950" s="11"/>
+      <c r="D950" s="11"/>
+      <c r="E950" s="11"/>
+    </row>
+    <row r="951" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C951" s="11"/>
+      <c r="D951" s="11"/>
+      <c r="E951" s="11"/>
+    </row>
+    <row r="952" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C952" s="11"/>
+      <c r="D952" s="11"/>
+      <c r="E952" s="11"/>
+    </row>
+    <row r="953" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C953" s="11"/>
+      <c r="D953" s="11"/>
+      <c r="E953" s="11"/>
+    </row>
+    <row r="954" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C954" s="11"/>
+      <c r="D954" s="11"/>
+      <c r="E954" s="11"/>
+    </row>
+    <row r="955" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C955" s="11"/>
+      <c r="D955" s="11"/>
+      <c r="E955" s="11"/>
+    </row>
+    <row r="956" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C956" s="11"/>
+      <c r="D956" s="11"/>
+      <c r="E956" s="11"/>
+    </row>
+    <row r="957" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C957" s="11"/>
+      <c r="D957" s="11"/>
+      <c r="E957" s="11"/>
+    </row>
+    <row r="958" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C958" s="11"/>
+      <c r="D958" s="11"/>
+      <c r="E958" s="11"/>
+    </row>
+    <row r="959" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C959" s="11"/>
+      <c r="D959" s="11"/>
+      <c r="E959" s="11"/>
+    </row>
+    <row r="960" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C960" s="11"/>
+      <c r="D960" s="11"/>
+      <c r="E960" s="11"/>
+    </row>
+    <row r="961" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C961" s="11"/>
+      <c r="D961" s="11"/>
+      <c r="E961" s="11"/>
+    </row>
+    <row r="962" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C962" s="11"/>
+      <c r="D962" s="11"/>
+      <c r="E962" s="11"/>
+    </row>
+    <row r="963" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C963" s="11"/>
+      <c r="D963" s="11"/>
+      <c r="E963" s="11"/>
+    </row>
+    <row r="964" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C964" s="11"/>
+      <c r="D964" s="11"/>
+      <c r="E964" s="11"/>
+    </row>
+    <row r="965" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C965" s="11"/>
+      <c r="D965" s="11"/>
+      <c r="E965" s="11"/>
+    </row>
+    <row r="966" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C966" s="11"/>
+      <c r="D966" s="11"/>
+      <c r="E966" s="11"/>
+    </row>
+    <row r="967" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C967" s="11"/>
+      <c r="D967" s="11"/>
+      <c r="E967" s="11"/>
+    </row>
+    <row r="968" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C968" s="11"/>
+      <c r="D968" s="11"/>
+      <c r="E968" s="11"/>
+    </row>
+    <row r="969" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C969" s="11"/>
+      <c r="D969" s="11"/>
+      <c r="E969" s="11"/>
+    </row>
+    <row r="970" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C970" s="11"/>
+      <c r="D970" s="11"/>
+      <c r="E970" s="11"/>
+    </row>
+    <row r="971" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C971" s="11"/>
+      <c r="D971" s="11"/>
+      <c r="E971" s="11"/>
+    </row>
+    <row r="972" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C972" s="11"/>
+      <c r="D972" s="11"/>
+      <c r="E972" s="11"/>
+    </row>
+    <row r="973" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C973" s="11"/>
+      <c r="D973" s="11"/>
+      <c r="E973" s="11"/>
+    </row>
+    <row r="974" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C974" s="11"/>
+      <c r="D974" s="11"/>
+      <c r="E974" s="11"/>
+    </row>
+    <row r="975" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C975" s="11"/>
+      <c r="D975" s="11"/>
+      <c r="E975" s="11"/>
+    </row>
+    <row r="976" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C976" s="11"/>
+      <c r="D976" s="11"/>
+      <c r="E976" s="11"/>
+    </row>
+    <row r="977" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C977" s="11"/>
+      <c r="D977" s="11"/>
+      <c r="E977" s="11"/>
+    </row>
+    <row r="978" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C978" s="11"/>
+      <c r="D978" s="11"/>
+      <c r="E978" s="11"/>
+    </row>
+    <row r="979" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C979" s="11"/>
+      <c r="D979" s="11"/>
+      <c r="E979" s="11"/>
+    </row>
+    <row r="980" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C980" s="11"/>
+      <c r="D980" s="11"/>
+      <c r="E980" s="11"/>
+    </row>
+    <row r="981" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C981" s="11"/>
+      <c r="D981" s="11"/>
+      <c r="E981" s="11"/>
+    </row>
+    <row r="982" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C982" s="11"/>
+      <c r="D982" s="11"/>
+      <c r="E982" s="11"/>
+    </row>
+    <row r="983" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C983" s="11"/>
+      <c r="D983" s="11"/>
+      <c r="E983" s="11"/>
+    </row>
+    <row r="984" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C984" s="11"/>
+      <c r="D984" s="11"/>
+      <c r="E984" s="11"/>
+    </row>
+    <row r="985" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C985" s="11"/>
+      <c r="D985" s="11"/>
+      <c r="E985" s="11"/>
+    </row>
+    <row r="986" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C986" s="11"/>
+      <c r="D986" s="11"/>
+      <c r="E986" s="11"/>
+    </row>
+    <row r="987" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C987" s="11"/>
+      <c r="D987" s="11"/>
+      <c r="E987" s="11"/>
+    </row>
+    <row r="988" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C988" s="11"/>
+      <c r="D988" s="11"/>
+      <c r="E988" s="11"/>
+    </row>
+    <row r="989" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C989" s="11"/>
+      <c r="D989" s="11"/>
+      <c r="E989" s="11"/>
+    </row>
+    <row r="990" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C990" s="11"/>
+      <c r="D990" s="11"/>
+      <c r="E990" s="11"/>
+    </row>
+    <row r="991" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C991" s="11"/>
+      <c r="D991" s="11"/>
+      <c r="E991" s="11"/>
+    </row>
+    <row r="992" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C992" s="11"/>
+      <c r="D992" s="11"/>
+      <c r="E992" s="11"/>
+    </row>
+    <row r="993" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C993" s="11"/>
+      <c r="D993" s="11"/>
+      <c r="E993" s="11"/>
+    </row>
+    <row r="994" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C994" s="11"/>
+      <c r="D994" s="11"/>
+      <c r="E994" s="11"/>
+    </row>
+    <row r="995" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C995" s="11"/>
+      <c r="D995" s="11"/>
+      <c r="E995" s="11"/>
+    </row>
+    <row r="996" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C996" s="11"/>
+      <c r="D996" s="11"/>
+      <c r="E996" s="11"/>
+    </row>
+    <row r="997" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C997" s="11"/>
+      <c r="D997" s="11"/>
+      <c r="E997" s="11"/>
+    </row>
+    <row r="998" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C998" s="11"/>
+      <c r="D998" s="11"/>
+      <c r="E998" s="11"/>
+    </row>
+    <row r="999" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C999" s="11"/>
+      <c r="D999" s="11"/>
+      <c r="E999" s="11"/>
+    </row>
+    <row r="1000" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1000" s="11"/>
+      <c r="D1000" s="11"/>
+      <c r="E1000" s="11"/>
+    </row>
+    <row r="1001" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1001" s="11"/>
+      <c r="D1001" s="11"/>
+      <c r="E1001" s="11"/>
+    </row>
+    <row r="1002" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1002" s="11"/>
+      <c r="D1002" s="11"/>
+      <c r="E1002" s="11"/>
+    </row>
+    <row r="1003" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1003" s="11"/>
+      <c r="D1003" s="11"/>
+      <c r="E1003" s="11"/>
+    </row>
+    <row r="1004" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1004" s="11"/>
+      <c r="D1004" s="11"/>
+      <c r="E1004" s="11"/>
+    </row>
+    <row r="1005" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1005" s="11"/>
+      <c r="D1005" s="11"/>
+      <c r="E1005" s="11"/>
+    </row>
+    <row r="1006" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1006" s="11"/>
+      <c r="D1006" s="11"/>
+      <c r="E1006" s="11"/>
+    </row>
+    <row r="1007" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1007" s="11"/>
+      <c r="D1007" s="11"/>
+      <c r="E1007" s="11"/>
+    </row>
+    <row r="1008" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1008" s="11"/>
+      <c r="D1008" s="11"/>
+      <c r="E1008" s="11"/>
+    </row>
+    <row r="1009" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1009" s="11"/>
+      <c r="D1009" s="11"/>
+      <c r="E1009" s="11"/>
+    </row>
+    <row r="1010" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1010" s="11"/>
+      <c r="D1010" s="11"/>
+      <c r="E1010" s="11"/>
+    </row>
+    <row r="1011" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1011" s="11"/>
+      <c r="D1011" s="11"/>
+      <c r="E1011" s="11"/>
+    </row>
+    <row r="1012" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1012" s="11"/>
+      <c r="D1012" s="11"/>
+      <c r="E1012" s="11"/>
+    </row>
+    <row r="1013" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1013" s="11"/>
+      <c r="D1013" s="11"/>
+      <c r="E1013" s="11"/>
+    </row>
+    <row r="1014" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1014" s="11"/>
+      <c r="D1014" s="11"/>
+      <c r="E1014" s="11"/>
+    </row>
+    <row r="1015" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1015" s="11"/>
+      <c r="D1015" s="11"/>
+      <c r="E1015" s="11"/>
+    </row>
+    <row r="1016" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1016" s="11"/>
+      <c r="D1016" s="11"/>
+      <c r="E1016" s="11"/>
+    </row>
+    <row r="1017" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1017" s="11"/>
+      <c r="D1017" s="11"/>
+      <c r="E1017" s="11"/>
+    </row>
+    <row r="1018" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1018" s="11"/>
+      <c r="D1018" s="11"/>
+      <c r="E1018" s="11"/>
+    </row>
+    <row r="1019" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1019" s="11"/>
+      <c r="D1019" s="11"/>
+      <c r="E1019" s="11"/>
+    </row>
+    <row r="1020" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1020" s="11"/>
+      <c r="D1020" s="11"/>
+      <c r="E1020" s="11"/>
+    </row>
+    <row r="1021" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1021" s="11"/>
+      <c r="D1021" s="11"/>
+      <c r="E1021" s="11"/>
+    </row>
+    <row r="1022" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1022" s="11"/>
+      <c r="D1022" s="11"/>
+      <c r="E1022" s="11"/>
+    </row>
+    <row r="1023" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1023" s="11"/>
+      <c r="D1023" s="11"/>
+      <c r="E1023" s="11"/>
+    </row>
+    <row r="1024" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1024" s="11"/>
+      <c r="D1024" s="11"/>
+      <c r="E1024" s="11"/>
+    </row>
+    <row r="1025" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1025" s="11"/>
+      <c r="D1025" s="11"/>
+      <c r="E1025" s="11"/>
+    </row>
+    <row r="1026" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1026" s="11"/>
+      <c r="D1026" s="11"/>
+      <c r="E1026" s="11"/>
+    </row>
+    <row r="1027" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1027" s="11"/>
+      <c r="D1027" s="11"/>
+      <c r="E1027" s="11"/>
+    </row>
+    <row r="1028" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1028" s="11"/>
+      <c r="D1028" s="11"/>
+      <c r="E1028" s="11"/>
+    </row>
+    <row r="1029" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1029" s="11"/>
+      <c r="D1029" s="11"/>
+      <c r="E1029" s="11"/>
+    </row>
+    <row r="1030" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1030" s="11"/>
+      <c r="D1030" s="11"/>
+      <c r="E1030" s="11"/>
+    </row>
+    <row r="1031" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1031" s="11"/>
+      <c r="D1031" s="11"/>
+      <c r="E1031" s="11"/>
+    </row>
+    <row r="1032" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1032" s="11"/>
+      <c r="D1032" s="11"/>
+      <c r="E1032" s="11"/>
+    </row>
+    <row r="1033" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1033" s="11"/>
+      <c r="D1033" s="11"/>
+      <c r="E1033" s="11"/>
+    </row>
+    <row r="1034" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1034" s="11"/>
+      <c r="D1034" s="11"/>
+      <c r="E1034" s="11"/>
+    </row>
+    <row r="1035" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1035" s="11"/>
+      <c r="D1035" s="11"/>
+      <c r="E1035" s="11"/>
+    </row>
+    <row r="1036" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1036" s="11"/>
+      <c r="D1036" s="11"/>
+      <c r="E1036" s="11"/>
+    </row>
+    <row r="1037" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1037" s="11"/>
+      <c r="D1037" s="11"/>
+      <c r="E1037" s="11"/>
+    </row>
+    <row r="1038" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1038" s="11"/>
+      <c r="D1038" s="11"/>
+      <c r="E1038" s="11"/>
+    </row>
+    <row r="1039" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1039" s="11"/>
+      <c r="D1039" s="11"/>
+      <c r="E1039" s="11"/>
+    </row>
+    <row r="1040" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1040" s="11"/>
+      <c r="D1040" s="11"/>
+      <c r="E1040" s="11"/>
+    </row>
+    <row r="1041" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1041" s="11"/>
+      <c r="D1041" s="11"/>
+      <c r="E1041" s="11"/>
+    </row>
+    <row r="1042" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1042" s="11"/>
+      <c r="D1042" s="11"/>
+      <c r="E1042" s="11"/>
+    </row>
+    <row r="1043" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1043" s="11"/>
+      <c r="D1043" s="11"/>
+      <c r="E1043" s="11"/>
+    </row>
+    <row r="1044" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1044" s="11"/>
+      <c r="D1044" s="11"/>
+      <c r="E1044" s="11"/>
+    </row>
+    <row r="1045" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1045" s="11"/>
+      <c r="D1045" s="11"/>
+      <c r="E1045" s="11"/>
+    </row>
+    <row r="1046" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1046" s="11"/>
+      <c r="D1046" s="11"/>
+      <c r="E1046" s="11"/>
+    </row>
+    <row r="1047" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1047" s="11"/>
+      <c r="D1047" s="11"/>
+      <c r="E1047" s="11"/>
+    </row>
+    <row r="1048" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1048" s="11"/>
+      <c r="D1048" s="11"/>
+      <c r="E1048" s="11"/>
+    </row>
+    <row r="1049" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1049" s="11"/>
+      <c r="D1049" s="11"/>
+      <c r="E1049" s="11"/>
+    </row>
+    <row r="1050" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1050" s="11"/>
+      <c r="D1050" s="11"/>
+      <c r="E1050" s="11"/>
+    </row>
+    <row r="1051" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1051" s="11"/>
+      <c r="D1051" s="11"/>
+      <c r="E1051" s="11"/>
+    </row>
+    <row r="1052" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1052" s="11"/>
+      <c r="D1052" s="11"/>
+      <c r="E1052" s="11"/>
+    </row>
+    <row r="1053" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1053" s="11"/>
+      <c r="D1053" s="11"/>
+      <c r="E1053" s="11"/>
+    </row>
+    <row r="1054" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1054" s="11"/>
+      <c r="D1054" s="11"/>
+      <c r="E1054" s="11"/>
+    </row>
+    <row r="1055" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1055" s="11"/>
+      <c r="D1055" s="11"/>
+      <c r="E1055" s="11"/>
+    </row>
+    <row r="1056" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1056" s="11"/>
+      <c r="D1056" s="11"/>
+      <c r="E1056" s="11"/>
+    </row>
+    <row r="1057" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1057" s="11"/>
+      <c r="D1057" s="11"/>
+      <c r="E1057" s="11"/>
+    </row>
+    <row r="1058" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1058" s="11"/>
+      <c r="D1058" s="11"/>
+      <c r="E1058" s="11"/>
+    </row>
+    <row r="1059" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1059" s="11"/>
+      <c r="D1059" s="11"/>
+      <c r="E1059" s="11"/>
+    </row>
+    <row r="1060" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1060" s="11"/>
+      <c r="D1060" s="11"/>
+      <c r="E1060" s="11"/>
+    </row>
+    <row r="1061" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1061" s="11"/>
+      <c r="D1061" s="11"/>
+      <c r="E1061" s="11"/>
+    </row>
+    <row r="1062" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1062" s="11"/>
+      <c r="D1062" s="11"/>
+      <c r="E1062" s="11"/>
+    </row>
+    <row r="1063" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1063" s="11"/>
+      <c r="D1063" s="11"/>
+      <c r="E1063" s="11"/>
+    </row>
+    <row r="1064" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1064" s="11"/>
+      <c r="D1064" s="11"/>
+      <c r="E1064" s="11"/>
+    </row>
+    <row r="1065" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1065" s="11"/>
+      <c r="D1065" s="11"/>
+      <c r="E1065" s="11"/>
+    </row>
+    <row r="1066" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1066" s="11"/>
+      <c r="D1066" s="11"/>
+      <c r="E1066" s="11"/>
+    </row>
+    <row r="1067" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1067" s="11"/>
+      <c r="D1067" s="11"/>
+      <c r="E1067" s="11"/>
+    </row>
+    <row r="1068" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1068" s="11"/>
+      <c r="D1068" s="11"/>
+      <c r="E1068" s="11"/>
+    </row>
+    <row r="1069" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1069" s="11"/>
+      <c r="D1069" s="11"/>
+      <c r="E1069" s="11"/>
+    </row>
+    <row r="1070" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1070" s="11"/>
+      <c r="D1070" s="11"/>
+      <c r="E1070" s="11"/>
+    </row>
+    <row r="1071" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1071" s="11"/>
+      <c r="D1071" s="11"/>
+      <c r="E1071" s="11"/>
+    </row>
+    <row r="1072" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1072" s="11"/>
+      <c r="D1072" s="11"/>
+      <c r="E1072" s="11"/>
+    </row>
+    <row r="1073" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1073" s="11"/>
+      <c r="D1073" s="11"/>
+      <c r="E1073" s="11"/>
+    </row>
+    <row r="1074" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1074" s="11"/>
+      <c r="D1074" s="11"/>
+      <c r="E1074" s="11"/>
+    </row>
+    <row r="1075" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1075" s="11"/>
+      <c r="D1075" s="11"/>
+      <c r="E1075" s="11"/>
+    </row>
+    <row r="1076" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1076" s="11"/>
+      <c r="D1076" s="11"/>
+      <c r="E1076" s="11"/>
+    </row>
+    <row r="1077" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1077" s="11"/>
+      <c r="D1077" s="11"/>
+      <c r="E1077" s="11"/>
+    </row>
+    <row r="1078" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1078" s="11"/>
+      <c r="D1078" s="11"/>
+      <c r="E1078" s="11"/>
+    </row>
+    <row r="1079" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1079" s="11"/>
+      <c r="D1079" s="11"/>
+      <c r="E1079" s="11"/>
+    </row>
+    <row r="1080" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1080" s="11"/>
+      <c r="D1080" s="11"/>
+      <c r="E1080" s="11"/>
+    </row>
+    <row r="1081" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1081" s="11"/>
+      <c r="D1081" s="11"/>
+      <c r="E1081" s="11"/>
+    </row>
+    <row r="1082" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1082" s="11"/>
+      <c r="D1082" s="11"/>
+      <c r="E1082" s="11"/>
+    </row>
+    <row r="1083" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1083" s="11"/>
+      <c r="D1083" s="11"/>
+      <c r="E1083" s="11"/>
+    </row>
+    <row r="1084" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1084" s="11"/>
+      <c r="D1084" s="11"/>
+      <c r="E1084" s="11"/>
+    </row>
+    <row r="1085" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1085" s="11"/>
+      <c r="D1085" s="11"/>
+      <c r="E1085" s="11"/>
+    </row>
+    <row r="1086" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1086" s="11"/>
+      <c r="D1086" s="11"/>
+      <c r="E1086" s="11"/>
+    </row>
+    <row r="1087" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1087" s="11"/>
+      <c r="D1087" s="11"/>
+      <c r="E1087" s="11"/>
+    </row>
+    <row r="1088" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1088" s="11"/>
+      <c r="D1088" s="11"/>
+      <c r="E1088" s="11"/>
+    </row>
+    <row r="1089" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1089" s="11"/>
+      <c r="D1089" s="11"/>
+      <c r="E1089" s="11"/>
+    </row>
+    <row r="1090" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1090" s="11"/>
+      <c r="D1090" s="11"/>
+      <c r="E1090" s="11"/>
+    </row>
+    <row r="1091" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1091" s="11"/>
+      <c r="D1091" s="11"/>
+      <c r="E1091" s="11"/>
+    </row>
+    <row r="1092" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1092" s="11"/>
+      <c r="D1092" s="11"/>
+      <c r="E1092" s="11"/>
+    </row>
+    <row r="1093" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1093" s="11"/>
+      <c r="D1093" s="11"/>
+      <c r="E1093" s="11"/>
+    </row>
+    <row r="1094" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1094" s="11"/>
+      <c r="D1094" s="11"/>
+      <c r="E1094" s="11"/>
+    </row>
+    <row r="1095" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1095" s="11"/>
+      <c r="D1095" s="11"/>
+      <c r="E1095" s="11"/>
+    </row>
+    <row r="1096" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1096" s="11"/>
+      <c r="D1096" s="11"/>
+      <c r="E1096" s="11"/>
+    </row>
+    <row r="1097" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1097" s="11"/>
+      <c r="D1097" s="11"/>
+      <c r="E1097" s="11"/>
+    </row>
+    <row r="1098" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1098" s="11"/>
+      <c r="D1098" s="11"/>
+      <c r="E1098" s="11"/>
+    </row>
+    <row r="1099" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1099" s="11"/>
+      <c r="D1099" s="11"/>
+      <c r="E1099" s="11"/>
+    </row>
+    <row r="1100" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1100" s="11"/>
+      <c r="D1100" s="11"/>
+      <c r="E1100" s="11"/>
+    </row>
+    <row r="1101" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1101" s="11"/>
+      <c r="D1101" s="11"/>
+      <c r="E1101" s="11"/>
+    </row>
+    <row r="1102" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1102" s="11"/>
+      <c r="D1102" s="11"/>
+      <c r="E1102" s="11"/>
+    </row>
+    <row r="1103" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1103" s="11"/>
+      <c r="D1103" s="11"/>
+      <c r="E1103" s="11"/>
+    </row>
+    <row r="1104" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1104" s="11"/>
+      <c r="D1104" s="11"/>
+      <c r="E1104" s="11"/>
+    </row>
+    <row r="1105" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1105" s="11"/>
+      <c r="D1105" s="11"/>
+      <c r="E1105" s="11"/>
+    </row>
+    <row r="1106" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1106" s="11"/>
+      <c r="D1106" s="11"/>
+      <c r="E1106" s="11"/>
+    </row>
+    <row r="1107" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1107" s="11"/>
+      <c r="D1107" s="11"/>
+      <c r="E1107" s="11"/>
+    </row>
+    <row r="1108" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1108" s="11"/>
+      <c r="D1108" s="11"/>
+      <c r="E1108" s="11"/>
+    </row>
+    <row r="1109" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1109" s="11"/>
+      <c r="D1109" s="11"/>
+      <c r="E1109" s="11"/>
+    </row>
+    <row r="1110" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1110" s="11"/>
+      <c r="D1110" s="11"/>
+      <c r="E1110" s="11"/>
+    </row>
+    <row r="1111" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1111" s="11"/>
+      <c r="D1111" s="11"/>
+      <c r="E1111" s="11"/>
+    </row>
+    <row r="1112" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1112" s="11"/>
+      <c r="D1112" s="11"/>
+      <c r="E1112" s="11"/>
+    </row>
+    <row r="1113" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1113" s="11"/>
+      <c r="D1113" s="11"/>
+      <c r="E1113" s="11"/>
+    </row>
+    <row r="1114" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1114" s="11"/>
+      <c r="D1114" s="11"/>
+      <c r="E1114" s="11"/>
+    </row>
+    <row r="1115" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1115" s="11"/>
+      <c r="D1115" s="11"/>
+      <c r="E1115" s="11"/>
+    </row>
+    <row r="1116" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1116" s="11"/>
+      <c r="D1116" s="11"/>
+      <c r="E1116" s="11"/>
+    </row>
+    <row r="1117" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1117" s="11"/>
+      <c r="D1117" s="11"/>
+      <c r="E1117" s="11"/>
+    </row>
+    <row r="1118" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1118" s="11"/>
+      <c r="D1118" s="11"/>
+      <c r="E1118" s="11"/>
+    </row>
+    <row r="1119" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1119" s="11"/>
+      <c r="D1119" s="11"/>
+      <c r="E1119" s="11"/>
+    </row>
+    <row r="1120" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1120" s="11"/>
+      <c r="D1120" s="11"/>
+      <c r="E1120" s="11"/>
+    </row>
+    <row r="1121" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1121" s="11"/>
+      <c r="D1121" s="11"/>
+      <c r="E1121" s="11"/>
+    </row>
+    <row r="1122" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1122" s="11"/>
+      <c r="D1122" s="11"/>
+      <c r="E1122" s="11"/>
+    </row>
+    <row r="1123" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1123" s="11"/>
+      <c r="D1123" s="11"/>
+      <c r="E1123" s="11"/>
+    </row>
+    <row r="1124" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1124" s="11"/>
+      <c r="D1124" s="11"/>
+      <c r="E1124" s="11"/>
+    </row>
+    <row r="1125" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1125" s="11"/>
+      <c r="D1125" s="11"/>
+      <c r="E1125" s="11"/>
+    </row>
+    <row r="1126" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1126" s="11"/>
+      <c r="D1126" s="11"/>
+      <c r="E1126" s="11"/>
+    </row>
+    <row r="1127" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1127" s="11"/>
+      <c r="D1127" s="11"/>
+      <c r="E1127" s="11"/>
+    </row>
+    <row r="1128" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1128" s="11"/>
+      <c r="D1128" s="11"/>
+      <c r="E1128" s="11"/>
+    </row>
+    <row r="1129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1129" s="11"/>
+      <c r="D1129" s="11"/>
+      <c r="E1129" s="11"/>
+    </row>
+    <row r="1130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1130" s="11"/>
+      <c r="D1130" s="11"/>
+      <c r="E1130" s="11"/>
+    </row>
+    <row r="1131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1131" s="11"/>
+      <c r="D1131" s="11"/>
+      <c r="E1131" s="11"/>
+    </row>
+    <row r="1132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1132" s="11"/>
+      <c r="D1132" s="11"/>
+      <c r="E1132" s="11"/>
+    </row>
+    <row r="1133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1133" s="11"/>
+      <c r="D1133" s="11"/>
+      <c r="E1133" s="11"/>
+    </row>
+    <row r="1134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1134" s="11"/>
+      <c r="D1134" s="11"/>
+      <c r="E1134" s="11"/>
+    </row>
+    <row r="1135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1135" s="11"/>
+      <c r="D1135" s="11"/>
+      <c r="E1135" s="11"/>
+    </row>
+    <row r="1136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1136" s="11"/>
+      <c r="D1136" s="11"/>
+      <c r="E1136" s="11"/>
+    </row>
+    <row r="1137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1137" s="11"/>
+      <c r="D1137" s="11"/>
+      <c r="E1137" s="11"/>
+    </row>
+    <row r="1138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1138" s="11"/>
+      <c r="D1138" s="11"/>
+      <c r="E1138" s="11"/>
+    </row>
+    <row r="1139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1139" s="11"/>
+      <c r="D1139" s="11"/>
+      <c r="E1139" s="11"/>
+    </row>
+    <row r="1140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1140" s="11"/>
+      <c r="D1140" s="11"/>
+      <c r="E1140" s="11"/>
+    </row>
+    <row r="1141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1141" s="11"/>
+      <c r="D1141" s="11"/>
+      <c r="E1141" s="11"/>
+    </row>
+    <row r="1142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1142" s="11"/>
+      <c r="D1142" s="11"/>
+      <c r="E1142" s="11"/>
+    </row>
+    <row r="1143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1143" s="11"/>
+      <c r="D1143" s="11"/>
+      <c r="E1143" s="11"/>
+    </row>
+    <row r="1144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1144" s="11"/>
+      <c r="D1144" s="11"/>
+      <c r="E1144" s="11"/>
+    </row>
+    <row r="1145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1145" s="11"/>
+      <c r="D1145" s="11"/>
+      <c r="E1145" s="11"/>
+    </row>
+    <row r="1146" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1146" s="11"/>
+      <c r="D1146" s="11"/>
+      <c r="E1146" s="11"/>
+    </row>
+    <row r="1147" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1147" s="11"/>
+      <c r="D1147" s="11"/>
+      <c r="E1147" s="11"/>
+    </row>
+    <row r="1148" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1148" s="11"/>
+      <c r="D1148" s="11"/>
+      <c r="E1148" s="11"/>
+    </row>
+    <row r="1149" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1149" s="11"/>
+      <c r="D1149" s="11"/>
+      <c r="E1149" s="11"/>
+    </row>
+    <row r="1150" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1150" s="11"/>
+      <c r="D1150" s="11"/>
+      <c r="E1150" s="11"/>
+    </row>
+    <row r="1151" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1151" s="11"/>
+      <c r="D1151" s="11"/>
+      <c r="E1151" s="11"/>
+    </row>
+    <row r="1152" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1152" s="11"/>
+      <c r="D1152" s="11"/>
+      <c r="E1152" s="11"/>
+    </row>
+    <row r="1153" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1153" s="11"/>
+      <c r="D1153" s="11"/>
+      <c r="E1153" s="11"/>
+    </row>
+    <row r="1154" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1154" s="11"/>
+      <c r="D1154" s="11"/>
+      <c r="E1154" s="11"/>
+    </row>
+    <row r="1155" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1155" s="11"/>
+      <c r="D1155" s="11"/>
+      <c r="E1155" s="11"/>
+    </row>
+    <row r="1156" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1156" s="11"/>
+      <c r="D1156" s="11"/>
+      <c r="E1156" s="11"/>
+    </row>
+    <row r="1157" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1157" s="11"/>
+      <c r="D1157" s="11"/>
+      <c r="E1157" s="11"/>
+    </row>
+    <row r="1158" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1158" s="11"/>
+      <c r="D1158" s="11"/>
+      <c r="E1158" s="11"/>
+    </row>
+    <row r="1159" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1159" s="11"/>
+      <c r="D1159" s="11"/>
+      <c r="E1159" s="11"/>
+    </row>
+    <row r="1160" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1160" s="11"/>
+      <c r="D1160" s="11"/>
+      <c r="E1160" s="11"/>
+    </row>
+    <row r="1161" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1161" s="11"/>
+      <c r="D1161" s="11"/>
+      <c r="E1161" s="11"/>
+    </row>
+    <row r="1162" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1162" s="11"/>
+      <c r="D1162" s="11"/>
+      <c r="E1162" s="11"/>
+    </row>
+    <row r="1163" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1163" s="11"/>
+      <c r="D1163" s="11"/>
+      <c r="E1163" s="11"/>
+    </row>
+    <row r="1164" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1164" s="11"/>
+      <c r="D1164" s="11"/>
+      <c r="E1164" s="11"/>
+    </row>
+    <row r="1165" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1165" s="11"/>
+      <c r="D1165" s="11"/>
+      <c r="E1165" s="11"/>
+    </row>
+    <row r="1166" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1166" s="11"/>
+      <c r="D1166" s="11"/>
+      <c r="E1166" s="11"/>
+    </row>
+    <row r="1167" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1167" s="11"/>
+      <c r="D1167" s="11"/>
+      <c r="E1167" s="11"/>
+    </row>
+    <row r="1168" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1168" s="11"/>
+      <c r="D1168" s="11"/>
+      <c r="E1168" s="11"/>
+    </row>
+    <row r="1169" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1169" s="11"/>
+      <c r="D1169" s="11"/>
+      <c r="E1169" s="11"/>
+    </row>
+    <row r="1170" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1170" s="11"/>
+      <c r="D1170" s="11"/>
+      <c r="E1170" s="11"/>
+    </row>
+    <row r="1171" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1171" s="11"/>
+      <c r="D1171" s="11"/>
+      <c r="E1171" s="11"/>
+    </row>
+    <row r="1172" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1172" s="11"/>
+      <c r="D1172" s="11"/>
+      <c r="E1172" s="11"/>
+    </row>
+    <row r="1173" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1173" s="11"/>
+      <c r="D1173" s="11"/>
+      <c r="E1173" s="11"/>
+    </row>
+    <row r="1174" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1174" s="11"/>
+      <c r="D1174" s="11"/>
+      <c r="E1174" s="11"/>
+    </row>
+    <row r="1175" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1175" s="11"/>
+      <c r="D1175" s="11"/>
+      <c r="E1175" s="11"/>
+    </row>
+    <row r="1176" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1176" s="11"/>
+      <c r="D1176" s="11"/>
+      <c r="E1176" s="11"/>
+    </row>
+    <row r="1177" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1177" s="11"/>
+      <c r="D1177" s="11"/>
+      <c r="E1177" s="11"/>
+    </row>
+    <row r="1178" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1178" s="11"/>
+      <c r="D1178" s="11"/>
+      <c r="E1178" s="11"/>
+    </row>
+    <row r="1179" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1179" s="11"/>
+      <c r="D1179" s="11"/>
+      <c r="E1179" s="11"/>
+    </row>
+    <row r="1180" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1180" s="11"/>
+      <c r="D1180" s="11"/>
+      <c r="E1180" s="11"/>
+    </row>
+    <row r="1181" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1181" s="11"/>
+      <c r="D1181" s="11"/>
+      <c r="E1181" s="11"/>
+    </row>
+    <row r="1182" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1182" s="11"/>
+      <c r="D1182" s="11"/>
+      <c r="E1182" s="11"/>
+    </row>
+    <row r="1183" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1183" s="11"/>
+      <c r="D1183" s="11"/>
+      <c r="E1183" s="11"/>
+    </row>
+    <row r="1184" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1184" s="11"/>
+      <c r="D1184" s="11"/>
+      <c r="E1184" s="11"/>
+    </row>
+    <row r="1185" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1185" s="11"/>
+      <c r="D1185" s="11"/>
+      <c r="E1185" s="11"/>
+    </row>
+    <row r="1186" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1186" s="11"/>
+      <c r="D1186" s="11"/>
+      <c r="E1186" s="11"/>
+    </row>
+    <row r="1187" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1187" s="11"/>
+      <c r="D1187" s="11"/>
+      <c r="E1187" s="11"/>
+    </row>
+    <row r="1188" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1188" s="11"/>
+      <c r="D1188" s="11"/>
+      <c r="E1188" s="11"/>
+    </row>
+    <row r="1189" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1189" s="11"/>
+      <c r="D1189" s="11"/>
+      <c r="E1189" s="11"/>
+    </row>
+    <row r="1190" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1190" s="11"/>
+      <c r="D1190" s="11"/>
+      <c r="E1190" s="11"/>
+    </row>
+    <row r="1191" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1191" s="11"/>
+      <c r="D1191" s="11"/>
+      <c r="E1191" s="11"/>
+    </row>
+    <row r="1192" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1192" s="11"/>
+      <c r="D1192" s="11"/>
+      <c r="E1192" s="11"/>
+    </row>
+    <row r="1193" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1193" s="11"/>
+      <c r="D1193" s="11"/>
+      <c r="E1193" s="11"/>
+    </row>
+    <row r="1194" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1194" s="11"/>
+      <c r="D1194" s="11"/>
+      <c r="E1194" s="11"/>
+    </row>
+    <row r="1195" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1195" s="11"/>
+      <c r="D1195" s="11"/>
+      <c r="E1195" s="11"/>
+    </row>
+    <row r="1196" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1196" s="11"/>
+      <c r="D1196" s="11"/>
+      <c r="E1196" s="11"/>
+    </row>
+    <row r="1197" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1197" s="11"/>
+      <c r="D1197" s="11"/>
+      <c r="E1197" s="11"/>
+    </row>
+    <row r="1198" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1198" s="11"/>
+      <c r="D1198" s="11"/>
+      <c r="E1198" s="11"/>
+    </row>
+    <row r="1199" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1199" s="11"/>
+      <c r="D1199" s="11"/>
+      <c r="E1199" s="11"/>
+    </row>
+    <row r="1200" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1200" s="11"/>
+      <c r="D1200" s="11"/>
+      <c r="E1200" s="11"/>
+    </row>
+    <row r="1201" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1201" s="11"/>
+      <c r="D1201" s="11"/>
+      <c r="E1201" s="11"/>
+    </row>
+    <row r="1202" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1202" s="11"/>
+      <c r="D1202" s="11"/>
+      <c r="E1202" s="11"/>
+    </row>
+    <row r="1203" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1203" s="11"/>
+      <c r="D1203" s="11"/>
+      <c r="E1203" s="11"/>
+    </row>
+    <row r="1204" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1204" s="11"/>
+      <c r="D1204" s="11"/>
+      <c r="E1204" s="11"/>
+    </row>
+    <row r="1205" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1205" s="11"/>
+      <c r="D1205" s="11"/>
+      <c r="E1205" s="11"/>
+    </row>
+    <row r="1206" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1206" s="11"/>
+      <c r="D1206" s="11"/>
+      <c r="E1206" s="11"/>
+    </row>
+    <row r="1207" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1207" s="11"/>
+      <c r="D1207" s="11"/>
+      <c r="E1207" s="11"/>
+    </row>
+    <row r="1208" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1208" s="11"/>
+      <c r="D1208" s="11"/>
+      <c r="E1208" s="11"/>
+    </row>
+    <row r="1209" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1209" s="11"/>
+      <c r="D1209" s="11"/>
+      <c r="E1209" s="11"/>
+    </row>
+    <row r="1210" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1210" s="11"/>
+      <c r="D1210" s="11"/>
+      <c r="E1210" s="11"/>
+    </row>
+    <row r="1211" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1211" s="11"/>
+      <c r="D1211" s="11"/>
+      <c r="E1211" s="11"/>
+    </row>
+    <row r="1212" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1212" s="11"/>
+      <c r="D1212" s="11"/>
+      <c r="E1212" s="11"/>
+    </row>
+    <row r="1213" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1213" s="11"/>
+      <c r="D1213" s="11"/>
+      <c r="E1213" s="11"/>
+    </row>
+    <row r="1214" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1214" s="11"/>
+      <c r="D1214" s="11"/>
+      <c r="E1214" s="11"/>
+    </row>
+    <row r="1215" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1215" s="11"/>
+      <c r="D1215" s="11"/>
+      <c r="E1215" s="11"/>
+    </row>
+    <row r="1216" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1216" s="11"/>
+      <c r="D1216" s="11"/>
+      <c r="E1216" s="11"/>
+    </row>
+    <row r="1217" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1217" s="11"/>
+      <c r="D1217" s="11"/>
+      <c r="E1217" s="11"/>
+    </row>
+    <row r="1218" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1218" s="11"/>
+      <c r="D1218" s="11"/>
+      <c r="E1218" s="11"/>
+    </row>
+    <row r="1219" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1219" s="11"/>
+      <c r="D1219" s="11"/>
+      <c r="E1219" s="11"/>
+    </row>
+    <row r="1220" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1220" s="11"/>
+      <c r="D1220" s="11"/>
+      <c r="E1220" s="11"/>
+    </row>
+    <row r="1221" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1221" s="11"/>
+      <c r="D1221" s="11"/>
+      <c r="E1221" s="11"/>
+    </row>
+    <row r="1222" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1222" s="11"/>
+      <c r="D1222" s="11"/>
+      <c r="E1222" s="11"/>
+    </row>
+    <row r="1223" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1223" s="11"/>
+      <c r="D1223" s="11"/>
+      <c r="E1223" s="11"/>
+    </row>
+    <row r="1224" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1224" s="11"/>
+      <c r="D1224" s="11"/>
+      <c r="E1224" s="11"/>
+    </row>
+    <row r="1225" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1225" s="11"/>
+      <c r="D1225" s="11"/>
+      <c r="E1225" s="11"/>
+    </row>
+    <row r="1226" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1226" s="11"/>
+      <c r="D1226" s="11"/>
+      <c r="E1226" s="11"/>
+    </row>
+    <row r="1227" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1227" s="11"/>
+      <c r="D1227" s="11"/>
+      <c r="E1227" s="11"/>
+    </row>
+    <row r="1228" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1228" s="11"/>
+      <c r="D1228" s="11"/>
+      <c r="E1228" s="11"/>
+    </row>
+    <row r="1229" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1229" s="11"/>
+      <c r="D1229" s="11"/>
+      <c r="E1229" s="11"/>
+    </row>
+    <row r="1230" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1230" s="11"/>
+      <c r="D1230" s="11"/>
+      <c r="E1230" s="11"/>
+    </row>
+    <row r="1231" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1231" s="11"/>
+      <c r="D1231" s="11"/>
+      <c r="E1231" s="11"/>
+    </row>
+    <row r="1232" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1232" s="11"/>
+      <c r="D1232" s="11"/>
+      <c r="E1232" s="11"/>
+    </row>
+    <row r="1233" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1233" s="11"/>
+      <c r="D1233" s="11"/>
+      <c r="E1233" s="11"/>
+    </row>
+    <row r="1234" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1234" s="11"/>
+      <c r="D1234" s="11"/>
+      <c r="E1234" s="11"/>
+    </row>
+    <row r="1235" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1235" s="11"/>
+      <c r="D1235" s="11"/>
+      <c r="E1235" s="11"/>
+    </row>
+    <row r="1236" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1236" s="11"/>
+      <c r="D1236" s="11"/>
+      <c r="E1236" s="11"/>
+    </row>
+    <row r="1237" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1237" s="11"/>
+      <c r="D1237" s="11"/>
+      <c r="E1237" s="11"/>
+    </row>
+    <row r="1238" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1238" s="11"/>
+      <c r="D1238" s="11"/>
+      <c r="E1238" s="11"/>
+    </row>
+    <row r="1239" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1239" s="11"/>
+      <c r="D1239" s="11"/>
+      <c r="E1239" s="11"/>
+    </row>
+    <row r="1240" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1240" s="11"/>
+      <c r="D1240" s="11"/>
+      <c r="E1240" s="11"/>
+    </row>
+    <row r="1241" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1241" s="11"/>
+      <c r="D1241" s="11"/>
+      <c r="E1241" s="11"/>
+    </row>
+    <row r="1242" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1242" s="11"/>
+      <c r="D1242" s="11"/>
+      <c r="E1242" s="11"/>
+    </row>
+    <row r="1243" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1243" s="11"/>
+      <c r="D1243" s="11"/>
+      <c r="E1243" s="11"/>
+    </row>
+    <row r="1244" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1244" s="11"/>
+      <c r="D1244" s="11"/>
+      <c r="E1244" s="11"/>
+    </row>
+    <row r="1245" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1245" s="11"/>
+      <c r="D1245" s="11"/>
+      <c r="E1245" s="11"/>
+    </row>
+    <row r="1246" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1246" s="11"/>
+      <c r="D1246" s="11"/>
+      <c r="E1246" s="11"/>
+    </row>
+    <row r="1247" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1247" s="11"/>
+      <c r="D1247" s="11"/>
+      <c r="E1247" s="11"/>
+    </row>
+    <row r="1248" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1248" s="11"/>
+      <c r="D1248" s="11"/>
+      <c r="E1248" s="11"/>
+    </row>
+    <row r="1249" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1249" s="11"/>
+      <c r="D1249" s="11"/>
+      <c r="E1249" s="11"/>
+    </row>
+    <row r="1250" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1250" s="11"/>
+      <c r="D1250" s="11"/>
+      <c r="E1250" s="11"/>
+    </row>
+    <row r="1251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1251" s="11"/>
+      <c r="D1251" s="11"/>
+      <c r="E1251" s="11"/>
+    </row>
+    <row r="1252" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1252" s="11"/>
+      <c r="D1252" s="11"/>
+      <c r="E1252" s="11"/>
+    </row>
+    <row r="1253" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1253" s="11"/>
+      <c r="D1253" s="11"/>
+      <c r="E1253" s="11"/>
+    </row>
+    <row r="1254" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1254" s="11"/>
+      <c r="D1254" s="11"/>
+      <c r="E1254" s="11"/>
+    </row>
+    <row r="1255" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1255" s="11"/>
+      <c r="D1255" s="11"/>
+      <c r="E1255" s="11"/>
+    </row>
+    <row r="1256" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1256" s="11"/>
+      <c r="D1256" s="11"/>
+      <c r="E1256" s="11"/>
+    </row>
+    <row r="1257" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1257" s="11"/>
+      <c r="D1257" s="11"/>
+      <c r="E1257" s="11"/>
+    </row>
+    <row r="1258" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1258" s="11"/>
+      <c r="D1258" s="11"/>
+      <c r="E1258" s="11"/>
+    </row>
+    <row r="1259" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1259" s="11"/>
+      <c r="D1259" s="11"/>
+      <c r="E1259" s="11"/>
+    </row>
+    <row r="1260" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1260" s="11"/>
+      <c r="D1260" s="11"/>
+      <c r="E1260" s="11"/>
+    </row>
+    <row r="1261" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1261" s="11"/>
+      <c r="D1261" s="11"/>
+      <c r="E1261" s="11"/>
+    </row>
+    <row r="1262" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1262" s="11"/>
+      <c r="D1262" s="11"/>
+      <c r="E1262" s="11"/>
+    </row>
+    <row r="1263" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1263" s="11"/>
+      <c r="D1263" s="11"/>
+      <c r="E1263" s="11"/>
+    </row>
+    <row r="1264" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1264" s="11"/>
+      <c r="D1264" s="11"/>
+      <c r="E1264" s="11"/>
+    </row>
+    <row r="1265" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1265" s="11"/>
+      <c r="D1265" s="11"/>
+      <c r="E1265" s="11"/>
+    </row>
+    <row r="1266" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1266" s="11"/>
+      <c r="D1266" s="11"/>
+      <c r="E1266" s="11"/>
+    </row>
+    <row r="1267" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1267" s="11"/>
+      <c r="D1267" s="11"/>
+      <c r="E1267" s="11"/>
+    </row>
+    <row r="1268" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1268" s="11"/>
+      <c r="D1268" s="11"/>
+      <c r="E1268" s="11"/>
+    </row>
+    <row r="1269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1269" s="11"/>
+      <c r="D1269" s="11"/>
+      <c r="E1269" s="11"/>
+    </row>
+    <row r="1270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1270" s="11"/>
+      <c r="D1270" s="11"/>
+      <c r="E1270" s="11"/>
+    </row>
+    <row r="1271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1271" s="11"/>
+      <c r="D1271" s="11"/>
+      <c r="E1271" s="11"/>
+    </row>
+    <row r="1272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1272" s="11"/>
+      <c r="D1272" s="11"/>
+      <c r="E1272" s="11"/>
+    </row>
+    <row r="1273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1273" s="11"/>
+      <c r="D1273" s="11"/>
+      <c r="E1273" s="11"/>
+    </row>
+    <row r="1274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1274" s="11"/>
+      <c r="D1274" s="11"/>
+      <c r="E1274" s="11"/>
+    </row>
+    <row r="1275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1275" s="11"/>
+      <c r="D1275" s="11"/>
+      <c r="E1275" s="11"/>
+    </row>
+    <row r="1276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1276" s="11"/>
+      <c r="D1276" s="11"/>
+      <c r="E1276" s="11"/>
+    </row>
+    <row r="1277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1277" s="11"/>
+      <c r="D1277" s="11"/>
+      <c r="E1277" s="11"/>
+    </row>
+    <row r="1278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1278" s="11"/>
+      <c r="D1278" s="11"/>
+      <c r="E1278" s="11"/>
+    </row>
+    <row r="1279" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1279" s="11"/>
+      <c r="D1279" s="11"/>
+      <c r="E1279" s="11"/>
+    </row>
+    <row r="1280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1280" s="11"/>
+      <c r="D1280" s="11"/>
+      <c r="E1280" s="11"/>
+    </row>
+    <row r="1281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1281" s="11"/>
+      <c r="D1281" s="11"/>
+      <c r="E1281" s="11"/>
+    </row>
+    <row r="1282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1282" s="11"/>
+      <c r="D1282" s="11"/>
+      <c r="E1282" s="11"/>
+    </row>
+    <row r="1283" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1283" s="11"/>
+      <c r="D1283" s="11"/>
+      <c r="E1283" s="11"/>
+    </row>
+    <row r="1284" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1284" s="11"/>
+      <c r="D1284" s="11"/>
+      <c r="E1284" s="11"/>
+    </row>
+    <row r="1285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1285" s="11"/>
+      <c r="D1285" s="11"/>
+      <c r="E1285" s="11"/>
+    </row>
+    <row r="1286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1286" s="11"/>
+      <c r="D1286" s="11"/>
+      <c r="E1286" s="11"/>
+    </row>
+    <row r="1287" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1287" s="11"/>
+      <c r="D1287" s="11"/>
+      <c r="E1287" s="11"/>
+    </row>
+    <row r="1288" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1288" s="11"/>
+      <c r="D1288" s="11"/>
+      <c r="E1288" s="11"/>
+    </row>
+    <row r="1289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1289" s="11"/>
+      <c r="D1289" s="11"/>
+      <c r="E1289" s="11"/>
+    </row>
+    <row r="1290" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1290" s="11"/>
+      <c r="D1290" s="11"/>
+      <c r="E1290" s="11"/>
+    </row>
+    <row r="1291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1291" s="11"/>
+      <c r="D1291" s="11"/>
+      <c r="E1291" s="11"/>
+    </row>
+    <row r="1292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1292" s="11"/>
+      <c r="D1292" s="11"/>
+      <c r="E1292" s="11"/>
+    </row>
+    <row r="1293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1293" s="11"/>
+      <c r="D1293" s="11"/>
+      <c r="E1293" s="11"/>
+    </row>
+    <row r="1294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1294" s="11"/>
+      <c r="D1294" s="11"/>
+      <c r="E1294" s="11"/>
+    </row>
+    <row r="1295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1295" s="11"/>
+      <c r="D1295" s="11"/>
+      <c r="E1295" s="11"/>
+    </row>
+    <row r="1296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1296" s="11"/>
+      <c r="D1296" s="11"/>
+      <c r="E1296" s="11"/>
+    </row>
+    <row r="1297" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1297" s="11"/>
+      <c r="D1297" s="11"/>
+      <c r="E1297" s="11"/>
+    </row>
+    <row r="1298" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1298" s="11"/>
+      <c r="D1298" s="11"/>
+      <c r="E1298" s="11"/>
+    </row>
+    <row r="1299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1299" s="11"/>
+      <c r="D1299" s="11"/>
+      <c r="E1299" s="11"/>
+    </row>
+    <row r="1300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1300" s="11"/>
+      <c r="D1300" s="11"/>
+      <c r="E1300" s="11"/>
+    </row>
+    <row r="1301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1301" s="11"/>
+      <c r="D1301" s="11"/>
+      <c r="E1301" s="11"/>
+    </row>
+    <row r="1302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1302" s="11"/>
+      <c r="D1302" s="11"/>
+      <c r="E1302" s="11"/>
+    </row>
+    <row r="1303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1303" s="11"/>
+      <c r="D1303" s="11"/>
+      <c r="E1303" s="11"/>
+    </row>
+    <row r="1304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1304" s="11"/>
+      <c r="D1304" s="11"/>
+      <c r="E1304" s="11"/>
+    </row>
+    <row r="1305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1305" s="11"/>
+      <c r="D1305" s="11"/>
+      <c r="E1305" s="11"/>
+    </row>
+    <row r="1306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1306" s="11"/>
+      <c r="D1306" s="11"/>
+      <c r="E1306" s="11"/>
+    </row>
+    <row r="1307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1307" s="11"/>
+      <c r="D1307" s="11"/>
+      <c r="E1307" s="11"/>
+    </row>
+    <row r="1308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1308" s="11"/>
+      <c r="D1308" s="11"/>
+      <c r="E1308" s="11"/>
+    </row>
+    <row r="1309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1309" s="11"/>
+      <c r="D1309" s="11"/>
+      <c r="E1309" s="11"/>
+    </row>
+    <row r="1310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1310" s="11"/>
+      <c r="D1310" s="11"/>
+      <c r="E1310" s="11"/>
+    </row>
+    <row r="1311" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1311" s="11"/>
+      <c r="D1311" s="11"/>
+      <c r="E1311" s="11"/>
+    </row>
+    <row r="1312" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1312" s="11"/>
+      <c r="D1312" s="11"/>
+      <c r="E1312" s="11"/>
+    </row>
+    <row r="1313" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1313" s="11"/>
+      <c r="D1313" s="11"/>
+      <c r="E1313" s="11"/>
+    </row>
+    <row r="1314" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1314" s="11"/>
+      <c r="D1314" s="11"/>
+      <c r="E1314" s="11"/>
+    </row>
+    <row r="1315" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1315" s="11"/>
+      <c r="D1315" s="11"/>
+      <c r="E1315" s="11"/>
+    </row>
+    <row r="1316" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1316" s="11"/>
+      <c r="D1316" s="11"/>
+      <c r="E1316" s="11"/>
+    </row>
+    <row r="1317" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1317" s="11"/>
+      <c r="D1317" s="11"/>
+      <c r="E1317" s="11"/>
+    </row>
+    <row r="1318" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1318" s="11"/>
+      <c r="D1318" s="11"/>
+      <c r="E1318" s="11"/>
+    </row>
+    <row r="1319" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1319" s="11"/>
+      <c r="D1319" s="11"/>
+      <c r="E1319" s="11"/>
+    </row>
+    <row r="1320" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1320" s="11"/>
+      <c r="D1320" s="11"/>
+      <c r="E1320" s="11"/>
+    </row>
+    <row r="1321" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1321" s="11"/>
+      <c r="D1321" s="11"/>
+      <c r="E1321" s="11"/>
+    </row>
+    <row r="1322" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1322" s="11"/>
+      <c r="D1322" s="11"/>
+      <c r="E1322" s="11"/>
+    </row>
+    <row r="1323" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1323" s="11"/>
+      <c r="D1323" s="11"/>
+      <c r="E1323" s="11"/>
+    </row>
+    <row r="1324" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1324" s="11"/>
+      <c r="D1324" s="11"/>
+      <c r="E1324" s="11"/>
+    </row>
+    <row r="1325" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1325" s="11"/>
+      <c r="D1325" s="11"/>
+      <c r="E1325" s="11"/>
+    </row>
+    <row r="1326" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1326" s="11"/>
+      <c r="D1326" s="11"/>
+      <c r="E1326" s="11"/>
+    </row>
+    <row r="1327" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1327" s="11"/>
+      <c r="D1327" s="11"/>
+      <c r="E1327" s="11"/>
+    </row>
+    <row r="1328" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1328" s="11"/>
+      <c r="D1328" s="11"/>
+      <c r="E1328" s="11"/>
+    </row>
+    <row r="1329" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1329" s="11"/>
+      <c r="D1329" s="11"/>
+      <c r="E1329" s="11"/>
+    </row>
+    <row r="1330" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1330" s="11"/>
+      <c r="D1330" s="11"/>
+      <c r="E1330" s="11"/>
+    </row>
+    <row r="1331" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1331" s="11"/>
+      <c r="D1331" s="11"/>
+      <c r="E1331" s="11"/>
+    </row>
+    <row r="1332" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1332" s="11"/>
+      <c r="D1332" s="11"/>
+      <c r="E1332" s="11"/>
+    </row>
+    <row r="1333" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1333" s="11"/>
+      <c r="D1333" s="11"/>
+      <c r="E1333" s="11"/>
+    </row>
+    <row r="1334" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1334" s="11"/>
+      <c r="D1334" s="11"/>
+      <c r="E1334" s="11"/>
+    </row>
+    <row r="1335" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1335" s="11"/>
+      <c r="D1335" s="11"/>
+      <c r="E1335" s="11"/>
+    </row>
+    <row r="1336" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1336" s="11"/>
+      <c r="D1336" s="11"/>
+      <c r="E1336" s="11"/>
+    </row>
+    <row r="1337" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1337" s="11"/>
+      <c r="D1337" s="11"/>
+      <c r="E1337" s="11"/>
+    </row>
+    <row r="1338" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1338" s="11"/>
+      <c r="D1338" s="11"/>
+      <c r="E1338" s="11"/>
+    </row>
+    <row r="1339" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1339" s="11"/>
+      <c r="D1339" s="11"/>
+      <c r="E1339" s="11"/>
+    </row>
+    <row r="1340" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1340" s="11"/>
+      <c r="D1340" s="11"/>
+      <c r="E1340" s="11"/>
+    </row>
+    <row r="1341" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1341" s="11"/>
+      <c r="D1341" s="11"/>
+      <c r="E1341" s="11"/>
+    </row>
+    <row r="1342" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1342" s="11"/>
+      <c r="D1342" s="11"/>
+      <c r="E1342" s="11"/>
+    </row>
+    <row r="1343" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1343" s="11"/>
+      <c r="D1343" s="11"/>
+      <c r="E1343" s="11"/>
+    </row>
+    <row r="1344" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1344" s="11"/>
+      <c r="D1344" s="11"/>
+      <c r="E1344" s="11"/>
+    </row>
+    <row r="1345" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1345" s="11"/>
+      <c r="D1345" s="11"/>
+      <c r="E1345" s="11"/>
+    </row>
+    <row r="1346" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1346" s="11"/>
+      <c r="D1346" s="11"/>
+      <c r="E1346" s="11"/>
+    </row>
+    <row r="1347" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1347" s="11"/>
+      <c r="D1347" s="11"/>
+      <c r="E1347" s="11"/>
+    </row>
+    <row r="1348" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1348" s="11"/>
+      <c r="D1348" s="11"/>
+      <c r="E1348" s="11"/>
+    </row>
+    <row r="1349" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1349" s="11"/>
+      <c r="D1349" s="11"/>
+      <c r="E1349" s="11"/>
+    </row>
+    <row r="1350" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1350" s="11"/>
+      <c r="D1350" s="11"/>
+      <c r="E1350" s="11"/>
+    </row>
+    <row r="1351" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1351" s="11"/>
+      <c r="D1351" s="11"/>
+      <c r="E1351" s="11"/>
+    </row>
+    <row r="1352" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1352" s="11"/>
+      <c r="D1352" s="11"/>
+      <c r="E1352" s="11"/>
+    </row>
+    <row r="1353" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1353" s="11"/>
+      <c r="D1353" s="11"/>
+      <c r="E1353" s="11"/>
+    </row>
+    <row r="1354" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1354" s="11"/>
+      <c r="D1354" s="11"/>
+      <c r="E1354" s="11"/>
+    </row>
+    <row r="1355" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1355" s="11"/>
+      <c r="D1355" s="11"/>
+      <c r="E1355" s="11"/>
+    </row>
+    <row r="1356" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1356" s="11"/>
+      <c r="D1356" s="11"/>
+      <c r="E1356" s="11"/>
+    </row>
+    <row r="1357" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1357" s="11"/>
+      <c r="D1357" s="11"/>
+      <c r="E1357" s="11"/>
+    </row>
+    <row r="1358" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1358" s="11"/>
+      <c r="D1358" s="11"/>
+      <c r="E1358" s="11"/>
+    </row>
+    <row r="1359" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1359" s="11"/>
+      <c r="D1359" s="11"/>
+      <c r="E1359" s="11"/>
+    </row>
+    <row r="1360" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1360" s="11"/>
+      <c r="D1360" s="11"/>
+      <c r="E1360" s="11"/>
+    </row>
+    <row r="1361" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1361" s="11"/>
+      <c r="D1361" s="11"/>
+      <c r="E1361" s="11"/>
+    </row>
+    <row r="1362" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1362" s="11"/>
+      <c r="D1362" s="11"/>
+      <c r="E1362" s="11"/>
+    </row>
+    <row r="1363" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1363" s="11"/>
+      <c r="D1363" s="11"/>
+      <c r="E1363" s="11"/>
+    </row>
+    <row r="1364" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1364" s="11"/>
+      <c r="D1364" s="11"/>
+      <c r="E1364" s="11"/>
+    </row>
+    <row r="1365" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1365" s="11"/>
+      <c r="D1365" s="11"/>
+      <c r="E1365" s="11"/>
+    </row>
+    <row r="1366" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1366" s="11"/>
+      <c r="D1366" s="11"/>
+      <c r="E1366" s="11"/>
+    </row>
+    <row r="1367" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1367" s="11"/>
+      <c r="D1367" s="11"/>
+      <c r="E1367" s="11"/>
+    </row>
+    <row r="1368" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1368" s="11"/>
+      <c r="D1368" s="11"/>
+      <c r="E1368" s="11"/>
+    </row>
+    <row r="1369" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1369" s="11"/>
+      <c r="D1369" s="11"/>
+      <c r="E1369" s="11"/>
+    </row>
+    <row r="1370" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1370" s="11"/>
+      <c r="D1370" s="11"/>
+      <c r="E1370" s="11"/>
+    </row>
+    <row r="1371" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1371" s="11"/>
+      <c r="D1371" s="11"/>
+      <c r="E1371" s="11"/>
+    </row>
+    <row r="1372" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1372" s="11"/>
+      <c r="D1372" s="11"/>
+      <c r="E1372" s="11"/>
+    </row>
+    <row r="1373" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1373" s="11"/>
+      <c r="D1373" s="11"/>
+      <c r="E1373" s="11"/>
+    </row>
+    <row r="1374" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1374" s="11"/>
+      <c r="D1374" s="11"/>
+      <c r="E1374" s="11"/>
+    </row>
+    <row r="1375" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1375" s="11"/>
+      <c r="D1375" s="11"/>
+      <c r="E1375" s="11"/>
+    </row>
+    <row r="1376" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1376" s="11"/>
+      <c r="D1376" s="11"/>
+      <c r="E1376" s="11"/>
+    </row>
+    <row r="1377" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1377" s="11"/>
+      <c r="D1377" s="11"/>
+      <c r="E1377" s="11"/>
+    </row>
+    <row r="1378" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1378" s="11"/>
+      <c r="D1378" s="11"/>
+      <c r="E1378" s="11"/>
+    </row>
+    <row r="1379" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1379" s="11"/>
+      <c r="D1379" s="11"/>
+      <c r="E1379" s="11"/>
+    </row>
+    <row r="1380" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1380" s="11"/>
+      <c r="D1380" s="11"/>
+      <c r="E1380" s="11"/>
+    </row>
+    <row r="1381" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1381" s="11"/>
+      <c r="D1381" s="11"/>
+      <c r="E1381" s="11"/>
+    </row>
+    <row r="1382" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1382" s="11"/>
+      <c r="D1382" s="11"/>
+      <c r="E1382" s="11"/>
+    </row>
+    <row r="1383" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1383" s="11"/>
+      <c r="D1383" s="11"/>
+      <c r="E1383" s="11"/>
+    </row>
+    <row r="1384" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1384" s="11"/>
+      <c r="D1384" s="11"/>
+      <c r="E1384" s="11"/>
+    </row>
+    <row r="1385" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1385" s="11"/>
+      <c r="D1385" s="11"/>
+      <c r="E1385" s="11"/>
+    </row>
+    <row r="1386" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1386" s="11"/>
+      <c r="D1386" s="11"/>
+      <c r="E1386" s="11"/>
+    </row>
+    <row r="1387" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1387" s="11"/>
+      <c r="D1387" s="11"/>
+      <c r="E1387" s="11"/>
+    </row>
+    <row r="1388" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1388" s="11"/>
+      <c r="D1388" s="11"/>
+      <c r="E1388" s="11"/>
+    </row>
+    <row r="1389" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1389" s="11"/>
+      <c r="D1389" s="11"/>
+      <c r="E1389" s="11"/>
+    </row>
+    <row r="1390" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1390" s="11"/>
+      <c r="D1390" s="11"/>
+      <c r="E1390" s="11"/>
+    </row>
+    <row r="1391" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1391" s="11"/>
+      <c r="D1391" s="11"/>
+      <c r="E1391" s="11"/>
+    </row>
+    <row r="1392" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1392" s="11"/>
+      <c r="D1392" s="11"/>
+      <c r="E1392" s="11"/>
+    </row>
+    <row r="1393" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1393" s="11"/>
+      <c r="D1393" s="11"/>
+      <c r="E1393" s="11"/>
+    </row>
+    <row r="1394" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1394" s="11"/>
+      <c r="D1394" s="11"/>
+      <c r="E1394" s="11"/>
+    </row>
+    <row r="1395" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1395" s="11"/>
+      <c r="D1395" s="11"/>
+      <c r="E1395" s="11"/>
+    </row>
+    <row r="1396" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1396" s="11"/>
+      <c r="D1396" s="11"/>
+      <c r="E1396" s="11"/>
+    </row>
+    <row r="1397" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1397" s="11"/>
+      <c r="D1397" s="11"/>
+      <c r="E1397" s="11"/>
+    </row>
+    <row r="1398" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1398" s="11"/>
+      <c r="D1398" s="11"/>
+      <c r="E1398" s="11"/>
+    </row>
+    <row r="1399" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1399" s="11"/>
+      <c r="D1399" s="11"/>
+      <c r="E1399" s="11"/>
+    </row>
+    <row r="1400" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1400" s="11"/>
+      <c r="D1400" s="11"/>
+      <c r="E1400" s="11"/>
+    </row>
+    <row r="1401" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1401" s="11"/>
+      <c r="D1401" s="11"/>
+      <c r="E1401" s="11"/>
+    </row>
+    <row r="1402" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1402" s="11"/>
+      <c r="D1402" s="11"/>
+      <c r="E1402" s="11"/>
+    </row>
+    <row r="1403" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1403" s="11"/>
+      <c r="D1403" s="11"/>
+      <c r="E1403" s="11"/>
+    </row>
+    <row r="1404" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1404" s="11"/>
+      <c r="D1404" s="11"/>
+      <c r="E1404" s="11"/>
+    </row>
+    <row r="1405" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1405" s="11"/>
+      <c r="D1405" s="11"/>
+      <c r="E1405" s="11"/>
+    </row>
+    <row r="1406" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1406" s="11"/>
+      <c r="D1406" s="11"/>
+      <c r="E1406" s="11"/>
+    </row>
+    <row r="1407" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1407" s="11"/>
+      <c r="D1407" s="11"/>
+      <c r="E1407" s="11"/>
+    </row>
+    <row r="1408" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1408" s="11"/>
+      <c r="D1408" s="11"/>
+      <c r="E1408" s="11"/>
+    </row>
+    <row r="1409" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1409" s="11"/>
+      <c r="D1409" s="11"/>
+      <c r="E1409" s="11"/>
+    </row>
+    <row r="1410" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1410" s="11"/>
+      <c r="D1410" s="11"/>
+      <c r="E1410" s="11"/>
+    </row>
+    <row r="1411" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1411" s="11"/>
+      <c r="D1411" s="11"/>
+      <c r="E1411" s="11"/>
+    </row>
+    <row r="1412" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1412" s="11"/>
+      <c r="D1412" s="11"/>
+      <c r="E1412" s="11"/>
+    </row>
+    <row r="1413" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1413" s="11"/>
+      <c r="D1413" s="11"/>
+      <c r="E1413" s="11"/>
+    </row>
+    <row r="1414" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1414" s="11"/>
+      <c r="D1414" s="11"/>
+      <c r="E1414" s="11"/>
+    </row>
+    <row r="1415" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1415" s="11"/>
+      <c r="D1415" s="11"/>
+      <c r="E1415" s="11"/>
+    </row>
+    <row r="1416" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1416" s="11"/>
+      <c r="D1416" s="11"/>
+      <c r="E1416" s="11"/>
+    </row>
+    <row r="1417" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1417" s="11"/>
+      <c r="D1417" s="11"/>
+      <c r="E1417" s="11"/>
+    </row>
+    <row r="1418" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1418" s="11"/>
+      <c r="D1418" s="11"/>
+      <c r="E1418" s="11"/>
+    </row>
+    <row r="1419" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1419" s="11"/>
+      <c r="D1419" s="11"/>
+      <c r="E1419" s="11"/>
+    </row>
+    <row r="1420" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1420" s="11"/>
+      <c r="D1420" s="11"/>
+      <c r="E1420" s="11"/>
+    </row>
+    <row r="1421" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1421" s="11"/>
+      <c r="D1421" s="11"/>
+      <c r="E1421" s="11"/>
+    </row>
+    <row r="1422" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1422" s="11"/>
+      <c r="D1422" s="11"/>
+      <c r="E1422" s="11"/>
+    </row>
+    <row r="1423" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1423" s="11"/>
+      <c r="D1423" s="11"/>
+      <c r="E1423" s="11"/>
+    </row>
+    <row r="1424" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1424" s="11"/>
+      <c r="D1424" s="11"/>
+      <c r="E1424" s="11"/>
+    </row>
+    <row r="1425" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1425" s="11"/>
+      <c r="D1425" s="11"/>
+      <c r="E1425" s="11"/>
+    </row>
+    <row r="1426" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1426" s="11"/>
+      <c r="D1426" s="11"/>
+      <c r="E1426" s="11"/>
+    </row>
+    <row r="1427" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1427" s="11"/>
+      <c r="D1427" s="11"/>
+      <c r="E1427" s="11"/>
+    </row>
+    <row r="1428" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1428" s="11"/>
+      <c r="D1428" s="11"/>
+      <c r="E1428" s="11"/>
+    </row>
+    <row r="1429" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1429" s="11"/>
+      <c r="D1429" s="11"/>
+      <c r="E1429" s="11"/>
+    </row>
+    <row r="1430" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1430" s="11"/>
+      <c r="D1430" s="11"/>
+      <c r="E1430" s="11"/>
+    </row>
+    <row r="1431" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1431" s="11"/>
+      <c r="D1431" s="11"/>
+      <c r="E1431" s="11"/>
+    </row>
+    <row r="1432" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1432" s="11"/>
+      <c r="D1432" s="11"/>
+      <c r="E1432" s="11"/>
+    </row>
+    <row r="1433" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1433" s="11"/>
+      <c r="D1433" s="11"/>
+      <c r="E1433" s="11"/>
+    </row>
+    <row r="1434" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1434" s="11"/>
+      <c r="D1434" s="11"/>
+      <c r="E1434" s="11"/>
+    </row>
+    <row r="1435" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1435" s="11"/>
+      <c r="D1435" s="11"/>
+      <c r="E1435" s="11"/>
+    </row>
+    <row r="1436" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1436" s="11"/>
+      <c r="D1436" s="11"/>
+      <c r="E1436" s="11"/>
+    </row>
+    <row r="1437" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1437" s="11"/>
+      <c r="D1437" s="11"/>
+      <c r="E1437" s="11"/>
+    </row>
+    <row r="1438" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1438" s="11"/>
+      <c r="D1438" s="11"/>
+      <c r="E1438" s="11"/>
+    </row>
+    <row r="1439" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1439" s="11"/>
+      <c r="D1439" s="11"/>
+      <c r="E1439" s="11"/>
+    </row>
+    <row r="1440" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1440" s="11"/>
+      <c r="D1440" s="11"/>
+      <c r="E1440" s="11"/>
+    </row>
+    <row r="1441" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1441" s="11"/>
+      <c r="D1441" s="11"/>
+      <c r="E1441" s="11"/>
+    </row>
+    <row r="1442" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1442" s="11"/>
+      <c r="D1442" s="11"/>
+      <c r="E1442" s="11"/>
+    </row>
+    <row r="1443" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1443" s="11"/>
+      <c r="D1443" s="11"/>
+      <c r="E1443" s="11"/>
+    </row>
+    <row r="1444" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1444" s="11"/>
+      <c r="D1444" s="11"/>
+      <c r="E1444" s="11"/>
+    </row>
+    <row r="1445" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1445" s="11"/>
+      <c r="D1445" s="11"/>
+      <c r="E1445" s="11"/>
+    </row>
+    <row r="1446" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1446" s="11"/>
+      <c r="D1446" s="11"/>
+      <c r="E1446" s="11"/>
+    </row>
+    <row r="1447" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1447" s="11"/>
+      <c r="D1447" s="11"/>
+      <c r="E1447" s="11"/>
+    </row>
+    <row r="1448" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1448" s="11"/>
+      <c r="D1448" s="11"/>
+      <c r="E1448" s="11"/>
+    </row>
+    <row r="1449" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1449" s="11"/>
+      <c r="D1449" s="11"/>
+      <c r="E1449" s="11"/>
+    </row>
+    <row r="1450" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1450" s="11"/>
+      <c r="D1450" s="11"/>
+      <c r="E1450" s="11"/>
+    </row>
+    <row r="1451" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1451" s="11"/>
+      <c r="D1451" s="11"/>
+      <c r="E1451" s="11"/>
+    </row>
+    <row r="1452" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1452" s="11"/>
+      <c r="D1452" s="11"/>
+      <c r="E1452" s="11"/>
+    </row>
+    <row r="1453" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1453" s="11"/>
+      <c r="D1453" s="11"/>
+      <c r="E1453" s="11"/>
+    </row>
+    <row r="1454" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1454" s="11"/>
+      <c r="D1454" s="11"/>
+      <c r="E1454" s="11"/>
+    </row>
+    <row r="1455" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1455" s="11"/>
+      <c r="D1455" s="11"/>
+      <c r="E1455" s="11"/>
+    </row>
+    <row r="1456" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1456" s="11"/>
+      <c r="D1456" s="11"/>
+      <c r="E1456" s="11"/>
+    </row>
+    <row r="1457" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1457" s="11"/>
+      <c r="D1457" s="11"/>
+      <c r="E1457" s="11"/>
+    </row>
+    <row r="1458" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1458" s="11"/>
+      <c r="D1458" s="11"/>
+      <c r="E1458" s="11"/>
+    </row>
+    <row r="1459" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1459" s="11"/>
+      <c r="D1459" s="11"/>
+      <c r="E1459" s="11"/>
+    </row>
+    <row r="1460" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1460" s="11"/>
+      <c r="D1460" s="11"/>
+      <c r="E1460" s="11"/>
+    </row>
+    <row r="1461" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1461" s="11"/>
+      <c r="D1461" s="11"/>
+      <c r="E1461" s="11"/>
+    </row>
+    <row r="1462" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1462" s="11"/>
+      <c r="D1462" s="11"/>
+      <c r="E1462" s="11"/>
+    </row>
+    <row r="1463" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1463" s="11"/>
+      <c r="D1463" s="11"/>
+      <c r="E1463" s="11"/>
+    </row>
+    <row r="1464" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1464" s="11"/>
+      <c r="D1464" s="11"/>
+      <c r="E1464" s="11"/>
+    </row>
+    <row r="1465" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1465" s="11"/>
+      <c r="D1465" s="11"/>
+      <c r="E1465" s="11"/>
+    </row>
+    <row r="1466" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1466" s="11"/>
+      <c r="D1466" s="11"/>
+      <c r="E1466" s="11"/>
+    </row>
+    <row r="1467" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1467" s="11"/>
+      <c r="D1467" s="11"/>
+      <c r="E1467" s="11"/>
+    </row>
+    <row r="1468" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1468" s="11"/>
+      <c r="D1468" s="11"/>
+      <c r="E1468" s="11"/>
+    </row>
+    <row r="1469" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1469" s="11"/>
+      <c r="D1469" s="11"/>
+      <c r="E1469" s="11"/>
+    </row>
+    <row r="1470" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1470" s="11"/>
+      <c r="D1470" s="11"/>
+      <c r="E1470" s="11"/>
+    </row>
+    <row r="1471" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1471" s="11"/>
+      <c r="D1471" s="11"/>
+      <c r="E1471" s="11"/>
+    </row>
+    <row r="1472" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1472" s="11"/>
+      <c r="D1472" s="11"/>
+      <c r="E1472" s="11"/>
+    </row>
+    <row r="1473" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1473" s="11"/>
+      <c r="D1473" s="11"/>
+      <c r="E1473" s="11"/>
+    </row>
+    <row r="1474" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1474" s="11"/>
+      <c r="D1474" s="11"/>
+      <c r="E1474" s="11"/>
+    </row>
+    <row r="1475" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1475" s="11"/>
+      <c r="D1475" s="11"/>
+      <c r="E1475" s="11"/>
+    </row>
+    <row r="1476" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1476" s="11"/>
+      <c r="D1476" s="11"/>
+      <c r="E1476" s="11"/>
+    </row>
+    <row r="1477" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1477" s="11"/>
+      <c r="D1477" s="11"/>
+      <c r="E1477" s="11"/>
+    </row>
+    <row r="1478" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1478" s="11"/>
+      <c r="D1478" s="11"/>
+      <c r="E1478" s="11"/>
+    </row>
+    <row r="1479" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1479" s="11"/>
+      <c r="D1479" s="11"/>
+      <c r="E1479" s="11"/>
+    </row>
+    <row r="1480" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1480" s="11"/>
+      <c r="D1480" s="11"/>
+      <c r="E1480" s="11"/>
+    </row>
+    <row r="1481" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1481" s="11"/>
+      <c r="D1481" s="11"/>
+      <c r="E1481" s="11"/>
+    </row>
+    <row r="1482" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1482" s="11"/>
+      <c r="D1482" s="11"/>
+      <c r="E1482" s="11"/>
+    </row>
+    <row r="1483" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1483" s="11"/>
+      <c r="D1483" s="11"/>
+      <c r="E1483" s="11"/>
+    </row>
+    <row r="1484" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1484" s="11"/>
+      <c r="D1484" s="11"/>
+      <c r="E1484" s="11"/>
+    </row>
+    <row r="1485" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1485" s="11"/>
+      <c r="D1485" s="11"/>
+      <c r="E1485" s="11"/>
+    </row>
+    <row r="1486" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1486" s="11"/>
+      <c r="D1486" s="11"/>
+      <c r="E1486" s="11"/>
+    </row>
+    <row r="1487" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1487" s="11"/>
+      <c r="D1487" s="11"/>
+      <c r="E1487" s="11"/>
+    </row>
+    <row r="1488" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1488" s="11"/>
+      <c r="D1488" s="11"/>
+      <c r="E1488" s="11"/>
+    </row>
+    <row r="1489" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1489" s="11"/>
+      <c r="D1489" s="11"/>
+      <c r="E1489" s="11"/>
+    </row>
+    <row r="1490" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1490" s="11"/>
+      <c r="D1490" s="11"/>
+      <c r="E1490" s="11"/>
+    </row>
+    <row r="1491" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1491" s="11"/>
+      <c r="D1491" s="11"/>
+      <c r="E1491" s="11"/>
+    </row>
+    <row r="1492" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1492" s="11"/>
+      <c r="D1492" s="11"/>
+      <c r="E1492" s="11"/>
+    </row>
+    <row r="1493" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1493" s="11"/>
+      <c r="D1493" s="11"/>
+      <c r="E1493" s="11"/>
+    </row>
+    <row r="1494" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1494" s="11"/>
+      <c r="D1494" s="11"/>
+      <c r="E1494" s="11"/>
+    </row>
+    <row r="1495" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1495" s="11"/>
+      <c r="D1495" s="11"/>
+      <c r="E1495" s="11"/>
+    </row>
+    <row r="1496" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1496" s="11"/>
+      <c r="D1496" s="11"/>
+      <c r="E1496" s="11"/>
+    </row>
+    <row r="1497" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1497" s="11"/>
+      <c r="D1497" s="11"/>
+      <c r="E1497" s="11"/>
+    </row>
+    <row r="1498" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1498" s="11"/>
+      <c r="D1498" s="11"/>
+      <c r="E1498" s="11"/>
+    </row>
+    <row r="1499" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1499" s="11"/>
+      <c r="D1499" s="11"/>
+      <c r="E1499" s="11"/>
+    </row>
+    <row r="1500" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1500" s="11"/>
+      <c r="D1500" s="11"/>
+      <c r="E1500" s="11"/>
+    </row>
+    <row r="1501" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1501" s="11"/>
+      <c r="D1501" s="11"/>
+      <c r="E1501" s="11"/>
+    </row>
+    <row r="1502" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1502" s="11"/>
+      <c r="D1502" s="11"/>
+      <c r="E1502" s="11"/>
+    </row>
+    <row r="1503" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1503" s="11"/>
+      <c r="D1503" s="11"/>
+      <c r="E1503" s="11"/>
+    </row>
+    <row r="1504" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1504" s="11"/>
+      <c r="D1504" s="11"/>
+      <c r="E1504" s="11"/>
+    </row>
+    <row r="1505" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1505" s="11"/>
+      <c r="D1505" s="11"/>
+      <c r="E1505" s="11"/>
+    </row>
+    <row r="1506" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1506" s="11"/>
+      <c r="D1506" s="11"/>
+      <c r="E1506" s="11"/>
+    </row>
+    <row r="1507" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1507" s="11"/>
+      <c r="D1507" s="11"/>
+      <c r="E1507" s="11"/>
+    </row>
+    <row r="1508" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1508" s="11"/>
+      <c r="D1508" s="11"/>
+      <c r="E1508" s="11"/>
+    </row>
+    <row r="1509" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1509" s="11"/>
+      <c r="D1509" s="11"/>
+      <c r="E1509" s="11"/>
+    </row>
+    <row r="1510" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1510" s="11"/>
+      <c r="D1510" s="11"/>
+      <c r="E1510" s="11"/>
+    </row>
+    <row r="1511" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1511" s="11"/>
+      <c r="D1511" s="11"/>
+      <c r="E1511" s="11"/>
+    </row>
+    <row r="1512" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1512" s="11"/>
+      <c r="D1512" s="11"/>
+      <c r="E1512" s="11"/>
+    </row>
+    <row r="1513" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1513" s="11"/>
+      <c r="D1513" s="11"/>
+      <c r="E1513" s="11"/>
+    </row>
+    <row r="1514" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1514" s="11"/>
+      <c r="D1514" s="11"/>
+      <c r="E1514" s="11"/>
+    </row>
+    <row r="1515" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1515" s="11"/>
+      <c r="D1515" s="11"/>
+      <c r="E1515" s="11"/>
+    </row>
+    <row r="1516" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1516" s="11"/>
+      <c r="D1516" s="11"/>
+      <c r="E1516" s="11"/>
+    </row>
+    <row r="1517" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1517" s="11"/>
+      <c r="D1517" s="11"/>
+      <c r="E1517" s="11"/>
+    </row>
+    <row r="1518" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1518" s="11"/>
+      <c r="D1518" s="11"/>
+      <c r="E1518" s="11"/>
+    </row>
+    <row r="1519" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1519" s="11"/>
+      <c r="D1519" s="11"/>
+      <c r="E1519" s="11"/>
+    </row>
+    <row r="1520" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1520" s="11"/>
+      <c r="D1520" s="11"/>
+      <c r="E1520" s="11"/>
+    </row>
+    <row r="1521" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1521" s="11"/>
+      <c r="D1521" s="11"/>
+      <c r="E1521" s="11"/>
+    </row>
+    <row r="1522" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1522" s="11"/>
+      <c r="D1522" s="11"/>
+      <c r="E1522" s="11"/>
+    </row>
+    <row r="1523" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1523" s="11"/>
+      <c r="D1523" s="11"/>
+      <c r="E1523" s="11"/>
+    </row>
+    <row r="1524" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1524" s="11"/>
+      <c r="D1524" s="11"/>
+      <c r="E1524" s="11"/>
+    </row>
+    <row r="1525" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1525" s="11"/>
+      <c r="D1525" s="11"/>
+      <c r="E1525" s="11"/>
+    </row>
+    <row r="1526" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1526" s="11"/>
+      <c r="D1526" s="11"/>
+      <c r="E1526" s="11"/>
+    </row>
+    <row r="1527" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1527" s="11"/>
+      <c r="D1527" s="11"/>
+      <c r="E1527" s="11"/>
+    </row>
+    <row r="1528" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1528" s="11"/>
+      <c r="D1528" s="11"/>
+      <c r="E1528" s="11"/>
+    </row>
+    <row r="1529" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1529" s="11"/>
+      <c r="D1529" s="11"/>
+      <c r="E1529" s="11"/>
+    </row>
+    <row r="1530" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1530" s="11"/>
+      <c r="D1530" s="11"/>
+      <c r="E1530" s="11"/>
+    </row>
+    <row r="1531" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1531" s="11"/>
+      <c r="D1531" s="11"/>
+      <c r="E1531" s="11"/>
+    </row>
+    <row r="1532" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1532" s="11"/>
+      <c r="D1532" s="11"/>
+      <c r="E1532" s="11"/>
+    </row>
+    <row r="1533" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1533" s="11"/>
+      <c r="D1533" s="11"/>
+      <c r="E1533" s="11"/>
+    </row>
+    <row r="1534" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1534" s="11"/>
+      <c r="D1534" s="11"/>
+      <c r="E1534" s="11"/>
+    </row>
+    <row r="1535" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1535" s="11"/>
+      <c r="D1535" s="11"/>
+      <c r="E1535" s="11"/>
+    </row>
+    <row r="1536" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1536" s="11"/>
+      <c r="D1536" s="11"/>
+      <c r="E1536" s="11"/>
+    </row>
+    <row r="1537" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1537" s="11"/>
+      <c r="D1537" s="11"/>
+      <c r="E1537" s="11"/>
+    </row>
+    <row r="1538" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1538" s="11"/>
+      <c r="D1538" s="11"/>
+      <c r="E1538" s="11"/>
+    </row>
+    <row r="1539" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1539" s="11"/>
+      <c r="D1539" s="11"/>
+      <c r="E1539" s="11"/>
+    </row>
+    <row r="1540" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1540" s="11"/>
+      <c r="D1540" s="11"/>
+      <c r="E1540" s="11"/>
+    </row>
+    <row r="1541" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1541" s="11"/>
+      <c r="D1541" s="11"/>
+      <c r="E1541" s="11"/>
+    </row>
+    <row r="1542" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1542" s="11"/>
+      <c r="D1542" s="11"/>
+      <c r="E1542" s="11"/>
+    </row>
+    <row r="1543" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1543" s="11"/>
+      <c r="D1543" s="11"/>
+      <c r="E1543" s="11"/>
+    </row>
+    <row r="1544" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1544" s="11"/>
+      <c r="D1544" s="11"/>
+      <c r="E1544" s="11"/>
+    </row>
+    <row r="1545" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1545" s="11"/>
+      <c r="D1545" s="11"/>
+      <c r="E1545" s="11"/>
+    </row>
+    <row r="1546" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1546" s="11"/>
+      <c r="D1546" s="11"/>
+      <c r="E1546" s="11"/>
+    </row>
+    <row r="1547" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1547" s="11"/>
+      <c r="D1547" s="11"/>
+      <c r="E1547" s="11"/>
+    </row>
+    <row r="1548" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1548" s="11"/>
+      <c r="D1548" s="11"/>
+      <c r="E1548" s="11"/>
+    </row>
+    <row r="1549" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1549" s="11"/>
+      <c r="D1549" s="11"/>
+      <c r="E1549" s="11"/>
+    </row>
+    <row r="1550" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1550" s="11"/>
+      <c r="D1550" s="11"/>
+      <c r="E1550" s="11"/>
+    </row>
+    <row r="1551" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1551" s="11"/>
+      <c r="D1551" s="11"/>
+      <c r="E1551" s="11"/>
+    </row>
+    <row r="1552" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1552" s="11"/>
+      <c r="D1552" s="11"/>
+      <c r="E1552" s="11"/>
+    </row>
+    <row r="1553" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1553" s="11"/>
+      <c r="D1553" s="11"/>
+      <c r="E1553" s="11"/>
+    </row>
+    <row r="1554" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1554" s="11"/>
+      <c r="D1554" s="11"/>
+      <c r="E1554" s="11"/>
+    </row>
+    <row r="1555" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1555" s="11"/>
+      <c r="D1555" s="11"/>
+      <c r="E1555" s="11"/>
+    </row>
+    <row r="1556" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1556" s="11"/>
+      <c r="D1556" s="11"/>
+      <c r="E1556" s="11"/>
+    </row>
+    <row r="1557" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1557" s="11"/>
+      <c r="D1557" s="11"/>
+      <c r="E1557" s="11"/>
+    </row>
+    <row r="1558" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1558" s="11"/>
+      <c r="D1558" s="11"/>
+      <c r="E1558" s="11"/>
+    </row>
+    <row r="1559" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1559" s="11"/>
+      <c r="D1559" s="11"/>
+      <c r="E1559" s="11"/>
+    </row>
+    <row r="1560" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1560" s="11"/>
+      <c r="D1560" s="11"/>
+      <c r="E1560" s="11"/>
+    </row>
+    <row r="1561" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1561" s="11"/>
+      <c r="D1561" s="11"/>
+      <c r="E1561" s="11"/>
+    </row>
+    <row r="1562" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1562" s="11"/>
+      <c r="D1562" s="11"/>
+      <c r="E1562" s="11"/>
+    </row>
+    <row r="1563" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1563" s="11"/>
+      <c r="D1563" s="11"/>
+      <c r="E1563" s="11"/>
+    </row>
+    <row r="1564" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1564" s="11"/>
+      <c r="D1564" s="11"/>
+      <c r="E1564" s="11"/>
+    </row>
+    <row r="1565" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1565" s="11"/>
+      <c r="D1565" s="11"/>
+      <c r="E1565" s="11"/>
+    </row>
+    <row r="1566" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1566" s="11"/>
+      <c r="D1566" s="11"/>
+      <c r="E1566" s="11"/>
+    </row>
+    <row r="1567" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1567" s="11"/>
+      <c r="D1567" s="11"/>
+      <c r="E1567" s="11"/>
+    </row>
+    <row r="1568" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1568" s="11"/>
+      <c r="D1568" s="11"/>
+      <c r="E1568" s="11"/>
+    </row>
+    <row r="1569" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1569" s="11"/>
+      <c r="D1569" s="11"/>
+      <c r="E1569" s="11"/>
+    </row>
+    <row r="1570" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1570" s="11"/>
+      <c r="D1570" s="11"/>
+      <c r="E1570" s="11"/>
+    </row>
+    <row r="1571" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1571" s="11"/>
+      <c r="D1571" s="11"/>
+      <c r="E1571" s="11"/>
+    </row>
+    <row r="1572" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1572" s="11"/>
+      <c r="D1572" s="11"/>
+      <c r="E1572" s="11"/>
+    </row>
+    <row r="1573" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1573" s="11"/>
+      <c r="D1573" s="11"/>
+      <c r="E1573" s="11"/>
+    </row>
+    <row r="1574" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1574" s="11"/>
+      <c r="D1574" s="11"/>
+      <c r="E1574" s="11"/>
+    </row>
+    <row r="1575" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1575" s="11"/>
+      <c r="D1575" s="11"/>
+      <c r="E1575" s="11"/>
+    </row>
+    <row r="1576" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1576" s="11"/>
+      <c r="D1576" s="11"/>
+      <c r="E1576" s="11"/>
+    </row>
+    <row r="1577" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1577" s="11"/>
+      <c r="D1577" s="11"/>
+      <c r="E1577" s="11"/>
+    </row>
+    <row r="1578" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1578" s="11"/>
+      <c r="D1578" s="11"/>
+      <c r="E1578" s="11"/>
+    </row>
+    <row r="1579" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1579" s="11"/>
+      <c r="D1579" s="11"/>
+      <c r="E1579" s="11"/>
+    </row>
+    <row r="1580" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1580" s="11"/>
+      <c r="D1580" s="11"/>
+      <c r="E1580" s="11"/>
+    </row>
+    <row r="1581" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1581" s="11"/>
+      <c r="D1581" s="11"/>
+      <c r="E1581" s="11"/>
+    </row>
+    <row r="1582" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1582" s="11"/>
+      <c r="D1582" s="11"/>
+      <c r="E1582" s="11"/>
+    </row>
+    <row r="1583" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1583" s="11"/>
+      <c r="D1583" s="11"/>
+      <c r="E1583" s="11"/>
+    </row>
+    <row r="1584" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1584" s="11"/>
+      <c r="D1584" s="11"/>
+      <c r="E1584" s="11"/>
+    </row>
+    <row r="1585" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1585" s="11"/>
+      <c r="D1585" s="11"/>
+      <c r="E1585" s="11"/>
+    </row>
+    <row r="1586" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1586" s="11"/>
+      <c r="D1586" s="11"/>
+      <c r="E1586" s="11"/>
+    </row>
+    <row r="1587" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1587" s="11"/>
+      <c r="D1587" s="11"/>
+      <c r="E1587" s="11"/>
+    </row>
+    <row r="1588" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1588" s="11"/>
+      <c r="D1588" s="11"/>
+      <c r="E1588" s="11"/>
+    </row>
+    <row r="1589" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1589" s="11"/>
+      <c r="D1589" s="11"/>
+      <c r="E1589" s="11"/>
+    </row>
+    <row r="1590" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1590" s="11"/>
+      <c r="D1590" s="11"/>
+      <c r="E1590" s="11"/>
+    </row>
+    <row r="1591" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1591" s="11"/>
+      <c r="D1591" s="11"/>
+      <c r="E1591" s="11"/>
+    </row>
+    <row r="1592" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1592" s="11"/>
+      <c r="D1592" s="11"/>
+      <c r="E1592" s="11"/>
+    </row>
+    <row r="1593" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1593" s="11"/>
+      <c r="D1593" s="11"/>
+      <c r="E1593" s="11"/>
+    </row>
+    <row r="1594" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1594" s="11"/>
+      <c r="D1594" s="11"/>
+      <c r="E1594" s="11"/>
+    </row>
+    <row r="1595" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1595" s="11"/>
+      <c r="D1595" s="11"/>
+      <c r="E1595" s="11"/>
+    </row>
+    <row r="1596" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1596" s="11"/>
+      <c r="D1596" s="11"/>
+      <c r="E1596" s="11"/>
+    </row>
+    <row r="1597" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1597" s="11"/>
+      <c r="D1597" s="11"/>
+      <c r="E1597" s="11"/>
+    </row>
+    <row r="1598" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1598" s="11"/>
+      <c r="D1598" s="11"/>
+      <c r="E1598" s="11"/>
+    </row>
+    <row r="1599" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1599" s="11"/>
+      <c r="D1599" s="11"/>
+      <c r="E1599" s="11"/>
+    </row>
+    <row r="1600" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1600" s="11"/>
+      <c r="D1600" s="11"/>
+      <c r="E1600" s="11"/>
+    </row>
+    <row r="1601" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1601" s="11"/>
+      <c r="D1601" s="11"/>
+      <c r="E1601" s="11"/>
+    </row>
+    <row r="1602" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1602" s="11"/>
+      <c r="D1602" s="11"/>
+      <c r="E1602" s="11"/>
+    </row>
+    <row r="1603" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1603" s="11"/>
+      <c r="D1603" s="11"/>
+      <c r="E1603" s="11"/>
+    </row>
+    <row r="1604" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1604" s="11"/>
+      <c r="D1604" s="11"/>
+      <c r="E1604" s="11"/>
+    </row>
+    <row r="1605" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1605" s="11"/>
+      <c r="D1605" s="11"/>
+      <c r="E1605" s="11"/>
+    </row>
+    <row r="1606" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1606" s="11"/>
+      <c r="D1606" s="11"/>
+      <c r="E1606" s="11"/>
+    </row>
+    <row r="1607" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1607" s="11"/>
+      <c r="D1607" s="11"/>
+      <c r="E1607" s="11"/>
+    </row>
+    <row r="1608" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1608" s="11"/>
+      <c r="D1608" s="11"/>
+      <c r="E1608" s="11"/>
+    </row>
+    <row r="1609" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1609" s="11"/>
+      <c r="D1609" s="11"/>
+      <c r="E1609" s="11"/>
+    </row>
+    <row r="1610" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1610" s="11"/>
+      <c r="D1610" s="11"/>
+      <c r="E1610" s="11"/>
+    </row>
+    <row r="1611" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1611" s="11"/>
+      <c r="D1611" s="11"/>
+      <c r="E1611" s="11"/>
+    </row>
+    <row r="1612" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1612" s="11"/>
+      <c r="D1612" s="11"/>
+      <c r="E1612" s="11"/>
+    </row>
+    <row r="1613" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1613" s="11"/>
+      <c r="D1613" s="11"/>
+      <c r="E1613" s="11"/>
+    </row>
+    <row r="1614" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1614" s="11"/>
+      <c r="D1614" s="11"/>
+      <c r="E1614" s="11"/>
+    </row>
+    <row r="1615" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1615" s="11"/>
+      <c r="D1615" s="11"/>
+      <c r="E1615" s="11"/>
+    </row>
+    <row r="1616" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1616" s="11"/>
+      <c r="D1616" s="11"/>
+      <c r="E1616" s="11"/>
+    </row>
+    <row r="1617" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1617" s="11"/>
+      <c r="D1617" s="11"/>
+      <c r="E1617" s="11"/>
+    </row>
+    <row r="1618" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1618" s="11"/>
+      <c r="D1618" s="11"/>
+      <c r="E1618" s="11"/>
+    </row>
+    <row r="1619" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1619" s="11"/>
+      <c r="D1619" s="11"/>
+      <c r="E1619" s="11"/>
+    </row>
+    <row r="1620" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1620" s="11"/>
+      <c r="D1620" s="11"/>
+      <c r="E1620" s="11"/>
+    </row>
+    <row r="1621" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1621" s="11"/>
+      <c r="D1621" s="11"/>
+      <c r="E1621" s="11"/>
+    </row>
+    <row r="1622" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1622" s="11"/>
+      <c r="D1622" s="11"/>
+      <c r="E1622" s="11"/>
+    </row>
+    <row r="1623" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1623" s="11"/>
+      <c r="D1623" s="11"/>
+      <c r="E1623" s="11"/>
+    </row>
+    <row r="1624" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1624" s="11"/>
+      <c r="D1624" s="11"/>
+      <c r="E1624" s="11"/>
+    </row>
+    <row r="1625" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1625" s="11"/>
+      <c r="D1625" s="11"/>
+      <c r="E1625" s="11"/>
+    </row>
+    <row r="1626" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1626" s="11"/>
+      <c r="D1626" s="11"/>
+      <c r="E1626" s="11"/>
+    </row>
+    <row r="1627" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1627" s="11"/>
+      <c r="D1627" s="11"/>
+      <c r="E1627" s="11"/>
+    </row>
+    <row r="1628" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1628" s="11"/>
+      <c r="D1628" s="11"/>
+      <c r="E1628" s="11"/>
+    </row>
+    <row r="1629" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1629" s="11"/>
+      <c r="D1629" s="11"/>
+      <c r="E1629" s="11"/>
+    </row>
+    <row r="1630" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1630" s="11"/>
+      <c r="D1630" s="11"/>
+      <c r="E1630" s="11"/>
+    </row>
+    <row r="1631" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1631" s="11"/>
+      <c r="D1631" s="11"/>
+      <c r="E1631" s="11"/>
+    </row>
+    <row r="1632" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1632" s="11"/>
+      <c r="D1632" s="11"/>
+      <c r="E1632" s="11"/>
+    </row>
+    <row r="1633" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1633" s="11"/>
+      <c r="D1633" s="11"/>
+      <c r="E1633" s="11"/>
+    </row>
+    <row r="1634" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1634" s="11"/>
+      <c r="D1634" s="11"/>
+      <c r="E1634" s="11"/>
+    </row>
+    <row r="1635" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1635" s="11"/>
+      <c r="D1635" s="11"/>
+      <c r="E1635" s="11"/>
+    </row>
+    <row r="1636" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1636" s="11"/>
+      <c r="D1636" s="11"/>
+      <c r="E1636" s="11"/>
+    </row>
+    <row r="1637" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1637" s="11"/>
+      <c r="D1637" s="11"/>
+      <c r="E1637" s="11"/>
+    </row>
+    <row r="1638" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1638" s="11"/>
+      <c r="D1638" s="11"/>
+      <c r="E1638" s="11"/>
+    </row>
+    <row r="1639" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1639" s="11"/>
+      <c r="D1639" s="11"/>
+      <c r="E1639" s="11"/>
+    </row>
+    <row r="1640" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1640" s="11"/>
+      <c r="D1640" s="11"/>
+      <c r="E1640" s="11"/>
+    </row>
+    <row r="1641" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1641" s="11"/>
+      <c r="D1641" s="11"/>
+      <c r="E1641" s="11"/>
+    </row>
+    <row r="1642" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1642" s="11"/>
+      <c r="D1642" s="11"/>
+      <c r="E1642" s="11"/>
+    </row>
+    <row r="1643" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1643" s="11"/>
+      <c r="D1643" s="11"/>
+      <c r="E1643" s="11"/>
+    </row>
+    <row r="1644" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C1644" s="11"/>
+      <c r="D1644" s="11"/>
+      <c r="E1644" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I140" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C49B2CA-D1EE-4DD2-9871-17046C2B8A45}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16301B57-982A-4FE5-BE9E-BE48EC1AAD0B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1260" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="152">
   <si>
     <t>POD</t>
   </si>
@@ -496,6 +496,9 @@
   </si>
   <si>
     <t>COSCO</t>
+  </si>
+  <si>
+    <t>1 al 16 de abril</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1644"/>
+  <dimension ref="A1:I1642"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -7419,111 +7422,495 @@
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C235" s="11"/>
-      <c r="D235" s="11"/>
-      <c r="E235" s="11"/>
+      <c r="A235" t="s">
+        <v>59</v>
+      </c>
+      <c r="B235" t="s">
+        <v>15</v>
+      </c>
+      <c r="C235" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D235" s="12">
+        <v>180</v>
+      </c>
+      <c r="E235" s="12">
+        <v>350</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G235" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H235" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I235" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C236" s="11"/>
-      <c r="D236" s="11"/>
-      <c r="E236" s="11"/>
+      <c r="A236" t="s">
+        <v>60</v>
+      </c>
+      <c r="B236" t="s">
+        <v>15</v>
+      </c>
+      <c r="C236" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D236" s="12">
+        <v>270</v>
+      </c>
+      <c r="E236" s="12">
+        <v>520</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G236" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H236" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C237" s="11"/>
-      <c r="D237" s="11"/>
-      <c r="E237" s="11"/>
+      <c r="A237" t="s">
+        <v>61</v>
+      </c>
+      <c r="B237" t="s">
+        <v>15</v>
+      </c>
+      <c r="C237" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D237" s="9">
+        <v>2080</v>
+      </c>
+      <c r="E237" s="9">
+        <v>3480</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G237" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H237" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I237" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C238" s="11"/>
-      <c r="D238" s="11"/>
-      <c r="E238" s="11"/>
+      <c r="A238" t="s">
+        <v>66</v>
+      </c>
+      <c r="B238" t="s">
+        <v>15</v>
+      </c>
+      <c r="C238" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D238" s="9">
+        <v>2080</v>
+      </c>
+      <c r="E238" s="9">
+        <v>3480</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G238" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H238" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I238" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C239" s="11"/>
-      <c r="D239" s="11"/>
-      <c r="E239" s="11"/>
+      <c r="A239" t="s">
+        <v>67</v>
+      </c>
+      <c r="B239" t="s">
+        <v>15</v>
+      </c>
+      <c r="C239" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D239" s="9">
+        <v>1880</v>
+      </c>
+      <c r="E239" s="9">
+        <v>3650</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G239" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H239" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I239" s="7" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C240" s="11"/>
-      <c r="D240" s="11"/>
-      <c r="E240" s="11"/>
-    </row>
-    <row r="241" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C241" s="11"/>
-      <c r="D241" s="11"/>
-      <c r="E241" s="11"/>
-    </row>
-    <row r="242" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C242" s="11"/>
-      <c r="D242" s="11"/>
-      <c r="E242" s="11"/>
-    </row>
-    <row r="243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C243" s="11"/>
-      <c r="D243" s="11"/>
-      <c r="E243" s="11"/>
-    </row>
-    <row r="244" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C244" s="11"/>
-      <c r="D244" s="11"/>
-      <c r="E244" s="11"/>
-    </row>
-    <row r="245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C245" s="11"/>
-      <c r="D245" s="11"/>
-      <c r="E245" s="11"/>
-    </row>
-    <row r="246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C246" s="11"/>
-      <c r="D246" s="11"/>
-      <c r="E246" s="11"/>
-    </row>
-    <row r="247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C247" s="11"/>
-      <c r="D247" s="11"/>
-      <c r="E247" s="11"/>
-    </row>
-    <row r="248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C248" s="11"/>
-      <c r="D248" s="11"/>
-      <c r="E248" s="11"/>
-    </row>
-    <row r="249" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C249" s="11"/>
-      <c r="D249" s="11"/>
-      <c r="E249" s="11"/>
-    </row>
-    <row r="250" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C250" s="11"/>
-      <c r="D250" s="11"/>
-      <c r="E250" s="11"/>
-    </row>
-    <row r="251" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>68</v>
+      </c>
+      <c r="B240" t="s">
+        <v>15</v>
+      </c>
+      <c r="C240" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D240" s="9">
+        <v>1880</v>
+      </c>
+      <c r="E240" s="9">
+        <v>3650</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G240" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H240" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>69</v>
+      </c>
+      <c r="B241" t="s">
+        <v>62</v>
+      </c>
+      <c r="C241" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D241" s="9">
+        <v>2060</v>
+      </c>
+      <c r="E241" s="9">
+        <v>3390</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G241" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H241" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I241" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>70</v>
+      </c>
+      <c r="B242" t="s">
+        <v>62</v>
+      </c>
+      <c r="C242" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D242" s="9">
+        <v>2060</v>
+      </c>
+      <c r="E242" s="9">
+        <v>3390</v>
+      </c>
+      <c r="F242" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G242" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H242" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I242" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>71</v>
+      </c>
+      <c r="B243" t="s">
+        <v>62</v>
+      </c>
+      <c r="C243" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D243" s="9">
+        <v>2060</v>
+      </c>
+      <c r="E243" s="9">
+        <v>3390</v>
+      </c>
+      <c r="F243" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G243" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H243" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I243" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>69</v>
+      </c>
+      <c r="B244" t="s">
+        <v>15</v>
+      </c>
+      <c r="C244" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D244" s="9">
+        <v>2560</v>
+      </c>
+      <c r="E244" s="9">
+        <v>4060</v>
+      </c>
+      <c r="F244" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G244" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H244" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I244" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>73</v>
+      </c>
+      <c r="B245" t="s">
+        <v>62</v>
+      </c>
+      <c r="C245" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D245" s="9">
+        <v>2060</v>
+      </c>
+      <c r="E245" s="9">
+        <v>3390</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G245" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H245" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I245" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>72</v>
+      </c>
+      <c r="B246" t="s">
+        <v>62</v>
+      </c>
+      <c r="C246" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D246" s="9">
+        <v>2340</v>
+      </c>
+      <c r="E246" s="9">
+        <v>3710</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G246" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H246" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I246" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>71</v>
+      </c>
+      <c r="B247" t="s">
+        <v>15</v>
+      </c>
+      <c r="C247" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D247" s="9">
+        <v>2560</v>
+      </c>
+      <c r="E247" s="9">
+        <v>4060</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G247" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H247" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I247" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>72</v>
+      </c>
+      <c r="B248" t="s">
+        <v>15</v>
+      </c>
+      <c r="C248" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D248" s="9">
+        <v>2840</v>
+      </c>
+      <c r="E248" s="9">
+        <v>4380</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G248" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H248" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>73</v>
+      </c>
+      <c r="B249" t="s">
+        <v>15</v>
+      </c>
+      <c r="C249" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D249" s="9">
+        <v>2560</v>
+      </c>
+      <c r="E249" s="9">
+        <v>4060</v>
+      </c>
+      <c r="F249" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G249" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H249" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I249" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>70</v>
+      </c>
+      <c r="B250" t="s">
+        <v>15</v>
+      </c>
+      <c r="C250" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D250" s="9">
+        <v>2560</v>
+      </c>
+      <c r="E250" s="9">
+        <v>4060</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="G250" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H250" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I250" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C251" s="11"/>
       <c r="D251" s="11"/>
       <c r="E251" s="11"/>
     </row>
-    <row r="252" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C252" s="11"/>
       <c r="D252" s="11"/>
       <c r="E252" s="11"/>
     </row>
-    <row r="253" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C253" s="11"/>
       <c r="D253" s="11"/>
       <c r="E253" s="11"/>
     </row>
-    <row r="254" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C254" s="11"/>
       <c r="D254" s="11"/>
       <c r="E254" s="11"/>
     </row>
-    <row r="255" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C255" s="11"/>
       <c r="D255" s="11"/>
       <c r="E255" s="11"/>
     </row>
-    <row r="256" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C256" s="11"/>
       <c r="D256" s="11"/>
       <c r="E256" s="11"/>
@@ -14457,16 +14844,6 @@
       <c r="C1642" s="11"/>
       <c r="D1642" s="11"/>
       <c r="E1642" s="11"/>
-    </row>
-    <row r="1643" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1643" s="11"/>
-      <c r="D1643" s="11"/>
-      <c r="E1643" s="11"/>
-    </row>
-    <row r="1644" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1644" s="11"/>
-      <c r="D1644" s="11"/>
-      <c r="E1644" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I140" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16301B57-982A-4FE5-BE9E-BE48EC1AAD0B}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152E633B-1386-48C4-AF22-5C9883A772CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7432,10 +7432,10 @@
         <v>12</v>
       </c>
       <c r="D235" s="12">
-        <v>180</v>
+        <v>230</v>
       </c>
       <c r="E235" s="12">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>151</v>
@@ -7461,10 +7461,10 @@
         <v>12</v>
       </c>
       <c r="D236" s="12">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="E236" s="12">
-        <v>520</v>
+        <v>570</v>
       </c>
       <c r="F236" s="7" t="s">
         <v>151</v>
@@ -7490,10 +7490,10 @@
         <v>12</v>
       </c>
       <c r="D237" s="9">
-        <v>2080</v>
+        <v>2180</v>
       </c>
       <c r="E237" s="9">
-        <v>3480</v>
+        <v>3580</v>
       </c>
       <c r="F237" s="7" t="s">
         <v>151</v>
@@ -7519,10 +7519,10 @@
         <v>12</v>
       </c>
       <c r="D238" s="9">
-        <v>2080</v>
+        <v>2180</v>
       </c>
       <c r="E238" s="9">
-        <v>3480</v>
+        <v>3580</v>
       </c>
       <c r="F238" s="7" t="s">
         <v>151</v>
@@ -7548,10 +7548,10 @@
         <v>12</v>
       </c>
       <c r="D239" s="9">
-        <v>1880</v>
+        <v>1980</v>
       </c>
       <c r="E239" s="9">
-        <v>3650</v>
+        <v>3750</v>
       </c>
       <c r="F239" s="7" t="s">
         <v>151</v>
@@ -7577,10 +7577,10 @@
         <v>12</v>
       </c>
       <c r="D240" s="9">
-        <v>1880</v>
+        <v>1980</v>
       </c>
       <c r="E240" s="9">
-        <v>3650</v>
+        <v>3750</v>
       </c>
       <c r="F240" s="7" t="s">
         <v>151</v>
@@ -7606,10 +7606,10 @@
         <v>12</v>
       </c>
       <c r="D241" s="9">
-        <v>2060</v>
+        <v>2160</v>
       </c>
       <c r="E241" s="9">
-        <v>3390</v>
+        <v>3490</v>
       </c>
       <c r="F241" s="7" t="s">
         <v>151</v>
@@ -7635,10 +7635,10 @@
         <v>12</v>
       </c>
       <c r="D242" s="9">
-        <v>2060</v>
+        <v>2160</v>
       </c>
       <c r="E242" s="9">
-        <v>3390</v>
+        <v>3490</v>
       </c>
       <c r="F242" s="7" t="s">
         <v>151</v>
@@ -7664,10 +7664,10 @@
         <v>12</v>
       </c>
       <c r="D243" s="9">
-        <v>2060</v>
+        <v>2160</v>
       </c>
       <c r="E243" s="9">
-        <v>3390</v>
+        <v>3490</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>151</v>
@@ -7693,10 +7693,10 @@
         <v>12</v>
       </c>
       <c r="D244" s="9">
-        <v>2560</v>
+        <v>2660</v>
       </c>
       <c r="E244" s="9">
-        <v>4060</v>
+        <v>4160</v>
       </c>
       <c r="F244" s="7" t="s">
         <v>151</v>
@@ -7722,10 +7722,10 @@
         <v>12</v>
       </c>
       <c r="D245" s="9">
-        <v>2060</v>
+        <v>2160</v>
       </c>
       <c r="E245" s="9">
-        <v>3390</v>
+        <v>3490</v>
       </c>
       <c r="F245" s="7" t="s">
         <v>151</v>
@@ -7751,10 +7751,10 @@
         <v>12</v>
       </c>
       <c r="D246" s="9">
-        <v>2340</v>
+        <v>2440</v>
       </c>
       <c r="E246" s="9">
-        <v>3710</v>
+        <v>3810</v>
       </c>
       <c r="F246" s="7" t="s">
         <v>151</v>
@@ -7780,10 +7780,10 @@
         <v>12</v>
       </c>
       <c r="D247" s="9">
-        <v>2560</v>
+        <v>2660</v>
       </c>
       <c r="E247" s="9">
-        <v>4060</v>
+        <v>4160</v>
       </c>
       <c r="F247" s="7" t="s">
         <v>151</v>
@@ -7809,10 +7809,10 @@
         <v>12</v>
       </c>
       <c r="D248" s="9">
-        <v>2840</v>
+        <v>2940</v>
       </c>
       <c r="E248" s="9">
-        <v>4380</v>
+        <v>4480</v>
       </c>
       <c r="F248" s="7" t="s">
         <v>151</v>
@@ -7838,10 +7838,10 @@
         <v>12</v>
       </c>
       <c r="D249" s="9">
-        <v>2560</v>
+        <v>2660</v>
       </c>
       <c r="E249" s="9">
-        <v>4060</v>
+        <v>4160</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>151</v>
@@ -7867,10 +7867,10 @@
         <v>12</v>
       </c>
       <c r="D250" s="9">
-        <v>2560</v>
+        <v>2660</v>
       </c>
       <c r="E250" s="9">
-        <v>4060</v>
+        <v>4160</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>151</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152E633B-1386-48C4-AF22-5C9883A772CD}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F506A961-8E4A-43A9-B6F2-F8F8A5C7E97F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7490,10 +7490,10 @@
         <v>12</v>
       </c>
       <c r="D237" s="9">
-        <v>2180</v>
+        <v>1620</v>
       </c>
       <c r="E237" s="9">
-        <v>3580</v>
+        <v>2460</v>
       </c>
       <c r="F237" s="7" t="s">
         <v>151</v>
@@ -7519,10 +7519,10 @@
         <v>12</v>
       </c>
       <c r="D238" s="9">
-        <v>2180</v>
+        <v>1620</v>
       </c>
       <c r="E238" s="9">
-        <v>3580</v>
+        <v>2460</v>
       </c>
       <c r="F238" s="7" t="s">
         <v>151</v>
@@ -7548,10 +7548,10 @@
         <v>12</v>
       </c>
       <c r="D239" s="9">
-        <v>1980</v>
+        <v>1410</v>
       </c>
       <c r="E239" s="9">
-        <v>3750</v>
+        <v>2630</v>
       </c>
       <c r="F239" s="7" t="s">
         <v>151</v>
@@ -7577,10 +7577,10 @@
         <v>12</v>
       </c>
       <c r="D240" s="9">
-        <v>1980</v>
+        <v>1410</v>
       </c>
       <c r="E240" s="9">
-        <v>3750</v>
+        <v>2630</v>
       </c>
       <c r="F240" s="7" t="s">
         <v>151</v>
@@ -7606,10 +7606,10 @@
         <v>12</v>
       </c>
       <c r="D241" s="9">
-        <v>2160</v>
+        <v>1870</v>
       </c>
       <c r="E241" s="9">
-        <v>3490</v>
+        <v>2910</v>
       </c>
       <c r="F241" s="7" t="s">
         <v>151</v>
@@ -7635,10 +7635,10 @@
         <v>12</v>
       </c>
       <c r="D242" s="9">
-        <v>2160</v>
+        <v>1870</v>
       </c>
       <c r="E242" s="9">
-        <v>3490</v>
+        <v>2910</v>
       </c>
       <c r="F242" s="7" t="s">
         <v>151</v>
@@ -7664,10 +7664,10 @@
         <v>12</v>
       </c>
       <c r="D243" s="9">
-        <v>2160</v>
+        <v>1870</v>
       </c>
       <c r="E243" s="9">
-        <v>3490</v>
+        <v>2910</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>151</v>
@@ -7693,10 +7693,10 @@
         <v>12</v>
       </c>
       <c r="D244" s="9">
-        <v>2660</v>
+        <v>2370</v>
       </c>
       <c r="E244" s="9">
-        <v>4160</v>
+        <v>3580</v>
       </c>
       <c r="F244" s="7" t="s">
         <v>151</v>
@@ -7722,10 +7722,10 @@
         <v>12</v>
       </c>
       <c r="D245" s="9">
-        <v>2160</v>
+        <v>1870</v>
       </c>
       <c r="E245" s="9">
-        <v>3490</v>
+        <v>2910</v>
       </c>
       <c r="F245" s="7" t="s">
         <v>151</v>
@@ -7751,10 +7751,10 @@
         <v>12</v>
       </c>
       <c r="D246" s="9">
-        <v>2440</v>
+        <v>2150</v>
       </c>
       <c r="E246" s="9">
-        <v>3810</v>
+        <v>3230</v>
       </c>
       <c r="F246" s="7" t="s">
         <v>151</v>
@@ -7780,10 +7780,10 @@
         <v>12</v>
       </c>
       <c r="D247" s="9">
-        <v>2660</v>
+        <v>2370</v>
       </c>
       <c r="E247" s="9">
-        <v>4160</v>
+        <v>3580</v>
       </c>
       <c r="F247" s="7" t="s">
         <v>151</v>
@@ -7809,10 +7809,10 @@
         <v>12</v>
       </c>
       <c r="D248" s="9">
-        <v>2940</v>
+        <v>2650</v>
       </c>
       <c r="E248" s="9">
-        <v>4480</v>
+        <v>3900</v>
       </c>
       <c r="F248" s="7" t="s">
         <v>151</v>
@@ -7838,10 +7838,10 @@
         <v>12</v>
       </c>
       <c r="D249" s="9">
-        <v>2660</v>
+        <v>2370</v>
       </c>
       <c r="E249" s="9">
-        <v>4160</v>
+        <v>3580</v>
       </c>
       <c r="F249" s="7" t="s">
         <v>151</v>
@@ -7867,10 +7867,10 @@
         <v>12</v>
       </c>
       <c r="D250" s="9">
-        <v>2660</v>
+        <v>2370</v>
       </c>
       <c r="E250" s="9">
-        <v>4160</v>
+        <v>3580</v>
       </c>
       <c r="F250" s="7" t="s">
         <v>151</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F506A961-8E4A-43A9-B6F2-F8F8A5C7E97F}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F422D37-6A6E-4179-9A27-0F096C826513}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2061" uniqueCount="159">
   <si>
     <t>POD</t>
   </si>
@@ -499,6 +499,27 @@
   </si>
   <si>
     <t>1 al 16 de abril</t>
+  </si>
+  <si>
+    <t>1 al 7 de abril</t>
+  </si>
+  <si>
+    <t>SHIMIZU</t>
+  </si>
+  <si>
+    <t>PASIR GUDANG</t>
+  </si>
+  <si>
+    <t>KOTA KINABALU</t>
+  </si>
+  <si>
+    <t>DELHI(ICD SONIPAT)</t>
+  </si>
+  <si>
+    <t>KANPUR</t>
+  </si>
+  <si>
+    <t>1 al 15 de abril</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1642"/>
+  <dimension ref="A1:M1642"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -7595,7 +7616,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>69</v>
       </c>
@@ -7624,7 +7645,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>70</v>
       </c>
@@ -7653,7 +7674,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>71</v>
       </c>
@@ -7682,7 +7703,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>69</v>
       </c>
@@ -7711,7 +7732,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>73</v>
       </c>
@@ -7740,7 +7761,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>72</v>
       </c>
@@ -7769,7 +7790,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>71</v>
       </c>
@@ -7798,7 +7819,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>72</v>
       </c>
@@ -7827,7 +7848,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>73</v>
       </c>
@@ -7856,7 +7877,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>70</v>
       </c>
@@ -7885,672 +7906,4000 @@
         <v>64</v>
       </c>
     </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C251" s="11"/>
-      <c r="D251" s="11"/>
-      <c r="E251" s="11"/>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C252" s="11"/>
-      <c r="D252" s="11"/>
-      <c r="E252" s="11"/>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C253" s="11"/>
-      <c r="D253" s="11"/>
-      <c r="E253" s="11"/>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C254" s="11"/>
-      <c r="D254" s="11"/>
-      <c r="E254" s="11"/>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C255" s="11"/>
-      <c r="D255" s="11"/>
-      <c r="E255" s="11"/>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C256" s="11"/>
-      <c r="D256" s="11"/>
-      <c r="E256" s="11"/>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C257" s="11"/>
-      <c r="D257" s="11"/>
-      <c r="E257" s="11"/>
-    </row>
-    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C258" s="11"/>
-      <c r="D258" s="11"/>
-      <c r="E258" s="11"/>
-    </row>
-    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A251" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B251" t="s">
+        <v>15</v>
+      </c>
+      <c r="C251" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D251" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E251" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F251" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H251" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I251" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J251" s="7"/>
+      <c r="K251" s="7"/>
+      <c r="L251" s="7"/>
+      <c r="M251" s="7"/>
+    </row>
+    <row r="252" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A252" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B252" t="s">
+        <v>15</v>
+      </c>
+      <c r="C252" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D252" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E252" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H252" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I252" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J252" s="7"/>
+      <c r="K252" s="7"/>
+      <c r="L252" s="7"/>
+      <c r="M252" s="7"/>
+    </row>
+    <row r="253" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A253" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B253" t="s">
+        <v>15</v>
+      </c>
+      <c r="C253" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D253" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E253" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H253" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I253" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J253" s="7"/>
+      <c r="K253" s="7"/>
+      <c r="L253" s="7"/>
+      <c r="M253" s="7"/>
+    </row>
+    <row r="254" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A254" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B254" t="s">
+        <v>15</v>
+      </c>
+      <c r="C254" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D254" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E254" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H254" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J254" s="7"/>
+      <c r="K254" s="7"/>
+      <c r="L254" s="7"/>
+      <c r="M254" s="7"/>
+    </row>
+    <row r="255" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A255" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B255" t="s">
+        <v>15</v>
+      </c>
+      <c r="C255" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D255" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E255" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H255" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I255" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J255" s="7"/>
+      <c r="K255" s="7"/>
+      <c r="L255" s="7"/>
+      <c r="M255" s="7"/>
+    </row>
+    <row r="256" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A256" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B256" t="s">
+        <v>15</v>
+      </c>
+      <c r="C256" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D256" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E256" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H256" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J256" s="7"/>
+      <c r="K256" s="7"/>
+      <c r="L256" s="7"/>
+      <c r="M256" s="7"/>
+    </row>
+    <row r="257" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A257" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B257" t="s">
+        <v>15</v>
+      </c>
+      <c r="C257" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D257" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E257" s="11">
+        <v>3140</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H257" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I257" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J257" s="7"/>
+      <c r="K257" s="7"/>
+      <c r="L257" s="7"/>
+      <c r="M257" s="7"/>
+    </row>
+    <row r="258" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A258" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B258" t="s">
+        <v>15</v>
+      </c>
+      <c r="C258" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D258" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E258" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H258" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I258" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J258" s="7"/>
+      <c r="K258" s="7"/>
+      <c r="L258" s="7"/>
+      <c r="M258" s="7"/>
+    </row>
+    <row r="259" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A259" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B259" t="s">
+        <v>15</v>
+      </c>
       <c r="C259" s="11"/>
-      <c r="D259" s="11"/>
-      <c r="E259" s="11"/>
-    </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C260" s="11"/>
-      <c r="D260" s="11"/>
-      <c r="E260" s="11"/>
-    </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C261" s="11"/>
-      <c r="D261" s="11"/>
-      <c r="E261" s="11"/>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C262" s="11"/>
-      <c r="D262" s="11"/>
-      <c r="E262" s="11"/>
-    </row>
-    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C263" s="11"/>
-      <c r="D263" s="11"/>
-      <c r="E263" s="11"/>
-    </row>
-    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C264" s="11"/>
-      <c r="D264" s="11"/>
-      <c r="E264" s="11"/>
-    </row>
-    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C265" s="11"/>
-      <c r="D265" s="11"/>
-      <c r="E265" s="11"/>
-    </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C266" s="11"/>
-      <c r="D266" s="11"/>
-      <c r="E266" s="11"/>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C267" s="11"/>
-      <c r="D267" s="11"/>
-      <c r="E267" s="11"/>
-    </row>
-    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C268" s="11"/>
-      <c r="D268" s="11"/>
-      <c r="E268" s="11"/>
-    </row>
-    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D259" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E259" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G259" s="8">
+        <v>18</v>
+      </c>
+      <c r="H259" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I259" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J259" s="7"/>
+      <c r="K259" s="7"/>
+      <c r="L259" s="7"/>
+      <c r="M259" s="7"/>
+    </row>
+    <row r="260" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A260" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B260" t="s">
+        <v>15</v>
+      </c>
+      <c r="C260" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D260" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E260" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H260" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J260" s="7"/>
+      <c r="K260" s="7"/>
+      <c r="L260" s="7"/>
+      <c r="M260" s="7"/>
+    </row>
+    <row r="261" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B261" t="s">
+        <v>15</v>
+      </c>
+      <c r="C261" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D261" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E261" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F261" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H261" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I261" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J261" s="7"/>
+      <c r="K261" s="7"/>
+      <c r="L261" s="7"/>
+      <c r="M261" s="7"/>
+    </row>
+    <row r="262" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A262" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B262" t="s">
+        <v>15</v>
+      </c>
+      <c r="C262" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D262" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E262" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F262" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H262" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I262" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J262" s="7"/>
+      <c r="K262" s="7"/>
+      <c r="L262" s="7"/>
+      <c r="M262" s="7"/>
+    </row>
+    <row r="263" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A263" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B263" t="s">
+        <v>15</v>
+      </c>
+      <c r="C263" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D263" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E263" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F263" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H263" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I263" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J263" s="7"/>
+      <c r="K263" s="7"/>
+      <c r="L263" s="7"/>
+      <c r="M263" s="7"/>
+    </row>
+    <row r="264" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A264" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B264" t="s">
+        <v>15</v>
+      </c>
+      <c r="C264" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D264" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E264" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F264" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H264" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I264" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J264" s="7"/>
+      <c r="K264" s="7"/>
+      <c r="L264" s="7"/>
+      <c r="M264" s="7"/>
+    </row>
+    <row r="265" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A265" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B265" t="s">
+        <v>15</v>
+      </c>
+      <c r="C265" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D265" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E265" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F265" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H265" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I265" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J265" s="7"/>
+      <c r="K265" s="7"/>
+      <c r="L265" s="7"/>
+      <c r="M265" s="7"/>
+    </row>
+    <row r="266" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A266" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B266" t="s">
+        <v>15</v>
+      </c>
+      <c r="C266" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D266" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E266" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H266" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I266" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J266" s="7"/>
+      <c r="K266" s="7"/>
+      <c r="L266" s="7"/>
+      <c r="M266" s="7"/>
+    </row>
+    <row r="267" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A267" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B267" t="s">
+        <v>15</v>
+      </c>
+      <c r="C267" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D267" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E267" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H267" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I267" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J267" s="7"/>
+      <c r="K267" s="7"/>
+      <c r="L267" s="7"/>
+      <c r="M267" s="7"/>
+    </row>
+    <row r="268" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A268" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B268" t="s">
+        <v>15</v>
+      </c>
+      <c r="C268" s="11">
+        <v>2880</v>
+      </c>
+      <c r="D268" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E268" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F268" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="H268" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I268" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J268" s="7"/>
+      <c r="K268" s="7"/>
+      <c r="L268" s="7"/>
+      <c r="M268" s="7"/>
+    </row>
+    <row r="269" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A269" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B269" t="s">
+        <v>15</v>
+      </c>
       <c r="C269" s="11"/>
-      <c r="D269" s="11"/>
-      <c r="E269" s="11"/>
-    </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D269" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E269" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F269" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G269" s="8">
+        <v>18</v>
+      </c>
+      <c r="H269" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I269" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J269" s="7"/>
+      <c r="K269" s="7"/>
+      <c r="L269" s="7"/>
+      <c r="M269" s="7"/>
+    </row>
+    <row r="270" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A270" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B270" t="s">
+        <v>15</v>
+      </c>
       <c r="C270" s="11"/>
-      <c r="D270" s="11"/>
-      <c r="E270" s="11"/>
-    </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D270" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E270" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F270" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G270" s="8">
+        <v>18</v>
+      </c>
+      <c r="H270" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I270" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J270" s="7"/>
+      <c r="K270" s="7"/>
+      <c r="L270" s="7"/>
+      <c r="M270" s="7"/>
+    </row>
+    <row r="271" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A271" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B271" t="s">
+        <v>15</v>
+      </c>
       <c r="C271" s="11"/>
-      <c r="D271" s="11"/>
-      <c r="E271" s="11"/>
-    </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D271" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E271" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F271" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G271" s="8">
+        <v>18</v>
+      </c>
+      <c r="H271" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I271" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J271" s="7"/>
+      <c r="K271" s="7"/>
+      <c r="L271" s="7"/>
+      <c r="M271" s="7"/>
+    </row>
+    <row r="272" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A272" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B272" t="s">
+        <v>15</v>
+      </c>
       <c r="C272" s="11"/>
-      <c r="D272" s="11"/>
-      <c r="E272" s="11"/>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D272" s="11">
+        <v>3040</v>
+      </c>
+      <c r="E272" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G272" s="8">
+        <v>18</v>
+      </c>
+      <c r="H272" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J272" s="7"/>
+      <c r="K272" s="7"/>
+      <c r="L272" s="7"/>
+      <c r="M272" s="7"/>
+    </row>
+    <row r="273" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A273" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B273" t="s">
+        <v>15</v>
+      </c>
       <c r="C273" s="11"/>
-      <c r="D273" s="11"/>
-      <c r="E273" s="11"/>
-    </row>
-    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D273" s="11">
+        <v>3200</v>
+      </c>
+      <c r="E273" s="11">
+        <v>3620</v>
+      </c>
+      <c r="F273" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G273" s="8">
+        <v>18</v>
+      </c>
+      <c r="H273" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I273" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J273" s="7"/>
+      <c r="K273" s="7"/>
+      <c r="L273" s="7"/>
+      <c r="M273" s="7"/>
+    </row>
+    <row r="274" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A274" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B274" t="s">
+        <v>15</v>
+      </c>
       <c r="C274" s="11"/>
-      <c r="D274" s="11"/>
-      <c r="E274" s="11"/>
-    </row>
-    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D274" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E274" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F274" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G274" s="8">
+        <v>18</v>
+      </c>
+      <c r="H274" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I274" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J274" s="7"/>
+      <c r="K274" s="7"/>
+      <c r="L274" s="7"/>
+      <c r="M274" s="7"/>
+    </row>
+    <row r="275" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A275" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B275" t="s">
+        <v>15</v>
+      </c>
       <c r="C275" s="11"/>
-      <c r="D275" s="11"/>
-      <c r="E275" s="11"/>
-    </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D275" s="11">
+        <v>3250</v>
+      </c>
+      <c r="E275" s="11">
+        <v>3670</v>
+      </c>
+      <c r="F275" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G275" s="8">
+        <v>18</v>
+      </c>
+      <c r="H275" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I275" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J275" s="7"/>
+      <c r="K275" s="7"/>
+      <c r="L275" s="7"/>
+      <c r="M275" s="7"/>
+    </row>
+    <row r="276" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A276" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B276" t="s">
+        <v>15</v>
+      </c>
       <c r="C276" s="11"/>
-      <c r="D276" s="11"/>
-      <c r="E276" s="11"/>
-    </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D276" s="11">
+        <v>3250</v>
+      </c>
+      <c r="E276" s="11">
+        <v>3670</v>
+      </c>
+      <c r="F276" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G276" s="8">
+        <v>18</v>
+      </c>
+      <c r="H276" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I276" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J276" s="7"/>
+      <c r="K276" s="7"/>
+      <c r="L276" s="7"/>
+      <c r="M276" s="7"/>
+    </row>
+    <row r="277" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A277" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B277" t="s">
+        <v>15</v>
+      </c>
       <c r="C277" s="11"/>
-      <c r="D277" s="11"/>
-      <c r="E277" s="11"/>
-    </row>
-    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D277" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E277" s="11">
+        <v>3350</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G277" s="8">
+        <v>18</v>
+      </c>
+      <c r="H277" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I277" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J277" s="7"/>
+      <c r="K277" s="7"/>
+      <c r="L277" s="7"/>
+      <c r="M277" s="7"/>
+    </row>
+    <row r="278" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A278" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B278" t="s">
+        <v>15</v>
+      </c>
       <c r="C278" s="11"/>
-      <c r="D278" s="11"/>
-      <c r="E278" s="11"/>
-    </row>
-    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D278" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E278" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F278" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G278" s="8">
+        <v>18</v>
+      </c>
+      <c r="H278" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I278" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J278" s="7"/>
+      <c r="K278" s="7"/>
+      <c r="L278" s="7"/>
+      <c r="M278" s="7"/>
+    </row>
+    <row r="279" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A279" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B279" t="s">
+        <v>15</v>
+      </c>
       <c r="C279" s="11"/>
-      <c r="D279" s="11"/>
-      <c r="E279" s="11"/>
-    </row>
-    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D279" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E279" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G279" s="8">
+        <v>18</v>
+      </c>
+      <c r="H279" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I279" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J279" s="7"/>
+      <c r="K279" s="7"/>
+      <c r="L279" s="7"/>
+      <c r="M279" s="7"/>
+    </row>
+    <row r="280" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A280" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B280" t="s">
+        <v>15</v>
+      </c>
       <c r="C280" s="11"/>
-      <c r="D280" s="11"/>
-      <c r="E280" s="11"/>
-    </row>
-    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D280" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E280" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G280" s="8">
+        <v>18</v>
+      </c>
+      <c r="H280" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I280" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J280" s="7"/>
+      <c r="K280" s="7"/>
+      <c r="L280" s="7"/>
+      <c r="M280" s="7"/>
+    </row>
+    <row r="281" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A281" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B281" t="s">
+        <v>15</v>
+      </c>
       <c r="C281" s="11"/>
-      <c r="D281" s="11"/>
-      <c r="E281" s="11"/>
-    </row>
-    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D281" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E281" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G281" s="8">
+        <v>18</v>
+      </c>
+      <c r="H281" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I281" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J281" s="7"/>
+      <c r="K281" s="7"/>
+      <c r="L281" s="7"/>
+      <c r="M281" s="7"/>
+    </row>
+    <row r="282" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A282" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B282" t="s">
+        <v>15</v>
+      </c>
       <c r="C282" s="11"/>
-      <c r="D282" s="11"/>
-      <c r="E282" s="11"/>
-    </row>
-    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D282" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E282" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G282" s="8">
+        <v>18</v>
+      </c>
+      <c r="H282" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J282" s="7"/>
+      <c r="K282" s="7"/>
+      <c r="L282" s="7"/>
+      <c r="M282" s="7"/>
+    </row>
+    <row r="283" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A283" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B283" t="s">
+        <v>15</v>
+      </c>
       <c r="C283" s="11"/>
-      <c r="D283" s="11"/>
-      <c r="E283" s="11"/>
-    </row>
-    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D283" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E283" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F283" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G283" s="8">
+        <v>18</v>
+      </c>
+      <c r="H283" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I283" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J283" s="7"/>
+      <c r="K283" s="7"/>
+      <c r="L283" s="7"/>
+      <c r="M283" s="7"/>
+    </row>
+    <row r="284" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A284" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B284" t="s">
+        <v>15</v>
+      </c>
       <c r="C284" s="11"/>
-      <c r="D284" s="11"/>
-      <c r="E284" s="11"/>
-    </row>
-    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D284" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E284" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F284" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G284" s="8">
+        <v>18</v>
+      </c>
+      <c r="H284" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J284" s="7"/>
+      <c r="K284" s="7"/>
+      <c r="L284" s="7"/>
+      <c r="M284" s="7"/>
+    </row>
+    <row r="285" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A285" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B285" t="s">
+        <v>15</v>
+      </c>
       <c r="C285" s="11"/>
-      <c r="D285" s="11"/>
-      <c r="E285" s="11"/>
-    </row>
-    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D285" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E285" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F285" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G285" s="8">
+        <v>18</v>
+      </c>
+      <c r="H285" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I285" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J285" s="7"/>
+      <c r="K285" s="7"/>
+      <c r="L285" s="7"/>
+      <c r="M285" s="7"/>
+    </row>
+    <row r="286" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A286" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B286" t="s">
+        <v>15</v>
+      </c>
       <c r="C286" s="11"/>
-      <c r="D286" s="11"/>
-      <c r="E286" s="11"/>
-    </row>
-    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D286" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E286" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G286" s="8">
+        <v>18</v>
+      </c>
+      <c r="H286" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I286" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J286" s="7"/>
+      <c r="K286" s="7"/>
+      <c r="L286" s="7"/>
+      <c r="M286" s="7"/>
+    </row>
+    <row r="287" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A287" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B287" t="s">
+        <v>15</v>
+      </c>
       <c r="C287" s="11"/>
-      <c r="D287" s="11"/>
-      <c r="E287" s="11"/>
-    </row>
-    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D287" s="11">
+        <v>3200</v>
+      </c>
+      <c r="E287" s="11">
+        <v>3620</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G287" s="8">
+        <v>18</v>
+      </c>
+      <c r="H287" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I287" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J287" s="7"/>
+      <c r="K287" s="7"/>
+      <c r="L287" s="7"/>
+      <c r="M287" s="7"/>
+    </row>
+    <row r="288" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A288" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B288" t="s">
+        <v>15</v>
+      </c>
       <c r="C288" s="11"/>
-      <c r="D288" s="11"/>
-      <c r="E288" s="11"/>
-    </row>
-    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D288" s="11">
+        <v>3250</v>
+      </c>
+      <c r="E288" s="11">
+        <v>3670</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G288" s="8">
+        <v>18</v>
+      </c>
+      <c r="H288" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J288" s="7"/>
+      <c r="K288" s="7"/>
+      <c r="L288" s="7"/>
+      <c r="M288" s="7"/>
+    </row>
+    <row r="289" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A289" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B289" t="s">
+        <v>15</v>
+      </c>
       <c r="C289" s="11"/>
-      <c r="D289" s="11"/>
-      <c r="E289" s="11"/>
-    </row>
-    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D289" s="11">
+        <v>3300</v>
+      </c>
+      <c r="E289" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G289" s="8">
+        <v>18</v>
+      </c>
+      <c r="H289" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I289" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J289" s="7"/>
+      <c r="K289" s="7"/>
+      <c r="L289" s="7"/>
+      <c r="M289" s="7"/>
+    </row>
+    <row r="290" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A290" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B290" t="s">
+        <v>15</v>
+      </c>
       <c r="C290" s="11"/>
-      <c r="D290" s="11"/>
-      <c r="E290" s="11"/>
-    </row>
-    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D290" s="11">
+        <v>3300</v>
+      </c>
+      <c r="E290" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G290" s="8">
+        <v>18</v>
+      </c>
+      <c r="H290" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J290" s="7"/>
+      <c r="K290" s="7"/>
+      <c r="L290" s="7"/>
+      <c r="M290" s="7"/>
+    </row>
+    <row r="291" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A291" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B291" t="s">
+        <v>15</v>
+      </c>
       <c r="C291" s="11"/>
-      <c r="D291" s="11"/>
-      <c r="E291" s="11"/>
-    </row>
-    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D291" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E291" s="11">
+        <v>3980</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G291" s="8">
+        <v>18</v>
+      </c>
+      <c r="H291" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I291" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J291" s="7"/>
+      <c r="K291" s="7"/>
+      <c r="L291" s="7"/>
+      <c r="M291" s="7"/>
+    </row>
+    <row r="292" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A292" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B292" t="s">
+        <v>15</v>
+      </c>
       <c r="C292" s="11"/>
-      <c r="D292" s="11"/>
-      <c r="E292" s="11"/>
-    </row>
-    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D292" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E292" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F292" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G292" s="8">
+        <v>18</v>
+      </c>
+      <c r="H292" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J292" s="7"/>
+      <c r="K292" s="7"/>
+      <c r="L292" s="7"/>
+      <c r="M292" s="7"/>
+    </row>
+    <row r="293" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A293" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B293" t="s">
+        <v>15</v>
+      </c>
       <c r="C293" s="11"/>
-      <c r="D293" s="11"/>
-      <c r="E293" s="11"/>
-    </row>
-    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D293" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E293" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G293" s="8">
+        <v>18</v>
+      </c>
+      <c r="H293" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I293" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J293" s="7"/>
+      <c r="K293" s="7"/>
+      <c r="L293" s="7"/>
+      <c r="M293" s="7"/>
+    </row>
+    <row r="294" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A294" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B294" t="s">
+        <v>15</v>
+      </c>
       <c r="C294" s="11"/>
-      <c r="D294" s="11"/>
-      <c r="E294" s="11"/>
-    </row>
-    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D294" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E294" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G294" s="8">
+        <v>18</v>
+      </c>
+      <c r="H294" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I294" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J294" s="7"/>
+      <c r="K294" s="7"/>
+      <c r="L294" s="7"/>
+      <c r="M294" s="7"/>
+    </row>
+    <row r="295" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A295" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B295" t="s">
+        <v>15</v>
+      </c>
       <c r="C295" s="11"/>
-      <c r="D295" s="11"/>
-      <c r="E295" s="11"/>
-    </row>
-    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D295" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E295" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G295" s="8">
+        <v>18</v>
+      </c>
+      <c r="H295" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I295" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J295" s="7"/>
+      <c r="K295" s="7"/>
+      <c r="L295" s="7"/>
+      <c r="M295" s="7"/>
+    </row>
+    <row r="296" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A296" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B296" t="s">
+        <v>15</v>
+      </c>
       <c r="C296" s="11"/>
-      <c r="D296" s="11"/>
-      <c r="E296" s="11"/>
-    </row>
-    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D296" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E296" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G296" s="8">
+        <v>18</v>
+      </c>
+      <c r="H296" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I296" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J296" s="7"/>
+      <c r="K296" s="7"/>
+      <c r="L296" s="7"/>
+      <c r="M296" s="7"/>
+    </row>
+    <row r="297" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" t="s">
+        <v>15</v>
+      </c>
       <c r="C297" s="11"/>
-      <c r="D297" s="11"/>
-      <c r="E297" s="11"/>
-    </row>
-    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D297" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E297" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F297" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G297" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H297" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I297" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J297" s="7"/>
+      <c r="K297" s="7"/>
+      <c r="L297" s="7"/>
+      <c r="M297" s="7"/>
+    </row>
+    <row r="298" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>20</v>
+      </c>
+      <c r="B298" t="s">
+        <v>15</v>
+      </c>
       <c r="C298" s="11"/>
-      <c r="D298" s="11"/>
-      <c r="E298" s="11"/>
-    </row>
-    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D298" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E298" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G298" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H298" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I298" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J298" s="7"/>
+      <c r="K298" s="7"/>
+      <c r="L298" s="7"/>
+      <c r="M298" s="7"/>
+    </row>
+    <row r="299" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>19</v>
+      </c>
+      <c r="B299" t="s">
+        <v>15</v>
+      </c>
       <c r="C299" s="11"/>
-      <c r="D299" s="11"/>
-      <c r="E299" s="11"/>
-    </row>
-    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D299" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E299" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G299" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I299" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J299" s="7"/>
+      <c r="K299" s="7"/>
+      <c r="L299" s="7"/>
+      <c r="M299" s="7"/>
+    </row>
+    <row r="300" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>16</v>
+      </c>
+      <c r="B300" t="s">
+        <v>15</v>
+      </c>
       <c r="C300" s="11"/>
-      <c r="D300" s="11"/>
-      <c r="E300" s="11"/>
-    </row>
-    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D300" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E300" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G300" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H300" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J300" s="7"/>
+      <c r="K300" s="7"/>
+      <c r="L300" s="7"/>
+      <c r="M300" s="7"/>
+    </row>
+    <row r="301" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>13</v>
+      </c>
+      <c r="B301" t="s">
+        <v>15</v>
+      </c>
       <c r="C301" s="11"/>
-      <c r="D301" s="11"/>
-      <c r="E301" s="11"/>
-    </row>
-    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D301" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E301" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F301" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H301" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I301" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J301" s="7"/>
+      <c r="K301" s="7"/>
+      <c r="L301" s="7"/>
+      <c r="M301" s="7"/>
+    </row>
+    <row r="302" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>5</v>
+      </c>
+      <c r="B302" t="s">
+        <v>15</v>
+      </c>
       <c r="C302" s="11"/>
-      <c r="D302" s="11"/>
-      <c r="E302" s="11"/>
-    </row>
-    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D302" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E302" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J302" s="7"/>
+      <c r="K302" s="7"/>
+      <c r="L302" s="7"/>
+      <c r="M302" s="7"/>
+    </row>
+    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>4</v>
+      </c>
+      <c r="B303" t="s">
+        <v>15</v>
+      </c>
       <c r="C303" s="11"/>
-      <c r="D303" s="11"/>
-      <c r="E303" s="11"/>
-    </row>
-    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D303" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E303" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F303" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J303" s="7"/>
+      <c r="K303" s="7"/>
+      <c r="L303" s="7"/>
+      <c r="M303" s="7"/>
+    </row>
+    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>131</v>
+      </c>
+      <c r="B304" t="s">
+        <v>15</v>
+      </c>
       <c r="C304" s="11"/>
-      <c r="D304" s="11"/>
-      <c r="E304" s="11"/>
-    </row>
-    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D304" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E304" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G304" s="8">
+        <v>17</v>
+      </c>
+      <c r="H304" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J304" s="7"/>
+      <c r="K304" s="7"/>
+      <c r="L304" s="7"/>
+      <c r="M304" s="7"/>
+    </row>
+    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>24</v>
+      </c>
+      <c r="B305" t="s">
+        <v>15</v>
+      </c>
       <c r="C305" s="11"/>
-      <c r="D305" s="11"/>
-      <c r="E305" s="11"/>
-    </row>
-    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D305" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E305" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G305" s="8">
+        <v>17</v>
+      </c>
+      <c r="H305" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J305" s="7"/>
+      <c r="K305" s="7"/>
+      <c r="L305" s="7"/>
+      <c r="M305" s="7"/>
+    </row>
+    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>25</v>
+      </c>
+      <c r="B306" t="s">
+        <v>15</v>
+      </c>
       <c r="C306" s="11"/>
-      <c r="D306" s="11"/>
-      <c r="E306" s="11"/>
-    </row>
-    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D306" s="11">
+        <v>2970</v>
+      </c>
+      <c r="E306" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G306" s="8">
+        <v>17</v>
+      </c>
+      <c r="H306" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J306" s="7"/>
+      <c r="K306" s="7"/>
+      <c r="L306" s="7"/>
+      <c r="M306" s="7"/>
+    </row>
+    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>26</v>
+      </c>
+      <c r="B307" t="s">
+        <v>15</v>
+      </c>
       <c r="C307" s="11"/>
-      <c r="D307" s="11"/>
-      <c r="E307" s="11"/>
-    </row>
-    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D307" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E307" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G307" s="8">
+        <v>17</v>
+      </c>
+      <c r="H307" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J307" s="7"/>
+      <c r="K307" s="7"/>
+      <c r="L307" s="7"/>
+      <c r="M307" s="7"/>
+    </row>
+    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>27</v>
+      </c>
+      <c r="B308" t="s">
+        <v>15</v>
+      </c>
       <c r="C308" s="11"/>
-      <c r="D308" s="11"/>
-      <c r="E308" s="11"/>
-    </row>
-    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D308" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E308" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G308" s="8">
+        <v>17</v>
+      </c>
+      <c r="H308" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J308" s="7"/>
+      <c r="K308" s="7"/>
+      <c r="L308" s="7"/>
+      <c r="M308" s="7"/>
+    </row>
+    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>48</v>
+      </c>
+      <c r="B309" t="s">
+        <v>15</v>
+      </c>
       <c r="C309" s="11"/>
-      <c r="D309" s="11"/>
-      <c r="E309" s="11"/>
-    </row>
-    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D309" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E309" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G309" s="8">
+        <v>17</v>
+      </c>
+      <c r="H309" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J309" s="7"/>
+      <c r="K309" s="7"/>
+      <c r="L309" s="7"/>
+      <c r="M309" s="7"/>
+    </row>
+    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>49</v>
+      </c>
+      <c r="B310" t="s">
+        <v>15</v>
+      </c>
       <c r="C310" s="11"/>
-      <c r="D310" s="11"/>
-      <c r="E310" s="11"/>
-    </row>
-    <row r="311" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D310" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E310" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G310" s="8">
+        <v>17</v>
+      </c>
+      <c r="H310" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J310" s="7"/>
+      <c r="K310" s="7"/>
+      <c r="L310" s="7"/>
+      <c r="M310" s="7"/>
+    </row>
+    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>28</v>
+      </c>
+      <c r="B311" t="s">
+        <v>15</v>
+      </c>
       <c r="C311" s="11"/>
-      <c r="D311" s="11"/>
-      <c r="E311" s="11"/>
-    </row>
-    <row r="312" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D311" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E311" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F311" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G311" s="8">
+        <v>17</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J311" s="7"/>
+      <c r="K311" s="7"/>
+      <c r="L311" s="7"/>
+      <c r="M311" s="7"/>
+    </row>
+    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>50</v>
+      </c>
+      <c r="B312" t="s">
+        <v>15</v>
+      </c>
       <c r="C312" s="11"/>
-      <c r="D312" s="11"/>
-      <c r="E312" s="11"/>
-    </row>
-    <row r="313" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D312" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E312" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F312" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G312" s="8">
+        <v>17</v>
+      </c>
+      <c r="H312" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J312" s="7"/>
+      <c r="K312" s="7"/>
+      <c r="L312" s="7"/>
+      <c r="M312" s="7"/>
+    </row>
+    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>51</v>
+      </c>
+      <c r="B313" t="s">
+        <v>15</v>
+      </c>
       <c r="C313" s="11"/>
-      <c r="D313" s="11"/>
-      <c r="E313" s="11"/>
-    </row>
-    <row r="314" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D313" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E313" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F313" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G313" s="8">
+        <v>17</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J313" s="7"/>
+      <c r="K313" s="7"/>
+      <c r="L313" s="7"/>
+      <c r="M313" s="7"/>
+    </row>
+    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>52</v>
+      </c>
+      <c r="B314" t="s">
+        <v>15</v>
+      </c>
       <c r="C314" s="11"/>
-      <c r="D314" s="11"/>
-      <c r="E314" s="11"/>
-    </row>
-    <row r="315" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D314" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E314" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G314" s="8">
+        <v>17</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J314" s="7"/>
+      <c r="K314" s="7"/>
+      <c r="L314" s="7"/>
+      <c r="M314" s="7"/>
+    </row>
+    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>29</v>
+      </c>
+      <c r="B315" t="s">
+        <v>15</v>
+      </c>
       <c r="C315" s="11"/>
-      <c r="D315" s="11"/>
-      <c r="E315" s="11"/>
-    </row>
-    <row r="316" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D315" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E315" s="11">
+        <v>3510</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G315" s="8">
+        <v>17</v>
+      </c>
+      <c r="H315" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J315" s="7"/>
+      <c r="K315" s="7"/>
+      <c r="L315" s="7"/>
+      <c r="M315" s="7"/>
+    </row>
+    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>30</v>
+      </c>
+      <c r="B316" t="s">
+        <v>15</v>
+      </c>
       <c r="C316" s="11"/>
-      <c r="D316" s="11"/>
-      <c r="E316" s="11"/>
-    </row>
-    <row r="317" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D316" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E316" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G316" s="8">
+        <v>17</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J316" s="7"/>
+      <c r="K316" s="7"/>
+      <c r="L316" s="7"/>
+      <c r="M316" s="7"/>
+    </row>
+    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>132</v>
+      </c>
+      <c r="B317" t="s">
+        <v>15</v>
+      </c>
       <c r="C317" s="11"/>
-      <c r="D317" s="11"/>
-      <c r="E317" s="11"/>
-    </row>
-    <row r="318" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D317" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E317" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G317" s="8">
+        <v>17</v>
+      </c>
+      <c r="H317" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J317" s="7"/>
+      <c r="K317" s="7"/>
+      <c r="L317" s="7"/>
+      <c r="M317" s="7"/>
+    </row>
+    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>133</v>
+      </c>
+      <c r="B318" t="s">
+        <v>15</v>
+      </c>
       <c r="C318" s="11"/>
-      <c r="D318" s="11"/>
-      <c r="E318" s="11"/>
-    </row>
-    <row r="319" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D318" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E318" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G318" s="8">
+        <v>17</v>
+      </c>
+      <c r="H318" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J318" s="7"/>
+      <c r="K318" s="7"/>
+      <c r="L318" s="7"/>
+      <c r="M318" s="7"/>
+    </row>
+    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>134</v>
+      </c>
+      <c r="B319" t="s">
+        <v>15</v>
+      </c>
       <c r="C319" s="11"/>
-      <c r="D319" s="11"/>
-      <c r="E319" s="11"/>
-    </row>
-    <row r="320" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D319" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E319" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G319" s="8">
+        <v>17</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J319" s="7"/>
+      <c r="K319" s="7"/>
+      <c r="L319" s="7"/>
+      <c r="M319" s="7"/>
+    </row>
+    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>31</v>
+      </c>
+      <c r="B320" t="s">
+        <v>15</v>
+      </c>
       <c r="C320" s="11"/>
-      <c r="D320" s="11"/>
-      <c r="E320" s="11"/>
-    </row>
-    <row r="321" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D320" s="11">
+        <v>3120</v>
+      </c>
+      <c r="E320" s="11">
+        <v>3450</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G320" s="8">
+        <v>17</v>
+      </c>
+      <c r="H320" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J320" s="7"/>
+      <c r="K320" s="7"/>
+      <c r="L320" s="7"/>
+      <c r="M320" s="7"/>
+    </row>
+    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>135</v>
+      </c>
+      <c r="B321" t="s">
+        <v>15</v>
+      </c>
       <c r="C321" s="11"/>
-      <c r="D321" s="11"/>
-      <c r="E321" s="11"/>
-    </row>
-    <row r="322" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D321" s="11">
+        <v>3150</v>
+      </c>
+      <c r="E321" s="11">
+        <v>3550</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G321" s="8">
+        <v>17</v>
+      </c>
+      <c r="H321" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J321" s="7"/>
+      <c r="K321" s="7"/>
+      <c r="L321" s="7"/>
+      <c r="M321" s="7"/>
+    </row>
+    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>53</v>
+      </c>
+      <c r="B322" t="s">
+        <v>15</v>
+      </c>
       <c r="C322" s="11"/>
-      <c r="D322" s="11"/>
-      <c r="E322" s="11"/>
-    </row>
-    <row r="323" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D322" s="11">
+        <v>3150</v>
+      </c>
+      <c r="E322" s="11">
+        <v>3550</v>
+      </c>
+      <c r="F322" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G322" s="8">
+        <v>17</v>
+      </c>
+      <c r="H322" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J322" s="7"/>
+      <c r="K322" s="7"/>
+      <c r="L322" s="7"/>
+      <c r="M322" s="7"/>
+    </row>
+    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>136</v>
+      </c>
+      <c r="B323" t="s">
+        <v>15</v>
+      </c>
       <c r="C323" s="11"/>
-      <c r="D323" s="11"/>
-      <c r="E323" s="11"/>
-    </row>
-    <row r="324" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D323" s="11">
+        <v>3080</v>
+      </c>
+      <c r="E323" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G323" s="8">
+        <v>17</v>
+      </c>
+      <c r="H323" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J323" s="7"/>
+      <c r="K323" s="7"/>
+      <c r="L323" s="7"/>
+      <c r="M323" s="7"/>
+    </row>
+    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>32</v>
+      </c>
+      <c r="B324" t="s">
+        <v>15</v>
+      </c>
       <c r="C324" s="11"/>
-      <c r="D324" s="11"/>
-      <c r="E324" s="11"/>
-    </row>
-    <row r="325" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D324" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E324" s="11">
+        <v>3440</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G324" s="8">
+        <v>17</v>
+      </c>
+      <c r="H324" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J324" s="7"/>
+      <c r="K324" s="7"/>
+      <c r="L324" s="7"/>
+      <c r="M324" s="7"/>
+    </row>
+    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>137</v>
+      </c>
+      <c r="B325" t="s">
+        <v>15</v>
+      </c>
       <c r="C325" s="11"/>
-      <c r="D325" s="11"/>
-      <c r="E325" s="11"/>
-    </row>
-    <row r="326" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D325" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E325" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G325" s="8">
+        <v>17</v>
+      </c>
+      <c r="H325" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J325" s="7"/>
+      <c r="K325" s="7"/>
+      <c r="L325" s="7"/>
+      <c r="M325" s="7"/>
+    </row>
+    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>138</v>
+      </c>
+      <c r="B326" t="s">
+        <v>15</v>
+      </c>
       <c r="C326" s="11"/>
-      <c r="D326" s="11"/>
-      <c r="E326" s="11"/>
-    </row>
-    <row r="327" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D326" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E326" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G326" s="8">
+        <v>17</v>
+      </c>
+      <c r="H326" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J326" s="7"/>
+      <c r="K326" s="7"/>
+      <c r="L326" s="7"/>
+      <c r="M326" s="7"/>
+    </row>
+    <row r="327" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>54</v>
+      </c>
+      <c r="B327" t="s">
+        <v>15</v>
+      </c>
       <c r="C327" s="11"/>
-      <c r="D327" s="11"/>
-      <c r="E327" s="11"/>
-    </row>
-    <row r="328" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D327" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E327" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G327" s="8">
+        <v>17</v>
+      </c>
+      <c r="H327" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J327" s="7"/>
+      <c r="K327" s="7"/>
+      <c r="L327" s="7"/>
+      <c r="M327" s="7"/>
+    </row>
+    <row r="328" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>55</v>
+      </c>
+      <c r="B328" t="s">
+        <v>15</v>
+      </c>
       <c r="C328" s="11"/>
-      <c r="D328" s="11"/>
-      <c r="E328" s="11"/>
-    </row>
-    <row r="329" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D328" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E328" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F328" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G328" s="8">
+        <v>17</v>
+      </c>
+      <c r="H328" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J328" s="7"/>
+      <c r="K328" s="7"/>
+      <c r="L328" s="7"/>
+      <c r="M328" s="7"/>
+    </row>
+    <row r="329" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>56</v>
+      </c>
+      <c r="B329" t="s">
+        <v>15</v>
+      </c>
       <c r="C329" s="11"/>
-      <c r="D329" s="11"/>
-      <c r="E329" s="11"/>
-    </row>
-    <row r="330" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D329" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E329" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G329" s="8">
+        <v>17</v>
+      </c>
+      <c r="H329" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I329" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J329" s="7"/>
+      <c r="K329" s="7"/>
+      <c r="L329" s="7"/>
+      <c r="M329" s="7"/>
+    </row>
+    <row r="330" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>57</v>
+      </c>
+      <c r="B330" t="s">
+        <v>15</v>
+      </c>
       <c r="C330" s="11"/>
-      <c r="D330" s="11"/>
-      <c r="E330" s="11"/>
-    </row>
-    <row r="331" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D330" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E330" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G330" s="8">
+        <v>17</v>
+      </c>
+      <c r="H330" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I330" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J330" s="7"/>
+      <c r="K330" s="7"/>
+      <c r="L330" s="7"/>
+      <c r="M330" s="7"/>
+    </row>
+    <row r="331" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>139</v>
+      </c>
+      <c r="B331" t="s">
+        <v>15</v>
+      </c>
       <c r="C331" s="11"/>
-      <c r="D331" s="11"/>
-      <c r="E331" s="11"/>
-    </row>
-    <row r="332" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D331" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E331" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F331" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G331" s="8">
+        <v>17</v>
+      </c>
+      <c r="H331" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I331" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J331" s="7"/>
+      <c r="K331" s="7"/>
+      <c r="L331" s="7"/>
+      <c r="M331" s="7"/>
+    </row>
+    <row r="332" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>140</v>
+      </c>
+      <c r="B332" t="s">
+        <v>15</v>
+      </c>
       <c r="C332" s="11"/>
-      <c r="D332" s="11"/>
-      <c r="E332" s="11"/>
-    </row>
-    <row r="333" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D332" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E332" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G332" s="8">
+        <v>17</v>
+      </c>
+      <c r="H332" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I332" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J332" s="7"/>
+      <c r="K332" s="7"/>
+      <c r="L332" s="7"/>
+      <c r="M332" s="7"/>
+    </row>
+    <row r="333" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>33</v>
+      </c>
+      <c r="B333" t="s">
+        <v>15</v>
+      </c>
       <c r="C333" s="11"/>
-      <c r="D333" s="11"/>
-      <c r="E333" s="11"/>
-    </row>
-    <row r="334" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D333" s="11">
+        <v>3140</v>
+      </c>
+      <c r="E333" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F333" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G333" s="8">
+        <v>17</v>
+      </c>
+      <c r="H333" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I333" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J333" s="7"/>
+      <c r="K333" s="7"/>
+      <c r="L333" s="7"/>
+      <c r="M333" s="7"/>
+    </row>
+    <row r="334" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>34</v>
+      </c>
+      <c r="B334" t="s">
+        <v>15</v>
+      </c>
       <c r="C334" s="11"/>
-      <c r="D334" s="11"/>
-      <c r="E334" s="11"/>
-    </row>
-    <row r="335" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D334" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E334" s="11">
+        <v>3510</v>
+      </c>
+      <c r="F334" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G334" s="8">
+        <v>17</v>
+      </c>
+      <c r="H334" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I334" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J334" s="7"/>
+      <c r="K334" s="7"/>
+      <c r="L334" s="7"/>
+      <c r="M334" s="7"/>
+    </row>
+    <row r="335" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>58</v>
+      </c>
+      <c r="B335" t="s">
+        <v>15</v>
+      </c>
       <c r="C335" s="11"/>
-      <c r="D335" s="11"/>
-      <c r="E335" s="11"/>
-    </row>
-    <row r="336" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D335" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E335" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F335" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G335" s="8">
+        <v>17</v>
+      </c>
+      <c r="H335" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I335" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J335" s="7"/>
+      <c r="K335" s="7"/>
+      <c r="L335" s="7"/>
+      <c r="M335" s="7"/>
+    </row>
+    <row r="336" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>141</v>
+      </c>
+      <c r="B336" t="s">
+        <v>15</v>
+      </c>
       <c r="C336" s="11"/>
-      <c r="D336" s="11"/>
-      <c r="E336" s="11"/>
-    </row>
-    <row r="337" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D336" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E336" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G336" s="8">
+        <v>17</v>
+      </c>
+      <c r="H336" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I336" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J336" s="7"/>
+      <c r="K336" s="7"/>
+      <c r="L336" s="7"/>
+      <c r="M336" s="7"/>
+    </row>
+    <row r="337" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>35</v>
+      </c>
+      <c r="B337" t="s">
+        <v>15</v>
+      </c>
       <c r="C337" s="11"/>
-      <c r="D337" s="11"/>
-      <c r="E337" s="11"/>
-    </row>
-    <row r="338" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D337" s="11">
+        <v>3320</v>
+      </c>
+      <c r="E337" s="11">
+        <v>3930</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G337" s="8">
+        <v>17</v>
+      </c>
+      <c r="H337" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I337" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J337" s="7"/>
+      <c r="K337" s="7"/>
+      <c r="L337" s="7"/>
+      <c r="M337" s="7"/>
+    </row>
+    <row r="338" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>142</v>
+      </c>
+      <c r="B338" t="s">
+        <v>15</v>
+      </c>
       <c r="C338" s="11"/>
-      <c r="D338" s="11"/>
-      <c r="E338" s="11"/>
-    </row>
-    <row r="339" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D338" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E338" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G338" s="8">
+        <v>17</v>
+      </c>
+      <c r="H338" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J338" s="7"/>
+      <c r="K338" s="7"/>
+      <c r="L338" s="7"/>
+      <c r="M338" s="7"/>
+    </row>
+    <row r="339" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>143</v>
+      </c>
+      <c r="B339" t="s">
+        <v>15</v>
+      </c>
       <c r="C339" s="11"/>
-      <c r="D339" s="11"/>
-      <c r="E339" s="11"/>
-    </row>
-    <row r="340" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D339" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E339" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G339" s="8">
+        <v>17</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J339" s="7"/>
+      <c r="K339" s="7"/>
+      <c r="L339" s="7"/>
+      <c r="M339" s="7"/>
+    </row>
+    <row r="340" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>144</v>
+      </c>
+      <c r="B340" t="s">
+        <v>15</v>
+      </c>
       <c r="C340" s="11"/>
-      <c r="D340" s="11"/>
-      <c r="E340" s="11"/>
-    </row>
-    <row r="341" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D340" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E340" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G340" s="8">
+        <v>17</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J340" s="7"/>
+      <c r="K340" s="7"/>
+      <c r="L340" s="7"/>
+      <c r="M340" s="7"/>
+    </row>
+    <row r="341" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>145</v>
+      </c>
+      <c r="B341" t="s">
+        <v>15</v>
+      </c>
       <c r="C341" s="11"/>
-      <c r="D341" s="11"/>
-      <c r="E341" s="11"/>
-    </row>
-    <row r="342" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D341" s="11">
+        <v>3160</v>
+      </c>
+      <c r="E341" s="11">
+        <v>3470</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G341" s="8">
+        <v>17</v>
+      </c>
+      <c r="H341" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I341" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J341" s="7"/>
+      <c r="K341" s="7"/>
+      <c r="L341" s="7"/>
+      <c r="M341" s="7"/>
+    </row>
+    <row r="342" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>146</v>
+      </c>
+      <c r="B342" t="s">
+        <v>15</v>
+      </c>
       <c r="C342" s="11"/>
-      <c r="D342" s="11"/>
-      <c r="E342" s="11"/>
-    </row>
-    <row r="343" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D342" s="11">
+        <v>3160</v>
+      </c>
+      <c r="E342" s="11">
+        <v>3470</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G342" s="8">
+        <v>17</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J342" s="7"/>
+      <c r="K342" s="7"/>
+      <c r="L342" s="7"/>
+      <c r="M342" s="7"/>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>75</v>
+      </c>
+      <c r="B343" t="s">
+        <v>15</v>
+      </c>
       <c r="C343" s="11"/>
-      <c r="D343" s="11"/>
-      <c r="E343" s="11"/>
-    </row>
-    <row r="344" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D343" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E343" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G343" s="8">
+        <v>18</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>76</v>
+      </c>
+      <c r="B344" t="s">
+        <v>15</v>
+      </c>
       <c r="C344" s="11"/>
-      <c r="D344" s="11"/>
-      <c r="E344" s="11"/>
-    </row>
-    <row r="345" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D344" s="11">
+        <v>3730</v>
+      </c>
+      <c r="E344" s="11">
+        <v>3730</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G344" s="8">
+        <v>18</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>77</v>
+      </c>
+      <c r="B345" t="s">
+        <v>15</v>
+      </c>
       <c r="C345" s="11"/>
-      <c r="D345" s="11"/>
-      <c r="E345" s="11"/>
-    </row>
-    <row r="346" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D345" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E345" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G345" s="8">
+        <v>18</v>
+      </c>
+      <c r="H345" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I345" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>78</v>
+      </c>
+      <c r="B346" t="s">
+        <v>15</v>
+      </c>
       <c r="C346" s="11"/>
-      <c r="D346" s="11"/>
-      <c r="E346" s="11"/>
-    </row>
-    <row r="347" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D346" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E346" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G346" s="8">
+        <v>18</v>
+      </c>
+      <c r="H346" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>79</v>
+      </c>
+      <c r="B347" t="s">
+        <v>15</v>
+      </c>
       <c r="C347" s="11"/>
-      <c r="D347" s="11"/>
-      <c r="E347" s="11"/>
-    </row>
-    <row r="348" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D347" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E347" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G347" s="8">
+        <v>18</v>
+      </c>
+      <c r="H347" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I347" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>80</v>
+      </c>
+      <c r="B348" t="s">
+        <v>15</v>
+      </c>
       <c r="C348" s="11"/>
-      <c r="D348" s="11"/>
-      <c r="E348" s="11"/>
-    </row>
-    <row r="349" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D348" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E348" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G348" s="8">
+        <v>18</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>81</v>
+      </c>
+      <c r="B349" t="s">
+        <v>15</v>
+      </c>
       <c r="C349" s="11"/>
-      <c r="D349" s="11"/>
-      <c r="E349" s="11"/>
-    </row>
-    <row r="350" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D349" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E349" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F349" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G349" s="8">
+        <v>18</v>
+      </c>
+      <c r="H349" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I349" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>82</v>
+      </c>
+      <c r="B350" t="s">
+        <v>15</v>
+      </c>
       <c r="C350" s="11"/>
-      <c r="D350" s="11"/>
-      <c r="E350" s="11"/>
-    </row>
-    <row r="351" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D350" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E350" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F350" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G350" s="8">
+        <v>18</v>
+      </c>
+      <c r="H350" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>83</v>
+      </c>
+      <c r="B351" t="s">
+        <v>15</v>
+      </c>
       <c r="C351" s="11"/>
-      <c r="D351" s="11"/>
-      <c r="E351" s="11"/>
-    </row>
-    <row r="352" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D351" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E351" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G351" s="8">
+        <v>18</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>84</v>
+      </c>
+      <c r="B352" t="s">
+        <v>15</v>
+      </c>
       <c r="C352" s="11"/>
-      <c r="D352" s="11"/>
-      <c r="E352" s="11"/>
-    </row>
-    <row r="353" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D352" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E352" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G352" s="8">
+        <v>18</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>85</v>
+      </c>
+      <c r="B353" t="s">
+        <v>15</v>
+      </c>
       <c r="C353" s="11"/>
-      <c r="D353" s="11"/>
-      <c r="E353" s="11"/>
-    </row>
-    <row r="354" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D353" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E353" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G353" s="8">
+        <v>18</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I353" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>86</v>
+      </c>
+      <c r="B354" t="s">
+        <v>15</v>
+      </c>
       <c r="C354" s="11"/>
-      <c r="D354" s="11"/>
-      <c r="E354" s="11"/>
-    </row>
-    <row r="355" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D354" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E354" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G354" s="8">
+        <v>18</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>153</v>
+      </c>
+      <c r="B355" t="s">
+        <v>15</v>
+      </c>
       <c r="C355" s="11"/>
-      <c r="D355" s="11"/>
-      <c r="E355" s="11"/>
-    </row>
-    <row r="356" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D355" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E355" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F355" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G355" s="8">
+        <v>18</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I355" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>115</v>
+      </c>
+      <c r="B356" t="s">
+        <v>15</v>
+      </c>
       <c r="C356" s="11"/>
-      <c r="D356" s="11"/>
-      <c r="E356" s="11"/>
-    </row>
-    <row r="357" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D356" s="11">
+        <v>3160</v>
+      </c>
+      <c r="E356" s="11">
+        <v>3160</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G356" s="8">
+        <v>18</v>
+      </c>
+      <c r="H356" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>88</v>
+      </c>
+      <c r="B357" t="s">
+        <v>15</v>
+      </c>
       <c r="C357" s="11"/>
-      <c r="D357" s="11"/>
-      <c r="E357" s="11"/>
-    </row>
-    <row r="358" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D357" s="11">
+        <v>3260</v>
+      </c>
+      <c r="E357" s="11">
+        <v>3260</v>
+      </c>
+      <c r="F357" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G357" s="8">
+        <v>18</v>
+      </c>
+      <c r="H357" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I357" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>90</v>
+      </c>
+      <c r="B358" t="s">
+        <v>15</v>
+      </c>
       <c r="C358" s="11"/>
-      <c r="D358" s="11"/>
-      <c r="E358" s="11"/>
-    </row>
-    <row r="359" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D358" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E358" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G358" s="8">
+        <v>18</v>
+      </c>
+      <c r="H358" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>154</v>
+      </c>
+      <c r="B359" t="s">
+        <v>15</v>
+      </c>
       <c r="C359" s="11"/>
-      <c r="D359" s="11"/>
-      <c r="E359" s="11"/>
-    </row>
-    <row r="360" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D359" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E359" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G359" s="8">
+        <v>18</v>
+      </c>
+      <c r="H359" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I359" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>92</v>
+      </c>
+      <c r="B360" t="s">
+        <v>15</v>
+      </c>
       <c r="C360" s="11"/>
-      <c r="D360" s="11"/>
-      <c r="E360" s="11"/>
-    </row>
-    <row r="361" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D360" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E360" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G360" s="8">
+        <v>18</v>
+      </c>
+      <c r="H360" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>155</v>
+      </c>
+      <c r="B361" t="s">
+        <v>15</v>
+      </c>
       <c r="C361" s="11"/>
-      <c r="D361" s="11"/>
-      <c r="E361" s="11"/>
-    </row>
-    <row r="362" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D361" s="11">
+        <v>3790</v>
+      </c>
+      <c r="E361" s="11">
+        <v>3790</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G361" s="8">
+        <v>18</v>
+      </c>
+      <c r="H361" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I361" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>93</v>
+      </c>
+      <c r="B362" t="s">
+        <v>15</v>
+      </c>
       <c r="C362" s="11"/>
-      <c r="D362" s="11"/>
-      <c r="E362" s="11"/>
-    </row>
-    <row r="363" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D362" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E362" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G362" s="8">
+        <v>18</v>
+      </c>
+      <c r="H362" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>94</v>
+      </c>
+      <c r="B363" t="s">
+        <v>15</v>
+      </c>
       <c r="C363" s="11"/>
-      <c r="D363" s="11"/>
-      <c r="E363" s="11"/>
-    </row>
-    <row r="364" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D363" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E363" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G363" s="8">
+        <v>18</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I363" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>95</v>
+      </c>
+      <c r="B364" t="s">
+        <v>15</v>
+      </c>
       <c r="C364" s="11"/>
-      <c r="D364" s="11"/>
-      <c r="E364" s="11"/>
-    </row>
-    <row r="365" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D364" s="11">
+        <v>3100</v>
+      </c>
+      <c r="E364" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G364" s="8">
+        <v>18</v>
+      </c>
+      <c r="H364" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>96</v>
+      </c>
+      <c r="B365" t="s">
+        <v>15</v>
+      </c>
       <c r="C365" s="11"/>
-      <c r="D365" s="11"/>
-      <c r="E365" s="11"/>
-    </row>
-    <row r="366" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D365" s="11">
+        <v>3230</v>
+      </c>
+      <c r="E365" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G365" s="8">
+        <v>18</v>
+      </c>
+      <c r="H365" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I365" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>97</v>
+      </c>
+      <c r="B366" t="s">
+        <v>15</v>
+      </c>
       <c r="C366" s="11"/>
-      <c r="D366" s="11"/>
-      <c r="E366" s="11"/>
-    </row>
-    <row r="367" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D366" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E366" s="11">
+        <v>3000</v>
+      </c>
+      <c r="F366" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G366" s="8">
+        <v>18</v>
+      </c>
+      <c r="H366" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>98</v>
+      </c>
+      <c r="B367" t="s">
+        <v>15</v>
+      </c>
       <c r="C367" s="11"/>
-      <c r="D367" s="11"/>
-      <c r="E367" s="11"/>
-    </row>
-    <row r="368" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D367" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E367" s="11">
+        <v>3000</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G367" s="8">
+        <v>18</v>
+      </c>
+      <c r="H367" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I367" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>99</v>
+      </c>
+      <c r="B368" t="s">
+        <v>15</v>
+      </c>
       <c r="C368" s="11"/>
-      <c r="D368" s="11"/>
-      <c r="E368" s="11"/>
-    </row>
-    <row r="369" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D368" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E368" s="11">
+        <v>3000</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G368" s="8">
+        <v>18</v>
+      </c>
+      <c r="H368" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I368" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>100</v>
+      </c>
+      <c r="B369" t="s">
+        <v>15</v>
+      </c>
       <c r="C369" s="11"/>
-      <c r="D369" s="11"/>
-      <c r="E369" s="11"/>
-    </row>
-    <row r="370" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D369" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E369" s="11">
+        <v>3000</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G369" s="8">
+        <v>18</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I369" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>101</v>
+      </c>
+      <c r="B370" t="s">
+        <v>15</v>
+      </c>
       <c r="C370" s="11"/>
-      <c r="D370" s="11"/>
-      <c r="E370" s="11"/>
-    </row>
-    <row r="371" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D370" s="11">
+        <v>3210</v>
+      </c>
+      <c r="E370" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F370" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G370" s="8">
+        <v>18</v>
+      </c>
+      <c r="H370" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I370" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>102</v>
+      </c>
+      <c r="B371" t="s">
+        <v>15</v>
+      </c>
       <c r="C371" s="11"/>
-      <c r="D371" s="11"/>
-      <c r="E371" s="11"/>
-    </row>
-    <row r="372" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D371" s="11">
+        <v>3210</v>
+      </c>
+      <c r="E371" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G371" s="8">
+        <v>18</v>
+      </c>
+      <c r="H371" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I371" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>103</v>
+      </c>
+      <c r="B372" t="s">
+        <v>15</v>
+      </c>
       <c r="C372" s="11"/>
-      <c r="D372" s="11"/>
-      <c r="E372" s="11"/>
-    </row>
-    <row r="373" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D372" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E372" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G372" s="8">
+        <v>18</v>
+      </c>
+      <c r="H372" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I372" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>104</v>
+      </c>
+      <c r="B373" t="s">
+        <v>15</v>
+      </c>
       <c r="C373" s="11"/>
-      <c r="D373" s="11"/>
-      <c r="E373" s="11"/>
-    </row>
-    <row r="374" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D373" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E373" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G373" s="8">
+        <v>18</v>
+      </c>
+      <c r="H373" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I373" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>105</v>
+      </c>
+      <c r="B374" t="s">
+        <v>15</v>
+      </c>
       <c r="C374" s="11"/>
-      <c r="D374" s="11"/>
-      <c r="E374" s="11"/>
-    </row>
-    <row r="375" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D374" s="11">
+        <v>3730</v>
+      </c>
+      <c r="E374" s="11">
+        <v>3730</v>
+      </c>
+      <c r="F374" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G374" s="8">
+        <v>18</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I374" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>106</v>
+      </c>
+      <c r="B375" t="s">
+        <v>15</v>
+      </c>
       <c r="C375" s="11"/>
-      <c r="D375" s="11"/>
-      <c r="E375" s="11"/>
-    </row>
-    <row r="376" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D375" s="11">
+        <v>3310</v>
+      </c>
+      <c r="E375" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F375" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G375" s="8">
+        <v>18</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I375" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>107</v>
+      </c>
+      <c r="B376" t="s">
+        <v>15</v>
+      </c>
       <c r="C376" s="11"/>
-      <c r="D376" s="11"/>
-      <c r="E376" s="11"/>
-    </row>
-    <row r="377" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D376" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E376" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F376" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G376" s="8">
+        <v>18</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I376" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>108</v>
+      </c>
+      <c r="B377" t="s">
+        <v>15</v>
+      </c>
       <c r="C377" s="11"/>
-      <c r="D377" s="11"/>
-      <c r="E377" s="11"/>
-    </row>
-    <row r="378" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D377" s="11">
+        <v>3420</v>
+      </c>
+      <c r="E377" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F377" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G377" s="8">
+        <v>18</v>
+      </c>
+      <c r="H377" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I377" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>109</v>
+      </c>
+      <c r="B378" t="s">
+        <v>15</v>
+      </c>
       <c r="C378" s="11"/>
-      <c r="D378" s="11"/>
-      <c r="E378" s="11"/>
-    </row>
-    <row r="379" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D378" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E378" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F378" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G378" s="8">
+        <v>18</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I378" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>110</v>
+      </c>
+      <c r="B379" t="s">
+        <v>15</v>
+      </c>
       <c r="C379" s="11"/>
-      <c r="D379" s="11"/>
-      <c r="E379" s="11"/>
-    </row>
-    <row r="380" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D379" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E379" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F379" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G379" s="8">
+        <v>18</v>
+      </c>
+      <c r="H379" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I379" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>110</v>
+      </c>
+      <c r="B380" t="s">
+        <v>15</v>
+      </c>
       <c r="C380" s="11"/>
-      <c r="D380" s="11"/>
-      <c r="E380" s="11"/>
-    </row>
-    <row r="381" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D380" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E380" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F380" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G380" s="8">
+        <v>18</v>
+      </c>
+      <c r="H380" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I380" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>156</v>
+      </c>
+      <c r="B381" t="s">
+        <v>15</v>
+      </c>
       <c r="C381" s="11"/>
-      <c r="D381" s="11"/>
-      <c r="E381" s="11"/>
-    </row>
-    <row r="382" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D381" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E381" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G381" s="8">
+        <v>18</v>
+      </c>
+      <c r="H381" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I381" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>103</v>
+      </c>
+      <c r="B382" t="s">
+        <v>15</v>
+      </c>
       <c r="C382" s="11"/>
-      <c r="D382" s="11"/>
-      <c r="E382" s="11"/>
-    </row>
-    <row r="383" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D382" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E382" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F382" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G382" s="8">
+        <v>18</v>
+      </c>
+      <c r="H382" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I382" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>157</v>
+      </c>
+      <c r="B383" t="s">
+        <v>15</v>
+      </c>
       <c r="C383" s="11"/>
-      <c r="D383" s="11"/>
-      <c r="E383" s="11"/>
-    </row>
-    <row r="384" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D383" s="11">
+        <v>3050</v>
+      </c>
+      <c r="E383" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F383" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="G383" s="8">
+        <v>18</v>
+      </c>
+      <c r="H383" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I383" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C384" s="11"/>
       <c r="D384" s="11"/>
       <c r="E384" s="11"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F422D37-6A6E-4179-9A27-0F096C826513}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29DC7938-7CEC-44B0-9A29-2DA0C14B7349}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10801,7 +10801,7 @@
       </c>
       <c r="C343" s="11"/>
       <c r="D343" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E343" s="11">
         <v>3310</v>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="C344" s="11"/>
       <c r="D344" s="11">
-        <v>3730</v>
+        <v>3260</v>
       </c>
       <c r="E344" s="11">
         <v>3730</v>
@@ -10855,7 +10855,7 @@
       </c>
       <c r="C345" s="11"/>
       <c r="D345" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E345" s="11">
         <v>3310</v>
@@ -10882,7 +10882,7 @@
       </c>
       <c r="C346" s="11"/>
       <c r="D346" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E346" s="11">
         <v>3310</v>
@@ -10909,7 +10909,7 @@
       </c>
       <c r="C347" s="11"/>
       <c r="D347" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E347" s="11">
         <v>3050</v>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="C348" s="11"/>
       <c r="D348" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E348" s="11">
         <v>3050</v>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="C349" s="11"/>
       <c r="D349" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E349" s="11">
         <v>3050</v>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="C350" s="11"/>
       <c r="D350" s="11">
-        <v>3100</v>
+        <v>2950</v>
       </c>
       <c r="E350" s="11">
         <v>3100</v>
@@ -11017,7 +11017,7 @@
       </c>
       <c r="C351" s="11"/>
       <c r="D351" s="11">
-        <v>3100</v>
+        <v>2950</v>
       </c>
       <c r="E351" s="11">
         <v>3100</v>
@@ -11044,7 +11044,7 @@
       </c>
       <c r="C352" s="11"/>
       <c r="D352" s="11">
-        <v>3100</v>
+        <v>2950</v>
       </c>
       <c r="E352" s="11">
         <v>3100</v>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C353" s="11"/>
       <c r="D353" s="11">
-        <v>3100</v>
+        <v>2950</v>
       </c>
       <c r="E353" s="11">
         <v>3100</v>
@@ -11098,7 +11098,7 @@
       </c>
       <c r="C354" s="11"/>
       <c r="D354" s="11">
-        <v>3100</v>
+        <v>2950</v>
       </c>
       <c r="E354" s="11">
         <v>3100</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="C355" s="11"/>
       <c r="D355" s="11">
-        <v>3420</v>
+        <v>3160</v>
       </c>
       <c r="E355" s="11">
         <v>3420</v>
@@ -11152,7 +11152,7 @@
       </c>
       <c r="C356" s="11"/>
       <c r="D356" s="11">
-        <v>3160</v>
+        <v>2840</v>
       </c>
       <c r="E356" s="11">
         <v>3160</v>
@@ -11179,7 +11179,7 @@
       </c>
       <c r="C357" s="11"/>
       <c r="D357" s="11">
-        <v>3260</v>
+        <v>2950</v>
       </c>
       <c r="E357" s="11">
         <v>3260</v>
@@ -11206,7 +11206,7 @@
       </c>
       <c r="C358" s="11"/>
       <c r="D358" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E358" s="11">
         <v>3310</v>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="C359" s="11"/>
       <c r="D359" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E359" s="11">
         <v>3310</v>
@@ -11260,7 +11260,7 @@
       </c>
       <c r="C360" s="11"/>
       <c r="D360" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E360" s="11">
         <v>3310</v>
@@ -11287,7 +11287,7 @@
       </c>
       <c r="C361" s="11"/>
       <c r="D361" s="11">
-        <v>3790</v>
+        <v>3310</v>
       </c>
       <c r="E361" s="11">
         <v>3790</v>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C362" s="11"/>
       <c r="D362" s="11">
-        <v>3100</v>
+        <v>3050</v>
       </c>
       <c r="E362" s="11">
         <v>3100</v>
@@ -11341,7 +11341,7 @@
       </c>
       <c r="C363" s="11"/>
       <c r="D363" s="11">
-        <v>3100</v>
+        <v>2840</v>
       </c>
       <c r="E363" s="11">
         <v>3100</v>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="C364" s="11"/>
       <c r="D364" s="11">
-        <v>3100</v>
+        <v>2840</v>
       </c>
       <c r="E364" s="11">
         <v>3100</v>
@@ -11395,7 +11395,7 @@
       </c>
       <c r="C365" s="11"/>
       <c r="D365" s="11">
-        <v>3230</v>
+        <v>2970</v>
       </c>
       <c r="E365" s="11">
         <v>3230</v>
@@ -11422,7 +11422,7 @@
       </c>
       <c r="C366" s="11"/>
       <c r="D366" s="11">
-        <v>3000</v>
+        <v>2840</v>
       </c>
       <c r="E366" s="11">
         <v>3000</v>
@@ -11449,7 +11449,7 @@
       </c>
       <c r="C367" s="11"/>
       <c r="D367" s="11">
-        <v>3000</v>
+        <v>2840</v>
       </c>
       <c r="E367" s="11">
         <v>3000</v>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="C368" s="11"/>
       <c r="D368" s="11">
-        <v>3000</v>
+        <v>2840</v>
       </c>
       <c r="E368" s="11">
         <v>3000</v>
@@ -11503,7 +11503,7 @@
       </c>
       <c r="C369" s="11"/>
       <c r="D369" s="11">
-        <v>3000</v>
+        <v>2840</v>
       </c>
       <c r="E369" s="11">
         <v>3000</v>
@@ -11530,7 +11530,7 @@
       </c>
       <c r="C370" s="11"/>
       <c r="D370" s="11">
-        <v>3210</v>
+        <v>2950</v>
       </c>
       <c r="E370" s="11">
         <v>3210</v>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C371" s="11"/>
       <c r="D371" s="11">
-        <v>3210</v>
+        <v>2950</v>
       </c>
       <c r="E371" s="11">
         <v>3210</v>
@@ -11584,7 +11584,7 @@
       </c>
       <c r="C372" s="11"/>
       <c r="D372" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E372" s="11">
         <v>3050</v>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="C373" s="11"/>
       <c r="D373" s="11">
-        <v>2790</v>
+        <v>2530</v>
       </c>
       <c r="E373" s="11">
         <v>2790</v>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="C374" s="11"/>
       <c r="D374" s="11">
-        <v>3730</v>
+        <v>3470</v>
       </c>
       <c r="E374" s="11">
         <v>3730</v>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="C375" s="11"/>
       <c r="D375" s="11">
-        <v>3310</v>
+        <v>3050</v>
       </c>
       <c r="E375" s="11">
         <v>3310</v>
@@ -11692,7 +11692,7 @@
       </c>
       <c r="C376" s="11"/>
       <c r="D376" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E376" s="11">
         <v>3050</v>
@@ -11719,7 +11719,7 @@
       </c>
       <c r="C377" s="11"/>
       <c r="D377" s="11">
-        <v>3420</v>
+        <v>3160</v>
       </c>
       <c r="E377" s="11">
         <v>3420</v>
@@ -11746,7 +11746,7 @@
       </c>
       <c r="C378" s="11"/>
       <c r="D378" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E378" s="11">
         <v>3050</v>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C379" s="11"/>
       <c r="D379" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E379" s="11">
         <v>3050</v>
@@ -11800,7 +11800,7 @@
       </c>
       <c r="C380" s="11"/>
       <c r="D380" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E380" s="11">
         <v>3050</v>
@@ -11827,7 +11827,7 @@
       </c>
       <c r="C381" s="11"/>
       <c r="D381" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E381" s="11">
         <v>3050</v>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="C382" s="11"/>
       <c r="D382" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E382" s="11">
         <v>3050</v>
@@ -11881,7 +11881,7 @@
       </c>
       <c r="C383" s="11"/>
       <c r="D383" s="11">
-        <v>3050</v>
+        <v>2790</v>
       </c>
       <c r="E383" s="11">
         <v>3050</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19AEC0C1-696C-486D-90E7-52738D7F75D3}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{243EC0F9-4332-45F5-97A7-319609B854C5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$252</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$442</definedName>
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1348" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="152">
   <si>
     <t>POD</t>
   </si>
@@ -493,6 +493,12 @@
   </si>
   <si>
     <t>OOCL</t>
+  </si>
+  <si>
+    <t>8 al 14 de abril</t>
+  </si>
+  <si>
+    <t>ONE</t>
   </si>
 </sst>
 </file>
@@ -998,7 +1004,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:M1370"/>
+  <dimension ref="A1:M1327"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1471,7 +1477,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1528,12 +1534,8 @@
       <c r="I18" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>20</v>
       </c>
@@ -1561,12 +1563,8 @@
       <c r="I19" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>19</v>
       </c>
@@ -1594,12 +1592,8 @@
       <c r="I20" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>16</v>
       </c>
@@ -1627,12 +1621,8 @@
       <c r="I21" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>13</v>
       </c>
@@ -1660,12 +1650,8 @@
       <c r="I22" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
         <v>5</v>
       </c>
@@ -1693,12 +1679,8 @@
       <c r="I23" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
         <v>4</v>
       </c>
@@ -1726,12 +1708,8 @@
       <c r="I24" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
         <v>120</v>
       </c>
@@ -1759,12 +1737,8 @@
       <c r="I25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
         <v>24</v>
       </c>
@@ -1790,12 +1764,8 @@
       <c r="I26" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
         <v>25</v>
       </c>
@@ -1823,12 +1793,8 @@
       <c r="I27" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>26</v>
       </c>
@@ -1856,12 +1822,8 @@
       <c r="I28" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>27</v>
       </c>
@@ -1889,12 +1851,8 @@
       <c r="I29" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
         <v>48</v>
       </c>
@@ -1922,12 +1880,8 @@
       <c r="I30" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J30" s="7"/>
-      <c r="K30" s="7"/>
-      <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>49</v>
       </c>
@@ -1955,12 +1909,8 @@
       <c r="I31" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J31" s="7"/>
-      <c r="K31" s="7"/>
-      <c r="L31" s="7"/>
-      <c r="M31" s="7"/>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>28</v>
       </c>
@@ -1988,12 +1938,8 @@
       <c r="I32" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J32" s="7"/>
-      <c r="K32" s="7"/>
-      <c r="L32" s="7"/>
-      <c r="M32" s="7"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>50</v>
       </c>
@@ -2021,12 +1967,8 @@
       <c r="I33" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J33" s="7"/>
-      <c r="K33" s="7"/>
-      <c r="L33" s="7"/>
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
         <v>51</v>
       </c>
@@ -2054,12 +1996,8 @@
       <c r="I34" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J34" s="7"/>
-      <c r="K34" s="7"/>
-      <c r="L34" s="7"/>
-      <c r="M34" s="7"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
         <v>52</v>
       </c>
@@ -2087,12 +2025,8 @@
       <c r="I35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J35" s="7"/>
-      <c r="K35" s="7"/>
-      <c r="L35" s="7"/>
-      <c r="M35" s="7"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="7" t="s">
         <v>29</v>
       </c>
@@ -2118,12 +2052,8 @@
       <c r="I36" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
         <v>30</v>
       </c>
@@ -2149,12 +2079,8 @@
       <c r="I37" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J37" s="7"/>
-      <c r="K37" s="7"/>
-      <c r="L37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="s">
         <v>121</v>
       </c>
@@ -2180,12 +2106,8 @@
       <c r="I38" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J38" s="7"/>
-      <c r="K38" s="7"/>
-      <c r="L38" s="7"/>
-      <c r="M38" s="7"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
         <v>122</v>
       </c>
@@ -2211,12 +2133,8 @@
       <c r="I39" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
-      <c r="M39" s="7"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="7" t="s">
         <v>123</v>
       </c>
@@ -2242,12 +2160,8 @@
       <c r="I40" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J40" s="7"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="7"/>
-      <c r="M40" s="7"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
         <v>31</v>
       </c>
@@ -2273,12 +2187,8 @@
       <c r="I41" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
-      <c r="M41" s="7"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="7" t="s">
         <v>124</v>
       </c>
@@ -2304,12 +2214,8 @@
       <c r="I42" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
-      <c r="M42" s="7"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
         <v>53</v>
       </c>
@@ -2335,12 +2241,8 @@
       <c r="I43" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J43" s="7"/>
-      <c r="K43" s="7"/>
-      <c r="L43" s="7"/>
-      <c r="M43" s="7"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="7" t="s">
         <v>125</v>
       </c>
@@ -2366,12 +2268,8 @@
       <c r="I44" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J44" s="7"/>
-      <c r="K44" s="7"/>
-      <c r="L44" s="7"/>
-      <c r="M44" s="7"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
         <v>32</v>
       </c>
@@ -2397,12 +2295,8 @@
       <c r="I45" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
         <v>126</v>
       </c>
@@ -2428,12 +2322,8 @@
       <c r="I46" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
         <v>127</v>
       </c>
@@ -2459,12 +2349,8 @@
       <c r="I47" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="7" t="s">
         <v>54</v>
       </c>
@@ -2490,10 +2376,6 @@
       <c r="I48" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
@@ -2521,10 +2403,6 @@
       <c r="I49" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
@@ -2552,10 +2430,6 @@
       <c r="I50" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
@@ -2583,10 +2457,6 @@
       <c r="I51" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
@@ -2614,10 +2484,6 @@
       <c r="I52" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
@@ -2645,10 +2511,6 @@
       <c r="I53" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J53" s="7"/>
-      <c r="K53" s="7"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
@@ -2676,10 +2538,6 @@
       <c r="I54" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J54" s="7"/>
-      <c r="K54" s="7"/>
-      <c r="L54" s="7"/>
-      <c r="M54" s="7"/>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
@@ -2707,10 +2565,6 @@
       <c r="I55" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J55" s="7"/>
-      <c r="K55" s="7"/>
-      <c r="L55" s="7"/>
-      <c r="M55" s="7"/>
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="7" t="s">
@@ -2738,10 +2592,6 @@
       <c r="I56" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J56" s="7"/>
-      <c r="K56" s="7"/>
-      <c r="L56" s="7"/>
-      <c r="M56" s="7"/>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
@@ -2769,10 +2619,6 @@
       <c r="I57" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J57" s="7"/>
-      <c r="K57" s="7"/>
-      <c r="L57" s="7"/>
-      <c r="M57" s="7"/>
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="7" t="s">
@@ -2800,10 +2646,6 @@
       <c r="I58" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J58" s="7"/>
-      <c r="K58" s="7"/>
-      <c r="L58" s="7"/>
-      <c r="M58" s="7"/>
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
@@ -2831,10 +2673,6 @@
       <c r="I59" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J59" s="7"/>
-      <c r="K59" s="7"/>
-      <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="7" t="s">
@@ -2862,10 +2700,6 @@
       <c r="I60" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
-      <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
@@ -2893,10 +2727,6 @@
       <c r="I61" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="7"/>
-      <c r="K61" s="7"/>
-      <c r="L61" s="7"/>
-      <c r="M61" s="7"/>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
@@ -2924,10 +2754,6 @@
       <c r="I62" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J62" s="7"/>
-      <c r="K62" s="7"/>
-      <c r="L62" s="7"/>
-      <c r="M62" s="7"/>
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
@@ -2955,10 +2781,6 @@
       <c r="I63" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="J63" s="7"/>
-      <c r="K63" s="7"/>
-      <c r="L63" s="7"/>
-      <c r="M63" s="7"/>
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
@@ -2977,8 +2799,8 @@
       <c r="F64" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G64" s="8" t="s">
-        <v>137</v>
+      <c r="G64" s="8">
+        <v>17</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>138</v>
@@ -3008,8 +2830,8 @@
       <c r="F65" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G65" s="8" t="s">
-        <v>137</v>
+      <c r="G65" s="8">
+        <v>17</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>138</v>
@@ -3039,8 +2861,8 @@
       <c r="F66" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G66" s="8" t="s">
-        <v>137</v>
+      <c r="G66" s="8">
+        <v>17</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>138</v>
@@ -3070,8 +2892,8 @@
       <c r="F67" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G67" s="8" t="s">
-        <v>137</v>
+      <c r="G67" s="8">
+        <v>17</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>138</v>
@@ -3101,8 +2923,8 @@
       <c r="F68" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G68" s="8" t="s">
-        <v>137</v>
+      <c r="G68" s="8">
+        <v>17</v>
       </c>
       <c r="H68" s="7" t="s">
         <v>138</v>
@@ -3132,8 +2954,8 @@
       <c r="F69" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G69" s="8" t="s">
-        <v>137</v>
+      <c r="G69" s="8">
+        <v>17</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>138</v>
@@ -3163,8 +2985,8 @@
       <c r="F70" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G70" s="8" t="s">
-        <v>137</v>
+      <c r="G70" s="8">
+        <v>17</v>
       </c>
       <c r="H70" s="7" t="s">
         <v>138</v>
@@ -8260,981 +8082,5182 @@
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C253" s="11"/>
-      <c r="D253" s="11"/>
-      <c r="E253" s="11"/>
+      <c r="A253" t="s">
+        <v>21</v>
+      </c>
+      <c r="B253" t="s">
+        <v>15</v>
+      </c>
+      <c r="C253">
+        <v>2620</v>
+      </c>
+      <c r="D253">
+        <v>2880</v>
+      </c>
+      <c r="E253">
+        <v>3090</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H253" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I253" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C254" s="11"/>
-      <c r="D254" s="11"/>
-      <c r="E254" s="11"/>
+      <c r="A254" t="s">
+        <v>20</v>
+      </c>
+      <c r="B254" t="s">
+        <v>15</v>
+      </c>
+      <c r="C254">
+        <v>2620</v>
+      </c>
+      <c r="D254">
+        <v>2880</v>
+      </c>
+      <c r="E254">
+        <v>3090</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H254" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C255" s="11"/>
-      <c r="D255" s="11"/>
-      <c r="E255" s="11"/>
+      <c r="A255" t="s">
+        <v>19</v>
+      </c>
+      <c r="B255" t="s">
+        <v>15</v>
+      </c>
+      <c r="C255">
+        <v>2620</v>
+      </c>
+      <c r="D255">
+        <v>2880</v>
+      </c>
+      <c r="E255">
+        <v>3090</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H255" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I255" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C256" s="11"/>
-      <c r="D256" s="11"/>
-      <c r="E256" s="11"/>
-    </row>
-    <row r="257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C257" s="11"/>
-      <c r="D257" s="11"/>
-      <c r="E257" s="11"/>
-    </row>
-    <row r="258" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C258" s="11"/>
-      <c r="D258" s="11"/>
-      <c r="E258" s="11"/>
-    </row>
-    <row r="259" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C259" s="11"/>
-      <c r="D259" s="11"/>
-      <c r="E259" s="11"/>
-    </row>
-    <row r="260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C260" s="11"/>
-      <c r="D260" s="11"/>
-      <c r="E260" s="11"/>
-    </row>
-    <row r="261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C261" s="11"/>
-      <c r="D261" s="11"/>
-      <c r="E261" s="11"/>
-    </row>
-    <row r="262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C262" s="11"/>
-      <c r="D262" s="11"/>
-      <c r="E262" s="11"/>
-    </row>
-    <row r="263" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C263" s="11"/>
-      <c r="D263" s="11"/>
-      <c r="E263" s="11"/>
-    </row>
-    <row r="264" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C264" s="11"/>
-      <c r="D264" s="11"/>
-      <c r="E264" s="11"/>
-    </row>
-    <row r="265" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C265" s="11"/>
-      <c r="D265" s="11"/>
-      <c r="E265" s="11"/>
-    </row>
-    <row r="266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C266" s="11"/>
-      <c r="D266" s="11"/>
-      <c r="E266" s="11"/>
-    </row>
-    <row r="267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C267" s="11"/>
-      <c r="D267" s="11"/>
-      <c r="E267" s="11"/>
-    </row>
-    <row r="268" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C268" s="11"/>
-      <c r="D268" s="11"/>
-      <c r="E268" s="11"/>
-    </row>
-    <row r="269" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C269" s="11"/>
-      <c r="D269" s="11"/>
-      <c r="E269" s="11"/>
-    </row>
-    <row r="270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C270" s="11"/>
-      <c r="D270" s="11"/>
-      <c r="E270" s="11"/>
-    </row>
-    <row r="271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C271" s="11"/>
-      <c r="D271" s="11"/>
-      <c r="E271" s="11"/>
-    </row>
-    <row r="272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C272" s="11"/>
-      <c r="D272" s="11"/>
-      <c r="E272" s="11"/>
-    </row>
-    <row r="273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C273" s="11"/>
-      <c r="D273" s="11"/>
-      <c r="E273" s="11"/>
-    </row>
-    <row r="274" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C274" s="11"/>
-      <c r="D274" s="11"/>
-      <c r="E274" s="11"/>
-    </row>
-    <row r="275" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C275" s="11"/>
-      <c r="D275" s="11"/>
-      <c r="E275" s="11"/>
-    </row>
-    <row r="276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C276" s="11"/>
-      <c r="D276" s="11"/>
-      <c r="E276" s="11"/>
-    </row>
-    <row r="277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C277" s="11"/>
-      <c r="D277" s="11"/>
-      <c r="E277" s="11"/>
-    </row>
-    <row r="278" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C278" s="11"/>
-      <c r="D278" s="11"/>
-      <c r="E278" s="11"/>
-    </row>
-    <row r="279" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C279" s="11"/>
-      <c r="D279" s="11"/>
-      <c r="E279" s="11"/>
-    </row>
-    <row r="280" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C280" s="11"/>
-      <c r="D280" s="11"/>
-      <c r="E280" s="11"/>
-    </row>
-    <row r="281" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C281" s="11"/>
-      <c r="D281" s="11"/>
-      <c r="E281" s="11"/>
-    </row>
-    <row r="282" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C282" s="11"/>
-      <c r="D282" s="11"/>
-      <c r="E282" s="11"/>
-    </row>
-    <row r="283" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C283" s="11"/>
-      <c r="D283" s="11"/>
-      <c r="E283" s="11"/>
-    </row>
-    <row r="284" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C284" s="11"/>
-      <c r="D284" s="11"/>
-      <c r="E284" s="11"/>
-    </row>
-    <row r="285" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C285" s="11"/>
-      <c r="D285" s="11"/>
-      <c r="E285" s="11"/>
-    </row>
-    <row r="286" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C286" s="11"/>
-      <c r="D286" s="11"/>
-      <c r="E286" s="11"/>
-    </row>
-    <row r="287" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C287" s="11"/>
-      <c r="D287" s="11"/>
-      <c r="E287" s="11"/>
-    </row>
-    <row r="288" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C288" s="11"/>
-      <c r="D288" s="11"/>
-      <c r="E288" s="11"/>
-    </row>
-    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C289" s="11"/>
-      <c r="D289" s="11"/>
-      <c r="E289" s="11"/>
-    </row>
-    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C290" s="11"/>
-      <c r="D290" s="11"/>
-      <c r="E290" s="11"/>
-    </row>
-    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C291" s="11"/>
-      <c r="D291" s="11"/>
-      <c r="E291" s="11"/>
-    </row>
-    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C292" s="11"/>
-      <c r="D292" s="11"/>
-      <c r="E292" s="11"/>
-    </row>
-    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C293" s="11"/>
-      <c r="D293" s="11"/>
-      <c r="E293" s="11"/>
-    </row>
-    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C294" s="11"/>
-      <c r="D294" s="11"/>
-      <c r="E294" s="11"/>
-    </row>
-    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C295" s="11"/>
-      <c r="D295" s="11"/>
-      <c r="E295" s="11"/>
-    </row>
-    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C296" s="11"/>
-      <c r="D296" s="11"/>
-      <c r="E296" s="11"/>
-    </row>
-    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C297" s="11"/>
-      <c r="D297" s="11"/>
-      <c r="E297" s="11"/>
-    </row>
-    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C298" s="11"/>
-      <c r="D298" s="11"/>
-      <c r="E298" s="11"/>
-    </row>
-    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>16</v>
+      </c>
+      <c r="B256" t="s">
+        <v>15</v>
+      </c>
+      <c r="C256">
+        <v>2620</v>
+      </c>
+      <c r="D256">
+        <v>2880</v>
+      </c>
+      <c r="E256">
+        <v>3090</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H256" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>13</v>
+      </c>
+      <c r="B257" t="s">
+        <v>15</v>
+      </c>
+      <c r="C257">
+        <v>2620</v>
+      </c>
+      <c r="D257">
+        <v>2880</v>
+      </c>
+      <c r="E257">
+        <v>3090</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H257" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I257" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>5</v>
+      </c>
+      <c r="B258" t="s">
+        <v>15</v>
+      </c>
+      <c r="C258">
+        <v>2620</v>
+      </c>
+      <c r="D258">
+        <v>2880</v>
+      </c>
+      <c r="E258">
+        <v>3090</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H258" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I258" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>4</v>
+      </c>
+      <c r="B259" t="s">
+        <v>15</v>
+      </c>
+      <c r="C259">
+        <v>2620</v>
+      </c>
+      <c r="D259">
+        <v>2880</v>
+      </c>
+      <c r="E259">
+        <v>3090</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H259" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I259" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>120</v>
+      </c>
+      <c r="B260" t="s">
+        <v>15</v>
+      </c>
+      <c r="C260">
+        <v>2830</v>
+      </c>
+      <c r="D260">
+        <v>2990</v>
+      </c>
+      <c r="E260">
+        <v>3300</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H260" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>24</v>
+      </c>
+      <c r="B261" t="s">
+        <v>15</v>
+      </c>
+      <c r="D261">
+        <v>2990</v>
+      </c>
+      <c r="E261">
+        <v>3300</v>
+      </c>
+      <c r="F261" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G261" s="8">
+        <v>18</v>
+      </c>
+      <c r="H261" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I261" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>25</v>
+      </c>
+      <c r="B262" t="s">
+        <v>15</v>
+      </c>
+      <c r="C262">
+        <v>2830</v>
+      </c>
+      <c r="D262">
+        <v>2930</v>
+      </c>
+      <c r="E262">
+        <v>3200</v>
+      </c>
+      <c r="F262" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H262" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I262" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>26</v>
+      </c>
+      <c r="B263" t="s">
+        <v>15</v>
+      </c>
+      <c r="C263">
+        <v>2830</v>
+      </c>
+      <c r="D263">
+        <v>2930</v>
+      </c>
+      <c r="E263">
+        <v>3200</v>
+      </c>
+      <c r="F263" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H263" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I263" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>27</v>
+      </c>
+      <c r="B264" t="s">
+        <v>15</v>
+      </c>
+      <c r="C264">
+        <v>2830</v>
+      </c>
+      <c r="D264">
+        <v>2930</v>
+      </c>
+      <c r="E264">
+        <v>3200</v>
+      </c>
+      <c r="F264" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H264" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I264" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>48</v>
+      </c>
+      <c r="B265" t="s">
+        <v>15</v>
+      </c>
+      <c r="C265">
+        <v>2830</v>
+      </c>
+      <c r="D265">
+        <v>2930</v>
+      </c>
+      <c r="E265">
+        <v>3200</v>
+      </c>
+      <c r="F265" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H265" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I265" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>49</v>
+      </c>
+      <c r="B266" t="s">
+        <v>15</v>
+      </c>
+      <c r="C266">
+        <v>2830</v>
+      </c>
+      <c r="D266">
+        <v>2930</v>
+      </c>
+      <c r="E266">
+        <v>3200</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H266" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I266" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>28</v>
+      </c>
+      <c r="B267" t="s">
+        <v>15</v>
+      </c>
+      <c r="C267">
+        <v>2830</v>
+      </c>
+      <c r="D267">
+        <v>2930</v>
+      </c>
+      <c r="E267">
+        <v>3200</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H267" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I267" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>50</v>
+      </c>
+      <c r="B268" t="s">
+        <v>15</v>
+      </c>
+      <c r="C268">
+        <v>2830</v>
+      </c>
+      <c r="D268">
+        <v>2930</v>
+      </c>
+      <c r="E268">
+        <v>3200</v>
+      </c>
+      <c r="F268" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H268" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I268" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>51</v>
+      </c>
+      <c r="B269" t="s">
+        <v>15</v>
+      </c>
+      <c r="C269">
+        <v>2830</v>
+      </c>
+      <c r="D269">
+        <v>2930</v>
+      </c>
+      <c r="E269">
+        <v>3200</v>
+      </c>
+      <c r="F269" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H269" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I269" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>52</v>
+      </c>
+      <c r="B270" t="s">
+        <v>15</v>
+      </c>
+      <c r="C270">
+        <v>2830</v>
+      </c>
+      <c r="D270">
+        <v>2930</v>
+      </c>
+      <c r="E270">
+        <v>3200</v>
+      </c>
+      <c r="F270" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="H270" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I270" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>29</v>
+      </c>
+      <c r="B271" t="s">
+        <v>15</v>
+      </c>
+      <c r="D271">
+        <v>2990</v>
+      </c>
+      <c r="E271">
+        <v>3300</v>
+      </c>
+      <c r="F271" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G271" s="8">
+        <v>18</v>
+      </c>
+      <c r="H271" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I271" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>30</v>
+      </c>
+      <c r="B272" t="s">
+        <v>15</v>
+      </c>
+      <c r="D272">
+        <v>2990</v>
+      </c>
+      <c r="E272">
+        <v>3300</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G272" s="8">
+        <v>18</v>
+      </c>
+      <c r="H272" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>121</v>
+      </c>
+      <c r="B273" t="s">
+        <v>15</v>
+      </c>
+      <c r="D273">
+        <v>2990</v>
+      </c>
+      <c r="E273">
+        <v>3300</v>
+      </c>
+      <c r="F273" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G273" s="8">
+        <v>18</v>
+      </c>
+      <c r="H273" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I273" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>122</v>
+      </c>
+      <c r="B274" t="s">
+        <v>15</v>
+      </c>
+      <c r="D274">
+        <v>2990</v>
+      </c>
+      <c r="E274">
+        <v>3250</v>
+      </c>
+      <c r="F274" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G274" s="8">
+        <v>18</v>
+      </c>
+      <c r="H274" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I274" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>123</v>
+      </c>
+      <c r="B275" t="s">
+        <v>15</v>
+      </c>
+      <c r="D275">
+        <v>3140</v>
+      </c>
+      <c r="E275">
+        <v>3560</v>
+      </c>
+      <c r="F275" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G275" s="8">
+        <v>18</v>
+      </c>
+      <c r="H275" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I275" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>31</v>
+      </c>
+      <c r="B276" t="s">
+        <v>15</v>
+      </c>
+      <c r="D276">
+        <v>3090</v>
+      </c>
+      <c r="E276">
+        <v>3410</v>
+      </c>
+      <c r="F276" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G276" s="8">
+        <v>18</v>
+      </c>
+      <c r="H276" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I276" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>124</v>
+      </c>
+      <c r="B277" t="s">
+        <v>15</v>
+      </c>
+      <c r="D277">
+        <v>3200</v>
+      </c>
+      <c r="E277">
+        <v>3620</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G277" s="8">
+        <v>18</v>
+      </c>
+      <c r="H277" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I277" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>53</v>
+      </c>
+      <c r="B278" t="s">
+        <v>15</v>
+      </c>
+      <c r="D278">
+        <v>3200</v>
+      </c>
+      <c r="E278">
+        <v>3620</v>
+      </c>
+      <c r="F278" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G278" s="8">
+        <v>18</v>
+      </c>
+      <c r="H278" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I278" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>125</v>
+      </c>
+      <c r="B279" t="s">
+        <v>15</v>
+      </c>
+      <c r="D279">
+        <v>3040</v>
+      </c>
+      <c r="E279">
+        <v>3300</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G279" s="8">
+        <v>18</v>
+      </c>
+      <c r="H279" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I279" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>32</v>
+      </c>
+      <c r="B280" t="s">
+        <v>15</v>
+      </c>
+      <c r="D280">
+        <v>3090</v>
+      </c>
+      <c r="E280">
+        <v>3410</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G280" s="8">
+        <v>18</v>
+      </c>
+      <c r="H280" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I280" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>126</v>
+      </c>
+      <c r="B281" t="s">
+        <v>15</v>
+      </c>
+      <c r="D281">
+        <v>3090</v>
+      </c>
+      <c r="E281">
+        <v>3410</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G281" s="8">
+        <v>18</v>
+      </c>
+      <c r="H281" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I281" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>127</v>
+      </c>
+      <c r="B282" t="s">
+        <v>15</v>
+      </c>
+      <c r="D282">
+        <v>3090</v>
+      </c>
+      <c r="E282">
+        <v>3410</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G282" s="8">
+        <v>18</v>
+      </c>
+      <c r="H282" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>54</v>
+      </c>
+      <c r="B283" t="s">
+        <v>15</v>
+      </c>
+      <c r="D283">
+        <v>3090</v>
+      </c>
+      <c r="E283">
+        <v>3410</v>
+      </c>
+      <c r="F283" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G283" s="8">
+        <v>18</v>
+      </c>
+      <c r="H283" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I283" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>55</v>
+      </c>
+      <c r="B284" t="s">
+        <v>15</v>
+      </c>
+      <c r="D284">
+        <v>3090</v>
+      </c>
+      <c r="E284">
+        <v>3410</v>
+      </c>
+      <c r="F284" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G284" s="8">
+        <v>18</v>
+      </c>
+      <c r="H284" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>56</v>
+      </c>
+      <c r="B285" t="s">
+        <v>15</v>
+      </c>
+      <c r="D285">
+        <v>3090</v>
+      </c>
+      <c r="E285">
+        <v>3410</v>
+      </c>
+      <c r="F285" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G285" s="8">
+        <v>18</v>
+      </c>
+      <c r="H285" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I285" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>57</v>
+      </c>
+      <c r="B286" t="s">
+        <v>15</v>
+      </c>
+      <c r="D286">
+        <v>3090</v>
+      </c>
+      <c r="E286">
+        <v>3410</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G286" s="8">
+        <v>18</v>
+      </c>
+      <c r="H286" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I286" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>128</v>
+      </c>
+      <c r="B287" t="s">
+        <v>15</v>
+      </c>
+      <c r="D287">
+        <v>3090</v>
+      </c>
+      <c r="E287">
+        <v>3410</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G287" s="8">
+        <v>18</v>
+      </c>
+      <c r="H287" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I287" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>129</v>
+      </c>
+      <c r="B288" t="s">
+        <v>15</v>
+      </c>
+      <c r="D288">
+        <v>3090</v>
+      </c>
+      <c r="E288">
+        <v>3410</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G288" s="8">
+        <v>18</v>
+      </c>
+      <c r="H288" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>33</v>
+      </c>
+      <c r="B289" t="s">
+        <v>15</v>
+      </c>
+      <c r="D289">
+        <v>3140</v>
+      </c>
+      <c r="E289">
+        <v>3560</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G289" s="8">
+        <v>18</v>
+      </c>
+      <c r="H289" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I289" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>34</v>
+      </c>
+      <c r="B290" t="s">
+        <v>15</v>
+      </c>
+      <c r="D290">
+        <v>3200</v>
+      </c>
+      <c r="E290">
+        <v>3620</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G290" s="8">
+        <v>18</v>
+      </c>
+      <c r="H290" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>58</v>
+      </c>
+      <c r="B291" t="s">
+        <v>15</v>
+      </c>
+      <c r="D291">
+        <v>3250</v>
+      </c>
+      <c r="E291">
+        <v>3720</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G291" s="8">
+        <v>18</v>
+      </c>
+      <c r="H291" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I291" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>130</v>
+      </c>
+      <c r="B292" t="s">
+        <v>15</v>
+      </c>
+      <c r="D292">
+        <v>3250</v>
+      </c>
+      <c r="E292">
+        <v>3720</v>
+      </c>
+      <c r="F292" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G292" s="8">
+        <v>18</v>
+      </c>
+      <c r="H292" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>35</v>
+      </c>
+      <c r="B293" t="s">
+        <v>15</v>
+      </c>
+      <c r="D293">
+        <v>3410</v>
+      </c>
+      <c r="E293">
+        <v>3930</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G293" s="8">
+        <v>18</v>
+      </c>
+      <c r="H293" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I293" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>131</v>
+      </c>
+      <c r="B294" t="s">
+        <v>15</v>
+      </c>
+      <c r="D294">
+        <v>3040</v>
+      </c>
+      <c r="E294">
+        <v>3250</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G294" s="8">
+        <v>18</v>
+      </c>
+      <c r="H294" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I294" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>132</v>
+      </c>
+      <c r="B295" t="s">
+        <v>15</v>
+      </c>
+      <c r="D295">
+        <v>3040</v>
+      </c>
+      <c r="E295">
+        <v>3250</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G295" s="8">
+        <v>18</v>
+      </c>
+      <c r="H295" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I295" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>133</v>
+      </c>
+      <c r="B296" t="s">
+        <v>15</v>
+      </c>
+      <c r="D296">
+        <v>3040</v>
+      </c>
+      <c r="E296">
+        <v>3250</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G296" s="8">
+        <v>18</v>
+      </c>
+      <c r="H296" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I296" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>134</v>
+      </c>
+      <c r="B297" t="s">
+        <v>15</v>
+      </c>
+      <c r="D297">
+        <v>3040</v>
+      </c>
+      <c r="E297">
+        <v>3250</v>
+      </c>
+      <c r="F297" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G297" s="8">
+        <v>18</v>
+      </c>
+      <c r="H297" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I297" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>135</v>
+      </c>
+      <c r="B298" t="s">
+        <v>15</v>
+      </c>
+      <c r="D298">
+        <v>3040</v>
+      </c>
+      <c r="E298">
+        <v>3250</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G298" s="8">
+        <v>18</v>
+      </c>
+      <c r="H298" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I298" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B299" t="s">
+        <v>15</v>
+      </c>
       <c r="C299" s="11"/>
-      <c r="D299" s="11"/>
-      <c r="E299" s="11"/>
-    </row>
-    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D299" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E299" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G299" s="8">
+        <v>17</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I299" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B300" t="s">
+        <v>15</v>
+      </c>
       <c r="C300" s="11"/>
-      <c r="D300" s="11"/>
-      <c r="E300" s="11"/>
-    </row>
-    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D300" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E300" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G300" s="8">
+        <v>17</v>
+      </c>
+      <c r="H300" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B301" t="s">
+        <v>15</v>
+      </c>
       <c r="C301" s="11"/>
-      <c r="D301" s="11"/>
-      <c r="E301" s="11"/>
-    </row>
-    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D301" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E301" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F301" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G301" s="8">
+        <v>17</v>
+      </c>
+      <c r="H301" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I301" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B302" t="s">
+        <v>15</v>
+      </c>
       <c r="C302" s="11"/>
-      <c r="D302" s="11"/>
-      <c r="E302" s="11"/>
-    </row>
-    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D302" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E302" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G302" s="8">
+        <v>17</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B303" t="s">
+        <v>15</v>
+      </c>
       <c r="C303" s="11"/>
-      <c r="D303" s="11"/>
-      <c r="E303" s="11"/>
-    </row>
-    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D303" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E303" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F303" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G303" s="8">
+        <v>17</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B304" t="s">
+        <v>15</v>
+      </c>
       <c r="C304" s="11"/>
-      <c r="D304" s="11"/>
-      <c r="E304" s="11"/>
-    </row>
-    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D304" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E304" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G304" s="8">
+        <v>17</v>
+      </c>
+      <c r="H304" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B305" t="s">
+        <v>15</v>
+      </c>
       <c r="C305" s="11"/>
-      <c r="D305" s="11"/>
-      <c r="E305" s="11"/>
-    </row>
-    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D305" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E305" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G305" s="8">
+        <v>17</v>
+      </c>
+      <c r="H305" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B306" t="s">
+        <v>15</v>
+      </c>
       <c r="C306" s="11"/>
-      <c r="D306" s="11"/>
-      <c r="E306" s="11"/>
-    </row>
-    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D306" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E306" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G306" s="8">
+        <v>17</v>
+      </c>
+      <c r="H306" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B307" t="s">
+        <v>15</v>
+      </c>
       <c r="C307" s="11"/>
-      <c r="D307" s="11"/>
-      <c r="E307" s="11"/>
-    </row>
-    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D307" s="7">
+        <v>2890</v>
+      </c>
+      <c r="E307" s="7">
+        <v>3100</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G307" s="8">
+        <v>17</v>
+      </c>
+      <c r="H307" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B308" t="s">
+        <v>15</v>
+      </c>
       <c r="C308" s="11"/>
-      <c r="D308" s="11"/>
-      <c r="E308" s="11"/>
-    </row>
-    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D308" s="7">
+        <v>2970</v>
+      </c>
+      <c r="E308" s="7">
+        <v>3260</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G308" s="8">
+        <v>17</v>
+      </c>
+      <c r="H308" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B309" t="s">
+        <v>15</v>
+      </c>
       <c r="C309" s="11"/>
-      <c r="D309" s="11"/>
-      <c r="E309" s="11"/>
-    </row>
-    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D309" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E309" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G309" s="8">
+        <v>17</v>
+      </c>
+      <c r="H309" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B310" t="s">
+        <v>15</v>
+      </c>
       <c r="C310" s="11"/>
-      <c r="D310" s="11"/>
-      <c r="E310" s="11"/>
-    </row>
-    <row r="311" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D310" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E310" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G310" s="8">
+        <v>17</v>
+      </c>
+      <c r="H310" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B311" t="s">
+        <v>15</v>
+      </c>
       <c r="C311" s="11"/>
-      <c r="D311" s="11"/>
-      <c r="E311" s="11"/>
-    </row>
-    <row r="312" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D311" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E311" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F311" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G311" s="8">
+        <v>17</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B312" t="s">
+        <v>15</v>
+      </c>
       <c r="C312" s="11"/>
-      <c r="D312" s="11"/>
-      <c r="E312" s="11"/>
-    </row>
-    <row r="313" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D312" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E312" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F312" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G312" s="8">
+        <v>17</v>
+      </c>
+      <c r="H312" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B313" t="s">
+        <v>15</v>
+      </c>
       <c r="C313" s="11"/>
-      <c r="D313" s="11"/>
-      <c r="E313" s="11"/>
-    </row>
-    <row r="314" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D313" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E313" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F313" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G313" s="8">
+        <v>17</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B314" t="s">
+        <v>15</v>
+      </c>
       <c r="C314" s="11"/>
-      <c r="D314" s="11"/>
-      <c r="E314" s="11"/>
-    </row>
-    <row r="315" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D314" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E314" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G314" s="8">
+        <v>17</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B315" t="s">
+        <v>15</v>
+      </c>
       <c r="C315" s="11"/>
-      <c r="D315" s="11"/>
-      <c r="E315" s="11"/>
-    </row>
-    <row r="316" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D315" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E315" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G315" s="8">
+        <v>17</v>
+      </c>
+      <c r="H315" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B316" t="s">
+        <v>15</v>
+      </c>
       <c r="C316" s="11"/>
-      <c r="D316" s="11"/>
-      <c r="E316" s="11"/>
-    </row>
-    <row r="317" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D316" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E316" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G316" s="8">
+        <v>17</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B317" t="s">
+        <v>15</v>
+      </c>
       <c r="C317" s="11"/>
-      <c r="D317" s="11"/>
-      <c r="E317" s="11"/>
-    </row>
-    <row r="318" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D317" s="7">
+        <v>3140</v>
+      </c>
+      <c r="E317" s="7">
+        <v>3510</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G317" s="8">
+        <v>17</v>
+      </c>
+      <c r="H317" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B318" t="s">
+        <v>15</v>
+      </c>
       <c r="C318" s="11"/>
-      <c r="D318" s="11"/>
-      <c r="E318" s="11"/>
-    </row>
-    <row r="319" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D318" s="7">
+        <v>2950</v>
+      </c>
+      <c r="E318" s="7">
+        <v>3210</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G318" s="8">
+        <v>17</v>
+      </c>
+      <c r="H318" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B319" t="s">
+        <v>15</v>
+      </c>
       <c r="C319" s="11"/>
-      <c r="D319" s="11"/>
-      <c r="E319" s="11"/>
-    </row>
-    <row r="320" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D319" s="7">
+        <v>3000</v>
+      </c>
+      <c r="E319" s="7">
+        <v>3260</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G319" s="8">
+        <v>17</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B320" t="s">
+        <v>15</v>
+      </c>
       <c r="C320" s="11"/>
-      <c r="D320" s="11"/>
-      <c r="E320" s="11"/>
-    </row>
-    <row r="321" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D320" s="7">
+        <v>3110</v>
+      </c>
+      <c r="E320" s="7">
+        <v>3420</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G320" s="8">
+        <v>17</v>
+      </c>
+      <c r="H320" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B321" t="s">
+        <v>15</v>
+      </c>
       <c r="C321" s="11"/>
-      <c r="D321" s="11"/>
-      <c r="E321" s="11"/>
-    </row>
-    <row r="322" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D321" s="7">
+        <v>3050</v>
+      </c>
+      <c r="E321" s="7">
+        <v>3420</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G321" s="8">
+        <v>17</v>
+      </c>
+      <c r="H321" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B322" t="s">
+        <v>15</v>
+      </c>
       <c r="C322" s="11"/>
-      <c r="D322" s="11"/>
-      <c r="E322" s="11"/>
-    </row>
-    <row r="323" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D322" s="7">
+        <v>3120</v>
+      </c>
+      <c r="E322" s="7">
+        <v>3450</v>
+      </c>
+      <c r="F322" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G322" s="8">
+        <v>17</v>
+      </c>
+      <c r="H322" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B323" t="s">
+        <v>15</v>
+      </c>
       <c r="C323" s="11"/>
-      <c r="D323" s="11"/>
-      <c r="E323" s="11"/>
-    </row>
-    <row r="324" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D323" s="7">
+        <v>3150</v>
+      </c>
+      <c r="E323" s="7">
+        <v>3550</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G323" s="8">
+        <v>17</v>
+      </c>
+      <c r="H323" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B324" t="s">
+        <v>15</v>
+      </c>
       <c r="C324" s="11"/>
-      <c r="D324" s="11"/>
-      <c r="E324" s="11"/>
-    </row>
-    <row r="325" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D324" s="7">
+        <v>3150</v>
+      </c>
+      <c r="E324" s="7">
+        <v>3550</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G324" s="8">
+        <v>17</v>
+      </c>
+      <c r="H324" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B325" t="s">
+        <v>15</v>
+      </c>
       <c r="C325" s="11"/>
-      <c r="D325" s="11"/>
-      <c r="E325" s="11"/>
-    </row>
-    <row r="326" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D325" s="7">
+        <v>3080</v>
+      </c>
+      <c r="E325" s="7">
+        <v>3420</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G325" s="8">
+        <v>17</v>
+      </c>
+      <c r="H325" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B326" t="s">
+        <v>15</v>
+      </c>
       <c r="C326" s="11"/>
-      <c r="D326" s="11"/>
-      <c r="E326" s="11"/>
-    </row>
-    <row r="327" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D326" s="7">
+        <v>3100</v>
+      </c>
+      <c r="E326" s="7">
+        <v>3440</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G326" s="8">
+        <v>17</v>
+      </c>
+      <c r="H326" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B327" t="s">
+        <v>15</v>
+      </c>
       <c r="C327" s="11"/>
-      <c r="D327" s="11"/>
-      <c r="E327" s="11"/>
-    </row>
-    <row r="328" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D327" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E327" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G327" s="8">
+        <v>17</v>
+      </c>
+      <c r="H327" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B328" t="s">
+        <v>15</v>
+      </c>
       <c r="C328" s="11"/>
-      <c r="D328" s="11"/>
-      <c r="E328" s="11"/>
-    </row>
-    <row r="329" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D328" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E328" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F328" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G328" s="8">
+        <v>17</v>
+      </c>
+      <c r="H328" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B329" t="s">
+        <v>15</v>
+      </c>
       <c r="C329" s="11"/>
-      <c r="D329" s="11"/>
-      <c r="E329" s="11"/>
-    </row>
-    <row r="330" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D329" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E329" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G329" s="8">
+        <v>17</v>
+      </c>
+      <c r="H329" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I329" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B330" t="s">
+        <v>15</v>
+      </c>
       <c r="C330" s="11"/>
-      <c r="D330" s="11"/>
-      <c r="E330" s="11"/>
-    </row>
-    <row r="331" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D330" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E330" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G330" s="8">
+        <v>17</v>
+      </c>
+      <c r="H330" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I330" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B331" t="s">
+        <v>15</v>
+      </c>
       <c r="C331" s="11"/>
-      <c r="D331" s="11"/>
-      <c r="E331" s="11"/>
-    </row>
-    <row r="332" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D331" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E331" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F331" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G331" s="8">
+        <v>17</v>
+      </c>
+      <c r="H331" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I331" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B332" t="s">
+        <v>15</v>
+      </c>
       <c r="C332" s="11"/>
-      <c r="D332" s="11"/>
-      <c r="E332" s="11"/>
-    </row>
-    <row r="333" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D332" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E332" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G332" s="8">
+        <v>17</v>
+      </c>
+      <c r="H332" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I332" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B333" t="s">
+        <v>15</v>
+      </c>
       <c r="C333" s="11"/>
-      <c r="D333" s="11"/>
-      <c r="E333" s="11"/>
-    </row>
-    <row r="334" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D333" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E333" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F333" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G333" s="8">
+        <v>17</v>
+      </c>
+      <c r="H333" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I333" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B334" t="s">
+        <v>15</v>
+      </c>
       <c r="C334" s="11"/>
-      <c r="D334" s="11"/>
-      <c r="E334" s="11"/>
-    </row>
-    <row r="335" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D334" s="7">
+        <v>3020</v>
+      </c>
+      <c r="E334" s="7">
+        <v>3320</v>
+      </c>
+      <c r="F334" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G334" s="8">
+        <v>17</v>
+      </c>
+      <c r="H334" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I334" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B335" t="s">
+        <v>15</v>
+      </c>
       <c r="C335" s="11"/>
-      <c r="D335" s="11"/>
-      <c r="E335" s="11"/>
-    </row>
-    <row r="336" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D335" s="7">
+        <v>3140</v>
+      </c>
+      <c r="E335" s="7">
+        <v>3540</v>
+      </c>
+      <c r="F335" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G335" s="8">
+        <v>17</v>
+      </c>
+      <c r="H335" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I335" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B336" t="s">
+        <v>15</v>
+      </c>
       <c r="C336" s="11"/>
-      <c r="D336" s="11"/>
-      <c r="E336" s="11"/>
-    </row>
-    <row r="337" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D336" s="7">
+        <v>3130</v>
+      </c>
+      <c r="E336" s="7">
+        <v>3510</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G336" s="8">
+        <v>17</v>
+      </c>
+      <c r="H336" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I336" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B337" t="s">
+        <v>15</v>
+      </c>
       <c r="C337" s="11"/>
-      <c r="D337" s="11"/>
-      <c r="E337" s="11"/>
-    </row>
-    <row r="338" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D337" s="7">
+        <v>3130</v>
+      </c>
+      <c r="E337" s="7">
+        <v>3580</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G337" s="8">
+        <v>17</v>
+      </c>
+      <c r="H337" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I337" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B338" t="s">
+        <v>15</v>
+      </c>
       <c r="C338" s="11"/>
-      <c r="D338" s="11"/>
-      <c r="E338" s="11"/>
-    </row>
-    <row r="339" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D338" s="7">
+        <v>3130</v>
+      </c>
+      <c r="E338" s="7">
+        <v>3580</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G338" s="8">
+        <v>17</v>
+      </c>
+      <c r="H338" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B339" t="s">
+        <v>15</v>
+      </c>
       <c r="C339" s="11"/>
-      <c r="D339" s="11"/>
-      <c r="E339" s="11"/>
-    </row>
-    <row r="340" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D339" s="7">
+        <v>3320</v>
+      </c>
+      <c r="E339" s="7">
+        <v>3930</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G339" s="8">
+        <v>17</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="B340" t="s">
+        <v>15</v>
+      </c>
       <c r="C340" s="11"/>
-      <c r="D340" s="11"/>
-      <c r="E340" s="11"/>
-    </row>
-    <row r="341" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D340" s="7">
+        <v>3000</v>
+      </c>
+      <c r="E340" s="7">
+        <v>3260</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G340" s="8">
+        <v>17</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B341" t="s">
+        <v>15</v>
+      </c>
       <c r="C341" s="11"/>
-      <c r="D341" s="11"/>
-      <c r="E341" s="11"/>
-    </row>
-    <row r="342" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D341" s="7">
+        <v>3100</v>
+      </c>
+      <c r="E341" s="7">
+        <v>3420</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G341" s="8">
+        <v>17</v>
+      </c>
+      <c r="H341" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I341" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B342" t="s">
+        <v>15</v>
+      </c>
       <c r="C342" s="11"/>
-      <c r="D342" s="11"/>
-      <c r="E342" s="11"/>
-    </row>
-    <row r="343" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D342" s="7">
+        <v>3100</v>
+      </c>
+      <c r="E342" s="7">
+        <v>3420</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G342" s="8">
+        <v>17</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B343" t="s">
+        <v>15</v>
+      </c>
       <c r="C343" s="11"/>
-      <c r="D343" s="11"/>
-      <c r="E343" s="11"/>
-    </row>
-    <row r="344" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D343" s="7">
+        <v>3160</v>
+      </c>
+      <c r="E343" s="7">
+        <v>3470</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G343" s="8">
+        <v>17</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="B344" t="s">
+        <v>15</v>
+      </c>
       <c r="C344" s="11"/>
-      <c r="D344" s="11"/>
-      <c r="E344" s="11"/>
-    </row>
-    <row r="345" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D344" s="7">
+        <v>3160</v>
+      </c>
+      <c r="E344" s="7">
+        <v>3470</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G344" s="8">
+        <v>17</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>5</v>
+      </c>
+      <c r="B345" t="s">
+        <v>62</v>
+      </c>
       <c r="C345" s="11"/>
-      <c r="D345" s="11"/>
-      <c r="E345" s="11"/>
-    </row>
-    <row r="346" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D345" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E345" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G345" s="8">
+        <v>14</v>
+      </c>
+      <c r="H345" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I345" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>4</v>
+      </c>
+      <c r="B346" t="s">
+        <v>62</v>
+      </c>
       <c r="C346" s="11"/>
-      <c r="D346" s="11"/>
-      <c r="E346" s="11"/>
-    </row>
-    <row r="347" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D346" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E346" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G346" s="8">
+        <v>14</v>
+      </c>
+      <c r="H346" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>107</v>
+      </c>
+      <c r="B347" t="s">
+        <v>62</v>
+      </c>
       <c r="C347" s="11"/>
-      <c r="D347" s="11"/>
-      <c r="E347" s="11"/>
-    </row>
-    <row r="348" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D347" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E347" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G347" s="8">
+        <v>14</v>
+      </c>
+      <c r="H347" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I347" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>108</v>
+      </c>
+      <c r="B348" t="s">
+        <v>62</v>
+      </c>
       <c r="C348" s="11"/>
-      <c r="D348" s="11"/>
-      <c r="E348" s="11"/>
-    </row>
-    <row r="349" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D348" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E348" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G348" s="8">
+        <v>14</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>109</v>
+      </c>
+      <c r="B349" t="s">
+        <v>62</v>
+      </c>
       <c r="C349" s="11"/>
-      <c r="D349" s="11"/>
-      <c r="E349" s="11"/>
-    </row>
-    <row r="350" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D349" s="11">
+        <v>2640</v>
+      </c>
+      <c r="E349" s="11">
+        <v>2950</v>
+      </c>
+      <c r="F349" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G349" s="8">
+        <v>14</v>
+      </c>
+      <c r="H349" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I349" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>52</v>
+      </c>
+      <c r="B350" t="s">
+        <v>62</v>
+      </c>
       <c r="C350" s="11"/>
-      <c r="D350" s="11"/>
-      <c r="E350" s="11"/>
-    </row>
-    <row r="351" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D350" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E350" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F350" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G350" s="8">
+        <v>14</v>
+      </c>
+      <c r="H350" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>35</v>
+      </c>
+      <c r="B351" t="s">
+        <v>62</v>
+      </c>
       <c r="C351" s="11"/>
-      <c r="D351" s="11"/>
-      <c r="E351" s="11"/>
-    </row>
-    <row r="352" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D351" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E351" s="11">
+        <v>3740</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G351" s="8">
+        <v>14</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>24</v>
+      </c>
+      <c r="B352" t="s">
+        <v>62</v>
+      </c>
       <c r="C352" s="11"/>
-      <c r="D352" s="11"/>
-      <c r="E352" s="11"/>
-    </row>
-    <row r="353" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D352" s="11">
+        <v>2900</v>
+      </c>
+      <c r="E352" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G352" s="8">
+        <v>14</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>50</v>
+      </c>
+      <c r="B353" t="s">
+        <v>62</v>
+      </c>
       <c r="C353" s="11"/>
-      <c r="D353" s="11"/>
-      <c r="E353" s="11"/>
-    </row>
-    <row r="354" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D353" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E353" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G353" s="8">
+        <v>14</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I353" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>29</v>
+      </c>
+      <c r="B354" t="s">
+        <v>62</v>
+      </c>
       <c r="C354" s="11"/>
-      <c r="D354" s="11"/>
-      <c r="E354" s="11"/>
-    </row>
-    <row r="355" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D354" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E354" s="11">
+        <v>3630</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G354" s="8">
+        <v>14</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>27</v>
+      </c>
+      <c r="B355" t="s">
+        <v>62</v>
+      </c>
       <c r="C355" s="11"/>
-      <c r="D355" s="11"/>
-      <c r="E355" s="11"/>
-    </row>
-    <row r="356" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D355" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E355" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F355" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G355" s="8">
+        <v>14</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I355" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>48</v>
+      </c>
+      <c r="B356" t="s">
+        <v>62</v>
+      </c>
       <c r="C356" s="11"/>
-      <c r="D356" s="11"/>
-      <c r="E356" s="11"/>
-    </row>
-    <row r="357" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D356" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E356" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G356" s="8">
+        <v>14</v>
+      </c>
+      <c r="H356" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>33</v>
+      </c>
+      <c r="B357" t="s">
+        <v>62</v>
+      </c>
       <c r="C357" s="11"/>
-      <c r="D357" s="11"/>
-      <c r="E357" s="11"/>
-    </row>
-    <row r="358" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D357" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E357" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F357" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G357" s="8">
+        <v>14</v>
+      </c>
+      <c r="H357" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I357" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>30</v>
+      </c>
+      <c r="B358" t="s">
+        <v>62</v>
+      </c>
       <c r="C358" s="11"/>
-      <c r="D358" s="11"/>
-      <c r="E358" s="11"/>
-    </row>
-    <row r="359" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D358" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E358" s="11">
+        <v>3530</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G358" s="8">
+        <v>14</v>
+      </c>
+      <c r="H358" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>56</v>
+      </c>
+      <c r="B359" t="s">
+        <v>62</v>
+      </c>
       <c r="C359" s="11"/>
-      <c r="D359" s="11"/>
-      <c r="E359" s="11"/>
-    </row>
-    <row r="360" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D359" s="11">
+        <v>2900</v>
+      </c>
+      <c r="E359" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G359" s="8">
+        <v>14</v>
+      </c>
+      <c r="H359" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I359" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>34</v>
+      </c>
+      <c r="B360" t="s">
+        <v>62</v>
+      </c>
       <c r="C360" s="11"/>
-      <c r="D360" s="11"/>
-      <c r="E360" s="11"/>
-    </row>
-    <row r="361" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D360" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E360" s="11">
+        <v>3480</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G360" s="8">
+        <v>14</v>
+      </c>
+      <c r="H360" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>28</v>
+      </c>
+      <c r="B361" t="s">
+        <v>62</v>
+      </c>
       <c r="C361" s="11"/>
-      <c r="D361" s="11"/>
-      <c r="E361" s="11"/>
-    </row>
-    <row r="362" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D361" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E361" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G361" s="8">
+        <v>14</v>
+      </c>
+      <c r="H361" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I361" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>57</v>
+      </c>
+      <c r="B362" t="s">
+        <v>62</v>
+      </c>
       <c r="C362" s="11"/>
-      <c r="D362" s="11"/>
-      <c r="E362" s="11"/>
-    </row>
-    <row r="363" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D362" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E362" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G362" s="8">
+        <v>14</v>
+      </c>
+      <c r="H362" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>13</v>
+      </c>
+      <c r="B363" t="s">
+        <v>62</v>
+      </c>
       <c r="C363" s="11"/>
-      <c r="D363" s="11"/>
-      <c r="E363" s="11"/>
-    </row>
-    <row r="364" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D363" s="11">
+        <v>2640</v>
+      </c>
+      <c r="E363" s="11">
+        <v>3000</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G363" s="8">
+        <v>14</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I363" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>112</v>
+      </c>
+      <c r="B364" t="s">
+        <v>62</v>
+      </c>
       <c r="C364" s="11"/>
-      <c r="D364" s="11"/>
-      <c r="E364" s="11"/>
-    </row>
-    <row r="365" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D364" s="11">
+        <v>2900</v>
+      </c>
+      <c r="E364" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G364" s="8">
+        <v>14</v>
+      </c>
+      <c r="H364" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>25</v>
+      </c>
+      <c r="B365" t="s">
+        <v>62</v>
+      </c>
       <c r="C365" s="11"/>
-      <c r="D365" s="11"/>
-      <c r="E365" s="11"/>
-    </row>
-    <row r="366" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D365" s="11">
+        <v>2900</v>
+      </c>
+      <c r="E365" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G365" s="8">
+        <v>14</v>
+      </c>
+      <c r="H365" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I365" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>21</v>
+      </c>
+      <c r="B366" t="s">
+        <v>62</v>
+      </c>
       <c r="C366" s="11"/>
-      <c r="D366" s="11"/>
-      <c r="E366" s="11"/>
-    </row>
-    <row r="367" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D366" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E366" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F366" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G366" s="8">
+        <v>14</v>
+      </c>
+      <c r="H366" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>51</v>
+      </c>
+      <c r="B367" t="s">
+        <v>62</v>
+      </c>
       <c r="C367" s="11"/>
-      <c r="D367" s="11"/>
-      <c r="E367" s="11"/>
-    </row>
-    <row r="368" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D367" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E367" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G367" s="8">
+        <v>14</v>
+      </c>
+      <c r="H367" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I367" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>53</v>
+      </c>
+      <c r="B368" t="s">
+        <v>62</v>
+      </c>
       <c r="C368" s="11"/>
-      <c r="D368" s="11"/>
-      <c r="E368" s="11"/>
-    </row>
-    <row r="369" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D368" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E368" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G368" s="8">
+        <v>14</v>
+      </c>
+      <c r="H368" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I368" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>32</v>
+      </c>
+      <c r="B369" t="s">
+        <v>62</v>
+      </c>
       <c r="C369" s="11"/>
-      <c r="D369" s="11"/>
-      <c r="E369" s="11"/>
-    </row>
-    <row r="370" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D369" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E369" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G369" s="8">
+        <v>14</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I369" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>16</v>
+      </c>
+      <c r="B370" t="s">
+        <v>62</v>
+      </c>
       <c r="C370" s="11"/>
-      <c r="D370" s="11"/>
-      <c r="E370" s="11"/>
-    </row>
-    <row r="371" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D370" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E370" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F370" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G370" s="8">
+        <v>14</v>
+      </c>
+      <c r="H370" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I370" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B371" t="s">
+        <v>62</v>
+      </c>
       <c r="C371" s="11"/>
-      <c r="D371" s="11"/>
-      <c r="E371" s="11"/>
-    </row>
-    <row r="372" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D371" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E371" s="11">
+        <v>3530</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G371" s="8">
+        <v>14</v>
+      </c>
+      <c r="H371" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I371" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>20</v>
+      </c>
+      <c r="B372" t="s">
+        <v>62</v>
+      </c>
       <c r="C372" s="11"/>
-      <c r="D372" s="11"/>
-      <c r="E372" s="11"/>
-    </row>
-    <row r="373" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D372" s="11">
+        <v>2580</v>
+      </c>
+      <c r="E372" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G372" s="8">
+        <v>14</v>
+      </c>
+      <c r="H372" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I372" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>114</v>
+      </c>
+      <c r="B373" t="s">
+        <v>62</v>
+      </c>
       <c r="C373" s="11"/>
-      <c r="D373" s="11"/>
-      <c r="E373" s="11"/>
-    </row>
-    <row r="374" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D373" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E373" s="11">
+        <v>3530</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G373" s="8">
+        <v>14</v>
+      </c>
+      <c r="H373" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I373" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>55</v>
+      </c>
+      <c r="B374" t="s">
+        <v>62</v>
+      </c>
       <c r="C374" s="11"/>
-      <c r="D374" s="11"/>
-      <c r="E374" s="11"/>
-    </row>
-    <row r="375" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D374" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E374" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F374" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G374" s="8">
+        <v>14</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I374" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>31</v>
+      </c>
+      <c r="B375" t="s">
+        <v>62</v>
+      </c>
       <c r="C375" s="11"/>
-      <c r="D375" s="11"/>
-      <c r="E375" s="11"/>
-    </row>
-    <row r="376" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D375" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E375" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F375" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G375" s="8">
+        <v>14</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I375" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>54</v>
+      </c>
+      <c r="B376" t="s">
+        <v>62</v>
+      </c>
       <c r="C376" s="11"/>
-      <c r="D376" s="11"/>
-      <c r="E376" s="11"/>
-    </row>
-    <row r="377" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D376" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E376" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F376" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G376" s="8">
+        <v>14</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I376" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>26</v>
+      </c>
+      <c r="B377" t="s">
+        <v>62</v>
+      </c>
       <c r="C377" s="11"/>
-      <c r="D377" s="11"/>
-      <c r="E377" s="11"/>
-    </row>
-    <row r="378" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D377" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E377" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F377" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G377" s="8">
+        <v>14</v>
+      </c>
+      <c r="H377" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I377" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>49</v>
+      </c>
+      <c r="B378" t="s">
+        <v>62</v>
+      </c>
       <c r="C378" s="11"/>
-      <c r="D378" s="11"/>
-      <c r="E378" s="11"/>
-    </row>
-    <row r="379" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D378" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E378" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F378" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G378" s="8">
+        <v>14</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I378" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>5</v>
+      </c>
+      <c r="B379" t="s">
+        <v>15</v>
+      </c>
       <c r="C379" s="11"/>
-      <c r="D379" s="11"/>
-      <c r="E379" s="11"/>
-    </row>
-    <row r="380" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D379" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E379" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F379" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G379" s="8">
+        <v>18</v>
+      </c>
+      <c r="H379" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I379" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>4</v>
+      </c>
+      <c r="B380" t="s">
+        <v>15</v>
+      </c>
       <c r="C380" s="11"/>
-      <c r="D380" s="11"/>
-      <c r="E380" s="11"/>
-    </row>
-    <row r="381" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D380" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E380" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F380" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G380" s="8">
+        <v>18</v>
+      </c>
+      <c r="H380" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I380" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>107</v>
+      </c>
+      <c r="B381" t="s">
+        <v>15</v>
+      </c>
       <c r="C381" s="11"/>
-      <c r="D381" s="11"/>
-      <c r="E381" s="11"/>
-    </row>
-    <row r="382" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D381" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E381" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G381" s="8">
+        <v>18</v>
+      </c>
+      <c r="H381" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I381" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>108</v>
+      </c>
+      <c r="B382" t="s">
+        <v>15</v>
+      </c>
       <c r="C382" s="11"/>
-      <c r="D382" s="11"/>
-      <c r="E382" s="11"/>
-    </row>
-    <row r="383" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D382" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E382" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F382" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G382" s="8">
+        <v>18</v>
+      </c>
+      <c r="H382" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I382" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>109</v>
+      </c>
+      <c r="B383" t="s">
+        <v>15</v>
+      </c>
       <c r="C383" s="11"/>
-      <c r="D383" s="11"/>
-      <c r="E383" s="11"/>
-    </row>
-    <row r="384" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D383" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E383" s="11">
+        <v>2860</v>
+      </c>
+      <c r="F383" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G383" s="8">
+        <v>18</v>
+      </c>
+      <c r="H383" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I383" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>52</v>
+      </c>
+      <c r="B384" t="s">
+        <v>15</v>
+      </c>
       <c r="C384" s="11"/>
-      <c r="D384" s="11"/>
-      <c r="E384" s="11"/>
-    </row>
-    <row r="385" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D384" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E384" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F384" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G384" s="8">
+        <v>18</v>
+      </c>
+      <c r="H384" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I384" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>35</v>
+      </c>
+      <c r="B385" t="s">
+        <v>15</v>
+      </c>
       <c r="C385" s="11"/>
-      <c r="D385" s="11"/>
-      <c r="E385" s="11"/>
-    </row>
-    <row r="386" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D385" s="11">
+        <v>3170</v>
+      </c>
+      <c r="E385" s="11">
+        <v>3750</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G385" s="8">
+        <v>18</v>
+      </c>
+      <c r="H385" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I385" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>24</v>
+      </c>
+      <c r="B386" t="s">
+        <v>15</v>
+      </c>
       <c r="C386" s="11"/>
-      <c r="D386" s="11"/>
-      <c r="E386" s="11"/>
-    </row>
-    <row r="387" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D386" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E386" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F386" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G386" s="8">
+        <v>18</v>
+      </c>
+      <c r="H386" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I386" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>50</v>
+      </c>
+      <c r="B387" t="s">
+        <v>15</v>
+      </c>
       <c r="C387" s="11"/>
-      <c r="D387" s="11"/>
-      <c r="E387" s="11"/>
-    </row>
-    <row r="388" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D387" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E387" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F387" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G387" s="8">
+        <v>18</v>
+      </c>
+      <c r="H387" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I387" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>29</v>
+      </c>
+      <c r="B388" t="s">
+        <v>15</v>
+      </c>
       <c r="C388" s="11"/>
-      <c r="D388" s="11"/>
-      <c r="E388" s="11"/>
-    </row>
-    <row r="389" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D388" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E388" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F388" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G388" s="8">
+        <v>18</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I388" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>27</v>
+      </c>
+      <c r="B389" t="s">
+        <v>15</v>
+      </c>
       <c r="C389" s="11"/>
-      <c r="D389" s="11"/>
-      <c r="E389" s="11"/>
-    </row>
-    <row r="390" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D389" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E389" s="11">
+        <v>3020</v>
+      </c>
+      <c r="F389" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G389" s="8">
+        <v>18</v>
+      </c>
+      <c r="H389" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I389" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>48</v>
+      </c>
+      <c r="B390" t="s">
+        <v>15</v>
+      </c>
       <c r="C390" s="11"/>
-      <c r="D390" s="11"/>
-      <c r="E390" s="11"/>
-    </row>
-    <row r="391" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D390" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E390" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F390" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G390" s="8">
+        <v>18</v>
+      </c>
+      <c r="H390" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I390" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>33</v>
+      </c>
+      <c r="B391" t="s">
+        <v>15</v>
+      </c>
       <c r="C391" s="11"/>
-      <c r="D391" s="11"/>
-      <c r="E391" s="11"/>
-    </row>
-    <row r="392" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D391" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E391" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F391" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G391" s="8">
+        <v>18</v>
+      </c>
+      <c r="H391" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I391" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>111</v>
+      </c>
+      <c r="B392" t="s">
+        <v>15</v>
+      </c>
       <c r="C392" s="11"/>
-      <c r="D392" s="11"/>
-      <c r="E392" s="11"/>
-    </row>
-    <row r="393" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D392" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E392" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F392" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G392" s="8">
+        <v>18</v>
+      </c>
+      <c r="H392" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I392" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>30</v>
+      </c>
+      <c r="B393" t="s">
+        <v>15</v>
+      </c>
       <c r="C393" s="11"/>
-      <c r="D393" s="11"/>
-      <c r="E393" s="11"/>
-    </row>
-    <row r="394" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D393" s="11">
+        <v>3070</v>
+      </c>
+      <c r="E393" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F393" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G393" s="8">
+        <v>18</v>
+      </c>
+      <c r="H393" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I393" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>56</v>
+      </c>
+      <c r="B394" t="s">
+        <v>15</v>
+      </c>
       <c r="C394" s="11"/>
-      <c r="D394" s="11"/>
-      <c r="E394" s="11"/>
-    </row>
-    <row r="395" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D394" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E394" s="11">
+        <v>3120</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G394" s="8">
+        <v>18</v>
+      </c>
+      <c r="H394" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I394" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>28</v>
+      </c>
+      <c r="B395" t="s">
+        <v>15</v>
+      </c>
       <c r="C395" s="11"/>
-      <c r="D395" s="11"/>
-      <c r="E395" s="11"/>
-    </row>
-    <row r="396" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D395" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E395" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G395" s="8">
+        <v>18</v>
+      </c>
+      <c r="H395" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I395" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>57</v>
+      </c>
+      <c r="B396" t="s">
+        <v>15</v>
+      </c>
       <c r="C396" s="11"/>
-      <c r="D396" s="11"/>
-      <c r="E396" s="11"/>
-    </row>
-    <row r="397" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D396" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E396" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G396" s="8">
+        <v>18</v>
+      </c>
+      <c r="H396" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I396" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>13</v>
+      </c>
+      <c r="B397" t="s">
+        <v>15</v>
+      </c>
       <c r="C397" s="11"/>
-      <c r="D397" s="11"/>
-      <c r="E397" s="11"/>
-    </row>
-    <row r="398" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D397" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E397" s="11">
+        <v>3020</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G397" s="8">
+        <v>18</v>
+      </c>
+      <c r="H397" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I397" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>112</v>
+      </c>
+      <c r="B398" t="s">
+        <v>15</v>
+      </c>
       <c r="C398" s="11"/>
-      <c r="D398" s="11"/>
-      <c r="E398" s="11"/>
-    </row>
-    <row r="399" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D398" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E398" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F398" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G398" s="8">
+        <v>18</v>
+      </c>
+      <c r="H398" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I398" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>25</v>
+      </c>
+      <c r="B399" t="s">
+        <v>15</v>
+      </c>
       <c r="C399" s="11"/>
-      <c r="D399" s="11"/>
-      <c r="E399" s="11"/>
-    </row>
-    <row r="400" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D399" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E399" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F399" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G399" s="8">
+        <v>18</v>
+      </c>
+      <c r="H399" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I399" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>19</v>
+      </c>
+      <c r="B400" t="s">
+        <v>15</v>
+      </c>
       <c r="C400" s="11"/>
-      <c r="D400" s="11"/>
-      <c r="E400" s="11"/>
-    </row>
-    <row r="401" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D400" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E400" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F400" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G400" s="8">
+        <v>18</v>
+      </c>
+      <c r="H400" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I400" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>21</v>
+      </c>
+      <c r="B401" t="s">
+        <v>15</v>
+      </c>
       <c r="C401" s="11"/>
-      <c r="D401" s="11"/>
-      <c r="E401" s="11"/>
-    </row>
-    <row r="402" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D401" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E401" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G401" s="8">
+        <v>18</v>
+      </c>
+      <c r="H401" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I401" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>51</v>
+      </c>
+      <c r="B402" t="s">
+        <v>15</v>
+      </c>
       <c r="C402" s="11"/>
-      <c r="D402" s="11"/>
-      <c r="E402" s="11"/>
-    </row>
-    <row r="403" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D402" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E402" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G402" s="8">
+        <v>18</v>
+      </c>
+      <c r="H402" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I402" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>53</v>
+      </c>
+      <c r="B403" t="s">
+        <v>15</v>
+      </c>
       <c r="C403" s="11"/>
-      <c r="D403" s="11"/>
-      <c r="E403" s="11"/>
-    </row>
-    <row r="404" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D403" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E403" s="11">
+        <v>3440</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G403" s="8">
+        <v>18</v>
+      </c>
+      <c r="H403" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I403" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>113</v>
+      </c>
+      <c r="B404" t="s">
+        <v>15</v>
+      </c>
       <c r="C404" s="11"/>
-      <c r="D404" s="11"/>
-      <c r="E404" s="11"/>
-    </row>
-    <row r="405" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D404" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E404" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G404" s="8">
+        <v>18</v>
+      </c>
+      <c r="H404" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I404" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>16</v>
+      </c>
+      <c r="B405" t="s">
+        <v>15</v>
+      </c>
       <c r="C405" s="11"/>
-      <c r="D405" s="11"/>
-      <c r="E405" s="11"/>
-    </row>
-    <row r="406" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D405" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E405" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G405" s="8">
+        <v>18</v>
+      </c>
+      <c r="H405" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I405" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B406" t="s">
+        <v>15</v>
+      </c>
       <c r="C406" s="11"/>
-      <c r="D406" s="11"/>
-      <c r="E406" s="11"/>
-    </row>
-    <row r="407" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D406" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E406" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G406" s="8">
+        <v>18</v>
+      </c>
+      <c r="H406" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I406" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>20</v>
+      </c>
+      <c r="B407" t="s">
+        <v>15</v>
+      </c>
       <c r="C407" s="11"/>
-      <c r="D407" s="11"/>
-      <c r="E407" s="11"/>
-    </row>
-    <row r="408" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D407" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E407" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G407" s="8">
+        <v>18</v>
+      </c>
+      <c r="H407" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I407" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>55</v>
+      </c>
+      <c r="B408" t="s">
+        <v>15</v>
+      </c>
       <c r="C408" s="11"/>
-      <c r="D408" s="11"/>
-      <c r="E408" s="11"/>
-    </row>
-    <row r="409" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D408" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E408" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G408" s="8">
+        <v>18</v>
+      </c>
+      <c r="H408" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I408" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>31</v>
+      </c>
+      <c r="B409" t="s">
+        <v>15</v>
+      </c>
       <c r="C409" s="11"/>
-      <c r="D409" s="11"/>
-      <c r="E409" s="11"/>
-    </row>
-    <row r="410" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D409" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E409" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G409" s="8">
+        <v>18</v>
+      </c>
+      <c r="H409" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I409" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>54</v>
+      </c>
+      <c r="B410" t="s">
+        <v>15</v>
+      </c>
       <c r="C410" s="11"/>
-      <c r="D410" s="11"/>
-      <c r="E410" s="11"/>
-    </row>
-    <row r="411" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D410" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E410" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F410" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G410" s="8">
+        <v>18</v>
+      </c>
+      <c r="H410" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I410" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>26</v>
+      </c>
+      <c r="B411" t="s">
+        <v>15</v>
+      </c>
       <c r="C411" s="11"/>
-      <c r="D411" s="11"/>
-      <c r="E411" s="11"/>
-    </row>
-    <row r="412" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D411" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E411" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G411" s="8">
+        <v>18</v>
+      </c>
+      <c r="H411" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I411" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>49</v>
+      </c>
+      <c r="B412" t="s">
+        <v>15</v>
+      </c>
       <c r="C412" s="11"/>
-      <c r="D412" s="11"/>
-      <c r="E412" s="11"/>
-    </row>
-    <row r="413" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C413" s="11"/>
-      <c r="D413" s="11"/>
-      <c r="E413" s="11"/>
-    </row>
-    <row r="414" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C414" s="11"/>
-      <c r="D414" s="11"/>
-      <c r="E414" s="11"/>
-    </row>
-    <row r="415" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D412" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E412" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G412" s="8">
+        <v>18</v>
+      </c>
+      <c r="H412" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I412" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>5</v>
+      </c>
+      <c r="B413" t="s">
+        <v>15</v>
+      </c>
+      <c r="C413" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D413" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E413" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G413" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H413" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I413" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>4</v>
+      </c>
+      <c r="B414" t="s">
+        <v>15</v>
+      </c>
+      <c r="C414" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D414" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E414" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F414" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G414" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H414" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I414" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>107</v>
+      </c>
+      <c r="B415" t="s">
+        <v>15</v>
+      </c>
       <c r="C415" s="11"/>
-      <c r="D415" s="11"/>
-      <c r="E415" s="11"/>
-    </row>
-    <row r="416" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D415" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E415" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F415" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G415" s="8">
+        <v>19</v>
+      </c>
+      <c r="H415" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I415" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>108</v>
+      </c>
+      <c r="B416" t="s">
+        <v>15</v>
+      </c>
       <c r="C416" s="11"/>
-      <c r="D416" s="11"/>
-      <c r="E416" s="11"/>
-    </row>
-    <row r="417" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D416" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E416" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F416" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G416" s="8">
+        <v>19</v>
+      </c>
+      <c r="H416" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I416" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>109</v>
+      </c>
+      <c r="B417" t="s">
+        <v>15</v>
+      </c>
       <c r="C417" s="11"/>
-      <c r="D417" s="11"/>
-      <c r="E417" s="11"/>
-    </row>
-    <row r="418" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D417" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E417" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F417" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G417" s="8">
+        <v>19</v>
+      </c>
+      <c r="H417" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I417" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>52</v>
+      </c>
+      <c r="B418" t="s">
+        <v>15</v>
+      </c>
       <c r="C418" s="11"/>
-      <c r="D418" s="11"/>
-      <c r="E418" s="11"/>
-    </row>
-    <row r="419" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D418" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E418" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G418" s="8">
+        <v>19</v>
+      </c>
+      <c r="H418" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I418" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>50</v>
+      </c>
+      <c r="B419" t="s">
+        <v>15</v>
+      </c>
       <c r="C419" s="11"/>
-      <c r="D419" s="11"/>
-      <c r="E419" s="11"/>
-    </row>
-    <row r="420" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D419" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E419" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G419" s="8">
+        <v>19</v>
+      </c>
+      <c r="H419" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I419" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>29</v>
+      </c>
+      <c r="B420" t="s">
+        <v>15</v>
+      </c>
       <c r="C420" s="11"/>
-      <c r="D420" s="11"/>
-      <c r="E420" s="11"/>
-    </row>
-    <row r="421" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D420" s="11">
+        <v>3170</v>
+      </c>
+      <c r="E420" s="11">
+        <v>3360</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G420" s="8">
+        <v>19</v>
+      </c>
+      <c r="H420" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I420" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>115</v>
+      </c>
+      <c r="B421" t="s">
+        <v>15</v>
+      </c>
       <c r="C421" s="11"/>
-      <c r="D421" s="11"/>
-      <c r="E421" s="11"/>
-    </row>
-    <row r="422" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D421" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E421" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F421" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G421" s="8">
+        <v>19</v>
+      </c>
+      <c r="H421" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I421" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>110</v>
+      </c>
+      <c r="B422" t="s">
+        <v>15</v>
+      </c>
       <c r="C422" s="11"/>
-      <c r="D422" s="11"/>
-      <c r="E422" s="11"/>
-    </row>
-    <row r="423" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D422" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E422" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F422" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G422" s="8">
+        <v>19</v>
+      </c>
+      <c r="H422" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I422" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>27</v>
+      </c>
+      <c r="B423" t="s">
+        <v>15</v>
+      </c>
       <c r="C423" s="11"/>
-      <c r="D423" s="11"/>
-      <c r="E423" s="11"/>
-    </row>
-    <row r="424" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D423" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E423" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F423" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G423" s="8">
+        <v>19</v>
+      </c>
+      <c r="H423" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I423" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>48</v>
+      </c>
+      <c r="B424" t="s">
+        <v>15</v>
+      </c>
       <c r="C424" s="11"/>
-      <c r="D424" s="11"/>
-      <c r="E424" s="11"/>
-    </row>
-    <row r="425" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D424" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E424" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F424" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G424" s="8">
+        <v>19</v>
+      </c>
+      <c r="H424" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I424" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>111</v>
+      </c>
+      <c r="B425" t="s">
+        <v>15</v>
+      </c>
       <c r="C425" s="11"/>
-      <c r="D425" s="11"/>
-      <c r="E425" s="11"/>
-    </row>
-    <row r="426" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D425" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E425" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F425" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G425" s="8">
+        <v>19</v>
+      </c>
+      <c r="H425" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I425" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>28</v>
+      </c>
+      <c r="B426" t="s">
+        <v>15</v>
+      </c>
       <c r="C426" s="11"/>
-      <c r="D426" s="11"/>
-      <c r="E426" s="11"/>
-    </row>
-    <row r="427" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D426" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E426" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F426" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G426" s="8">
+        <v>19</v>
+      </c>
+      <c r="H426" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I426" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>112</v>
+      </c>
+      <c r="B427" t="s">
+        <v>15</v>
+      </c>
       <c r="C427" s="11"/>
-      <c r="D427" s="11"/>
-      <c r="E427" s="11"/>
-    </row>
-    <row r="428" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D427" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E427" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F427" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G427" s="8">
+        <v>19</v>
+      </c>
+      <c r="H427" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I427" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>116</v>
+      </c>
+      <c r="B428" t="s">
+        <v>15</v>
+      </c>
       <c r="C428" s="11"/>
-      <c r="D428" s="11"/>
-      <c r="E428" s="11"/>
-    </row>
-    <row r="429" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D428" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E428" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F428" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G428" s="8">
+        <v>19</v>
+      </c>
+      <c r="H428" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I428" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>25</v>
+      </c>
+      <c r="B429" t="s">
+        <v>15</v>
+      </c>
       <c r="C429" s="11"/>
-      <c r="D429" s="11"/>
-      <c r="E429" s="11"/>
-    </row>
-    <row r="430" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C430" s="11"/>
-      <c r="D430" s="11"/>
-      <c r="E430" s="11"/>
-    </row>
-    <row r="431" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C431" s="11"/>
-      <c r="D431" s="11"/>
-      <c r="E431" s="11"/>
-    </row>
-    <row r="432" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D429" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E429" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F429" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G429" s="8">
+        <v>19</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I429" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>19</v>
+      </c>
+      <c r="B430" t="s">
+        <v>15</v>
+      </c>
+      <c r="C430" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D430" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E430" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F430" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G430" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I430" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>21</v>
+      </c>
+      <c r="B431" t="s">
+        <v>15</v>
+      </c>
+      <c r="C431" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D431" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E431" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G431" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I431" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>51</v>
+      </c>
+      <c r="B432" t="s">
+        <v>15</v>
+      </c>
       <c r="C432" s="11"/>
-      <c r="D432" s="11"/>
-      <c r="E432" s="11"/>
-    </row>
-    <row r="433" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D432" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E432" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G432" s="8">
+        <v>19</v>
+      </c>
+      <c r="H432" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I432" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>113</v>
+      </c>
+      <c r="B433" t="s">
+        <v>15</v>
+      </c>
       <c r="C433" s="11"/>
-      <c r="D433" s="11"/>
-      <c r="E433" s="11"/>
-    </row>
-    <row r="434" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D433" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E433" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G433" s="8">
+        <v>19</v>
+      </c>
+      <c r="H433" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I433" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>16</v>
+      </c>
+      <c r="B434" t="s">
+        <v>15</v>
+      </c>
       <c r="C434" s="11"/>
-      <c r="D434" s="11"/>
-      <c r="E434" s="11"/>
-    </row>
-    <row r="435" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D434" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E434" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G434" s="8">
+        <v>19</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>26</v>
+      </c>
+      <c r="B435" t="s">
+        <v>15</v>
+      </c>
       <c r="C435" s="11"/>
-      <c r="D435" s="11"/>
-      <c r="E435" s="11"/>
-    </row>
-    <row r="436" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D435" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E435" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G435" s="8">
+        <v>19</v>
+      </c>
+      <c r="H435" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I435" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>49</v>
+      </c>
+      <c r="B436" t="s">
+        <v>15</v>
+      </c>
       <c r="C436" s="11"/>
-      <c r="D436" s="11"/>
-      <c r="E436" s="11"/>
-    </row>
-    <row r="437" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D436" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E436" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G436" s="8">
+        <v>19</v>
+      </c>
+      <c r="H436" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>5</v>
+      </c>
+      <c r="B437" t="s">
+        <v>15</v>
+      </c>
       <c r="C437" s="11"/>
-      <c r="D437" s="11"/>
-      <c r="E437" s="11"/>
-    </row>
-    <row r="438" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D437" s="11">
+        <v>2820</v>
+      </c>
+      <c r="E437" s="11">
+        <v>2970</v>
+      </c>
+      <c r="F437" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G437" s="8">
+        <v>18</v>
+      </c>
+      <c r="H437" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I437" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>4</v>
+      </c>
+      <c r="B438" t="s">
+        <v>15</v>
+      </c>
       <c r="C438" s="11"/>
-      <c r="D438" s="11"/>
-      <c r="E438" s="11"/>
-    </row>
-    <row r="439" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D438" s="11">
+        <v>2820</v>
+      </c>
+      <c r="E438" s="11">
+        <v>2970</v>
+      </c>
+      <c r="F438" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G438" s="8">
+        <v>18</v>
+      </c>
+      <c r="H438" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I438" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>13</v>
+      </c>
+      <c r="B439" t="s">
+        <v>15</v>
+      </c>
       <c r="C439" s="11"/>
-      <c r="D439" s="11"/>
-      <c r="E439" s="11"/>
-    </row>
-    <row r="440" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D439" s="11">
+        <v>2870</v>
+      </c>
+      <c r="E439" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G439" s="8">
+        <v>18</v>
+      </c>
+      <c r="H439" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I439" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A440" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B440" t="s">
+        <v>15</v>
+      </c>
       <c r="C440" s="11"/>
-      <c r="D440" s="11"/>
-      <c r="E440" s="11"/>
-    </row>
-    <row r="441" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D440" s="11">
+        <v>2820</v>
+      </c>
+      <c r="E440" s="11">
+        <v>2970</v>
+      </c>
+      <c r="F440" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G440" s="8">
+        <v>18</v>
+      </c>
+      <c r="H440" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I440" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>30</v>
+      </c>
+      <c r="B441" t="s">
+        <v>15</v>
+      </c>
       <c r="C441" s="11"/>
-      <c r="D441" s="11"/>
-      <c r="E441" s="11"/>
-    </row>
-    <row r="442" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D441" s="11">
+        <v>2920</v>
+      </c>
+      <c r="E441" s="11">
+        <v>3180</v>
+      </c>
+      <c r="F441" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G441" s="8">
+        <v>18</v>
+      </c>
+      <c r="H441" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I441" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>24</v>
+      </c>
+      <c r="B442" t="s">
+        <v>15</v>
+      </c>
       <c r="C442" s="11"/>
-      <c r="D442" s="11"/>
-      <c r="E442" s="11"/>
-    </row>
-    <row r="443" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D442" s="11">
+        <v>2920</v>
+      </c>
+      <c r="E442" s="11">
+        <v>3080</v>
+      </c>
+      <c r="F442" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G442" s="8">
+        <v>18</v>
+      </c>
+      <c r="H442" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I442" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C443" s="11"/>
       <c r="D443" s="11"/>
       <c r="E443" s="11"/>
-    </row>
-    <row r="444" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="F443" s="7"/>
+      <c r="G443" s="8"/>
+      <c r="H443" s="7"/>
+      <c r="I443" s="7"/>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C444" s="11"/>
       <c r="D444" s="11"/>
       <c r="E444" s="11"/>
-    </row>
-    <row r="445" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="F444" s="7"/>
+      <c r="G444" s="8"/>
+      <c r="H444" s="7"/>
+      <c r="I444" s="7"/>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C445" s="11"/>
       <c r="D445" s="11"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C446" s="11"/>
       <c r="D446" s="11"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C447" s="11"/>
       <c r="D447" s="11"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C448" s="11"/>
       <c r="D448" s="11"/>
       <c r="E448" s="11"/>
@@ -13634,223 +17657,8 @@
       <c r="D1327" s="11"/>
       <c r="E1327" s="11"/>
     </row>
-    <row r="1328" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1328" s="11"/>
-      <c r="D1328" s="11"/>
-      <c r="E1328" s="11"/>
-    </row>
-    <row r="1329" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1329" s="11"/>
-      <c r="D1329" s="11"/>
-      <c r="E1329" s="11"/>
-    </row>
-    <row r="1330" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1330" s="11"/>
-      <c r="D1330" s="11"/>
-      <c r="E1330" s="11"/>
-    </row>
-    <row r="1331" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1331" s="11"/>
-      <c r="D1331" s="11"/>
-      <c r="E1331" s="11"/>
-    </row>
-    <row r="1332" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1332" s="11"/>
-      <c r="D1332" s="11"/>
-      <c r="E1332" s="11"/>
-    </row>
-    <row r="1333" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1333" s="11"/>
-      <c r="D1333" s="11"/>
-      <c r="E1333" s="11"/>
-    </row>
-    <row r="1334" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1334" s="11"/>
-      <c r="D1334" s="11"/>
-      <c r="E1334" s="11"/>
-    </row>
-    <row r="1335" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1335" s="11"/>
-      <c r="D1335" s="11"/>
-      <c r="E1335" s="11"/>
-    </row>
-    <row r="1336" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1336" s="11"/>
-      <c r="D1336" s="11"/>
-      <c r="E1336" s="11"/>
-    </row>
-    <row r="1337" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1337" s="11"/>
-      <c r="D1337" s="11"/>
-      <c r="E1337" s="11"/>
-    </row>
-    <row r="1338" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1338" s="11"/>
-      <c r="D1338" s="11"/>
-      <c r="E1338" s="11"/>
-    </row>
-    <row r="1339" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1339" s="11"/>
-      <c r="D1339" s="11"/>
-      <c r="E1339" s="11"/>
-    </row>
-    <row r="1340" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1340" s="11"/>
-      <c r="D1340" s="11"/>
-      <c r="E1340" s="11"/>
-    </row>
-    <row r="1341" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1341" s="11"/>
-      <c r="D1341" s="11"/>
-      <c r="E1341" s="11"/>
-    </row>
-    <row r="1342" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1342" s="11"/>
-      <c r="D1342" s="11"/>
-      <c r="E1342" s="11"/>
-    </row>
-    <row r="1343" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1343" s="11"/>
-      <c r="D1343" s="11"/>
-      <c r="E1343" s="11"/>
-    </row>
-    <row r="1344" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1344" s="11"/>
-      <c r="D1344" s="11"/>
-      <c r="E1344" s="11"/>
-    </row>
-    <row r="1345" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1345" s="11"/>
-      <c r="D1345" s="11"/>
-      <c r="E1345" s="11"/>
-    </row>
-    <row r="1346" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1346" s="11"/>
-      <c r="D1346" s="11"/>
-      <c r="E1346" s="11"/>
-    </row>
-    <row r="1347" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1347" s="11"/>
-      <c r="D1347" s="11"/>
-      <c r="E1347" s="11"/>
-    </row>
-    <row r="1348" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1348" s="11"/>
-      <c r="D1348" s="11"/>
-      <c r="E1348" s="11"/>
-    </row>
-    <row r="1349" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1349" s="11"/>
-      <c r="D1349" s="11"/>
-      <c r="E1349" s="11"/>
-    </row>
-    <row r="1350" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1350" s="11"/>
-      <c r="D1350" s="11"/>
-      <c r="E1350" s="11"/>
-    </row>
-    <row r="1351" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1351" s="11"/>
-      <c r="D1351" s="11"/>
-      <c r="E1351" s="11"/>
-    </row>
-    <row r="1352" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1352" s="11"/>
-      <c r="D1352" s="11"/>
-      <c r="E1352" s="11"/>
-    </row>
-    <row r="1353" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1353" s="11"/>
-      <c r="D1353" s="11"/>
-      <c r="E1353" s="11"/>
-    </row>
-    <row r="1354" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1354" s="11"/>
-      <c r="D1354" s="11"/>
-      <c r="E1354" s="11"/>
-    </row>
-    <row r="1355" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1355" s="11"/>
-      <c r="D1355" s="11"/>
-      <c r="E1355" s="11"/>
-    </row>
-    <row r="1356" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1356" s="11"/>
-      <c r="D1356" s="11"/>
-      <c r="E1356" s="11"/>
-    </row>
-    <row r="1357" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1357" s="11"/>
-      <c r="D1357" s="11"/>
-      <c r="E1357" s="11"/>
-    </row>
-    <row r="1358" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1358" s="11"/>
-      <c r="D1358" s="11"/>
-      <c r="E1358" s="11"/>
-    </row>
-    <row r="1359" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1359" s="11"/>
-      <c r="D1359" s="11"/>
-      <c r="E1359" s="11"/>
-    </row>
-    <row r="1360" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1360" s="11"/>
-      <c r="D1360" s="11"/>
-      <c r="E1360" s="11"/>
-    </row>
-    <row r="1361" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1361" s="11"/>
-      <c r="D1361" s="11"/>
-      <c r="E1361" s="11"/>
-    </row>
-    <row r="1362" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1362" s="11"/>
-      <c r="D1362" s="11"/>
-      <c r="E1362" s="11"/>
-    </row>
-    <row r="1363" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1363" s="11"/>
-      <c r="D1363" s="11"/>
-      <c r="E1363" s="11"/>
-    </row>
-    <row r="1364" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1364" s="11"/>
-      <c r="D1364" s="11"/>
-      <c r="E1364" s="11"/>
-    </row>
-    <row r="1365" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1365" s="11"/>
-      <c r="D1365" s="11"/>
-      <c r="E1365" s="11"/>
-    </row>
-    <row r="1366" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1366" s="11"/>
-      <c r="D1366" s="11"/>
-      <c r="E1366" s="11"/>
-    </row>
-    <row r="1367" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1367" s="11"/>
-      <c r="D1367" s="11"/>
-      <c r="E1367" s="11"/>
-    </row>
-    <row r="1368" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1368" s="11"/>
-      <c r="D1368" s="11"/>
-      <c r="E1368" s="11"/>
-    </row>
-    <row r="1369" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1369" s="11"/>
-      <c r="D1369" s="11"/>
-      <c r="E1369" s="11"/>
-    </row>
-    <row r="1370" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1370" s="11"/>
-      <c r="D1370" s="11"/>
-      <c r="E1370" s="11"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I252" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
+  <autoFilter ref="A1:I442" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{243EC0F9-4332-45F5-97A7-319609B854C5}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01FE64C9-3FC2-40A2-A937-D86919374F89}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$442</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$344</definedName>
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="153">
   <si>
     <t>POD</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t>ONE</t>
+  </si>
+  <si>
+    <t>XINGANG(TIANJIN)</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:M1327"/>
+  <dimension ref="A1:M1228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -11273,8 +11276,8 @@
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A371" s="7" t="s">
-        <v>120</v>
+      <c r="A371" t="s">
+        <v>152</v>
       </c>
       <c r="B371" t="s">
         <v>62</v>
@@ -11495,21 +11498,23 @@
       <c r="B379" t="s">
         <v>15</v>
       </c>
-      <c r="C379" s="11"/>
+      <c r="C379" s="11">
+        <v>2460</v>
+      </c>
       <c r="D379" s="11">
-        <v>2700</v>
+        <v>2670</v>
       </c>
       <c r="E379" s="11">
-        <v>2810</v>
+        <v>2880</v>
       </c>
       <c r="F379" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G379" s="8">
-        <v>18</v>
+      <c r="G379" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="H379" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I379" s="7" t="s">
         <v>118</v>
@@ -11524,19 +11529,19 @@
       </c>
       <c r="C380" s="11"/>
       <c r="D380" s="11">
-        <v>2700</v>
+        <v>2670</v>
       </c>
       <c r="E380" s="11">
-        <v>2810</v>
+        <v>2880</v>
       </c>
       <c r="F380" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G380" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I380" s="7" t="s">
         <v>118</v>
@@ -11551,19 +11556,19 @@
       </c>
       <c r="C381" s="11"/>
       <c r="D381" s="11">
-        <v>2700</v>
+        <v>2670</v>
       </c>
       <c r="E381" s="11">
-        <v>2810</v>
+        <v>2880</v>
       </c>
       <c r="F381" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G381" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I381" s="7" t="s">
         <v>118</v>
@@ -11571,26 +11576,26 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="B382" t="s">
         <v>15</v>
       </c>
       <c r="C382" s="11"/>
       <c r="D382" s="11">
-        <v>2700</v>
+        <v>2780</v>
       </c>
       <c r="E382" s="11">
-        <v>2810</v>
+        <v>3040</v>
       </c>
       <c r="F382" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G382" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H382" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I382" s="7" t="s">
         <v>118</v>
@@ -11598,26 +11603,26 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="B383" t="s">
         <v>15</v>
       </c>
       <c r="C383" s="11"/>
       <c r="D383" s="11">
-        <v>2750</v>
+        <v>2950</v>
       </c>
       <c r="E383" s="11">
-        <v>2860</v>
+        <v>3440</v>
       </c>
       <c r="F383" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G383" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H383" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I383" s="7" t="s">
         <v>118</v>
@@ -11625,26 +11630,26 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B384" t="s">
         <v>15</v>
       </c>
       <c r="C384" s="11"/>
       <c r="D384" s="11">
-        <v>2860</v>
+        <v>2720</v>
       </c>
       <c r="E384" s="11">
-        <v>3070</v>
+        <v>2980</v>
       </c>
       <c r="F384" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G384" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H384" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I384" s="7" t="s">
         <v>118</v>
@@ -11652,26 +11657,26 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B385" t="s">
         <v>15</v>
       </c>
       <c r="C385" s="11"/>
       <c r="D385" s="11">
-        <v>3170</v>
+        <v>2780</v>
       </c>
       <c r="E385" s="11">
-        <v>3750</v>
+        <v>3060</v>
       </c>
       <c r="F385" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G385" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H385" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I385" s="7" t="s">
         <v>118</v>
@@ -11679,26 +11684,26 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B386" t="s">
         <v>15</v>
       </c>
       <c r="C386" s="11"/>
       <c r="D386" s="11">
-        <v>2750</v>
+        <v>2720</v>
       </c>
       <c r="E386" s="11">
-        <v>2910</v>
+        <v>2980</v>
       </c>
       <c r="F386" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G386" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H386" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I386" s="7" t="s">
         <v>118</v>
@@ -11706,26 +11711,26 @@
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="B387" t="s">
         <v>15</v>
       </c>
       <c r="C387" s="11"/>
       <c r="D387" s="11">
-        <v>2860</v>
+        <v>2820</v>
       </c>
       <c r="E387" s="11">
-        <v>3070</v>
+        <v>3090</v>
       </c>
       <c r="F387" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G387" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H387" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I387" s="7" t="s">
         <v>118</v>
@@ -11733,26 +11738,26 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="B388" t="s">
         <v>15</v>
       </c>
       <c r="C388" s="11"/>
       <c r="D388" s="11">
-        <v>2910</v>
+        <v>2770</v>
       </c>
       <c r="E388" s="11">
-        <v>3230</v>
+        <v>3070</v>
       </c>
       <c r="F388" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G388" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H388" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I388" s="7" t="s">
         <v>118</v>
@@ -11767,19 +11772,19 @@
       </c>
       <c r="C389" s="11"/>
       <c r="D389" s="11">
-        <v>2810</v>
+        <v>2770</v>
       </c>
       <c r="E389" s="11">
-        <v>3020</v>
+        <v>3090</v>
       </c>
       <c r="F389" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G389" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H389" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I389" s="7" t="s">
         <v>118</v>
@@ -11794,19 +11799,19 @@
       </c>
       <c r="C390" s="11"/>
       <c r="D390" s="11">
-        <v>2860</v>
+        <v>2780</v>
       </c>
       <c r="E390" s="11">
-        <v>3070</v>
+        <v>3050</v>
       </c>
       <c r="F390" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G390" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H390" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I390" s="7" t="s">
         <v>118</v>
@@ -11821,19 +11826,19 @@
       </c>
       <c r="C391" s="11"/>
       <c r="D391" s="11">
-        <v>2960</v>
+        <v>2850</v>
       </c>
       <c r="E391" s="11">
-        <v>3330</v>
+        <v>3190</v>
       </c>
       <c r="F391" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G391" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H391" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I391" s="7" t="s">
         <v>118</v>
@@ -11841,26 +11846,26 @@
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>111</v>
+        <v>30</v>
       </c>
       <c r="B392" t="s">
         <v>15</v>
       </c>
       <c r="C392" s="11"/>
       <c r="D392" s="11">
-        <v>2960</v>
+        <v>2770</v>
       </c>
       <c r="E392" s="11">
-        <v>3330</v>
+        <v>3090</v>
       </c>
       <c r="F392" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G392" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H392" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I392" s="7" t="s">
         <v>118</v>
@@ -11868,26 +11873,26 @@
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>30</v>
+        <v>147</v>
       </c>
       <c r="B393" t="s">
         <v>15</v>
       </c>
       <c r="C393" s="11"/>
       <c r="D393" s="11">
-        <v>3070</v>
+        <v>2770</v>
       </c>
       <c r="E393" s="11">
-        <v>3540</v>
+        <v>3060</v>
       </c>
       <c r="F393" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G393" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H393" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I393" s="7" t="s">
         <v>118</v>
@@ -11902,19 +11907,19 @@
       </c>
       <c r="C394" s="11"/>
       <c r="D394" s="11">
-        <v>2860</v>
+        <v>2790</v>
       </c>
       <c r="E394" s="11">
-        <v>3120</v>
+        <v>3030</v>
       </c>
       <c r="F394" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G394" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H394" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I394" s="7" t="s">
         <v>118</v>
@@ -11922,26 +11927,26 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B395" t="s">
         <v>15</v>
       </c>
       <c r="C395" s="11"/>
       <c r="D395" s="11">
-        <v>2860</v>
+        <v>2910</v>
       </c>
       <c r="E395" s="11">
-        <v>3070</v>
+        <v>3300</v>
       </c>
       <c r="F395" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G395" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H395" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I395" s="7" t="s">
         <v>118</v>
@@ -11949,26 +11954,26 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="B396" t="s">
         <v>15</v>
       </c>
       <c r="C396" s="11"/>
       <c r="D396" s="11">
-        <v>2910</v>
+        <v>2780</v>
       </c>
       <c r="E396" s="11">
-        <v>3230</v>
+        <v>3060</v>
       </c>
       <c r="F396" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G396" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H396" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I396" s="7" t="s">
         <v>118</v>
@@ -11976,26 +11981,26 @@
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="B397" t="s">
         <v>15</v>
       </c>
       <c r="C397" s="11"/>
       <c r="D397" s="11">
-        <v>2810</v>
+        <v>2770</v>
       </c>
       <c r="E397" s="11">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="F397" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G397" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H397" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I397" s="7" t="s">
         <v>118</v>
@@ -12003,26 +12008,26 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="B398" t="s">
         <v>15</v>
       </c>
       <c r="C398" s="11"/>
       <c r="D398" s="11">
-        <v>2860</v>
+        <v>2720</v>
       </c>
       <c r="E398" s="11">
-        <v>3070</v>
+        <v>2980</v>
       </c>
       <c r="F398" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G398" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H398" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I398" s="7" t="s">
         <v>118</v>
@@ -12030,26 +12035,26 @@
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>25</v>
+        <v>112</v>
       </c>
       <c r="B399" t="s">
         <v>15</v>
       </c>
       <c r="C399" s="11"/>
       <c r="D399" s="11">
-        <v>2860</v>
+        <v>2780</v>
       </c>
       <c r="E399" s="11">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="F399" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G399" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H399" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I399" s="7" t="s">
         <v>118</v>
@@ -12057,26 +12062,26 @@
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>19</v>
+        <v>116</v>
       </c>
       <c r="B400" t="s">
         <v>15</v>
       </c>
       <c r="C400" s="11"/>
       <c r="D400" s="11">
-        <v>2750</v>
+        <v>2770</v>
       </c>
       <c r="E400" s="11">
-        <v>2910</v>
+        <v>3040</v>
       </c>
       <c r="F400" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G400" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H400" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I400" s="7" t="s">
         <v>118</v>
@@ -12084,26 +12089,26 @@
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B401" t="s">
         <v>15</v>
       </c>
       <c r="C401" s="11"/>
       <c r="D401" s="11">
-        <v>2700</v>
+        <v>2810</v>
       </c>
       <c r="E401" s="11">
-        <v>2810</v>
+        <v>3150</v>
       </c>
       <c r="F401" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G401" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H401" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I401" s="7" t="s">
         <v>118</v>
@@ -12111,26 +12116,26 @@
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="B402" t="s">
         <v>15</v>
       </c>
       <c r="C402" s="11"/>
       <c r="D402" s="11">
-        <v>2860</v>
+        <v>2670</v>
       </c>
       <c r="E402" s="11">
-        <v>3070</v>
+        <v>2880</v>
       </c>
       <c r="F402" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G402" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H402" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I402" s="7" t="s">
         <v>118</v>
@@ -12138,26 +12143,26 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B403" t="s">
         <v>15</v>
       </c>
       <c r="C403" s="11"/>
       <c r="D403" s="11">
-        <v>3020</v>
+        <v>2670</v>
       </c>
       <c r="E403" s="11">
-        <v>3440</v>
+        <v>2880</v>
       </c>
       <c r="F403" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G403" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H403" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I403" s="7" t="s">
         <v>118</v>
@@ -12165,26 +12170,26 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>113</v>
+        <v>51</v>
       </c>
       <c r="B404" t="s">
         <v>15</v>
       </c>
       <c r="C404" s="11"/>
       <c r="D404" s="11">
-        <v>2860</v>
+        <v>2780</v>
       </c>
       <c r="E404" s="11">
-        <v>3070</v>
+        <v>3060</v>
       </c>
       <c r="F404" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G404" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H404" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I404" s="7" t="s">
         <v>118</v>
@@ -12192,53 +12197,53 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="B405" t="s">
         <v>15</v>
       </c>
       <c r="C405" s="11"/>
       <c r="D405" s="11">
-        <v>2700</v>
+        <v>2850</v>
       </c>
       <c r="E405" s="11">
-        <v>2810</v>
+        <v>3180</v>
       </c>
       <c r="F405" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G405" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H405" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I405" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A406" s="7" t="s">
-        <v>120</v>
+      <c r="A406" t="s">
+        <v>32</v>
       </c>
       <c r="B406" t="s">
         <v>15</v>
       </c>
       <c r="C406" s="11"/>
       <c r="D406" s="11">
-        <v>2750</v>
+        <v>2810</v>
       </c>
       <c r="E406" s="11">
-        <v>2910</v>
+        <v>3090</v>
       </c>
       <c r="F406" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G406" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H406" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I406" s="7" t="s">
         <v>118</v>
@@ -12246,26 +12251,26 @@
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B407" t="s">
         <v>15</v>
       </c>
       <c r="C407" s="11"/>
       <c r="D407" s="11">
-        <v>2750</v>
+        <v>2720</v>
       </c>
       <c r="E407" s="11">
-        <v>2910</v>
+        <v>2980</v>
       </c>
       <c r="F407" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G407" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H407" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I407" s="7" t="s">
         <v>118</v>
@@ -12273,26 +12278,28 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>55</v>
+        <v>152</v>
       </c>
       <c r="B408" t="s">
         <v>15</v>
       </c>
-      <c r="C408" s="11"/>
+      <c r="C408" s="11">
+        <v>2460</v>
+      </c>
       <c r="D408" s="11">
-        <v>2910</v>
+        <v>2670</v>
       </c>
       <c r="E408" s="11">
-        <v>3230</v>
+        <v>2880</v>
       </c>
       <c r="F408" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G408" s="8">
-        <v>18</v>
+      <c r="G408" s="8" t="s">
+        <v>137</v>
       </c>
       <c r="H408" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I408" s="7" t="s">
         <v>118</v>
@@ -12300,26 +12307,26 @@
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="B409" t="s">
         <v>15</v>
       </c>
       <c r="C409" s="11"/>
       <c r="D409" s="11">
-        <v>2960</v>
+        <v>2770</v>
       </c>
       <c r="E409" s="11">
-        <v>3330</v>
+        <v>3030</v>
       </c>
       <c r="F409" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G409" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H409" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I409" s="7" t="s">
         <v>118</v>
@@ -12327,26 +12334,26 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="B410" t="s">
         <v>15</v>
       </c>
       <c r="C410" s="11"/>
       <c r="D410" s="11">
-        <v>2910</v>
+        <v>2670</v>
       </c>
       <c r="E410" s="11">
-        <v>3230</v>
+        <v>2880</v>
       </c>
       <c r="F410" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G410" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H410" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I410" s="7" t="s">
         <v>118</v>
@@ -12354,26 +12361,26 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>26</v>
+        <v>114</v>
       </c>
       <c r="B411" t="s">
         <v>15</v>
       </c>
       <c r="C411" s="11"/>
       <c r="D411" s="11">
-        <v>2860</v>
+        <v>2930</v>
       </c>
       <c r="E411" s="11">
-        <v>3070</v>
+        <v>3360</v>
       </c>
       <c r="F411" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G411" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H411" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I411" s="7" t="s">
         <v>118</v>
@@ -12381,26 +12388,26 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B412" t="s">
         <v>15</v>
       </c>
       <c r="C412" s="11"/>
       <c r="D412" s="11">
-        <v>2860</v>
+        <v>2770</v>
       </c>
       <c r="E412" s="11">
-        <v>3070</v>
+        <v>3030</v>
       </c>
       <c r="F412" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G412" s="8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H412" s="7" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I412" s="7" t="s">
         <v>118</v>
@@ -12408,28 +12415,26 @@
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="B413" t="s">
         <v>15</v>
       </c>
-      <c r="C413" s="11">
-        <v>2600</v>
-      </c>
+      <c r="C413" s="11"/>
       <c r="D413" s="11">
-        <v>2860</v>
+        <v>2770</v>
       </c>
       <c r="E413" s="11">
-        <v>2940</v>
+        <v>3090</v>
       </c>
       <c r="F413" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G413" s="8" t="s">
-        <v>119</v>
+      <c r="G413" s="8">
+        <v>17</v>
       </c>
       <c r="H413" s="7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I413" s="7" t="s">
         <v>118</v>
@@ -12437,28 +12442,26 @@
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B414" t="s">
         <v>15</v>
       </c>
-      <c r="C414" s="11">
-        <v>2600</v>
-      </c>
+      <c r="C414" s="11"/>
       <c r="D414" s="11">
-        <v>2860</v>
+        <v>2770</v>
       </c>
       <c r="E414" s="11">
-        <v>2940</v>
+        <v>3030</v>
       </c>
       <c r="F414" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G414" s="8" t="s">
-        <v>119</v>
+      <c r="G414" s="8">
+        <v>17</v>
       </c>
       <c r="H414" s="7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I414" s="7" t="s">
         <v>118</v>
@@ -12466,26 +12469,26 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>107</v>
+        <v>26</v>
       </c>
       <c r="B415" t="s">
         <v>15</v>
       </c>
       <c r="C415" s="11"/>
       <c r="D415" s="11">
-        <v>2860</v>
+        <v>2780</v>
       </c>
       <c r="E415" s="11">
-        <v>2940</v>
+        <v>3060</v>
       </c>
       <c r="F415" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G415" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H415" s="7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I415" s="7" t="s">
         <v>118</v>
@@ -12493,26 +12496,26 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="B416" t="s">
         <v>15</v>
       </c>
       <c r="C416" s="11"/>
       <c r="D416" s="11">
-        <v>2860</v>
+        <v>2790</v>
       </c>
       <c r="E416" s="11">
-        <v>2940</v>
+        <v>3060</v>
       </c>
       <c r="F416" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G416" s="8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H416" s="7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="I416" s="7" t="s">
         <v>118</v>
@@ -12520,26 +12523,26 @@
     </row>
     <row r="417" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>109</v>
+        <v>5</v>
       </c>
       <c r="B417" t="s">
         <v>15</v>
       </c>
       <c r="C417" s="11"/>
       <c r="D417" s="11">
-        <v>2960</v>
+        <v>2700</v>
       </c>
       <c r="E417" s="11">
-        <v>3100</v>
+        <v>2810</v>
       </c>
       <c r="F417" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G417" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H417" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I417" s="7" t="s">
         <v>118</v>
@@ -12547,26 +12550,26 @@
     </row>
     <row r="418" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B418" t="s">
         <v>15</v>
       </c>
       <c r="C418" s="11"/>
       <c r="D418" s="11">
-        <v>3020</v>
+        <v>2700</v>
       </c>
       <c r="E418" s="11">
-        <v>3250</v>
+        <v>2810</v>
       </c>
       <c r="F418" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G418" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H418" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I418" s="7" t="s">
         <v>118</v>
@@ -12574,26 +12577,26 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="B419" t="s">
         <v>15</v>
       </c>
       <c r="C419" s="11"/>
       <c r="D419" s="11">
-        <v>2960</v>
+        <v>2700</v>
       </c>
       <c r="E419" s="11">
-        <v>3150</v>
+        <v>2810</v>
       </c>
       <c r="F419" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G419" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H419" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I419" s="7" t="s">
         <v>118</v>
@@ -12601,26 +12604,26 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="B420" t="s">
         <v>15</v>
       </c>
       <c r="C420" s="11"/>
       <c r="D420" s="11">
-        <v>3170</v>
+        <v>2700</v>
       </c>
       <c r="E420" s="11">
-        <v>3360</v>
+        <v>2810</v>
       </c>
       <c r="F420" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G420" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H420" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I420" s="7" t="s">
         <v>118</v>
@@ -12628,26 +12631,26 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B421" t="s">
         <v>15</v>
       </c>
       <c r="C421" s="11"/>
       <c r="D421" s="11">
-        <v>2960</v>
+        <v>2750</v>
       </c>
       <c r="E421" s="11">
-        <v>3150</v>
+        <v>2860</v>
       </c>
       <c r="F421" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G421" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I421" s="7" t="s">
         <v>118</v>
@@ -12655,26 +12658,26 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>110</v>
+        <v>52</v>
       </c>
       <c r="B422" t="s">
         <v>15</v>
       </c>
       <c r="C422" s="11"/>
       <c r="D422" s="11">
-        <v>2960</v>
+        <v>2860</v>
       </c>
       <c r="E422" s="11">
-        <v>3150</v>
+        <v>3070</v>
       </c>
       <c r="F422" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G422" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H422" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I422" s="7" t="s">
         <v>118</v>
@@ -12682,26 +12685,26 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B423" t="s">
         <v>15</v>
       </c>
       <c r="C423" s="11"/>
       <c r="D423" s="11">
-        <v>2960</v>
+        <v>3170</v>
       </c>
       <c r="E423" s="11">
-        <v>3150</v>
+        <v>3750</v>
       </c>
       <c r="F423" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G423" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H423" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I423" s="7" t="s">
         <v>118</v>
@@ -12709,26 +12712,26 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B424" t="s">
         <v>15</v>
       </c>
       <c r="C424" s="11"/>
       <c r="D424" s="11">
-        <v>2960</v>
+        <v>2750</v>
       </c>
       <c r="E424" s="11">
-        <v>3150</v>
+        <v>2910</v>
       </c>
       <c r="F424" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G424" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H424" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I424" s="7" t="s">
         <v>118</v>
@@ -12736,26 +12739,26 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="B425" t="s">
         <v>15</v>
       </c>
       <c r="C425" s="11"/>
       <c r="D425" s="11">
-        <v>2960</v>
+        <v>2860</v>
       </c>
       <c r="E425" s="11">
-        <v>3150</v>
+        <v>3070</v>
       </c>
       <c r="F425" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G425" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H425" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I425" s="7" t="s">
         <v>118</v>
@@ -12763,26 +12766,26 @@
     </row>
     <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B426" t="s">
         <v>15</v>
       </c>
       <c r="C426" s="11"/>
       <c r="D426" s="11">
-        <v>2960</v>
+        <v>2910</v>
       </c>
       <c r="E426" s="11">
-        <v>3150</v>
+        <v>3230</v>
       </c>
       <c r="F426" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G426" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H426" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I426" s="7" t="s">
         <v>118</v>
@@ -12790,26 +12793,26 @@
     </row>
     <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="B427" t="s">
         <v>15</v>
       </c>
       <c r="C427" s="11"/>
       <c r="D427" s="11">
-        <v>2960</v>
+        <v>2810</v>
       </c>
       <c r="E427" s="11">
-        <v>3150</v>
+        <v>3020</v>
       </c>
       <c r="F427" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G427" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H427" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I427" s="7" t="s">
         <v>118</v>
@@ -12817,26 +12820,26 @@
     </row>
     <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>116</v>
+        <v>48</v>
       </c>
       <c r="B428" t="s">
         <v>15</v>
       </c>
       <c r="C428" s="11"/>
       <c r="D428" s="11">
-        <v>2960</v>
+        <v>2860</v>
       </c>
       <c r="E428" s="11">
-        <v>3150</v>
+        <v>3070</v>
       </c>
       <c r="F428" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G428" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H428" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I428" s="7" t="s">
         <v>118</v>
@@ -12844,26 +12847,26 @@
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B429" t="s">
         <v>15</v>
       </c>
       <c r="C429" s="11"/>
       <c r="D429" s="11">
-        <v>3020</v>
+        <v>2960</v>
       </c>
       <c r="E429" s="11">
-        <v>3250</v>
+        <v>3330</v>
       </c>
       <c r="F429" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G429" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H429" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I429" s="7" t="s">
         <v>118</v>
@@ -12871,28 +12874,26 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="B430" t="s">
         <v>15</v>
       </c>
-      <c r="C430" s="11">
-        <v>2600</v>
-      </c>
+      <c r="C430" s="11"/>
       <c r="D430" s="11">
-        <v>2860</v>
+        <v>2960</v>
       </c>
       <c r="E430" s="11">
-        <v>2940</v>
+        <v>3330</v>
       </c>
       <c r="F430" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G430" s="8" t="s">
-        <v>119</v>
+      <c r="G430" s="8">
+        <v>18</v>
       </c>
       <c r="H430" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I430" s="7" t="s">
         <v>118</v>
@@ -12900,28 +12901,26 @@
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B431" t="s">
         <v>15</v>
       </c>
-      <c r="C431" s="11">
-        <v>2600</v>
-      </c>
+      <c r="C431" s="11"/>
       <c r="D431" s="11">
-        <v>2860</v>
+        <v>3070</v>
       </c>
       <c r="E431" s="11">
-        <v>2940</v>
+        <v>3540</v>
       </c>
       <c r="F431" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G431" s="8" t="s">
-        <v>119</v>
+      <c r="G431" s="8">
+        <v>18</v>
       </c>
       <c r="H431" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I431" s="7" t="s">
         <v>118</v>
@@ -12929,26 +12928,26 @@
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B432" t="s">
         <v>15</v>
       </c>
       <c r="C432" s="11"/>
       <c r="D432" s="11">
-        <v>2960</v>
+        <v>2860</v>
       </c>
       <c r="E432" s="11">
-        <v>3150</v>
+        <v>3120</v>
       </c>
       <c r="F432" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G432" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H432" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I432" s="7" t="s">
         <v>118</v>
@@ -12956,26 +12955,26 @@
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="B433" t="s">
         <v>15</v>
       </c>
       <c r="C433" s="11"/>
       <c r="D433" s="11">
-        <v>2960</v>
+        <v>2860</v>
       </c>
       <c r="E433" s="11">
-        <v>3150</v>
+        <v>3070</v>
       </c>
       <c r="F433" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G433" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H433" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I433" s="7" t="s">
         <v>118</v>
@@ -12983,26 +12982,26 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="B434" t="s">
         <v>15</v>
       </c>
       <c r="C434" s="11"/>
       <c r="D434" s="11">
-        <v>3020</v>
+        <v>2910</v>
       </c>
       <c r="E434" s="11">
-        <v>3250</v>
+        <v>3230</v>
       </c>
       <c r="F434" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G434" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H434" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I434" s="7" t="s">
         <v>118</v>
@@ -13010,26 +13009,26 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B435" t="s">
         <v>15</v>
       </c>
       <c r="C435" s="11"/>
       <c r="D435" s="11">
-        <v>2960</v>
+        <v>2810</v>
       </c>
       <c r="E435" s="11">
-        <v>3150</v>
+        <v>3020</v>
       </c>
       <c r="F435" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G435" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H435" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I435" s="7" t="s">
         <v>118</v>
@@ -13037,26 +13036,26 @@
     </row>
     <row r="436" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="B436" t="s">
         <v>15</v>
       </c>
       <c r="C436" s="11"/>
       <c r="D436" s="11">
-        <v>2960</v>
+        <v>2860</v>
       </c>
       <c r="E436" s="11">
-        <v>3150</v>
+        <v>3070</v>
       </c>
       <c r="F436" s="7" t="s">
         <v>150</v>
       </c>
       <c r="G436" s="8">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H436" s="7" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I436" s="7" t="s">
         <v>118</v>
@@ -13064,17 +13063,17 @@
     </row>
     <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B437" t="s">
         <v>15</v>
       </c>
       <c r="C437" s="11"/>
       <c r="D437" s="11">
-        <v>2820</v>
+        <v>2860</v>
       </c>
       <c r="E437" s="11">
-        <v>2970</v>
+        <v>3070</v>
       </c>
       <c r="F437" s="7" t="s">
         <v>150</v>
@@ -13083,7 +13082,7 @@
         <v>18</v>
       </c>
       <c r="H437" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I437" s="7" t="s">
         <v>118</v>
@@ -13091,17 +13090,17 @@
     </row>
     <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B438" t="s">
         <v>15</v>
       </c>
       <c r="C438" s="11"/>
       <c r="D438" s="11">
-        <v>2820</v>
+        <v>2750</v>
       </c>
       <c r="E438" s="11">
-        <v>2970</v>
+        <v>2910</v>
       </c>
       <c r="F438" s="7" t="s">
         <v>150</v>
@@ -13110,7 +13109,7 @@
         <v>18</v>
       </c>
       <c r="H438" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I438" s="7" t="s">
         <v>118</v>
@@ -13118,17 +13117,17 @@
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B439" t="s">
         <v>15</v>
       </c>
       <c r="C439" s="11"/>
       <c r="D439" s="11">
-        <v>2870</v>
+        <v>2700</v>
       </c>
       <c r="E439" s="11">
-        <v>3030</v>
+        <v>2810</v>
       </c>
       <c r="F439" s="7" t="s">
         <v>150</v>
@@ -13137,25 +13136,25 @@
         <v>18</v>
       </c>
       <c r="H439" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I439" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A440" s="7" t="s">
-        <v>120</v>
+      <c r="A440" t="s">
+        <v>51</v>
       </c>
       <c r="B440" t="s">
         <v>15</v>
       </c>
       <c r="C440" s="11"/>
       <c r="D440" s="11">
-        <v>2820</v>
+        <v>2860</v>
       </c>
       <c r="E440" s="11">
-        <v>2970</v>
+        <v>3070</v>
       </c>
       <c r="F440" s="7" t="s">
         <v>150</v>
@@ -13164,7 +13163,7 @@
         <v>18</v>
       </c>
       <c r="H440" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I440" s="7" t="s">
         <v>118</v>
@@ -13172,17 +13171,17 @@
     </row>
     <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B441" t="s">
         <v>15</v>
       </c>
       <c r="C441" s="11"/>
       <c r="D441" s="11">
-        <v>2920</v>
+        <v>3020</v>
       </c>
       <c r="E441" s="11">
-        <v>3180</v>
+        <v>3440</v>
       </c>
       <c r="F441" s="7" t="s">
         <v>150</v>
@@ -13191,7 +13190,7 @@
         <v>18</v>
       </c>
       <c r="H441" s="7" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="I441" s="7" t="s">
         <v>118</v>
@@ -13199,17 +13198,17 @@
     </row>
     <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="B442" t="s">
         <v>15</v>
       </c>
       <c r="C442" s="11"/>
       <c r="D442" s="11">
-        <v>2920</v>
+        <v>2860</v>
       </c>
       <c r="E442" s="11">
-        <v>3080</v>
+        <v>3070</v>
       </c>
       <c r="F442" s="7" t="s">
         <v>150</v>
@@ -13218,4447 +13217,5389 @@
         <v>18</v>
       </c>
       <c r="H442" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I442" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>16</v>
+      </c>
+      <c r="B443" t="s">
+        <v>15</v>
+      </c>
+      <c r="C443" s="11"/>
+      <c r="D443" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E443" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F443" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G443" s="8">
+        <v>18</v>
+      </c>
+      <c r="H443" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I443" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>152</v>
+      </c>
+      <c r="B444" t="s">
+        <v>15</v>
+      </c>
+      <c r="C444" s="11"/>
+      <c r="D444" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E444" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F444" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G444" s="8">
+        <v>18</v>
+      </c>
+      <c r="H444" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I444" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>20</v>
+      </c>
+      <c r="B445" t="s">
+        <v>15</v>
+      </c>
+      <c r="C445" s="11"/>
+      <c r="D445" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E445" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F445" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G445" s="8">
+        <v>18</v>
+      </c>
+      <c r="H445" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I445" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>55</v>
+      </c>
+      <c r="B446" t="s">
+        <v>15</v>
+      </c>
+      <c r="C446" s="11"/>
+      <c r="D446" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E446" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F446" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G446" s="8">
+        <v>18</v>
+      </c>
+      <c r="H446" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I446" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>31</v>
+      </c>
+      <c r="B447" t="s">
+        <v>15</v>
+      </c>
+      <c r="C447" s="11"/>
+      <c r="D447" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E447" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F447" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G447" s="8">
+        <v>18</v>
+      </c>
+      <c r="H447" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I447" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>54</v>
+      </c>
+      <c r="B448" t="s">
+        <v>15</v>
+      </c>
+      <c r="C448" s="11"/>
+      <c r="D448" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E448" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F448" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G448" s="8">
+        <v>18</v>
+      </c>
+      <c r="H448" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I448" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>26</v>
+      </c>
+      <c r="B449" t="s">
+        <v>15</v>
+      </c>
+      <c r="C449" s="11"/>
+      <c r="D449" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E449" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F449" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G449" s="8">
+        <v>18</v>
+      </c>
+      <c r="H449" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I449" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>49</v>
+      </c>
+      <c r="B450" t="s">
+        <v>15</v>
+      </c>
+      <c r="C450" s="11"/>
+      <c r="D450" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E450" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F450" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G450" s="8">
+        <v>18</v>
+      </c>
+      <c r="H450" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="I450" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>5</v>
+      </c>
+      <c r="B451" t="s">
+        <v>15</v>
+      </c>
+      <c r="C451" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D451" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E451" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F451" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G451" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H451" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I451" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>4</v>
+      </c>
+      <c r="B452" t="s">
+        <v>15</v>
+      </c>
+      <c r="C452" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D452" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E452" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F452" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G452" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H452" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I452" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>107</v>
+      </c>
+      <c r="B453" t="s">
+        <v>15</v>
+      </c>
+      <c r="C453" s="11"/>
+      <c r="D453" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E453" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F453" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G453" s="8">
+        <v>19</v>
+      </c>
+      <c r="H453" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I453" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>108</v>
+      </c>
+      <c r="B454" t="s">
+        <v>15</v>
+      </c>
+      <c r="C454" s="11"/>
+      <c r="D454" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E454" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F454" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G454" s="8">
+        <v>19</v>
+      </c>
+      <c r="H454" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I454" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>109</v>
+      </c>
+      <c r="B455" t="s">
+        <v>15</v>
+      </c>
+      <c r="C455" s="11"/>
+      <c r="D455" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E455" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F455" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G455" s="8">
+        <v>19</v>
+      </c>
+      <c r="H455" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I455" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>52</v>
+      </c>
+      <c r="B456" t="s">
+        <v>15</v>
+      </c>
+      <c r="C456" s="11"/>
+      <c r="D456" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E456" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F456" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G456" s="8">
+        <v>19</v>
+      </c>
+      <c r="H456" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I456" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>50</v>
+      </c>
+      <c r="B457" t="s">
+        <v>15</v>
+      </c>
+      <c r="C457" s="11"/>
+      <c r="D457" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E457" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F457" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G457" s="8">
+        <v>19</v>
+      </c>
+      <c r="H457" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I457" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>29</v>
+      </c>
+      <c r="B458" t="s">
+        <v>15</v>
+      </c>
+      <c r="C458" s="11"/>
+      <c r="D458" s="11">
+        <v>3170</v>
+      </c>
+      <c r="E458" s="11">
+        <v>3360</v>
+      </c>
+      <c r="F458" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G458" s="8">
+        <v>19</v>
+      </c>
+      <c r="H458" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I458" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>115</v>
+      </c>
+      <c r="B459" t="s">
+        <v>15</v>
+      </c>
+      <c r="C459" s="11"/>
+      <c r="D459" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E459" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F459" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G459" s="8">
+        <v>19</v>
+      </c>
+      <c r="H459" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I459" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>110</v>
+      </c>
+      <c r="B460" t="s">
+        <v>15</v>
+      </c>
+      <c r="C460" s="11"/>
+      <c r="D460" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E460" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F460" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G460" s="8">
+        <v>19</v>
+      </c>
+      <c r="H460" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I460" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>27</v>
+      </c>
+      <c r="B461" t="s">
+        <v>15</v>
+      </c>
+      <c r="C461" s="11"/>
+      <c r="D461" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E461" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F461" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G461" s="8">
+        <v>19</v>
+      </c>
+      <c r="H461" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I461" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>48</v>
+      </c>
+      <c r="B462" t="s">
+        <v>15</v>
+      </c>
+      <c r="C462" s="11"/>
+      <c r="D462" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E462" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F462" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G462" s="8">
+        <v>19</v>
+      </c>
+      <c r="H462" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I462" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>111</v>
+      </c>
+      <c r="B463" t="s">
+        <v>15</v>
+      </c>
+      <c r="C463" s="11"/>
+      <c r="D463" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E463" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F463" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G463" s="8">
+        <v>19</v>
+      </c>
+      <c r="H463" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I463" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>28</v>
+      </c>
+      <c r="B464" t="s">
+        <v>15</v>
+      </c>
+      <c r="C464" s="11"/>
+      <c r="D464" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E464" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F464" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G464" s="8">
+        <v>19</v>
+      </c>
+      <c r="H464" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I464" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>112</v>
+      </c>
+      <c r="B465" t="s">
+        <v>15</v>
+      </c>
+      <c r="C465" s="11"/>
+      <c r="D465" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E465" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F465" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G465" s="8">
+        <v>19</v>
+      </c>
+      <c r="H465" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I465" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>116</v>
+      </c>
+      <c r="B466" t="s">
+        <v>15</v>
+      </c>
+      <c r="C466" s="11"/>
+      <c r="D466" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E466" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F466" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G466" s="8">
+        <v>19</v>
+      </c>
+      <c r="H466" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I466" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>25</v>
+      </c>
+      <c r="B467" t="s">
+        <v>15</v>
+      </c>
+      <c r="C467" s="11"/>
+      <c r="D467" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E467" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F467" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G467" s="8">
+        <v>19</v>
+      </c>
+      <c r="H467" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I467" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>19</v>
+      </c>
+      <c r="B468" t="s">
+        <v>15</v>
+      </c>
+      <c r="C468" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D468" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E468" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F468" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G468" s="8">
+        <v>19</v>
+      </c>
+      <c r="H468" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I468" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>21</v>
+      </c>
+      <c r="B469" t="s">
+        <v>15</v>
+      </c>
+      <c r="C469" s="11">
+        <v>2600</v>
+      </c>
+      <c r="D469" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E469" s="11">
+        <v>2940</v>
+      </c>
+      <c r="F469" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G469" s="8">
+        <v>19</v>
+      </c>
+      <c r="H469" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I469" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>51</v>
+      </c>
+      <c r="B470" t="s">
+        <v>15</v>
+      </c>
+      <c r="C470" s="11"/>
+      <c r="D470" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E470" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F470" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G470" s="8">
+        <v>19</v>
+      </c>
+      <c r="H470" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I470" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>113</v>
+      </c>
+      <c r="B471" t="s">
+        <v>15</v>
+      </c>
+      <c r="C471" s="11"/>
+      <c r="D471" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E471" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F471" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G471" s="8">
+        <v>19</v>
+      </c>
+      <c r="H471" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I471" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>16</v>
+      </c>
+      <c r="B472" t="s">
+        <v>15</v>
+      </c>
+      <c r="C472" s="11"/>
+      <c r="D472" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E472" s="11">
+        <v>3250</v>
+      </c>
+      <c r="F472" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G472" s="8">
+        <v>19</v>
+      </c>
+      <c r="H472" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I472" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>26</v>
+      </c>
+      <c r="B473" t="s">
+        <v>15</v>
+      </c>
+      <c r="C473" s="11"/>
+      <c r="D473" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E473" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F473" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G473" s="8">
+        <v>19</v>
+      </c>
+      <c r="H473" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I473" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>49</v>
+      </c>
+      <c r="B474" t="s">
+        <v>15</v>
+      </c>
+      <c r="C474" s="11"/>
+      <c r="D474" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E474" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F474" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G474" s="8">
+        <v>19</v>
+      </c>
+      <c r="H474" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I474" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>5</v>
+      </c>
+      <c r="B475" t="s">
+        <v>15</v>
+      </c>
+      <c r="C475" s="11"/>
+      <c r="D475" s="11">
+        <v>2610</v>
+      </c>
+      <c r="E475" s="11">
+        <v>2820</v>
+      </c>
+      <c r="F475" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G475" s="8">
+        <v>18</v>
+      </c>
+      <c r="H475" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="I442" s="7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C443" s="11"/>
-      <c r="D443" s="11"/>
-      <c r="E443" s="11"/>
-      <c r="F443" s="7"/>
-      <c r="G443" s="8"/>
-      <c r="H443" s="7"/>
-      <c r="I443" s="7"/>
-    </row>
-    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C444" s="11"/>
-      <c r="D444" s="11"/>
-      <c r="E444" s="11"/>
-      <c r="F444" s="7"/>
-      <c r="G444" s="8"/>
-      <c r="H444" s="7"/>
-      <c r="I444" s="7"/>
-    </row>
-    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C445" s="11"/>
-      <c r="D445" s="11"/>
-      <c r="E445" s="11"/>
-    </row>
-    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C446" s="11"/>
-      <c r="D446" s="11"/>
-      <c r="E446" s="11"/>
-    </row>
-    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C447" s="11"/>
-      <c r="D447" s="11"/>
-      <c r="E447" s="11"/>
-    </row>
-    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C448" s="11"/>
-      <c r="D448" s="11"/>
-      <c r="E448" s="11"/>
-    </row>
-    <row r="449" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C449" s="11"/>
-      <c r="D449" s="11"/>
-      <c r="E449" s="11"/>
-    </row>
-    <row r="450" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C450" s="11"/>
-      <c r="D450" s="11"/>
-      <c r="E450" s="11"/>
-    </row>
-    <row r="451" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C451" s="11"/>
-      <c r="D451" s="11"/>
-      <c r="E451" s="11"/>
-    </row>
-    <row r="452" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C452" s="11"/>
-      <c r="D452" s="11"/>
-      <c r="E452" s="11"/>
-    </row>
-    <row r="453" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C453" s="11"/>
-      <c r="D453" s="11"/>
-      <c r="E453" s="11"/>
-    </row>
-    <row r="454" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C454" s="11"/>
-      <c r="D454" s="11"/>
-      <c r="E454" s="11"/>
-    </row>
-    <row r="455" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C455" s="11"/>
-      <c r="D455" s="11"/>
-      <c r="E455" s="11"/>
-    </row>
-    <row r="456" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C456" s="11"/>
-      <c r="D456" s="11"/>
-      <c r="E456" s="11"/>
-    </row>
-    <row r="457" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C457" s="11"/>
-      <c r="D457" s="11"/>
-      <c r="E457" s="11"/>
-    </row>
-    <row r="458" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C458" s="11"/>
-      <c r="D458" s="11"/>
-      <c r="E458" s="11"/>
-    </row>
-    <row r="459" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C459" s="11"/>
-      <c r="D459" s="11"/>
-      <c r="E459" s="11"/>
-    </row>
-    <row r="460" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C460" s="11"/>
-      <c r="D460" s="11"/>
-      <c r="E460" s="11"/>
-    </row>
-    <row r="461" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C461" s="11"/>
-      <c r="D461" s="11"/>
-      <c r="E461" s="11"/>
-    </row>
-    <row r="462" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C462" s="11"/>
-      <c r="D462" s="11"/>
-      <c r="E462" s="11"/>
-    </row>
-    <row r="463" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C463" s="11"/>
-      <c r="D463" s="11"/>
-      <c r="E463" s="11"/>
-    </row>
-    <row r="464" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C464" s="11"/>
-      <c r="D464" s="11"/>
-      <c r="E464" s="11"/>
-    </row>
-    <row r="465" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C465" s="11"/>
-      <c r="D465" s="11"/>
-      <c r="E465" s="11"/>
-    </row>
-    <row r="466" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C466" s="11"/>
-      <c r="D466" s="11"/>
-      <c r="E466" s="11"/>
-    </row>
-    <row r="467" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C467" s="11"/>
-      <c r="D467" s="11"/>
-      <c r="E467" s="11"/>
-    </row>
-    <row r="468" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C468" s="11"/>
-      <c r="D468" s="11"/>
-      <c r="E468" s="11"/>
-    </row>
-    <row r="469" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C469" s="11"/>
-      <c r="D469" s="11"/>
-      <c r="E469" s="11"/>
-    </row>
-    <row r="470" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C470" s="11"/>
-      <c r="D470" s="11"/>
-      <c r="E470" s="11"/>
-    </row>
-    <row r="471" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C471" s="11"/>
-      <c r="D471" s="11"/>
-      <c r="E471" s="11"/>
-    </row>
-    <row r="472" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C472" s="11"/>
-      <c r="D472" s="11"/>
-      <c r="E472" s="11"/>
-    </row>
-    <row r="473" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C473" s="11"/>
-      <c r="D473" s="11"/>
-      <c r="E473" s="11"/>
-    </row>
-    <row r="474" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C474" s="11"/>
-      <c r="D474" s="11"/>
-      <c r="E474" s="11"/>
-    </row>
-    <row r="475" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C475" s="11"/>
-      <c r="D475" s="11"/>
-      <c r="E475" s="11"/>
-    </row>
-    <row r="476" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="I475" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>4</v>
+      </c>
+      <c r="B476" t="s">
+        <v>15</v>
+      </c>
       <c r="C476" s="11"/>
-      <c r="D476" s="11"/>
-      <c r="E476" s="11"/>
-    </row>
-    <row r="477" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D476" s="11">
+        <v>2610</v>
+      </c>
+      <c r="E476" s="11">
+        <v>2820</v>
+      </c>
+      <c r="F476" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G476" s="8">
+        <v>18</v>
+      </c>
+      <c r="H476" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I476" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>13</v>
+      </c>
+      <c r="B477" t="s">
+        <v>15</v>
+      </c>
       <c r="C477" s="11"/>
-      <c r="D477" s="11"/>
-      <c r="E477" s="11"/>
-    </row>
-    <row r="478" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D477" s="11">
+        <v>2660</v>
+      </c>
+      <c r="E477" s="11">
+        <v>2870</v>
+      </c>
+      <c r="F477" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G477" s="8">
+        <v>18</v>
+      </c>
+      <c r="H477" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I477" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>152</v>
+      </c>
+      <c r="B478" t="s">
+        <v>15</v>
+      </c>
       <c r="C478" s="11"/>
-      <c r="D478" s="11"/>
-      <c r="E478" s="11"/>
-    </row>
-    <row r="479" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D478" s="11">
+        <v>2610</v>
+      </c>
+      <c r="E478" s="11">
+        <v>2820</v>
+      </c>
+      <c r="F478" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G478" s="8">
+        <v>18</v>
+      </c>
+      <c r="H478" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I478" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>30</v>
+      </c>
+      <c r="B479" t="s">
+        <v>15</v>
+      </c>
       <c r="C479" s="11"/>
-      <c r="D479" s="11"/>
-      <c r="E479" s="11"/>
-    </row>
-    <row r="480" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D479" s="11">
+        <v>2710</v>
+      </c>
+      <c r="E479" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F479" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G479" s="8">
+        <v>18</v>
+      </c>
+      <c r="H479" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I479" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>24</v>
+      </c>
+      <c r="B480" t="s">
+        <v>15</v>
+      </c>
       <c r="C480" s="11"/>
-      <c r="D480" s="11"/>
-      <c r="E480" s="11"/>
-    </row>
-    <row r="481" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D480" s="11">
+        <v>2710</v>
+      </c>
+      <c r="E480" s="11">
+        <v>2920</v>
+      </c>
+      <c r="F480" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G480" s="8">
+        <v>18</v>
+      </c>
+      <c r="H480" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="I480" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="481" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C481" s="11"/>
       <c r="D481" s="11"/>
       <c r="E481" s="11"/>
-    </row>
-    <row r="482" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G481" s="8"/>
+    </row>
+    <row r="482" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C482" s="11"/>
       <c r="D482" s="11"/>
       <c r="E482" s="11"/>
-    </row>
-    <row r="483" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G482" s="8"/>
+    </row>
+    <row r="483" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C483" s="11"/>
       <c r="D483" s="11"/>
       <c r="E483" s="11"/>
-    </row>
-    <row r="484" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G483" s="8"/>
+    </row>
+    <row r="484" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C484" s="11"/>
       <c r="D484" s="11"/>
       <c r="E484" s="11"/>
-    </row>
-    <row r="485" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G484" s="8"/>
+    </row>
+    <row r="485" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C485" s="11"/>
       <c r="D485" s="11"/>
       <c r="E485" s="11"/>
-    </row>
-    <row r="486" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G485" s="8"/>
+    </row>
+    <row r="486" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C486" s="11"/>
       <c r="D486" s="11"/>
       <c r="E486" s="11"/>
-    </row>
-    <row r="487" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G486" s="8"/>
+    </row>
+    <row r="487" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C487" s="11"/>
       <c r="D487" s="11"/>
       <c r="E487" s="11"/>
-    </row>
-    <row r="488" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G487" s="8"/>
+    </row>
+    <row r="488" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C488" s="11"/>
       <c r="D488" s="11"/>
       <c r="E488" s="11"/>
-    </row>
-    <row r="489" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G488" s="8"/>
+    </row>
+    <row r="489" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C489" s="11"/>
       <c r="D489" s="11"/>
       <c r="E489" s="11"/>
-    </row>
-    <row r="490" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G489" s="8"/>
+    </row>
+    <row r="490" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C490" s="11"/>
       <c r="D490" s="11"/>
       <c r="E490" s="11"/>
-    </row>
-    <row r="491" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G490" s="8"/>
+    </row>
+    <row r="491" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C491" s="11"/>
       <c r="D491" s="11"/>
       <c r="E491" s="11"/>
-    </row>
-    <row r="492" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G491" s="8"/>
+    </row>
+    <row r="492" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C492" s="11"/>
       <c r="D492" s="11"/>
       <c r="E492" s="11"/>
-    </row>
-    <row r="493" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G492" s="8"/>
+    </row>
+    <row r="493" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C493" s="11"/>
       <c r="D493" s="11"/>
       <c r="E493" s="11"/>
-    </row>
-    <row r="494" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G493" s="8"/>
+    </row>
+    <row r="494" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C494" s="11"/>
       <c r="D494" s="11"/>
       <c r="E494" s="11"/>
-    </row>
-    <row r="495" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G494" s="8"/>
+    </row>
+    <row r="495" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C495" s="11"/>
       <c r="D495" s="11"/>
       <c r="E495" s="11"/>
-    </row>
-    <row r="496" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G495" s="8"/>
+    </row>
+    <row r="496" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C496" s="11"/>
       <c r="D496" s="11"/>
       <c r="E496" s="11"/>
-    </row>
-    <row r="497" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G496" s="8"/>
+    </row>
+    <row r="497" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C497" s="11"/>
       <c r="D497" s="11"/>
       <c r="E497" s="11"/>
-    </row>
-    <row r="498" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G497" s="8"/>
+    </row>
+    <row r="498" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C498" s="11"/>
       <c r="D498" s="11"/>
       <c r="E498" s="11"/>
-    </row>
-    <row r="499" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G498" s="8"/>
+    </row>
+    <row r="499" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C499" s="11"/>
       <c r="D499" s="11"/>
       <c r="E499" s="11"/>
-    </row>
-    <row r="500" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G499" s="8"/>
+    </row>
+    <row r="500" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C500" s="11"/>
       <c r="D500" s="11"/>
       <c r="E500" s="11"/>
-    </row>
-    <row r="501" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G500" s="8"/>
+    </row>
+    <row r="501" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C501" s="11"/>
       <c r="D501" s="11"/>
       <c r="E501" s="11"/>
-    </row>
-    <row r="502" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G501" s="8"/>
+    </row>
+    <row r="502" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C502" s="11"/>
       <c r="D502" s="11"/>
       <c r="E502" s="11"/>
-    </row>
-    <row r="503" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G502" s="8"/>
+    </row>
+    <row r="503" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C503" s="11"/>
       <c r="D503" s="11"/>
       <c r="E503" s="11"/>
-    </row>
-    <row r="504" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G503" s="8"/>
+    </row>
+    <row r="504" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C504" s="11"/>
       <c r="D504" s="11"/>
       <c r="E504" s="11"/>
-    </row>
-    <row r="505" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G504" s="8"/>
+    </row>
+    <row r="505" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C505" s="11"/>
       <c r="D505" s="11"/>
       <c r="E505" s="11"/>
-    </row>
-    <row r="506" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G505" s="8"/>
+    </row>
+    <row r="506" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C506" s="11"/>
       <c r="D506" s="11"/>
       <c r="E506" s="11"/>
-    </row>
-    <row r="507" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G506" s="8"/>
+    </row>
+    <row r="507" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C507" s="11"/>
       <c r="D507" s="11"/>
       <c r="E507" s="11"/>
-    </row>
-    <row r="508" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G507" s="8"/>
+    </row>
+    <row r="508" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C508" s="11"/>
       <c r="D508" s="11"/>
       <c r="E508" s="11"/>
-    </row>
-    <row r="509" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G508" s="8"/>
+    </row>
+    <row r="509" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C509" s="11"/>
       <c r="D509" s="11"/>
       <c r="E509" s="11"/>
-    </row>
-    <row r="510" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G509" s="8"/>
+    </row>
+    <row r="510" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C510" s="11"/>
       <c r="D510" s="11"/>
       <c r="E510" s="11"/>
-    </row>
-    <row r="511" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G510" s="8"/>
+    </row>
+    <row r="511" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C511" s="11"/>
       <c r="D511" s="11"/>
       <c r="E511" s="11"/>
-    </row>
-    <row r="512" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G511" s="8"/>
+    </row>
+    <row r="512" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C512" s="11"/>
       <c r="D512" s="11"/>
       <c r="E512" s="11"/>
-    </row>
-    <row r="513" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G512" s="8"/>
+    </row>
+    <row r="513" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C513" s="11"/>
       <c r="D513" s="11"/>
       <c r="E513" s="11"/>
-    </row>
-    <row r="514" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G513" s="8"/>
+    </row>
+    <row r="514" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C514" s="11"/>
       <c r="D514" s="11"/>
       <c r="E514" s="11"/>
-    </row>
-    <row r="515" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G514" s="8"/>
+    </row>
+    <row r="515" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C515" s="11"/>
       <c r="D515" s="11"/>
       <c r="E515" s="11"/>
-    </row>
-    <row r="516" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G515" s="8"/>
+    </row>
+    <row r="516" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C516" s="11"/>
       <c r="D516" s="11"/>
       <c r="E516" s="11"/>
-    </row>
-    <row r="517" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G516" s="8"/>
+    </row>
+    <row r="517" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C517" s="11"/>
       <c r="D517" s="11"/>
       <c r="E517" s="11"/>
-    </row>
-    <row r="518" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G517" s="8"/>
+    </row>
+    <row r="518" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C518" s="11"/>
       <c r="D518" s="11"/>
       <c r="E518" s="11"/>
-    </row>
-    <row r="519" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G518" s="8"/>
+    </row>
+    <row r="519" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C519" s="11"/>
       <c r="D519" s="11"/>
       <c r="E519" s="11"/>
-    </row>
-    <row r="520" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G519" s="8"/>
+    </row>
+    <row r="520" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C520" s="11"/>
       <c r="D520" s="11"/>
       <c r="E520" s="11"/>
-    </row>
-    <row r="521" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G520" s="8"/>
+    </row>
+    <row r="521" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C521" s="11"/>
       <c r="D521" s="11"/>
       <c r="E521" s="11"/>
-    </row>
-    <row r="522" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G521" s="8"/>
+    </row>
+    <row r="522" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C522" s="11"/>
       <c r="D522" s="11"/>
       <c r="E522" s="11"/>
-    </row>
-    <row r="523" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G522" s="8"/>
+    </row>
+    <row r="523" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C523" s="11"/>
       <c r="D523" s="11"/>
       <c r="E523" s="11"/>
-    </row>
-    <row r="524" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G523" s="8"/>
+    </row>
+    <row r="524" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C524" s="11"/>
       <c r="D524" s="11"/>
       <c r="E524" s="11"/>
-    </row>
-    <row r="525" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G524" s="8"/>
+    </row>
+    <row r="525" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C525" s="11"/>
       <c r="D525" s="11"/>
       <c r="E525" s="11"/>
-    </row>
-    <row r="526" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G525" s="8"/>
+    </row>
+    <row r="526" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C526" s="11"/>
       <c r="D526" s="11"/>
       <c r="E526" s="11"/>
-    </row>
-    <row r="527" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G526" s="8"/>
+    </row>
+    <row r="527" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C527" s="11"/>
       <c r="D527" s="11"/>
       <c r="E527" s="11"/>
-    </row>
-    <row r="528" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G527" s="8"/>
+    </row>
+    <row r="528" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C528" s="11"/>
       <c r="D528" s="11"/>
       <c r="E528" s="11"/>
-    </row>
-    <row r="529" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G528" s="8"/>
+    </row>
+    <row r="529" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C529" s="11"/>
       <c r="D529" s="11"/>
       <c r="E529" s="11"/>
-    </row>
-    <row r="530" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G529" s="8"/>
+    </row>
+    <row r="530" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C530" s="11"/>
       <c r="D530" s="11"/>
       <c r="E530" s="11"/>
-    </row>
-    <row r="531" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G530" s="8"/>
+    </row>
+    <row r="531" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C531" s="11"/>
       <c r="D531" s="11"/>
       <c r="E531" s="11"/>
-    </row>
-    <row r="532" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G531" s="8"/>
+    </row>
+    <row r="532" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C532" s="11"/>
       <c r="D532" s="11"/>
       <c r="E532" s="11"/>
-    </row>
-    <row r="533" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G532" s="8"/>
+    </row>
+    <row r="533" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C533" s="11"/>
       <c r="D533" s="11"/>
       <c r="E533" s="11"/>
-    </row>
-    <row r="534" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G533" s="8"/>
+    </row>
+    <row r="534" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C534" s="11"/>
       <c r="D534" s="11"/>
       <c r="E534" s="11"/>
-    </row>
-    <row r="535" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G534" s="8"/>
+    </row>
+    <row r="535" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C535" s="11"/>
       <c r="D535" s="11"/>
       <c r="E535" s="11"/>
-    </row>
-    <row r="536" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G535" s="8"/>
+    </row>
+    <row r="536" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C536" s="11"/>
       <c r="D536" s="11"/>
       <c r="E536" s="11"/>
-    </row>
-    <row r="537" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G536" s="8"/>
+    </row>
+    <row r="537" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C537" s="11"/>
       <c r="D537" s="11"/>
       <c r="E537" s="11"/>
-    </row>
-    <row r="538" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G537" s="8"/>
+    </row>
+    <row r="538" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C538" s="11"/>
       <c r="D538" s="11"/>
       <c r="E538" s="11"/>
-    </row>
-    <row r="539" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G538" s="8"/>
+    </row>
+    <row r="539" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C539" s="11"/>
       <c r="D539" s="11"/>
       <c r="E539" s="11"/>
-    </row>
-    <row r="540" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G539" s="8"/>
+    </row>
+    <row r="540" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C540" s="11"/>
       <c r="D540" s="11"/>
       <c r="E540" s="11"/>
-    </row>
-    <row r="541" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G540" s="8"/>
+    </row>
+    <row r="541" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C541" s="11"/>
       <c r="D541" s="11"/>
       <c r="E541" s="11"/>
-    </row>
-    <row r="542" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G541" s="8"/>
+    </row>
+    <row r="542" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C542" s="11"/>
       <c r="D542" s="11"/>
       <c r="E542" s="11"/>
-    </row>
-    <row r="543" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G542" s="8"/>
+    </row>
+    <row r="543" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C543" s="11"/>
       <c r="D543" s="11"/>
       <c r="E543" s="11"/>
-    </row>
-    <row r="544" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G543" s="8"/>
+    </row>
+    <row r="544" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C544" s="11"/>
       <c r="D544" s="11"/>
       <c r="E544" s="11"/>
-    </row>
-    <row r="545" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G544" s="8"/>
+    </row>
+    <row r="545" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C545" s="11"/>
       <c r="D545" s="11"/>
       <c r="E545" s="11"/>
-    </row>
-    <row r="546" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G545" s="8"/>
+    </row>
+    <row r="546" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C546" s="11"/>
       <c r="D546" s="11"/>
       <c r="E546" s="11"/>
-    </row>
-    <row r="547" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G546" s="8"/>
+    </row>
+    <row r="547" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C547" s="11"/>
       <c r="D547" s="11"/>
       <c r="E547" s="11"/>
-    </row>
-    <row r="548" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G547" s="8"/>
+    </row>
+    <row r="548" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C548" s="11"/>
       <c r="D548" s="11"/>
       <c r="E548" s="11"/>
-    </row>
-    <row r="549" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G548" s="8"/>
+    </row>
+    <row r="549" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C549" s="11"/>
       <c r="D549" s="11"/>
       <c r="E549" s="11"/>
-    </row>
-    <row r="550" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G549" s="8"/>
+    </row>
+    <row r="550" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C550" s="11"/>
       <c r="D550" s="11"/>
       <c r="E550" s="11"/>
-    </row>
-    <row r="551" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G550" s="8"/>
+    </row>
+    <row r="551" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C551" s="11"/>
       <c r="D551" s="11"/>
       <c r="E551" s="11"/>
-    </row>
-    <row r="552" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G551" s="8"/>
+    </row>
+    <row r="552" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C552" s="11"/>
       <c r="D552" s="11"/>
       <c r="E552" s="11"/>
-    </row>
-    <row r="553" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G552" s="8"/>
+    </row>
+    <row r="553" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C553" s="11"/>
       <c r="D553" s="11"/>
       <c r="E553" s="11"/>
-    </row>
-    <row r="554" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G553" s="8"/>
+    </row>
+    <row r="554" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C554" s="11"/>
       <c r="D554" s="11"/>
       <c r="E554" s="11"/>
-    </row>
-    <row r="555" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G554" s="8"/>
+    </row>
+    <row r="555" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C555" s="11"/>
       <c r="D555" s="11"/>
       <c r="E555" s="11"/>
-    </row>
-    <row r="556" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G555" s="8"/>
+    </row>
+    <row r="556" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C556" s="11"/>
       <c r="D556" s="11"/>
       <c r="E556" s="11"/>
-    </row>
-    <row r="557" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G556" s="8"/>
+    </row>
+    <row r="557" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C557" s="11"/>
       <c r="D557" s="11"/>
       <c r="E557" s="11"/>
-    </row>
-    <row r="558" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G557" s="8"/>
+    </row>
+    <row r="558" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C558" s="11"/>
       <c r="D558" s="11"/>
       <c r="E558" s="11"/>
-    </row>
-    <row r="559" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G558" s="8"/>
+    </row>
+    <row r="559" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C559" s="11"/>
       <c r="D559" s="11"/>
       <c r="E559" s="11"/>
-    </row>
-    <row r="560" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G559" s="8"/>
+    </row>
+    <row r="560" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C560" s="11"/>
       <c r="D560" s="11"/>
       <c r="E560" s="11"/>
-    </row>
-    <row r="561" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G560" s="8"/>
+    </row>
+    <row r="561" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C561" s="11"/>
       <c r="D561" s="11"/>
       <c r="E561" s="11"/>
-    </row>
-    <row r="562" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G561" s="8"/>
+    </row>
+    <row r="562" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C562" s="11"/>
       <c r="D562" s="11"/>
       <c r="E562" s="11"/>
-    </row>
-    <row r="563" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G562" s="8"/>
+    </row>
+    <row r="563" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C563" s="11"/>
       <c r="D563" s="11"/>
       <c r="E563" s="11"/>
-    </row>
-    <row r="564" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G563" s="8"/>
+    </row>
+    <row r="564" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C564" s="11"/>
       <c r="D564" s="11"/>
       <c r="E564" s="11"/>
-    </row>
-    <row r="565" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G564" s="8"/>
+    </row>
+    <row r="565" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C565" s="11"/>
       <c r="D565" s="11"/>
       <c r="E565" s="11"/>
-    </row>
-    <row r="566" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G565" s="8"/>
+    </row>
+    <row r="566" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C566" s="11"/>
       <c r="D566" s="11"/>
       <c r="E566" s="11"/>
-    </row>
-    <row r="567" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G566" s="8"/>
+    </row>
+    <row r="567" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C567" s="11"/>
       <c r="D567" s="11"/>
       <c r="E567" s="11"/>
-    </row>
-    <row r="568" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G567" s="8"/>
+    </row>
+    <row r="568" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C568" s="11"/>
       <c r="D568" s="11"/>
       <c r="E568" s="11"/>
-    </row>
-    <row r="569" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G568" s="8"/>
+    </row>
+    <row r="569" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C569" s="11"/>
       <c r="D569" s="11"/>
       <c r="E569" s="11"/>
-    </row>
-    <row r="570" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G569" s="8"/>
+    </row>
+    <row r="570" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C570" s="11"/>
       <c r="D570" s="11"/>
       <c r="E570" s="11"/>
-    </row>
-    <row r="571" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G570" s="8"/>
+    </row>
+    <row r="571" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C571" s="11"/>
       <c r="D571" s="11"/>
       <c r="E571" s="11"/>
-    </row>
-    <row r="572" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G571" s="8"/>
+    </row>
+    <row r="572" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C572" s="11"/>
       <c r="D572" s="11"/>
       <c r="E572" s="11"/>
-    </row>
-    <row r="573" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G572" s="8"/>
+    </row>
+    <row r="573" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C573" s="11"/>
       <c r="D573" s="11"/>
       <c r="E573" s="11"/>
-    </row>
-    <row r="574" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G573" s="8"/>
+    </row>
+    <row r="574" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C574" s="11"/>
       <c r="D574" s="11"/>
       <c r="E574" s="11"/>
-    </row>
-    <row r="575" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G574" s="8"/>
+    </row>
+    <row r="575" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C575" s="11"/>
       <c r="D575" s="11"/>
       <c r="E575" s="11"/>
-    </row>
-    <row r="576" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G575" s="8"/>
+    </row>
+    <row r="576" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C576" s="11"/>
       <c r="D576" s="11"/>
       <c r="E576" s="11"/>
-    </row>
-    <row r="577" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G576" s="8"/>
+    </row>
+    <row r="577" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C577" s="11"/>
       <c r="D577" s="11"/>
       <c r="E577" s="11"/>
-    </row>
-    <row r="578" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G577" s="8"/>
+    </row>
+    <row r="578" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C578" s="11"/>
       <c r="D578" s="11"/>
       <c r="E578" s="11"/>
-    </row>
-    <row r="579" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G578" s="8"/>
+    </row>
+    <row r="579" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C579" s="11"/>
       <c r="D579" s="11"/>
       <c r="E579" s="11"/>
-    </row>
-    <row r="580" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G579" s="8"/>
+    </row>
+    <row r="580" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C580" s="11"/>
       <c r="D580" s="11"/>
       <c r="E580" s="11"/>
-    </row>
-    <row r="581" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G580" s="8"/>
+    </row>
+    <row r="581" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C581" s="11"/>
       <c r="D581" s="11"/>
       <c r="E581" s="11"/>
-    </row>
-    <row r="582" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G581" s="8"/>
+    </row>
+    <row r="582" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C582" s="11"/>
       <c r="D582" s="11"/>
       <c r="E582" s="11"/>
-    </row>
-    <row r="583" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G582" s="8"/>
+    </row>
+    <row r="583" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C583" s="11"/>
       <c r="D583" s="11"/>
       <c r="E583" s="11"/>
-    </row>
-    <row r="584" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G583" s="8"/>
+    </row>
+    <row r="584" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C584" s="11"/>
       <c r="D584" s="11"/>
       <c r="E584" s="11"/>
-    </row>
-    <row r="585" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G584" s="8"/>
+    </row>
+    <row r="585" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C585" s="11"/>
       <c r="D585" s="11"/>
       <c r="E585" s="11"/>
-    </row>
-    <row r="586" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G585" s="8"/>
+    </row>
+    <row r="586" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C586" s="11"/>
       <c r="D586" s="11"/>
       <c r="E586" s="11"/>
-    </row>
-    <row r="587" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G586" s="8"/>
+    </row>
+    <row r="587" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C587" s="11"/>
       <c r="D587" s="11"/>
       <c r="E587" s="11"/>
-    </row>
-    <row r="588" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G587" s="8"/>
+    </row>
+    <row r="588" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C588" s="11"/>
       <c r="D588" s="11"/>
       <c r="E588" s="11"/>
-    </row>
-    <row r="589" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G588" s="8"/>
+    </row>
+    <row r="589" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C589" s="11"/>
       <c r="D589" s="11"/>
       <c r="E589" s="11"/>
-    </row>
-    <row r="590" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G589" s="8"/>
+    </row>
+    <row r="590" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C590" s="11"/>
       <c r="D590" s="11"/>
       <c r="E590" s="11"/>
-    </row>
-    <row r="591" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G590" s="8"/>
+    </row>
+    <row r="591" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C591" s="11"/>
       <c r="D591" s="11"/>
       <c r="E591" s="11"/>
-    </row>
-    <row r="592" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G591" s="8"/>
+    </row>
+    <row r="592" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C592" s="11"/>
       <c r="D592" s="11"/>
       <c r="E592" s="11"/>
-    </row>
-    <row r="593" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G592" s="8"/>
+    </row>
+    <row r="593" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C593" s="11"/>
       <c r="D593" s="11"/>
       <c r="E593" s="11"/>
-    </row>
-    <row r="594" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G593" s="8"/>
+    </row>
+    <row r="594" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C594" s="11"/>
       <c r="D594" s="11"/>
       <c r="E594" s="11"/>
-    </row>
-    <row r="595" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G594" s="8"/>
+    </row>
+    <row r="595" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C595" s="11"/>
       <c r="D595" s="11"/>
       <c r="E595" s="11"/>
-    </row>
-    <row r="596" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G595" s="8"/>
+    </row>
+    <row r="596" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C596" s="11"/>
       <c r="D596" s="11"/>
       <c r="E596" s="11"/>
-    </row>
-    <row r="597" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G596" s="8"/>
+    </row>
+    <row r="597" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C597" s="11"/>
       <c r="D597" s="11"/>
       <c r="E597" s="11"/>
-    </row>
-    <row r="598" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G597" s="8"/>
+    </row>
+    <row r="598" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C598" s="11"/>
       <c r="D598" s="11"/>
       <c r="E598" s="11"/>
-    </row>
-    <row r="599" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G598" s="8"/>
+    </row>
+    <row r="599" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C599" s="11"/>
       <c r="D599" s="11"/>
       <c r="E599" s="11"/>
-    </row>
-    <row r="600" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G599" s="8"/>
+    </row>
+    <row r="600" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C600" s="11"/>
       <c r="D600" s="11"/>
       <c r="E600" s="11"/>
-    </row>
-    <row r="601" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G600" s="8"/>
+    </row>
+    <row r="601" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C601" s="11"/>
       <c r="D601" s="11"/>
       <c r="E601" s="11"/>
-    </row>
-    <row r="602" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G601" s="8"/>
+    </row>
+    <row r="602" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C602" s="11"/>
       <c r="D602" s="11"/>
       <c r="E602" s="11"/>
-    </row>
-    <row r="603" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G602" s="8"/>
+    </row>
+    <row r="603" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C603" s="11"/>
       <c r="D603" s="11"/>
       <c r="E603" s="11"/>
-    </row>
-    <row r="604" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G603" s="8"/>
+    </row>
+    <row r="604" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C604" s="11"/>
       <c r="D604" s="11"/>
       <c r="E604" s="11"/>
-    </row>
-    <row r="605" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G604" s="8"/>
+    </row>
+    <row r="605" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C605" s="11"/>
       <c r="D605" s="11"/>
       <c r="E605" s="11"/>
-    </row>
-    <row r="606" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G605" s="8"/>
+    </row>
+    <row r="606" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C606" s="11"/>
       <c r="D606" s="11"/>
       <c r="E606" s="11"/>
-    </row>
-    <row r="607" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G606" s="8"/>
+    </row>
+    <row r="607" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C607" s="11"/>
       <c r="D607" s="11"/>
       <c r="E607" s="11"/>
-    </row>
-    <row r="608" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G607" s="8"/>
+    </row>
+    <row r="608" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C608" s="11"/>
       <c r="D608" s="11"/>
       <c r="E608" s="11"/>
-    </row>
-    <row r="609" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G608" s="8"/>
+    </row>
+    <row r="609" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C609" s="11"/>
       <c r="D609" s="11"/>
       <c r="E609" s="11"/>
-    </row>
-    <row r="610" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G609" s="8"/>
+    </row>
+    <row r="610" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C610" s="11"/>
       <c r="D610" s="11"/>
       <c r="E610" s="11"/>
-    </row>
-    <row r="611" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G610" s="8"/>
+    </row>
+    <row r="611" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C611" s="11"/>
       <c r="D611" s="11"/>
       <c r="E611" s="11"/>
-    </row>
-    <row r="612" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G611" s="8"/>
+    </row>
+    <row r="612" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C612" s="11"/>
       <c r="D612" s="11"/>
       <c r="E612" s="11"/>
-    </row>
-    <row r="613" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G612" s="8"/>
+    </row>
+    <row r="613" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C613" s="11"/>
       <c r="D613" s="11"/>
       <c r="E613" s="11"/>
-    </row>
-    <row r="614" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G613" s="8"/>
+    </row>
+    <row r="614" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C614" s="11"/>
       <c r="D614" s="11"/>
       <c r="E614" s="11"/>
-    </row>
-    <row r="615" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G614" s="8"/>
+    </row>
+    <row r="615" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C615" s="11"/>
       <c r="D615" s="11"/>
       <c r="E615" s="11"/>
-    </row>
-    <row r="616" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G615" s="8"/>
+    </row>
+    <row r="616" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C616" s="11"/>
       <c r="D616" s="11"/>
       <c r="E616" s="11"/>
-    </row>
-    <row r="617" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G616" s="8"/>
+    </row>
+    <row r="617" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C617" s="11"/>
       <c r="D617" s="11"/>
       <c r="E617" s="11"/>
-    </row>
-    <row r="618" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G617" s="8"/>
+    </row>
+    <row r="618" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C618" s="11"/>
       <c r="D618" s="11"/>
       <c r="E618" s="11"/>
-    </row>
-    <row r="619" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G618" s="8"/>
+    </row>
+    <row r="619" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C619" s="11"/>
       <c r="D619" s="11"/>
       <c r="E619" s="11"/>
-    </row>
-    <row r="620" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G619" s="8"/>
+    </row>
+    <row r="620" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C620" s="11"/>
       <c r="D620" s="11"/>
       <c r="E620" s="11"/>
-    </row>
-    <row r="621" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G620" s="8"/>
+    </row>
+    <row r="621" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C621" s="11"/>
       <c r="D621" s="11"/>
       <c r="E621" s="11"/>
-    </row>
-    <row r="622" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G621" s="8"/>
+    </row>
+    <row r="622" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C622" s="11"/>
       <c r="D622" s="11"/>
       <c r="E622" s="11"/>
-    </row>
-    <row r="623" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G622" s="8"/>
+    </row>
+    <row r="623" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C623" s="11"/>
       <c r="D623" s="11"/>
       <c r="E623" s="11"/>
-    </row>
-    <row r="624" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G623" s="8"/>
+    </row>
+    <row r="624" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C624" s="11"/>
       <c r="D624" s="11"/>
       <c r="E624" s="11"/>
-    </row>
-    <row r="625" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G624" s="8"/>
+    </row>
+    <row r="625" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C625" s="11"/>
       <c r="D625" s="11"/>
       <c r="E625" s="11"/>
-    </row>
-    <row r="626" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G625" s="8"/>
+    </row>
+    <row r="626" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C626" s="11"/>
       <c r="D626" s="11"/>
       <c r="E626" s="11"/>
-    </row>
-    <row r="627" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G626" s="8"/>
+    </row>
+    <row r="627" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C627" s="11"/>
       <c r="D627" s="11"/>
       <c r="E627" s="11"/>
-    </row>
-    <row r="628" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G627" s="8"/>
+    </row>
+    <row r="628" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C628" s="11"/>
       <c r="D628" s="11"/>
       <c r="E628" s="11"/>
-    </row>
-    <row r="629" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G628" s="8"/>
+    </row>
+    <row r="629" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C629" s="11"/>
       <c r="D629" s="11"/>
       <c r="E629" s="11"/>
-    </row>
-    <row r="630" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G629" s="8"/>
+    </row>
+    <row r="630" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C630" s="11"/>
       <c r="D630" s="11"/>
       <c r="E630" s="11"/>
-    </row>
-    <row r="631" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G630" s="8"/>
+    </row>
+    <row r="631" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C631" s="11"/>
       <c r="D631" s="11"/>
       <c r="E631" s="11"/>
-    </row>
-    <row r="632" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G631" s="8"/>
+    </row>
+    <row r="632" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C632" s="11"/>
       <c r="D632" s="11"/>
       <c r="E632" s="11"/>
-    </row>
-    <row r="633" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G632" s="8"/>
+    </row>
+    <row r="633" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C633" s="11"/>
       <c r="D633" s="11"/>
       <c r="E633" s="11"/>
-    </row>
-    <row r="634" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G633" s="8"/>
+    </row>
+    <row r="634" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C634" s="11"/>
       <c r="D634" s="11"/>
       <c r="E634" s="11"/>
-    </row>
-    <row r="635" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G634" s="8"/>
+    </row>
+    <row r="635" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C635" s="11"/>
       <c r="D635" s="11"/>
       <c r="E635" s="11"/>
-    </row>
-    <row r="636" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G635" s="8"/>
+    </row>
+    <row r="636" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C636" s="11"/>
       <c r="D636" s="11"/>
       <c r="E636" s="11"/>
-    </row>
-    <row r="637" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G636" s="8"/>
+    </row>
+    <row r="637" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C637" s="11"/>
       <c r="D637" s="11"/>
       <c r="E637" s="11"/>
-    </row>
-    <row r="638" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G637" s="8"/>
+    </row>
+    <row r="638" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C638" s="11"/>
       <c r="D638" s="11"/>
       <c r="E638" s="11"/>
-    </row>
-    <row r="639" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G638" s="8"/>
+    </row>
+    <row r="639" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C639" s="11"/>
       <c r="D639" s="11"/>
       <c r="E639" s="11"/>
-    </row>
-    <row r="640" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G639" s="8"/>
+    </row>
+    <row r="640" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C640" s="11"/>
       <c r="D640" s="11"/>
       <c r="E640" s="11"/>
-    </row>
-    <row r="641" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G640" s="8"/>
+    </row>
+    <row r="641" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C641" s="11"/>
       <c r="D641" s="11"/>
       <c r="E641" s="11"/>
-    </row>
-    <row r="642" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G641" s="8"/>
+    </row>
+    <row r="642" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C642" s="11"/>
       <c r="D642" s="11"/>
       <c r="E642" s="11"/>
-    </row>
-    <row r="643" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G642" s="8"/>
+    </row>
+    <row r="643" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C643" s="11"/>
       <c r="D643" s="11"/>
       <c r="E643" s="11"/>
-    </row>
-    <row r="644" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G643" s="8"/>
+    </row>
+    <row r="644" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C644" s="11"/>
       <c r="D644" s="11"/>
       <c r="E644" s="11"/>
-    </row>
-    <row r="645" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G644" s="8"/>
+    </row>
+    <row r="645" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C645" s="11"/>
       <c r="D645" s="11"/>
       <c r="E645" s="11"/>
-    </row>
-    <row r="646" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G645" s="8"/>
+    </row>
+    <row r="646" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C646" s="11"/>
       <c r="D646" s="11"/>
       <c r="E646" s="11"/>
-    </row>
-    <row r="647" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G646" s="8"/>
+    </row>
+    <row r="647" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C647" s="11"/>
       <c r="D647" s="11"/>
       <c r="E647" s="11"/>
-    </row>
-    <row r="648" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G647" s="8"/>
+    </row>
+    <row r="648" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C648" s="11"/>
       <c r="D648" s="11"/>
       <c r="E648" s="11"/>
-    </row>
-    <row r="649" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G648" s="8"/>
+    </row>
+    <row r="649" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C649" s="11"/>
       <c r="D649" s="11"/>
       <c r="E649" s="11"/>
-    </row>
-    <row r="650" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G649" s="8"/>
+    </row>
+    <row r="650" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C650" s="11"/>
       <c r="D650" s="11"/>
       <c r="E650" s="11"/>
-    </row>
-    <row r="651" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G650" s="8"/>
+    </row>
+    <row r="651" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C651" s="11"/>
       <c r="D651" s="11"/>
       <c r="E651" s="11"/>
-    </row>
-    <row r="652" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G651" s="8"/>
+    </row>
+    <row r="652" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C652" s="11"/>
       <c r="D652" s="11"/>
       <c r="E652" s="11"/>
-    </row>
-    <row r="653" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G652" s="8"/>
+    </row>
+    <row r="653" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C653" s="11"/>
       <c r="D653" s="11"/>
       <c r="E653" s="11"/>
-    </row>
-    <row r="654" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G653" s="8"/>
+    </row>
+    <row r="654" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C654" s="11"/>
       <c r="D654" s="11"/>
       <c r="E654" s="11"/>
-    </row>
-    <row r="655" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G654" s="8"/>
+    </row>
+    <row r="655" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C655" s="11"/>
       <c r="D655" s="11"/>
       <c r="E655" s="11"/>
-    </row>
-    <row r="656" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G655" s="8"/>
+    </row>
+    <row r="656" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C656" s="11"/>
       <c r="D656" s="11"/>
       <c r="E656" s="11"/>
-    </row>
-    <row r="657" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G656" s="8"/>
+    </row>
+    <row r="657" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C657" s="11"/>
       <c r="D657" s="11"/>
       <c r="E657" s="11"/>
-    </row>
-    <row r="658" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G657" s="8"/>
+    </row>
+    <row r="658" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C658" s="11"/>
       <c r="D658" s="11"/>
       <c r="E658" s="11"/>
-    </row>
-    <row r="659" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G658" s="8"/>
+    </row>
+    <row r="659" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C659" s="11"/>
       <c r="D659" s="11"/>
       <c r="E659" s="11"/>
-    </row>
-    <row r="660" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G659" s="8"/>
+    </row>
+    <row r="660" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C660" s="11"/>
       <c r="D660" s="11"/>
       <c r="E660" s="11"/>
-    </row>
-    <row r="661" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G660" s="8"/>
+    </row>
+    <row r="661" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C661" s="11"/>
       <c r="D661" s="11"/>
       <c r="E661" s="11"/>
-    </row>
-    <row r="662" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G661" s="8"/>
+    </row>
+    <row r="662" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C662" s="11"/>
       <c r="D662" s="11"/>
       <c r="E662" s="11"/>
-    </row>
-    <row r="663" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G662" s="8"/>
+    </row>
+    <row r="663" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C663" s="11"/>
       <c r="D663" s="11"/>
       <c r="E663" s="11"/>
-    </row>
-    <row r="664" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G663" s="8"/>
+    </row>
+    <row r="664" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C664" s="11"/>
       <c r="D664" s="11"/>
       <c r="E664" s="11"/>
-    </row>
-    <row r="665" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G664" s="8"/>
+    </row>
+    <row r="665" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C665" s="11"/>
       <c r="D665" s="11"/>
       <c r="E665" s="11"/>
-    </row>
-    <row r="666" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G665" s="8"/>
+    </row>
+    <row r="666" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C666" s="11"/>
       <c r="D666" s="11"/>
       <c r="E666" s="11"/>
-    </row>
-    <row r="667" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G666" s="8"/>
+    </row>
+    <row r="667" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C667" s="11"/>
       <c r="D667" s="11"/>
       <c r="E667" s="11"/>
-    </row>
-    <row r="668" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G667" s="8"/>
+    </row>
+    <row r="668" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C668" s="11"/>
       <c r="D668" s="11"/>
       <c r="E668" s="11"/>
-    </row>
-    <row r="669" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G668" s="8"/>
+    </row>
+    <row r="669" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C669" s="11"/>
       <c r="D669" s="11"/>
       <c r="E669" s="11"/>
-    </row>
-    <row r="670" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G669" s="8"/>
+    </row>
+    <row r="670" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C670" s="11"/>
       <c r="D670" s="11"/>
       <c r="E670" s="11"/>
-    </row>
-    <row r="671" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G670" s="8"/>
+    </row>
+    <row r="671" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C671" s="11"/>
       <c r="D671" s="11"/>
       <c r="E671" s="11"/>
-    </row>
-    <row r="672" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G671" s="8"/>
+    </row>
+    <row r="672" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C672" s="11"/>
       <c r="D672" s="11"/>
       <c r="E672" s="11"/>
-    </row>
-    <row r="673" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G672" s="8"/>
+    </row>
+    <row r="673" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C673" s="11"/>
       <c r="D673" s="11"/>
       <c r="E673" s="11"/>
-    </row>
-    <row r="674" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G673" s="8"/>
+    </row>
+    <row r="674" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C674" s="11"/>
       <c r="D674" s="11"/>
       <c r="E674" s="11"/>
-    </row>
-    <row r="675" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G674" s="8"/>
+    </row>
+    <row r="675" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C675" s="11"/>
       <c r="D675" s="11"/>
       <c r="E675" s="11"/>
-    </row>
-    <row r="676" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G675" s="8"/>
+    </row>
+    <row r="676" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C676" s="11"/>
       <c r="D676" s="11"/>
       <c r="E676" s="11"/>
-    </row>
-    <row r="677" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G676" s="8"/>
+    </row>
+    <row r="677" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C677" s="11"/>
       <c r="D677" s="11"/>
       <c r="E677" s="11"/>
-    </row>
-    <row r="678" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G677" s="8"/>
+    </row>
+    <row r="678" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C678" s="11"/>
       <c r="D678" s="11"/>
       <c r="E678" s="11"/>
-    </row>
-    <row r="679" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G678" s="8"/>
+    </row>
+    <row r="679" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C679" s="11"/>
       <c r="D679" s="11"/>
       <c r="E679" s="11"/>
-    </row>
-    <row r="680" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G679" s="8"/>
+    </row>
+    <row r="680" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C680" s="11"/>
       <c r="D680" s="11"/>
       <c r="E680" s="11"/>
-    </row>
-    <row r="681" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G680" s="8"/>
+    </row>
+    <row r="681" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C681" s="11"/>
       <c r="D681" s="11"/>
       <c r="E681" s="11"/>
-    </row>
-    <row r="682" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G681" s="8"/>
+    </row>
+    <row r="682" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C682" s="11"/>
       <c r="D682" s="11"/>
       <c r="E682" s="11"/>
-    </row>
-    <row r="683" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G682" s="8"/>
+    </row>
+    <row r="683" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C683" s="11"/>
       <c r="D683" s="11"/>
       <c r="E683" s="11"/>
-    </row>
-    <row r="684" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G683" s="8"/>
+    </row>
+    <row r="684" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C684" s="11"/>
       <c r="D684" s="11"/>
       <c r="E684" s="11"/>
-    </row>
-    <row r="685" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G684" s="8"/>
+    </row>
+    <row r="685" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C685" s="11"/>
       <c r="D685" s="11"/>
       <c r="E685" s="11"/>
-    </row>
-    <row r="686" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G685" s="8"/>
+    </row>
+    <row r="686" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C686" s="11"/>
       <c r="D686" s="11"/>
       <c r="E686" s="11"/>
-    </row>
-    <row r="687" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G686" s="8"/>
+    </row>
+    <row r="687" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C687" s="11"/>
       <c r="D687" s="11"/>
       <c r="E687" s="11"/>
-    </row>
-    <row r="688" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G687" s="8"/>
+    </row>
+    <row r="688" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C688" s="11"/>
       <c r="D688" s="11"/>
       <c r="E688" s="11"/>
-    </row>
-    <row r="689" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G688" s="8"/>
+    </row>
+    <row r="689" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C689" s="11"/>
       <c r="D689" s="11"/>
       <c r="E689" s="11"/>
-    </row>
-    <row r="690" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G689" s="8"/>
+    </row>
+    <row r="690" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C690" s="11"/>
       <c r="D690" s="11"/>
       <c r="E690" s="11"/>
-    </row>
-    <row r="691" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G690" s="8"/>
+    </row>
+    <row r="691" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C691" s="11"/>
       <c r="D691" s="11"/>
       <c r="E691" s="11"/>
-    </row>
-    <row r="692" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G691" s="8"/>
+    </row>
+    <row r="692" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C692" s="11"/>
       <c r="D692" s="11"/>
       <c r="E692" s="11"/>
-    </row>
-    <row r="693" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G692" s="8"/>
+    </row>
+    <row r="693" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C693" s="11"/>
       <c r="D693" s="11"/>
       <c r="E693" s="11"/>
-    </row>
-    <row r="694" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G693" s="8"/>
+    </row>
+    <row r="694" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C694" s="11"/>
       <c r="D694" s="11"/>
       <c r="E694" s="11"/>
-    </row>
-    <row r="695" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G694" s="8"/>
+    </row>
+    <row r="695" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C695" s="11"/>
       <c r="D695" s="11"/>
       <c r="E695" s="11"/>
-    </row>
-    <row r="696" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G695" s="8"/>
+    </row>
+    <row r="696" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C696" s="11"/>
       <c r="D696" s="11"/>
       <c r="E696" s="11"/>
-    </row>
-    <row r="697" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G696" s="8"/>
+    </row>
+    <row r="697" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C697" s="11"/>
       <c r="D697" s="11"/>
       <c r="E697" s="11"/>
-    </row>
-    <row r="698" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G697" s="8"/>
+    </row>
+    <row r="698" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C698" s="11"/>
       <c r="D698" s="11"/>
       <c r="E698" s="11"/>
-    </row>
-    <row r="699" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G698" s="8"/>
+    </row>
+    <row r="699" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C699" s="11"/>
       <c r="D699" s="11"/>
       <c r="E699" s="11"/>
-    </row>
-    <row r="700" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G699" s="8"/>
+    </row>
+    <row r="700" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C700" s="11"/>
       <c r="D700" s="11"/>
       <c r="E700" s="11"/>
-    </row>
-    <row r="701" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G700" s="8"/>
+    </row>
+    <row r="701" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C701" s="11"/>
       <c r="D701" s="11"/>
       <c r="E701" s="11"/>
-    </row>
-    <row r="702" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G701" s="8"/>
+    </row>
+    <row r="702" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C702" s="11"/>
       <c r="D702" s="11"/>
       <c r="E702" s="11"/>
-    </row>
-    <row r="703" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G702" s="8"/>
+    </row>
+    <row r="703" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C703" s="11"/>
       <c r="D703" s="11"/>
       <c r="E703" s="11"/>
-    </row>
-    <row r="704" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G703" s="8"/>
+    </row>
+    <row r="704" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C704" s="11"/>
       <c r="D704" s="11"/>
       <c r="E704" s="11"/>
-    </row>
-    <row r="705" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G704" s="8"/>
+    </row>
+    <row r="705" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C705" s="11"/>
       <c r="D705" s="11"/>
       <c r="E705" s="11"/>
-    </row>
-    <row r="706" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G705" s="8"/>
+    </row>
+    <row r="706" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C706" s="11"/>
       <c r="D706" s="11"/>
       <c r="E706" s="11"/>
-    </row>
-    <row r="707" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G706" s="8"/>
+    </row>
+    <row r="707" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C707" s="11"/>
       <c r="D707" s="11"/>
       <c r="E707" s="11"/>
-    </row>
-    <row r="708" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G707" s="8"/>
+    </row>
+    <row r="708" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C708" s="11"/>
       <c r="D708" s="11"/>
       <c r="E708" s="11"/>
-    </row>
-    <row r="709" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G708" s="8"/>
+    </row>
+    <row r="709" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C709" s="11"/>
       <c r="D709" s="11"/>
       <c r="E709" s="11"/>
-    </row>
-    <row r="710" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G709" s="8"/>
+    </row>
+    <row r="710" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C710" s="11"/>
       <c r="D710" s="11"/>
       <c r="E710" s="11"/>
-    </row>
-    <row r="711" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G710" s="8"/>
+    </row>
+    <row r="711" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C711" s="11"/>
       <c r="D711" s="11"/>
       <c r="E711" s="11"/>
-    </row>
-    <row r="712" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G711" s="8"/>
+    </row>
+    <row r="712" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C712" s="11"/>
       <c r="D712" s="11"/>
       <c r="E712" s="11"/>
-    </row>
-    <row r="713" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G712" s="8"/>
+    </row>
+    <row r="713" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C713" s="11"/>
       <c r="D713" s="11"/>
       <c r="E713" s="11"/>
-    </row>
-    <row r="714" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G713" s="8"/>
+    </row>
+    <row r="714" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C714" s="11"/>
       <c r="D714" s="11"/>
       <c r="E714" s="11"/>
-    </row>
-    <row r="715" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G714" s="8"/>
+    </row>
+    <row r="715" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C715" s="11"/>
       <c r="D715" s="11"/>
       <c r="E715" s="11"/>
-    </row>
-    <row r="716" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G715" s="8"/>
+    </row>
+    <row r="716" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C716" s="11"/>
       <c r="D716" s="11"/>
       <c r="E716" s="11"/>
-    </row>
-    <row r="717" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G716" s="8"/>
+    </row>
+    <row r="717" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C717" s="11"/>
       <c r="D717" s="11"/>
       <c r="E717" s="11"/>
-    </row>
-    <row r="718" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G717" s="8"/>
+    </row>
+    <row r="718" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C718" s="11"/>
       <c r="D718" s="11"/>
       <c r="E718" s="11"/>
-    </row>
-    <row r="719" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G718" s="8"/>
+    </row>
+    <row r="719" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C719" s="11"/>
       <c r="D719" s="11"/>
       <c r="E719" s="11"/>
-    </row>
-    <row r="720" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G719" s="8"/>
+    </row>
+    <row r="720" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C720" s="11"/>
       <c r="D720" s="11"/>
       <c r="E720" s="11"/>
-    </row>
-    <row r="721" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G720" s="8"/>
+    </row>
+    <row r="721" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C721" s="11"/>
       <c r="D721" s="11"/>
       <c r="E721" s="11"/>
-    </row>
-    <row r="722" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G721" s="8"/>
+    </row>
+    <row r="722" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C722" s="11"/>
       <c r="D722" s="11"/>
       <c r="E722" s="11"/>
-    </row>
-    <row r="723" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G722" s="8"/>
+    </row>
+    <row r="723" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C723" s="11"/>
       <c r="D723" s="11"/>
       <c r="E723" s="11"/>
-    </row>
-    <row r="724" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G723" s="8"/>
+    </row>
+    <row r="724" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C724" s="11"/>
       <c r="D724" s="11"/>
       <c r="E724" s="11"/>
-    </row>
-    <row r="725" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G724" s="8"/>
+    </row>
+    <row r="725" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C725" s="11"/>
       <c r="D725" s="11"/>
       <c r="E725" s="11"/>
-    </row>
-    <row r="726" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G725" s="8"/>
+    </row>
+    <row r="726" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C726" s="11"/>
       <c r="D726" s="11"/>
       <c r="E726" s="11"/>
-    </row>
-    <row r="727" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G726" s="8"/>
+    </row>
+    <row r="727" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C727" s="11"/>
       <c r="D727" s="11"/>
       <c r="E727" s="11"/>
-    </row>
-    <row r="728" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G727" s="8"/>
+    </row>
+    <row r="728" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C728" s="11"/>
       <c r="D728" s="11"/>
       <c r="E728" s="11"/>
-    </row>
-    <row r="729" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G728" s="8"/>
+    </row>
+    <row r="729" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C729" s="11"/>
       <c r="D729" s="11"/>
       <c r="E729" s="11"/>
-    </row>
-    <row r="730" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G729" s="8"/>
+    </row>
+    <row r="730" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C730" s="11"/>
       <c r="D730" s="11"/>
       <c r="E730" s="11"/>
-    </row>
-    <row r="731" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G730" s="8"/>
+    </row>
+    <row r="731" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C731" s="11"/>
       <c r="D731" s="11"/>
       <c r="E731" s="11"/>
-    </row>
-    <row r="732" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G731" s="8"/>
+    </row>
+    <row r="732" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C732" s="11"/>
       <c r="D732" s="11"/>
       <c r="E732" s="11"/>
-    </row>
-    <row r="733" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G732" s="8"/>
+    </row>
+    <row r="733" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C733" s="11"/>
       <c r="D733" s="11"/>
       <c r="E733" s="11"/>
-    </row>
-    <row r="734" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G733" s="8"/>
+    </row>
+    <row r="734" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C734" s="11"/>
       <c r="D734" s="11"/>
       <c r="E734" s="11"/>
-    </row>
-    <row r="735" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G734" s="8"/>
+    </row>
+    <row r="735" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C735" s="11"/>
       <c r="D735" s="11"/>
       <c r="E735" s="11"/>
-    </row>
-    <row r="736" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G735" s="8"/>
+    </row>
+    <row r="736" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C736" s="11"/>
       <c r="D736" s="11"/>
       <c r="E736" s="11"/>
-    </row>
-    <row r="737" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G736" s="8"/>
+    </row>
+    <row r="737" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C737" s="11"/>
       <c r="D737" s="11"/>
       <c r="E737" s="11"/>
-    </row>
-    <row r="738" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G737" s="8"/>
+    </row>
+    <row r="738" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C738" s="11"/>
       <c r="D738" s="11"/>
       <c r="E738" s="11"/>
-    </row>
-    <row r="739" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G738" s="8"/>
+    </row>
+    <row r="739" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C739" s="11"/>
       <c r="D739" s="11"/>
       <c r="E739" s="11"/>
-    </row>
-    <row r="740" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G739" s="8"/>
+    </row>
+    <row r="740" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C740" s="11"/>
       <c r="D740" s="11"/>
       <c r="E740" s="11"/>
-    </row>
-    <row r="741" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G740" s="8"/>
+    </row>
+    <row r="741" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C741" s="11"/>
       <c r="D741" s="11"/>
       <c r="E741" s="11"/>
-    </row>
-    <row r="742" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G741" s="8"/>
+    </row>
+    <row r="742" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C742" s="11"/>
       <c r="D742" s="11"/>
       <c r="E742" s="11"/>
-    </row>
-    <row r="743" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G742" s="8"/>
+    </row>
+    <row r="743" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C743" s="11"/>
       <c r="D743" s="11"/>
       <c r="E743" s="11"/>
-    </row>
-    <row r="744" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G743" s="8"/>
+    </row>
+    <row r="744" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C744" s="11"/>
       <c r="D744" s="11"/>
       <c r="E744" s="11"/>
-    </row>
-    <row r="745" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G744" s="8"/>
+    </row>
+    <row r="745" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C745" s="11"/>
       <c r="D745" s="11"/>
       <c r="E745" s="11"/>
-    </row>
-    <row r="746" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G745" s="8"/>
+    </row>
+    <row r="746" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C746" s="11"/>
       <c r="D746" s="11"/>
       <c r="E746" s="11"/>
-    </row>
-    <row r="747" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G746" s="8"/>
+    </row>
+    <row r="747" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C747" s="11"/>
       <c r="D747" s="11"/>
       <c r="E747" s="11"/>
-    </row>
-    <row r="748" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G747" s="8"/>
+    </row>
+    <row r="748" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C748" s="11"/>
       <c r="D748" s="11"/>
       <c r="E748" s="11"/>
-    </row>
-    <row r="749" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G748" s="8"/>
+    </row>
+    <row r="749" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C749" s="11"/>
       <c r="D749" s="11"/>
       <c r="E749" s="11"/>
-    </row>
-    <row r="750" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G749" s="8"/>
+    </row>
+    <row r="750" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C750" s="11"/>
       <c r="D750" s="11"/>
       <c r="E750" s="11"/>
-    </row>
-    <row r="751" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G750" s="8"/>
+    </row>
+    <row r="751" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C751" s="11"/>
       <c r="D751" s="11"/>
       <c r="E751" s="11"/>
-    </row>
-    <row r="752" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G751" s="8"/>
+    </row>
+    <row r="752" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C752" s="11"/>
       <c r="D752" s="11"/>
       <c r="E752" s="11"/>
-    </row>
-    <row r="753" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G752" s="8"/>
+    </row>
+    <row r="753" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C753" s="11"/>
       <c r="D753" s="11"/>
       <c r="E753" s="11"/>
-    </row>
-    <row r="754" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G753" s="8"/>
+    </row>
+    <row r="754" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C754" s="11"/>
       <c r="D754" s="11"/>
       <c r="E754" s="11"/>
-    </row>
-    <row r="755" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G754" s="8"/>
+    </row>
+    <row r="755" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C755" s="11"/>
       <c r="D755" s="11"/>
       <c r="E755" s="11"/>
-    </row>
-    <row r="756" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G755" s="8"/>
+    </row>
+    <row r="756" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C756" s="11"/>
       <c r="D756" s="11"/>
       <c r="E756" s="11"/>
-    </row>
-    <row r="757" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G756" s="8"/>
+    </row>
+    <row r="757" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C757" s="11"/>
       <c r="D757" s="11"/>
       <c r="E757" s="11"/>
-    </row>
-    <row r="758" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G757" s="8"/>
+    </row>
+    <row r="758" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C758" s="11"/>
       <c r="D758" s="11"/>
       <c r="E758" s="11"/>
-    </row>
-    <row r="759" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G758" s="8"/>
+    </row>
+    <row r="759" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C759" s="11"/>
       <c r="D759" s="11"/>
       <c r="E759" s="11"/>
-    </row>
-    <row r="760" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G759" s="8"/>
+    </row>
+    <row r="760" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C760" s="11"/>
       <c r="D760" s="11"/>
       <c r="E760" s="11"/>
-    </row>
-    <row r="761" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G760" s="8"/>
+    </row>
+    <row r="761" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C761" s="11"/>
       <c r="D761" s="11"/>
       <c r="E761" s="11"/>
-    </row>
-    <row r="762" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G761" s="8"/>
+    </row>
+    <row r="762" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C762" s="11"/>
       <c r="D762" s="11"/>
       <c r="E762" s="11"/>
-    </row>
-    <row r="763" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G762" s="8"/>
+    </row>
+    <row r="763" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C763" s="11"/>
       <c r="D763" s="11"/>
       <c r="E763" s="11"/>
-    </row>
-    <row r="764" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G763" s="8"/>
+    </row>
+    <row r="764" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C764" s="11"/>
       <c r="D764" s="11"/>
       <c r="E764" s="11"/>
-    </row>
-    <row r="765" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G764" s="8"/>
+    </row>
+    <row r="765" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C765" s="11"/>
       <c r="D765" s="11"/>
       <c r="E765" s="11"/>
-    </row>
-    <row r="766" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G765" s="8"/>
+    </row>
+    <row r="766" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C766" s="11"/>
       <c r="D766" s="11"/>
       <c r="E766" s="11"/>
-    </row>
-    <row r="767" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G766" s="8"/>
+    </row>
+    <row r="767" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C767" s="11"/>
       <c r="D767" s="11"/>
       <c r="E767" s="11"/>
-    </row>
-    <row r="768" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G767" s="8"/>
+    </row>
+    <row r="768" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C768" s="11"/>
       <c r="D768" s="11"/>
       <c r="E768" s="11"/>
-    </row>
-    <row r="769" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G768" s="8"/>
+    </row>
+    <row r="769" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C769" s="11"/>
       <c r="D769" s="11"/>
       <c r="E769" s="11"/>
-    </row>
-    <row r="770" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G769" s="8"/>
+    </row>
+    <row r="770" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C770" s="11"/>
       <c r="D770" s="11"/>
       <c r="E770" s="11"/>
-    </row>
-    <row r="771" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G770" s="8"/>
+    </row>
+    <row r="771" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C771" s="11"/>
       <c r="D771" s="11"/>
       <c r="E771" s="11"/>
-    </row>
-    <row r="772" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G771" s="8"/>
+    </row>
+    <row r="772" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C772" s="11"/>
       <c r="D772" s="11"/>
       <c r="E772" s="11"/>
-    </row>
-    <row r="773" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G772" s="8"/>
+    </row>
+    <row r="773" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C773" s="11"/>
       <c r="D773" s="11"/>
       <c r="E773" s="11"/>
-    </row>
-    <row r="774" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G773" s="8"/>
+    </row>
+    <row r="774" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C774" s="11"/>
       <c r="D774" s="11"/>
       <c r="E774" s="11"/>
-    </row>
-    <row r="775" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G774" s="8"/>
+    </row>
+    <row r="775" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C775" s="11"/>
       <c r="D775" s="11"/>
       <c r="E775" s="11"/>
-    </row>
-    <row r="776" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G775" s="8"/>
+    </row>
+    <row r="776" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C776" s="11"/>
       <c r="D776" s="11"/>
       <c r="E776" s="11"/>
-    </row>
-    <row r="777" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G776" s="8"/>
+    </row>
+    <row r="777" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C777" s="11"/>
       <c r="D777" s="11"/>
       <c r="E777" s="11"/>
-    </row>
-    <row r="778" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G777" s="8"/>
+    </row>
+    <row r="778" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C778" s="11"/>
       <c r="D778" s="11"/>
       <c r="E778" s="11"/>
-    </row>
-    <row r="779" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G778" s="8"/>
+    </row>
+    <row r="779" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C779" s="11"/>
       <c r="D779" s="11"/>
       <c r="E779" s="11"/>
-    </row>
-    <row r="780" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G779" s="8"/>
+    </row>
+    <row r="780" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C780" s="11"/>
       <c r="D780" s="11"/>
       <c r="E780" s="11"/>
-    </row>
-    <row r="781" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G780" s="8"/>
+    </row>
+    <row r="781" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C781" s="11"/>
       <c r="D781" s="11"/>
       <c r="E781" s="11"/>
-    </row>
-    <row r="782" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G781" s="8"/>
+    </row>
+    <row r="782" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C782" s="11"/>
       <c r="D782" s="11"/>
       <c r="E782" s="11"/>
-    </row>
-    <row r="783" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G782" s="8"/>
+    </row>
+    <row r="783" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C783" s="11"/>
       <c r="D783" s="11"/>
       <c r="E783" s="11"/>
-    </row>
-    <row r="784" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G783" s="8"/>
+    </row>
+    <row r="784" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C784" s="11"/>
       <c r="D784" s="11"/>
       <c r="E784" s="11"/>
-    </row>
-    <row r="785" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G784" s="8"/>
+    </row>
+    <row r="785" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C785" s="11"/>
       <c r="D785" s="11"/>
       <c r="E785" s="11"/>
-    </row>
-    <row r="786" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G785" s="8"/>
+    </row>
+    <row r="786" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C786" s="11"/>
       <c r="D786" s="11"/>
       <c r="E786" s="11"/>
-    </row>
-    <row r="787" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G786" s="8"/>
+    </row>
+    <row r="787" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C787" s="11"/>
       <c r="D787" s="11"/>
       <c r="E787" s="11"/>
-    </row>
-    <row r="788" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G787" s="8"/>
+    </row>
+    <row r="788" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C788" s="11"/>
       <c r="D788" s="11"/>
       <c r="E788" s="11"/>
-    </row>
-    <row r="789" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G788" s="8"/>
+    </row>
+    <row r="789" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C789" s="11"/>
       <c r="D789" s="11"/>
       <c r="E789" s="11"/>
-    </row>
-    <row r="790" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G789" s="8"/>
+    </row>
+    <row r="790" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C790" s="11"/>
       <c r="D790" s="11"/>
       <c r="E790" s="11"/>
-    </row>
-    <row r="791" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G790" s="8"/>
+    </row>
+    <row r="791" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C791" s="11"/>
       <c r="D791" s="11"/>
       <c r="E791" s="11"/>
-    </row>
-    <row r="792" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G791" s="8"/>
+    </row>
+    <row r="792" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C792" s="11"/>
       <c r="D792" s="11"/>
       <c r="E792" s="11"/>
-    </row>
-    <row r="793" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G792" s="8"/>
+    </row>
+    <row r="793" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C793" s="11"/>
       <c r="D793" s="11"/>
       <c r="E793" s="11"/>
-    </row>
-    <row r="794" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G793" s="8"/>
+    </row>
+    <row r="794" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C794" s="11"/>
       <c r="D794" s="11"/>
       <c r="E794" s="11"/>
-    </row>
-    <row r="795" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G794" s="8"/>
+    </row>
+    <row r="795" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C795" s="11"/>
       <c r="D795" s="11"/>
       <c r="E795" s="11"/>
-    </row>
-    <row r="796" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G795" s="8"/>
+    </row>
+    <row r="796" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C796" s="11"/>
       <c r="D796" s="11"/>
       <c r="E796" s="11"/>
-    </row>
-    <row r="797" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G796" s="8"/>
+    </row>
+    <row r="797" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C797" s="11"/>
       <c r="D797" s="11"/>
       <c r="E797" s="11"/>
-    </row>
-    <row r="798" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G797" s="8"/>
+    </row>
+    <row r="798" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C798" s="11"/>
       <c r="D798" s="11"/>
       <c r="E798" s="11"/>
-    </row>
-    <row r="799" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G798" s="8"/>
+    </row>
+    <row r="799" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C799" s="11"/>
       <c r="D799" s="11"/>
       <c r="E799" s="11"/>
-    </row>
-    <row r="800" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G799" s="8"/>
+    </row>
+    <row r="800" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C800" s="11"/>
       <c r="D800" s="11"/>
       <c r="E800" s="11"/>
-    </row>
-    <row r="801" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G800" s="8"/>
+    </row>
+    <row r="801" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C801" s="11"/>
       <c r="D801" s="11"/>
       <c r="E801" s="11"/>
-    </row>
-    <row r="802" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G801" s="8"/>
+    </row>
+    <row r="802" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C802" s="11"/>
       <c r="D802" s="11"/>
       <c r="E802" s="11"/>
-    </row>
-    <row r="803" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G802" s="8"/>
+    </row>
+    <row r="803" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C803" s="11"/>
       <c r="D803" s="11"/>
       <c r="E803" s="11"/>
-    </row>
-    <row r="804" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G803" s="8"/>
+    </row>
+    <row r="804" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C804" s="11"/>
       <c r="D804" s="11"/>
       <c r="E804" s="11"/>
-    </row>
-    <row r="805" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G804" s="8"/>
+    </row>
+    <row r="805" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C805" s="11"/>
       <c r="D805" s="11"/>
       <c r="E805" s="11"/>
-    </row>
-    <row r="806" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G805" s="8"/>
+    </row>
+    <row r="806" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C806" s="11"/>
       <c r="D806" s="11"/>
       <c r="E806" s="11"/>
-    </row>
-    <row r="807" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G806" s="8"/>
+    </row>
+    <row r="807" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C807" s="11"/>
       <c r="D807" s="11"/>
       <c r="E807" s="11"/>
-    </row>
-    <row r="808" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G807" s="8"/>
+    </row>
+    <row r="808" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C808" s="11"/>
       <c r="D808" s="11"/>
       <c r="E808" s="11"/>
-    </row>
-    <row r="809" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G808" s="8"/>
+    </row>
+    <row r="809" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C809" s="11"/>
       <c r="D809" s="11"/>
       <c r="E809" s="11"/>
-    </row>
-    <row r="810" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G809" s="8"/>
+    </row>
+    <row r="810" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C810" s="11"/>
       <c r="D810" s="11"/>
       <c r="E810" s="11"/>
-    </row>
-    <row r="811" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G810" s="8"/>
+    </row>
+    <row r="811" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C811" s="11"/>
       <c r="D811" s="11"/>
       <c r="E811" s="11"/>
-    </row>
-    <row r="812" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G811" s="8"/>
+    </row>
+    <row r="812" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C812" s="11"/>
       <c r="D812" s="11"/>
       <c r="E812" s="11"/>
-    </row>
-    <row r="813" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G812" s="8"/>
+    </row>
+    <row r="813" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C813" s="11"/>
       <c r="D813" s="11"/>
       <c r="E813" s="11"/>
-    </row>
-    <row r="814" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G813" s="8"/>
+    </row>
+    <row r="814" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C814" s="11"/>
       <c r="D814" s="11"/>
       <c r="E814" s="11"/>
-    </row>
-    <row r="815" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G814" s="8"/>
+    </row>
+    <row r="815" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C815" s="11"/>
       <c r="D815" s="11"/>
       <c r="E815" s="11"/>
-    </row>
-    <row r="816" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G815" s="8"/>
+    </row>
+    <row r="816" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C816" s="11"/>
       <c r="D816" s="11"/>
       <c r="E816" s="11"/>
-    </row>
-    <row r="817" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G816" s="8"/>
+    </row>
+    <row r="817" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C817" s="11"/>
       <c r="D817" s="11"/>
       <c r="E817" s="11"/>
-    </row>
-    <row r="818" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G817" s="8"/>
+    </row>
+    <row r="818" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C818" s="11"/>
       <c r="D818" s="11"/>
       <c r="E818" s="11"/>
-    </row>
-    <row r="819" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G818" s="8"/>
+    </row>
+    <row r="819" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C819" s="11"/>
       <c r="D819" s="11"/>
       <c r="E819" s="11"/>
-    </row>
-    <row r="820" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G819" s="8"/>
+    </row>
+    <row r="820" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C820" s="11"/>
       <c r="D820" s="11"/>
       <c r="E820" s="11"/>
-    </row>
-    <row r="821" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G820" s="8"/>
+    </row>
+    <row r="821" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C821" s="11"/>
       <c r="D821" s="11"/>
       <c r="E821" s="11"/>
-    </row>
-    <row r="822" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G821" s="8"/>
+    </row>
+    <row r="822" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C822" s="11"/>
       <c r="D822" s="11"/>
       <c r="E822" s="11"/>
-    </row>
-    <row r="823" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G822" s="8"/>
+    </row>
+    <row r="823" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C823" s="11"/>
       <c r="D823" s="11"/>
       <c r="E823" s="11"/>
-    </row>
-    <row r="824" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G823" s="8"/>
+    </row>
+    <row r="824" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C824" s="11"/>
       <c r="D824" s="11"/>
       <c r="E824" s="11"/>
-    </row>
-    <row r="825" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G824" s="8"/>
+    </row>
+    <row r="825" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C825" s="11"/>
       <c r="D825" s="11"/>
       <c r="E825" s="11"/>
-    </row>
-    <row r="826" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G825" s="8"/>
+    </row>
+    <row r="826" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C826" s="11"/>
       <c r="D826" s="11"/>
       <c r="E826" s="11"/>
-    </row>
-    <row r="827" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G826" s="8"/>
+    </row>
+    <row r="827" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C827" s="11"/>
       <c r="D827" s="11"/>
       <c r="E827" s="11"/>
-    </row>
-    <row r="828" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G827" s="8"/>
+    </row>
+    <row r="828" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C828" s="11"/>
       <c r="D828" s="11"/>
       <c r="E828" s="11"/>
-    </row>
-    <row r="829" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G828" s="8"/>
+    </row>
+    <row r="829" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C829" s="11"/>
       <c r="D829" s="11"/>
       <c r="E829" s="11"/>
-    </row>
-    <row r="830" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G829" s="8"/>
+    </row>
+    <row r="830" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C830" s="11"/>
       <c r="D830" s="11"/>
       <c r="E830" s="11"/>
-    </row>
-    <row r="831" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G830" s="8"/>
+    </row>
+    <row r="831" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C831" s="11"/>
       <c r="D831" s="11"/>
       <c r="E831" s="11"/>
-    </row>
-    <row r="832" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G831" s="8"/>
+    </row>
+    <row r="832" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C832" s="11"/>
       <c r="D832" s="11"/>
       <c r="E832" s="11"/>
-    </row>
-    <row r="833" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G832" s="8"/>
+    </row>
+    <row r="833" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C833" s="11"/>
       <c r="D833" s="11"/>
       <c r="E833" s="11"/>
-    </row>
-    <row r="834" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G833" s="8"/>
+    </row>
+    <row r="834" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C834" s="11"/>
       <c r="D834" s="11"/>
       <c r="E834" s="11"/>
-    </row>
-    <row r="835" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G834" s="8"/>
+    </row>
+    <row r="835" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C835" s="11"/>
       <c r="D835" s="11"/>
       <c r="E835" s="11"/>
-    </row>
-    <row r="836" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G835" s="8"/>
+    </row>
+    <row r="836" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C836" s="11"/>
       <c r="D836" s="11"/>
       <c r="E836" s="11"/>
-    </row>
-    <row r="837" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G836" s="8"/>
+    </row>
+    <row r="837" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C837" s="11"/>
       <c r="D837" s="11"/>
       <c r="E837" s="11"/>
-    </row>
-    <row r="838" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G837" s="8"/>
+    </row>
+    <row r="838" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C838" s="11"/>
       <c r="D838" s="11"/>
       <c r="E838" s="11"/>
-    </row>
-    <row r="839" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G838" s="8"/>
+    </row>
+    <row r="839" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C839" s="11"/>
       <c r="D839" s="11"/>
       <c r="E839" s="11"/>
-    </row>
-    <row r="840" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G839" s="8"/>
+    </row>
+    <row r="840" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C840" s="11"/>
       <c r="D840" s="11"/>
       <c r="E840" s="11"/>
-    </row>
-    <row r="841" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G840" s="8"/>
+    </row>
+    <row r="841" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C841" s="11"/>
       <c r="D841" s="11"/>
       <c r="E841" s="11"/>
-    </row>
-    <row r="842" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G841" s="8"/>
+    </row>
+    <row r="842" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C842" s="11"/>
       <c r="D842" s="11"/>
       <c r="E842" s="11"/>
-    </row>
-    <row r="843" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G842" s="8"/>
+    </row>
+    <row r="843" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C843" s="11"/>
       <c r="D843" s="11"/>
       <c r="E843" s="11"/>
-    </row>
-    <row r="844" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G843" s="8"/>
+    </row>
+    <row r="844" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C844" s="11"/>
       <c r="D844" s="11"/>
       <c r="E844" s="11"/>
-    </row>
-    <row r="845" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G844" s="8"/>
+    </row>
+    <row r="845" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C845" s="11"/>
       <c r="D845" s="11"/>
       <c r="E845" s="11"/>
-    </row>
-    <row r="846" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G845" s="8"/>
+    </row>
+    <row r="846" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C846" s="11"/>
       <c r="D846" s="11"/>
       <c r="E846" s="11"/>
-    </row>
-    <row r="847" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G846" s="8"/>
+    </row>
+    <row r="847" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C847" s="11"/>
       <c r="D847" s="11"/>
       <c r="E847" s="11"/>
-    </row>
-    <row r="848" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G847" s="8"/>
+    </row>
+    <row r="848" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C848" s="11"/>
       <c r="D848" s="11"/>
       <c r="E848" s="11"/>
-    </row>
-    <row r="849" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G848" s="8"/>
+    </row>
+    <row r="849" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C849" s="11"/>
       <c r="D849" s="11"/>
       <c r="E849" s="11"/>
-    </row>
-    <row r="850" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G849" s="8"/>
+    </row>
+    <row r="850" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C850" s="11"/>
       <c r="D850" s="11"/>
       <c r="E850" s="11"/>
-    </row>
-    <row r="851" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G850" s="8"/>
+    </row>
+    <row r="851" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C851" s="11"/>
       <c r="D851" s="11"/>
       <c r="E851" s="11"/>
-    </row>
-    <row r="852" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G851" s="8"/>
+    </row>
+    <row r="852" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C852" s="11"/>
       <c r="D852" s="11"/>
       <c r="E852" s="11"/>
-    </row>
-    <row r="853" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G852" s="8"/>
+    </row>
+    <row r="853" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C853" s="11"/>
       <c r="D853" s="11"/>
       <c r="E853" s="11"/>
-    </row>
-    <row r="854" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G853" s="8"/>
+    </row>
+    <row r="854" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C854" s="11"/>
       <c r="D854" s="11"/>
       <c r="E854" s="11"/>
-    </row>
-    <row r="855" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G854" s="8"/>
+    </row>
+    <row r="855" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C855" s="11"/>
       <c r="D855" s="11"/>
       <c r="E855" s="11"/>
-    </row>
-    <row r="856" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G855" s="8"/>
+    </row>
+    <row r="856" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C856" s="11"/>
       <c r="D856" s="11"/>
       <c r="E856" s="11"/>
-    </row>
-    <row r="857" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G856" s="8"/>
+    </row>
+    <row r="857" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C857" s="11"/>
       <c r="D857" s="11"/>
       <c r="E857" s="11"/>
-    </row>
-    <row r="858" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G857" s="8"/>
+    </row>
+    <row r="858" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C858" s="11"/>
       <c r="D858" s="11"/>
       <c r="E858" s="11"/>
-    </row>
-    <row r="859" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G858" s="8"/>
+    </row>
+    <row r="859" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C859" s="11"/>
       <c r="D859" s="11"/>
       <c r="E859" s="11"/>
-    </row>
-    <row r="860" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G859" s="8"/>
+    </row>
+    <row r="860" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C860" s="11"/>
       <c r="D860" s="11"/>
       <c r="E860" s="11"/>
-    </row>
-    <row r="861" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G860" s="8"/>
+    </row>
+    <row r="861" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C861" s="11"/>
       <c r="D861" s="11"/>
       <c r="E861" s="11"/>
-    </row>
-    <row r="862" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G861" s="8"/>
+    </row>
+    <row r="862" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C862" s="11"/>
       <c r="D862" s="11"/>
       <c r="E862" s="11"/>
-    </row>
-    <row r="863" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G862" s="8"/>
+    </row>
+    <row r="863" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C863" s="11"/>
       <c r="D863" s="11"/>
       <c r="E863" s="11"/>
-    </row>
-    <row r="864" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G863" s="8"/>
+    </row>
+    <row r="864" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C864" s="11"/>
       <c r="D864" s="11"/>
       <c r="E864" s="11"/>
-    </row>
-    <row r="865" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G864" s="8"/>
+    </row>
+    <row r="865" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C865" s="11"/>
       <c r="D865" s="11"/>
       <c r="E865" s="11"/>
-    </row>
-    <row r="866" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G865" s="8"/>
+    </row>
+    <row r="866" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C866" s="11"/>
       <c r="D866" s="11"/>
       <c r="E866" s="11"/>
-    </row>
-    <row r="867" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G866" s="8"/>
+    </row>
+    <row r="867" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C867" s="11"/>
       <c r="D867" s="11"/>
       <c r="E867" s="11"/>
-    </row>
-    <row r="868" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G867" s="8"/>
+    </row>
+    <row r="868" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C868" s="11"/>
       <c r="D868" s="11"/>
       <c r="E868" s="11"/>
-    </row>
-    <row r="869" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G868" s="8"/>
+    </row>
+    <row r="869" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C869" s="11"/>
       <c r="D869" s="11"/>
       <c r="E869" s="11"/>
-    </row>
-    <row r="870" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G869" s="8"/>
+    </row>
+    <row r="870" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C870" s="11"/>
       <c r="D870" s="11"/>
       <c r="E870" s="11"/>
-    </row>
-    <row r="871" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G870" s="8"/>
+    </row>
+    <row r="871" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C871" s="11"/>
       <c r="D871" s="11"/>
       <c r="E871" s="11"/>
-    </row>
-    <row r="872" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G871" s="8"/>
+    </row>
+    <row r="872" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C872" s="11"/>
       <c r="D872" s="11"/>
       <c r="E872" s="11"/>
-    </row>
-    <row r="873" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G872" s="8"/>
+    </row>
+    <row r="873" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C873" s="11"/>
       <c r="D873" s="11"/>
       <c r="E873" s="11"/>
-    </row>
-    <row r="874" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G873" s="8"/>
+    </row>
+    <row r="874" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C874" s="11"/>
       <c r="D874" s="11"/>
       <c r="E874" s="11"/>
-    </row>
-    <row r="875" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G874" s="8"/>
+    </row>
+    <row r="875" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C875" s="11"/>
       <c r="D875" s="11"/>
       <c r="E875" s="11"/>
-    </row>
-    <row r="876" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G875" s="8"/>
+    </row>
+    <row r="876" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C876" s="11"/>
       <c r="D876" s="11"/>
       <c r="E876" s="11"/>
-    </row>
-    <row r="877" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G876" s="8"/>
+    </row>
+    <row r="877" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C877" s="11"/>
       <c r="D877" s="11"/>
       <c r="E877" s="11"/>
-    </row>
-    <row r="878" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G877" s="8"/>
+    </row>
+    <row r="878" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C878" s="11"/>
       <c r="D878" s="11"/>
       <c r="E878" s="11"/>
-    </row>
-    <row r="879" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G878" s="8"/>
+    </row>
+    <row r="879" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C879" s="11"/>
       <c r="D879" s="11"/>
       <c r="E879" s="11"/>
-    </row>
-    <row r="880" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G879" s="8"/>
+    </row>
+    <row r="880" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C880" s="11"/>
       <c r="D880" s="11"/>
       <c r="E880" s="11"/>
-    </row>
-    <row r="881" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G880" s="8"/>
+    </row>
+    <row r="881" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C881" s="11"/>
       <c r="D881" s="11"/>
       <c r="E881" s="11"/>
-    </row>
-    <row r="882" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G881" s="8"/>
+    </row>
+    <row r="882" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C882" s="11"/>
       <c r="D882" s="11"/>
       <c r="E882" s="11"/>
-    </row>
-    <row r="883" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G882" s="8"/>
+    </row>
+    <row r="883" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C883" s="11"/>
       <c r="D883" s="11"/>
       <c r="E883" s="11"/>
-    </row>
-    <row r="884" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G883" s="8"/>
+    </row>
+    <row r="884" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C884" s="11"/>
       <c r="D884" s="11"/>
       <c r="E884" s="11"/>
-    </row>
-    <row r="885" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G884" s="8"/>
+    </row>
+    <row r="885" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C885" s="11"/>
       <c r="D885" s="11"/>
       <c r="E885" s="11"/>
-    </row>
-    <row r="886" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G885" s="8"/>
+    </row>
+    <row r="886" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C886" s="11"/>
       <c r="D886" s="11"/>
       <c r="E886" s="11"/>
-    </row>
-    <row r="887" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G886" s="8"/>
+    </row>
+    <row r="887" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C887" s="11"/>
       <c r="D887" s="11"/>
       <c r="E887" s="11"/>
-    </row>
-    <row r="888" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G887" s="8"/>
+    </row>
+    <row r="888" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C888" s="11"/>
       <c r="D888" s="11"/>
       <c r="E888" s="11"/>
-    </row>
-    <row r="889" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G888" s="8"/>
+    </row>
+    <row r="889" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C889" s="11"/>
       <c r="D889" s="11"/>
       <c r="E889" s="11"/>
-    </row>
-    <row r="890" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G889" s="8"/>
+    </row>
+    <row r="890" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C890" s="11"/>
       <c r="D890" s="11"/>
       <c r="E890" s="11"/>
-    </row>
-    <row r="891" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G890" s="8"/>
+    </row>
+    <row r="891" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C891" s="11"/>
       <c r="D891" s="11"/>
       <c r="E891" s="11"/>
-    </row>
-    <row r="892" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G891" s="8"/>
+    </row>
+    <row r="892" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C892" s="11"/>
       <c r="D892" s="11"/>
       <c r="E892" s="11"/>
-    </row>
-    <row r="893" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G892" s="8"/>
+    </row>
+    <row r="893" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C893" s="11"/>
       <c r="D893" s="11"/>
       <c r="E893" s="11"/>
-    </row>
-    <row r="894" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G893" s="8"/>
+    </row>
+    <row r="894" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C894" s="11"/>
       <c r="D894" s="11"/>
       <c r="E894" s="11"/>
-    </row>
-    <row r="895" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G894" s="8"/>
+    </row>
+    <row r="895" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C895" s="11"/>
       <c r="D895" s="11"/>
       <c r="E895" s="11"/>
-    </row>
-    <row r="896" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G895" s="8"/>
+    </row>
+    <row r="896" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C896" s="11"/>
       <c r="D896" s="11"/>
       <c r="E896" s="11"/>
-    </row>
-    <row r="897" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G896" s="8"/>
+    </row>
+    <row r="897" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C897" s="11"/>
       <c r="D897" s="11"/>
       <c r="E897" s="11"/>
-    </row>
-    <row r="898" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G897" s="8"/>
+    </row>
+    <row r="898" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C898" s="11"/>
       <c r="D898" s="11"/>
       <c r="E898" s="11"/>
-    </row>
-    <row r="899" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G898" s="8"/>
+    </row>
+    <row r="899" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C899" s="11"/>
       <c r="D899" s="11"/>
       <c r="E899" s="11"/>
-    </row>
-    <row r="900" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G899" s="8"/>
+    </row>
+    <row r="900" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C900" s="11"/>
       <c r="D900" s="11"/>
       <c r="E900" s="11"/>
-    </row>
-    <row r="901" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G900" s="8"/>
+    </row>
+    <row r="901" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C901" s="11"/>
       <c r="D901" s="11"/>
       <c r="E901" s="11"/>
-    </row>
-    <row r="902" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G901" s="8"/>
+    </row>
+    <row r="902" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C902" s="11"/>
       <c r="D902" s="11"/>
       <c r="E902" s="11"/>
-    </row>
-    <row r="903" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G902" s="8"/>
+    </row>
+    <row r="903" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C903" s="11"/>
       <c r="D903" s="11"/>
       <c r="E903" s="11"/>
-    </row>
-    <row r="904" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G903" s="8"/>
+    </row>
+    <row r="904" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C904" s="11"/>
       <c r="D904" s="11"/>
       <c r="E904" s="11"/>
-    </row>
-    <row r="905" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G904" s="8"/>
+    </row>
+    <row r="905" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C905" s="11"/>
       <c r="D905" s="11"/>
       <c r="E905" s="11"/>
-    </row>
-    <row r="906" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G905" s="8"/>
+    </row>
+    <row r="906" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C906" s="11"/>
       <c r="D906" s="11"/>
       <c r="E906" s="11"/>
-    </row>
-    <row r="907" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G906" s="8"/>
+    </row>
+    <row r="907" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C907" s="11"/>
       <c r="D907" s="11"/>
       <c r="E907" s="11"/>
-    </row>
-    <row r="908" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G907" s="8"/>
+    </row>
+    <row r="908" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C908" s="11"/>
       <c r="D908" s="11"/>
       <c r="E908" s="11"/>
-    </row>
-    <row r="909" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G908" s="8"/>
+    </row>
+    <row r="909" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C909" s="11"/>
       <c r="D909" s="11"/>
       <c r="E909" s="11"/>
-    </row>
-    <row r="910" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G909" s="8"/>
+    </row>
+    <row r="910" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C910" s="11"/>
       <c r="D910" s="11"/>
       <c r="E910" s="11"/>
-    </row>
-    <row r="911" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G910" s="8"/>
+    </row>
+    <row r="911" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C911" s="11"/>
       <c r="D911" s="11"/>
       <c r="E911" s="11"/>
-    </row>
-    <row r="912" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G911" s="8"/>
+    </row>
+    <row r="912" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C912" s="11"/>
       <c r="D912" s="11"/>
       <c r="E912" s="11"/>
-    </row>
-    <row r="913" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G912" s="8"/>
+    </row>
+    <row r="913" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C913" s="11"/>
       <c r="D913" s="11"/>
       <c r="E913" s="11"/>
-    </row>
-    <row r="914" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G913" s="8"/>
+    </row>
+    <row r="914" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C914" s="11"/>
       <c r="D914" s="11"/>
       <c r="E914" s="11"/>
-    </row>
-    <row r="915" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G914" s="8"/>
+    </row>
+    <row r="915" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C915" s="11"/>
       <c r="D915" s="11"/>
       <c r="E915" s="11"/>
-    </row>
-    <row r="916" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G915" s="8"/>
+    </row>
+    <row r="916" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C916" s="11"/>
       <c r="D916" s="11"/>
       <c r="E916" s="11"/>
-    </row>
-    <row r="917" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G916" s="8"/>
+    </row>
+    <row r="917" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C917" s="11"/>
       <c r="D917" s="11"/>
       <c r="E917" s="11"/>
-    </row>
-    <row r="918" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G917" s="8"/>
+    </row>
+    <row r="918" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C918" s="11"/>
       <c r="D918" s="11"/>
       <c r="E918" s="11"/>
-    </row>
-    <row r="919" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G918" s="8"/>
+    </row>
+    <row r="919" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C919" s="11"/>
       <c r="D919" s="11"/>
       <c r="E919" s="11"/>
-    </row>
-    <row r="920" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G919" s="8"/>
+    </row>
+    <row r="920" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C920" s="11"/>
       <c r="D920" s="11"/>
       <c r="E920" s="11"/>
-    </row>
-    <row r="921" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G920" s="8"/>
+    </row>
+    <row r="921" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C921" s="11"/>
       <c r="D921" s="11"/>
       <c r="E921" s="11"/>
-    </row>
-    <row r="922" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G921" s="8"/>
+    </row>
+    <row r="922" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C922" s="11"/>
       <c r="D922" s="11"/>
       <c r="E922" s="11"/>
-    </row>
-    <row r="923" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G922" s="8"/>
+    </row>
+    <row r="923" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C923" s="11"/>
       <c r="D923" s="11"/>
       <c r="E923" s="11"/>
-    </row>
-    <row r="924" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G923" s="8"/>
+    </row>
+    <row r="924" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C924" s="11"/>
       <c r="D924" s="11"/>
       <c r="E924" s="11"/>
-    </row>
-    <row r="925" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G924" s="8"/>
+    </row>
+    <row r="925" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C925" s="11"/>
       <c r="D925" s="11"/>
       <c r="E925" s="11"/>
-    </row>
-    <row r="926" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G925" s="8"/>
+    </row>
+    <row r="926" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C926" s="11"/>
       <c r="D926" s="11"/>
       <c r="E926" s="11"/>
-    </row>
-    <row r="927" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G926" s="8"/>
+    </row>
+    <row r="927" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C927" s="11"/>
       <c r="D927" s="11"/>
       <c r="E927" s="11"/>
-    </row>
-    <row r="928" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G927" s="8"/>
+    </row>
+    <row r="928" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C928" s="11"/>
       <c r="D928" s="11"/>
       <c r="E928" s="11"/>
-    </row>
-    <row r="929" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G928" s="8"/>
+    </row>
+    <row r="929" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C929" s="11"/>
       <c r="D929" s="11"/>
       <c r="E929" s="11"/>
-    </row>
-    <row r="930" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G929" s="8"/>
+    </row>
+    <row r="930" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C930" s="11"/>
       <c r="D930" s="11"/>
       <c r="E930" s="11"/>
-    </row>
-    <row r="931" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G930" s="8"/>
+    </row>
+    <row r="931" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C931" s="11"/>
       <c r="D931" s="11"/>
       <c r="E931" s="11"/>
-    </row>
-    <row r="932" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G931" s="8"/>
+    </row>
+    <row r="932" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C932" s="11"/>
       <c r="D932" s="11"/>
       <c r="E932" s="11"/>
-    </row>
-    <row r="933" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G932" s="8"/>
+    </row>
+    <row r="933" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C933" s="11"/>
       <c r="D933" s="11"/>
       <c r="E933" s="11"/>
-    </row>
-    <row r="934" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G933" s="8"/>
+    </row>
+    <row r="934" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C934" s="11"/>
       <c r="D934" s="11"/>
       <c r="E934" s="11"/>
-    </row>
-    <row r="935" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G934" s="8"/>
+    </row>
+    <row r="935" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C935" s="11"/>
       <c r="D935" s="11"/>
       <c r="E935" s="11"/>
-    </row>
-    <row r="936" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G935" s="8"/>
+    </row>
+    <row r="936" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C936" s="11"/>
       <c r="D936" s="11"/>
       <c r="E936" s="11"/>
-    </row>
-    <row r="937" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G936" s="8"/>
+    </row>
+    <row r="937" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C937" s="11"/>
       <c r="D937" s="11"/>
       <c r="E937" s="11"/>
-    </row>
-    <row r="938" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G937" s="8"/>
+    </row>
+    <row r="938" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C938" s="11"/>
       <c r="D938" s="11"/>
       <c r="E938" s="11"/>
-    </row>
-    <row r="939" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G938" s="8"/>
+    </row>
+    <row r="939" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C939" s="11"/>
       <c r="D939" s="11"/>
       <c r="E939" s="11"/>
-    </row>
-    <row r="940" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G939" s="8"/>
+    </row>
+    <row r="940" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C940" s="11"/>
       <c r="D940" s="11"/>
       <c r="E940" s="11"/>
-    </row>
-    <row r="941" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G940" s="8"/>
+    </row>
+    <row r="941" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C941" s="11"/>
       <c r="D941" s="11"/>
       <c r="E941" s="11"/>
-    </row>
-    <row r="942" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G941" s="8"/>
+    </row>
+    <row r="942" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C942" s="11"/>
       <c r="D942" s="11"/>
       <c r="E942" s="11"/>
-    </row>
-    <row r="943" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G942" s="8"/>
+    </row>
+    <row r="943" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C943" s="11"/>
       <c r="D943" s="11"/>
       <c r="E943" s="11"/>
-    </row>
-    <row r="944" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G943" s="8"/>
+    </row>
+    <row r="944" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C944" s="11"/>
       <c r="D944" s="11"/>
       <c r="E944" s="11"/>
-    </row>
-    <row r="945" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G944" s="8"/>
+    </row>
+    <row r="945" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C945" s="11"/>
       <c r="D945" s="11"/>
       <c r="E945" s="11"/>
-    </row>
-    <row r="946" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G945" s="8"/>
+    </row>
+    <row r="946" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C946" s="11"/>
       <c r="D946" s="11"/>
       <c r="E946" s="11"/>
-    </row>
-    <row r="947" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G946" s="8"/>
+    </row>
+    <row r="947" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C947" s="11"/>
       <c r="D947" s="11"/>
       <c r="E947" s="11"/>
-    </row>
-    <row r="948" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G947" s="8"/>
+    </row>
+    <row r="948" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C948" s="11"/>
       <c r="D948" s="11"/>
       <c r="E948" s="11"/>
-    </row>
-    <row r="949" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G948" s="8"/>
+    </row>
+    <row r="949" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C949" s="11"/>
       <c r="D949" s="11"/>
       <c r="E949" s="11"/>
-    </row>
-    <row r="950" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G949" s="8"/>
+    </row>
+    <row r="950" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C950" s="11"/>
       <c r="D950" s="11"/>
       <c r="E950" s="11"/>
-    </row>
-    <row r="951" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G950" s="8"/>
+    </row>
+    <row r="951" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C951" s="11"/>
       <c r="D951" s="11"/>
       <c r="E951" s="11"/>
-    </row>
-    <row r="952" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G951" s="8"/>
+    </row>
+    <row r="952" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C952" s="11"/>
       <c r="D952" s="11"/>
       <c r="E952" s="11"/>
-    </row>
-    <row r="953" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G952" s="8"/>
+    </row>
+    <row r="953" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C953" s="11"/>
       <c r="D953" s="11"/>
       <c r="E953" s="11"/>
-    </row>
-    <row r="954" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G953" s="8"/>
+    </row>
+    <row r="954" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C954" s="11"/>
       <c r="D954" s="11"/>
       <c r="E954" s="11"/>
-    </row>
-    <row r="955" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G954" s="8"/>
+    </row>
+    <row r="955" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C955" s="11"/>
       <c r="D955" s="11"/>
       <c r="E955" s="11"/>
-    </row>
-    <row r="956" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G955" s="8"/>
+    </row>
+    <row r="956" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C956" s="11"/>
       <c r="D956" s="11"/>
       <c r="E956" s="11"/>
-    </row>
-    <row r="957" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G956" s="8"/>
+    </row>
+    <row r="957" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C957" s="11"/>
       <c r="D957" s="11"/>
       <c r="E957" s="11"/>
-    </row>
-    <row r="958" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G957" s="8"/>
+    </row>
+    <row r="958" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C958" s="11"/>
       <c r="D958" s="11"/>
       <c r="E958" s="11"/>
-    </row>
-    <row r="959" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G958" s="8"/>
+    </row>
+    <row r="959" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C959" s="11"/>
       <c r="D959" s="11"/>
       <c r="E959" s="11"/>
-    </row>
-    <row r="960" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G959" s="8"/>
+    </row>
+    <row r="960" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C960" s="11"/>
       <c r="D960" s="11"/>
       <c r="E960" s="11"/>
-    </row>
-    <row r="961" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G960" s="8"/>
+    </row>
+    <row r="961" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C961" s="11"/>
       <c r="D961" s="11"/>
       <c r="E961" s="11"/>
-    </row>
-    <row r="962" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G961" s="8"/>
+    </row>
+    <row r="962" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C962" s="11"/>
       <c r="D962" s="11"/>
       <c r="E962" s="11"/>
-    </row>
-    <row r="963" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G962" s="8"/>
+    </row>
+    <row r="963" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C963" s="11"/>
       <c r="D963" s="11"/>
       <c r="E963" s="11"/>
-    </row>
-    <row r="964" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G963" s="8"/>
+    </row>
+    <row r="964" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C964" s="11"/>
       <c r="D964" s="11"/>
       <c r="E964" s="11"/>
-    </row>
-    <row r="965" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G964" s="8"/>
+    </row>
+    <row r="965" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C965" s="11"/>
       <c r="D965" s="11"/>
       <c r="E965" s="11"/>
-    </row>
-    <row r="966" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G965" s="8"/>
+    </row>
+    <row r="966" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C966" s="11"/>
       <c r="D966" s="11"/>
       <c r="E966" s="11"/>
-    </row>
-    <row r="967" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G966" s="8"/>
+    </row>
+    <row r="967" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C967" s="11"/>
       <c r="D967" s="11"/>
       <c r="E967" s="11"/>
-    </row>
-    <row r="968" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G967" s="8"/>
+    </row>
+    <row r="968" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C968" s="11"/>
       <c r="D968" s="11"/>
       <c r="E968" s="11"/>
-    </row>
-    <row r="969" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G968" s="8"/>
+    </row>
+    <row r="969" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C969" s="11"/>
       <c r="D969" s="11"/>
       <c r="E969" s="11"/>
-    </row>
-    <row r="970" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G969" s="8"/>
+    </row>
+    <row r="970" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C970" s="11"/>
       <c r="D970" s="11"/>
       <c r="E970" s="11"/>
-    </row>
-    <row r="971" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G970" s="8"/>
+    </row>
+    <row r="971" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C971" s="11"/>
       <c r="D971" s="11"/>
       <c r="E971" s="11"/>
-    </row>
-    <row r="972" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G971" s="8"/>
+    </row>
+    <row r="972" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C972" s="11"/>
       <c r="D972" s="11"/>
       <c r="E972" s="11"/>
-    </row>
-    <row r="973" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G972" s="8"/>
+    </row>
+    <row r="973" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C973" s="11"/>
       <c r="D973" s="11"/>
       <c r="E973" s="11"/>
-    </row>
-    <row r="974" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G973" s="8"/>
+    </row>
+    <row r="974" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C974" s="11"/>
       <c r="D974" s="11"/>
       <c r="E974" s="11"/>
-    </row>
-    <row r="975" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G974" s="8"/>
+    </row>
+    <row r="975" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C975" s="11"/>
       <c r="D975" s="11"/>
       <c r="E975" s="11"/>
-    </row>
-    <row r="976" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G975" s="8"/>
+    </row>
+    <row r="976" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C976" s="11"/>
       <c r="D976" s="11"/>
       <c r="E976" s="11"/>
-    </row>
-    <row r="977" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G976" s="8"/>
+    </row>
+    <row r="977" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C977" s="11"/>
       <c r="D977" s="11"/>
       <c r="E977" s="11"/>
-    </row>
-    <row r="978" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G977" s="8"/>
+    </row>
+    <row r="978" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C978" s="11"/>
       <c r="D978" s="11"/>
       <c r="E978" s="11"/>
-    </row>
-    <row r="979" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G978" s="8"/>
+    </row>
+    <row r="979" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C979" s="11"/>
       <c r="D979" s="11"/>
       <c r="E979" s="11"/>
-    </row>
-    <row r="980" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G979" s="8"/>
+    </row>
+    <row r="980" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C980" s="11"/>
       <c r="D980" s="11"/>
       <c r="E980" s="11"/>
-    </row>
-    <row r="981" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G980" s="8"/>
+    </row>
+    <row r="981" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C981" s="11"/>
       <c r="D981" s="11"/>
       <c r="E981" s="11"/>
-    </row>
-    <row r="982" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G981" s="8"/>
+    </row>
+    <row r="982" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C982" s="11"/>
       <c r="D982" s="11"/>
       <c r="E982" s="11"/>
-    </row>
-    <row r="983" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G982" s="8"/>
+    </row>
+    <row r="983" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C983" s="11"/>
       <c r="D983" s="11"/>
       <c r="E983" s="11"/>
-    </row>
-    <row r="984" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G983" s="8"/>
+    </row>
+    <row r="984" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C984" s="11"/>
       <c r="D984" s="11"/>
       <c r="E984" s="11"/>
-    </row>
-    <row r="985" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G984" s="8"/>
+    </row>
+    <row r="985" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C985" s="11"/>
       <c r="D985" s="11"/>
       <c r="E985" s="11"/>
-    </row>
-    <row r="986" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G985" s="8"/>
+    </row>
+    <row r="986" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C986" s="11"/>
       <c r="D986" s="11"/>
       <c r="E986" s="11"/>
-    </row>
-    <row r="987" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G986" s="8"/>
+    </row>
+    <row r="987" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C987" s="11"/>
       <c r="D987" s="11"/>
       <c r="E987" s="11"/>
-    </row>
-    <row r="988" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G987" s="8"/>
+    </row>
+    <row r="988" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C988" s="11"/>
       <c r="D988" s="11"/>
       <c r="E988" s="11"/>
-    </row>
-    <row r="989" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G988" s="8"/>
+    </row>
+    <row r="989" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C989" s="11"/>
       <c r="D989" s="11"/>
       <c r="E989" s="11"/>
-    </row>
-    <row r="990" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G989" s="8"/>
+    </row>
+    <row r="990" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C990" s="11"/>
       <c r="D990" s="11"/>
       <c r="E990" s="11"/>
-    </row>
-    <row r="991" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G990" s="8"/>
+    </row>
+    <row r="991" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C991" s="11"/>
       <c r="D991" s="11"/>
       <c r="E991" s="11"/>
-    </row>
-    <row r="992" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G991" s="8"/>
+    </row>
+    <row r="992" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C992" s="11"/>
       <c r="D992" s="11"/>
       <c r="E992" s="11"/>
-    </row>
-    <row r="993" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G992" s="8"/>
+    </row>
+    <row r="993" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C993" s="11"/>
       <c r="D993" s="11"/>
       <c r="E993" s="11"/>
-    </row>
-    <row r="994" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G993" s="8"/>
+    </row>
+    <row r="994" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C994" s="11"/>
       <c r="D994" s="11"/>
       <c r="E994" s="11"/>
-    </row>
-    <row r="995" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G994" s="8"/>
+    </row>
+    <row r="995" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C995" s="11"/>
       <c r="D995" s="11"/>
       <c r="E995" s="11"/>
-    </row>
-    <row r="996" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G995" s="8"/>
+    </row>
+    <row r="996" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C996" s="11"/>
       <c r="D996" s="11"/>
       <c r="E996" s="11"/>
-    </row>
-    <row r="997" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G996" s="8"/>
+    </row>
+    <row r="997" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C997" s="11"/>
       <c r="D997" s="11"/>
       <c r="E997" s="11"/>
-    </row>
-    <row r="998" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G997" s="8"/>
+    </row>
+    <row r="998" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C998" s="11"/>
       <c r="D998" s="11"/>
       <c r="E998" s="11"/>
-    </row>
-    <row r="999" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G998" s="8"/>
+    </row>
+    <row r="999" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C999" s="11"/>
       <c r="D999" s="11"/>
       <c r="E999" s="11"/>
-    </row>
-    <row r="1000" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G999" s="8"/>
+    </row>
+    <row r="1000" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1000" s="11"/>
       <c r="D1000" s="11"/>
       <c r="E1000" s="11"/>
-    </row>
-    <row r="1001" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1000" s="8"/>
+    </row>
+    <row r="1001" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1001" s="11"/>
       <c r="D1001" s="11"/>
       <c r="E1001" s="11"/>
-    </row>
-    <row r="1002" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1001" s="8"/>
+    </row>
+    <row r="1002" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1002" s="11"/>
       <c r="D1002" s="11"/>
       <c r="E1002" s="11"/>
-    </row>
-    <row r="1003" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1002" s="8"/>
+    </row>
+    <row r="1003" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1003" s="11"/>
       <c r="D1003" s="11"/>
       <c r="E1003" s="11"/>
-    </row>
-    <row r="1004" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1003" s="8"/>
+    </row>
+    <row r="1004" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1004" s="11"/>
       <c r="D1004" s="11"/>
       <c r="E1004" s="11"/>
-    </row>
-    <row r="1005" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1004" s="8"/>
+    </row>
+    <row r="1005" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1005" s="11"/>
       <c r="D1005" s="11"/>
       <c r="E1005" s="11"/>
-    </row>
-    <row r="1006" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1005" s="8"/>
+    </row>
+    <row r="1006" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1006" s="11"/>
       <c r="D1006" s="11"/>
       <c r="E1006" s="11"/>
-    </row>
-    <row r="1007" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1006" s="8"/>
+    </row>
+    <row r="1007" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1007" s="11"/>
       <c r="D1007" s="11"/>
       <c r="E1007" s="11"/>
-    </row>
-    <row r="1008" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1007" s="8"/>
+    </row>
+    <row r="1008" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1008" s="11"/>
       <c r="D1008" s="11"/>
       <c r="E1008" s="11"/>
-    </row>
-    <row r="1009" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1008" s="8"/>
+    </row>
+    <row r="1009" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1009" s="11"/>
       <c r="D1009" s="11"/>
       <c r="E1009" s="11"/>
-    </row>
-    <row r="1010" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1009" s="8"/>
+    </row>
+    <row r="1010" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1010" s="11"/>
       <c r="D1010" s="11"/>
       <c r="E1010" s="11"/>
-    </row>
-    <row r="1011" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1010" s="8"/>
+    </row>
+    <row r="1011" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1011" s="11"/>
       <c r="D1011" s="11"/>
       <c r="E1011" s="11"/>
-    </row>
-    <row r="1012" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1011" s="8"/>
+    </row>
+    <row r="1012" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1012" s="11"/>
       <c r="D1012" s="11"/>
       <c r="E1012" s="11"/>
-    </row>
-    <row r="1013" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1012" s="8"/>
+    </row>
+    <row r="1013" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1013" s="11"/>
       <c r="D1013" s="11"/>
       <c r="E1013" s="11"/>
-    </row>
-    <row r="1014" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1013" s="8"/>
+    </row>
+    <row r="1014" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1014" s="11"/>
       <c r="D1014" s="11"/>
       <c r="E1014" s="11"/>
-    </row>
-    <row r="1015" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1014" s="8"/>
+    </row>
+    <row r="1015" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1015" s="11"/>
       <c r="D1015" s="11"/>
       <c r="E1015" s="11"/>
-    </row>
-    <row r="1016" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1015" s="8"/>
+    </row>
+    <row r="1016" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1016" s="11"/>
       <c r="D1016" s="11"/>
       <c r="E1016" s="11"/>
-    </row>
-    <row r="1017" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1016" s="8"/>
+    </row>
+    <row r="1017" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1017" s="11"/>
       <c r="D1017" s="11"/>
       <c r="E1017" s="11"/>
-    </row>
-    <row r="1018" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1017" s="8"/>
+    </row>
+    <row r="1018" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1018" s="11"/>
       <c r="D1018" s="11"/>
       <c r="E1018" s="11"/>
-    </row>
-    <row r="1019" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1018" s="8"/>
+    </row>
+    <row r="1019" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1019" s="11"/>
       <c r="D1019" s="11"/>
       <c r="E1019" s="11"/>
-    </row>
-    <row r="1020" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1019" s="8"/>
+    </row>
+    <row r="1020" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1020" s="11"/>
       <c r="D1020" s="11"/>
       <c r="E1020" s="11"/>
-    </row>
-    <row r="1021" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1020" s="8"/>
+    </row>
+    <row r="1021" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1021" s="11"/>
       <c r="D1021" s="11"/>
       <c r="E1021" s="11"/>
-    </row>
-    <row r="1022" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1021" s="8"/>
+    </row>
+    <row r="1022" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1022" s="11"/>
       <c r="D1022" s="11"/>
       <c r="E1022" s="11"/>
-    </row>
-    <row r="1023" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1022" s="8"/>
+    </row>
+    <row r="1023" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1023" s="11"/>
       <c r="D1023" s="11"/>
       <c r="E1023" s="11"/>
-    </row>
-    <row r="1024" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1023" s="8"/>
+    </row>
+    <row r="1024" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1024" s="11"/>
       <c r="D1024" s="11"/>
       <c r="E1024" s="11"/>
-    </row>
-    <row r="1025" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1024" s="8"/>
+    </row>
+    <row r="1025" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1025" s="11"/>
       <c r="D1025" s="11"/>
       <c r="E1025" s="11"/>
-    </row>
-    <row r="1026" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1025" s="8"/>
+    </row>
+    <row r="1026" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1026" s="11"/>
       <c r="D1026" s="11"/>
       <c r="E1026" s="11"/>
-    </row>
-    <row r="1027" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1026" s="8"/>
+    </row>
+    <row r="1027" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1027" s="11"/>
       <c r="D1027" s="11"/>
       <c r="E1027" s="11"/>
-    </row>
-    <row r="1028" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1027" s="8"/>
+    </row>
+    <row r="1028" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1028" s="11"/>
       <c r="D1028" s="11"/>
       <c r="E1028" s="11"/>
-    </row>
-    <row r="1029" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1028" s="8"/>
+    </row>
+    <row r="1029" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1029" s="11"/>
       <c r="D1029" s="11"/>
       <c r="E1029" s="11"/>
-    </row>
-    <row r="1030" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1029" s="8"/>
+    </row>
+    <row r="1030" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1030" s="11"/>
       <c r="D1030" s="11"/>
       <c r="E1030" s="11"/>
-    </row>
-    <row r="1031" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1030" s="8"/>
+    </row>
+    <row r="1031" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1031" s="11"/>
       <c r="D1031" s="11"/>
       <c r="E1031" s="11"/>
-    </row>
-    <row r="1032" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1031" s="8"/>
+    </row>
+    <row r="1032" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1032" s="11"/>
       <c r="D1032" s="11"/>
       <c r="E1032" s="11"/>
-    </row>
-    <row r="1033" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1032" s="8"/>
+    </row>
+    <row r="1033" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1033" s="11"/>
       <c r="D1033" s="11"/>
       <c r="E1033" s="11"/>
-    </row>
-    <row r="1034" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1033" s="8"/>
+    </row>
+    <row r="1034" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1034" s="11"/>
       <c r="D1034" s="11"/>
       <c r="E1034" s="11"/>
-    </row>
-    <row r="1035" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1034" s="8"/>
+    </row>
+    <row r="1035" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1035" s="11"/>
       <c r="D1035" s="11"/>
       <c r="E1035" s="11"/>
-    </row>
-    <row r="1036" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1035" s="8"/>
+    </row>
+    <row r="1036" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1036" s="11"/>
       <c r="D1036" s="11"/>
       <c r="E1036" s="11"/>
-    </row>
-    <row r="1037" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1036" s="8"/>
+    </row>
+    <row r="1037" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1037" s="11"/>
       <c r="D1037" s="11"/>
       <c r="E1037" s="11"/>
-    </row>
-    <row r="1038" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1037" s="8"/>
+    </row>
+    <row r="1038" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1038" s="11"/>
       <c r="D1038" s="11"/>
       <c r="E1038" s="11"/>
-    </row>
-    <row r="1039" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1038" s="8"/>
+    </row>
+    <row r="1039" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1039" s="11"/>
       <c r="D1039" s="11"/>
       <c r="E1039" s="11"/>
-    </row>
-    <row r="1040" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1039" s="8"/>
+    </row>
+    <row r="1040" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1040" s="11"/>
       <c r="D1040" s="11"/>
       <c r="E1040" s="11"/>
-    </row>
-    <row r="1041" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1040" s="8"/>
+    </row>
+    <row r="1041" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1041" s="11"/>
       <c r="D1041" s="11"/>
       <c r="E1041" s="11"/>
-    </row>
-    <row r="1042" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1041" s="8"/>
+    </row>
+    <row r="1042" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1042" s="11"/>
       <c r="D1042" s="11"/>
       <c r="E1042" s="11"/>
-    </row>
-    <row r="1043" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1042" s="8"/>
+    </row>
+    <row r="1043" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1043" s="11"/>
       <c r="D1043" s="11"/>
       <c r="E1043" s="11"/>
-    </row>
-    <row r="1044" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1043" s="8"/>
+    </row>
+    <row r="1044" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1044" s="11"/>
       <c r="D1044" s="11"/>
       <c r="E1044" s="11"/>
-    </row>
-    <row r="1045" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1044" s="8"/>
+    </row>
+    <row r="1045" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1045" s="11"/>
       <c r="D1045" s="11"/>
       <c r="E1045" s="11"/>
-    </row>
-    <row r="1046" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1045" s="8"/>
+    </row>
+    <row r="1046" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1046" s="11"/>
       <c r="D1046" s="11"/>
       <c r="E1046" s="11"/>
-    </row>
-    <row r="1047" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1046" s="8"/>
+    </row>
+    <row r="1047" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1047" s="11"/>
       <c r="D1047" s="11"/>
       <c r="E1047" s="11"/>
-    </row>
-    <row r="1048" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1047" s="8"/>
+    </row>
+    <row r="1048" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1048" s="11"/>
       <c r="D1048" s="11"/>
       <c r="E1048" s="11"/>
-    </row>
-    <row r="1049" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1048" s="8"/>
+    </row>
+    <row r="1049" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1049" s="11"/>
       <c r="D1049" s="11"/>
       <c r="E1049" s="11"/>
-    </row>
-    <row r="1050" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1049" s="8"/>
+    </row>
+    <row r="1050" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1050" s="11"/>
       <c r="D1050" s="11"/>
       <c r="E1050" s="11"/>
-    </row>
-    <row r="1051" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1050" s="8"/>
+    </row>
+    <row r="1051" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1051" s="11"/>
       <c r="D1051" s="11"/>
       <c r="E1051" s="11"/>
-    </row>
-    <row r="1052" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1051" s="8"/>
+    </row>
+    <row r="1052" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1052" s="11"/>
       <c r="D1052" s="11"/>
       <c r="E1052" s="11"/>
-    </row>
-    <row r="1053" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1052" s="8"/>
+    </row>
+    <row r="1053" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1053" s="11"/>
       <c r="D1053" s="11"/>
       <c r="E1053" s="11"/>
-    </row>
-    <row r="1054" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1053" s="8"/>
+    </row>
+    <row r="1054" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1054" s="11"/>
       <c r="D1054" s="11"/>
       <c r="E1054" s="11"/>
-    </row>
-    <row r="1055" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1054" s="8"/>
+    </row>
+    <row r="1055" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1055" s="11"/>
       <c r="D1055" s="11"/>
       <c r="E1055" s="11"/>
-    </row>
-    <row r="1056" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1055" s="8"/>
+    </row>
+    <row r="1056" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1056" s="11"/>
       <c r="D1056" s="11"/>
       <c r="E1056" s="11"/>
-    </row>
-    <row r="1057" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1056" s="8"/>
+    </row>
+    <row r="1057" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1057" s="11"/>
       <c r="D1057" s="11"/>
       <c r="E1057" s="11"/>
-    </row>
-    <row r="1058" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1057" s="8"/>
+    </row>
+    <row r="1058" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1058" s="11"/>
       <c r="D1058" s="11"/>
       <c r="E1058" s="11"/>
-    </row>
-    <row r="1059" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1058" s="8"/>
+    </row>
+    <row r="1059" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1059" s="11"/>
       <c r="D1059" s="11"/>
       <c r="E1059" s="11"/>
-    </row>
-    <row r="1060" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1059" s="8"/>
+    </row>
+    <row r="1060" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1060" s="11"/>
       <c r="D1060" s="11"/>
       <c r="E1060" s="11"/>
-    </row>
-    <row r="1061" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1060" s="8"/>
+    </row>
+    <row r="1061" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1061" s="11"/>
       <c r="D1061" s="11"/>
       <c r="E1061" s="11"/>
-    </row>
-    <row r="1062" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1061" s="8"/>
+    </row>
+    <row r="1062" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1062" s="11"/>
       <c r="D1062" s="11"/>
       <c r="E1062" s="11"/>
-    </row>
-    <row r="1063" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1062" s="8"/>
+    </row>
+    <row r="1063" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1063" s="11"/>
       <c r="D1063" s="11"/>
       <c r="E1063" s="11"/>
-    </row>
-    <row r="1064" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1063" s="8"/>
+    </row>
+    <row r="1064" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1064" s="11"/>
       <c r="D1064" s="11"/>
       <c r="E1064" s="11"/>
-    </row>
-    <row r="1065" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1064" s="8"/>
+    </row>
+    <row r="1065" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1065" s="11"/>
       <c r="D1065" s="11"/>
       <c r="E1065" s="11"/>
-    </row>
-    <row r="1066" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1065" s="8"/>
+    </row>
+    <row r="1066" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1066" s="11"/>
       <c r="D1066" s="11"/>
       <c r="E1066" s="11"/>
-    </row>
-    <row r="1067" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1066" s="8"/>
+    </row>
+    <row r="1067" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1067" s="11"/>
       <c r="D1067" s="11"/>
       <c r="E1067" s="11"/>
-    </row>
-    <row r="1068" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1067" s="8"/>
+    </row>
+    <row r="1068" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1068" s="11"/>
       <c r="D1068" s="11"/>
       <c r="E1068" s="11"/>
-    </row>
-    <row r="1069" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1068" s="8"/>
+    </row>
+    <row r="1069" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1069" s="11"/>
       <c r="D1069" s="11"/>
       <c r="E1069" s="11"/>
-    </row>
-    <row r="1070" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1069" s="8"/>
+    </row>
+    <row r="1070" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1070" s="11"/>
       <c r="D1070" s="11"/>
       <c r="E1070" s="11"/>
-    </row>
-    <row r="1071" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1070" s="8"/>
+    </row>
+    <row r="1071" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1071" s="11"/>
       <c r="D1071" s="11"/>
       <c r="E1071" s="11"/>
-    </row>
-    <row r="1072" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1071" s="8"/>
+    </row>
+    <row r="1072" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1072" s="11"/>
       <c r="D1072" s="11"/>
       <c r="E1072" s="11"/>
-    </row>
-    <row r="1073" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1072" s="8"/>
+    </row>
+    <row r="1073" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1073" s="11"/>
       <c r="D1073" s="11"/>
       <c r="E1073" s="11"/>
-    </row>
-    <row r="1074" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1073" s="8"/>
+    </row>
+    <row r="1074" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1074" s="11"/>
       <c r="D1074" s="11"/>
       <c r="E1074" s="11"/>
-    </row>
-    <row r="1075" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1074" s="8"/>
+    </row>
+    <row r="1075" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1075" s="11"/>
       <c r="D1075" s="11"/>
       <c r="E1075" s="11"/>
-    </row>
-    <row r="1076" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1075" s="8"/>
+    </row>
+    <row r="1076" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1076" s="11"/>
       <c r="D1076" s="11"/>
       <c r="E1076" s="11"/>
-    </row>
-    <row r="1077" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1076" s="8"/>
+    </row>
+    <row r="1077" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1077" s="11"/>
       <c r="D1077" s="11"/>
       <c r="E1077" s="11"/>
-    </row>
-    <row r="1078" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1077" s="8"/>
+    </row>
+    <row r="1078" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1078" s="11"/>
       <c r="D1078" s="11"/>
       <c r="E1078" s="11"/>
-    </row>
-    <row r="1079" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1078" s="8"/>
+    </row>
+    <row r="1079" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1079" s="11"/>
       <c r="D1079" s="11"/>
       <c r="E1079" s="11"/>
-    </row>
-    <row r="1080" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1079" s="8"/>
+    </row>
+    <row r="1080" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1080" s="11"/>
       <c r="D1080" s="11"/>
       <c r="E1080" s="11"/>
-    </row>
-    <row r="1081" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1080" s="8"/>
+    </row>
+    <row r="1081" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1081" s="11"/>
       <c r="D1081" s="11"/>
       <c r="E1081" s="11"/>
-    </row>
-    <row r="1082" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1081" s="8"/>
+    </row>
+    <row r="1082" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1082" s="11"/>
       <c r="D1082" s="11"/>
       <c r="E1082" s="11"/>
-    </row>
-    <row r="1083" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1082" s="8"/>
+    </row>
+    <row r="1083" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1083" s="11"/>
       <c r="D1083" s="11"/>
       <c r="E1083" s="11"/>
-    </row>
-    <row r="1084" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1083" s="8"/>
+    </row>
+    <row r="1084" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1084" s="11"/>
       <c r="D1084" s="11"/>
       <c r="E1084" s="11"/>
-    </row>
-    <row r="1085" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1084" s="8"/>
+    </row>
+    <row r="1085" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1085" s="11"/>
       <c r="D1085" s="11"/>
       <c r="E1085" s="11"/>
-    </row>
-    <row r="1086" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1085" s="8"/>
+    </row>
+    <row r="1086" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1086" s="11"/>
       <c r="D1086" s="11"/>
       <c r="E1086" s="11"/>
-    </row>
-    <row r="1087" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1086" s="8"/>
+    </row>
+    <row r="1087" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1087" s="11"/>
       <c r="D1087" s="11"/>
       <c r="E1087" s="11"/>
-    </row>
-    <row r="1088" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1087" s="8"/>
+    </row>
+    <row r="1088" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1088" s="11"/>
       <c r="D1088" s="11"/>
       <c r="E1088" s="11"/>
-    </row>
-    <row r="1089" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1088" s="8"/>
+    </row>
+    <row r="1089" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1089" s="11"/>
       <c r="D1089" s="11"/>
       <c r="E1089" s="11"/>
-    </row>
-    <row r="1090" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1089" s="8"/>
+    </row>
+    <row r="1090" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1090" s="11"/>
       <c r="D1090" s="11"/>
       <c r="E1090" s="11"/>
-    </row>
-    <row r="1091" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1090" s="8"/>
+    </row>
+    <row r="1091" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1091" s="11"/>
       <c r="D1091" s="11"/>
       <c r="E1091" s="11"/>
-    </row>
-    <row r="1092" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1091" s="8"/>
+    </row>
+    <row r="1092" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1092" s="11"/>
       <c r="D1092" s="11"/>
       <c r="E1092" s="11"/>
-    </row>
-    <row r="1093" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1092" s="8"/>
+    </row>
+    <row r="1093" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1093" s="11"/>
       <c r="D1093" s="11"/>
       <c r="E1093" s="11"/>
-    </row>
-    <row r="1094" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1093" s="8"/>
+    </row>
+    <row r="1094" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1094" s="11"/>
       <c r="D1094" s="11"/>
       <c r="E1094" s="11"/>
-    </row>
-    <row r="1095" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1094" s="8"/>
+    </row>
+    <row r="1095" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1095" s="11"/>
       <c r="D1095" s="11"/>
       <c r="E1095" s="11"/>
-    </row>
-    <row r="1096" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1095" s="8"/>
+    </row>
+    <row r="1096" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1096" s="11"/>
       <c r="D1096" s="11"/>
       <c r="E1096" s="11"/>
-    </row>
-    <row r="1097" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1096" s="8"/>
+    </row>
+    <row r="1097" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1097" s="11"/>
       <c r="D1097" s="11"/>
       <c r="E1097" s="11"/>
-    </row>
-    <row r="1098" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1097" s="8"/>
+    </row>
+    <row r="1098" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1098" s="11"/>
       <c r="D1098" s="11"/>
       <c r="E1098" s="11"/>
-    </row>
-    <row r="1099" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1098" s="8"/>
+    </row>
+    <row r="1099" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1099" s="11"/>
       <c r="D1099" s="11"/>
       <c r="E1099" s="11"/>
-    </row>
-    <row r="1100" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1099" s="8"/>
+    </row>
+    <row r="1100" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1100" s="11"/>
       <c r="D1100" s="11"/>
       <c r="E1100" s="11"/>
-    </row>
-    <row r="1101" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1100" s="8"/>
+    </row>
+    <row r="1101" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1101" s="11"/>
       <c r="D1101" s="11"/>
       <c r="E1101" s="11"/>
-    </row>
-    <row r="1102" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1101" s="8"/>
+    </row>
+    <row r="1102" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1102" s="11"/>
       <c r="D1102" s="11"/>
       <c r="E1102" s="11"/>
-    </row>
-    <row r="1103" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1102" s="8"/>
+    </row>
+    <row r="1103" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1103" s="11"/>
       <c r="D1103" s="11"/>
       <c r="E1103" s="11"/>
-    </row>
-    <row r="1104" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1103" s="8"/>
+    </row>
+    <row r="1104" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1104" s="11"/>
       <c r="D1104" s="11"/>
       <c r="E1104" s="11"/>
-    </row>
-    <row r="1105" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1104" s="8"/>
+    </row>
+    <row r="1105" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1105" s="11"/>
       <c r="D1105" s="11"/>
       <c r="E1105" s="11"/>
-    </row>
-    <row r="1106" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1105" s="8"/>
+    </row>
+    <row r="1106" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1106" s="11"/>
       <c r="D1106" s="11"/>
       <c r="E1106" s="11"/>
-    </row>
-    <row r="1107" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1106" s="8"/>
+    </row>
+    <row r="1107" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1107" s="11"/>
       <c r="D1107" s="11"/>
       <c r="E1107" s="11"/>
-    </row>
-    <row r="1108" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1107" s="8"/>
+    </row>
+    <row r="1108" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1108" s="11"/>
       <c r="D1108" s="11"/>
       <c r="E1108" s="11"/>
-    </row>
-    <row r="1109" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1108" s="8"/>
+    </row>
+    <row r="1109" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1109" s="11"/>
       <c r="D1109" s="11"/>
       <c r="E1109" s="11"/>
-    </row>
-    <row r="1110" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1109" s="8"/>
+    </row>
+    <row r="1110" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1110" s="11"/>
       <c r="D1110" s="11"/>
       <c r="E1110" s="11"/>
-    </row>
-    <row r="1111" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1110" s="8"/>
+    </row>
+    <row r="1111" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1111" s="11"/>
       <c r="D1111" s="11"/>
       <c r="E1111" s="11"/>
-    </row>
-    <row r="1112" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1111" s="8"/>
+    </row>
+    <row r="1112" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1112" s="11"/>
       <c r="D1112" s="11"/>
       <c r="E1112" s="11"/>
-    </row>
-    <row r="1113" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1112" s="8"/>
+    </row>
+    <row r="1113" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1113" s="11"/>
       <c r="D1113" s="11"/>
       <c r="E1113" s="11"/>
-    </row>
-    <row r="1114" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1113" s="8"/>
+    </row>
+    <row r="1114" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1114" s="11"/>
       <c r="D1114" s="11"/>
       <c r="E1114" s="11"/>
-    </row>
-    <row r="1115" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1114" s="8"/>
+    </row>
+    <row r="1115" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1115" s="11"/>
       <c r="D1115" s="11"/>
       <c r="E1115" s="11"/>
-    </row>
-    <row r="1116" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1115" s="8"/>
+    </row>
+    <row r="1116" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1116" s="11"/>
       <c r="D1116" s="11"/>
       <c r="E1116" s="11"/>
-    </row>
-    <row r="1117" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1116" s="8"/>
+    </row>
+    <row r="1117" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1117" s="11"/>
       <c r="D1117" s="11"/>
       <c r="E1117" s="11"/>
-    </row>
-    <row r="1118" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1117" s="8"/>
+    </row>
+    <row r="1118" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1118" s="11"/>
       <c r="D1118" s="11"/>
       <c r="E1118" s="11"/>
-    </row>
-    <row r="1119" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1118" s="8"/>
+    </row>
+    <row r="1119" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1119" s="11"/>
       <c r="D1119" s="11"/>
       <c r="E1119" s="11"/>
-    </row>
-    <row r="1120" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1119" s="8"/>
+    </row>
+    <row r="1120" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1120" s="11"/>
       <c r="D1120" s="11"/>
       <c r="E1120" s="11"/>
-    </row>
-    <row r="1121" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1120" s="8"/>
+    </row>
+    <row r="1121" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1121" s="11"/>
       <c r="D1121" s="11"/>
       <c r="E1121" s="11"/>
-    </row>
-    <row r="1122" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1121" s="8"/>
+    </row>
+    <row r="1122" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1122" s="11"/>
       <c r="D1122" s="11"/>
       <c r="E1122" s="11"/>
-    </row>
-    <row r="1123" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1122" s="8"/>
+    </row>
+    <row r="1123" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1123" s="11"/>
       <c r="D1123" s="11"/>
       <c r="E1123" s="11"/>
-    </row>
-    <row r="1124" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1123" s="8"/>
+    </row>
+    <row r="1124" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1124" s="11"/>
       <c r="D1124" s="11"/>
       <c r="E1124" s="11"/>
-    </row>
-    <row r="1125" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1124" s="8"/>
+    </row>
+    <row r="1125" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1125" s="11"/>
       <c r="D1125" s="11"/>
       <c r="E1125" s="11"/>
-    </row>
-    <row r="1126" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1125" s="8"/>
+    </row>
+    <row r="1126" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1126" s="11"/>
       <c r="D1126" s="11"/>
       <c r="E1126" s="11"/>
-    </row>
-    <row r="1127" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1126" s="8"/>
+    </row>
+    <row r="1127" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1127" s="11"/>
       <c r="D1127" s="11"/>
       <c r="E1127" s="11"/>
-    </row>
-    <row r="1128" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1127" s="8"/>
+    </row>
+    <row r="1128" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1128" s="11"/>
       <c r="D1128" s="11"/>
       <c r="E1128" s="11"/>
-    </row>
-    <row r="1129" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1128" s="8"/>
+    </row>
+    <row r="1129" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1129" s="11"/>
       <c r="D1129" s="11"/>
       <c r="E1129" s="11"/>
-    </row>
-    <row r="1130" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1129" s="8"/>
+    </row>
+    <row r="1130" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1130" s="11"/>
       <c r="D1130" s="11"/>
       <c r="E1130" s="11"/>
-    </row>
-    <row r="1131" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1130" s="8"/>
+    </row>
+    <row r="1131" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1131" s="11"/>
       <c r="D1131" s="11"/>
       <c r="E1131" s="11"/>
-    </row>
-    <row r="1132" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1131" s="8"/>
+    </row>
+    <row r="1132" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1132" s="11"/>
       <c r="D1132" s="11"/>
       <c r="E1132" s="11"/>
-    </row>
-    <row r="1133" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1132" s="8"/>
+    </row>
+    <row r="1133" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1133" s="11"/>
       <c r="D1133" s="11"/>
       <c r="E1133" s="11"/>
-    </row>
-    <row r="1134" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1133" s="8"/>
+    </row>
+    <row r="1134" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1134" s="11"/>
       <c r="D1134" s="11"/>
       <c r="E1134" s="11"/>
-    </row>
-    <row r="1135" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1134" s="8"/>
+    </row>
+    <row r="1135" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1135" s="11"/>
       <c r="D1135" s="11"/>
       <c r="E1135" s="11"/>
-    </row>
-    <row r="1136" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1135" s="8"/>
+    </row>
+    <row r="1136" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1136" s="11"/>
       <c r="D1136" s="11"/>
       <c r="E1136" s="11"/>
-    </row>
-    <row r="1137" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1136" s="8"/>
+    </row>
+    <row r="1137" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1137" s="11"/>
       <c r="D1137" s="11"/>
       <c r="E1137" s="11"/>
-    </row>
-    <row r="1138" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1137" s="8"/>
+    </row>
+    <row r="1138" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1138" s="11"/>
       <c r="D1138" s="11"/>
       <c r="E1138" s="11"/>
-    </row>
-    <row r="1139" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1138" s="8"/>
+    </row>
+    <row r="1139" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1139" s="11"/>
       <c r="D1139" s="11"/>
       <c r="E1139" s="11"/>
-    </row>
-    <row r="1140" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1139" s="8"/>
+    </row>
+    <row r="1140" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1140" s="11"/>
       <c r="D1140" s="11"/>
       <c r="E1140" s="11"/>
-    </row>
-    <row r="1141" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1140" s="8"/>
+    </row>
+    <row r="1141" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1141" s="11"/>
       <c r="D1141" s="11"/>
       <c r="E1141" s="11"/>
-    </row>
-    <row r="1142" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1141" s="8"/>
+    </row>
+    <row r="1142" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1142" s="11"/>
       <c r="D1142" s="11"/>
       <c r="E1142" s="11"/>
-    </row>
-    <row r="1143" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1142" s="8"/>
+    </row>
+    <row r="1143" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1143" s="11"/>
       <c r="D1143" s="11"/>
       <c r="E1143" s="11"/>
-    </row>
-    <row r="1144" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1143" s="8"/>
+    </row>
+    <row r="1144" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1144" s="11"/>
       <c r="D1144" s="11"/>
       <c r="E1144" s="11"/>
-    </row>
-    <row r="1145" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1144" s="8"/>
+    </row>
+    <row r="1145" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1145" s="11"/>
       <c r="D1145" s="11"/>
       <c r="E1145" s="11"/>
-    </row>
-    <row r="1146" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1145" s="8"/>
+    </row>
+    <row r="1146" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1146" s="11"/>
       <c r="D1146" s="11"/>
       <c r="E1146" s="11"/>
-    </row>
-    <row r="1147" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1146" s="8"/>
+    </row>
+    <row r="1147" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1147" s="11"/>
       <c r="D1147" s="11"/>
       <c r="E1147" s="11"/>
-    </row>
-    <row r="1148" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1147" s="8"/>
+    </row>
+    <row r="1148" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1148" s="11"/>
       <c r="D1148" s="11"/>
       <c r="E1148" s="11"/>
-    </row>
-    <row r="1149" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1148" s="8"/>
+    </row>
+    <row r="1149" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1149" s="11"/>
       <c r="D1149" s="11"/>
       <c r="E1149" s="11"/>
-    </row>
-    <row r="1150" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1149" s="8"/>
+    </row>
+    <row r="1150" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1150" s="11"/>
       <c r="D1150" s="11"/>
       <c r="E1150" s="11"/>
-    </row>
-    <row r="1151" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1150" s="8"/>
+    </row>
+    <row r="1151" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1151" s="11"/>
       <c r="D1151" s="11"/>
       <c r="E1151" s="11"/>
-    </row>
-    <row r="1152" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1151" s="8"/>
+    </row>
+    <row r="1152" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1152" s="11"/>
       <c r="D1152" s="11"/>
       <c r="E1152" s="11"/>
-    </row>
-    <row r="1153" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1152" s="8"/>
+    </row>
+    <row r="1153" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1153" s="11"/>
       <c r="D1153" s="11"/>
       <c r="E1153" s="11"/>
-    </row>
-    <row r="1154" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1153" s="8"/>
+    </row>
+    <row r="1154" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1154" s="11"/>
       <c r="D1154" s="11"/>
       <c r="E1154" s="11"/>
-    </row>
-    <row r="1155" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1154" s="8"/>
+    </row>
+    <row r="1155" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1155" s="11"/>
       <c r="D1155" s="11"/>
       <c r="E1155" s="11"/>
-    </row>
-    <row r="1156" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1155" s="8"/>
+    </row>
+    <row r="1156" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1156" s="11"/>
       <c r="D1156" s="11"/>
       <c r="E1156" s="11"/>
-    </row>
-    <row r="1157" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1156" s="8"/>
+    </row>
+    <row r="1157" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1157" s="11"/>
       <c r="D1157" s="11"/>
       <c r="E1157" s="11"/>
-    </row>
-    <row r="1158" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1157" s="8"/>
+    </row>
+    <row r="1158" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1158" s="11"/>
       <c r="D1158" s="11"/>
       <c r="E1158" s="11"/>
-    </row>
-    <row r="1159" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1158" s="8"/>
+    </row>
+    <row r="1159" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1159" s="11"/>
       <c r="D1159" s="11"/>
       <c r="E1159" s="11"/>
-    </row>
-    <row r="1160" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1159" s="8"/>
+    </row>
+    <row r="1160" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1160" s="11"/>
       <c r="D1160" s="11"/>
       <c r="E1160" s="11"/>
-    </row>
-    <row r="1161" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1160" s="8"/>
+    </row>
+    <row r="1161" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1161" s="11"/>
       <c r="D1161" s="11"/>
       <c r="E1161" s="11"/>
-    </row>
-    <row r="1162" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1161" s="8"/>
+    </row>
+    <row r="1162" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1162" s="11"/>
       <c r="D1162" s="11"/>
       <c r="E1162" s="11"/>
-    </row>
-    <row r="1163" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1162" s="8"/>
+    </row>
+    <row r="1163" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1163" s="11"/>
       <c r="D1163" s="11"/>
       <c r="E1163" s="11"/>
-    </row>
-    <row r="1164" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1163" s="8"/>
+    </row>
+    <row r="1164" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1164" s="11"/>
       <c r="D1164" s="11"/>
       <c r="E1164" s="11"/>
-    </row>
-    <row r="1165" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1164" s="8"/>
+    </row>
+    <row r="1165" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1165" s="11"/>
       <c r="D1165" s="11"/>
       <c r="E1165" s="11"/>
-    </row>
-    <row r="1166" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1165" s="8"/>
+    </row>
+    <row r="1166" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1166" s="11"/>
       <c r="D1166" s="11"/>
       <c r="E1166" s="11"/>
-    </row>
-    <row r="1167" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1166" s="8"/>
+    </row>
+    <row r="1167" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1167" s="11"/>
       <c r="D1167" s="11"/>
       <c r="E1167" s="11"/>
-    </row>
-    <row r="1168" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1167" s="8"/>
+    </row>
+    <row r="1168" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1168" s="11"/>
       <c r="D1168" s="11"/>
       <c r="E1168" s="11"/>
-    </row>
-    <row r="1169" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1168" s="8"/>
+    </row>
+    <row r="1169" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1169" s="11"/>
       <c r="D1169" s="11"/>
       <c r="E1169" s="11"/>
-    </row>
-    <row r="1170" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1169" s="8"/>
+    </row>
+    <row r="1170" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1170" s="11"/>
       <c r="D1170" s="11"/>
       <c r="E1170" s="11"/>
-    </row>
-    <row r="1171" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1170" s="8"/>
+    </row>
+    <row r="1171" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1171" s="11"/>
       <c r="D1171" s="11"/>
       <c r="E1171" s="11"/>
-    </row>
-    <row r="1172" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1171" s="8"/>
+    </row>
+    <row r="1172" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1172" s="11"/>
       <c r="D1172" s="11"/>
       <c r="E1172" s="11"/>
-    </row>
-    <row r="1173" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1172" s="8"/>
+    </row>
+    <row r="1173" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1173" s="11"/>
       <c r="D1173" s="11"/>
       <c r="E1173" s="11"/>
-    </row>
-    <row r="1174" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1173" s="8"/>
+    </row>
+    <row r="1174" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1174" s="11"/>
       <c r="D1174" s="11"/>
       <c r="E1174" s="11"/>
-    </row>
-    <row r="1175" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1174" s="8"/>
+    </row>
+    <row r="1175" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1175" s="11"/>
       <c r="D1175" s="11"/>
       <c r="E1175" s="11"/>
-    </row>
-    <row r="1176" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1175" s="8"/>
+    </row>
+    <row r="1176" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1176" s="11"/>
       <c r="D1176" s="11"/>
       <c r="E1176" s="11"/>
-    </row>
-    <row r="1177" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1176" s="8"/>
+    </row>
+    <row r="1177" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1177" s="11"/>
       <c r="D1177" s="11"/>
       <c r="E1177" s="11"/>
-    </row>
-    <row r="1178" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1177" s="8"/>
+    </row>
+    <row r="1178" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1178" s="11"/>
       <c r="D1178" s="11"/>
       <c r="E1178" s="11"/>
-    </row>
-    <row r="1179" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="G1178" s="8"/>
+    </row>
+    <row r="1179" spans="3:7" x14ac:dyDescent="0.25">
       <c r="C1179" s="11"/>
       <c r="D1179" s="11"/>
       <c r="E1179" s="11"/>
-    </row>
-    <row r="1180" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1180" s="11"/>
-      <c r="D1180" s="11"/>
-      <c r="E1180" s="11"/>
-    </row>
-    <row r="1181" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1181" s="11"/>
-      <c r="D1181" s="11"/>
-      <c r="E1181" s="11"/>
-    </row>
-    <row r="1182" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1182" s="11"/>
-      <c r="D1182" s="11"/>
-      <c r="E1182" s="11"/>
-    </row>
-    <row r="1183" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1183" s="11"/>
-      <c r="D1183" s="11"/>
-      <c r="E1183" s="11"/>
-    </row>
-    <row r="1184" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1184" s="11"/>
-      <c r="D1184" s="11"/>
-      <c r="E1184" s="11"/>
-    </row>
-    <row r="1185" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1185" s="11"/>
-      <c r="D1185" s="11"/>
-      <c r="E1185" s="11"/>
-    </row>
-    <row r="1186" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1186" s="11"/>
-      <c r="D1186" s="11"/>
-      <c r="E1186" s="11"/>
-    </row>
-    <row r="1187" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1187" s="11"/>
-      <c r="D1187" s="11"/>
-      <c r="E1187" s="11"/>
-    </row>
-    <row r="1188" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1188" s="11"/>
-      <c r="D1188" s="11"/>
-      <c r="E1188" s="11"/>
-    </row>
-    <row r="1189" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1189" s="11"/>
-      <c r="D1189" s="11"/>
-      <c r="E1189" s="11"/>
-    </row>
-    <row r="1190" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1190" s="11"/>
-      <c r="D1190" s="11"/>
-      <c r="E1190" s="11"/>
-    </row>
-    <row r="1191" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1191" s="11"/>
-      <c r="D1191" s="11"/>
-      <c r="E1191" s="11"/>
-    </row>
-    <row r="1192" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1192" s="11"/>
-      <c r="D1192" s="11"/>
-      <c r="E1192" s="11"/>
-    </row>
-    <row r="1193" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1193" s="11"/>
-      <c r="D1193" s="11"/>
-      <c r="E1193" s="11"/>
-    </row>
-    <row r="1194" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1194" s="11"/>
-      <c r="D1194" s="11"/>
-      <c r="E1194" s="11"/>
-    </row>
-    <row r="1195" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1195" s="11"/>
-      <c r="D1195" s="11"/>
-      <c r="E1195" s="11"/>
-    </row>
-    <row r="1196" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1196" s="11"/>
-      <c r="D1196" s="11"/>
-      <c r="E1196" s="11"/>
-    </row>
-    <row r="1197" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1197" s="11"/>
-      <c r="D1197" s="11"/>
-      <c r="E1197" s="11"/>
-    </row>
-    <row r="1198" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1198" s="11"/>
-      <c r="D1198" s="11"/>
-      <c r="E1198" s="11"/>
-    </row>
-    <row r="1199" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1199" s="11"/>
-      <c r="D1199" s="11"/>
-      <c r="E1199" s="11"/>
-    </row>
-    <row r="1200" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1200" s="11"/>
-      <c r="D1200" s="11"/>
-      <c r="E1200" s="11"/>
-    </row>
-    <row r="1201" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1201" s="11"/>
-      <c r="D1201" s="11"/>
-      <c r="E1201" s="11"/>
-    </row>
-    <row r="1202" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1202" s="11"/>
-      <c r="D1202" s="11"/>
-      <c r="E1202" s="11"/>
-    </row>
-    <row r="1203" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1203" s="11"/>
-      <c r="D1203" s="11"/>
-      <c r="E1203" s="11"/>
-    </row>
-    <row r="1204" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1204" s="11"/>
-      <c r="D1204" s="11"/>
-      <c r="E1204" s="11"/>
-    </row>
-    <row r="1205" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1205" s="11"/>
-      <c r="D1205" s="11"/>
-      <c r="E1205" s="11"/>
-    </row>
-    <row r="1206" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1206" s="11"/>
-      <c r="D1206" s="11"/>
-      <c r="E1206" s="11"/>
-    </row>
-    <row r="1207" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1207" s="11"/>
-      <c r="D1207" s="11"/>
-      <c r="E1207" s="11"/>
-    </row>
-    <row r="1208" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1208" s="11"/>
-      <c r="D1208" s="11"/>
-      <c r="E1208" s="11"/>
-    </row>
-    <row r="1209" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1209" s="11"/>
-      <c r="D1209" s="11"/>
-      <c r="E1209" s="11"/>
-    </row>
-    <row r="1210" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1210" s="11"/>
-      <c r="D1210" s="11"/>
-      <c r="E1210" s="11"/>
-    </row>
-    <row r="1211" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1211" s="11"/>
-      <c r="D1211" s="11"/>
-      <c r="E1211" s="11"/>
-    </row>
-    <row r="1212" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1212" s="11"/>
-      <c r="D1212" s="11"/>
-      <c r="E1212" s="11"/>
-    </row>
-    <row r="1213" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1213" s="11"/>
-      <c r="D1213" s="11"/>
-      <c r="E1213" s="11"/>
-    </row>
-    <row r="1214" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1214" s="11"/>
-      <c r="D1214" s="11"/>
-      <c r="E1214" s="11"/>
-    </row>
-    <row r="1215" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1215" s="11"/>
-      <c r="D1215" s="11"/>
-      <c r="E1215" s="11"/>
-    </row>
-    <row r="1216" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1216" s="11"/>
-      <c r="D1216" s="11"/>
-      <c r="E1216" s="11"/>
-    </row>
-    <row r="1217" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1217" s="11"/>
-      <c r="D1217" s="11"/>
-      <c r="E1217" s="11"/>
-    </row>
-    <row r="1218" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1218" s="11"/>
-      <c r="D1218" s="11"/>
-      <c r="E1218" s="11"/>
-    </row>
-    <row r="1219" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1219" s="11"/>
-      <c r="D1219" s="11"/>
-      <c r="E1219" s="11"/>
-    </row>
-    <row r="1220" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1220" s="11"/>
-      <c r="D1220" s="11"/>
-      <c r="E1220" s="11"/>
-    </row>
-    <row r="1221" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1221" s="11"/>
-      <c r="D1221" s="11"/>
-      <c r="E1221" s="11"/>
-    </row>
-    <row r="1222" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1222" s="11"/>
-      <c r="D1222" s="11"/>
-      <c r="E1222" s="11"/>
-    </row>
-    <row r="1223" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1223" s="11"/>
-      <c r="D1223" s="11"/>
-      <c r="E1223" s="11"/>
-    </row>
-    <row r="1224" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1224" s="11"/>
-      <c r="D1224" s="11"/>
-      <c r="E1224" s="11"/>
-    </row>
-    <row r="1225" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1225" s="11"/>
-      <c r="D1225" s="11"/>
-      <c r="E1225" s="11"/>
-    </row>
-    <row r="1226" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1226" s="11"/>
-      <c r="D1226" s="11"/>
-      <c r="E1226" s="11"/>
-    </row>
-    <row r="1227" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1227" s="11"/>
-      <c r="D1227" s="11"/>
-      <c r="E1227" s="11"/>
-    </row>
-    <row r="1228" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1228" s="11"/>
-      <c r="D1228" s="11"/>
-      <c r="E1228" s="11"/>
-    </row>
-    <row r="1229" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1229" s="11"/>
-      <c r="D1229" s="11"/>
-      <c r="E1229" s="11"/>
-    </row>
-    <row r="1230" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1230" s="11"/>
-      <c r="D1230" s="11"/>
-      <c r="E1230" s="11"/>
-    </row>
-    <row r="1231" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1231" s="11"/>
-      <c r="D1231" s="11"/>
-      <c r="E1231" s="11"/>
-    </row>
-    <row r="1232" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1232" s="11"/>
-      <c r="D1232" s="11"/>
-      <c r="E1232" s="11"/>
-    </row>
-    <row r="1233" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1233" s="11"/>
-      <c r="D1233" s="11"/>
-      <c r="E1233" s="11"/>
-    </row>
-    <row r="1234" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1234" s="11"/>
-      <c r="D1234" s="11"/>
-      <c r="E1234" s="11"/>
-    </row>
-    <row r="1235" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1235" s="11"/>
-      <c r="D1235" s="11"/>
-      <c r="E1235" s="11"/>
-    </row>
-    <row r="1236" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1236" s="11"/>
-      <c r="D1236" s="11"/>
-      <c r="E1236" s="11"/>
-    </row>
-    <row r="1237" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1237" s="11"/>
-      <c r="D1237" s="11"/>
-      <c r="E1237" s="11"/>
-    </row>
-    <row r="1238" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1238" s="11"/>
-      <c r="D1238" s="11"/>
-      <c r="E1238" s="11"/>
-    </row>
-    <row r="1239" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1239" s="11"/>
-      <c r="D1239" s="11"/>
-      <c r="E1239" s="11"/>
-    </row>
-    <row r="1240" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1240" s="11"/>
-      <c r="D1240" s="11"/>
-      <c r="E1240" s="11"/>
-    </row>
-    <row r="1241" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1241" s="11"/>
-      <c r="D1241" s="11"/>
-      <c r="E1241" s="11"/>
-    </row>
-    <row r="1242" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1242" s="11"/>
-      <c r="D1242" s="11"/>
-      <c r="E1242" s="11"/>
-    </row>
-    <row r="1243" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1243" s="11"/>
-      <c r="D1243" s="11"/>
-      <c r="E1243" s="11"/>
-    </row>
-    <row r="1244" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1244" s="11"/>
-      <c r="D1244" s="11"/>
-      <c r="E1244" s="11"/>
-    </row>
-    <row r="1245" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1245" s="11"/>
-      <c r="D1245" s="11"/>
-      <c r="E1245" s="11"/>
-    </row>
-    <row r="1246" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1246" s="11"/>
-      <c r="D1246" s="11"/>
-      <c r="E1246" s="11"/>
-    </row>
-    <row r="1247" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1247" s="11"/>
-      <c r="D1247" s="11"/>
-      <c r="E1247" s="11"/>
-    </row>
-    <row r="1248" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1248" s="11"/>
-      <c r="D1248" s="11"/>
-      <c r="E1248" s="11"/>
-    </row>
-    <row r="1249" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1249" s="11"/>
-      <c r="D1249" s="11"/>
-      <c r="E1249" s="11"/>
-    </row>
-    <row r="1250" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1250" s="11"/>
-      <c r="D1250" s="11"/>
-      <c r="E1250" s="11"/>
-    </row>
-    <row r="1251" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1251" s="11"/>
-      <c r="D1251" s="11"/>
-      <c r="E1251" s="11"/>
-    </row>
-    <row r="1252" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1252" s="11"/>
-      <c r="D1252" s="11"/>
-      <c r="E1252" s="11"/>
-    </row>
-    <row r="1253" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1253" s="11"/>
-      <c r="D1253" s="11"/>
-      <c r="E1253" s="11"/>
-    </row>
-    <row r="1254" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1254" s="11"/>
-      <c r="D1254" s="11"/>
-      <c r="E1254" s="11"/>
-    </row>
-    <row r="1255" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1255" s="11"/>
-      <c r="D1255" s="11"/>
-      <c r="E1255" s="11"/>
-    </row>
-    <row r="1256" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1256" s="11"/>
-      <c r="D1256" s="11"/>
-      <c r="E1256" s="11"/>
-    </row>
-    <row r="1257" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1257" s="11"/>
-      <c r="D1257" s="11"/>
-      <c r="E1257" s="11"/>
-    </row>
-    <row r="1258" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1258" s="11"/>
-      <c r="D1258" s="11"/>
-      <c r="E1258" s="11"/>
-    </row>
-    <row r="1259" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1259" s="11"/>
-      <c r="D1259" s="11"/>
-      <c r="E1259" s="11"/>
-    </row>
-    <row r="1260" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1260" s="11"/>
-      <c r="D1260" s="11"/>
-      <c r="E1260" s="11"/>
-    </row>
-    <row r="1261" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1261" s="11"/>
-      <c r="D1261" s="11"/>
-      <c r="E1261" s="11"/>
-    </row>
-    <row r="1262" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1262" s="11"/>
-      <c r="D1262" s="11"/>
-      <c r="E1262" s="11"/>
-    </row>
-    <row r="1263" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1263" s="11"/>
-      <c r="D1263" s="11"/>
-      <c r="E1263" s="11"/>
-    </row>
-    <row r="1264" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1264" s="11"/>
-      <c r="D1264" s="11"/>
-      <c r="E1264" s="11"/>
-    </row>
-    <row r="1265" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1265" s="11"/>
-      <c r="D1265" s="11"/>
-      <c r="E1265" s="11"/>
-    </row>
-    <row r="1266" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1266" s="11"/>
-      <c r="D1266" s="11"/>
-      <c r="E1266" s="11"/>
-    </row>
-    <row r="1267" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1267" s="11"/>
-      <c r="D1267" s="11"/>
-      <c r="E1267" s="11"/>
-    </row>
-    <row r="1268" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1268" s="11"/>
-      <c r="D1268" s="11"/>
-      <c r="E1268" s="11"/>
-    </row>
-    <row r="1269" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1269" s="11"/>
-      <c r="D1269" s="11"/>
-      <c r="E1269" s="11"/>
-    </row>
-    <row r="1270" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1270" s="11"/>
-      <c r="D1270" s="11"/>
-      <c r="E1270" s="11"/>
-    </row>
-    <row r="1271" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1271" s="11"/>
-      <c r="D1271" s="11"/>
-      <c r="E1271" s="11"/>
-    </row>
-    <row r="1272" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1272" s="11"/>
-      <c r="D1272" s="11"/>
-      <c r="E1272" s="11"/>
-    </row>
-    <row r="1273" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1273" s="11"/>
-      <c r="D1273" s="11"/>
-      <c r="E1273" s="11"/>
-    </row>
-    <row r="1274" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1274" s="11"/>
-      <c r="D1274" s="11"/>
-      <c r="E1274" s="11"/>
-    </row>
-    <row r="1275" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1275" s="11"/>
-      <c r="D1275" s="11"/>
-      <c r="E1275" s="11"/>
-    </row>
-    <row r="1276" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1276" s="11"/>
-      <c r="D1276" s="11"/>
-      <c r="E1276" s="11"/>
-    </row>
-    <row r="1277" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1277" s="11"/>
-      <c r="D1277" s="11"/>
-      <c r="E1277" s="11"/>
-    </row>
-    <row r="1278" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1278" s="11"/>
-      <c r="D1278" s="11"/>
-      <c r="E1278" s="11"/>
-    </row>
-    <row r="1279" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1279" s="11"/>
-      <c r="D1279" s="11"/>
-      <c r="E1279" s="11"/>
-    </row>
-    <row r="1280" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1280" s="11"/>
-      <c r="D1280" s="11"/>
-      <c r="E1280" s="11"/>
-    </row>
-    <row r="1281" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1281" s="11"/>
-      <c r="D1281" s="11"/>
-      <c r="E1281" s="11"/>
-    </row>
-    <row r="1282" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1282" s="11"/>
-      <c r="D1282" s="11"/>
-      <c r="E1282" s="11"/>
-    </row>
-    <row r="1283" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1283" s="11"/>
-      <c r="D1283" s="11"/>
-      <c r="E1283" s="11"/>
-    </row>
-    <row r="1284" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1284" s="11"/>
-      <c r="D1284" s="11"/>
-      <c r="E1284" s="11"/>
-    </row>
-    <row r="1285" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1285" s="11"/>
-      <c r="D1285" s="11"/>
-      <c r="E1285" s="11"/>
-    </row>
-    <row r="1286" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1286" s="11"/>
-      <c r="D1286" s="11"/>
-      <c r="E1286" s="11"/>
-    </row>
-    <row r="1287" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1287" s="11"/>
-      <c r="D1287" s="11"/>
-      <c r="E1287" s="11"/>
-    </row>
-    <row r="1288" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1288" s="11"/>
-      <c r="D1288" s="11"/>
-      <c r="E1288" s="11"/>
-    </row>
-    <row r="1289" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1289" s="11"/>
-      <c r="D1289" s="11"/>
-      <c r="E1289" s="11"/>
-    </row>
-    <row r="1290" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1290" s="11"/>
-      <c r="D1290" s="11"/>
-      <c r="E1290" s="11"/>
-    </row>
-    <row r="1291" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1291" s="11"/>
-      <c r="D1291" s="11"/>
-      <c r="E1291" s="11"/>
-    </row>
-    <row r="1292" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1292" s="11"/>
-      <c r="D1292" s="11"/>
-      <c r="E1292" s="11"/>
-    </row>
-    <row r="1293" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1293" s="11"/>
-      <c r="D1293" s="11"/>
-      <c r="E1293" s="11"/>
-    </row>
-    <row r="1294" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1294" s="11"/>
-      <c r="D1294" s="11"/>
-      <c r="E1294" s="11"/>
-    </row>
-    <row r="1295" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1295" s="11"/>
-      <c r="D1295" s="11"/>
-      <c r="E1295" s="11"/>
-    </row>
-    <row r="1296" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1296" s="11"/>
-      <c r="D1296" s="11"/>
-      <c r="E1296" s="11"/>
-    </row>
-    <row r="1297" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1297" s="11"/>
-      <c r="D1297" s="11"/>
-      <c r="E1297" s="11"/>
-    </row>
-    <row r="1298" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1298" s="11"/>
-      <c r="D1298" s="11"/>
-      <c r="E1298" s="11"/>
-    </row>
-    <row r="1299" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1299" s="11"/>
-      <c r="D1299" s="11"/>
-      <c r="E1299" s="11"/>
-    </row>
-    <row r="1300" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1300" s="11"/>
-      <c r="D1300" s="11"/>
-      <c r="E1300" s="11"/>
-    </row>
-    <row r="1301" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1301" s="11"/>
-      <c r="D1301" s="11"/>
-      <c r="E1301" s="11"/>
-    </row>
-    <row r="1302" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1302" s="11"/>
-      <c r="D1302" s="11"/>
-      <c r="E1302" s="11"/>
-    </row>
-    <row r="1303" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1303" s="11"/>
-      <c r="D1303" s="11"/>
-      <c r="E1303" s="11"/>
-    </row>
-    <row r="1304" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1304" s="11"/>
-      <c r="D1304" s="11"/>
-      <c r="E1304" s="11"/>
-    </row>
-    <row r="1305" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1305" s="11"/>
-      <c r="D1305" s="11"/>
-      <c r="E1305" s="11"/>
-    </row>
-    <row r="1306" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1306" s="11"/>
-      <c r="D1306" s="11"/>
-      <c r="E1306" s="11"/>
-    </row>
-    <row r="1307" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1307" s="11"/>
-      <c r="D1307" s="11"/>
-      <c r="E1307" s="11"/>
-    </row>
-    <row r="1308" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1308" s="11"/>
-      <c r="D1308" s="11"/>
-      <c r="E1308" s="11"/>
-    </row>
-    <row r="1309" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1309" s="11"/>
-      <c r="D1309" s="11"/>
-      <c r="E1309" s="11"/>
-    </row>
-    <row r="1310" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1310" s="11"/>
-      <c r="D1310" s="11"/>
-      <c r="E1310" s="11"/>
-    </row>
-    <row r="1311" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1311" s="11"/>
-      <c r="D1311" s="11"/>
-      <c r="E1311" s="11"/>
-    </row>
-    <row r="1312" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1312" s="11"/>
-      <c r="D1312" s="11"/>
-      <c r="E1312" s="11"/>
-    </row>
-    <row r="1313" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1313" s="11"/>
-      <c r="D1313" s="11"/>
-      <c r="E1313" s="11"/>
-    </row>
-    <row r="1314" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1314" s="11"/>
-      <c r="D1314" s="11"/>
-      <c r="E1314" s="11"/>
-    </row>
-    <row r="1315" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1315" s="11"/>
-      <c r="D1315" s="11"/>
-      <c r="E1315" s="11"/>
-    </row>
-    <row r="1316" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1316" s="11"/>
-      <c r="D1316" s="11"/>
-      <c r="E1316" s="11"/>
-    </row>
-    <row r="1317" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1317" s="11"/>
-      <c r="D1317" s="11"/>
-      <c r="E1317" s="11"/>
-    </row>
-    <row r="1318" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1318" s="11"/>
-      <c r="D1318" s="11"/>
-      <c r="E1318" s="11"/>
-    </row>
-    <row r="1319" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1319" s="11"/>
-      <c r="D1319" s="11"/>
-      <c r="E1319" s="11"/>
-    </row>
-    <row r="1320" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1320" s="11"/>
-      <c r="D1320" s="11"/>
-      <c r="E1320" s="11"/>
-    </row>
-    <row r="1321" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1321" s="11"/>
-      <c r="D1321" s="11"/>
-      <c r="E1321" s="11"/>
-    </row>
-    <row r="1322" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1322" s="11"/>
-      <c r="D1322" s="11"/>
-      <c r="E1322" s="11"/>
-    </row>
-    <row r="1323" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1323" s="11"/>
-      <c r="D1323" s="11"/>
-      <c r="E1323" s="11"/>
-    </row>
-    <row r="1324" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1324" s="11"/>
-      <c r="D1324" s="11"/>
-      <c r="E1324" s="11"/>
-    </row>
-    <row r="1325" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1325" s="11"/>
-      <c r="D1325" s="11"/>
-      <c r="E1325" s="11"/>
-    </row>
-    <row r="1326" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1326" s="11"/>
-      <c r="D1326" s="11"/>
-      <c r="E1326" s="11"/>
-    </row>
-    <row r="1327" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C1327" s="11"/>
-      <c r="D1327" s="11"/>
-      <c r="E1327" s="11"/>
+      <c r="G1179" s="8"/>
+    </row>
+    <row r="1180" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G1180" s="8"/>
+    </row>
+    <row r="1181" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G1181" s="8"/>
+    </row>
+    <row r="1182" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G1182" s="8"/>
+    </row>
+    <row r="1183" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G1183" s="8"/>
+    </row>
+    <row r="1184" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="G1184" s="8"/>
+    </row>
+    <row r="1185" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1185" s="8"/>
+    </row>
+    <row r="1186" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1186" s="8"/>
+    </row>
+    <row r="1187" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1187" s="8"/>
+    </row>
+    <row r="1188" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1188" s="8"/>
+    </row>
+    <row r="1189" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1189" s="8"/>
+    </row>
+    <row r="1190" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1190" s="8"/>
+    </row>
+    <row r="1191" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1191" s="8"/>
+    </row>
+    <row r="1192" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1192" s="8"/>
+    </row>
+    <row r="1193" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1193" s="8"/>
+    </row>
+    <row r="1194" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1194" s="8"/>
+    </row>
+    <row r="1195" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1195" s="8"/>
+    </row>
+    <row r="1196" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1196" s="8"/>
+    </row>
+    <row r="1197" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1197" s="8"/>
+    </row>
+    <row r="1198" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1198" s="8"/>
+    </row>
+    <row r="1199" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1199" s="8"/>
+    </row>
+    <row r="1200" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1200" s="8"/>
+    </row>
+    <row r="1201" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1201" s="8"/>
+    </row>
+    <row r="1202" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1202" s="8"/>
+    </row>
+    <row r="1203" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1203" s="8"/>
+    </row>
+    <row r="1204" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1204" s="8"/>
+    </row>
+    <row r="1205" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1205" s="8"/>
+    </row>
+    <row r="1206" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1206" s="8"/>
+    </row>
+    <row r="1207" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1207" s="8"/>
+    </row>
+    <row r="1208" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1208" s="8"/>
+    </row>
+    <row r="1209" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1209" s="8"/>
+    </row>
+    <row r="1210" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1210" s="8"/>
+    </row>
+    <row r="1211" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1211" s="8"/>
+    </row>
+    <row r="1212" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1212" s="8"/>
+    </row>
+    <row r="1213" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1213" s="8"/>
+    </row>
+    <row r="1214" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1214" s="8"/>
+    </row>
+    <row r="1215" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1215" s="8"/>
+    </row>
+    <row r="1216" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1216" s="8"/>
+    </row>
+    <row r="1217" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1217" s="8"/>
+    </row>
+    <row r="1218" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1218" s="8"/>
+    </row>
+    <row r="1219" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1219" s="8"/>
+    </row>
+    <row r="1220" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1220" s="8"/>
+    </row>
+    <row r="1221" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1221" s="8"/>
+    </row>
+    <row r="1222" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1222" s="8"/>
+    </row>
+    <row r="1223" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1223" s="8"/>
+    </row>
+    <row r="1224" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1224" s="8"/>
+    </row>
+    <row r="1225" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1225" s="8"/>
+    </row>
+    <row r="1226" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1226" s="8"/>
+    </row>
+    <row r="1227" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1227" s="8"/>
+    </row>
+    <row r="1228" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G1228" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I442" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
+  <autoFilter ref="A1:I344" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDDC653D-BE62-4985-9952-BBD554E93013}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60BB41DC-38E7-428D-AC77-F7C8A6F6A150}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$286</definedName>
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="151">
   <si>
     <t>POD</t>
   </si>
@@ -496,9 +496,6 @@
   </si>
   <si>
     <t>ONE</t>
-  </si>
-  <si>
-    <t>XINGANG(TIANJIN)</t>
   </si>
 </sst>
 </file>
@@ -5805,8 +5802,8 @@
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>151</v>
+      <c r="A177" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B177" t="s">
         <v>62</v>
@@ -6806,8 +6803,8 @@
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>151</v>
+      <c r="A214" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B214" t="s">
         <v>15</v>
@@ -7780,8 +7777,8 @@
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
-        <v>151</v>
+      <c r="A250" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B250" t="s">
         <v>15</v>
@@ -8706,8 +8703,8 @@
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A284" t="s">
-        <v>151</v>
+      <c r="A284" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B284" t="s">
         <v>15</v>
@@ -13128,7 +13125,7 @@
       <c r="G1034" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I150" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
+  <autoFilter ref="A1:I286" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60BB41DC-38E7-428D-AC77-F7C8A6F6A150}"/>
+  <xr:revisionPtr revIDLastSave="89" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE7481F8-E578-4902-8AB9-EDDCB025757A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="153">
   <si>
     <t>POD</t>
   </si>
@@ -496,6 +496,12 @@
   </si>
   <si>
     <t>ONE</t>
+  </si>
+  <si>
+    <t>XINGANG(TIANJIN)</t>
+  </si>
+  <si>
+    <t>15 al 19 de abril</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1007,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I1034"/>
+  <dimension ref="A1:I984"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -8784,876 +8790,3744 @@
       </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>5</v>
+      </c>
+      <c r="B287" t="s">
+        <v>62</v>
+      </c>
       <c r="C287" s="11"/>
-      <c r="D287" s="11"/>
-      <c r="E287" s="11"/>
-      <c r="G287" s="8"/>
+      <c r="D287" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E287" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G287" s="8">
+        <v>14</v>
+      </c>
+      <c r="H287" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I287" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>4</v>
+      </c>
+      <c r="B288" t="s">
+        <v>62</v>
+      </c>
       <c r="C288" s="11"/>
-      <c r="D288" s="11"/>
-      <c r="E288" s="11"/>
-      <c r="G288" s="8"/>
-    </row>
-    <row r="289" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D288" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E288" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G288" s="8">
+        <v>14</v>
+      </c>
+      <c r="H288" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>107</v>
+      </c>
+      <c r="B289" t="s">
+        <v>62</v>
+      </c>
       <c r="C289" s="11"/>
-      <c r="D289" s="11"/>
-      <c r="E289" s="11"/>
-      <c r="G289" s="8"/>
-    </row>
-    <row r="290" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D289" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E289" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G289" s="8">
+        <v>14</v>
+      </c>
+      <c r="H289" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I289" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>108</v>
+      </c>
+      <c r="B290" t="s">
+        <v>62</v>
+      </c>
       <c r="C290" s="11"/>
-      <c r="D290" s="11"/>
-      <c r="E290" s="11"/>
-      <c r="G290" s="8"/>
-    </row>
-    <row r="291" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D290" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E290" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G290" s="8">
+        <v>14</v>
+      </c>
+      <c r="H290" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>109</v>
+      </c>
+      <c r="B291" t="s">
+        <v>62</v>
+      </c>
       <c r="C291" s="11"/>
-      <c r="D291" s="11"/>
-      <c r="E291" s="11"/>
-      <c r="G291" s="8"/>
-    </row>
-    <row r="292" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D291" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E291" s="11">
+        <v>2850</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G291" s="8">
+        <v>14</v>
+      </c>
+      <c r="H291" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I291" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>52</v>
+      </c>
+      <c r="B292" t="s">
+        <v>62</v>
+      </c>
       <c r="C292" s="11"/>
-      <c r="D292" s="11"/>
-      <c r="E292" s="11"/>
-      <c r="G292" s="8"/>
-    </row>
-    <row r="293" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D292" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E292" s="11">
+        <v>3110</v>
+      </c>
+      <c r="F292" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G292" s="8">
+        <v>14</v>
+      </c>
+      <c r="H292" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>35</v>
+      </c>
+      <c r="B293" t="s">
+        <v>62</v>
+      </c>
       <c r="C293" s="11"/>
-      <c r="D293" s="11"/>
-      <c r="E293" s="11"/>
-      <c r="G293" s="8"/>
-    </row>
-    <row r="294" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D293" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E293" s="11">
+        <v>3630</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G293" s="8">
+        <v>14</v>
+      </c>
+      <c r="H293" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I293" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>24</v>
+      </c>
+      <c r="B294" t="s">
+        <v>62</v>
+      </c>
       <c r="C294" s="11"/>
-      <c r="D294" s="11"/>
-      <c r="E294" s="11"/>
-      <c r="G294" s="8"/>
-    </row>
-    <row r="295" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D294" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E294" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G294" s="8">
+        <v>14</v>
+      </c>
+      <c r="H294" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I294" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>50</v>
+      </c>
+      <c r="B295" t="s">
+        <v>62</v>
+      </c>
       <c r="C295" s="11"/>
-      <c r="D295" s="11"/>
-      <c r="E295" s="11"/>
-      <c r="G295" s="8"/>
-    </row>
-    <row r="296" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D295" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E295" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G295" s="8">
+        <v>14</v>
+      </c>
+      <c r="H295" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I295" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>29</v>
+      </c>
+      <c r="B296" t="s">
+        <v>62</v>
+      </c>
       <c r="C296" s="11"/>
-      <c r="D296" s="11"/>
-      <c r="E296" s="11"/>
-      <c r="G296" s="8"/>
-    </row>
-    <row r="297" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D296" s="11">
+        <v>3160</v>
+      </c>
+      <c r="E296" s="11">
+        <v>3530</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G296" s="8">
+        <v>14</v>
+      </c>
+      <c r="H296" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I296" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>27</v>
+      </c>
+      <c r="B297" t="s">
+        <v>62</v>
+      </c>
       <c r="C297" s="11"/>
-      <c r="D297" s="11"/>
-      <c r="E297" s="11"/>
-      <c r="G297" s="8"/>
-    </row>
-    <row r="298" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D297" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E297" s="11">
+        <v>3110</v>
+      </c>
+      <c r="F297" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G297" s="8">
+        <v>14</v>
+      </c>
+      <c r="H297" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I297" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>48</v>
+      </c>
+      <c r="B298" t="s">
+        <v>62</v>
+      </c>
       <c r="C298" s="11"/>
-      <c r="D298" s="11"/>
-      <c r="E298" s="11"/>
-      <c r="G298" s="8"/>
-    </row>
-    <row r="299" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D298" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E298" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G298" s="8">
+        <v>14</v>
+      </c>
+      <c r="H298" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I298" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>33</v>
+      </c>
+      <c r="B299" t="s">
+        <v>62</v>
+      </c>
       <c r="C299" s="11"/>
-      <c r="D299" s="11"/>
-      <c r="E299" s="11"/>
-      <c r="G299" s="8"/>
-    </row>
-    <row r="300" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D299" s="11">
+        <v>2900</v>
+      </c>
+      <c r="E299" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G299" s="8">
+        <v>14</v>
+      </c>
+      <c r="H299" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I299" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>30</v>
+      </c>
+      <c r="B300" t="s">
+        <v>62</v>
+      </c>
       <c r="C300" s="11"/>
-      <c r="D300" s="11"/>
-      <c r="E300" s="11"/>
-      <c r="G300" s="8"/>
-    </row>
-    <row r="301" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D300" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E300" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G300" s="8">
+        <v>14</v>
+      </c>
+      <c r="H300" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>56</v>
+      </c>
+      <c r="B301" t="s">
+        <v>62</v>
+      </c>
       <c r="C301" s="11"/>
-      <c r="D301" s="11"/>
-      <c r="E301" s="11"/>
-      <c r="G301" s="8"/>
-    </row>
-    <row r="302" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D301" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E301" s="11">
+        <v>3160</v>
+      </c>
+      <c r="F301" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G301" s="8">
+        <v>14</v>
+      </c>
+      <c r="H301" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I301" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>34</v>
+      </c>
+      <c r="B302" t="s">
+        <v>62</v>
+      </c>
       <c r="C302" s="11"/>
-      <c r="D302" s="11"/>
-      <c r="E302" s="11"/>
-      <c r="G302" s="8"/>
-    </row>
-    <row r="303" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D302" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E302" s="11">
+        <v>3370</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G302" s="8">
+        <v>14</v>
+      </c>
+      <c r="H302" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>28</v>
+      </c>
+      <c r="B303" t="s">
+        <v>62</v>
+      </c>
       <c r="C303" s="11"/>
-      <c r="D303" s="11"/>
-      <c r="E303" s="11"/>
-      <c r="G303" s="8"/>
-    </row>
-    <row r="304" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D303" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E303" s="11">
+        <v>3160</v>
+      </c>
+      <c r="F303" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G303" s="8">
+        <v>14</v>
+      </c>
+      <c r="H303" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>57</v>
+      </c>
+      <c r="B304" t="s">
+        <v>62</v>
+      </c>
       <c r="C304" s="11"/>
-      <c r="D304" s="11"/>
-      <c r="E304" s="11"/>
-      <c r="G304" s="8"/>
-    </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D304" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E304" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G304" s="8">
+        <v>14</v>
+      </c>
+      <c r="H304" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>13</v>
+      </c>
+      <c r="B305" t="s">
+        <v>62</v>
+      </c>
       <c r="C305" s="11"/>
-      <c r="D305" s="11"/>
-      <c r="E305" s="11"/>
-      <c r="G305" s="8"/>
-    </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D305" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E305" s="11">
+        <v>2900</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G305" s="8">
+        <v>14</v>
+      </c>
+      <c r="H305" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>112</v>
+      </c>
+      <c r="B306" t="s">
+        <v>62</v>
+      </c>
       <c r="C306" s="11"/>
-      <c r="D306" s="11"/>
-      <c r="E306" s="11"/>
-      <c r="G306" s="8"/>
-    </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D306" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E306" s="11">
+        <v>3210</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G306" s="8">
+        <v>14</v>
+      </c>
+      <c r="H306" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>25</v>
+      </c>
+      <c r="B307" t="s">
+        <v>62</v>
+      </c>
       <c r="C307" s="11"/>
-      <c r="D307" s="11"/>
-      <c r="E307" s="11"/>
-      <c r="G307" s="8"/>
-    </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D307" s="11">
+        <v>3000</v>
+      </c>
+      <c r="E307" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G307" s="8">
+        <v>14</v>
+      </c>
+      <c r="H307" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>21</v>
+      </c>
+      <c r="B308" t="s">
+        <v>62</v>
+      </c>
       <c r="C308" s="11"/>
-      <c r="D308" s="11"/>
-      <c r="E308" s="11"/>
-      <c r="G308" s="8"/>
-    </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D308" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E308" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G308" s="8">
+        <v>14</v>
+      </c>
+      <c r="H308" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>51</v>
+      </c>
+      <c r="B309" t="s">
+        <v>62</v>
+      </c>
       <c r="C309" s="11"/>
-      <c r="D309" s="11"/>
-      <c r="E309" s="11"/>
-      <c r="G309" s="8"/>
-    </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D309" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E309" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G309" s="8">
+        <v>14</v>
+      </c>
+      <c r="H309" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>53</v>
+      </c>
+      <c r="B310" t="s">
+        <v>62</v>
+      </c>
       <c r="C310" s="11"/>
-      <c r="D310" s="11"/>
-      <c r="E310" s="11"/>
-      <c r="G310" s="8"/>
-    </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D310" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E310" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G310" s="8">
+        <v>14</v>
+      </c>
+      <c r="H310" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>32</v>
+      </c>
+      <c r="B311" t="s">
+        <v>62</v>
+      </c>
       <c r="C311" s="11"/>
-      <c r="D311" s="11"/>
-      <c r="E311" s="11"/>
-      <c r="G311" s="8"/>
-    </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D311" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E311" s="11">
+        <v>3160</v>
+      </c>
+      <c r="F311" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G311" s="8">
+        <v>14</v>
+      </c>
+      <c r="H311" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>16</v>
+      </c>
+      <c r="B312" t="s">
+        <v>62</v>
+      </c>
       <c r="C312" s="11"/>
-      <c r="D312" s="11"/>
-      <c r="E312" s="11"/>
-      <c r="G312" s="8"/>
-    </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D312" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E312" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F312" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G312" s="8">
+        <v>14</v>
+      </c>
+      <c r="H312" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>151</v>
+      </c>
+      <c r="B313" t="s">
+        <v>62</v>
+      </c>
       <c r="C313" s="11"/>
-      <c r="D313" s="11"/>
-      <c r="E313" s="11"/>
-      <c r="G313" s="8"/>
-    </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D313" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E313" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F313" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G313" s="8">
+        <v>14</v>
+      </c>
+      <c r="H313" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>20</v>
+      </c>
+      <c r="B314" t="s">
+        <v>62</v>
+      </c>
       <c r="C314" s="11"/>
-      <c r="D314" s="11"/>
-      <c r="E314" s="11"/>
-      <c r="G314" s="8"/>
-    </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D314" s="11">
+        <v>2690</v>
+      </c>
+      <c r="E314" s="11">
+        <v>2790</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G314" s="8">
+        <v>14</v>
+      </c>
+      <c r="H314" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>114</v>
+      </c>
+      <c r="B315" t="s">
+        <v>62</v>
+      </c>
       <c r="C315" s="11"/>
-      <c r="D315" s="11"/>
-      <c r="E315" s="11"/>
-      <c r="G315" s="8"/>
-    </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D315" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E315" s="11">
+        <v>3420</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G315" s="8">
+        <v>14</v>
+      </c>
+      <c r="H315" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>55</v>
+      </c>
+      <c r="B316" t="s">
+        <v>62</v>
+      </c>
       <c r="C316" s="11"/>
-      <c r="D316" s="11"/>
-      <c r="E316" s="11"/>
-      <c r="G316" s="8"/>
-    </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D316" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E316" s="11">
+        <v>3110</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G316" s="8">
+        <v>14</v>
+      </c>
+      <c r="H316" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>31</v>
+      </c>
+      <c r="B317" t="s">
+        <v>62</v>
+      </c>
       <c r="C317" s="11"/>
-      <c r="D317" s="11"/>
-      <c r="E317" s="11"/>
-      <c r="G317" s="8"/>
-    </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D317" s="11">
+        <v>3110</v>
+      </c>
+      <c r="E317" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G317" s="8">
+        <v>14</v>
+      </c>
+      <c r="H317" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>54</v>
+      </c>
+      <c r="B318" t="s">
+        <v>62</v>
+      </c>
       <c r="C318" s="11"/>
-      <c r="D318" s="11"/>
-      <c r="E318" s="11"/>
-      <c r="G318" s="8"/>
-    </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D318" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E318" s="11">
+        <v>3160</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G318" s="8">
+        <v>14</v>
+      </c>
+      <c r="H318" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>26</v>
+      </c>
+      <c r="B319" t="s">
+        <v>62</v>
+      </c>
       <c r="C319" s="11"/>
-      <c r="D319" s="11"/>
-      <c r="E319" s="11"/>
-      <c r="G319" s="8"/>
-    </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D319" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E319" s="11">
+        <v>3270</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G319" s="8">
+        <v>14</v>
+      </c>
+      <c r="H319" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>49</v>
+      </c>
+      <c r="B320" t="s">
+        <v>62</v>
+      </c>
       <c r="C320" s="11"/>
-      <c r="D320" s="11"/>
-      <c r="E320" s="11"/>
-      <c r="G320" s="8"/>
-    </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C321" s="11"/>
-      <c r="D321" s="11"/>
-      <c r="E321" s="11"/>
-      <c r="G321" s="8"/>
-    </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D320" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E320" s="11">
+        <v>3320</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G320" s="8">
+        <v>14</v>
+      </c>
+      <c r="H320" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>5</v>
+      </c>
+      <c r="B321" t="s">
+        <v>15</v>
+      </c>
+      <c r="C321" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D321" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E321" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G321" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H321" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>4</v>
+      </c>
+      <c r="B322" t="s">
+        <v>15</v>
+      </c>
       <c r="C322" s="11"/>
-      <c r="D322" s="11"/>
-      <c r="E322" s="11"/>
-      <c r="G322" s="8"/>
-    </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D322" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E322" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F322" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G322" s="8">
+        <v>17</v>
+      </c>
+      <c r="H322" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>107</v>
+      </c>
+      <c r="B323" t="s">
+        <v>15</v>
+      </c>
       <c r="C323" s="11"/>
-      <c r="D323" s="11"/>
-      <c r="E323" s="11"/>
-      <c r="G323" s="8"/>
-    </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D323" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E323" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G323" s="8">
+        <v>17</v>
+      </c>
+      <c r="H323" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>52</v>
+      </c>
+      <c r="B324" t="s">
+        <v>15</v>
+      </c>
       <c r="C324" s="11"/>
-      <c r="D324" s="11"/>
-      <c r="E324" s="11"/>
-      <c r="G324" s="8"/>
-    </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D324" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E324" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G324" s="8">
+        <v>17</v>
+      </c>
+      <c r="H324" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>35</v>
+      </c>
+      <c r="B325" t="s">
+        <v>15</v>
+      </c>
       <c r="C325" s="11"/>
-      <c r="D325" s="11"/>
-      <c r="E325" s="11"/>
-      <c r="G325" s="8"/>
-    </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D325" s="11">
+        <v>2950</v>
+      </c>
+      <c r="E325" s="11">
+        <v>3440</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G325" s="8">
+        <v>17</v>
+      </c>
+      <c r="H325" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>24</v>
+      </c>
+      <c r="B326" t="s">
+        <v>15</v>
+      </c>
       <c r="C326" s="11"/>
-      <c r="D326" s="11"/>
-      <c r="E326" s="11"/>
-      <c r="G326" s="8"/>
-    </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D326" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E326" s="11">
+        <v>2980</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G326" s="8">
+        <v>17</v>
+      </c>
+      <c r="H326" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>50</v>
+      </c>
+      <c r="B327" t="s">
+        <v>15</v>
+      </c>
       <c r="C327" s="11"/>
-      <c r="D327" s="11"/>
-      <c r="E327" s="11"/>
-      <c r="G327" s="8"/>
-    </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D327" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E327" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F327" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G327" s="8">
+        <v>17</v>
+      </c>
+      <c r="H327" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>29</v>
+      </c>
+      <c r="B328" t="s">
+        <v>15</v>
+      </c>
       <c r="C328" s="11"/>
-      <c r="D328" s="11"/>
-      <c r="E328" s="11"/>
-      <c r="G328" s="8"/>
-    </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D328" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E328" s="11">
+        <v>2980</v>
+      </c>
+      <c r="F328" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G328" s="8">
+        <v>17</v>
+      </c>
+      <c r="H328" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>115</v>
+      </c>
+      <c r="B329" t="s">
+        <v>15</v>
+      </c>
       <c r="C329" s="11"/>
-      <c r="D329" s="11"/>
-      <c r="E329" s="11"/>
-      <c r="G329" s="8"/>
-    </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D329" s="11">
+        <v>2820</v>
+      </c>
+      <c r="E329" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G329" s="8">
+        <v>17</v>
+      </c>
+      <c r="H329" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I329" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="330" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>110</v>
+      </c>
+      <c r="B330" t="s">
+        <v>15</v>
+      </c>
       <c r="C330" s="11"/>
-      <c r="D330" s="11"/>
-      <c r="E330" s="11"/>
-      <c r="G330" s="8"/>
-    </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D330" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E330" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G330" s="8">
+        <v>17</v>
+      </c>
+      <c r="H330" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I330" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="331" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>27</v>
+      </c>
+      <c r="B331" t="s">
+        <v>15</v>
+      </c>
       <c r="C331" s="11"/>
-      <c r="D331" s="11"/>
-      <c r="E331" s="11"/>
-      <c r="G331" s="8"/>
-    </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D331" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E331" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F331" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G331" s="8">
+        <v>17</v>
+      </c>
+      <c r="H331" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I331" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="332" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>48</v>
+      </c>
+      <c r="B332" t="s">
+        <v>15</v>
+      </c>
       <c r="C332" s="11"/>
-      <c r="D332" s="11"/>
-      <c r="E332" s="11"/>
-      <c r="G332" s="8"/>
-    </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D332" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E332" s="11">
+        <v>3050</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G332" s="8">
+        <v>17</v>
+      </c>
+      <c r="H332" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I332" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="333" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>33</v>
+      </c>
+      <c r="B333" t="s">
+        <v>15</v>
+      </c>
       <c r="C333" s="11"/>
-      <c r="D333" s="11"/>
-      <c r="E333" s="11"/>
-      <c r="G333" s="8"/>
-    </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D333" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E333" s="11">
+        <v>3190</v>
+      </c>
+      <c r="F333" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G333" s="8">
+        <v>17</v>
+      </c>
+      <c r="H333" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I333" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="334" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>30</v>
+      </c>
+      <c r="B334" t="s">
+        <v>15</v>
+      </c>
       <c r="C334" s="11"/>
-      <c r="D334" s="11"/>
-      <c r="E334" s="11"/>
-      <c r="G334" s="8"/>
-    </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D334" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E334" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F334" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G334" s="8">
+        <v>17</v>
+      </c>
+      <c r="H334" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I334" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="335" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>146</v>
+      </c>
+      <c r="B335" t="s">
+        <v>15</v>
+      </c>
       <c r="C335" s="11"/>
-      <c r="D335" s="11"/>
-      <c r="E335" s="11"/>
-      <c r="G335" s="8"/>
-    </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D335" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E335" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F335" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G335" s="8">
+        <v>17</v>
+      </c>
+      <c r="H335" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I335" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="336" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>56</v>
+      </c>
+      <c r="B336" t="s">
+        <v>15</v>
+      </c>
       <c r="C336" s="11"/>
-      <c r="D336" s="11"/>
-      <c r="E336" s="11"/>
-      <c r="G336" s="8"/>
-    </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D336" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E336" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G336" s="8">
+        <v>17</v>
+      </c>
+      <c r="H336" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I336" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="337" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>34</v>
+      </c>
+      <c r="B337" t="s">
+        <v>15</v>
+      </c>
       <c r="C337" s="11"/>
-      <c r="D337" s="11"/>
-      <c r="E337" s="11"/>
-      <c r="G337" s="8"/>
-    </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D337" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E337" s="11">
+        <v>3300</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G337" s="8">
+        <v>17</v>
+      </c>
+      <c r="H337" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I337" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>28</v>
+      </c>
+      <c r="B338" t="s">
+        <v>15</v>
+      </c>
       <c r="C338" s="11"/>
-      <c r="D338" s="11"/>
-      <c r="E338" s="11"/>
-      <c r="G338" s="8"/>
-    </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D338" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E338" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G338" s="8">
+        <v>17</v>
+      </c>
+      <c r="H338" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>57</v>
+      </c>
+      <c r="B339" t="s">
+        <v>15</v>
+      </c>
       <c r="C339" s="11"/>
-      <c r="D339" s="11"/>
-      <c r="E339" s="11"/>
-      <c r="G339" s="8"/>
-    </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D339" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E339" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G339" s="8">
+        <v>17</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>13</v>
+      </c>
+      <c r="B340" t="s">
+        <v>15</v>
+      </c>
       <c r="C340" s="11"/>
-      <c r="D340" s="11"/>
-      <c r="E340" s="11"/>
-      <c r="G340" s="8"/>
-    </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D340" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E340" s="11">
+        <v>2980</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G340" s="8">
+        <v>17</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>112</v>
+      </c>
+      <c r="B341" t="s">
+        <v>15</v>
+      </c>
       <c r="C341" s="11"/>
-      <c r="D341" s="11"/>
-      <c r="E341" s="11"/>
-      <c r="G341" s="8"/>
-    </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D341" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E341" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G341" s="8">
+        <v>17</v>
+      </c>
+      <c r="H341" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I341" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>116</v>
+      </c>
+      <c r="B342" t="s">
+        <v>15</v>
+      </c>
       <c r="C342" s="11"/>
-      <c r="D342" s="11"/>
-      <c r="E342" s="11"/>
-      <c r="G342" s="8"/>
-    </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D342" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E342" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G342" s="8">
+        <v>17</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>25</v>
+      </c>
+      <c r="B343" t="s">
+        <v>15</v>
+      </c>
       <c r="C343" s="11"/>
-      <c r="D343" s="11"/>
-      <c r="E343" s="11"/>
-      <c r="G343" s="8"/>
-    </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D343" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E343" s="11">
+        <v>3150</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G343" s="8">
+        <v>17</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>19</v>
+      </c>
+      <c r="B344" t="s">
+        <v>15</v>
+      </c>
       <c r="C344" s="11"/>
-      <c r="D344" s="11"/>
-      <c r="E344" s="11"/>
-      <c r="G344" s="8"/>
-    </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D344" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E344" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G344" s="8">
+        <v>17</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>21</v>
+      </c>
+      <c r="B345" t="s">
+        <v>15</v>
+      </c>
       <c r="C345" s="11"/>
-      <c r="D345" s="11"/>
-      <c r="E345" s="11"/>
-      <c r="G345" s="8"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D345" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E345" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G345" s="8">
+        <v>17</v>
+      </c>
+      <c r="H345" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I345" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>51</v>
+      </c>
+      <c r="B346" t="s">
+        <v>15</v>
+      </c>
       <c r="C346" s="11"/>
-      <c r="D346" s="11"/>
-      <c r="E346" s="11"/>
-      <c r="G346" s="8"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D346" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E346" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G346" s="8">
+        <v>17</v>
+      </c>
+      <c r="H346" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>53</v>
+      </c>
+      <c r="B347" t="s">
+        <v>15</v>
+      </c>
       <c r="C347" s="11"/>
-      <c r="D347" s="11"/>
-      <c r="E347" s="11"/>
-      <c r="G347" s="8"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D347" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E347" s="11">
+        <v>3180</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G347" s="8">
+        <v>17</v>
+      </c>
+      <c r="H347" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I347" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>32</v>
+      </c>
+      <c r="B348" t="s">
+        <v>15</v>
+      </c>
       <c r="C348" s="11"/>
-      <c r="D348" s="11"/>
-      <c r="E348" s="11"/>
-      <c r="G348" s="8"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D348" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E348" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G348" s="8">
+        <v>17</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>16</v>
+      </c>
+      <c r="B349" t="s">
+        <v>15</v>
+      </c>
       <c r="C349" s="11"/>
-      <c r="D349" s="11"/>
-      <c r="E349" s="11"/>
-      <c r="G349" s="8"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C350" s="11"/>
-      <c r="D350" s="11"/>
-      <c r="E350" s="11"/>
-      <c r="G350" s="8"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D349" s="11">
+        <v>2720</v>
+      </c>
+      <c r="E349" s="11">
+        <v>2980</v>
+      </c>
+      <c r="F349" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G349" s="8">
+        <v>17</v>
+      </c>
+      <c r="H349" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I349" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>151</v>
+      </c>
+      <c r="B350" t="s">
+        <v>15</v>
+      </c>
+      <c r="C350" s="11">
+        <v>2670</v>
+      </c>
+      <c r="D350" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E350" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F350" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G350" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="H350" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>147</v>
+      </c>
+      <c r="B351" t="s">
+        <v>15</v>
+      </c>
       <c r="C351" s="11"/>
-      <c r="D351" s="11"/>
-      <c r="E351" s="11"/>
-      <c r="G351" s="8"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D351" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E351" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G351" s="8">
+        <v>17</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>20</v>
+      </c>
+      <c r="B352" t="s">
+        <v>15</v>
+      </c>
       <c r="C352" s="11"/>
-      <c r="D352" s="11"/>
-      <c r="E352" s="11"/>
-      <c r="G352" s="8"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D352" s="11">
+        <v>2670</v>
+      </c>
+      <c r="E352" s="11">
+        <v>2880</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G352" s="8">
+        <v>17</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>114</v>
+      </c>
+      <c r="B353" t="s">
+        <v>15</v>
+      </c>
       <c r="C353" s="11"/>
-      <c r="D353" s="11"/>
-      <c r="E353" s="11"/>
-      <c r="G353" s="8"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D353" s="11">
+        <v>2930</v>
+      </c>
+      <c r="E353" s="11">
+        <v>3360</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G353" s="8">
+        <v>17</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I353" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>55</v>
+      </c>
+      <c r="B354" t="s">
+        <v>15</v>
+      </c>
       <c r="C354" s="11"/>
-      <c r="D354" s="11"/>
-      <c r="E354" s="11"/>
-      <c r="G354" s="8"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D354" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E354" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G354" s="8">
+        <v>17</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>121</v>
+      </c>
+      <c r="B355" t="s">
+        <v>15</v>
+      </c>
       <c r="C355" s="11"/>
-      <c r="D355" s="11"/>
-      <c r="E355" s="11"/>
-      <c r="G355" s="8"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D355" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E355" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F355" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G355" s="8">
+        <v>17</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I355" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>54</v>
+      </c>
+      <c r="B356" t="s">
+        <v>15</v>
+      </c>
       <c r="C356" s="11"/>
-      <c r="D356" s="11"/>
-      <c r="E356" s="11"/>
-      <c r="G356" s="8"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D356" s="11">
+        <v>2770</v>
+      </c>
+      <c r="E356" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G356" s="8">
+        <v>17</v>
+      </c>
+      <c r="H356" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>26</v>
+      </c>
+      <c r="B357" t="s">
+        <v>15</v>
+      </c>
       <c r="C357" s="11"/>
-      <c r="D357" s="11"/>
-      <c r="E357" s="11"/>
-      <c r="G357" s="8"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D357" s="11">
+        <v>2780</v>
+      </c>
+      <c r="E357" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F357" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G357" s="8">
+        <v>17</v>
+      </c>
+      <c r="H357" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I357" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>49</v>
+      </c>
+      <c r="B358" t="s">
+        <v>15</v>
+      </c>
       <c r="C358" s="11"/>
-      <c r="D358" s="11"/>
-      <c r="E358" s="11"/>
-      <c r="G358" s="8"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D358" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E358" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G358" s="8">
+        <v>17</v>
+      </c>
+      <c r="H358" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>5</v>
+      </c>
+      <c r="B359" t="s">
+        <v>15</v>
+      </c>
       <c r="C359" s="11"/>
-      <c r="D359" s="11"/>
-      <c r="E359" s="11"/>
-      <c r="G359" s="8"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D359" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E359" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G359" s="8">
+        <v>18</v>
+      </c>
+      <c r="H359" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I359" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>4</v>
+      </c>
+      <c r="B360" t="s">
+        <v>15</v>
+      </c>
       <c r="C360" s="11"/>
-      <c r="D360" s="11"/>
-      <c r="E360" s="11"/>
-      <c r="G360" s="8"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D360" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E360" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G360" s="8">
+        <v>18</v>
+      </c>
+      <c r="H360" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>107</v>
+      </c>
+      <c r="B361" t="s">
+        <v>15</v>
+      </c>
       <c r="C361" s="11"/>
-      <c r="D361" s="11"/>
-      <c r="E361" s="11"/>
-      <c r="G361" s="8"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D361" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E361" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G361" s="8">
+        <v>18</v>
+      </c>
+      <c r="H361" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I361" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>108</v>
+      </c>
+      <c r="B362" t="s">
+        <v>15</v>
+      </c>
       <c r="C362" s="11"/>
-      <c r="D362" s="11"/>
-      <c r="E362" s="11"/>
-      <c r="G362" s="8"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D362" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E362" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G362" s="8">
+        <v>18</v>
+      </c>
+      <c r="H362" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>109</v>
+      </c>
+      <c r="B363" t="s">
+        <v>15</v>
+      </c>
       <c r="C363" s="11"/>
-      <c r="D363" s="11"/>
-      <c r="E363" s="11"/>
-      <c r="G363" s="8"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D363" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E363" s="11">
+        <v>2860</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G363" s="8">
+        <v>18</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I363" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>52</v>
+      </c>
+      <c r="B364" t="s">
+        <v>15</v>
+      </c>
       <c r="C364" s="11"/>
-      <c r="D364" s="11"/>
-      <c r="E364" s="11"/>
-      <c r="G364" s="8"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D364" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E364" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G364" s="8">
+        <v>18</v>
+      </c>
+      <c r="H364" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>35</v>
+      </c>
+      <c r="B365" t="s">
+        <v>15</v>
+      </c>
       <c r="C365" s="11"/>
-      <c r="D365" s="11"/>
-      <c r="E365" s="11"/>
-      <c r="G365" s="8"/>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D365" s="11">
+        <v>3170</v>
+      </c>
+      <c r="E365" s="11">
+        <v>3750</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G365" s="8">
+        <v>18</v>
+      </c>
+      <c r="H365" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I365" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>24</v>
+      </c>
+      <c r="B366" t="s">
+        <v>15</v>
+      </c>
       <c r="C366" s="11"/>
-      <c r="D366" s="11"/>
-      <c r="E366" s="11"/>
-      <c r="G366" s="8"/>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D366" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E366" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F366" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G366" s="8">
+        <v>18</v>
+      </c>
+      <c r="H366" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>50</v>
+      </c>
+      <c r="B367" t="s">
+        <v>15</v>
+      </c>
       <c r="C367" s="11"/>
-      <c r="D367" s="11"/>
-      <c r="E367" s="11"/>
-      <c r="G367" s="8"/>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D367" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E367" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G367" s="8">
+        <v>18</v>
+      </c>
+      <c r="H367" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I367" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>29</v>
+      </c>
+      <c r="B368" t="s">
+        <v>15</v>
+      </c>
       <c r="C368" s="11"/>
-      <c r="D368" s="11"/>
-      <c r="E368" s="11"/>
-      <c r="G368" s="8"/>
-    </row>
-    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D368" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E368" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G368" s="8">
+        <v>18</v>
+      </c>
+      <c r="H368" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I368" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>27</v>
+      </c>
+      <c r="B369" t="s">
+        <v>15</v>
+      </c>
       <c r="C369" s="11"/>
-      <c r="D369" s="11"/>
-      <c r="E369" s="11"/>
-      <c r="G369" s="8"/>
-    </row>
-    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D369" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E369" s="11">
+        <v>3020</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G369" s="8">
+        <v>18</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I369" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>48</v>
+      </c>
+      <c r="B370" t="s">
+        <v>15</v>
+      </c>
       <c r="C370" s="11"/>
-      <c r="D370" s="11"/>
-      <c r="E370" s="11"/>
-      <c r="G370" s="8"/>
-    </row>
-    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D370" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E370" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F370" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G370" s="8">
+        <v>18</v>
+      </c>
+      <c r="H370" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I370" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>33</v>
+      </c>
+      <c r="B371" t="s">
+        <v>15</v>
+      </c>
       <c r="C371" s="11"/>
-      <c r="D371" s="11"/>
-      <c r="E371" s="11"/>
-      <c r="G371" s="8"/>
-    </row>
-    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D371" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E371" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G371" s="8">
+        <v>18</v>
+      </c>
+      <c r="H371" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I371" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>111</v>
+      </c>
+      <c r="B372" t="s">
+        <v>15</v>
+      </c>
       <c r="C372" s="11"/>
-      <c r="D372" s="11"/>
-      <c r="E372" s="11"/>
-      <c r="G372" s="8"/>
-    </row>
-    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D372" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E372" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G372" s="8">
+        <v>18</v>
+      </c>
+      <c r="H372" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I372" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>30</v>
+      </c>
+      <c r="B373" t="s">
+        <v>15</v>
+      </c>
       <c r="C373" s="11"/>
-      <c r="D373" s="11"/>
-      <c r="E373" s="11"/>
-      <c r="G373" s="8"/>
-    </row>
-    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D373" s="11">
+        <v>3070</v>
+      </c>
+      <c r="E373" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G373" s="8">
+        <v>18</v>
+      </c>
+      <c r="H373" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I373" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>56</v>
+      </c>
+      <c r="B374" t="s">
+        <v>15</v>
+      </c>
       <c r="C374" s="11"/>
-      <c r="D374" s="11"/>
-      <c r="E374" s="11"/>
-      <c r="G374" s="8"/>
-    </row>
-    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D374" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E374" s="11">
+        <v>3120</v>
+      </c>
+      <c r="F374" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G374" s="8">
+        <v>18</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I374" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>28</v>
+      </c>
+      <c r="B375" t="s">
+        <v>15</v>
+      </c>
       <c r="C375" s="11"/>
-      <c r="D375" s="11"/>
-      <c r="E375" s="11"/>
-      <c r="G375" s="8"/>
-    </row>
-    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D375" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E375" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F375" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G375" s="8">
+        <v>18</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I375" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>57</v>
+      </c>
+      <c r="B376" t="s">
+        <v>15</v>
+      </c>
       <c r="C376" s="11"/>
-      <c r="D376" s="11"/>
-      <c r="E376" s="11"/>
-      <c r="G376" s="8"/>
-    </row>
-    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D376" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E376" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F376" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G376" s="8">
+        <v>18</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I376" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>13</v>
+      </c>
+      <c r="B377" t="s">
+        <v>15</v>
+      </c>
       <c r="C377" s="11"/>
-      <c r="D377" s="11"/>
-      <c r="E377" s="11"/>
-      <c r="G377" s="8"/>
-    </row>
-    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D377" s="11">
+        <v>2810</v>
+      </c>
+      <c r="E377" s="11">
+        <v>3020</v>
+      </c>
+      <c r="F377" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G377" s="8">
+        <v>18</v>
+      </c>
+      <c r="H377" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I377" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>112</v>
+      </c>
+      <c r="B378" t="s">
+        <v>15</v>
+      </c>
       <c r="C378" s="11"/>
-      <c r="D378" s="11"/>
-      <c r="E378" s="11"/>
-      <c r="G378" s="8"/>
-    </row>
-    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D378" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E378" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F378" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G378" s="8">
+        <v>18</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I378" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>25</v>
+      </c>
+      <c r="B379" t="s">
+        <v>15</v>
+      </c>
       <c r="C379" s="11"/>
-      <c r="D379" s="11"/>
-      <c r="E379" s="11"/>
-      <c r="G379" s="8"/>
-    </row>
-    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D379" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E379" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F379" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G379" s="8">
+        <v>18</v>
+      </c>
+      <c r="H379" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I379" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>19</v>
+      </c>
+      <c r="B380" t="s">
+        <v>15</v>
+      </c>
       <c r="C380" s="11"/>
-      <c r="D380" s="11"/>
-      <c r="E380" s="11"/>
-      <c r="G380" s="8"/>
-    </row>
-    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D380" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E380" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F380" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G380" s="8">
+        <v>18</v>
+      </c>
+      <c r="H380" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I380" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>21</v>
+      </c>
+      <c r="B381" t="s">
+        <v>15</v>
+      </c>
       <c r="C381" s="11"/>
-      <c r="D381" s="11"/>
-      <c r="E381" s="11"/>
-      <c r="G381" s="8"/>
-    </row>
-    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D381" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E381" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G381" s="8">
+        <v>18</v>
+      </c>
+      <c r="H381" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I381" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>51</v>
+      </c>
+      <c r="B382" t="s">
+        <v>15</v>
+      </c>
       <c r="C382" s="11"/>
-      <c r="D382" s="11"/>
-      <c r="E382" s="11"/>
-      <c r="G382" s="8"/>
-    </row>
-    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D382" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E382" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F382" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G382" s="8">
+        <v>18</v>
+      </c>
+      <c r="H382" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I382" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>53</v>
+      </c>
+      <c r="B383" t="s">
+        <v>15</v>
+      </c>
       <c r="C383" s="11"/>
-      <c r="D383" s="11"/>
-      <c r="E383" s="11"/>
-      <c r="G383" s="8"/>
-    </row>
-    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D383" s="11">
+        <v>3020</v>
+      </c>
+      <c r="E383" s="11">
+        <v>3440</v>
+      </c>
+      <c r="F383" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G383" s="8">
+        <v>18</v>
+      </c>
+      <c r="H383" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I383" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>113</v>
+      </c>
+      <c r="B384" t="s">
+        <v>15</v>
+      </c>
       <c r="C384" s="11"/>
-      <c r="D384" s="11"/>
-      <c r="E384" s="11"/>
-      <c r="G384" s="8"/>
-    </row>
-    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D384" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E384" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F384" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G384" s="8">
+        <v>18</v>
+      </c>
+      <c r="H384" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I384" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>16</v>
+      </c>
+      <c r="B385" t="s">
+        <v>15</v>
+      </c>
       <c r="C385" s="11"/>
-      <c r="D385" s="11"/>
-      <c r="E385" s="11"/>
-      <c r="G385" s="8"/>
-    </row>
-    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D385" s="11">
+        <v>2700</v>
+      </c>
+      <c r="E385" s="11">
+        <v>2810</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G385" s="8">
+        <v>18</v>
+      </c>
+      <c r="H385" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I385" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>151</v>
+      </c>
+      <c r="B386" t="s">
+        <v>15</v>
+      </c>
       <c r="C386" s="11"/>
-      <c r="D386" s="11"/>
-      <c r="E386" s="11"/>
-      <c r="G386" s="8"/>
-    </row>
-    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D386" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E386" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F386" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G386" s="8">
+        <v>18</v>
+      </c>
+      <c r="H386" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I386" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>20</v>
+      </c>
+      <c r="B387" t="s">
+        <v>15</v>
+      </c>
       <c r="C387" s="11"/>
-      <c r="D387" s="11"/>
-      <c r="E387" s="11"/>
-      <c r="G387" s="8"/>
-    </row>
-    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D387" s="11">
+        <v>2750</v>
+      </c>
+      <c r="E387" s="11">
+        <v>2910</v>
+      </c>
+      <c r="F387" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G387" s="8">
+        <v>18</v>
+      </c>
+      <c r="H387" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I387" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>55</v>
+      </c>
+      <c r="B388" t="s">
+        <v>15</v>
+      </c>
       <c r="C388" s="11"/>
-      <c r="D388" s="11"/>
-      <c r="E388" s="11"/>
-      <c r="G388" s="8"/>
-    </row>
-    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D388" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E388" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F388" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G388" s="8">
+        <v>18</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I388" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>31</v>
+      </c>
+      <c r="B389" t="s">
+        <v>15</v>
+      </c>
       <c r="C389" s="11"/>
-      <c r="D389" s="11"/>
-      <c r="E389" s="11"/>
-      <c r="G389" s="8"/>
-    </row>
-    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D389" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E389" s="11">
+        <v>3330</v>
+      </c>
+      <c r="F389" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G389" s="8">
+        <v>18</v>
+      </c>
+      <c r="H389" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I389" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>54</v>
+      </c>
+      <c r="B390" t="s">
+        <v>15</v>
+      </c>
       <c r="C390" s="11"/>
-      <c r="D390" s="11"/>
-      <c r="E390" s="11"/>
-      <c r="G390" s="8"/>
-    </row>
-    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D390" s="11">
+        <v>2910</v>
+      </c>
+      <c r="E390" s="11">
+        <v>3230</v>
+      </c>
+      <c r="F390" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G390" s="8">
+        <v>18</v>
+      </c>
+      <c r="H390" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I390" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>26</v>
+      </c>
+      <c r="B391" t="s">
+        <v>15</v>
+      </c>
       <c r="C391" s="11"/>
-      <c r="D391" s="11"/>
-      <c r="E391" s="11"/>
-      <c r="G391" s="8"/>
-    </row>
-    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D391" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E391" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F391" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G391" s="8">
+        <v>18</v>
+      </c>
+      <c r="H391" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I391" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>49</v>
+      </c>
+      <c r="B392" t="s">
+        <v>15</v>
+      </c>
       <c r="C392" s="11"/>
-      <c r="D392" s="11"/>
-      <c r="E392" s="11"/>
-      <c r="G392" s="8"/>
-    </row>
-    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C393" s="11"/>
-      <c r="D393" s="11"/>
-      <c r="E393" s="11"/>
-      <c r="G393" s="8"/>
-    </row>
-    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C394" s="11"/>
-      <c r="D394" s="11"/>
-      <c r="E394" s="11"/>
-      <c r="G394" s="8"/>
-    </row>
-    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D392" s="11">
+        <v>2860</v>
+      </c>
+      <c r="E392" s="11">
+        <v>3070</v>
+      </c>
+      <c r="F392" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G392" s="8">
+        <v>18</v>
+      </c>
+      <c r="H392" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="I392" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>5</v>
+      </c>
+      <c r="B393" t="s">
+        <v>15</v>
+      </c>
+      <c r="C393" s="11">
+        <v>2330</v>
+      </c>
+      <c r="D393" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E393" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F393" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G393" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H393" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I393" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>4</v>
+      </c>
+      <c r="B394" t="s">
+        <v>15</v>
+      </c>
+      <c r="C394" s="11">
+        <v>2330</v>
+      </c>
+      <c r="D394" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E394" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G394" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H394" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I394" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>107</v>
+      </c>
+      <c r="B395" t="s">
+        <v>15</v>
+      </c>
       <c r="C395" s="11"/>
-      <c r="D395" s="11"/>
-      <c r="E395" s="11"/>
-      <c r="G395" s="8"/>
-    </row>
-    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D395" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E395" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G395" s="8">
+        <v>19</v>
+      </c>
+      <c r="H395" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I395" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>108</v>
+      </c>
+      <c r="B396" t="s">
+        <v>15</v>
+      </c>
       <c r="C396" s="11"/>
-      <c r="D396" s="11"/>
-      <c r="E396" s="11"/>
-      <c r="G396" s="8"/>
-    </row>
-    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D396" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E396" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G396" s="8">
+        <v>19</v>
+      </c>
+      <c r="H396" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I396" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>109</v>
+      </c>
+      <c r="B397" t="s">
+        <v>15</v>
+      </c>
       <c r="C397" s="11"/>
-      <c r="D397" s="11"/>
-      <c r="E397" s="11"/>
-      <c r="G397" s="8"/>
-    </row>
-    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D397" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E397" s="11">
+        <v>3040</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G397" s="8">
+        <v>19</v>
+      </c>
+      <c r="H397" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I397" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>52</v>
+      </c>
+      <c r="B398" t="s">
+        <v>15</v>
+      </c>
       <c r="C398" s="11"/>
-      <c r="D398" s="11"/>
-      <c r="E398" s="11"/>
-      <c r="G398" s="8"/>
-    </row>
-    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D398" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E398" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F398" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G398" s="8">
+        <v>19</v>
+      </c>
+      <c r="H398" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I398" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>50</v>
+      </c>
+      <c r="B399" t="s">
+        <v>15</v>
+      </c>
       <c r="C399" s="11"/>
-      <c r="D399" s="11"/>
-      <c r="E399" s="11"/>
-      <c r="G399" s="8"/>
-    </row>
-    <row r="400" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D399" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E399" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F399" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G399" s="8">
+        <v>19</v>
+      </c>
+      <c r="H399" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I399" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>29</v>
+      </c>
+      <c r="B400" t="s">
+        <v>15</v>
+      </c>
       <c r="C400" s="11"/>
-      <c r="D400" s="11"/>
-      <c r="E400" s="11"/>
-      <c r="G400" s="8"/>
-    </row>
-    <row r="401" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D400" s="11">
+        <v>3150</v>
+      </c>
+      <c r="E400" s="11">
+        <v>3310</v>
+      </c>
+      <c r="F400" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G400" s="8">
+        <v>19</v>
+      </c>
+      <c r="H400" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I400" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>115</v>
+      </c>
+      <c r="B401" t="s">
+        <v>15</v>
+      </c>
       <c r="C401" s="11"/>
-      <c r="D401" s="11"/>
-      <c r="E401" s="11"/>
-      <c r="G401" s="8"/>
-    </row>
-    <row r="402" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D401" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E401" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G401" s="8">
+        <v>19</v>
+      </c>
+      <c r="H401" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I401" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>110</v>
+      </c>
+      <c r="B402" t="s">
+        <v>15</v>
+      </c>
       <c r="C402" s="11"/>
-      <c r="D402" s="11"/>
-      <c r="E402" s="11"/>
-      <c r="G402" s="8"/>
-    </row>
-    <row r="403" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D402" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E402" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G402" s="8">
+        <v>19</v>
+      </c>
+      <c r="H402" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I402" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>27</v>
+      </c>
+      <c r="B403" t="s">
+        <v>15</v>
+      </c>
       <c r="C403" s="11"/>
-      <c r="D403" s="11"/>
-      <c r="E403" s="11"/>
-      <c r="G403" s="8"/>
-    </row>
-    <row r="404" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D403" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E403" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G403" s="8">
+        <v>19</v>
+      </c>
+      <c r="H403" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I403" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>48</v>
+      </c>
+      <c r="B404" t="s">
+        <v>15</v>
+      </c>
       <c r="C404" s="11"/>
-      <c r="D404" s="11"/>
-      <c r="E404" s="11"/>
-      <c r="G404" s="8"/>
-    </row>
-    <row r="405" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D404" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E404" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G404" s="8">
+        <v>19</v>
+      </c>
+      <c r="H404" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I404" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>111</v>
+      </c>
+      <c r="B405" t="s">
+        <v>15</v>
+      </c>
       <c r="C405" s="11"/>
-      <c r="D405" s="11"/>
-      <c r="E405" s="11"/>
-      <c r="G405" s="8"/>
-    </row>
-    <row r="406" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D405" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E405" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G405" s="8">
+        <v>19</v>
+      </c>
+      <c r="H405" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I405" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>28</v>
+      </c>
+      <c r="B406" t="s">
+        <v>15</v>
+      </c>
       <c r="C406" s="11"/>
-      <c r="D406" s="11"/>
-      <c r="E406" s="11"/>
-      <c r="G406" s="8"/>
-    </row>
-    <row r="407" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D406" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E406" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G406" s="8">
+        <v>19</v>
+      </c>
+      <c r="H406" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I406" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>112</v>
+      </c>
+      <c r="B407" t="s">
+        <v>15</v>
+      </c>
       <c r="C407" s="11"/>
-      <c r="D407" s="11"/>
-      <c r="E407" s="11"/>
-      <c r="G407" s="8"/>
-    </row>
-    <row r="408" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D407" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E407" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G407" s="8">
+        <v>19</v>
+      </c>
+      <c r="H407" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I407" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>116</v>
+      </c>
+      <c r="B408" t="s">
+        <v>15</v>
+      </c>
       <c r="C408" s="11"/>
-      <c r="D408" s="11"/>
-      <c r="E408" s="11"/>
-      <c r="G408" s="8"/>
-    </row>
-    <row r="409" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D408" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E408" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G408" s="8">
+        <v>19</v>
+      </c>
+      <c r="H408" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I408" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>25</v>
+      </c>
+      <c r="B409" t="s">
+        <v>15</v>
+      </c>
       <c r="C409" s="11"/>
-      <c r="D409" s="11"/>
-      <c r="E409" s="11"/>
-      <c r="G409" s="8"/>
-    </row>
-    <row r="410" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C410" s="11"/>
-      <c r="D410" s="11"/>
-      <c r="E410" s="11"/>
-      <c r="G410" s="8"/>
-    </row>
-    <row r="411" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C411" s="11"/>
-      <c r="D411" s="11"/>
-      <c r="E411" s="11"/>
-      <c r="G411" s="8"/>
-    </row>
-    <row r="412" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D409" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E409" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G409" s="8">
+        <v>19</v>
+      </c>
+      <c r="H409" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I409" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>19</v>
+      </c>
+      <c r="B410" t="s">
+        <v>15</v>
+      </c>
+      <c r="C410" s="11">
+        <v>2330</v>
+      </c>
+      <c r="D410" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E410" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F410" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G410" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H410" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I410" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>21</v>
+      </c>
+      <c r="B411" t="s">
+        <v>15</v>
+      </c>
+      <c r="C411" s="11">
+        <v>2330</v>
+      </c>
+      <c r="D411" s="11">
+        <v>2830</v>
+      </c>
+      <c r="E411" s="11">
+        <v>2890</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G411" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="H411" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I411" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>51</v>
+      </c>
+      <c r="B412" t="s">
+        <v>15</v>
+      </c>
       <c r="C412" s="11"/>
-      <c r="D412" s="11"/>
-      <c r="E412" s="11"/>
-      <c r="G412" s="8"/>
-    </row>
-    <row r="413" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D412" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E412" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G412" s="8">
+        <v>19</v>
+      </c>
+      <c r="H412" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I412" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>113</v>
+      </c>
+      <c r="B413" t="s">
+        <v>15</v>
+      </c>
       <c r="C413" s="11"/>
-      <c r="D413" s="11"/>
-      <c r="E413" s="11"/>
-      <c r="G413" s="8"/>
-    </row>
-    <row r="414" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D413" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E413" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G413" s="8">
+        <v>19</v>
+      </c>
+      <c r="H413" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I413" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>16</v>
+      </c>
+      <c r="B414" t="s">
+        <v>15</v>
+      </c>
       <c r="C414" s="11"/>
-      <c r="D414" s="11"/>
-      <c r="E414" s="11"/>
-      <c r="G414" s="8"/>
-    </row>
-    <row r="415" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D414" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E414" s="11">
+        <v>3200</v>
+      </c>
+      <c r="F414" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G414" s="8">
+        <v>19</v>
+      </c>
+      <c r="H414" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I414" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>26</v>
+      </c>
+      <c r="B415" t="s">
+        <v>15</v>
+      </c>
       <c r="C415" s="11"/>
-      <c r="D415" s="11"/>
-      <c r="E415" s="11"/>
-      <c r="G415" s="8"/>
-    </row>
-    <row r="416" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D415" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E415" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F415" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G415" s="8">
+        <v>19</v>
+      </c>
+      <c r="H415" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I415" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>49</v>
+      </c>
+      <c r="B416" t="s">
+        <v>15</v>
+      </c>
       <c r="C416" s="11"/>
-      <c r="D416" s="11"/>
-      <c r="E416" s="11"/>
-      <c r="G416" s="8"/>
-    </row>
-    <row r="417" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D416" s="11">
+        <v>2940</v>
+      </c>
+      <c r="E416" s="11">
+        <v>3100</v>
+      </c>
+      <c r="F416" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G416" s="8">
+        <v>19</v>
+      </c>
+      <c r="H416" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="I416" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>5</v>
+      </c>
+      <c r="B417" t="s">
+        <v>15</v>
+      </c>
       <c r="C417" s="11"/>
-      <c r="D417" s="11"/>
-      <c r="E417" s="11"/>
-      <c r="G417" s="8"/>
-    </row>
-    <row r="418" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D417" s="11">
+        <v>2610</v>
+      </c>
+      <c r="E417" s="11">
+        <v>2820</v>
+      </c>
+      <c r="F417" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G417" s="8">
+        <v>18</v>
+      </c>
+      <c r="H417" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I417" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>4</v>
+      </c>
+      <c r="B418" t="s">
+        <v>15</v>
+      </c>
       <c r="C418" s="11"/>
-      <c r="D418" s="11"/>
-      <c r="E418" s="11"/>
-      <c r="G418" s="8"/>
-    </row>
-    <row r="419" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D418" s="11">
+        <v>2610</v>
+      </c>
+      <c r="E418" s="11">
+        <v>2820</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G418" s="8">
+        <v>18</v>
+      </c>
+      <c r="H418" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I418" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>13</v>
+      </c>
+      <c r="B419" t="s">
+        <v>15</v>
+      </c>
       <c r="C419" s="11"/>
-      <c r="D419" s="11"/>
-      <c r="E419" s="11"/>
-      <c r="G419" s="8"/>
-    </row>
-    <row r="420" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D419" s="11">
+        <v>2660</v>
+      </c>
+      <c r="E419" s="11">
+        <v>2870</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G419" s="8">
+        <v>18</v>
+      </c>
+      <c r="H419" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I419" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>151</v>
+      </c>
+      <c r="B420" t="s">
+        <v>15</v>
+      </c>
       <c r="C420" s="11"/>
-      <c r="D420" s="11"/>
-      <c r="E420" s="11"/>
-      <c r="G420" s="8"/>
-    </row>
-    <row r="421" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D420" s="11">
+        <v>2610</v>
+      </c>
+      <c r="E420" s="11">
+        <v>2820</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G420" s="8">
+        <v>18</v>
+      </c>
+      <c r="H420" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I420" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>30</v>
+      </c>
+      <c r="B421" t="s">
+        <v>15</v>
+      </c>
       <c r="C421" s="11"/>
-      <c r="D421" s="11"/>
-      <c r="E421" s="11"/>
-      <c r="G421" s="8"/>
-    </row>
-    <row r="422" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D421" s="11">
+        <v>2710</v>
+      </c>
+      <c r="E421" s="11">
+        <v>3030</v>
+      </c>
+      <c r="F421" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G421" s="8">
+        <v>18</v>
+      </c>
+      <c r="H421" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I421" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>24</v>
+      </c>
+      <c r="B422" t="s">
+        <v>15</v>
+      </c>
       <c r="C422" s="11"/>
-      <c r="D422" s="11"/>
-      <c r="E422" s="11"/>
-      <c r="G422" s="8"/>
-    </row>
-    <row r="423" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="D422" s="11">
+        <v>2710</v>
+      </c>
+      <c r="E422" s="11">
+        <v>2920</v>
+      </c>
+      <c r="F422" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G422" s="8">
+        <v>18</v>
+      </c>
+      <c r="H422" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="I422" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C423" s="11"/>
       <c r="D423" s="11"/>
       <c r="E423" s="11"/>
       <c r="G423" s="8"/>
     </row>
-    <row r="424" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C424" s="11"/>
       <c r="D424" s="11"/>
       <c r="E424" s="11"/>
       <c r="G424" s="8"/>
     </row>
-    <row r="425" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C425" s="11"/>
       <c r="D425" s="11"/>
       <c r="E425" s="11"/>
       <c r="G425" s="8"/>
     </row>
-    <row r="426" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C426" s="11"/>
       <c r="D426" s="11"/>
       <c r="E426" s="11"/>
       <c r="G426" s="8"/>
     </row>
-    <row r="427" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C427" s="11"/>
       <c r="D427" s="11"/>
       <c r="E427" s="11"/>
       <c r="G427" s="8"/>
     </row>
-    <row r="428" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C428" s="11"/>
       <c r="D428" s="11"/>
       <c r="E428" s="11"/>
       <c r="G428" s="8"/>
     </row>
-    <row r="429" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C429" s="11"/>
       <c r="D429" s="11"/>
       <c r="E429" s="11"/>
       <c r="G429" s="8"/>
     </row>
-    <row r="430" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C430" s="11"/>
       <c r="D430" s="11"/>
       <c r="E430" s="11"/>
       <c r="G430" s="8"/>
     </row>
-    <row r="431" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C431" s="11"/>
       <c r="D431" s="11"/>
       <c r="E431" s="11"/>
       <c r="G431" s="8"/>
     </row>
-    <row r="432" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C432" s="11"/>
       <c r="D432" s="11"/>
       <c r="E432" s="11"/>
@@ -12678,451 +15552,151 @@
       <c r="G935" s="8"/>
     </row>
     <row r="936" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C936" s="11"/>
-      <c r="D936" s="11"/>
-      <c r="E936" s="11"/>
       <c r="G936" s="8"/>
     </row>
     <row r="937" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C937" s="11"/>
-      <c r="D937" s="11"/>
-      <c r="E937" s="11"/>
       <c r="G937" s="8"/>
     </row>
     <row r="938" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C938" s="11"/>
-      <c r="D938" s="11"/>
-      <c r="E938" s="11"/>
       <c r="G938" s="8"/>
     </row>
     <row r="939" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C939" s="11"/>
-      <c r="D939" s="11"/>
-      <c r="E939" s="11"/>
       <c r="G939" s="8"/>
     </row>
     <row r="940" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C940" s="11"/>
-      <c r="D940" s="11"/>
-      <c r="E940" s="11"/>
       <c r="G940" s="8"/>
     </row>
     <row r="941" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C941" s="11"/>
-      <c r="D941" s="11"/>
-      <c r="E941" s="11"/>
       <c r="G941" s="8"/>
     </row>
     <row r="942" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C942" s="11"/>
-      <c r="D942" s="11"/>
-      <c r="E942" s="11"/>
       <c r="G942" s="8"/>
     </row>
     <row r="943" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C943" s="11"/>
-      <c r="D943" s="11"/>
-      <c r="E943" s="11"/>
       <c r="G943" s="8"/>
     </row>
     <row r="944" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C944" s="11"/>
-      <c r="D944" s="11"/>
-      <c r="E944" s="11"/>
       <c r="G944" s="8"/>
     </row>
-    <row r="945" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C945" s="11"/>
-      <c r="D945" s="11"/>
-      <c r="E945" s="11"/>
+    <row r="945" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G945" s="8"/>
     </row>
-    <row r="946" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C946" s="11"/>
-      <c r="D946" s="11"/>
-      <c r="E946" s="11"/>
+    <row r="946" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G946" s="8"/>
     </row>
-    <row r="947" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C947" s="11"/>
-      <c r="D947" s="11"/>
-      <c r="E947" s="11"/>
+    <row r="947" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G947" s="8"/>
     </row>
-    <row r="948" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C948" s="11"/>
-      <c r="D948" s="11"/>
-      <c r="E948" s="11"/>
+    <row r="948" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G948" s="8"/>
     </row>
-    <row r="949" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C949" s="11"/>
-      <c r="D949" s="11"/>
-      <c r="E949" s="11"/>
+    <row r="949" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G949" s="8"/>
     </row>
-    <row r="950" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C950" s="11"/>
-      <c r="D950" s="11"/>
-      <c r="E950" s="11"/>
+    <row r="950" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G950" s="8"/>
     </row>
-    <row r="951" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C951" s="11"/>
-      <c r="D951" s="11"/>
-      <c r="E951" s="11"/>
+    <row r="951" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G951" s="8"/>
     </row>
-    <row r="952" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C952" s="11"/>
-      <c r="D952" s="11"/>
-      <c r="E952" s="11"/>
+    <row r="952" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G952" s="8"/>
     </row>
-    <row r="953" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C953" s="11"/>
-      <c r="D953" s="11"/>
-      <c r="E953" s="11"/>
+    <row r="953" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G953" s="8"/>
     </row>
-    <row r="954" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C954" s="11"/>
-      <c r="D954" s="11"/>
-      <c r="E954" s="11"/>
+    <row r="954" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G954" s="8"/>
     </row>
-    <row r="955" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C955" s="11"/>
-      <c r="D955" s="11"/>
-      <c r="E955" s="11"/>
+    <row r="955" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G955" s="8"/>
     </row>
-    <row r="956" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C956" s="11"/>
-      <c r="D956" s="11"/>
-      <c r="E956" s="11"/>
+    <row r="956" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G956" s="8"/>
     </row>
-    <row r="957" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C957" s="11"/>
-      <c r="D957" s="11"/>
-      <c r="E957" s="11"/>
+    <row r="957" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G957" s="8"/>
     </row>
-    <row r="958" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C958" s="11"/>
-      <c r="D958" s="11"/>
-      <c r="E958" s="11"/>
+    <row r="958" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G958" s="8"/>
     </row>
-    <row r="959" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C959" s="11"/>
-      <c r="D959" s="11"/>
-      <c r="E959" s="11"/>
+    <row r="959" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G959" s="8"/>
     </row>
-    <row r="960" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C960" s="11"/>
-      <c r="D960" s="11"/>
-      <c r="E960" s="11"/>
+    <row r="960" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G960" s="8"/>
     </row>
-    <row r="961" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C961" s="11"/>
-      <c r="D961" s="11"/>
-      <c r="E961" s="11"/>
+    <row r="961" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G961" s="8"/>
     </row>
-    <row r="962" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C962" s="11"/>
-      <c r="D962" s="11"/>
-      <c r="E962" s="11"/>
+    <row r="962" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G962" s="8"/>
     </row>
-    <row r="963" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C963" s="11"/>
-      <c r="D963" s="11"/>
-      <c r="E963" s="11"/>
+    <row r="963" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G963" s="8"/>
     </row>
-    <row r="964" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C964" s="11"/>
-      <c r="D964" s="11"/>
-      <c r="E964" s="11"/>
+    <row r="964" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G964" s="8"/>
     </row>
-    <row r="965" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C965" s="11"/>
-      <c r="D965" s="11"/>
-      <c r="E965" s="11"/>
+    <row r="965" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G965" s="8"/>
     </row>
-    <row r="966" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C966" s="11"/>
-      <c r="D966" s="11"/>
-      <c r="E966" s="11"/>
+    <row r="966" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G966" s="8"/>
     </row>
-    <row r="967" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C967" s="11"/>
-      <c r="D967" s="11"/>
-      <c r="E967" s="11"/>
+    <row r="967" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G967" s="8"/>
     </row>
-    <row r="968" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C968" s="11"/>
-      <c r="D968" s="11"/>
-      <c r="E968" s="11"/>
+    <row r="968" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G968" s="8"/>
     </row>
-    <row r="969" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C969" s="11"/>
-      <c r="D969" s="11"/>
-      <c r="E969" s="11"/>
+    <row r="969" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G969" s="8"/>
     </row>
-    <row r="970" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C970" s="11"/>
-      <c r="D970" s="11"/>
-      <c r="E970" s="11"/>
+    <row r="970" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G970" s="8"/>
     </row>
-    <row r="971" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C971" s="11"/>
-      <c r="D971" s="11"/>
-      <c r="E971" s="11"/>
+    <row r="971" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G971" s="8"/>
     </row>
-    <row r="972" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C972" s="11"/>
-      <c r="D972" s="11"/>
-      <c r="E972" s="11"/>
+    <row r="972" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G972" s="8"/>
     </row>
-    <row r="973" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C973" s="11"/>
-      <c r="D973" s="11"/>
-      <c r="E973" s="11"/>
+    <row r="973" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G973" s="8"/>
     </row>
-    <row r="974" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C974" s="11"/>
-      <c r="D974" s="11"/>
-      <c r="E974" s="11"/>
+    <row r="974" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G974" s="8"/>
     </row>
-    <row r="975" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C975" s="11"/>
-      <c r="D975" s="11"/>
-      <c r="E975" s="11"/>
+    <row r="975" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G975" s="8"/>
     </row>
-    <row r="976" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C976" s="11"/>
-      <c r="D976" s="11"/>
-      <c r="E976" s="11"/>
+    <row r="976" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G976" s="8"/>
     </row>
-    <row r="977" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C977" s="11"/>
-      <c r="D977" s="11"/>
-      <c r="E977" s="11"/>
+    <row r="977" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G977" s="8"/>
     </row>
-    <row r="978" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C978" s="11"/>
-      <c r="D978" s="11"/>
-      <c r="E978" s="11"/>
+    <row r="978" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G978" s="8"/>
     </row>
-    <row r="979" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C979" s="11"/>
-      <c r="D979" s="11"/>
-      <c r="E979" s="11"/>
+    <row r="979" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G979" s="8"/>
     </row>
-    <row r="980" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C980" s="11"/>
-      <c r="D980" s="11"/>
-      <c r="E980" s="11"/>
+    <row r="980" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G980" s="8"/>
     </row>
-    <row r="981" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C981" s="11"/>
-      <c r="D981" s="11"/>
-      <c r="E981" s="11"/>
+    <row r="981" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G981" s="8"/>
     </row>
-    <row r="982" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C982" s="11"/>
-      <c r="D982" s="11"/>
-      <c r="E982" s="11"/>
+    <row r="982" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G982" s="8"/>
     </row>
-    <row r="983" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C983" s="11"/>
-      <c r="D983" s="11"/>
-      <c r="E983" s="11"/>
+    <row r="983" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G983" s="8"/>
     </row>
-    <row r="984" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C984" s="11"/>
-      <c r="D984" s="11"/>
-      <c r="E984" s="11"/>
+    <row r="984" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G984" s="8"/>
-    </row>
-    <row r="985" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C985" s="11"/>
-      <c r="D985" s="11"/>
-      <c r="E985" s="11"/>
-      <c r="G985" s="8"/>
-    </row>
-    <row r="986" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G986" s="8"/>
-    </row>
-    <row r="987" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G987" s="8"/>
-    </row>
-    <row r="988" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G988" s="8"/>
-    </row>
-    <row r="989" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G989" s="8"/>
-    </row>
-    <row r="990" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G990" s="8"/>
-    </row>
-    <row r="991" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G991" s="8"/>
-    </row>
-    <row r="992" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G992" s="8"/>
-    </row>
-    <row r="993" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G993" s="8"/>
-    </row>
-    <row r="994" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G994" s="8"/>
-    </row>
-    <row r="995" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G995" s="8"/>
-    </row>
-    <row r="996" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G996" s="8"/>
-    </row>
-    <row r="997" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G997" s="8"/>
-    </row>
-    <row r="998" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G998" s="8"/>
-    </row>
-    <row r="999" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G999" s="8"/>
-    </row>
-    <row r="1000" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1000" s="8"/>
-    </row>
-    <row r="1001" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1001" s="8"/>
-    </row>
-    <row r="1002" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1002" s="8"/>
-    </row>
-    <row r="1003" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1003" s="8"/>
-    </row>
-    <row r="1004" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1004" s="8"/>
-    </row>
-    <row r="1005" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1005" s="8"/>
-    </row>
-    <row r="1006" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1006" s="8"/>
-    </row>
-    <row r="1007" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1007" s="8"/>
-    </row>
-    <row r="1008" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1008" s="8"/>
-    </row>
-    <row r="1009" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1009" s="8"/>
-    </row>
-    <row r="1010" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1010" s="8"/>
-    </row>
-    <row r="1011" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1011" s="8"/>
-    </row>
-    <row r="1012" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1012" s="8"/>
-    </row>
-    <row r="1013" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1013" s="8"/>
-    </row>
-    <row r="1014" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1014" s="8"/>
-    </row>
-    <row r="1015" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1015" s="8"/>
-    </row>
-    <row r="1016" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1016" s="8"/>
-    </row>
-    <row r="1017" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1017" s="8"/>
-    </row>
-    <row r="1018" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1018" s="8"/>
-    </row>
-    <row r="1019" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1019" s="8"/>
-    </row>
-    <row r="1020" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1020" s="8"/>
-    </row>
-    <row r="1021" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1021" s="8"/>
-    </row>
-    <row r="1022" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1022" s="8"/>
-    </row>
-    <row r="1023" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1023" s="8"/>
-    </row>
-    <row r="1024" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1024" s="8"/>
-    </row>
-    <row r="1025" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1025" s="8"/>
-    </row>
-    <row r="1026" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1026" s="8"/>
-    </row>
-    <row r="1027" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1027" s="8"/>
-    </row>
-    <row r="1028" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1028" s="8"/>
-    </row>
-    <row r="1029" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1029" s="8"/>
-    </row>
-    <row r="1030" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1030" s="8"/>
-    </row>
-    <row r="1031" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1031" s="8"/>
-    </row>
-    <row r="1032" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1032" s="8"/>
-    </row>
-    <row r="1033" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1033" s="8"/>
-    </row>
-    <row r="1034" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G1034" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I286" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="89" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE7481F8-E578-4902-8AB9-EDDCB025757A}"/>
+  <xr:revisionPtr revIDLastSave="90" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{709B5509-3F25-4771-9D4A-88258AE0D013}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2617,19 +2617,19 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="A59" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B59" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59">
+      <c r="B59" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="11">
         <v>2620</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="11">
         <v>2880</v>
       </c>
-      <c r="E59">
+      <c r="E59" s="11">
         <v>3090</v>
       </c>
       <c r="F59" s="7" t="s">
@@ -2646,19 +2646,19 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="A60" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B60" t="s">
-        <v>15</v>
-      </c>
-      <c r="C60">
+      <c r="B60" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="11">
         <v>2620</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="11">
         <v>2880</v>
       </c>
-      <c r="E60">
+      <c r="E60" s="11">
         <v>3090</v>
       </c>
       <c r="F60" s="7" t="s">
@@ -2675,19 +2675,19 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="A61" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B61" t="s">
-        <v>15</v>
-      </c>
-      <c r="C61">
+      <c r="B61" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" s="11">
         <v>2620</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="11">
         <v>2880</v>
       </c>
-      <c r="E61">
+      <c r="E61" s="11">
         <v>3090</v>
       </c>
       <c r="F61" s="7" t="s">
@@ -2704,19 +2704,19 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
+      <c r="A62" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B62" t="s">
-        <v>15</v>
-      </c>
-      <c r="C62">
+      <c r="B62" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C62" s="11">
         <v>2620</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="11">
         <v>2880</v>
       </c>
-      <c r="E62">
+      <c r="E62" s="11">
         <v>3090</v>
       </c>
       <c r="F62" s="7" t="s">
@@ -2733,19 +2733,19 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
+      <c r="A63" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B63" t="s">
-        <v>15</v>
-      </c>
-      <c r="C63">
+      <c r="B63" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C63" s="11">
         <v>2620</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="11">
         <v>2880</v>
       </c>
-      <c r="E63">
+      <c r="E63" s="11">
         <v>3090</v>
       </c>
       <c r="F63" s="7" t="s">
@@ -2762,19 +2762,19 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
+      <c r="A64" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B64" t="s">
-        <v>15</v>
-      </c>
-      <c r="C64">
+      <c r="B64" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C64" s="11">
         <v>2620</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="11">
         <v>2880</v>
       </c>
-      <c r="E64">
+      <c r="E64" s="11">
         <v>3090</v>
       </c>
       <c r="F64" s="7" t="s">
@@ -2791,19 +2791,19 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="A65" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65">
+      <c r="B65" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="11">
         <v>2620</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="11">
         <v>2880</v>
       </c>
-      <c r="E65">
+      <c r="E65" s="11">
         <v>3090</v>
       </c>
       <c r="F65" s="7" t="s">
@@ -2820,19 +2820,19 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
+      <c r="A66" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B66" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66">
+      <c r="B66" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="11">
         <v>2830</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="11">
         <v>2990</v>
       </c>
-      <c r="E66">
+      <c r="E66" s="11">
         <v>3300</v>
       </c>
       <c r="F66" s="7" t="s">
@@ -2849,16 +2849,17 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
+      <c r="A67" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B67" t="s">
-        <v>15</v>
-      </c>
-      <c r="D67">
+      <c r="B67" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11">
         <v>2990</v>
       </c>
-      <c r="E67">
+      <c r="E67" s="11">
         <v>3300</v>
       </c>
       <c r="F67" s="7" t="s">
@@ -2875,19 +2876,19 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
+      <c r="A68" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B68" t="s">
-        <v>15</v>
-      </c>
-      <c r="C68">
+      <c r="B68" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C68" s="11">
         <v>2830</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="11">
         <v>2930</v>
       </c>
-      <c r="E68">
+      <c r="E68" s="11">
         <v>3200</v>
       </c>
       <c r="F68" s="7" t="s">
@@ -2904,19 +2905,19 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="A69" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B69" t="s">
-        <v>15</v>
-      </c>
-      <c r="C69">
+      <c r="B69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="11">
         <v>2830</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="11">
         <v>2930</v>
       </c>
-      <c r="E69">
+      <c r="E69" s="11">
         <v>3200</v>
       </c>
       <c r="F69" s="7" t="s">
@@ -2933,19 +2934,19 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="A70" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B70" t="s">
-        <v>15</v>
-      </c>
-      <c r="C70">
+      <c r="B70" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" s="11">
         <v>2830</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="11">
         <v>2930</v>
       </c>
-      <c r="E70">
+      <c r="E70" s="11">
         <v>3200</v>
       </c>
       <c r="F70" s="7" t="s">
@@ -2962,19 +2963,19 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
+      <c r="A71" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B71" t="s">
-        <v>15</v>
-      </c>
-      <c r="C71">
+      <c r="B71" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71" s="11">
         <v>2830</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="11">
         <v>2930</v>
       </c>
-      <c r="E71">
+      <c r="E71" s="11">
         <v>3200</v>
       </c>
       <c r="F71" s="7" t="s">
@@ -2991,19 +2992,19 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="A72" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B72" t="s">
-        <v>15</v>
-      </c>
-      <c r="C72">
+      <c r="B72" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C72" s="11">
         <v>2830</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="11">
         <v>2930</v>
       </c>
-      <c r="E72">
+      <c r="E72" s="11">
         <v>3200</v>
       </c>
       <c r="F72" s="7" t="s">
@@ -3020,19 +3021,19 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
+      <c r="A73" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B73" t="s">
-        <v>15</v>
-      </c>
-      <c r="C73">
+      <c r="B73" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="11">
         <v>2830</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="11">
         <v>2930</v>
       </c>
-      <c r="E73">
+      <c r="E73" s="11">
         <v>3200</v>
       </c>
       <c r="F73" s="7" t="s">
@@ -3049,19 +3050,19 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
+      <c r="A74" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B74" t="s">
-        <v>15</v>
-      </c>
-      <c r="C74">
+      <c r="B74" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="11">
         <v>2830</v>
       </c>
-      <c r="D74">
+      <c r="D74" s="11">
         <v>2930</v>
       </c>
-      <c r="E74">
+      <c r="E74" s="11">
         <v>3200</v>
       </c>
       <c r="F74" s="7" t="s">
@@ -3078,19 +3079,19 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+      <c r="A75" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B75" t="s">
-        <v>15</v>
-      </c>
-      <c r="C75">
+      <c r="B75" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="11">
         <v>2830</v>
       </c>
-      <c r="D75">
+      <c r="D75" s="11">
         <v>2930</v>
       </c>
-      <c r="E75">
+      <c r="E75" s="11">
         <v>3200</v>
       </c>
       <c r="F75" s="7" t="s">
@@ -3107,19 +3108,19 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="A76" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B76" t="s">
-        <v>15</v>
-      </c>
-      <c r="C76">
+      <c r="B76" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="11">
         <v>2830</v>
       </c>
-      <c r="D76">
+      <c r="D76" s="11">
         <v>2930</v>
       </c>
-      <c r="E76">
+      <c r="E76" s="11">
         <v>3200</v>
       </c>
       <c r="F76" s="7" t="s">
@@ -3136,16 +3137,17 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
+      <c r="A77" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B77" t="s">
-        <v>15</v>
-      </c>
-      <c r="D77">
+      <c r="B77" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="7"/>
+      <c r="D77" s="11">
         <v>2990</v>
       </c>
-      <c r="E77">
+      <c r="E77" s="11">
         <v>3300</v>
       </c>
       <c r="F77" s="7" t="s">
@@ -3162,16 +3164,17 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="A78" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B78" t="s">
-        <v>15</v>
-      </c>
-      <c r="D78">
+      <c r="B78" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C78" s="7"/>
+      <c r="D78" s="11">
         <v>2990</v>
       </c>
-      <c r="E78">
+      <c r="E78" s="11">
         <v>3300</v>
       </c>
       <c r="F78" s="7" t="s">
@@ -3188,16 +3191,17 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="A79" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B79" t="s">
-        <v>15</v>
-      </c>
-      <c r="D79">
+      <c r="B79" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C79" s="7"/>
+      <c r="D79" s="11">
         <v>2990</v>
       </c>
-      <c r="E79">
+      <c r="E79" s="11">
         <v>3300</v>
       </c>
       <c r="F79" s="7" t="s">
@@ -3214,16 +3218,17 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
+      <c r="A80" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B80" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80">
+      <c r="B80" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="7"/>
+      <c r="D80" s="11">
         <v>2990</v>
       </c>
-      <c r="E80">
+      <c r="E80" s="11">
         <v>3250</v>
       </c>
       <c r="F80" s="7" t="s">
@@ -3240,16 +3245,17 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
+      <c r="A81" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="B81" t="s">
-        <v>15</v>
-      </c>
-      <c r="D81">
+      <c r="B81" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="7"/>
+      <c r="D81" s="11">
         <v>3140</v>
       </c>
-      <c r="E81">
+      <c r="E81" s="11">
         <v>3560</v>
       </c>
       <c r="F81" s="7" t="s">
@@ -3266,16 +3272,17 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
+      <c r="A82" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B82" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82">
+      <c r="B82" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="7"/>
+      <c r="D82" s="11">
         <v>3090</v>
       </c>
-      <c r="E82">
+      <c r="E82" s="11">
         <v>3410</v>
       </c>
       <c r="F82" s="7" t="s">
@@ -3292,16 +3299,17 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
+      <c r="A83" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B83" t="s">
-        <v>15</v>
-      </c>
-      <c r="D83">
+      <c r="B83" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="7"/>
+      <c r="D83" s="11">
         <v>3200</v>
       </c>
-      <c r="E83">
+      <c r="E83" s="11">
         <v>3620</v>
       </c>
       <c r="F83" s="7" t="s">
@@ -3318,16 +3326,17 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
+      <c r="A84" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="B84" t="s">
-        <v>15</v>
-      </c>
-      <c r="D84">
+      <c r="B84" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="7"/>
+      <c r="D84" s="11">
         <v>3200</v>
       </c>
-      <c r="E84">
+      <c r="E84" s="11">
         <v>3620</v>
       </c>
       <c r="F84" s="7" t="s">
@@ -3344,16 +3353,17 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
+      <c r="A85" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="B85" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85">
+      <c r="B85" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="7"/>
+      <c r="D85" s="11">
         <v>3040</v>
       </c>
-      <c r="E85">
+      <c r="E85" s="11">
         <v>3300</v>
       </c>
       <c r="F85" s="7" t="s">
@@ -3370,16 +3380,17 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
+      <c r="A86" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B86" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86">
+      <c r="B86" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="7"/>
+      <c r="D86" s="11">
         <v>3090</v>
       </c>
-      <c r="E86">
+      <c r="E86" s="11">
         <v>3410</v>
       </c>
       <c r="F86" s="7" t="s">
@@ -3396,16 +3407,17 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+      <c r="A87" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B87" t="s">
-        <v>15</v>
-      </c>
-      <c r="D87">
+      <c r="B87" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="7"/>
+      <c r="D87" s="11">
         <v>3090</v>
       </c>
-      <c r="E87">
+      <c r="E87" s="11">
         <v>3410</v>
       </c>
       <c r="F87" s="7" t="s">
@@ -3422,16 +3434,17 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+      <c r="A88" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B88" t="s">
-        <v>15</v>
-      </c>
-      <c r="D88">
+      <c r="B88" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="7"/>
+      <c r="D88" s="11">
         <v>3090</v>
       </c>
-      <c r="E88">
+      <c r="E88" s="11">
         <v>3410</v>
       </c>
       <c r="F88" s="7" t="s">
@@ -3448,16 +3461,17 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+      <c r="A89" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="B89" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89">
+      <c r="B89" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="7"/>
+      <c r="D89" s="11">
         <v>3090</v>
       </c>
-      <c r="E89">
+      <c r="E89" s="11">
         <v>3410</v>
       </c>
       <c r="F89" s="7" t="s">
@@ -3474,16 +3488,17 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
+      <c r="A90" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B90" t="s">
-        <v>15</v>
-      </c>
-      <c r="D90">
+      <c r="B90" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="7"/>
+      <c r="D90" s="11">
         <v>3090</v>
       </c>
-      <c r="E90">
+      <c r="E90" s="11">
         <v>3410</v>
       </c>
       <c r="F90" s="7" t="s">
@@ -3500,16 +3515,17 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
+      <c r="A91" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B91" t="s">
-        <v>15</v>
-      </c>
-      <c r="D91">
+      <c r="B91" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="7"/>
+      <c r="D91" s="11">
         <v>3090</v>
       </c>
-      <c r="E91">
+      <c r="E91" s="11">
         <v>3410</v>
       </c>
       <c r="F91" s="7" t="s">
@@ -3526,16 +3542,17 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
+      <c r="A92" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B92" t="s">
-        <v>15</v>
-      </c>
-      <c r="D92">
+      <c r="B92" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C92" s="7"/>
+      <c r="D92" s="11">
         <v>3090</v>
       </c>
-      <c r="E92">
+      <c r="E92" s="11">
         <v>3410</v>
       </c>
       <c r="F92" s="7" t="s">
@@ -3552,16 +3569,17 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
+      <c r="A93" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B93" t="s">
-        <v>15</v>
-      </c>
-      <c r="D93">
+      <c r="B93" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="7"/>
+      <c r="D93" s="11">
         <v>3090</v>
       </c>
-      <c r="E93">
+      <c r="E93" s="11">
         <v>3410</v>
       </c>
       <c r="F93" s="7" t="s">
@@ -3578,16 +3596,17 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
+      <c r="A94" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="B94" t="s">
-        <v>15</v>
-      </c>
-      <c r="D94">
+      <c r="B94" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="7"/>
+      <c r="D94" s="11">
         <v>3090</v>
       </c>
-      <c r="E94">
+      <c r="E94" s="11">
         <v>3410</v>
       </c>
       <c r="F94" s="7" t="s">
@@ -3604,16 +3623,17 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
+      <c r="A95" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B95" t="s">
-        <v>15</v>
-      </c>
-      <c r="D95">
+      <c r="B95" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="7"/>
+      <c r="D95" s="11">
         <v>3140</v>
       </c>
-      <c r="E95">
+      <c r="E95" s="11">
         <v>3560</v>
       </c>
       <c r="F95" s="7" t="s">
@@ -3630,16 +3650,17 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
+      <c r="A96" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B96" t="s">
-        <v>15</v>
-      </c>
-      <c r="D96">
+      <c r="B96" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="11">
         <v>3200</v>
       </c>
-      <c r="E96">
+      <c r="E96" s="11">
         <v>3620</v>
       </c>
       <c r="F96" s="7" t="s">
@@ -3656,16 +3677,17 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
+      <c r="A97" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B97" t="s">
-        <v>15</v>
-      </c>
-      <c r="D97">
+      <c r="B97" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="7"/>
+      <c r="D97" s="11">
         <v>3250</v>
       </c>
-      <c r="E97">
+      <c r="E97" s="11">
         <v>3720</v>
       </c>
       <c r="F97" s="7" t="s">
@@ -3682,16 +3704,17 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
+      <c r="A98" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B98" t="s">
-        <v>15</v>
-      </c>
-      <c r="D98">
+      <c r="B98" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="7"/>
+      <c r="D98" s="11">
         <v>3250</v>
       </c>
-      <c r="E98">
+      <c r="E98" s="11">
         <v>3720</v>
       </c>
       <c r="F98" s="7" t="s">
@@ -3708,16 +3731,17 @@
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
+      <c r="A99" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B99" t="s">
-        <v>15</v>
-      </c>
-      <c r="D99">
+      <c r="B99" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="7"/>
+      <c r="D99" s="11">
         <v>3410</v>
       </c>
-      <c r="E99">
+      <c r="E99" s="11">
         <v>3930</v>
       </c>
       <c r="F99" s="7" t="s">
@@ -3734,16 +3758,17 @@
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
+      <c r="A100" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="B100" t="s">
-        <v>15</v>
-      </c>
-      <c r="D100">
+      <c r="B100" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="7"/>
+      <c r="D100" s="11">
         <v>3040</v>
       </c>
-      <c r="E100">
+      <c r="E100" s="11">
         <v>3250</v>
       </c>
       <c r="F100" s="7" t="s">
@@ -3760,16 +3785,17 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
+      <c r="A101" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B101" t="s">
-        <v>15</v>
-      </c>
-      <c r="D101">
+      <c r="B101" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="7"/>
+      <c r="D101" s="11">
         <v>3040</v>
       </c>
-      <c r="E101">
+      <c r="E101" s="11">
         <v>3250</v>
       </c>
       <c r="F101" s="7" t="s">
@@ -3786,16 +3812,17 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
+      <c r="A102" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B102" t="s">
-        <v>15</v>
-      </c>
-      <c r="D102">
+      <c r="B102" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="7"/>
+      <c r="D102" s="11">
         <v>3040</v>
       </c>
-      <c r="E102">
+      <c r="E102" s="11">
         <v>3250</v>
       </c>
       <c r="F102" s="7" t="s">
@@ -3812,16 +3839,17 @@
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
+      <c r="A103" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B103" t="s">
-        <v>15</v>
-      </c>
-      <c r="D103">
+      <c r="B103" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" s="7"/>
+      <c r="D103" s="11">
         <v>3040</v>
       </c>
-      <c r="E103">
+      <c r="E103" s="11">
         <v>3250</v>
       </c>
       <c r="F103" s="7" t="s">
@@ -3838,16 +3866,17 @@
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+      <c r="A104" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B104" t="s">
-        <v>15</v>
-      </c>
-      <c r="D104">
+      <c r="B104" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" s="7"/>
+      <c r="D104" s="11">
         <v>3040</v>
       </c>
-      <c r="E104">
+      <c r="E104" s="11">
         <v>3250</v>
       </c>
       <c r="F104" s="7" t="s">
@@ -3871,11 +3900,11 @@
         <v>15</v>
       </c>
       <c r="C105" s="11"/>
-      <c r="D105" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E105" s="7">
-        <v>3100</v>
+      <c r="D105" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E105" s="11">
+        <v>2840</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>149</v>
@@ -3898,11 +3927,11 @@
         <v>15</v>
       </c>
       <c r="C106" s="11"/>
-      <c r="D106" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E106" s="7">
-        <v>3100</v>
+      <c r="D106" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E106" s="11">
+        <v>2840</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>149</v>
@@ -3925,11 +3954,11 @@
         <v>15</v>
       </c>
       <c r="C107" s="11"/>
-      <c r="D107" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E107" s="7">
-        <v>3100</v>
+      <c r="D107" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E107" s="11">
+        <v>2840</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>149</v>
@@ -3952,11 +3981,11 @@
         <v>15</v>
       </c>
       <c r="C108" s="11"/>
-      <c r="D108" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E108" s="7">
-        <v>3100</v>
+      <c r="D108" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E108" s="11">
+        <v>2840</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>149</v>
@@ -3979,11 +4008,11 @@
         <v>15</v>
       </c>
       <c r="C109" s="11"/>
-      <c r="D109" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E109" s="7">
-        <v>3100</v>
+      <c r="D109" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E109" s="11">
+        <v>2840</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>149</v>
@@ -4006,11 +4035,11 @@
         <v>15</v>
       </c>
       <c r="C110" s="11"/>
-      <c r="D110" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E110" s="7">
-        <v>3100</v>
+      <c r="D110" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E110" s="11">
+        <v>2840</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>149</v>
@@ -4033,11 +4062,11 @@
         <v>15</v>
       </c>
       <c r="C111" s="11"/>
-      <c r="D111" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E111" s="7">
-        <v>3100</v>
+      <c r="D111" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E111" s="11">
+        <v>2840</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>149</v>
@@ -4060,11 +4089,11 @@
         <v>15</v>
       </c>
       <c r="C112" s="11"/>
-      <c r="D112" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E112" s="7">
-        <v>3100</v>
+      <c r="D112" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E112" s="11">
+        <v>2840</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>149</v>
@@ -4087,11 +4116,11 @@
         <v>15</v>
       </c>
       <c r="C113" s="11"/>
-      <c r="D113" s="7">
-        <v>2890</v>
-      </c>
-      <c r="E113" s="7">
-        <v>3100</v>
+      <c r="D113" s="11">
+        <v>2630</v>
+      </c>
+      <c r="E113" s="11">
+        <v>2840</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>149</v>
@@ -4114,11 +4143,11 @@
         <v>15</v>
       </c>
       <c r="C114" s="11"/>
-      <c r="D114" s="7">
-        <v>2970</v>
-      </c>
-      <c r="E114" s="7">
-        <v>3260</v>
+      <c r="D114" s="11">
+        <v>2710</v>
+      </c>
+      <c r="E114" s="11">
+        <v>3000</v>
       </c>
       <c r="F114" s="7" t="s">
         <v>149</v>
@@ -4141,11 +4170,11 @@
         <v>15</v>
       </c>
       <c r="C115" s="11"/>
-      <c r="D115" s="7">
+      <c r="D115" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E115" s="11">
         <v>2950</v>
-      </c>
-      <c r="E115" s="7">
-        <v>3210</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>149</v>
@@ -4168,11 +4197,11 @@
         <v>15</v>
       </c>
       <c r="C116" s="11"/>
-      <c r="D116" s="7">
+      <c r="D116" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E116" s="11">
         <v>2950</v>
-      </c>
-      <c r="E116" s="7">
-        <v>3210</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>149</v>
@@ -4195,11 +4224,11 @@
         <v>15</v>
       </c>
       <c r="C117" s="11"/>
-      <c r="D117" s="7">
+      <c r="D117" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E117" s="11">
         <v>2950</v>
-      </c>
-      <c r="E117" s="7">
-        <v>3210</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>149</v>
@@ -4222,11 +4251,11 @@
         <v>15</v>
       </c>
       <c r="C118" s="11"/>
-      <c r="D118" s="7">
+      <c r="D118" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E118" s="11">
         <v>2950</v>
-      </c>
-      <c r="E118" s="7">
-        <v>3210</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>149</v>
@@ -4249,11 +4278,11 @@
         <v>15</v>
       </c>
       <c r="C119" s="11"/>
-      <c r="D119" s="7">
+      <c r="D119" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E119" s="11">
         <v>2950</v>
-      </c>
-      <c r="E119" s="7">
-        <v>3210</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>149</v>
@@ -4276,11 +4305,11 @@
         <v>15</v>
       </c>
       <c r="C120" s="11"/>
-      <c r="D120" s="7">
+      <c r="D120" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E120" s="11">
         <v>2950</v>
-      </c>
-      <c r="E120" s="7">
-        <v>3210</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>149</v>
@@ -4303,11 +4332,11 @@
         <v>15</v>
       </c>
       <c r="C121" s="11"/>
-      <c r="D121" s="7">
+      <c r="D121" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E121" s="11">
         <v>2950</v>
-      </c>
-      <c r="E121" s="7">
-        <v>3210</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>149</v>
@@ -4330,11 +4359,11 @@
         <v>15</v>
       </c>
       <c r="C122" s="11"/>
-      <c r="D122" s="7">
+      <c r="D122" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E122" s="11">
         <v>2950</v>
-      </c>
-      <c r="E122" s="7">
-        <v>3210</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>149</v>
@@ -4357,11 +4386,11 @@
         <v>15</v>
       </c>
       <c r="C123" s="11"/>
-      <c r="D123" s="7">
-        <v>3140</v>
-      </c>
-      <c r="E123" s="7">
-        <v>3510</v>
+      <c r="D123" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E123" s="11">
+        <v>3250</v>
       </c>
       <c r="F123" s="7" t="s">
         <v>149</v>
@@ -4384,11 +4413,11 @@
         <v>15</v>
       </c>
       <c r="C124" s="11"/>
-      <c r="D124" s="7">
+      <c r="D124" s="11">
+        <v>2680</v>
+      </c>
+      <c r="E124" s="11">
         <v>2950</v>
-      </c>
-      <c r="E124" s="7">
-        <v>3210</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>149</v>
@@ -4411,11 +4440,11 @@
         <v>15</v>
       </c>
       <c r="C125" s="11"/>
-      <c r="D125" s="7">
+      <c r="D125" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E125" s="11">
         <v>3000</v>
-      </c>
-      <c r="E125" s="7">
-        <v>3260</v>
       </c>
       <c r="F125" s="7" t="s">
         <v>149</v>
@@ -4438,11 +4467,11 @@
         <v>15</v>
       </c>
       <c r="C126" s="11"/>
-      <c r="D126" s="7">
-        <v>3110</v>
-      </c>
-      <c r="E126" s="7">
-        <v>3420</v>
+      <c r="D126" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E126" s="11">
+        <v>3160</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>149</v>
@@ -4465,11 +4494,11 @@
         <v>15</v>
       </c>
       <c r="C127" s="11"/>
-      <c r="D127" s="7">
-        <v>3050</v>
-      </c>
-      <c r="E127" s="7">
-        <v>3420</v>
+      <c r="D127" s="11">
+        <v>2790</v>
+      </c>
+      <c r="E127" s="11">
+        <v>3160</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>149</v>
@@ -4492,11 +4521,11 @@
         <v>15</v>
       </c>
       <c r="C128" s="11"/>
-      <c r="D128" s="7">
-        <v>3120</v>
-      </c>
-      <c r="E128" s="7">
-        <v>3450</v>
+      <c r="D128" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E128" s="11">
+        <v>3190</v>
       </c>
       <c r="F128" s="7" t="s">
         <v>149</v>
@@ -4519,11 +4548,11 @@
         <v>15</v>
       </c>
       <c r="C129" s="11"/>
-      <c r="D129" s="7">
-        <v>3150</v>
-      </c>
-      <c r="E129" s="7">
-        <v>3550</v>
+      <c r="D129" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E129" s="11">
+        <v>3290</v>
       </c>
       <c r="F129" s="7" t="s">
         <v>149</v>
@@ -4546,11 +4575,11 @@
         <v>15</v>
       </c>
       <c r="C130" s="11"/>
-      <c r="D130" s="7">
-        <v>3150</v>
-      </c>
-      <c r="E130" s="7">
-        <v>3550</v>
+      <c r="D130" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E130" s="11">
+        <v>3290</v>
       </c>
       <c r="F130" s="7" t="s">
         <v>149</v>
@@ -4573,11 +4602,11 @@
         <v>15</v>
       </c>
       <c r="C131" s="11"/>
-      <c r="D131" s="7">
-        <v>3080</v>
-      </c>
-      <c r="E131" s="7">
-        <v>3420</v>
+      <c r="D131" s="11">
+        <v>2820</v>
+      </c>
+      <c r="E131" s="11">
+        <v>3160</v>
       </c>
       <c r="F131" s="7" t="s">
         <v>149</v>
@@ -4600,11 +4629,11 @@
         <v>15</v>
       </c>
       <c r="C132" s="11"/>
-      <c r="D132" s="7">
-        <v>3100</v>
-      </c>
-      <c r="E132" s="7">
-        <v>3440</v>
+      <c r="D132" s="11">
+        <v>2840</v>
+      </c>
+      <c r="E132" s="11">
+        <v>3180</v>
       </c>
       <c r="F132" s="7" t="s">
         <v>149</v>
@@ -4627,11 +4656,11 @@
         <v>15</v>
       </c>
       <c r="C133" s="11"/>
-      <c r="D133" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E133" s="7">
-        <v>3320</v>
+      <c r="D133" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E133" s="11">
+        <v>3060</v>
       </c>
       <c r="F133" s="7" t="s">
         <v>149</v>
@@ -4654,11 +4683,11 @@
         <v>15</v>
       </c>
       <c r="C134" s="11"/>
-      <c r="D134" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E134" s="7">
-        <v>3320</v>
+      <c r="D134" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E134" s="11">
+        <v>3060</v>
       </c>
       <c r="F134" s="7" t="s">
         <v>149</v>
@@ -4681,11 +4710,11 @@
         <v>15</v>
       </c>
       <c r="C135" s="11"/>
-      <c r="D135" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E135" s="7">
-        <v>3320</v>
+      <c r="D135" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E135" s="11">
+        <v>3060</v>
       </c>
       <c r="F135" s="7" t="s">
         <v>149</v>
@@ -4708,11 +4737,11 @@
         <v>15</v>
       </c>
       <c r="C136" s="11"/>
-      <c r="D136" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E136" s="7">
-        <v>3320</v>
+      <c r="D136" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E136" s="11">
+        <v>3060</v>
       </c>
       <c r="F136" s="7" t="s">
         <v>149</v>
@@ -4735,11 +4764,11 @@
         <v>15</v>
       </c>
       <c r="C137" s="11"/>
-      <c r="D137" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E137" s="7">
-        <v>3320</v>
+      <c r="D137" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E137" s="11">
+        <v>3060</v>
       </c>
       <c r="F137" s="7" t="s">
         <v>149</v>
@@ -4762,11 +4791,11 @@
         <v>15</v>
       </c>
       <c r="C138" s="11"/>
-      <c r="D138" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E138" s="7">
-        <v>3320</v>
+      <c r="D138" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E138" s="11">
+        <v>3060</v>
       </c>
       <c r="F138" s="7" t="s">
         <v>149</v>
@@ -4789,11 +4818,11 @@
         <v>15</v>
       </c>
       <c r="C139" s="11"/>
-      <c r="D139" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E139" s="7">
-        <v>3320</v>
+      <c r="D139" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E139" s="11">
+        <v>3060</v>
       </c>
       <c r="F139" s="7" t="s">
         <v>149</v>
@@ -4816,11 +4845,11 @@
         <v>15</v>
       </c>
       <c r="C140" s="11"/>
-      <c r="D140" s="7">
-        <v>3020</v>
-      </c>
-      <c r="E140" s="7">
-        <v>3320</v>
+      <c r="D140" s="11">
+        <v>2760</v>
+      </c>
+      <c r="E140" s="11">
+        <v>3060</v>
       </c>
       <c r="F140" s="7" t="s">
         <v>149</v>
@@ -4843,11 +4872,11 @@
         <v>15</v>
       </c>
       <c r="C141" s="11"/>
-      <c r="D141" s="7">
-        <v>3140</v>
-      </c>
-      <c r="E141" s="7">
-        <v>3540</v>
+      <c r="D141" s="11">
+        <v>2880</v>
+      </c>
+      <c r="E141" s="11">
+        <v>3280</v>
       </c>
       <c r="F141" s="7" t="s">
         <v>149</v>
@@ -4870,11 +4899,11 @@
         <v>15</v>
       </c>
       <c r="C142" s="11"/>
-      <c r="D142" s="7">
-        <v>3130</v>
-      </c>
-      <c r="E142" s="7">
-        <v>3510</v>
+      <c r="D142" s="11">
+        <v>2870</v>
+      </c>
+      <c r="E142" s="11">
+        <v>3250</v>
       </c>
       <c r="F142" s="7" t="s">
         <v>149</v>
@@ -4897,11 +4926,11 @@
         <v>15</v>
       </c>
       <c r="C143" s="11"/>
-      <c r="D143" s="7">
-        <v>3130</v>
-      </c>
-      <c r="E143" s="7">
-        <v>3580</v>
+      <c r="D143" s="11">
+        <v>2870</v>
+      </c>
+      <c r="E143" s="11">
+        <v>3310</v>
       </c>
       <c r="F143" s="7" t="s">
         <v>149</v>
@@ -4924,11 +4953,11 @@
         <v>15</v>
       </c>
       <c r="C144" s="11"/>
-      <c r="D144" s="7">
-        <v>3130</v>
-      </c>
-      <c r="E144" s="7">
-        <v>3580</v>
+      <c r="D144" s="11">
+        <v>2870</v>
+      </c>
+      <c r="E144" s="11">
+        <v>3310</v>
       </c>
       <c r="F144" s="7" t="s">
         <v>149</v>
@@ -4951,11 +4980,11 @@
         <v>15</v>
       </c>
       <c r="C145" s="11"/>
-      <c r="D145" s="7">
-        <v>3320</v>
-      </c>
-      <c r="E145" s="7">
-        <v>3930</v>
+      <c r="D145" s="11">
+        <v>3060</v>
+      </c>
+      <c r="E145" s="11">
+        <v>3670</v>
       </c>
       <c r="F145" s="7" t="s">
         <v>149</v>
@@ -4978,11 +5007,11 @@
         <v>15</v>
       </c>
       <c r="C146" s="11"/>
-      <c r="D146" s="7">
+      <c r="D146" s="11">
+        <v>2740</v>
+      </c>
+      <c r="E146" s="11">
         <v>3000</v>
-      </c>
-      <c r="E146" s="7">
-        <v>3260</v>
       </c>
       <c r="F146" s="7" t="s">
         <v>149</v>
@@ -5005,11 +5034,11 @@
         <v>15</v>
       </c>
       <c r="C147" s="11"/>
-      <c r="D147" s="7">
-        <v>3100</v>
-      </c>
-      <c r="E147" s="7">
-        <v>3420</v>
+      <c r="D147" s="11">
+        <v>2840</v>
+      </c>
+      <c r="E147" s="11">
+        <v>3160</v>
       </c>
       <c r="F147" s="7" t="s">
         <v>149</v>
@@ -5032,11 +5061,11 @@
         <v>15</v>
       </c>
       <c r="C148" s="11"/>
-      <c r="D148" s="7">
-        <v>3100</v>
-      </c>
-      <c r="E148" s="7">
-        <v>3420</v>
+      <c r="D148" s="11">
+        <v>2840</v>
+      </c>
+      <c r="E148" s="11">
+        <v>3160</v>
       </c>
       <c r="F148" s="7" t="s">
         <v>149</v>
@@ -5059,11 +5088,11 @@
         <v>15</v>
       </c>
       <c r="C149" s="11"/>
-      <c r="D149" s="7">
-        <v>3160</v>
-      </c>
-      <c r="E149" s="7">
-        <v>3470</v>
+      <c r="D149" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E149" s="11">
+        <v>3210</v>
       </c>
       <c r="F149" s="7" t="s">
         <v>149</v>
@@ -5086,11 +5115,11 @@
         <v>15</v>
       </c>
       <c r="C150" s="11"/>
-      <c r="D150" s="7">
-        <v>3160</v>
-      </c>
-      <c r="E150" s="7">
-        <v>3470</v>
+      <c r="D150" s="11">
+        <v>2890</v>
+      </c>
+      <c r="E150" s="11">
+        <v>3210</v>
       </c>
       <c r="F150" s="7" t="s">
         <v>149</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{709B5509-3F25-4771-9D4A-88258AE0D013}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31DFDF28-A93C-4C7C-8868-920B0DE3368A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$286</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$422</definedName>
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2195" uniqueCount="152">
   <si>
     <t>POD</t>
   </si>
@@ -496,9 +496,6 @@
   </si>
   <si>
     <t>ONE</t>
-  </si>
-  <si>
-    <t>XINGANG(TIANJIN)</t>
   </si>
   <si>
     <t>15 al 19 de abril</t>
@@ -8833,7 +8830,7 @@
         <v>2790</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G287" s="8">
         <v>14</v>
@@ -8860,7 +8857,7 @@
         <v>2790</v>
       </c>
       <c r="F288" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G288" s="8">
         <v>14</v>
@@ -8887,7 +8884,7 @@
         <v>2790</v>
       </c>
       <c r="F289" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G289" s="8">
         <v>14</v>
@@ -8914,7 +8911,7 @@
         <v>2790</v>
       </c>
       <c r="F290" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G290" s="8">
         <v>14</v>
@@ -8941,7 +8938,7 @@
         <v>2850</v>
       </c>
       <c r="F291" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G291" s="8">
         <v>14</v>
@@ -8968,7 +8965,7 @@
         <v>3110</v>
       </c>
       <c r="F292" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G292" s="8">
         <v>14</v>
@@ -8995,7 +8992,7 @@
         <v>3630</v>
       </c>
       <c r="F293" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G293" s="8">
         <v>14</v>
@@ -9022,7 +9019,7 @@
         <v>3270</v>
       </c>
       <c r="F294" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G294" s="8">
         <v>14</v>
@@ -9049,7 +9046,7 @@
         <v>3320</v>
       </c>
       <c r="F295" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G295" s="8">
         <v>14</v>
@@ -9076,7 +9073,7 @@
         <v>3530</v>
       </c>
       <c r="F296" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G296" s="8">
         <v>14</v>
@@ -9103,7 +9100,7 @@
         <v>3110</v>
       </c>
       <c r="F297" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G297" s="8">
         <v>14</v>
@@ -9130,7 +9127,7 @@
         <v>3270</v>
       </c>
       <c r="F298" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G298" s="8">
         <v>14</v>
@@ -9157,7 +9154,7 @@
         <v>3210</v>
       </c>
       <c r="F299" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G299" s="8">
         <v>14</v>
@@ -9184,7 +9181,7 @@
         <v>3420</v>
       </c>
       <c r="F300" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G300" s="8">
         <v>14</v>
@@ -9211,7 +9208,7 @@
         <v>3160</v>
       </c>
       <c r="F301" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G301" s="8">
         <v>14</v>
@@ -9238,7 +9235,7 @@
         <v>3370</v>
       </c>
       <c r="F302" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G302" s="8">
         <v>14</v>
@@ -9265,7 +9262,7 @@
         <v>3160</v>
       </c>
       <c r="F303" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G303" s="8">
         <v>14</v>
@@ -9292,7 +9289,7 @@
         <v>3270</v>
       </c>
       <c r="F304" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G304" s="8">
         <v>14</v>
@@ -9319,7 +9316,7 @@
         <v>2900</v>
       </c>
       <c r="F305" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G305" s="8">
         <v>14</v>
@@ -9346,7 +9343,7 @@
         <v>3210</v>
       </c>
       <c r="F306" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G306" s="8">
         <v>14</v>
@@ -9373,7 +9370,7 @@
         <v>3270</v>
       </c>
       <c r="F307" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G307" s="8">
         <v>14</v>
@@ -9400,7 +9397,7 @@
         <v>2790</v>
       </c>
       <c r="F308" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G308" s="8">
         <v>14</v>
@@ -9427,7 +9424,7 @@
         <v>3320</v>
       </c>
       <c r="F309" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G309" s="8">
         <v>14</v>
@@ -9454,7 +9451,7 @@
         <v>3270</v>
       </c>
       <c r="F310" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G310" s="8">
         <v>14</v>
@@ -9481,7 +9478,7 @@
         <v>3160</v>
       </c>
       <c r="F311" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G311" s="8">
         <v>14</v>
@@ -9508,7 +9505,7 @@
         <v>2790</v>
       </c>
       <c r="F312" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G312" s="8">
         <v>14</v>
@@ -9521,8 +9518,8 @@
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>151</v>
+      <c r="A313" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B313" t="s">
         <v>62</v>
@@ -9535,7 +9532,7 @@
         <v>3420</v>
       </c>
       <c r="F313" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G313" s="8">
         <v>14</v>
@@ -9562,7 +9559,7 @@
         <v>2790</v>
       </c>
       <c r="F314" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G314" s="8">
         <v>14</v>
@@ -9589,7 +9586,7 @@
         <v>3420</v>
       </c>
       <c r="F315" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G315" s="8">
         <v>14</v>
@@ -9616,7 +9613,7 @@
         <v>3110</v>
       </c>
       <c r="F316" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G316" s="8">
         <v>14</v>
@@ -9643,7 +9640,7 @@
         <v>3270</v>
       </c>
       <c r="F317" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G317" s="8">
         <v>14</v>
@@ -9670,7 +9667,7 @@
         <v>3160</v>
       </c>
       <c r="F318" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G318" s="8">
         <v>14</v>
@@ -9697,7 +9694,7 @@
         <v>3270</v>
       </c>
       <c r="F319" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G319" s="8">
         <v>14</v>
@@ -9724,7 +9721,7 @@
         <v>3320</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G320" s="8">
         <v>14</v>
@@ -9753,7 +9750,7 @@
         <v>2880</v>
       </c>
       <c r="F321" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G321" s="8" t="s">
         <v>137</v>
@@ -9780,7 +9777,7 @@
         <v>2880</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G322" s="8">
         <v>17</v>
@@ -9807,7 +9804,7 @@
         <v>2880</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G323" s="8">
         <v>17</v>
@@ -9834,7 +9831,7 @@
         <v>3040</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G324" s="8">
         <v>17</v>
@@ -9861,7 +9858,7 @@
         <v>3440</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G325" s="8">
         <v>17</v>
@@ -9888,7 +9885,7 @@
         <v>2980</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G326" s="8">
         <v>17</v>
@@ -9915,7 +9912,7 @@
         <v>3060</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G327" s="8">
         <v>17</v>
@@ -9942,7 +9939,7 @@
         <v>2980</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G328" s="8">
         <v>17</v>
@@ -9969,7 +9966,7 @@
         <v>3090</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G329" s="8">
         <v>17</v>
@@ -9996,7 +9993,7 @@
         <v>3070</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G330" s="8">
         <v>17</v>
@@ -10023,7 +10020,7 @@
         <v>3090</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G331" s="8">
         <v>17</v>
@@ -10050,7 +10047,7 @@
         <v>3050</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G332" s="8">
         <v>17</v>
@@ -10077,7 +10074,7 @@
         <v>3190</v>
       </c>
       <c r="F333" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G333" s="8">
         <v>17</v>
@@ -10104,7 +10101,7 @@
         <v>3090</v>
       </c>
       <c r="F334" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G334" s="8">
         <v>17</v>
@@ -10131,7 +10128,7 @@
         <v>3060</v>
       </c>
       <c r="F335" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G335" s="8">
         <v>17</v>
@@ -10158,7 +10155,7 @@
         <v>3030</v>
       </c>
       <c r="F336" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G336" s="8">
         <v>17</v>
@@ -10185,7 +10182,7 @@
         <v>3300</v>
       </c>
       <c r="F337" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G337" s="8">
         <v>17</v>
@@ -10212,7 +10209,7 @@
         <v>3060</v>
       </c>
       <c r="F338" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G338" s="8">
         <v>17</v>
@@ -10239,7 +10236,7 @@
         <v>3030</v>
       </c>
       <c r="F339" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G339" s="8">
         <v>17</v>
@@ -10266,7 +10263,7 @@
         <v>2980</v>
       </c>
       <c r="F340" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G340" s="8">
         <v>17</v>
@@ -10293,7 +10290,7 @@
         <v>3060</v>
       </c>
       <c r="F341" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G341" s="8">
         <v>17</v>
@@ -10320,7 +10317,7 @@
         <v>3040</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G342" s="8">
         <v>17</v>
@@ -10347,7 +10344,7 @@
         <v>3150</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G343" s="8">
         <v>17</v>
@@ -10374,7 +10371,7 @@
         <v>2880</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G344" s="8">
         <v>17</v>
@@ -10401,7 +10398,7 @@
         <v>2880</v>
       </c>
       <c r="F345" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G345" s="8">
         <v>17</v>
@@ -10428,7 +10425,7 @@
         <v>3060</v>
       </c>
       <c r="F346" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G346" s="8">
         <v>17</v>
@@ -10455,7 +10452,7 @@
         <v>3180</v>
       </c>
       <c r="F347" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G347" s="8">
         <v>17</v>
@@ -10482,7 +10479,7 @@
         <v>3090</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G348" s="8">
         <v>17</v>
@@ -10509,7 +10506,7 @@
         <v>2980</v>
       </c>
       <c r="F349" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G349" s="8">
         <v>17</v>
@@ -10522,8 +10519,8 @@
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>151</v>
+      <c r="A350" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B350" t="s">
         <v>15</v>
@@ -10538,7 +10535,7 @@
         <v>2880</v>
       </c>
       <c r="F350" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G350" s="8" t="s">
         <v>137</v>
@@ -10565,7 +10562,7 @@
         <v>3030</v>
       </c>
       <c r="F351" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G351" s="8">
         <v>17</v>
@@ -10592,7 +10589,7 @@
         <v>2880</v>
       </c>
       <c r="F352" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G352" s="8">
         <v>17</v>
@@ -10619,7 +10616,7 @@
         <v>3360</v>
       </c>
       <c r="F353" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G353" s="8">
         <v>17</v>
@@ -10646,7 +10643,7 @@
         <v>3030</v>
       </c>
       <c r="F354" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G354" s="8">
         <v>17</v>
@@ -10673,7 +10670,7 @@
         <v>3090</v>
       </c>
       <c r="F355" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G355" s="8">
         <v>17</v>
@@ -10700,7 +10697,7 @@
         <v>3030</v>
       </c>
       <c r="F356" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G356" s="8">
         <v>17</v>
@@ -10727,7 +10724,7 @@
         <v>3060</v>
       </c>
       <c r="F357" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G357" s="8">
         <v>17</v>
@@ -10754,7 +10751,7 @@
         <v>3060</v>
       </c>
       <c r="F358" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G358" s="8">
         <v>17</v>
@@ -10781,7 +10778,7 @@
         <v>2810</v>
       </c>
       <c r="F359" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G359" s="8">
         <v>18</v>
@@ -10808,7 +10805,7 @@
         <v>2810</v>
       </c>
       <c r="F360" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G360" s="8">
         <v>18</v>
@@ -10835,7 +10832,7 @@
         <v>2810</v>
       </c>
       <c r="F361" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G361" s="8">
         <v>18</v>
@@ -10862,7 +10859,7 @@
         <v>2810</v>
       </c>
       <c r="F362" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G362" s="8">
         <v>18</v>
@@ -10889,7 +10886,7 @@
         <v>2860</v>
       </c>
       <c r="F363" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G363" s="8">
         <v>18</v>
@@ -10916,7 +10913,7 @@
         <v>3070</v>
       </c>
       <c r="F364" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G364" s="8">
         <v>18</v>
@@ -10943,7 +10940,7 @@
         <v>3750</v>
       </c>
       <c r="F365" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G365" s="8">
         <v>18</v>
@@ -10970,7 +10967,7 @@
         <v>2910</v>
       </c>
       <c r="F366" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G366" s="8">
         <v>18</v>
@@ -10997,7 +10994,7 @@
         <v>3070</v>
       </c>
       <c r="F367" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G367" s="8">
         <v>18</v>
@@ -11024,7 +11021,7 @@
         <v>3230</v>
       </c>
       <c r="F368" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G368" s="8">
         <v>18</v>
@@ -11051,7 +11048,7 @@
         <v>3020</v>
       </c>
       <c r="F369" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G369" s="8">
         <v>18</v>
@@ -11078,7 +11075,7 @@
         <v>3070</v>
       </c>
       <c r="F370" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G370" s="8">
         <v>18</v>
@@ -11105,7 +11102,7 @@
         <v>3330</v>
       </c>
       <c r="F371" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G371" s="8">
         <v>18</v>
@@ -11132,7 +11129,7 @@
         <v>3330</v>
       </c>
       <c r="F372" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G372" s="8">
         <v>18</v>
@@ -11159,7 +11156,7 @@
         <v>3540</v>
       </c>
       <c r="F373" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G373" s="8">
         <v>18</v>
@@ -11186,7 +11183,7 @@
         <v>3120</v>
       </c>
       <c r="F374" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G374" s="8">
         <v>18</v>
@@ -11213,7 +11210,7 @@
         <v>3070</v>
       </c>
       <c r="F375" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G375" s="8">
         <v>18</v>
@@ -11240,7 +11237,7 @@
         <v>3230</v>
       </c>
       <c r="F376" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G376" s="8">
         <v>18</v>
@@ -11267,7 +11264,7 @@
         <v>3020</v>
       </c>
       <c r="F377" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G377" s="8">
         <v>18</v>
@@ -11294,7 +11291,7 @@
         <v>3070</v>
       </c>
       <c r="F378" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G378" s="8">
         <v>18</v>
@@ -11321,7 +11318,7 @@
         <v>3070</v>
       </c>
       <c r="F379" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G379" s="8">
         <v>18</v>
@@ -11348,7 +11345,7 @@
         <v>2910</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G380" s="8">
         <v>18</v>
@@ -11375,7 +11372,7 @@
         <v>2810</v>
       </c>
       <c r="F381" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G381" s="8">
         <v>18</v>
@@ -11402,7 +11399,7 @@
         <v>3070</v>
       </c>
       <c r="F382" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G382" s="8">
         <v>18</v>
@@ -11429,7 +11426,7 @@
         <v>3440</v>
       </c>
       <c r="F383" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G383" s="8">
         <v>18</v>
@@ -11456,7 +11453,7 @@
         <v>3070</v>
       </c>
       <c r="F384" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G384" s="8">
         <v>18</v>
@@ -11483,7 +11480,7 @@
         <v>2810</v>
       </c>
       <c r="F385" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G385" s="8">
         <v>18</v>
@@ -11496,8 +11493,8 @@
       </c>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A386" t="s">
-        <v>151</v>
+      <c r="A386" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B386" t="s">
         <v>15</v>
@@ -11510,7 +11507,7 @@
         <v>2910</v>
       </c>
       <c r="F386" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G386" s="8">
         <v>18</v>
@@ -11537,7 +11534,7 @@
         <v>2910</v>
       </c>
       <c r="F387" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G387" s="8">
         <v>18</v>
@@ -11564,7 +11561,7 @@
         <v>3230</v>
       </c>
       <c r="F388" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G388" s="8">
         <v>18</v>
@@ -11591,7 +11588,7 @@
         <v>3330</v>
       </c>
       <c r="F389" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G389" s="8">
         <v>18</v>
@@ -11618,7 +11615,7 @@
         <v>3230</v>
       </c>
       <c r="F390" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G390" s="8">
         <v>18</v>
@@ -11645,7 +11642,7 @@
         <v>3070</v>
       </c>
       <c r="F391" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G391" s="8">
         <v>18</v>
@@ -11672,7 +11669,7 @@
         <v>3070</v>
       </c>
       <c r="F392" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G392" s="8">
         <v>18</v>
@@ -11701,7 +11698,7 @@
         <v>2890</v>
       </c>
       <c r="F393" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G393" s="8" t="s">
         <v>119</v>
@@ -11730,7 +11727,7 @@
         <v>2890</v>
       </c>
       <c r="F394" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G394" s="8" t="s">
         <v>119</v>
@@ -11757,7 +11754,7 @@
         <v>2890</v>
       </c>
       <c r="F395" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G395" s="8">
         <v>19</v>
@@ -11784,7 +11781,7 @@
         <v>2890</v>
       </c>
       <c r="F396" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G396" s="8">
         <v>19</v>
@@ -11811,7 +11808,7 @@
         <v>3040</v>
       </c>
       <c r="F397" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G397" s="8">
         <v>19</v>
@@ -11838,7 +11835,7 @@
         <v>3200</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G398" s="8">
         <v>19</v>
@@ -11865,7 +11862,7 @@
         <v>3100</v>
       </c>
       <c r="F399" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G399" s="8">
         <v>19</v>
@@ -11892,7 +11889,7 @@
         <v>3310</v>
       </c>
       <c r="F400" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G400" s="8">
         <v>19</v>
@@ -11919,7 +11916,7 @@
         <v>3100</v>
       </c>
       <c r="F401" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G401" s="8">
         <v>19</v>
@@ -11946,7 +11943,7 @@
         <v>3100</v>
       </c>
       <c r="F402" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G402" s="8">
         <v>19</v>
@@ -11973,7 +11970,7 @@
         <v>3100</v>
       </c>
       <c r="F403" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G403" s="8">
         <v>19</v>
@@ -12000,7 +11997,7 @@
         <v>3100</v>
       </c>
       <c r="F404" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G404" s="8">
         <v>19</v>
@@ -12027,7 +12024,7 @@
         <v>3100</v>
       </c>
       <c r="F405" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G405" s="8">
         <v>19</v>
@@ -12054,7 +12051,7 @@
         <v>3100</v>
       </c>
       <c r="F406" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G406" s="8">
         <v>19</v>
@@ -12081,7 +12078,7 @@
         <v>3100</v>
       </c>
       <c r="F407" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G407" s="8">
         <v>19</v>
@@ -12108,7 +12105,7 @@
         <v>3100</v>
       </c>
       <c r="F408" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G408" s="8">
         <v>19</v>
@@ -12135,7 +12132,7 @@
         <v>3200</v>
       </c>
       <c r="F409" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G409" s="8">
         <v>19</v>
@@ -12164,7 +12161,7 @@
         <v>2890</v>
       </c>
       <c r="F410" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G410" s="8" t="s">
         <v>119</v>
@@ -12193,7 +12190,7 @@
         <v>2890</v>
       </c>
       <c r="F411" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G411" s="8" t="s">
         <v>119</v>
@@ -12220,7 +12217,7 @@
         <v>3100</v>
       </c>
       <c r="F412" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G412" s="8">
         <v>19</v>
@@ -12247,7 +12244,7 @@
         <v>3100</v>
       </c>
       <c r="F413" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G413" s="8">
         <v>19</v>
@@ -12274,7 +12271,7 @@
         <v>3200</v>
       </c>
       <c r="F414" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G414" s="8">
         <v>19</v>
@@ -12301,7 +12298,7 @@
         <v>3100</v>
       </c>
       <c r="F415" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G415" s="8">
         <v>19</v>
@@ -12328,7 +12325,7 @@
         <v>3100</v>
       </c>
       <c r="F416" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G416" s="8">
         <v>19</v>
@@ -12355,7 +12352,7 @@
         <v>2820</v>
       </c>
       <c r="F417" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G417" s="8">
         <v>18</v>
@@ -12382,7 +12379,7 @@
         <v>2820</v>
       </c>
       <c r="F418" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G418" s="8">
         <v>18</v>
@@ -12409,7 +12406,7 @@
         <v>2870</v>
       </c>
       <c r="F419" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G419" s="8">
         <v>18</v>
@@ -12422,8 +12419,8 @@
       </c>
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>151</v>
+      <c r="A420" s="7" t="s">
+        <v>120</v>
       </c>
       <c r="B420" t="s">
         <v>15</v>
@@ -12436,7 +12433,7 @@
         <v>2820</v>
       </c>
       <c r="F420" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G420" s="8">
         <v>18</v>
@@ -12463,7 +12460,7 @@
         <v>3030</v>
       </c>
       <c r="F421" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G421" s="8">
         <v>18</v>
@@ -12490,7 +12487,7 @@
         <v>2920</v>
       </c>
       <c r="F422" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G422" s="8">
         <v>18</v>
@@ -15728,7 +15725,7 @@
       <c r="G984" s="8"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I286" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
+  <autoFilter ref="A1:I422" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31DFDF28-A93C-4C7C-8868-920B0DE3368A}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD0D5424-F3A1-4414-954F-88B237B409A0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -498,7 +498,7 @@
     <t>ONE</t>
   </si>
   <si>
-    <t>15 al 19 de abril</t>
+    <t>15 al 21de abril</t>
   </si>
 </sst>
 </file>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{689C26CF-BD68-47CC-A334-73DC7BB1549E}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B16F9D39-EE54-4BC7-AF0C-64099D6F0110}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="153">
   <si>
     <t>POD</t>
   </si>
@@ -499,6 +499,9 @@
   </si>
   <si>
     <t>15 al 21 de abril</t>
+  </si>
+  <si>
+    <t>GUAYAQUIL/POSORJA</t>
   </si>
 </sst>
 </file>
@@ -2622,10 +2625,10 @@
       </c>
       <c r="C59" s="11"/>
       <c r="D59" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E59" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>150</v>
@@ -2649,10 +2652,10 @@
       </c>
       <c r="C60" s="11"/>
       <c r="D60" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E60" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F60" s="7" t="s">
         <v>150</v>
@@ -2676,10 +2679,10 @@
       </c>
       <c r="C61" s="11"/>
       <c r="D61" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E61" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>150</v>
@@ -2703,10 +2706,10 @@
       </c>
       <c r="C62" s="11"/>
       <c r="D62" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E62" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F62" s="7" t="s">
         <v>150</v>
@@ -2730,10 +2733,10 @@
       </c>
       <c r="C63" s="11"/>
       <c r="D63" s="11">
-        <v>2740</v>
+        <v>2560</v>
       </c>
       <c r="E63" s="11">
-        <v>2850</v>
+        <v>2660</v>
       </c>
       <c r="F63" s="7" t="s">
         <v>150</v>
@@ -2757,10 +2760,10 @@
       </c>
       <c r="C64" s="11"/>
       <c r="D64" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E64" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="F64" s="7" t="s">
         <v>150</v>
@@ -2784,10 +2787,10 @@
       </c>
       <c r="C65" s="11"/>
       <c r="D65" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="E65" s="11">
-        <v>3630</v>
+        <v>3460</v>
       </c>
       <c r="F65" s="7" t="s">
         <v>150</v>
@@ -2811,10 +2814,10 @@
       </c>
       <c r="C66" s="11"/>
       <c r="D66" s="11">
-        <v>3000</v>
+        <v>2860</v>
       </c>
       <c r="E66" s="11">
-        <v>3270</v>
+        <v>3110</v>
       </c>
       <c r="F66" s="7" t="s">
         <v>150</v>
@@ -2838,10 +2841,10 @@
       </c>
       <c r="C67" s="11"/>
       <c r="D67" s="11">
-        <v>3060</v>
+        <v>2910</v>
       </c>
       <c r="E67" s="11">
-        <v>3320</v>
+        <v>3160</v>
       </c>
       <c r="F67" s="7" t="s">
         <v>150</v>
@@ -2865,10 +2868,10 @@
       </c>
       <c r="C68" s="11"/>
       <c r="D68" s="11">
-        <v>3160</v>
+        <v>3010</v>
       </c>
       <c r="E68" s="11">
-        <v>3530</v>
+        <v>3360</v>
       </c>
       <c r="F68" s="7" t="s">
         <v>150</v>
@@ -2892,10 +2895,10 @@
       </c>
       <c r="C69" s="11"/>
       <c r="D69" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E69" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="F69" s="7" t="s">
         <v>150</v>
@@ -2919,10 +2922,10 @@
       </c>
       <c r="C70" s="11"/>
       <c r="D70" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E70" s="11">
         <v>3110</v>
-      </c>
-      <c r="E70" s="11">
-        <v>3270</v>
       </c>
       <c r="F70" s="7" t="s">
         <v>150</v>
@@ -2946,10 +2949,10 @@
       </c>
       <c r="C71" s="11"/>
       <c r="D71" s="11">
-        <v>2900</v>
+        <v>2760</v>
       </c>
       <c r="E71" s="11">
-        <v>3210</v>
+        <v>3060</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>150</v>
@@ -2973,10 +2976,10 @@
       </c>
       <c r="C72" s="11"/>
       <c r="D72" s="11">
-        <v>3060</v>
+        <v>2910</v>
       </c>
       <c r="E72" s="11">
-        <v>3420</v>
+        <v>3260</v>
       </c>
       <c r="F72" s="7" t="s">
         <v>150</v>
@@ -3000,10 +3003,10 @@
       </c>
       <c r="C73" s="11"/>
       <c r="D73" s="11">
-        <v>3000</v>
+        <v>2860</v>
       </c>
       <c r="E73" s="11">
-        <v>3160</v>
+        <v>3010</v>
       </c>
       <c r="F73" s="7" t="s">
         <v>150</v>
@@ -3027,10 +3030,10 @@
       </c>
       <c r="C74" s="11"/>
       <c r="D74" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="E74" s="11">
-        <v>3370</v>
+        <v>3210</v>
       </c>
       <c r="F74" s="7" t="s">
         <v>150</v>
@@ -3054,10 +3057,10 @@
       </c>
       <c r="C75" s="11"/>
       <c r="D75" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E75" s="11">
-        <v>3160</v>
+        <v>3010</v>
       </c>
       <c r="F75" s="7" t="s">
         <v>150</v>
@@ -3081,10 +3084,10 @@
       </c>
       <c r="C76" s="11"/>
       <c r="D76" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E76" s="11">
-        <v>3270</v>
+        <v>3110</v>
       </c>
       <c r="F76" s="7" t="s">
         <v>150</v>
@@ -3108,10 +3111,10 @@
       </c>
       <c r="C77" s="11"/>
       <c r="D77" s="11">
-        <v>2740</v>
+        <v>2610</v>
       </c>
       <c r="E77" s="11">
-        <v>2900</v>
+        <v>2760</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>150</v>
@@ -3189,10 +3192,10 @@
       </c>
       <c r="C80" s="11"/>
       <c r="D80" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E80" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F80" s="7" t="s">
         <v>150</v>
@@ -3216,10 +3219,10 @@
       </c>
       <c r="C81" s="11"/>
       <c r="D81" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="E81" s="11">
-        <v>3320</v>
+        <v>3160</v>
       </c>
       <c r="F81" s="7" t="s">
         <v>150</v>
@@ -3243,10 +3246,10 @@
       </c>
       <c r="C82" s="11"/>
       <c r="D82" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E82" s="11">
-        <v>3270</v>
+        <v>3110</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>150</v>
@@ -3270,10 +3273,10 @@
       </c>
       <c r="C83" s="11"/>
       <c r="D83" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E83" s="11">
-        <v>3160</v>
+        <v>3010</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>150</v>
@@ -3297,10 +3300,10 @@
       </c>
       <c r="C84" s="11"/>
       <c r="D84" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E84" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>150</v>
@@ -3324,10 +3327,10 @@
       </c>
       <c r="C85" s="11"/>
       <c r="D85" s="11">
-        <v>3060</v>
+        <v>2910</v>
       </c>
       <c r="E85" s="11">
-        <v>3420</v>
+        <v>3260</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>150</v>
@@ -3351,10 +3354,10 @@
       </c>
       <c r="C86" s="11"/>
       <c r="D86" s="11">
-        <v>2690</v>
+        <v>2560</v>
       </c>
       <c r="E86" s="11">
-        <v>2790</v>
+        <v>2660</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>150</v>
@@ -3378,10 +3381,10 @@
       </c>
       <c r="C87" s="11"/>
       <c r="D87" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="E87" s="11">
-        <v>3420</v>
+        <v>3260</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>150</v>
@@ -3405,10 +3408,10 @@
       </c>
       <c r="C88" s="11"/>
       <c r="D88" s="11">
-        <v>2950</v>
+        <v>2810</v>
       </c>
       <c r="E88" s="11">
-        <v>3110</v>
+        <v>2960</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>150</v>
@@ -3432,10 +3435,10 @@
       </c>
       <c r="C89" s="11"/>
       <c r="D89" s="11">
+        <v>2960</v>
+      </c>
+      <c r="E89" s="11">
         <v>3110</v>
-      </c>
-      <c r="E89" s="11">
-        <v>3270</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>150</v>
@@ -4566,7 +4569,7 @@
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C131" s="11"/>
       <c r="D131" s="11">
@@ -4593,7 +4596,7 @@
         <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C132" s="11"/>
       <c r="D132" s="11">
@@ -4620,7 +4623,7 @@
         <v>107</v>
       </c>
       <c r="B133" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C133" s="11"/>
       <c r="D133" s="11">
@@ -4647,7 +4650,7 @@
         <v>108</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C134" s="11"/>
       <c r="D134" s="11">
@@ -4674,7 +4677,7 @@
         <v>109</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C135" s="11"/>
       <c r="D135" s="11">
@@ -4701,7 +4704,7 @@
         <v>52</v>
       </c>
       <c r="B136" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C136" s="11"/>
       <c r="D136" s="11">
@@ -4728,7 +4731,7 @@
         <v>35</v>
       </c>
       <c r="B137" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C137" s="11"/>
       <c r="D137" s="11">
@@ -4755,7 +4758,7 @@
         <v>24</v>
       </c>
       <c r="B138" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C138" s="11"/>
       <c r="D138" s="11">
@@ -4782,7 +4785,7 @@
         <v>50</v>
       </c>
       <c r="B139" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C139" s="11"/>
       <c r="D139" s="11">
@@ -4809,7 +4812,7 @@
         <v>29</v>
       </c>
       <c r="B140" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C140" s="11"/>
       <c r="D140" s="11">
@@ -4836,7 +4839,7 @@
         <v>27</v>
       </c>
       <c r="B141" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C141" s="11"/>
       <c r="D141" s="11">
@@ -4863,7 +4866,7 @@
         <v>48</v>
       </c>
       <c r="B142" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C142" s="11"/>
       <c r="D142" s="11">
@@ -4890,7 +4893,7 @@
         <v>33</v>
       </c>
       <c r="B143" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C143" s="11"/>
       <c r="D143" s="11">
@@ -4917,7 +4920,7 @@
         <v>111</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C144" s="11"/>
       <c r="D144" s="11">
@@ -4944,7 +4947,7 @@
         <v>30</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C145" s="11"/>
       <c r="D145" s="11">
@@ -4971,7 +4974,7 @@
         <v>56</v>
       </c>
       <c r="B146" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C146" s="11"/>
       <c r="D146" s="11">
@@ -4998,7 +5001,7 @@
         <v>28</v>
       </c>
       <c r="B147" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C147" s="11"/>
       <c r="D147" s="11">
@@ -5025,7 +5028,7 @@
         <v>57</v>
       </c>
       <c r="B148" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C148" s="11"/>
       <c r="D148" s="11">
@@ -5052,7 +5055,7 @@
         <v>13</v>
       </c>
       <c r="B149" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C149" s="11"/>
       <c r="D149" s="11">
@@ -5079,7 +5082,7 @@
         <v>112</v>
       </c>
       <c r="B150" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C150" s="11"/>
       <c r="D150" s="11">
@@ -5106,7 +5109,7 @@
         <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C151" s="11"/>
       <c r="D151" s="11">
@@ -5133,7 +5136,7 @@
         <v>19</v>
       </c>
       <c r="B152" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C152" s="11"/>
       <c r="D152" s="11">
@@ -5160,7 +5163,7 @@
         <v>21</v>
       </c>
       <c r="B153" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C153" s="11"/>
       <c r="D153" s="11">
@@ -5187,7 +5190,7 @@
         <v>51</v>
       </c>
       <c r="B154" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C154" s="11"/>
       <c r="D154" s="11">
@@ -5214,7 +5217,7 @@
         <v>53</v>
       </c>
       <c r="B155" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C155" s="11"/>
       <c r="D155" s="11">
@@ -5241,7 +5244,7 @@
         <v>113</v>
       </c>
       <c r="B156" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C156" s="11"/>
       <c r="D156" s="11">
@@ -5268,7 +5271,7 @@
         <v>16</v>
       </c>
       <c r="B157" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C157" s="11"/>
       <c r="D157" s="11">
@@ -5295,7 +5298,7 @@
         <v>120</v>
       </c>
       <c r="B158" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C158" s="11"/>
       <c r="D158" s="11">
@@ -5322,7 +5325,7 @@
         <v>20</v>
       </c>
       <c r="B159" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C159" s="11"/>
       <c r="D159" s="11">
@@ -5349,7 +5352,7 @@
         <v>55</v>
       </c>
       <c r="B160" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C160" s="11"/>
       <c r="D160" s="11">
@@ -5376,7 +5379,7 @@
         <v>31</v>
       </c>
       <c r="B161" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C161" s="11"/>
       <c r="D161" s="11">
@@ -5403,7 +5406,7 @@
         <v>54</v>
       </c>
       <c r="B162" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C162" s="11"/>
       <c r="D162" s="11">
@@ -5430,7 +5433,7 @@
         <v>26</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C163" s="11"/>
       <c r="D163" s="11">
@@ -5457,7 +5460,7 @@
         <v>49</v>
       </c>
       <c r="B164" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="C164" s="11"/>
       <c r="D164" s="11">

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DCCF5B2C-ACE2-4889-BD5C-02DEF6F42B2F}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4657E206-01F6-4964-BC52-5C1BECE2A02E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,9 +453,6 @@
     <t>COSCO</t>
   </si>
   <si>
-    <t>1 al 16 de abril</t>
-  </si>
-  <si>
     <t>SHIMIZU</t>
   </si>
   <si>
@@ -520,6 +517,9 @@
   </si>
   <si>
     <t>16 al 31 de abril</t>
+  </si>
+  <si>
+    <t>15 al 30 de abril</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:I665"/>
+  <dimension ref="A1:K665"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1034,7 +1034,7 @@
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>2</v>
       </c>
@@ -1063,7 +1063,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1074,13 +1074,13 @@
         <v>12</v>
       </c>
       <c r="D2" s="12">
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="E2" s="12">
-        <v>400</v>
+        <v>660</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G2" s="7" t="s">
         <v>73</v>
@@ -1091,8 +1091,10 @@
       <c r="I2" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1103,13 +1105,13 @@
         <v>12</v>
       </c>
       <c r="D3" s="12">
-        <v>320</v>
+        <v>450</v>
       </c>
       <c r="E3" s="12">
-        <v>570</v>
+        <v>830</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>73</v>
@@ -1120,8 +1122,10 @@
       <c r="I3" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -1132,13 +1136,13 @@
         <v>12</v>
       </c>
       <c r="D4" s="9">
-        <v>1620</v>
+        <v>1885</v>
       </c>
       <c r="E4" s="9">
-        <v>2460</v>
+        <v>2990</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>73</v>
@@ -1149,8 +1153,10 @@
       <c r="I4" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -1161,13 +1167,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="9">
-        <v>1620</v>
+        <v>1885</v>
       </c>
       <c r="E5" s="9">
-        <v>2460</v>
+        <v>2990</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>73</v>
@@ -1178,8 +1184,10 @@
       <c r="I5" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -1190,13 +1198,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="9">
-        <v>1410</v>
+        <v>1675</v>
       </c>
       <c r="E6" s="9">
-        <v>2630</v>
+        <v>3160</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>73</v>
@@ -1207,8 +1215,10 @@
       <c r="I6" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1219,13 +1229,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="9">
-        <v>1410</v>
+        <v>1675</v>
       </c>
       <c r="E7" s="9">
-        <v>2630</v>
+        <v>3160</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>73</v>
@@ -1236,8 +1246,10 @@
       <c r="I7" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -1248,13 +1260,13 @@
         <v>12</v>
       </c>
       <c r="D8" s="9">
-        <v>1870</v>
+        <v>2135</v>
       </c>
       <c r="E8" s="9">
-        <v>2910</v>
+        <v>3440</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>73</v>
@@ -1265,8 +1277,10 @@
       <c r="I8" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -1277,13 +1291,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="9">
-        <v>1870</v>
+        <v>2135</v>
       </c>
       <c r="E9" s="9">
-        <v>2910</v>
+        <v>3440</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>73</v>
@@ -1294,8 +1308,10 @@
       <c r="I9" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1306,13 +1322,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="9">
-        <v>1870</v>
+        <v>2135</v>
       </c>
       <c r="E10" s="9">
-        <v>2910</v>
+        <v>3440</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>73</v>
@@ -1323,8 +1339,10 @@
       <c r="I10" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -1335,13 +1353,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="9">
-        <v>2370</v>
+        <v>2635</v>
       </c>
       <c r="E11" s="9">
-        <v>3580</v>
+        <v>4110</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>73</v>
@@ -1352,8 +1370,10 @@
       <c r="I11" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1364,13 +1384,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="9">
-        <v>1870</v>
+        <v>2135</v>
       </c>
       <c r="E12" s="9">
-        <v>2910</v>
+        <v>3440</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>73</v>
@@ -1381,8 +1401,10 @@
       <c r="I12" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -1393,13 +1415,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="9">
-        <v>2150</v>
+        <v>2415</v>
       </c>
       <c r="E13" s="9">
-        <v>3230</v>
+        <v>3760</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>73</v>
@@ -1410,8 +1432,10 @@
       <c r="I13" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1422,13 +1446,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="9">
-        <v>2370</v>
+        <v>2635</v>
       </c>
       <c r="E14" s="9">
-        <v>3580</v>
+        <v>4110</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>73</v>
@@ -1439,8 +1463,10 @@
       <c r="I14" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -1451,13 +1477,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="9">
-        <v>2650</v>
+        <v>2915</v>
       </c>
       <c r="E15" s="9">
-        <v>3900</v>
+        <v>4430</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>73</v>
@@ -1468,8 +1494,10 @@
       <c r="I15" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -1480,13 +1508,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="9">
-        <v>2370</v>
+        <v>2635</v>
       </c>
       <c r="E16" s="9">
-        <v>3580</v>
+        <v>4110</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>73</v>
@@ -1497,8 +1525,10 @@
       <c r="I16" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -1509,13 +1539,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="9">
-        <v>2370</v>
+        <v>2635</v>
       </c>
       <c r="E17" s="9">
-        <v>3580</v>
+        <v>4110</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>73</v>
@@ -1526,8 +1556,10 @@
       <c r="I17" s="7" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1542,7 +1574,7 @@
         <v>2660</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G18" s="8">
         <v>14</v>
@@ -1554,7 +1586,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1569,7 +1601,7 @@
         <v>2660</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G19" s="8">
         <v>14</v>
@@ -1581,7 +1613,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -1596,7 +1628,7 @@
         <v>2660</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G20" s="8">
         <v>14</v>
@@ -1608,7 +1640,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>105</v>
       </c>
@@ -1623,7 +1655,7 @@
         <v>2660</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G21" s="8">
         <v>14</v>
@@ -1635,7 +1667,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>106</v>
       </c>
@@ -1650,7 +1682,7 @@
         <v>2660</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G22" s="8">
         <v>14</v>
@@ -1662,7 +1694,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1677,7 +1709,7 @@
         <v>2960</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G23" s="8">
         <v>14</v>
@@ -1689,7 +1721,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -1704,7 +1736,7 @@
         <v>3460</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G24" s="8">
         <v>14</v>
@@ -1716,7 +1748,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1731,7 +1763,7 @@
         <v>3110</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G25" s="8">
         <v>14</v>
@@ -1743,7 +1775,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1758,7 +1790,7 @@
         <v>3160</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G26" s="8">
         <v>14</v>
@@ -1770,7 +1802,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1785,7 +1817,7 @@
         <v>3360</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G27" s="8">
         <v>14</v>
@@ -1797,7 +1829,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1812,7 +1844,7 @@
         <v>2960</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G28" s="8">
         <v>14</v>
@@ -1824,7 +1856,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -1839,7 +1871,7 @@
         <v>3110</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G29" s="8">
         <v>14</v>
@@ -1851,7 +1883,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1866,7 +1898,7 @@
         <v>3060</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G30" s="8">
         <v>14</v>
@@ -1878,7 +1910,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -1893,7 +1925,7 @@
         <v>3260</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G31" s="8">
         <v>14</v>
@@ -1905,7 +1937,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>56</v>
       </c>
@@ -1920,7 +1952,7 @@
         <v>3010</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G32" s="8">
         <v>14</v>
@@ -1947,7 +1979,7 @@
         <v>3210</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G33" s="8">
         <v>14</v>
@@ -1974,7 +2006,7 @@
         <v>3010</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G34" s="8">
         <v>14</v>
@@ -2001,7 +2033,7 @@
         <v>3110</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G35" s="8">
         <v>14</v>
@@ -2028,7 +2060,7 @@
         <v>2760</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G36" s="8">
         <v>14</v>
@@ -2055,7 +2087,7 @@
         <v>3210</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G37" s="8">
         <v>14</v>
@@ -2082,7 +2114,7 @@
         <v>3270</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G38" s="8">
         <v>14</v>
@@ -2109,7 +2141,7 @@
         <v>2660</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G39" s="8">
         <v>14</v>
@@ -2136,7 +2168,7 @@
         <v>3160</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G40" s="8">
         <v>14</v>
@@ -2163,7 +2195,7 @@
         <v>3110</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G41" s="8">
         <v>14</v>
@@ -2190,7 +2222,7 @@
         <v>3010</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G42" s="8">
         <v>14</v>
@@ -2217,7 +2249,7 @@
         <v>2660</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G43" s="8">
         <v>14</v>
@@ -2244,7 +2276,7 @@
         <v>3260</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G44" s="8">
         <v>14</v>
@@ -2271,7 +2303,7 @@
         <v>2660</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G45" s="8">
         <v>14</v>
@@ -2298,7 +2330,7 @@
         <v>3260</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G46" s="8">
         <v>14</v>
@@ -2325,7 +2357,7 @@
         <v>2960</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G47" s="8">
         <v>14</v>
@@ -2352,7 +2384,7 @@
         <v>3110</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G48" s="8">
         <v>14</v>
@@ -2379,7 +2411,7 @@
         <v>3160</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G49" s="8">
         <v>14</v>
@@ -2406,7 +2438,7 @@
         <v>3270</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G50" s="8">
         <v>14</v>
@@ -2433,7 +2465,7 @@
         <v>3320</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G51" s="8">
         <v>14</v>
@@ -2462,7 +2494,7 @@
         <v>2880</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G52" s="8" t="s">
         <v>134</v>
@@ -2489,7 +2521,7 @@
         <v>2880</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G53" s="8">
         <v>17</v>
@@ -2516,7 +2548,7 @@
         <v>2880</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G54" s="8">
         <v>17</v>
@@ -2543,7 +2575,7 @@
         <v>3040</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G55" s="8">
         <v>17</v>
@@ -2570,7 +2602,7 @@
         <v>3440</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G56" s="8">
         <v>17</v>
@@ -2597,7 +2629,7 @@
         <v>2980</v>
       </c>
       <c r="F57" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G57" s="8">
         <v>17</v>
@@ -2624,7 +2656,7 @@
         <v>3060</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G58" s="8">
         <v>17</v>
@@ -2651,7 +2683,7 @@
         <v>2980</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G59" s="8">
         <v>17</v>
@@ -2678,7 +2710,7 @@
         <v>3090</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G60" s="8">
         <v>17</v>
@@ -2705,7 +2737,7 @@
         <v>3070</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G61" s="8">
         <v>17</v>
@@ -2732,7 +2764,7 @@
         <v>3090</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G62" s="8">
         <v>17</v>
@@ -2759,7 +2791,7 @@
         <v>3050</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G63" s="8">
         <v>17</v>
@@ -2786,7 +2818,7 @@
         <v>3190</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G64" s="8">
         <v>17</v>
@@ -2813,7 +2845,7 @@
         <v>3090</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G65" s="8">
         <v>17</v>
@@ -2827,7 +2859,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
@@ -2840,7 +2872,7 @@
         <v>3060</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G66" s="8">
         <v>17</v>
@@ -2867,7 +2899,7 @@
         <v>3030</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G67" s="8">
         <v>17</v>
@@ -2894,7 +2926,7 @@
         <v>3300</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G68" s="8">
         <v>17</v>
@@ -2921,7 +2953,7 @@
         <v>3060</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G69" s="8">
         <v>17</v>
@@ -2948,7 +2980,7 @@
         <v>3030</v>
       </c>
       <c r="F70" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G70" s="8">
         <v>17</v>
@@ -2975,7 +3007,7 @@
         <v>2980</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G71" s="8">
         <v>17</v>
@@ -3002,7 +3034,7 @@
         <v>3060</v>
       </c>
       <c r="F72" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G72" s="8">
         <v>17</v>
@@ -3029,7 +3061,7 @@
         <v>3040</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G73" s="8">
         <v>17</v>
@@ -3056,7 +3088,7 @@
         <v>3150</v>
       </c>
       <c r="F74" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G74" s="8">
         <v>17</v>
@@ -3083,7 +3115,7 @@
         <v>2880</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G75" s="8">
         <v>17</v>
@@ -3110,7 +3142,7 @@
         <v>2880</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G76" s="8">
         <v>17</v>
@@ -3137,7 +3169,7 @@
         <v>3060</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G77" s="8">
         <v>17</v>
@@ -3164,7 +3196,7 @@
         <v>3180</v>
       </c>
       <c r="F78" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G78" s="8">
         <v>17</v>
@@ -3191,7 +3223,7 @@
         <v>3090</v>
       </c>
       <c r="F79" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G79" s="8">
         <v>17</v>
@@ -3218,7 +3250,7 @@
         <v>2980</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G80" s="8">
         <v>17</v>
@@ -3247,7 +3279,7 @@
         <v>2880</v>
       </c>
       <c r="F81" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>134</v>
@@ -3261,7 +3293,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B82" t="s">
         <v>15</v>
@@ -3274,7 +3306,7 @@
         <v>3030</v>
       </c>
       <c r="F82" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G82" s="8">
         <v>17</v>
@@ -3301,7 +3333,7 @@
         <v>2880</v>
       </c>
       <c r="F83" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G83" s="8">
         <v>17</v>
@@ -3328,7 +3360,7 @@
         <v>3360</v>
       </c>
       <c r="F84" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G84" s="8">
         <v>17</v>
@@ -3355,7 +3387,7 @@
         <v>3030</v>
       </c>
       <c r="F85" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G85" s="8">
         <v>17</v>
@@ -3382,7 +3414,7 @@
         <v>3090</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G86" s="8">
         <v>17</v>
@@ -3409,7 +3441,7 @@
         <v>3030</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G87" s="8">
         <v>17</v>
@@ -3436,7 +3468,7 @@
         <v>3060</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G88" s="8">
         <v>17</v>
@@ -3463,7 +3495,7 @@
         <v>3060</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G89" s="8">
         <v>17</v>
@@ -3480,7 +3512,7 @@
         <v>5</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C90" s="11"/>
       <c r="D90" s="11">
@@ -3490,13 +3522,13 @@
         <v>2810</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G90" s="8">
         <v>18</v>
       </c>
       <c r="H90" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>115</v>
@@ -3507,7 +3539,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C91" s="11"/>
       <c r="D91" s="11">
@@ -3517,13 +3549,13 @@
         <v>2810</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G91" s="8">
         <v>18</v>
       </c>
       <c r="H91" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>115</v>
@@ -3534,7 +3566,7 @@
         <v>104</v>
       </c>
       <c r="B92" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C92" s="11"/>
       <c r="D92" s="11">
@@ -3544,13 +3576,13 @@
         <v>2810</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G92" s="8">
         <v>18</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>115</v>
@@ -3561,7 +3593,7 @@
         <v>105</v>
       </c>
       <c r="B93" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C93" s="11"/>
       <c r="D93" s="11">
@@ -3571,13 +3603,13 @@
         <v>2810</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G93" s="8">
         <v>18</v>
       </c>
       <c r="H93" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>115</v>
@@ -3588,7 +3620,7 @@
         <v>106</v>
       </c>
       <c r="B94" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C94" s="11"/>
       <c r="D94" s="11">
@@ -3598,13 +3630,13 @@
         <v>2860</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G94" s="8">
         <v>18</v>
       </c>
       <c r="H94" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I94" s="7" t="s">
         <v>115</v>
@@ -3615,7 +3647,7 @@
         <v>52</v>
       </c>
       <c r="B95" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C95" s="11"/>
       <c r="D95" s="11">
@@ -3625,13 +3657,13 @@
         <v>3070</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G95" s="8">
         <v>18</v>
       </c>
       <c r="H95" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I95" s="7" t="s">
         <v>115</v>
@@ -3642,7 +3674,7 @@
         <v>35</v>
       </c>
       <c r="B96" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C96" s="11"/>
       <c r="D96" s="11">
@@ -3652,13 +3684,13 @@
         <v>3750</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G96" s="8">
         <v>18</v>
       </c>
       <c r="H96" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>115</v>
@@ -3669,7 +3701,7 @@
         <v>24</v>
       </c>
       <c r="B97" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C97" s="11"/>
       <c r="D97" s="11">
@@ -3679,13 +3711,13 @@
         <v>2910</v>
       </c>
       <c r="F97" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G97" s="8">
         <v>18</v>
       </c>
       <c r="H97" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I97" s="7" t="s">
         <v>115</v>
@@ -3696,7 +3728,7 @@
         <v>50</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C98" s="11"/>
       <c r="D98" s="11">
@@ -3706,13 +3738,13 @@
         <v>3070</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G98" s="8">
         <v>18</v>
       </c>
       <c r="H98" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>115</v>
@@ -3723,7 +3755,7 @@
         <v>29</v>
       </c>
       <c r="B99" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C99" s="11"/>
       <c r="D99" s="11">
@@ -3733,13 +3765,13 @@
         <v>3230</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G99" s="8">
         <v>18</v>
       </c>
       <c r="H99" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>115</v>
@@ -3750,7 +3782,7 @@
         <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C100" s="11"/>
       <c r="D100" s="11">
@@ -3760,13 +3792,13 @@
         <v>3020</v>
       </c>
       <c r="F100" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G100" s="8">
         <v>18</v>
       </c>
       <c r="H100" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I100" s="7" t="s">
         <v>115</v>
@@ -3777,7 +3809,7 @@
         <v>48</v>
       </c>
       <c r="B101" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C101" s="11"/>
       <c r="D101" s="11">
@@ -3787,13 +3819,13 @@
         <v>3070</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G101" s="8">
         <v>18</v>
       </c>
       <c r="H101" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I101" s="7" t="s">
         <v>115</v>
@@ -3804,7 +3836,7 @@
         <v>33</v>
       </c>
       <c r="B102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C102" s="11"/>
       <c r="D102" s="11">
@@ -3814,13 +3846,13 @@
         <v>3330</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G102" s="8">
         <v>18</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>115</v>
@@ -3831,7 +3863,7 @@
         <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C103" s="11"/>
       <c r="D103" s="11">
@@ -3841,13 +3873,13 @@
         <v>3330</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G103" s="8">
         <v>18</v>
       </c>
       <c r="H103" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>115</v>
@@ -3858,7 +3890,7 @@
         <v>30</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C104" s="11"/>
       <c r="D104" s="11">
@@ -3868,13 +3900,13 @@
         <v>3540</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G104" s="8">
         <v>18</v>
       </c>
       <c r="H104" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>115</v>
@@ -3885,7 +3917,7 @@
         <v>56</v>
       </c>
       <c r="B105" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C105" s="11"/>
       <c r="D105" s="11">
@@ -3895,13 +3927,13 @@
         <v>3120</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G105" s="8">
         <v>18</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I105" s="7" t="s">
         <v>115</v>
@@ -3912,7 +3944,7 @@
         <v>28</v>
       </c>
       <c r="B106" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C106" s="11"/>
       <c r="D106" s="11">
@@ -3922,13 +3954,13 @@
         <v>3070</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G106" s="8">
         <v>18</v>
       </c>
       <c r="H106" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I106" s="7" t="s">
         <v>115</v>
@@ -3939,7 +3971,7 @@
         <v>57</v>
       </c>
       <c r="B107" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C107" s="11"/>
       <c r="D107" s="11">
@@ -3949,13 +3981,13 @@
         <v>3230</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G107" s="8">
         <v>18</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I107" s="7" t="s">
         <v>115</v>
@@ -3966,7 +3998,7 @@
         <v>13</v>
       </c>
       <c r="B108" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C108" s="11"/>
       <c r="D108" s="11">
@@ -3976,13 +4008,13 @@
         <v>3020</v>
       </c>
       <c r="F108" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G108" s="8">
         <v>18</v>
       </c>
       <c r="H108" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I108" s="7" t="s">
         <v>115</v>
@@ -3993,7 +4025,7 @@
         <v>109</v>
       </c>
       <c r="B109" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C109" s="11"/>
       <c r="D109" s="11">
@@ -4003,13 +4035,13 @@
         <v>3070</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G109" s="8">
         <v>18</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I109" s="7" t="s">
         <v>115</v>
@@ -4020,7 +4052,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C110" s="11"/>
       <c r="D110" s="11">
@@ -4030,13 +4062,13 @@
         <v>3070</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G110" s="8">
         <v>18</v>
       </c>
       <c r="H110" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>115</v>
@@ -4047,7 +4079,7 @@
         <v>19</v>
       </c>
       <c r="B111" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C111" s="11"/>
       <c r="D111" s="11">
@@ -4057,13 +4089,13 @@
         <v>2910</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G111" s="8">
         <v>18</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>115</v>
@@ -4074,7 +4106,7 @@
         <v>21</v>
       </c>
       <c r="B112" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C112" s="11"/>
       <c r="D112" s="11">
@@ -4084,13 +4116,13 @@
         <v>2810</v>
       </c>
       <c r="F112" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G112" s="8">
         <v>18</v>
       </c>
       <c r="H112" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I112" s="7" t="s">
         <v>115</v>
@@ -4101,7 +4133,7 @@
         <v>51</v>
       </c>
       <c r="B113" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C113" s="11"/>
       <c r="D113" s="11">
@@ -4111,13 +4143,13 @@
         <v>3070</v>
       </c>
       <c r="F113" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G113" s="8">
         <v>18</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I113" s="7" t="s">
         <v>115</v>
@@ -4128,7 +4160,7 @@
         <v>53</v>
       </c>
       <c r="B114" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C114" s="11"/>
       <c r="D114" s="11">
@@ -4138,13 +4170,13 @@
         <v>3440</v>
       </c>
       <c r="F114" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G114" s="8">
         <v>18</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I114" s="7" t="s">
         <v>115</v>
@@ -4155,7 +4187,7 @@
         <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C115" s="11"/>
       <c r="D115" s="11">
@@ -4165,13 +4197,13 @@
         <v>3070</v>
       </c>
       <c r="F115" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G115" s="8">
         <v>18</v>
       </c>
       <c r="H115" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I115" s="7" t="s">
         <v>115</v>
@@ -4182,7 +4214,7 @@
         <v>16</v>
       </c>
       <c r="B116" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C116" s="11"/>
       <c r="D116" s="11">
@@ -4192,13 +4224,13 @@
         <v>2810</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G116" s="8">
         <v>18</v>
       </c>
       <c r="H116" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>115</v>
@@ -4209,7 +4241,7 @@
         <v>117</v>
       </c>
       <c r="B117" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C117" s="11"/>
       <c r="D117" s="11">
@@ -4219,13 +4251,13 @@
         <v>2910</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G117" s="8">
         <v>18</v>
       </c>
       <c r="H117" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>115</v>
@@ -4236,7 +4268,7 @@
         <v>20</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C118" s="11"/>
       <c r="D118" s="11">
@@ -4246,13 +4278,13 @@
         <v>2910</v>
       </c>
       <c r="F118" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G118" s="8">
         <v>18</v>
       </c>
       <c r="H118" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>115</v>
@@ -4263,7 +4295,7 @@
         <v>55</v>
       </c>
       <c r="B119" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C119" s="11"/>
       <c r="D119" s="11">
@@ -4273,13 +4305,13 @@
         <v>3230</v>
       </c>
       <c r="F119" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G119" s="8">
         <v>18</v>
       </c>
       <c r="H119" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>115</v>
@@ -4290,7 +4322,7 @@
         <v>31</v>
       </c>
       <c r="B120" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C120" s="11"/>
       <c r="D120" s="11">
@@ -4300,13 +4332,13 @@
         <v>3330</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G120" s="8">
         <v>18</v>
       </c>
       <c r="H120" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>115</v>
@@ -4317,7 +4349,7 @@
         <v>54</v>
       </c>
       <c r="B121" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C121" s="11"/>
       <c r="D121" s="11">
@@ -4327,13 +4359,13 @@
         <v>3230</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G121" s="8">
         <v>18</v>
       </c>
       <c r="H121" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I121" s="7" t="s">
         <v>115</v>
@@ -4344,7 +4376,7 @@
         <v>26</v>
       </c>
       <c r="B122" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C122" s="11"/>
       <c r="D122" s="11">
@@ -4354,13 +4386,13 @@
         <v>3070</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G122" s="8">
         <v>18</v>
       </c>
       <c r="H122" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I122" s="7" t="s">
         <v>115</v>
@@ -4371,7 +4403,7 @@
         <v>49</v>
       </c>
       <c r="B123" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C123" s="11"/>
       <c r="D123" s="11">
@@ -4381,13 +4413,13 @@
         <v>3070</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G123" s="8">
         <v>18</v>
       </c>
       <c r="H123" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>115</v>
@@ -4410,7 +4442,7 @@
         <v>2890</v>
       </c>
       <c r="F124" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>116</v>
@@ -4439,7 +4471,7 @@
         <v>2890</v>
       </c>
       <c r="F125" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G125" s="8" t="s">
         <v>116</v>
@@ -4466,7 +4498,7 @@
         <v>2890</v>
       </c>
       <c r="F126" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G126" s="8">
         <v>19</v>
@@ -4493,7 +4525,7 @@
         <v>2890</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G127" s="8">
         <v>19</v>
@@ -4520,7 +4552,7 @@
         <v>3040</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G128" s="8">
         <v>19</v>
@@ -4547,7 +4579,7 @@
         <v>3200</v>
       </c>
       <c r="F129" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G129" s="8">
         <v>19</v>
@@ -4574,7 +4606,7 @@
         <v>3100</v>
       </c>
       <c r="F130" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G130" s="8">
         <v>19</v>
@@ -4601,7 +4633,7 @@
         <v>3310</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G131" s="8">
         <v>19</v>
@@ -4628,7 +4660,7 @@
         <v>3100</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G132" s="8">
         <v>19</v>
@@ -4655,7 +4687,7 @@
         <v>3100</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G133" s="8">
         <v>19</v>
@@ -4682,7 +4714,7 @@
         <v>3100</v>
       </c>
       <c r="F134" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G134" s="8">
         <v>19</v>
@@ -4709,7 +4741,7 @@
         <v>3100</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G135" s="8">
         <v>19</v>
@@ -4736,7 +4768,7 @@
         <v>3100</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G136" s="8">
         <v>19</v>
@@ -4763,7 +4795,7 @@
         <v>3100</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G137" s="8">
         <v>19</v>
@@ -4790,7 +4822,7 @@
         <v>3100</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G138" s="8">
         <v>19</v>
@@ -4817,7 +4849,7 @@
         <v>3100</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G139" s="8">
         <v>19</v>
@@ -4844,7 +4876,7 @@
         <v>3200</v>
       </c>
       <c r="F140" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G140" s="8">
         <v>19</v>
@@ -4873,7 +4905,7 @@
         <v>2890</v>
       </c>
       <c r="F141" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>116</v>
@@ -4902,7 +4934,7 @@
         <v>2890</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>116</v>
@@ -4929,7 +4961,7 @@
         <v>3100</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G143" s="8">
         <v>19</v>
@@ -4956,7 +4988,7 @@
         <v>3100</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G144" s="8">
         <v>19</v>
@@ -4983,7 +5015,7 @@
         <v>3200</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G145" s="8">
         <v>19</v>
@@ -5010,7 +5042,7 @@
         <v>3100</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G146" s="8">
         <v>19</v>
@@ -5037,7 +5069,7 @@
         <v>3100</v>
       </c>
       <c r="F147" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G147" s="8">
         <v>19</v>
@@ -5064,13 +5096,13 @@
         <v>2820</v>
       </c>
       <c r="F148" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G148" s="8">
         <v>18</v>
       </c>
       <c r="H148" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I148" t="s">
         <v>115</v>
@@ -5091,13 +5123,13 @@
         <v>2820</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G149" s="8">
         <v>18</v>
       </c>
       <c r="H149" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I149" t="s">
         <v>115</v>
@@ -5118,13 +5150,13 @@
         <v>2870</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G150" s="8">
         <v>18</v>
       </c>
       <c r="H150" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I150" t="s">
         <v>115</v>
@@ -5145,13 +5177,13 @@
         <v>2820</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G151" s="8">
         <v>18</v>
       </c>
       <c r="H151" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I151" t="s">
         <v>115</v>
@@ -5172,13 +5204,13 @@
         <v>3030</v>
       </c>
       <c r="F152" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G152" s="8">
         <v>18</v>
       </c>
       <c r="H152" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I152" t="s">
         <v>115</v>
@@ -5199,13 +5231,13 @@
         <v>2920</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G153" s="8">
         <v>18</v>
       </c>
       <c r="H153" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I153" t="s">
         <v>115</v>
@@ -5228,7 +5260,7 @@
         <v>2780</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>133</v>
@@ -5257,7 +5289,7 @@
         <v>2780</v>
       </c>
       <c r="F155" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>133</v>
@@ -5286,7 +5318,7 @@
         <v>2780</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>133</v>
@@ -5315,7 +5347,7 @@
         <v>2780</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>133</v>
@@ -5344,7 +5376,7 @@
         <v>2780</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>133</v>
@@ -5373,7 +5405,7 @@
         <v>2780</v>
       </c>
       <c r="F159" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>133</v>
@@ -5402,7 +5434,7 @@
         <v>2780</v>
       </c>
       <c r="F160" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>133</v>
@@ -5431,7 +5463,7 @@
         <v>2990</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>133</v>
@@ -5458,7 +5490,7 @@
         <v>2990</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G162" s="8">
         <v>18</v>
@@ -5487,7 +5519,7 @@
         <v>2880</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>133</v>
@@ -5516,7 +5548,7 @@
         <v>2880</v>
       </c>
       <c r="F164" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>133</v>
@@ -5545,7 +5577,7 @@
         <v>2880</v>
       </c>
       <c r="F165" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>133</v>
@@ -5574,7 +5606,7 @@
         <v>2880</v>
       </c>
       <c r="F166" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>133</v>
@@ -5603,7 +5635,7 @@
         <v>2880</v>
       </c>
       <c r="F167" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>133</v>
@@ -5632,7 +5664,7 @@
         <v>2880</v>
       </c>
       <c r="F168" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>133</v>
@@ -5661,7 +5693,7 @@
         <v>2880</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>133</v>
@@ -5690,7 +5722,7 @@
         <v>2880</v>
       </c>
       <c r="F170" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>133</v>
@@ -5719,7 +5751,7 @@
         <v>2880</v>
       </c>
       <c r="F171" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G171" s="8" t="s">
         <v>133</v>
@@ -5746,7 +5778,7 @@
         <v>2990</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G172" s="8">
         <v>18</v>
@@ -5773,7 +5805,7 @@
         <v>2990</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G173" s="8">
         <v>18</v>
@@ -5800,7 +5832,7 @@
         <v>2990</v>
       </c>
       <c r="F174" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G174" s="8">
         <v>18</v>
@@ -5827,7 +5859,7 @@
         <v>2930</v>
       </c>
       <c r="F175" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G175" s="8">
         <v>18</v>
@@ -5854,7 +5886,7 @@
         <v>3250</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G176" s="8">
         <v>18</v>
@@ -5881,7 +5913,7 @@
         <v>3090</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G177" s="8">
         <v>18</v>
@@ -5908,7 +5940,7 @@
         <v>3300</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G178" s="8">
         <v>18</v>
@@ -5935,7 +5967,7 @@
         <v>3300</v>
       </c>
       <c r="F179" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G179" s="8">
         <v>18</v>
@@ -5962,7 +5994,7 @@
         <v>2990</v>
       </c>
       <c r="F180" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G180" s="8">
         <v>18</v>
@@ -5989,7 +6021,7 @@
         <v>3090</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G181" s="8">
         <v>18</v>
@@ -6016,7 +6048,7 @@
         <v>3090</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G182" s="8">
         <v>18</v>
@@ -6043,7 +6075,7 @@
         <v>3090</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G183" s="8">
         <v>18</v>
@@ -6070,7 +6102,7 @@
         <v>3090</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G184" s="8">
         <v>18</v>
@@ -6097,7 +6129,7 @@
         <v>3090</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G185" s="8">
         <v>18</v>
@@ -6124,7 +6156,7 @@
         <v>3090</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G186" s="8">
         <v>18</v>
@@ -6151,7 +6183,7 @@
         <v>3090</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G187" s="8">
         <v>18</v>
@@ -6178,7 +6210,7 @@
         <v>3090</v>
       </c>
       <c r="F188" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G188" s="8">
         <v>18</v>
@@ -6205,7 +6237,7 @@
         <v>3090</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G189" s="8">
         <v>18</v>
@@ -6232,7 +6264,7 @@
         <v>3250</v>
       </c>
       <c r="F190" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G190" s="8">
         <v>18</v>
@@ -6259,7 +6291,7 @@
         <v>3300</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G191" s="8">
         <v>18</v>
@@ -6286,7 +6318,7 @@
         <v>3410</v>
       </c>
       <c r="F192" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G192" s="8">
         <v>18</v>
@@ -6313,7 +6345,7 @@
         <v>3410</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G193" s="8">
         <v>18</v>
@@ -6340,7 +6372,7 @@
         <v>3620</v>
       </c>
       <c r="F194" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G194" s="8">
         <v>18</v>
@@ -6367,7 +6399,7 @@
         <v>2930</v>
       </c>
       <c r="F195" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G195" s="8">
         <v>18</v>
@@ -6394,7 +6426,7 @@
         <v>2930</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G196" s="8">
         <v>18</v>
@@ -6421,7 +6453,7 @@
         <v>2930</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G197" s="8">
         <v>18</v>
@@ -6448,7 +6480,7 @@
         <v>2930</v>
       </c>
       <c r="F198" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G198" s="8">
         <v>18</v>
@@ -6475,7 +6507,7 @@
         <v>2930</v>
       </c>
       <c r="F199" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G199" s="8">
         <v>18</v>
@@ -6502,7 +6534,7 @@
         <v>2740</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G200" s="8">
         <v>17</v>
@@ -6529,7 +6561,7 @@
         <v>2740</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G201" s="8">
         <v>17</v>
@@ -6556,7 +6588,7 @@
         <v>2740</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G202" s="8">
         <v>17</v>
@@ -6583,7 +6615,7 @@
         <v>2740</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G203" s="8">
         <v>17</v>
@@ -6610,7 +6642,7 @@
         <v>2740</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G204" s="8">
         <v>17</v>
@@ -6637,7 +6669,7 @@
         <v>2740</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G205" s="8">
         <v>17</v>
@@ -6664,7 +6696,7 @@
         <v>2740</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G206" s="8">
         <v>17</v>
@@ -6691,7 +6723,7 @@
         <v>2740</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G207" s="8">
         <v>17</v>
@@ -6718,7 +6750,7 @@
         <v>2740</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G208" s="8">
         <v>17</v>
@@ -6745,7 +6777,7 @@
         <v>2890</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G209" s="8">
         <v>17</v>
@@ -6772,7 +6804,7 @@
         <v>2840</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G210" s="8">
         <v>17</v>
@@ -6799,7 +6831,7 @@
         <v>2840</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G211" s="8">
         <v>17</v>
@@ -6826,7 +6858,7 @@
         <v>2840</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G212" s="8">
         <v>17</v>
@@ -6853,7 +6885,7 @@
         <v>2840</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G213" s="8">
         <v>17</v>
@@ -6880,7 +6912,7 @@
         <v>2840</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G214" s="8">
         <v>17</v>
@@ -6907,7 +6939,7 @@
         <v>2840</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G215" s="8">
         <v>17</v>
@@ -6934,7 +6966,7 @@
         <v>2840</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G216" s="8">
         <v>17</v>
@@ -6961,7 +6993,7 @@
         <v>2840</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G217" s="8">
         <v>17</v>
@@ -6988,7 +7020,7 @@
         <v>3150</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G218" s="8">
         <v>17</v>
@@ -7015,7 +7047,7 @@
         <v>2840</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G219" s="8">
         <v>17</v>
@@ -7042,7 +7074,7 @@
         <v>2890</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G220" s="8">
         <v>17</v>
@@ -7069,7 +7101,7 @@
         <v>3050</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G221" s="8">
         <v>17</v>
@@ -7096,7 +7128,7 @@
         <v>3050</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G222" s="8">
         <v>17</v>
@@ -7123,7 +7155,7 @@
         <v>3090</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G223" s="8">
         <v>17</v>
@@ -7150,7 +7182,7 @@
         <v>3180</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G224" s="8">
         <v>17</v>
@@ -7177,7 +7209,7 @@
         <v>3180</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G225" s="8">
         <v>17</v>
@@ -7204,7 +7236,7 @@
         <v>3050</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G226" s="8">
         <v>17</v>
@@ -7231,7 +7263,7 @@
         <v>3070</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G227" s="8">
         <v>17</v>
@@ -7258,7 +7290,7 @@
         <v>2960</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G228" s="8">
         <v>17</v>
@@ -7285,7 +7317,7 @@
         <v>2960</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G229" s="8">
         <v>17</v>
@@ -7312,7 +7344,7 @@
         <v>2960</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G230" s="8">
         <v>17</v>
@@ -7339,7 +7371,7 @@
         <v>2960</v>
       </c>
       <c r="F231" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G231" s="8">
         <v>17</v>
@@ -7366,7 +7398,7 @@
         <v>2960</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G232" s="8">
         <v>17</v>
@@ -7393,7 +7425,7 @@
         <v>2960</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G233" s="8">
         <v>17</v>
@@ -7420,7 +7452,7 @@
         <v>2960</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G234" s="8">
         <v>17</v>
@@ -7447,7 +7479,7 @@
         <v>2960</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G235" s="8">
         <v>17</v>
@@ -7474,7 +7506,7 @@
         <v>3170</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G236" s="8">
         <v>17</v>
@@ -7501,7 +7533,7 @@
         <v>3140</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G237" s="8">
         <v>17</v>
@@ -7528,7 +7560,7 @@
         <v>3210</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G238" s="8">
         <v>17</v>
@@ -7555,7 +7587,7 @@
         <v>3210</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G239" s="8">
         <v>17</v>
@@ -7582,7 +7614,7 @@
         <v>3560</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G240" s="8">
         <v>17</v>
@@ -7609,7 +7641,7 @@
         <v>2890</v>
       </c>
       <c r="F241" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G241" s="8">
         <v>17</v>
@@ -7636,7 +7668,7 @@
         <v>3050</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G242" s="8">
         <v>17</v>
@@ -7663,7 +7695,7 @@
         <v>3050</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G243" s="8">
         <v>17</v>
@@ -7690,7 +7722,7 @@
         <v>3100</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G244" s="8">
         <v>17</v>
@@ -7717,7 +7749,7 @@
         <v>3100</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="G245" s="8">
         <v>17</v>
@@ -7744,7 +7776,7 @@
         <v>2610</v>
       </c>
       <c r="F246" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G246" s="8">
         <v>14</v>
@@ -7771,7 +7803,7 @@
         <v>2610</v>
       </c>
       <c r="F247" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G247" s="8">
         <v>14</v>
@@ -7798,7 +7830,7 @@
         <v>2610</v>
       </c>
       <c r="F248" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G248" s="8">
         <v>14</v>
@@ -7825,7 +7857,7 @@
         <v>2610</v>
       </c>
       <c r="F249" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G249" s="8">
         <v>14</v>
@@ -7852,7 +7884,7 @@
         <v>2610</v>
       </c>
       <c r="F250" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G250" s="8">
         <v>14</v>
@@ -7879,7 +7911,7 @@
         <v>2910</v>
       </c>
       <c r="F251" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G251" s="8">
         <v>14</v>
@@ -7906,7 +7938,7 @@
         <v>3410</v>
       </c>
       <c r="F252" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G252" s="8">
         <v>14</v>
@@ -7933,7 +7965,7 @@
         <v>3060</v>
       </c>
       <c r="F253" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G253" s="8">
         <v>14</v>
@@ -7960,7 +7992,7 @@
         <v>3110</v>
       </c>
       <c r="F254" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G254" s="8">
         <v>14</v>
@@ -7987,7 +8019,7 @@
         <v>3310</v>
       </c>
       <c r="F255" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G255" s="8">
         <v>14</v>
@@ -8014,7 +8046,7 @@
         <v>2910</v>
       </c>
       <c r="F256" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G256" s="8">
         <v>14</v>
@@ -8041,7 +8073,7 @@
         <v>3060</v>
       </c>
       <c r="F257" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G257" s="8">
         <v>14</v>
@@ -8068,7 +8100,7 @@
         <v>3010</v>
       </c>
       <c r="F258" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G258" s="8">
         <v>14</v>
@@ -8095,7 +8127,7 @@
         <v>3210</v>
       </c>
       <c r="F259" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G259" s="8">
         <v>14</v>
@@ -8122,7 +8154,7 @@
         <v>2960</v>
       </c>
       <c r="F260" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G260" s="8">
         <v>14</v>
@@ -8149,7 +8181,7 @@
         <v>3160</v>
       </c>
       <c r="F261" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G261" s="8">
         <v>14</v>
@@ -8176,7 +8208,7 @@
         <v>2960</v>
       </c>
       <c r="F262" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G262" s="8">
         <v>14</v>
@@ -8203,7 +8235,7 @@
         <v>3060</v>
       </c>
       <c r="F263" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G263" s="8">
         <v>14</v>
@@ -8230,7 +8262,7 @@
         <v>2710</v>
       </c>
       <c r="F264" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G264" s="8">
         <v>14</v>
@@ -8257,7 +8289,7 @@
         <v>3010</v>
       </c>
       <c r="F265" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G265" s="8">
         <v>14</v>
@@ -8284,7 +8316,7 @@
         <v>3060</v>
       </c>
       <c r="F266" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G266" s="8">
         <v>14</v>
@@ -8311,7 +8343,7 @@
         <v>2610</v>
       </c>
       <c r="F267" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G267" s="8">
         <v>14</v>
@@ -8338,7 +8370,7 @@
         <v>3110</v>
       </c>
       <c r="F268" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G268" s="8">
         <v>14</v>
@@ -8365,7 +8397,7 @@
         <v>3060</v>
       </c>
       <c r="F269" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G269" s="8">
         <v>14</v>
@@ -8392,7 +8424,7 @@
         <v>2960</v>
       </c>
       <c r="F270" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G270" s="8">
         <v>14</v>
@@ -8419,7 +8451,7 @@
         <v>2610</v>
       </c>
       <c r="F271" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G271" s="8">
         <v>14</v>
@@ -8446,7 +8478,7 @@
         <v>3210</v>
       </c>
       <c r="F272" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G272" s="8">
         <v>14</v>
@@ -8473,7 +8505,7 @@
         <v>2610</v>
       </c>
       <c r="F273" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G273" s="8">
         <v>14</v>
@@ -8500,7 +8532,7 @@
         <v>3210</v>
       </c>
       <c r="F274" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G274" s="8">
         <v>14</v>
@@ -8527,7 +8559,7 @@
         <v>2910</v>
       </c>
       <c r="F275" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G275" s="8">
         <v>14</v>
@@ -8554,7 +8586,7 @@
         <v>3060</v>
       </c>
       <c r="F276" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G276" s="8">
         <v>14</v>
@@ -8581,7 +8613,7 @@
         <v>2960</v>
       </c>
       <c r="F277" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G277" s="8">
         <v>14</v>
@@ -8608,7 +8640,7 @@
         <v>3060</v>
       </c>
       <c r="F278" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G278" s="8">
         <v>14</v>
@@ -8635,7 +8667,7 @@
         <v>3110</v>
       </c>
       <c r="F279" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G279" s="8">
         <v>14</v>
@@ -8664,7 +8696,7 @@
         <v>2670</v>
       </c>
       <c r="F280" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G280" s="8" t="s">
         <v>134</v>
@@ -8691,7 +8723,7 @@
         <v>2670</v>
       </c>
       <c r="F281" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G281" s="8">
         <v>17</v>
@@ -8718,7 +8750,7 @@
         <v>2670</v>
       </c>
       <c r="F282" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G282" s="8">
         <v>17</v>
@@ -8745,7 +8777,7 @@
         <v>2830</v>
       </c>
       <c r="F283" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G283" s="8">
         <v>17</v>
@@ -8772,7 +8804,7 @@
         <v>3230</v>
       </c>
       <c r="F284" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G284" s="8">
         <v>17</v>
@@ -8799,7 +8831,7 @@
         <v>2770</v>
       </c>
       <c r="F285" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G285" s="8">
         <v>17</v>
@@ -8826,7 +8858,7 @@
         <v>2850</v>
       </c>
       <c r="F286" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G286" s="8">
         <v>17</v>
@@ -8853,7 +8885,7 @@
         <v>2770</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G287" s="8">
         <v>17</v>
@@ -8880,7 +8912,7 @@
         <v>2880</v>
       </c>
       <c r="F288" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G288" s="8">
         <v>17</v>
@@ -8907,7 +8939,7 @@
         <v>2860</v>
       </c>
       <c r="F289" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G289" s="8">
         <v>17</v>
@@ -8934,7 +8966,7 @@
         <v>2880</v>
       </c>
       <c r="F290" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G290" s="8">
         <v>17</v>
@@ -8961,7 +8993,7 @@
         <v>2840</v>
       </c>
       <c r="F291" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G291" s="8">
         <v>17</v>
@@ -8988,7 +9020,7 @@
         <v>2980</v>
       </c>
       <c r="F292" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G292" s="8">
         <v>17</v>
@@ -9015,7 +9047,7 @@
         <v>2880</v>
       </c>
       <c r="F293" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G293" s="8">
         <v>17</v>
@@ -9029,7 +9061,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B294" t="s">
         <v>15</v>
@@ -9042,7 +9074,7 @@
         <v>2850</v>
       </c>
       <c r="F294" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G294" s="8">
         <v>17</v>
@@ -9069,7 +9101,7 @@
         <v>2820</v>
       </c>
       <c r="F295" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G295" s="8">
         <v>17</v>
@@ -9096,7 +9128,7 @@
         <v>3090</v>
       </c>
       <c r="F296" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G296" s="8">
         <v>17</v>
@@ -9123,7 +9155,7 @@
         <v>2850</v>
       </c>
       <c r="F297" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G297" s="8">
         <v>17</v>
@@ -9150,7 +9182,7 @@
         <v>2820</v>
       </c>
       <c r="F298" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G298" s="8">
         <v>17</v>
@@ -9177,7 +9209,7 @@
         <v>2770</v>
       </c>
       <c r="F299" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G299" s="8">
         <v>17</v>
@@ -9204,7 +9236,7 @@
         <v>2850</v>
       </c>
       <c r="F300" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G300" s="8">
         <v>17</v>
@@ -9231,7 +9263,7 @@
         <v>2830</v>
       </c>
       <c r="F301" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G301" s="8">
         <v>17</v>
@@ -9258,7 +9290,7 @@
         <v>2940</v>
       </c>
       <c r="F302" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G302" s="8">
         <v>17</v>
@@ -9285,7 +9317,7 @@
         <v>2670</v>
       </c>
       <c r="F303" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G303" s="8">
         <v>17</v>
@@ -9312,7 +9344,7 @@
         <v>2670</v>
       </c>
       <c r="F304" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G304" s="8">
         <v>17</v>
@@ -9339,7 +9371,7 @@
         <v>2850</v>
       </c>
       <c r="F305" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G305" s="8">
         <v>17</v>
@@ -9366,7 +9398,7 @@
         <v>2970</v>
       </c>
       <c r="F306" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G306" s="8">
         <v>17</v>
@@ -9393,7 +9425,7 @@
         <v>2880</v>
       </c>
       <c r="F307" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G307" s="8">
         <v>17</v>
@@ -9420,7 +9452,7 @@
         <v>2770</v>
       </c>
       <c r="F308" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G308" s="8">
         <v>17</v>
@@ -9449,7 +9481,7 @@
         <v>2670</v>
       </c>
       <c r="F309" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G309" s="8" t="s">
         <v>134</v>
@@ -9463,7 +9495,7 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B310" t="s">
         <v>15</v>
@@ -9476,7 +9508,7 @@
         <v>2820</v>
       </c>
       <c r="F310" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G310" s="8">
         <v>17</v>
@@ -9503,7 +9535,7 @@
         <v>2670</v>
       </c>
       <c r="F311" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G311" s="8">
         <v>17</v>
@@ -9530,7 +9562,7 @@
         <v>3150</v>
       </c>
       <c r="F312" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G312" s="8">
         <v>17</v>
@@ -9557,7 +9589,7 @@
         <v>2820</v>
       </c>
       <c r="F313" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G313" s="8">
         <v>17</v>
@@ -9584,7 +9616,7 @@
         <v>2880</v>
       </c>
       <c r="F314" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G314" s="8">
         <v>17</v>
@@ -9611,7 +9643,7 @@
         <v>2820</v>
       </c>
       <c r="F315" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G315" s="8">
         <v>17</v>
@@ -9638,7 +9670,7 @@
         <v>2850</v>
       </c>
       <c r="F316" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G316" s="8">
         <v>17</v>
@@ -9665,7 +9697,7 @@
         <v>2850</v>
       </c>
       <c r="F317" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G317" s="8">
         <v>17</v>
@@ -9682,7 +9714,7 @@
         <v>5</v>
       </c>
       <c r="B318" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C318" s="11"/>
       <c r="D318" s="11">
@@ -9692,13 +9724,13 @@
         <v>2810</v>
       </c>
       <c r="F318" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G318" s="8">
         <v>18</v>
       </c>
       <c r="H318" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I318" s="7" t="s">
         <v>115</v>
@@ -9709,7 +9741,7 @@
         <v>4</v>
       </c>
       <c r="B319" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C319" s="11"/>
       <c r="D319" s="11">
@@ -9719,13 +9751,13 @@
         <v>2810</v>
       </c>
       <c r="F319" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G319" s="8">
         <v>18</v>
       </c>
       <c r="H319" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I319" s="7" t="s">
         <v>115</v>
@@ -9736,7 +9768,7 @@
         <v>104</v>
       </c>
       <c r="B320" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C320" s="11"/>
       <c r="D320" s="11">
@@ -9746,13 +9778,13 @@
         <v>2810</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G320" s="8">
         <v>18</v>
       </c>
       <c r="H320" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I320" s="7" t="s">
         <v>115</v>
@@ -9763,7 +9795,7 @@
         <v>105</v>
       </c>
       <c r="B321" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C321" s="11"/>
       <c r="D321" s="11">
@@ -9773,13 +9805,13 @@
         <v>2810</v>
       </c>
       <c r="F321" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G321" s="8">
         <v>18</v>
       </c>
       <c r="H321" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I321" s="7" t="s">
         <v>115</v>
@@ -9790,7 +9822,7 @@
         <v>106</v>
       </c>
       <c r="B322" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C322" s="11"/>
       <c r="D322" s="11">
@@ -9800,13 +9832,13 @@
         <v>2860</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G322" s="8">
         <v>18</v>
       </c>
       <c r="H322" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I322" s="7" t="s">
         <v>115</v>
@@ -9817,7 +9849,7 @@
         <v>52</v>
       </c>
       <c r="B323" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C323" s="11"/>
       <c r="D323" s="11">
@@ -9827,13 +9859,13 @@
         <v>3070</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G323" s="8">
         <v>18</v>
       </c>
       <c r="H323" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I323" s="7" t="s">
         <v>115</v>
@@ -9844,7 +9876,7 @@
         <v>35</v>
       </c>
       <c r="B324" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C324" s="11"/>
       <c r="D324" s="11">
@@ -9854,13 +9886,13 @@
         <v>3750</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G324" s="8">
         <v>18</v>
       </c>
       <c r="H324" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I324" s="7" t="s">
         <v>115</v>
@@ -9871,7 +9903,7 @@
         <v>24</v>
       </c>
       <c r="B325" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C325" s="11"/>
       <c r="D325" s="11">
@@ -9881,13 +9913,13 @@
         <v>2910</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G325" s="8">
         <v>18</v>
       </c>
       <c r="H325" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I325" s="7" t="s">
         <v>115</v>
@@ -9898,7 +9930,7 @@
         <v>50</v>
       </c>
       <c r="B326" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C326" s="11"/>
       <c r="D326" s="11">
@@ -9908,13 +9940,13 @@
         <v>3070</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G326" s="8">
         <v>18</v>
       </c>
       <c r="H326" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I326" s="7" t="s">
         <v>115</v>
@@ -9925,7 +9957,7 @@
         <v>29</v>
       </c>
       <c r="B327" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C327" s="11"/>
       <c r="D327" s="11">
@@ -9935,13 +9967,13 @@
         <v>3230</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G327" s="8">
         <v>18</v>
       </c>
       <c r="H327" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I327" s="7" t="s">
         <v>115</v>
@@ -9952,7 +9984,7 @@
         <v>27</v>
       </c>
       <c r="B328" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C328" s="11"/>
       <c r="D328" s="11">
@@ -9962,13 +9994,13 @@
         <v>3020</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G328" s="8">
         <v>18</v>
       </c>
       <c r="H328" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I328" s="7" t="s">
         <v>115</v>
@@ -9979,7 +10011,7 @@
         <v>48</v>
       </c>
       <c r="B329" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C329" s="11"/>
       <c r="D329" s="11">
@@ -9989,13 +10021,13 @@
         <v>3070</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G329" s="8">
         <v>18</v>
       </c>
       <c r="H329" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I329" s="7" t="s">
         <v>115</v>
@@ -10006,7 +10038,7 @@
         <v>33</v>
       </c>
       <c r="B330" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C330" s="11"/>
       <c r="D330" s="11">
@@ -10016,13 +10048,13 @@
         <v>3330</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G330" s="8">
         <v>18</v>
       </c>
       <c r="H330" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I330" s="7" t="s">
         <v>115</v>
@@ -10033,7 +10065,7 @@
         <v>108</v>
       </c>
       <c r="B331" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C331" s="11"/>
       <c r="D331" s="11">
@@ -10043,13 +10075,13 @@
         <v>3330</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G331" s="8">
         <v>18</v>
       </c>
       <c r="H331" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I331" s="7" t="s">
         <v>115</v>
@@ -10060,7 +10092,7 @@
         <v>30</v>
       </c>
       <c r="B332" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C332" s="11"/>
       <c r="D332" s="11">
@@ -10070,13 +10102,13 @@
         <v>3540</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G332" s="8">
         <v>18</v>
       </c>
       <c r="H332" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I332" s="7" t="s">
         <v>115</v>
@@ -10087,7 +10119,7 @@
         <v>56</v>
       </c>
       <c r="B333" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C333" s="11"/>
       <c r="D333" s="11">
@@ -10097,13 +10129,13 @@
         <v>3120</v>
       </c>
       <c r="F333" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G333" s="8">
         <v>18</v>
       </c>
       <c r="H333" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I333" s="7" t="s">
         <v>115</v>
@@ -10114,7 +10146,7 @@
         <v>28</v>
       </c>
       <c r="B334" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C334" s="11"/>
       <c r="D334" s="11">
@@ -10124,13 +10156,13 @@
         <v>3070</v>
       </c>
       <c r="F334" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G334" s="8">
         <v>18</v>
       </c>
       <c r="H334" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I334" s="7" t="s">
         <v>115</v>
@@ -10141,7 +10173,7 @@
         <v>57</v>
       </c>
       <c r="B335" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C335" s="11"/>
       <c r="D335" s="11">
@@ -10151,13 +10183,13 @@
         <v>3230</v>
       </c>
       <c r="F335" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G335" s="8">
         <v>18</v>
       </c>
       <c r="H335" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I335" s="7" t="s">
         <v>115</v>
@@ -10168,7 +10200,7 @@
         <v>13</v>
       </c>
       <c r="B336" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C336" s="11"/>
       <c r="D336" s="11">
@@ -10178,13 +10210,13 @@
         <v>3020</v>
       </c>
       <c r="F336" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G336" s="8">
         <v>18</v>
       </c>
       <c r="H336" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I336" s="7" t="s">
         <v>115</v>
@@ -10195,7 +10227,7 @@
         <v>109</v>
       </c>
       <c r="B337" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C337" s="11"/>
       <c r="D337" s="11">
@@ -10205,13 +10237,13 @@
         <v>3070</v>
       </c>
       <c r="F337" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G337" s="8">
         <v>18</v>
       </c>
       <c r="H337" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I337" s="7" t="s">
         <v>115</v>
@@ -10222,7 +10254,7 @@
         <v>25</v>
       </c>
       <c r="B338" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C338" s="11"/>
       <c r="D338" s="11">
@@ -10232,13 +10264,13 @@
         <v>3070</v>
       </c>
       <c r="F338" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G338" s="8">
         <v>18</v>
       </c>
       <c r="H338" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I338" s="7" t="s">
         <v>115</v>
@@ -10249,7 +10281,7 @@
         <v>19</v>
       </c>
       <c r="B339" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C339" s="11"/>
       <c r="D339" s="11">
@@ -10259,13 +10291,13 @@
         <v>2910</v>
       </c>
       <c r="F339" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G339" s="8">
         <v>18</v>
       </c>
       <c r="H339" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I339" s="7" t="s">
         <v>115</v>
@@ -10276,7 +10308,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C340" s="11"/>
       <c r="D340" s="11">
@@ -10286,13 +10318,13 @@
         <v>2810</v>
       </c>
       <c r="F340" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G340" s="8">
         <v>18</v>
       </c>
       <c r="H340" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I340" s="7" t="s">
         <v>115</v>
@@ -10303,7 +10335,7 @@
         <v>51</v>
       </c>
       <c r="B341" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C341" s="11"/>
       <c r="D341" s="11">
@@ -10313,13 +10345,13 @@
         <v>3070</v>
       </c>
       <c r="F341" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G341" s="8">
         <v>18</v>
       </c>
       <c r="H341" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I341" s="7" t="s">
         <v>115</v>
@@ -10330,7 +10362,7 @@
         <v>53</v>
       </c>
       <c r="B342" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C342" s="11"/>
       <c r="D342" s="11">
@@ -10340,13 +10372,13 @@
         <v>3440</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G342" s="8">
         <v>18</v>
       </c>
       <c r="H342" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I342" s="7" t="s">
         <v>115</v>
@@ -10357,7 +10389,7 @@
         <v>110</v>
       </c>
       <c r="B343" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C343" s="11"/>
       <c r="D343" s="11">
@@ -10367,13 +10399,13 @@
         <v>3070</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G343" s="8">
         <v>18</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I343" s="7" t="s">
         <v>115</v>
@@ -10384,7 +10416,7 @@
         <v>16</v>
       </c>
       <c r="B344" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C344" s="11"/>
       <c r="D344" s="11">
@@ -10394,13 +10426,13 @@
         <v>2810</v>
       </c>
       <c r="F344" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G344" s="8">
         <v>18</v>
       </c>
       <c r="H344" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I344" s="7" t="s">
         <v>115</v>
@@ -10411,7 +10443,7 @@
         <v>117</v>
       </c>
       <c r="B345" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C345" s="11"/>
       <c r="D345" s="11">
@@ -10421,13 +10453,13 @@
         <v>2910</v>
       </c>
       <c r="F345" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G345" s="8">
         <v>18</v>
       </c>
       <c r="H345" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I345" s="7" t="s">
         <v>115</v>
@@ -10438,7 +10470,7 @@
         <v>20</v>
       </c>
       <c r="B346" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C346" s="11"/>
       <c r="D346" s="11">
@@ -10448,13 +10480,13 @@
         <v>2910</v>
       </c>
       <c r="F346" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G346" s="8">
         <v>18</v>
       </c>
       <c r="H346" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I346" s="7" t="s">
         <v>115</v>
@@ -10465,7 +10497,7 @@
         <v>55</v>
       </c>
       <c r="B347" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C347" s="11"/>
       <c r="D347" s="11">
@@ -10475,13 +10507,13 @@
         <v>3230</v>
       </c>
       <c r="F347" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G347" s="8">
         <v>18</v>
       </c>
       <c r="H347" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I347" s="7" t="s">
         <v>115</v>
@@ -10492,7 +10524,7 @@
         <v>31</v>
       </c>
       <c r="B348" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C348" s="11"/>
       <c r="D348" s="11">
@@ -10502,13 +10534,13 @@
         <v>3330</v>
       </c>
       <c r="F348" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G348" s="8">
         <v>18</v>
       </c>
       <c r="H348" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I348" s="7" t="s">
         <v>115</v>
@@ -10519,7 +10551,7 @@
         <v>54</v>
       </c>
       <c r="B349" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C349" s="11"/>
       <c r="D349" s="11">
@@ -10529,13 +10561,13 @@
         <v>3230</v>
       </c>
       <c r="F349" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G349" s="8">
         <v>18</v>
       </c>
       <c r="H349" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I349" s="7" t="s">
         <v>115</v>
@@ -10546,7 +10578,7 @@
         <v>26</v>
       </c>
       <c r="B350" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C350" s="11"/>
       <c r="D350" s="11">
@@ -10556,13 +10588,13 @@
         <v>3070</v>
       </c>
       <c r="F350" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G350" s="8">
         <v>18</v>
       </c>
       <c r="H350" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I350" s="7" t="s">
         <v>115</v>
@@ -10573,7 +10605,7 @@
         <v>49</v>
       </c>
       <c r="B351" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C351" s="11"/>
       <c r="D351" s="11">
@@ -10583,13 +10615,13 @@
         <v>3070</v>
       </c>
       <c r="F351" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G351" s="8">
         <v>18</v>
       </c>
       <c r="H351" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I351" s="7" t="s">
         <v>115</v>
@@ -10612,7 +10644,7 @@
         <v>2730</v>
       </c>
       <c r="F352" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G352" s="8" t="s">
         <v>116</v>
@@ -10641,7 +10673,7 @@
         <v>2730</v>
       </c>
       <c r="F353" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G353" s="8" t="s">
         <v>116</v>
@@ -10668,7 +10700,7 @@
         <v>2730</v>
       </c>
       <c r="F354" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G354" s="8">
         <v>19</v>
@@ -10695,7 +10727,7 @@
         <v>2730</v>
       </c>
       <c r="F355" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G355" s="8">
         <v>19</v>
@@ -10722,7 +10754,7 @@
         <v>2890</v>
       </c>
       <c r="F356" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G356" s="8">
         <v>19</v>
@@ -10749,7 +10781,7 @@
         <v>3040</v>
       </c>
       <c r="F357" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G357" s="8">
         <v>19</v>
@@ -10776,7 +10808,7 @@
         <v>2940</v>
       </c>
       <c r="F358" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G358" s="8">
         <v>19</v>
@@ -10803,7 +10835,7 @@
         <v>3150</v>
       </c>
       <c r="F359" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G359" s="8">
         <v>19</v>
@@ -10830,7 +10862,7 @@
         <v>2940</v>
       </c>
       <c r="F360" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G360" s="8">
         <v>19</v>
@@ -10857,7 +10889,7 @@
         <v>2940</v>
       </c>
       <c r="F361" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G361" s="8">
         <v>19</v>
@@ -10884,7 +10916,7 @@
         <v>2940</v>
       </c>
       <c r="F362" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G362" s="8">
         <v>19</v>
@@ -10911,7 +10943,7 @@
         <v>2940</v>
       </c>
       <c r="F363" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G363" s="8">
         <v>19</v>
@@ -10938,7 +10970,7 @@
         <v>2940</v>
       </c>
       <c r="F364" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G364" s="8">
         <v>19</v>
@@ -10965,7 +10997,7 @@
         <v>2940</v>
       </c>
       <c r="F365" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G365" s="8">
         <v>19</v>
@@ -10992,7 +11024,7 @@
         <v>2940</v>
       </c>
       <c r="F366" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G366" s="8">
         <v>19</v>
@@ -11019,7 +11051,7 @@
         <v>2940</v>
       </c>
       <c r="F367" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G367" s="8">
         <v>19</v>
@@ -11046,7 +11078,7 @@
         <v>3040</v>
       </c>
       <c r="F368" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G368" s="8">
         <v>19</v>
@@ -11075,7 +11107,7 @@
         <v>2730</v>
       </c>
       <c r="F369" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G369" s="8" t="s">
         <v>116</v>
@@ -11104,7 +11136,7 @@
         <v>2730</v>
       </c>
       <c r="F370" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G370" s="8" t="s">
         <v>116</v>
@@ -11131,7 +11163,7 @@
         <v>2940</v>
       </c>
       <c r="F371" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G371" s="8">
         <v>19</v>
@@ -11158,7 +11190,7 @@
         <v>2940</v>
       </c>
       <c r="F372" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G372" s="8">
         <v>19</v>
@@ -11185,7 +11217,7 @@
         <v>3040</v>
       </c>
       <c r="F373" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G373" s="8">
         <v>19</v>
@@ -11212,7 +11244,7 @@
         <v>2940</v>
       </c>
       <c r="F374" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G374" s="8">
         <v>19</v>
@@ -11239,7 +11271,7 @@
         <v>2940</v>
       </c>
       <c r="F375" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G375" s="8">
         <v>19</v>
@@ -11266,13 +11298,13 @@
         <v>2610</v>
       </c>
       <c r="F376" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G376" s="8">
         <v>18</v>
       </c>
       <c r="H376" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I376" s="7" t="s">
         <v>115</v>
@@ -11293,13 +11325,13 @@
         <v>2610</v>
       </c>
       <c r="F377" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G377" s="8">
         <v>18</v>
       </c>
       <c r="H377" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I377" s="7" t="s">
         <v>115</v>
@@ -11320,13 +11352,13 @@
         <v>2660</v>
       </c>
       <c r="F378" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G378" s="8">
         <v>18</v>
       </c>
       <c r="H378" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I378" s="7" t="s">
         <v>115</v>
@@ -11347,13 +11379,13 @@
         <v>2610</v>
       </c>
       <c r="F379" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G379" s="8">
         <v>18</v>
       </c>
       <c r="H379" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I379" s="7" t="s">
         <v>115</v>
@@ -11374,13 +11406,13 @@
         <v>2820</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G380" s="8">
         <v>18</v>
       </c>
       <c r="H380" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I380" s="7" t="s">
         <v>115</v>
@@ -11401,13 +11433,13 @@
         <v>2710</v>
       </c>
       <c r="F381" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G381" s="8">
         <v>18</v>
       </c>
       <c r="H381" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I381" s="7" t="s">
         <v>115</v>
@@ -11428,7 +11460,7 @@
         <v>3210</v>
       </c>
       <c r="F382" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G382" s="8">
         <v>18</v>
@@ -11455,7 +11487,7 @@
         <v>3630</v>
       </c>
       <c r="F383" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G383" s="8">
         <v>18</v>
@@ -11482,7 +11514,7 @@
         <v>3210</v>
       </c>
       <c r="F384" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G384" s="8">
         <v>18</v>
@@ -11509,7 +11541,7 @@
         <v>3210</v>
       </c>
       <c r="F385" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G385" s="8">
         <v>18</v>
@@ -11536,7 +11568,7 @@
         <v>2890</v>
       </c>
       <c r="F386" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G386" s="8">
         <v>18</v>
@@ -11563,7 +11595,7 @@
         <v>2890</v>
       </c>
       <c r="F387" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G387" s="8">
         <v>18</v>
@@ -11590,7 +11622,7 @@
         <v>3210</v>
       </c>
       <c r="F388" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G388" s="8">
         <v>18</v>
@@ -11604,7 +11636,7 @@
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B389" t="s">
         <v>15</v>
@@ -11617,7 +11649,7 @@
         <v>2890</v>
       </c>
       <c r="F389" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G389" s="8">
         <v>18</v>
@@ -11631,7 +11663,7 @@
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B390" t="s">
         <v>15</v>
@@ -11644,7 +11676,7 @@
         <v>2890</v>
       </c>
       <c r="F390" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G390" s="8">
         <v>18</v>
@@ -11671,7 +11703,7 @@
         <v>2890</v>
       </c>
       <c r="F391" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G391" s="8">
         <v>18</v>
@@ -11698,7 +11730,7 @@
         <v>2890</v>
       </c>
       <c r="F392" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G392" s="8">
         <v>18</v>
@@ -11712,7 +11744,7 @@
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B393" t="s">
         <v>15</v>
@@ -11725,7 +11757,7 @@
         <v>2890</v>
       </c>
       <c r="F393" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G393" s="8">
         <v>18</v>
@@ -11752,7 +11784,7 @@
         <v>2890</v>
       </c>
       <c r="F394" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G394" s="8">
         <v>18</v>
@@ -11766,7 +11798,7 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B395" t="s">
         <v>15</v>
@@ -11779,7 +11811,7 @@
         <v>2890</v>
       </c>
       <c r="F395" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G395" s="8">
         <v>18</v>
@@ -11793,7 +11825,7 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B396" t="s">
         <v>15</v>
@@ -11806,7 +11838,7 @@
         <v>2890</v>
       </c>
       <c r="F396" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G396" s="8">
         <v>18</v>
@@ -11833,7 +11865,7 @@
         <v>2890</v>
       </c>
       <c r="F397" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G397" s="8">
         <v>18</v>
@@ -11860,7 +11892,7 @@
         <v>2890</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G398" s="8">
         <v>18</v>
@@ -11887,7 +11919,7 @@
         <v>2890</v>
       </c>
       <c r="F399" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G399" s="8">
         <v>18</v>
@@ -11914,7 +11946,7 @@
         <v>2890</v>
       </c>
       <c r="F400" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G400" s="8">
         <v>18</v>
@@ -11941,7 +11973,7 @@
         <v>2890</v>
       </c>
       <c r="F401" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G401" s="8">
         <v>18</v>
@@ -11968,7 +12000,7 @@
         <v>2890</v>
       </c>
       <c r="F402" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G402" s="8">
         <v>18</v>
@@ -11982,7 +12014,7 @@
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B403" t="s">
         <v>15</v>
@@ -11995,7 +12027,7 @@
         <v>3210</v>
       </c>
       <c r="F403" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G403" s="8">
         <v>18</v>
@@ -12009,7 +12041,7 @@
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B404" t="s">
         <v>15</v>
@@ -12022,7 +12054,7 @@
         <v>3210</v>
       </c>
       <c r="F404" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G404" s="8">
         <v>18</v>
@@ -12049,7 +12081,7 @@
         <v>2580</v>
       </c>
       <c r="F405" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G405" s="8">
         <v>18</v>
@@ -12076,7 +12108,7 @@
         <v>2680</v>
       </c>
       <c r="F406" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G406" s="8">
         <v>18</v>
@@ -12090,7 +12122,7 @@
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B407" t="s">
         <v>15</v>
@@ -12103,7 +12135,7 @@
         <v>2580</v>
       </c>
       <c r="F407" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G407" s="8">
         <v>18</v>
@@ -12130,7 +12162,7 @@
         <v>3310</v>
       </c>
       <c r="F408" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G408" s="8">
         <v>18</v>
@@ -12144,7 +12176,7 @@
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B409" t="s">
         <v>15</v>
@@ -12157,7 +12189,7 @@
         <v>3310</v>
       </c>
       <c r="F409" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G409" s="8">
         <v>18</v>
@@ -12171,7 +12203,7 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B410" t="s">
         <v>15</v>
@@ -12184,7 +12216,7 @@
         <v>3310</v>
       </c>
       <c r="F410" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G410" s="8">
         <v>18</v>
@@ -12198,7 +12230,7 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B411" t="s">
         <v>15</v>
@@ -12211,7 +12243,7 @@
         <v>3790</v>
       </c>
       <c r="F411" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G411" s="8">
         <v>18</v>
@@ -12238,7 +12270,7 @@
         <v>3000</v>
       </c>
       <c r="F412" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G412" s="8">
         <v>18</v>
@@ -12265,7 +12297,7 @@
         <v>3000</v>
       </c>
       <c r="F413" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G413" s="8">
         <v>18</v>
@@ -12292,7 +12324,7 @@
         <v>3000</v>
       </c>
       <c r="F414" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G414" s="8">
         <v>18</v>
@@ -12319,7 +12351,7 @@
         <v>3120</v>
       </c>
       <c r="F415" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G415" s="8">
         <v>18</v>
@@ -12333,7 +12365,7 @@
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B416" t="s">
         <v>15</v>
@@ -12346,7 +12378,7 @@
         <v>3160</v>
       </c>
       <c r="F416" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G416" s="8">
         <v>18</v>
@@ -12373,7 +12405,7 @@
         <v>3160</v>
       </c>
       <c r="F417" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G417" s="8">
         <v>18</v>
@@ -12400,7 +12432,7 @@
         <v>3160</v>
       </c>
       <c r="F418" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G418" s="8">
         <v>18</v>
@@ -12427,7 +12459,7 @@
         <v>3160</v>
       </c>
       <c r="F419" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G419" s="8">
         <v>18</v>
@@ -12441,7 +12473,7 @@
     </row>
     <row r="420" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B420" t="s">
         <v>15</v>
@@ -12454,7 +12486,7 @@
         <v>3160</v>
       </c>
       <c r="F420" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G420" s="8">
         <v>18</v>
@@ -12481,7 +12513,7 @@
         <v>3160</v>
       </c>
       <c r="F421" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G421" s="8">
         <v>18</v>
@@ -12508,7 +12540,7 @@
         <v>2680</v>
       </c>
       <c r="F422" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G422" s="8">
         <v>18</v>
@@ -12535,7 +12567,7 @@
         <v>2680</v>
       </c>
       <c r="F423" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G423" s="8">
         <v>18</v>
@@ -12562,7 +12594,7 @@
         <v>3630</v>
       </c>
       <c r="F424" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G424" s="8">
         <v>18</v>
@@ -12589,7 +12621,7 @@
         <v>3210</v>
       </c>
       <c r="F425" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G425" s="8">
         <v>18</v>
@@ -12616,7 +12648,7 @@
         <v>2680</v>
       </c>
       <c r="F426" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G426" s="8">
         <v>18</v>
@@ -12643,7 +12675,7 @@
         <v>3310</v>
       </c>
       <c r="F427" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G427" s="8">
         <v>18</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C4AAA34-1265-4D38-B22A-C7343A56E1D2}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6FA20E5E-A914-40AE-B852-63847AF8FF34}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="159">
   <si>
     <t>POD</t>
   </si>
@@ -516,10 +516,10 @@
     <t>15 al 30 de abril</t>
   </si>
   <si>
-    <t>22 al 26 de abril</t>
-  </si>
-  <si>
-    <t>22 al 28 de abril</t>
+    <t>x</t>
+  </si>
+  <si>
+    <t>1 al 14 de mayo</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:K437"/>
+  <dimension ref="A1:K345"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -6296,7 +6296,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>95</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>96</v>
       </c>
@@ -6350,7 +6350,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>97</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>98</v>
       </c>
@@ -6404,7 +6404,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>99</v>
       </c>
@@ -6431,7 +6431,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>100</v>
       </c>
@@ -6458,7 +6458,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>101</v>
       </c>
@@ -6485,7 +6485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="7" t="s">
         <v>21</v>
       </c>
@@ -6502,7 +6502,7 @@
         <v>2780</v>
       </c>
       <c r="F200" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G200" s="8" t="s">
         <v>133</v>
@@ -6513,8 +6513,11 @@
       <c r="I200" s="7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J200" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
         <v>20</v>
       </c>
@@ -6531,7 +6534,7 @@
         <v>2780</v>
       </c>
       <c r="F201" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G201" s="8" t="s">
         <v>133</v>
@@ -6543,7 +6546,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="7" t="s">
         <v>19</v>
       </c>
@@ -6560,7 +6563,7 @@
         <v>2780</v>
       </c>
       <c r="F202" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>133</v>
@@ -6572,7 +6575,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
         <v>16</v>
       </c>
@@ -6589,7 +6592,7 @@
         <v>2780</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G203" s="8" t="s">
         <v>133</v>
@@ -6601,7 +6604,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="7" t="s">
         <v>13</v>
       </c>
@@ -6618,7 +6621,7 @@
         <v>2780</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G204" s="8" t="s">
         <v>133</v>
@@ -6630,7 +6633,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
         <v>5</v>
       </c>
@@ -6647,7 +6650,7 @@
         <v>2780</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>133</v>
@@ -6659,7 +6662,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="7" t="s">
         <v>4</v>
       </c>
@@ -6676,7 +6679,7 @@
         <v>2780</v>
       </c>
       <c r="F206" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>133</v>
@@ -6688,7 +6691,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
         <v>117</v>
       </c>
@@ -6705,7 +6708,7 @@
         <v>2990</v>
       </c>
       <c r="F207" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G207" s="8" t="s">
         <v>133</v>
@@ -6717,7 +6720,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="7" t="s">
         <v>24</v>
       </c>
@@ -6732,7 +6735,7 @@
         <v>2990</v>
       </c>
       <c r="F208" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G208" s="8">
         <v>18</v>
@@ -6761,7 +6764,7 @@
         <v>2880</v>
       </c>
       <c r="F209" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G209" s="8" t="s">
         <v>133</v>
@@ -6790,7 +6793,7 @@
         <v>2880</v>
       </c>
       <c r="F210" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>133</v>
@@ -6819,7 +6822,7 @@
         <v>2880</v>
       </c>
       <c r="F211" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>133</v>
@@ -6848,7 +6851,7 @@
         <v>2880</v>
       </c>
       <c r="F212" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G212" s="8" t="s">
         <v>133</v>
@@ -6877,7 +6880,7 @@
         <v>2880</v>
       </c>
       <c r="F213" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G213" s="8" t="s">
         <v>133</v>
@@ -6906,7 +6909,7 @@
         <v>2880</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G214" s="8" t="s">
         <v>133</v>
@@ -6935,7 +6938,7 @@
         <v>2880</v>
       </c>
       <c r="F215" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>133</v>
@@ -6964,7 +6967,7 @@
         <v>2880</v>
       </c>
       <c r="F216" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G216" s="8" t="s">
         <v>133</v>
@@ -6993,7 +6996,7 @@
         <v>2880</v>
       </c>
       <c r="F217" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G217" s="8" t="s">
         <v>133</v>
@@ -7020,7 +7023,7 @@
         <v>2990</v>
       </c>
       <c r="F218" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G218" s="8">
         <v>18</v>
@@ -7047,7 +7050,7 @@
         <v>2990</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G219" s="8">
         <v>18</v>
@@ -7074,7 +7077,7 @@
         <v>2990</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G220" s="8">
         <v>18</v>
@@ -7101,7 +7104,7 @@
         <v>2930</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G221" s="8">
         <v>18</v>
@@ -7128,7 +7131,7 @@
         <v>3250</v>
       </c>
       <c r="F222" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G222" s="8">
         <v>18</v>
@@ -7155,7 +7158,7 @@
         <v>3090</v>
       </c>
       <c r="F223" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G223" s="8">
         <v>18</v>
@@ -7182,7 +7185,7 @@
         <v>3300</v>
       </c>
       <c r="F224" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G224" s="8">
         <v>18</v>
@@ -7209,7 +7212,7 @@
         <v>3300</v>
       </c>
       <c r="F225" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G225" s="8">
         <v>18</v>
@@ -7236,7 +7239,7 @@
         <v>2990</v>
       </c>
       <c r="F226" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G226" s="8">
         <v>18</v>
@@ -7263,7 +7266,7 @@
         <v>3090</v>
       </c>
       <c r="F227" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G227" s="8">
         <v>18</v>
@@ -7290,7 +7293,7 @@
         <v>3090</v>
       </c>
       <c r="F228" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G228" s="8">
         <v>18</v>
@@ -7317,7 +7320,7 @@
         <v>3090</v>
       </c>
       <c r="F229" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G229" s="8">
         <v>18</v>
@@ -7344,7 +7347,7 @@
         <v>3090</v>
       </c>
       <c r="F230" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G230" s="8">
         <v>18</v>
@@ -7371,7 +7374,7 @@
         <v>3090</v>
       </c>
       <c r="F231" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G231" s="8">
         <v>18</v>
@@ -7398,7 +7401,7 @@
         <v>3090</v>
       </c>
       <c r="F232" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G232" s="8">
         <v>18</v>
@@ -7425,7 +7428,7 @@
         <v>3090</v>
       </c>
       <c r="F233" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G233" s="8">
         <v>18</v>
@@ -7452,7 +7455,7 @@
         <v>3090</v>
       </c>
       <c r="F234" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G234" s="8">
         <v>18</v>
@@ -7479,7 +7482,7 @@
         <v>3090</v>
       </c>
       <c r="F235" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G235" s="8">
         <v>18</v>
@@ -7506,7 +7509,7 @@
         <v>3250</v>
       </c>
       <c r="F236" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G236" s="8">
         <v>18</v>
@@ -7533,7 +7536,7 @@
         <v>3300</v>
       </c>
       <c r="F237" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G237" s="8">
         <v>18</v>
@@ -7560,7 +7563,7 @@
         <v>3410</v>
       </c>
       <c r="F238" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G238" s="8">
         <v>18</v>
@@ -7587,7 +7590,7 @@
         <v>3410</v>
       </c>
       <c r="F239" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G239" s="8">
         <v>18</v>
@@ -7614,7 +7617,7 @@
         <v>3620</v>
       </c>
       <c r="F240" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G240" s="8">
         <v>18</v>
@@ -7641,7 +7644,7 @@
         <v>2930</v>
       </c>
       <c r="F241" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G241" s="8">
         <v>18</v>
@@ -7668,7 +7671,7 @@
         <v>2930</v>
       </c>
       <c r="F242" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G242" s="8">
         <v>18</v>
@@ -7695,7 +7698,7 @@
         <v>2930</v>
       </c>
       <c r="F243" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G243" s="8">
         <v>18</v>
@@ -7722,7 +7725,7 @@
         <v>2930</v>
       </c>
       <c r="F244" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G244" s="8">
         <v>18</v>
@@ -7749,7 +7752,7 @@
         <v>2930</v>
       </c>
       <c r="F245" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G245" s="8">
         <v>18</v>
@@ -9034,703 +9037,151 @@
       <c r="G296" s="8"/>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C297" s="11"/>
-      <c r="D297" s="11"/>
-      <c r="E297" s="11"/>
       <c r="G297" s="8"/>
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C298" s="11"/>
-      <c r="D298" s="11"/>
-      <c r="E298" s="11"/>
       <c r="G298" s="8"/>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C299" s="11"/>
-      <c r="D299" s="11"/>
-      <c r="E299" s="11"/>
       <c r="G299" s="8"/>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C300" s="11"/>
-      <c r="D300" s="11"/>
-      <c r="E300" s="11"/>
       <c r="G300" s="8"/>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C301" s="11"/>
-      <c r="D301" s="11"/>
-      <c r="E301" s="11"/>
       <c r="G301" s="8"/>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C302" s="11"/>
-      <c r="D302" s="11"/>
-      <c r="E302" s="11"/>
       <c r="G302" s="8"/>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C303" s="11"/>
-      <c r="D303" s="11"/>
-      <c r="E303" s="11"/>
       <c r="G303" s="8"/>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C304" s="11"/>
-      <c r="D304" s="11"/>
-      <c r="E304" s="11"/>
       <c r="G304" s="8"/>
     </row>
-    <row r="305" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C305" s="11"/>
-      <c r="D305" s="11"/>
-      <c r="E305" s="11"/>
+    <row r="305" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G305" s="8"/>
     </row>
-    <row r="306" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C306" s="11"/>
-      <c r="D306" s="11"/>
-      <c r="E306" s="11"/>
+    <row r="306" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G306" s="8"/>
     </row>
-    <row r="307" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C307" s="11"/>
-      <c r="D307" s="11"/>
-      <c r="E307" s="11"/>
+    <row r="307" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G307" s="8"/>
     </row>
-    <row r="308" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C308" s="11"/>
-      <c r="D308" s="11"/>
-      <c r="E308" s="11"/>
+    <row r="308" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G308" s="8"/>
     </row>
-    <row r="309" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C309" s="11"/>
-      <c r="D309" s="11"/>
-      <c r="E309" s="11"/>
+    <row r="309" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G309" s="8"/>
     </row>
-    <row r="310" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C310" s="11"/>
-      <c r="D310" s="11"/>
-      <c r="E310" s="11"/>
+    <row r="310" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G310" s="8"/>
     </row>
-    <row r="311" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C311" s="11"/>
-      <c r="D311" s="11"/>
-      <c r="E311" s="11"/>
+    <row r="311" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G311" s="8"/>
     </row>
-    <row r="312" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C312" s="11"/>
-      <c r="D312" s="11"/>
-      <c r="E312" s="11"/>
+    <row r="312" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G312" s="8"/>
     </row>
-    <row r="313" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C313" s="11"/>
-      <c r="D313" s="11"/>
-      <c r="E313" s="11"/>
+    <row r="313" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G313" s="8"/>
     </row>
-    <row r="314" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C314" s="11"/>
-      <c r="D314" s="11"/>
-      <c r="E314" s="11"/>
+    <row r="314" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G314" s="8"/>
     </row>
-    <row r="315" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C315" s="11"/>
-      <c r="D315" s="11"/>
-      <c r="E315" s="11"/>
+    <row r="315" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G315" s="8"/>
     </row>
-    <row r="316" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C316" s="11"/>
-      <c r="D316" s="11"/>
-      <c r="E316" s="11"/>
+    <row r="316" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G316" s="8"/>
     </row>
-    <row r="317" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C317" s="11"/>
-      <c r="D317" s="11"/>
-      <c r="E317" s="11"/>
+    <row r="317" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G317" s="8"/>
     </row>
-    <row r="318" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C318" s="11"/>
-      <c r="D318" s="11"/>
-      <c r="E318" s="11"/>
+    <row r="318" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G318" s="8"/>
     </row>
-    <row r="319" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C319" s="11"/>
-      <c r="D319" s="11"/>
-      <c r="E319" s="11"/>
+    <row r="319" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G319" s="8"/>
     </row>
-    <row r="320" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C320" s="11"/>
-      <c r="D320" s="11"/>
-      <c r="E320" s="11"/>
+    <row r="320" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G320" s="8"/>
     </row>
-    <row r="321" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C321" s="11"/>
-      <c r="D321" s="11"/>
-      <c r="E321" s="11"/>
+    <row r="321" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G321" s="8"/>
     </row>
-    <row r="322" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C322" s="11"/>
-      <c r="D322" s="11"/>
-      <c r="E322" s="11"/>
+    <row r="322" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G322" s="8"/>
     </row>
-    <row r="323" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C323" s="11"/>
-      <c r="D323" s="11"/>
-      <c r="E323" s="11"/>
+    <row r="323" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G323" s="8"/>
     </row>
-    <row r="324" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C324" s="11"/>
-      <c r="D324" s="11"/>
-      <c r="E324" s="11"/>
+    <row r="324" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G324" s="8"/>
     </row>
-    <row r="325" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C325" s="11"/>
-      <c r="D325" s="11"/>
-      <c r="E325" s="11"/>
+    <row r="325" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G325" s="8"/>
     </row>
-    <row r="326" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C326" s="11"/>
-      <c r="D326" s="11"/>
-      <c r="E326" s="11"/>
+    <row r="326" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G326" s="8"/>
     </row>
-    <row r="327" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C327" s="11"/>
-      <c r="D327" s="11"/>
-      <c r="E327" s="11"/>
+    <row r="327" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G327" s="8"/>
     </row>
-    <row r="328" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C328" s="11"/>
-      <c r="D328" s="11"/>
-      <c r="E328" s="11"/>
+    <row r="328" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G328" s="8"/>
     </row>
-    <row r="329" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C329" s="11"/>
-      <c r="D329" s="11"/>
-      <c r="E329" s="11"/>
+    <row r="329" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G329" s="8"/>
     </row>
-    <row r="330" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C330" s="11"/>
-      <c r="D330" s="11"/>
-      <c r="E330" s="11"/>
+    <row r="330" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G330" s="8"/>
     </row>
-    <row r="331" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C331" s="11"/>
-      <c r="D331" s="11"/>
-      <c r="E331" s="11"/>
+    <row r="331" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G331" s="8"/>
     </row>
-    <row r="332" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C332" s="11"/>
-      <c r="D332" s="11"/>
-      <c r="E332" s="11"/>
+    <row r="332" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G332" s="8"/>
     </row>
-    <row r="333" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C333" s="11"/>
-      <c r="D333" s="11"/>
-      <c r="E333" s="11"/>
+    <row r="333" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G333" s="8"/>
     </row>
-    <row r="334" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C334" s="11"/>
-      <c r="D334" s="11"/>
-      <c r="E334" s="11"/>
+    <row r="334" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G334" s="8"/>
     </row>
-    <row r="335" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C335" s="11"/>
-      <c r="D335" s="11"/>
-      <c r="E335" s="11"/>
+    <row r="335" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G335" s="8"/>
     </row>
-    <row r="336" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C336" s="11"/>
-      <c r="D336" s="11"/>
-      <c r="E336" s="11"/>
+    <row r="336" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G336" s="8"/>
     </row>
-    <row r="337" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C337" s="11"/>
-      <c r="D337" s="11"/>
-      <c r="E337" s="11"/>
+    <row r="337" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G337" s="8"/>
     </row>
-    <row r="338" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C338" s="11"/>
-      <c r="D338" s="11"/>
-      <c r="E338" s="11"/>
+    <row r="338" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G338" s="8"/>
     </row>
-    <row r="339" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C339" s="11"/>
-      <c r="D339" s="11"/>
-      <c r="E339" s="11"/>
+    <row r="339" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G339" s="8"/>
     </row>
-    <row r="340" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C340" s="11"/>
-      <c r="D340" s="11"/>
-      <c r="E340" s="11"/>
+    <row r="340" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G340" s="8"/>
     </row>
-    <row r="341" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C341" s="11"/>
-      <c r="D341" s="11"/>
-      <c r="E341" s="11"/>
+    <row r="341" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G341" s="8"/>
     </row>
-    <row r="342" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C342" s="11"/>
-      <c r="D342" s="11"/>
-      <c r="E342" s="11"/>
+    <row r="342" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G342" s="8"/>
     </row>
-    <row r="343" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C343" s="11"/>
-      <c r="D343" s="11"/>
-      <c r="E343" s="11"/>
+    <row r="343" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G343" s="8"/>
     </row>
-    <row r="344" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C344" s="11"/>
-      <c r="D344" s="11"/>
-      <c r="E344" s="11"/>
+    <row r="344" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G344" s="8"/>
     </row>
-    <row r="345" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C345" s="11"/>
-      <c r="D345" s="11"/>
-      <c r="E345" s="11"/>
+    <row r="345" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G345" s="8"/>
-    </row>
-    <row r="346" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C346" s="11"/>
-      <c r="D346" s="11"/>
-      <c r="E346" s="11"/>
-      <c r="G346" s="8"/>
-    </row>
-    <row r="347" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C347" s="11"/>
-      <c r="D347" s="11"/>
-      <c r="E347" s="11"/>
-      <c r="G347" s="8"/>
-    </row>
-    <row r="348" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C348" s="11"/>
-      <c r="D348" s="11"/>
-      <c r="E348" s="11"/>
-      <c r="G348" s="8"/>
-    </row>
-    <row r="349" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C349" s="11"/>
-      <c r="D349" s="11"/>
-      <c r="E349" s="11"/>
-      <c r="G349" s="8"/>
-    </row>
-    <row r="350" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C350" s="11"/>
-      <c r="D350" s="11"/>
-      <c r="E350" s="11"/>
-      <c r="G350" s="8"/>
-    </row>
-    <row r="351" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C351" s="11"/>
-      <c r="D351" s="11"/>
-      <c r="E351" s="11"/>
-      <c r="G351" s="8"/>
-    </row>
-    <row r="352" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C352" s="11"/>
-      <c r="D352" s="11"/>
-      <c r="E352" s="11"/>
-      <c r="G352" s="8"/>
-    </row>
-    <row r="353" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C353" s="11"/>
-      <c r="D353" s="11"/>
-      <c r="E353" s="11"/>
-      <c r="G353" s="8"/>
-    </row>
-    <row r="354" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C354" s="11"/>
-      <c r="D354" s="11"/>
-      <c r="E354" s="11"/>
-      <c r="G354" s="8"/>
-    </row>
-    <row r="355" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C355" s="11"/>
-      <c r="D355" s="11"/>
-      <c r="E355" s="11"/>
-      <c r="G355" s="8"/>
-    </row>
-    <row r="356" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C356" s="11"/>
-      <c r="D356" s="11"/>
-      <c r="E356" s="11"/>
-      <c r="G356" s="8"/>
-    </row>
-    <row r="357" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C357" s="11"/>
-      <c r="D357" s="11"/>
-      <c r="E357" s="11"/>
-      <c r="G357" s="8"/>
-    </row>
-    <row r="358" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C358" s="11"/>
-      <c r="D358" s="11"/>
-      <c r="E358" s="11"/>
-      <c r="G358" s="8"/>
-    </row>
-    <row r="359" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C359" s="11"/>
-      <c r="D359" s="11"/>
-      <c r="E359" s="11"/>
-      <c r="G359" s="8"/>
-    </row>
-    <row r="360" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C360" s="11"/>
-      <c r="D360" s="11"/>
-      <c r="E360" s="11"/>
-      <c r="G360" s="8"/>
-    </row>
-    <row r="361" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C361" s="11"/>
-      <c r="D361" s="11"/>
-      <c r="E361" s="11"/>
-      <c r="G361" s="8"/>
-    </row>
-    <row r="362" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C362" s="11"/>
-      <c r="D362" s="11"/>
-      <c r="E362" s="11"/>
-      <c r="G362" s="8"/>
-    </row>
-    <row r="363" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C363" s="11"/>
-      <c r="D363" s="11"/>
-      <c r="E363" s="11"/>
-      <c r="G363" s="8"/>
-    </row>
-    <row r="364" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C364" s="11"/>
-      <c r="D364" s="11"/>
-      <c r="E364" s="11"/>
-      <c r="G364" s="8"/>
-    </row>
-    <row r="365" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C365" s="11"/>
-      <c r="D365" s="11"/>
-      <c r="E365" s="11"/>
-      <c r="G365" s="8"/>
-    </row>
-    <row r="366" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C366" s="11"/>
-      <c r="D366" s="11"/>
-      <c r="E366" s="11"/>
-      <c r="G366" s="8"/>
-    </row>
-    <row r="367" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C367" s="11"/>
-      <c r="D367" s="11"/>
-      <c r="E367" s="11"/>
-      <c r="G367" s="8"/>
-    </row>
-    <row r="368" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C368" s="11"/>
-      <c r="D368" s="11"/>
-      <c r="E368" s="11"/>
-      <c r="G368" s="8"/>
-    </row>
-    <row r="369" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C369" s="11"/>
-      <c r="D369" s="11"/>
-      <c r="E369" s="11"/>
-      <c r="G369" s="8"/>
-    </row>
-    <row r="370" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C370" s="11"/>
-      <c r="D370" s="11"/>
-      <c r="E370" s="11"/>
-      <c r="G370" s="8"/>
-    </row>
-    <row r="371" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C371" s="11"/>
-      <c r="D371" s="11"/>
-      <c r="E371" s="11"/>
-      <c r="G371" s="8"/>
-    </row>
-    <row r="372" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C372" s="11"/>
-      <c r="D372" s="11"/>
-      <c r="E372" s="11"/>
-      <c r="G372" s="8"/>
-    </row>
-    <row r="373" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C373" s="11"/>
-      <c r="D373" s="11"/>
-      <c r="E373" s="11"/>
-      <c r="G373" s="8"/>
-    </row>
-    <row r="374" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C374" s="11"/>
-      <c r="D374" s="11"/>
-      <c r="E374" s="11"/>
-      <c r="G374" s="8"/>
-    </row>
-    <row r="375" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C375" s="11"/>
-      <c r="D375" s="11"/>
-      <c r="E375" s="11"/>
-      <c r="G375" s="8"/>
-    </row>
-    <row r="376" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C376" s="11"/>
-      <c r="D376" s="11"/>
-      <c r="E376" s="11"/>
-      <c r="G376" s="8"/>
-    </row>
-    <row r="377" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C377" s="11"/>
-      <c r="D377" s="11"/>
-      <c r="E377" s="11"/>
-      <c r="G377" s="8"/>
-    </row>
-    <row r="378" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C378" s="11"/>
-      <c r="D378" s="11"/>
-      <c r="E378" s="11"/>
-      <c r="G378" s="8"/>
-    </row>
-    <row r="379" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C379" s="11"/>
-      <c r="D379" s="11"/>
-      <c r="E379" s="11"/>
-      <c r="G379" s="8"/>
-    </row>
-    <row r="380" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C380" s="11"/>
-      <c r="D380" s="11"/>
-      <c r="E380" s="11"/>
-      <c r="G380" s="8"/>
-    </row>
-    <row r="381" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C381" s="11"/>
-      <c r="D381" s="11"/>
-      <c r="E381" s="11"/>
-      <c r="G381" s="8"/>
-    </row>
-    <row r="382" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C382" s="11"/>
-      <c r="D382" s="11"/>
-      <c r="E382" s="11"/>
-      <c r="G382" s="8"/>
-    </row>
-    <row r="383" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C383" s="11"/>
-      <c r="D383" s="11"/>
-      <c r="E383" s="11"/>
-      <c r="G383" s="8"/>
-    </row>
-    <row r="384" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C384" s="11"/>
-      <c r="D384" s="11"/>
-      <c r="E384" s="11"/>
-      <c r="G384" s="8"/>
-    </row>
-    <row r="385" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C385" s="11"/>
-      <c r="D385" s="11"/>
-      <c r="E385" s="11"/>
-      <c r="G385" s="8"/>
-    </row>
-    <row r="386" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C386" s="11"/>
-      <c r="D386" s="11"/>
-      <c r="E386" s="11"/>
-      <c r="G386" s="8"/>
-    </row>
-    <row r="387" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C387" s="11"/>
-      <c r="D387" s="11"/>
-      <c r="E387" s="11"/>
-      <c r="G387" s="8"/>
-    </row>
-    <row r="388" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C388" s="11"/>
-      <c r="D388" s="11"/>
-      <c r="E388" s="11"/>
-      <c r="G388" s="8"/>
-    </row>
-    <row r="389" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G389" s="8"/>
-    </row>
-    <row r="390" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G390" s="8"/>
-    </row>
-    <row r="391" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G391" s="8"/>
-    </row>
-    <row r="392" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G392" s="8"/>
-    </row>
-    <row r="393" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G393" s="8"/>
-    </row>
-    <row r="394" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G394" s="8"/>
-    </row>
-    <row r="395" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G395" s="8"/>
-    </row>
-    <row r="396" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G396" s="8"/>
-    </row>
-    <row r="397" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G397" s="8"/>
-    </row>
-    <row r="398" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G398" s="8"/>
-    </row>
-    <row r="399" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G399" s="8"/>
-    </row>
-    <row r="400" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="G400" s="8"/>
-    </row>
-    <row r="401" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G401" s="8"/>
-    </row>
-    <row r="402" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G402" s="8"/>
-    </row>
-    <row r="403" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G403" s="8"/>
-    </row>
-    <row r="404" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G404" s="8"/>
-    </row>
-    <row r="405" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G405" s="8"/>
-    </row>
-    <row r="406" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G406" s="8"/>
-    </row>
-    <row r="407" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G407" s="8"/>
-    </row>
-    <row r="408" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G408" s="8"/>
-    </row>
-    <row r="409" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G409" s="8"/>
-    </row>
-    <row r="410" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G410" s="8"/>
-    </row>
-    <row r="411" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G411" s="8"/>
-    </row>
-    <row r="412" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G412" s="8"/>
-    </row>
-    <row r="413" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G413" s="8"/>
-    </row>
-    <row r="414" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G414" s="8"/>
-    </row>
-    <row r="415" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G415" s="8"/>
-    </row>
-    <row r="416" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G416" s="8"/>
-    </row>
-    <row r="417" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G417" s="8"/>
-    </row>
-    <row r="418" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G418" s="8"/>
-    </row>
-    <row r="419" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G419" s="8"/>
-    </row>
-    <row r="420" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G420" s="8"/>
-    </row>
-    <row r="421" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G421" s="8"/>
-    </row>
-    <row r="422" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G422" s="8"/>
-    </row>
-    <row r="423" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G423" s="8"/>
-    </row>
-    <row r="424" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G424" s="8"/>
-    </row>
-    <row r="425" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G425" s="8"/>
-    </row>
-    <row r="426" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G426" s="8"/>
-    </row>
-    <row r="427" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G427" s="8"/>
-    </row>
-    <row r="428" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G428" s="8"/>
-    </row>
-    <row r="429" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G429" s="8"/>
-    </row>
-    <row r="430" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G430" s="8"/>
-    </row>
-    <row r="431" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G431" s="8"/>
-    </row>
-    <row r="432" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G432" s="8"/>
-    </row>
-    <row r="433" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G433" s="8"/>
-    </row>
-    <row r="434" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G434" s="8"/>
-    </row>
-    <row r="435" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G435" s="8"/>
-    </row>
-    <row r="436" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G436" s="8"/>
-    </row>
-    <row r="437" spans="7:7" x14ac:dyDescent="0.25">
-      <c r="G437" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I17" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84E20C45-E70D-44EB-92EC-9149F3424FB9}"/>
+  <xr:revisionPtr revIDLastSave="132" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{107D5F45-1308-45A8-A437-7AA2DB2D5694}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="115">
   <si>
     <t>POD</t>
   </si>
@@ -897,9 +897,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{CA184AB0-5897-42AC-ACAA-83512778E556}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;c1368056-4f06-43fe-9f8c-b9724961ccaa&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:K338"/>
+  <dimension ref="A1:K639"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -10191,13 +10213,5182 @@
       </c>
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>5</v>
+      </c>
+      <c r="B338" t="s">
+        <v>62</v>
+      </c>
       <c r="C338" s="11"/>
-      <c r="D338" s="11"/>
-      <c r="E338" s="11"/>
-      <c r="F338" s="7"/>
-      <c r="G338" s="8"/>
-      <c r="H338" s="7"/>
-      <c r="I338" s="7"/>
+      <c r="D338" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E338" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F338" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G338" s="8">
+        <v>14</v>
+      </c>
+      <c r="H338" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="339" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>4</v>
+      </c>
+      <c r="B339" t="s">
+        <v>62</v>
+      </c>
+      <c r="C339" s="11"/>
+      <c r="D339" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E339" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G339" s="8">
+        <v>14</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="340" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>74</v>
+      </c>
+      <c r="B340" t="s">
+        <v>62</v>
+      </c>
+      <c r="C340" s="11"/>
+      <c r="D340" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E340" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G340" s="8">
+        <v>14</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="341" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>75</v>
+      </c>
+      <c r="B341" t="s">
+        <v>62</v>
+      </c>
+      <c r="C341" s="11"/>
+      <c r="D341" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E341" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G341" s="8">
+        <v>14</v>
+      </c>
+      <c r="H341" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I341" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="342" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>76</v>
+      </c>
+      <c r="B342" t="s">
+        <v>62</v>
+      </c>
+      <c r="C342" s="11"/>
+      <c r="D342" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E342" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G342" s="8">
+        <v>14</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="343" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>52</v>
+      </c>
+      <c r="B343" t="s">
+        <v>62</v>
+      </c>
+      <c r="C343" s="11"/>
+      <c r="D343" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E343" s="11">
+        <v>3760</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G343" s="8">
+        <v>14</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="344" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>35</v>
+      </c>
+      <c r="B344" t="s">
+        <v>62</v>
+      </c>
+      <c r="C344" s="11"/>
+      <c r="D344" s="11">
+        <v>3530</v>
+      </c>
+      <c r="E344" s="11">
+        <v>4260</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G344" s="8">
+        <v>14</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="345" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>24</v>
+      </c>
+      <c r="B345" t="s">
+        <v>62</v>
+      </c>
+      <c r="C345" s="11"/>
+      <c r="D345" s="11">
+        <v>3430</v>
+      </c>
+      <c r="E345" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G345" s="8">
+        <v>14</v>
+      </c>
+      <c r="H345" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I345" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="346" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>50</v>
+      </c>
+      <c r="B346" t="s">
+        <v>62</v>
+      </c>
+      <c r="C346" s="11"/>
+      <c r="D346" s="11">
+        <v>3480</v>
+      </c>
+      <c r="E346" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F346" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G346" s="8">
+        <v>14</v>
+      </c>
+      <c r="H346" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="347" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>29</v>
+      </c>
+      <c r="B347" t="s">
+        <v>62</v>
+      </c>
+      <c r="C347" s="11"/>
+      <c r="D347" s="11">
+        <v>3580</v>
+      </c>
+      <c r="E347" s="11">
+        <v>4160</v>
+      </c>
+      <c r="F347" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G347" s="8">
+        <v>14</v>
+      </c>
+      <c r="H347" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I347" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="348" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>27</v>
+      </c>
+      <c r="B348" t="s">
+        <v>62</v>
+      </c>
+      <c r="C348" s="11"/>
+      <c r="D348" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E348" s="11">
+        <v>3760</v>
+      </c>
+      <c r="F348" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G348" s="8">
+        <v>14</v>
+      </c>
+      <c r="H348" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="349" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>48</v>
+      </c>
+      <c r="B349" t="s">
+        <v>62</v>
+      </c>
+      <c r="C349" s="11"/>
+      <c r="D349" s="11">
+        <v>3530</v>
+      </c>
+      <c r="E349" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F349" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G349" s="8">
+        <v>14</v>
+      </c>
+      <c r="H349" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I349" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="350" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>33</v>
+      </c>
+      <c r="B350" t="s">
+        <v>62</v>
+      </c>
+      <c r="C350" s="11"/>
+      <c r="D350" s="11">
+        <v>3330</v>
+      </c>
+      <c r="E350" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F350" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G350" s="8">
+        <v>14</v>
+      </c>
+      <c r="H350" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="351" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>30</v>
+      </c>
+      <c r="B351" t="s">
+        <v>62</v>
+      </c>
+      <c r="C351" s="11"/>
+      <c r="D351" s="11">
+        <v>3480</v>
+      </c>
+      <c r="E351" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G351" s="8">
+        <v>14</v>
+      </c>
+      <c r="H351" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="352" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>56</v>
+      </c>
+      <c r="B352" t="s">
+        <v>62</v>
+      </c>
+      <c r="C352" s="11"/>
+      <c r="D352" s="11">
+        <v>3430</v>
+      </c>
+      <c r="E352" s="11">
+        <v>3810</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G352" s="8">
+        <v>14</v>
+      </c>
+      <c r="H352" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="353" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>34</v>
+      </c>
+      <c r="B353" t="s">
+        <v>62</v>
+      </c>
+      <c r="C353" s="11"/>
+      <c r="D353" s="11">
+        <v>3530</v>
+      </c>
+      <c r="E353" s="11">
+        <v>4010</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G353" s="8">
+        <v>14</v>
+      </c>
+      <c r="H353" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I353" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="354" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>28</v>
+      </c>
+      <c r="B354" t="s">
+        <v>62</v>
+      </c>
+      <c r="C354" s="11"/>
+      <c r="D354" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E354" s="11">
+        <v>3810</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G354" s="8">
+        <v>14</v>
+      </c>
+      <c r="H354" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="355" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>57</v>
+      </c>
+      <c r="B355" t="s">
+        <v>62</v>
+      </c>
+      <c r="C355" s="11"/>
+      <c r="D355" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E355" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F355" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G355" s="8">
+        <v>14</v>
+      </c>
+      <c r="H355" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I355" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="356" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>13</v>
+      </c>
+      <c r="B356" t="s">
+        <v>62</v>
+      </c>
+      <c r="C356" s="11"/>
+      <c r="D356" s="11">
+        <v>3180</v>
+      </c>
+      <c r="E356" s="11">
+        <v>3560</v>
+      </c>
+      <c r="F356" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G356" s="8">
+        <v>14</v>
+      </c>
+      <c r="H356" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="357" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>79</v>
+      </c>
+      <c r="B357" t="s">
+        <v>62</v>
+      </c>
+      <c r="C357" s="11"/>
+      <c r="D357" s="11">
+        <v>3430</v>
+      </c>
+      <c r="E357" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F357" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G357" s="8">
+        <v>14</v>
+      </c>
+      <c r="H357" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I357" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="358" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A358" t="s">
+        <v>25</v>
+      </c>
+      <c r="B358" t="s">
+        <v>62</v>
+      </c>
+      <c r="C358" s="11"/>
+      <c r="D358" s="11">
+        <v>3430</v>
+      </c>
+      <c r="E358" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G358" s="8">
+        <v>14</v>
+      </c>
+      <c r="H358" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="359" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A359" t="s">
+        <v>21</v>
+      </c>
+      <c r="B359" t="s">
+        <v>62</v>
+      </c>
+      <c r="C359" s="11"/>
+      <c r="D359" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E359" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F359" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G359" s="8">
+        <v>14</v>
+      </c>
+      <c r="H359" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I359" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="360" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A360" t="s">
+        <v>51</v>
+      </c>
+      <c r="B360" t="s">
+        <v>62</v>
+      </c>
+      <c r="C360" s="11"/>
+      <c r="D360" s="11">
+        <v>3530</v>
+      </c>
+      <c r="E360" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F360" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G360" s="8">
+        <v>14</v>
+      </c>
+      <c r="H360" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="361" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A361" t="s">
+        <v>53</v>
+      </c>
+      <c r="B361" t="s">
+        <v>62</v>
+      </c>
+      <c r="C361" s="11"/>
+      <c r="D361" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E361" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G361" s="8">
+        <v>14</v>
+      </c>
+      <c r="H361" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I361" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="362" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
+        <v>32</v>
+      </c>
+      <c r="B362" t="s">
+        <v>62</v>
+      </c>
+      <c r="C362" s="11"/>
+      <c r="D362" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E362" s="11">
+        <v>3810</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G362" s="8">
+        <v>14</v>
+      </c>
+      <c r="H362" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="363" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A363" t="s">
+        <v>16</v>
+      </c>
+      <c r="B363" t="s">
+        <v>62</v>
+      </c>
+      <c r="C363" s="11"/>
+      <c r="D363" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E363" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G363" s="8">
+        <v>14</v>
+      </c>
+      <c r="H363" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I363" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="364" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A364" t="s">
+        <v>87</v>
+      </c>
+      <c r="B364" t="s">
+        <v>62</v>
+      </c>
+      <c r="C364" s="11"/>
+      <c r="D364" s="11">
+        <v>3480</v>
+      </c>
+      <c r="E364" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G364" s="8">
+        <v>14</v>
+      </c>
+      <c r="H364" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="365" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A365" t="s">
+        <v>20</v>
+      </c>
+      <c r="B365" t="s">
+        <v>62</v>
+      </c>
+      <c r="C365" s="11"/>
+      <c r="D365" s="11">
+        <v>3130</v>
+      </c>
+      <c r="E365" s="11">
+        <v>3460</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G365" s="8">
+        <v>14</v>
+      </c>
+      <c r="H365" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I365" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="366" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A366" t="s">
+        <v>81</v>
+      </c>
+      <c r="B366" t="s">
+        <v>62</v>
+      </c>
+      <c r="C366" s="11"/>
+      <c r="D366" s="11">
+        <v>3530</v>
+      </c>
+      <c r="E366" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F366" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G366" s="8">
+        <v>14</v>
+      </c>
+      <c r="H366" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="367" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A367" t="s">
+        <v>55</v>
+      </c>
+      <c r="B367" t="s">
+        <v>62</v>
+      </c>
+      <c r="C367" s="11"/>
+      <c r="D367" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E367" s="11">
+        <v>3760</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G367" s="8">
+        <v>14</v>
+      </c>
+      <c r="H367" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I367" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="368" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A368" t="s">
+        <v>31</v>
+      </c>
+      <c r="B368" t="s">
+        <v>62</v>
+      </c>
+      <c r="C368" s="11"/>
+      <c r="D368" s="11">
+        <v>3530</v>
+      </c>
+      <c r="E368" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F368" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G368" s="8">
+        <v>14</v>
+      </c>
+      <c r="H368" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I368" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="369" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
+        <v>54</v>
+      </c>
+      <c r="B369" t="s">
+        <v>62</v>
+      </c>
+      <c r="C369" s="11"/>
+      <c r="D369" s="11">
+        <v>3380</v>
+      </c>
+      <c r="E369" s="11">
+        <v>3810</v>
+      </c>
+      <c r="F369" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G369" s="8">
+        <v>14</v>
+      </c>
+      <c r="H369" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I369" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="370" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>26</v>
+      </c>
+      <c r="B370" t="s">
+        <v>62</v>
+      </c>
+      <c r="C370" s="11"/>
+      <c r="D370" s="11">
+        <v>3480</v>
+      </c>
+      <c r="E370" s="11">
+        <v>3910</v>
+      </c>
+      <c r="F370" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G370" s="8">
+        <v>14</v>
+      </c>
+      <c r="H370" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I370" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="371" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A371" t="s">
+        <v>49</v>
+      </c>
+      <c r="B371" t="s">
+        <v>62</v>
+      </c>
+      <c r="C371" s="11"/>
+      <c r="D371" s="11">
+        <v>3480</v>
+      </c>
+      <c r="E371" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F371" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G371" s="8">
+        <v>14</v>
+      </c>
+      <c r="H371" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I371" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="372" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A372" t="s">
+        <v>5</v>
+      </c>
+      <c r="B372" t="s">
+        <v>15</v>
+      </c>
+      <c r="C372" s="11">
+        <v>3170</v>
+      </c>
+      <c r="D372" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E372" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F372" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G372" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H372" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I372" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="373" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A373" t="s">
+        <v>4</v>
+      </c>
+      <c r="B373" t="s">
+        <v>15</v>
+      </c>
+      <c r="C373" s="11"/>
+      <c r="D373" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E373" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F373" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G373" s="8">
+        <v>17</v>
+      </c>
+      <c r="H373" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I373" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="374" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A374" t="s">
+        <v>74</v>
+      </c>
+      <c r="B374" t="s">
+        <v>15</v>
+      </c>
+      <c r="C374" s="11"/>
+      <c r="D374" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E374" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F374" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G374" s="8">
+        <v>17</v>
+      </c>
+      <c r="H374" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I374" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="375" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A375" t="s">
+        <v>52</v>
+      </c>
+      <c r="B375" t="s">
+        <v>15</v>
+      </c>
+      <c r="C375" s="11"/>
+      <c r="D375" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E375" s="11">
+        <v>3930</v>
+      </c>
+      <c r="F375" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G375" s="8">
+        <v>17</v>
+      </c>
+      <c r="H375" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I375" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="376" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A376" t="s">
+        <v>35</v>
+      </c>
+      <c r="B376" t="s">
+        <v>15</v>
+      </c>
+      <c r="C376" s="11"/>
+      <c r="D376" s="11">
+        <v>3830</v>
+      </c>
+      <c r="E376" s="11">
+        <v>4310</v>
+      </c>
+      <c r="F376" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G376" s="8">
+        <v>17</v>
+      </c>
+      <c r="H376" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I376" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="377" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A377" t="s">
+        <v>24</v>
+      </c>
+      <c r="B377" t="s">
+        <v>15</v>
+      </c>
+      <c r="C377" s="11"/>
+      <c r="D377" s="11">
+        <v>3620</v>
+      </c>
+      <c r="E377" s="11">
+        <v>3870</v>
+      </c>
+      <c r="F377" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G377" s="8">
+        <v>17</v>
+      </c>
+      <c r="H377" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I377" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="378" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>50</v>
+      </c>
+      <c r="B378" t="s">
+        <v>15</v>
+      </c>
+      <c r="C378" s="11"/>
+      <c r="D378" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E378" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F378" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G378" s="8">
+        <v>17</v>
+      </c>
+      <c r="H378" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I378" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="379" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>29</v>
+      </c>
+      <c r="B379" t="s">
+        <v>15</v>
+      </c>
+      <c r="C379" s="11"/>
+      <c r="D379" s="11">
+        <v>3620</v>
+      </c>
+      <c r="E379" s="11">
+        <v>3870</v>
+      </c>
+      <c r="F379" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G379" s="8">
+        <v>17</v>
+      </c>
+      <c r="H379" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I379" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="380" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A380" t="s">
+        <v>82</v>
+      </c>
+      <c r="B380" t="s">
+        <v>15</v>
+      </c>
+      <c r="C380" s="11"/>
+      <c r="D380" s="11">
+        <v>3720</v>
+      </c>
+      <c r="E380" s="11">
+        <v>3970</v>
+      </c>
+      <c r="F380" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G380" s="8">
+        <v>17</v>
+      </c>
+      <c r="H380" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I380" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="381" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A381" t="s">
+        <v>77</v>
+      </c>
+      <c r="B381" t="s">
+        <v>15</v>
+      </c>
+      <c r="C381" s="11"/>
+      <c r="D381" s="11">
+        <v>3670</v>
+      </c>
+      <c r="E381" s="11">
+        <v>3950</v>
+      </c>
+      <c r="F381" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G381" s="8">
+        <v>17</v>
+      </c>
+      <c r="H381" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I381" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="382" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A382" t="s">
+        <v>27</v>
+      </c>
+      <c r="B382" t="s">
+        <v>15</v>
+      </c>
+      <c r="C382" s="11"/>
+      <c r="D382" s="11">
+        <v>3670</v>
+      </c>
+      <c r="E382" s="11">
+        <v>3970</v>
+      </c>
+      <c r="F382" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G382" s="8">
+        <v>17</v>
+      </c>
+      <c r="H382" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I382" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="383" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A383" t="s">
+        <v>48</v>
+      </c>
+      <c r="B383" t="s">
+        <v>15</v>
+      </c>
+      <c r="C383" s="11"/>
+      <c r="D383" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E383" s="11">
+        <v>3930</v>
+      </c>
+      <c r="F383" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G383" s="8">
+        <v>17</v>
+      </c>
+      <c r="H383" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I383" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="384" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A384" t="s">
+        <v>33</v>
+      </c>
+      <c r="B384" t="s">
+        <v>15</v>
+      </c>
+      <c r="C384" s="11"/>
+      <c r="D384" s="11">
+        <v>3740</v>
+      </c>
+      <c r="E384" s="11">
+        <v>4070</v>
+      </c>
+      <c r="F384" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G384" s="8">
+        <v>17</v>
+      </c>
+      <c r="H384" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I384" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="385" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A385" t="s">
+        <v>30</v>
+      </c>
+      <c r="B385" t="s">
+        <v>15</v>
+      </c>
+      <c r="C385" s="11"/>
+      <c r="D385" s="11">
+        <v>3670</v>
+      </c>
+      <c r="E385" s="11">
+        <v>3970</v>
+      </c>
+      <c r="F385" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G385" s="8">
+        <v>17</v>
+      </c>
+      <c r="H385" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I385" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="386" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A386" t="s">
+        <v>106</v>
+      </c>
+      <c r="B386" t="s">
+        <v>15</v>
+      </c>
+      <c r="C386" s="11"/>
+      <c r="D386" s="11">
+        <v>3670</v>
+      </c>
+      <c r="E386" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F386" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G386" s="8">
+        <v>17</v>
+      </c>
+      <c r="H386" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I386" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="387" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
+        <v>56</v>
+      </c>
+      <c r="B387" t="s">
+        <v>15</v>
+      </c>
+      <c r="C387" s="11"/>
+      <c r="D387" s="11">
+        <v>3690</v>
+      </c>
+      <c r="E387" s="11">
+        <v>3920</v>
+      </c>
+      <c r="F387" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G387" s="8">
+        <v>17</v>
+      </c>
+      <c r="H387" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I387" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="388" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
+        <v>34</v>
+      </c>
+      <c r="B388" t="s">
+        <v>15</v>
+      </c>
+      <c r="C388" s="11"/>
+      <c r="D388" s="11">
+        <v>3800</v>
+      </c>
+      <c r="E388" s="11">
+        <v>4170</v>
+      </c>
+      <c r="F388" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G388" s="8">
+        <v>17</v>
+      </c>
+      <c r="H388" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I388" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="389" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
+        <v>28</v>
+      </c>
+      <c r="B389" t="s">
+        <v>15</v>
+      </c>
+      <c r="C389" s="11"/>
+      <c r="D389" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E389" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F389" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G389" s="8">
+        <v>17</v>
+      </c>
+      <c r="H389" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I389" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="390" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>57</v>
+      </c>
+      <c r="B390" t="s">
+        <v>15</v>
+      </c>
+      <c r="C390" s="11"/>
+      <c r="D390" s="11">
+        <v>3660</v>
+      </c>
+      <c r="E390" s="11">
+        <v>3920</v>
+      </c>
+      <c r="F390" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G390" s="8">
+        <v>17</v>
+      </c>
+      <c r="H390" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I390" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="391" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A391" t="s">
+        <v>13</v>
+      </c>
+      <c r="B391" t="s">
+        <v>15</v>
+      </c>
+      <c r="C391" s="11"/>
+      <c r="D391" s="11">
+        <v>3620</v>
+      </c>
+      <c r="E391" s="11">
+        <v>3870</v>
+      </c>
+      <c r="F391" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G391" s="8">
+        <v>17</v>
+      </c>
+      <c r="H391" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I391" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="392" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A392" t="s">
+        <v>79</v>
+      </c>
+      <c r="B392" t="s">
+        <v>15</v>
+      </c>
+      <c r="C392" s="11"/>
+      <c r="D392" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E392" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F392" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G392" s="8">
+        <v>17</v>
+      </c>
+      <c r="H392" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I392" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="393" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A393" t="s">
+        <v>83</v>
+      </c>
+      <c r="B393" t="s">
+        <v>15</v>
+      </c>
+      <c r="C393" s="11"/>
+      <c r="D393" s="11">
+        <v>3670</v>
+      </c>
+      <c r="E393" s="11">
+        <v>3930</v>
+      </c>
+      <c r="F393" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G393" s="8">
+        <v>17</v>
+      </c>
+      <c r="H393" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I393" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="394" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A394" t="s">
+        <v>25</v>
+      </c>
+      <c r="B394" t="s">
+        <v>15</v>
+      </c>
+      <c r="C394" s="11"/>
+      <c r="D394" s="11">
+        <v>3710</v>
+      </c>
+      <c r="E394" s="11">
+        <v>4030</v>
+      </c>
+      <c r="F394" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G394" s="8">
+        <v>17</v>
+      </c>
+      <c r="H394" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I394" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="395" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A395" t="s">
+        <v>19</v>
+      </c>
+      <c r="B395" t="s">
+        <v>15</v>
+      </c>
+      <c r="C395" s="11"/>
+      <c r="D395" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E395" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F395" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G395" s="8">
+        <v>17</v>
+      </c>
+      <c r="H395" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I395" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="396" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A396" t="s">
+        <v>21</v>
+      </c>
+      <c r="B396" t="s">
+        <v>15</v>
+      </c>
+      <c r="C396" s="11"/>
+      <c r="D396" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E396" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F396" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G396" s="8">
+        <v>17</v>
+      </c>
+      <c r="H396" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I396" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="397" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A397" t="s">
+        <v>51</v>
+      </c>
+      <c r="B397" t="s">
+        <v>15</v>
+      </c>
+      <c r="C397" s="11"/>
+      <c r="D397" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E397" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F397" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G397" s="8">
+        <v>17</v>
+      </c>
+      <c r="H397" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I397" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="398" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>53</v>
+      </c>
+      <c r="B398" t="s">
+        <v>15</v>
+      </c>
+      <c r="C398" s="11"/>
+      <c r="D398" s="11">
+        <v>3740</v>
+      </c>
+      <c r="E398" s="11">
+        <v>4050</v>
+      </c>
+      <c r="F398" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G398" s="8">
+        <v>17</v>
+      </c>
+      <c r="H398" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I398" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="399" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>32</v>
+      </c>
+      <c r="B399" t="s">
+        <v>15</v>
+      </c>
+      <c r="C399" s="11"/>
+      <c r="D399" s="11">
+        <v>3700</v>
+      </c>
+      <c r="E399" s="11">
+        <v>3970</v>
+      </c>
+      <c r="F399" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G399" s="8">
+        <v>17</v>
+      </c>
+      <c r="H399" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I399" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="400" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>16</v>
+      </c>
+      <c r="B400" t="s">
+        <v>15</v>
+      </c>
+      <c r="C400" s="11"/>
+      <c r="D400" s="11">
+        <v>3620</v>
+      </c>
+      <c r="E400" s="11">
+        <v>3870</v>
+      </c>
+      <c r="F400" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G400" s="8">
+        <v>17</v>
+      </c>
+      <c r="H400" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I400" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="401" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A401" t="s">
+        <v>87</v>
+      </c>
+      <c r="B401" t="s">
+        <v>15</v>
+      </c>
+      <c r="C401" s="11">
+        <v>3170</v>
+      </c>
+      <c r="D401" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E401" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G401" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="H401" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I401" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="402" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A402" t="s">
+        <v>107</v>
+      </c>
+      <c r="B402" t="s">
+        <v>15</v>
+      </c>
+      <c r="C402" s="11"/>
+      <c r="D402" s="11">
+        <v>3660</v>
+      </c>
+      <c r="E402" s="11">
+        <v>3920</v>
+      </c>
+      <c r="F402" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G402" s="8">
+        <v>17</v>
+      </c>
+      <c r="H402" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I402" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="403" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A403" t="s">
+        <v>20</v>
+      </c>
+      <c r="B403" t="s">
+        <v>15</v>
+      </c>
+      <c r="C403" s="11"/>
+      <c r="D403" s="11">
+        <v>3570</v>
+      </c>
+      <c r="E403" s="11">
+        <v>3770</v>
+      </c>
+      <c r="F403" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G403" s="8">
+        <v>17</v>
+      </c>
+      <c r="H403" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I403" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="404" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A404" t="s">
+        <v>81</v>
+      </c>
+      <c r="B404" t="s">
+        <v>15</v>
+      </c>
+      <c r="C404" s="11"/>
+      <c r="D404" s="11">
+        <v>3820</v>
+      </c>
+      <c r="E404" s="11">
+        <v>4230</v>
+      </c>
+      <c r="F404" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G404" s="8">
+        <v>17</v>
+      </c>
+      <c r="H404" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I404" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="405" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A405" t="s">
+        <v>55</v>
+      </c>
+      <c r="B405" t="s">
+        <v>15</v>
+      </c>
+      <c r="C405" s="11"/>
+      <c r="D405" s="11">
+        <v>3660</v>
+      </c>
+      <c r="E405" s="11">
+        <v>3920</v>
+      </c>
+      <c r="F405" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G405" s="8">
+        <v>17</v>
+      </c>
+      <c r="H405" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I405" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="406" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>88</v>
+      </c>
+      <c r="B406" t="s">
+        <v>15</v>
+      </c>
+      <c r="C406" s="11"/>
+      <c r="D406" s="11">
+        <v>3670</v>
+      </c>
+      <c r="E406" s="11">
+        <v>3970</v>
+      </c>
+      <c r="F406" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G406" s="8">
+        <v>17</v>
+      </c>
+      <c r="H406" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I406" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="407" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A407" t="s">
+        <v>54</v>
+      </c>
+      <c r="B407" t="s">
+        <v>15</v>
+      </c>
+      <c r="C407" s="11"/>
+      <c r="D407" s="11">
+        <v>3660</v>
+      </c>
+      <c r="E407" s="11">
+        <v>3920</v>
+      </c>
+      <c r="F407" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G407" s="8">
+        <v>17</v>
+      </c>
+      <c r="H407" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I407" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="408" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A408" t="s">
+        <v>26</v>
+      </c>
+      <c r="B408" t="s">
+        <v>15</v>
+      </c>
+      <c r="C408" s="11"/>
+      <c r="D408" s="11">
+        <v>3680</v>
+      </c>
+      <c r="E408" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F408" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G408" s="8">
+        <v>17</v>
+      </c>
+      <c r="H408" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I408" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="409" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A409" t="s">
+        <v>49</v>
+      </c>
+      <c r="B409" t="s">
+        <v>15</v>
+      </c>
+      <c r="C409" s="11"/>
+      <c r="D409" s="11">
+        <v>3690</v>
+      </c>
+      <c r="E409" s="11">
+        <v>3940</v>
+      </c>
+      <c r="F409" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G409" s="8">
+        <v>17</v>
+      </c>
+      <c r="H409" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I409" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="410" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A410" t="s">
+        <v>5</v>
+      </c>
+      <c r="B410" t="s">
+        <v>110</v>
+      </c>
+      <c r="C410" s="11"/>
+      <c r="D410" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E410" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F410" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G410" s="8">
+        <v>18</v>
+      </c>
+      <c r="H410" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I410" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="411" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A411" t="s">
+        <v>4</v>
+      </c>
+      <c r="B411" t="s">
+        <v>110</v>
+      </c>
+      <c r="C411" s="11"/>
+      <c r="D411" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E411" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F411" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G411" s="8">
+        <v>18</v>
+      </c>
+      <c r="H411" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I411" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="412" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A412" t="s">
+        <v>74</v>
+      </c>
+      <c r="B412" t="s">
+        <v>110</v>
+      </c>
+      <c r="C412" s="11"/>
+      <c r="D412" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E412" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F412" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G412" s="8">
+        <v>18</v>
+      </c>
+      <c r="H412" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I412" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="413" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A413" t="s">
+        <v>75</v>
+      </c>
+      <c r="B413" t="s">
+        <v>110</v>
+      </c>
+      <c r="C413" s="11"/>
+      <c r="D413" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E413" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F413" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G413" s="8">
+        <v>18</v>
+      </c>
+      <c r="H413" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I413" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="414" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A414" t="s">
+        <v>76</v>
+      </c>
+      <c r="B414" t="s">
+        <v>110</v>
+      </c>
+      <c r="C414" s="11"/>
+      <c r="D414" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E414" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F414" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G414" s="8">
+        <v>18</v>
+      </c>
+      <c r="H414" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I414" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="415" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A415" t="s">
+        <v>52</v>
+      </c>
+      <c r="B415" t="s">
+        <v>110</v>
+      </c>
+      <c r="C415" s="11"/>
+      <c r="D415" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E415" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F415" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G415" s="8">
+        <v>18</v>
+      </c>
+      <c r="H415" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I415" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="416" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A416" t="s">
+        <v>35</v>
+      </c>
+      <c r="B416" t="s">
+        <v>110</v>
+      </c>
+      <c r="C416" s="11"/>
+      <c r="D416" s="11">
+        <v>4210</v>
+      </c>
+      <c r="E416" s="11">
+        <v>4860</v>
+      </c>
+      <c r="F416" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G416" s="8">
+        <v>18</v>
+      </c>
+      <c r="H416" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I416" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="417" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A417" t="s">
+        <v>24</v>
+      </c>
+      <c r="B417" t="s">
+        <v>110</v>
+      </c>
+      <c r="C417" s="11"/>
+      <c r="D417" s="11">
+        <v>3810</v>
+      </c>
+      <c r="E417" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F417" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G417" s="8">
+        <v>18</v>
+      </c>
+      <c r="H417" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I417" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="418" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A418" t="s">
+        <v>50</v>
+      </c>
+      <c r="B418" t="s">
+        <v>110</v>
+      </c>
+      <c r="C418" s="11"/>
+      <c r="D418" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E418" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F418" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G418" s="8">
+        <v>18</v>
+      </c>
+      <c r="H418" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I418" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="419" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A419" t="s">
+        <v>29</v>
+      </c>
+      <c r="B419" t="s">
+        <v>110</v>
+      </c>
+      <c r="C419" s="11"/>
+      <c r="D419" s="11">
+        <v>3960</v>
+      </c>
+      <c r="E419" s="11">
+        <v>4360</v>
+      </c>
+      <c r="F419" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G419" s="8">
+        <v>18</v>
+      </c>
+      <c r="H419" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I419" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="420" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>27</v>
+      </c>
+      <c r="B420" t="s">
+        <v>110</v>
+      </c>
+      <c r="C420" s="11"/>
+      <c r="D420" s="11">
+        <v>3860</v>
+      </c>
+      <c r="E420" s="11">
+        <v>4160</v>
+      </c>
+      <c r="F420" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G420" s="8">
+        <v>18</v>
+      </c>
+      <c r="H420" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I420" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="421" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>48</v>
+      </c>
+      <c r="B421" t="s">
+        <v>110</v>
+      </c>
+      <c r="C421" s="11"/>
+      <c r="D421" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E421" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F421" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G421" s="8">
+        <v>18</v>
+      </c>
+      <c r="H421" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I421" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="422" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A422" t="s">
+        <v>33</v>
+      </c>
+      <c r="B422" t="s">
+        <v>110</v>
+      </c>
+      <c r="C422" s="11"/>
+      <c r="D422" s="11">
+        <v>4010</v>
+      </c>
+      <c r="E422" s="11">
+        <v>4460</v>
+      </c>
+      <c r="F422" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G422" s="8">
+        <v>18</v>
+      </c>
+      <c r="H422" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I422" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="423" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A423" t="s">
+        <v>78</v>
+      </c>
+      <c r="B423" t="s">
+        <v>110</v>
+      </c>
+      <c r="C423" s="11"/>
+      <c r="D423" s="11">
+        <v>4010</v>
+      </c>
+      <c r="E423" s="11">
+        <v>4460</v>
+      </c>
+      <c r="F423" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G423" s="8">
+        <v>18</v>
+      </c>
+      <c r="H423" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I423" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="424" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A424" t="s">
+        <v>30</v>
+      </c>
+      <c r="B424" t="s">
+        <v>110</v>
+      </c>
+      <c r="C424" s="11"/>
+      <c r="D424" s="11">
+        <v>4110</v>
+      </c>
+      <c r="E424" s="11">
+        <v>4660</v>
+      </c>
+      <c r="F424" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G424" s="8">
+        <v>18</v>
+      </c>
+      <c r="H424" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I424" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="425" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A425" t="s">
+        <v>56</v>
+      </c>
+      <c r="B425" t="s">
+        <v>110</v>
+      </c>
+      <c r="C425" s="11"/>
+      <c r="D425" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E425" s="11">
+        <v>4260</v>
+      </c>
+      <c r="F425" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G425" s="8">
+        <v>18</v>
+      </c>
+      <c r="H425" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I425" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="426" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A426" t="s">
+        <v>28</v>
+      </c>
+      <c r="B426" t="s">
+        <v>110</v>
+      </c>
+      <c r="C426" s="11"/>
+      <c r="D426" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E426" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F426" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G426" s="8">
+        <v>18</v>
+      </c>
+      <c r="H426" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I426" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="427" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A427" t="s">
+        <v>57</v>
+      </c>
+      <c r="B427" t="s">
+        <v>110</v>
+      </c>
+      <c r="C427" s="11"/>
+      <c r="D427" s="11">
+        <v>3960</v>
+      </c>
+      <c r="E427" s="11">
+        <v>4360</v>
+      </c>
+      <c r="F427" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G427" s="8">
+        <v>18</v>
+      </c>
+      <c r="H427" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I427" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="428" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A428" t="s">
+        <v>13</v>
+      </c>
+      <c r="B428" t="s">
+        <v>110</v>
+      </c>
+      <c r="C428" s="11"/>
+      <c r="D428" s="11">
+        <v>3860</v>
+      </c>
+      <c r="E428" s="11">
+        <v>4160</v>
+      </c>
+      <c r="F428" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G428" s="8">
+        <v>18</v>
+      </c>
+      <c r="H428" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I428" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>79</v>
+      </c>
+      <c r="B429" t="s">
+        <v>110</v>
+      </c>
+      <c r="C429" s="11"/>
+      <c r="D429" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E429" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F429" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G429" s="8">
+        <v>18</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I429" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>25</v>
+      </c>
+      <c r="B430" t="s">
+        <v>110</v>
+      </c>
+      <c r="C430" s="11"/>
+      <c r="D430" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E430" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F430" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G430" s="8">
+        <v>18</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I430" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>19</v>
+      </c>
+      <c r="B431" t="s">
+        <v>110</v>
+      </c>
+      <c r="C431" s="11"/>
+      <c r="D431" s="11">
+        <v>3810</v>
+      </c>
+      <c r="E431" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G431" s="8">
+        <v>18</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I431" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>21</v>
+      </c>
+      <c r="B432" t="s">
+        <v>110</v>
+      </c>
+      <c r="C432" s="11"/>
+      <c r="D432" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E432" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G432" s="8">
+        <v>18</v>
+      </c>
+      <c r="H432" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I432" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>51</v>
+      </c>
+      <c r="B433" t="s">
+        <v>110</v>
+      </c>
+      <c r="C433" s="11"/>
+      <c r="D433" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E433" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G433" s="8">
+        <v>18</v>
+      </c>
+      <c r="H433" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I433" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>53</v>
+      </c>
+      <c r="B434" t="s">
+        <v>110</v>
+      </c>
+      <c r="C434" s="11"/>
+      <c r="D434" s="11">
+        <v>4060</v>
+      </c>
+      <c r="E434" s="11">
+        <v>4560</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G434" s="8">
+        <v>18</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>80</v>
+      </c>
+      <c r="B435" t="s">
+        <v>110</v>
+      </c>
+      <c r="C435" s="11"/>
+      <c r="D435" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E435" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G435" s="8">
+        <v>18</v>
+      </c>
+      <c r="H435" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I435" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>16</v>
+      </c>
+      <c r="B436" t="s">
+        <v>110</v>
+      </c>
+      <c r="C436" s="11"/>
+      <c r="D436" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E436" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G436" s="8">
+        <v>18</v>
+      </c>
+      <c r="H436" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A437" t="s">
+        <v>87</v>
+      </c>
+      <c r="B437" t="s">
+        <v>110</v>
+      </c>
+      <c r="C437" s="11"/>
+      <c r="D437" s="11">
+        <v>3810</v>
+      </c>
+      <c r="E437" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F437" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G437" s="8">
+        <v>18</v>
+      </c>
+      <c r="H437" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I437" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A438" t="s">
+        <v>20</v>
+      </c>
+      <c r="B438" t="s">
+        <v>110</v>
+      </c>
+      <c r="C438" s="11"/>
+      <c r="D438" s="11">
+        <v>3810</v>
+      </c>
+      <c r="E438" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F438" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G438" s="8">
+        <v>18</v>
+      </c>
+      <c r="H438" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I438" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A439" t="s">
+        <v>55</v>
+      </c>
+      <c r="B439" t="s">
+        <v>110</v>
+      </c>
+      <c r="C439" s="11"/>
+      <c r="D439" s="11">
+        <v>3960</v>
+      </c>
+      <c r="E439" s="11">
+        <v>4360</v>
+      </c>
+      <c r="F439" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G439" s="8">
+        <v>18</v>
+      </c>
+      <c r="H439" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I439" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A440" t="s">
+        <v>31</v>
+      </c>
+      <c r="B440" t="s">
+        <v>110</v>
+      </c>
+      <c r="C440" s="11"/>
+      <c r="D440" s="11">
+        <v>4010</v>
+      </c>
+      <c r="E440" s="11">
+        <v>4460</v>
+      </c>
+      <c r="F440" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G440" s="8">
+        <v>18</v>
+      </c>
+      <c r="H440" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I440" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A441" t="s">
+        <v>54</v>
+      </c>
+      <c r="B441" t="s">
+        <v>110</v>
+      </c>
+      <c r="C441" s="11"/>
+      <c r="D441" s="11">
+        <v>3960</v>
+      </c>
+      <c r="E441" s="11">
+        <v>4360</v>
+      </c>
+      <c r="F441" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G441" s="8">
+        <v>18</v>
+      </c>
+      <c r="H441" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I441" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A442" t="s">
+        <v>26</v>
+      </c>
+      <c r="B442" t="s">
+        <v>110</v>
+      </c>
+      <c r="C442" s="11"/>
+      <c r="D442" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E442" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F442" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G442" s="8">
+        <v>18</v>
+      </c>
+      <c r="H442" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I442" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A443" t="s">
+        <v>49</v>
+      </c>
+      <c r="B443" t="s">
+        <v>110</v>
+      </c>
+      <c r="C443" s="11"/>
+      <c r="D443" s="11">
+        <v>3910</v>
+      </c>
+      <c r="E443" s="11">
+        <v>4210</v>
+      </c>
+      <c r="F443" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G443" s="8">
+        <v>18</v>
+      </c>
+      <c r="H443" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I443" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A444" t="s">
+        <v>5</v>
+      </c>
+      <c r="B444" t="s">
+        <v>15</v>
+      </c>
+      <c r="C444" s="11">
+        <v>3460</v>
+      </c>
+      <c r="D444" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E444" s="11">
+        <v>3660</v>
+      </c>
+      <c r="F444" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G444" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H444" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I444" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A445" t="s">
+        <v>4</v>
+      </c>
+      <c r="B445" t="s">
+        <v>15</v>
+      </c>
+      <c r="C445" s="11">
+        <v>3460</v>
+      </c>
+      <c r="D445" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E445" s="11">
+        <v>3660</v>
+      </c>
+      <c r="F445" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G445" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H445" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I445" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A446" t="s">
+        <v>74</v>
+      </c>
+      <c r="B446" t="s">
+        <v>15</v>
+      </c>
+      <c r="C446" s="11"/>
+      <c r="D446" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E446" s="11">
+        <v>3660</v>
+      </c>
+      <c r="F446" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G446" s="8">
+        <v>19</v>
+      </c>
+      <c r="H446" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I446" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A447" t="s">
+        <v>75</v>
+      </c>
+      <c r="B447" t="s">
+        <v>15</v>
+      </c>
+      <c r="C447" s="11"/>
+      <c r="D447" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E447" s="11">
+        <v>3660</v>
+      </c>
+      <c r="F447" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G447" s="8">
+        <v>19</v>
+      </c>
+      <c r="H447" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I447" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A448" t="s">
+        <v>76</v>
+      </c>
+      <c r="B448" t="s">
+        <v>15</v>
+      </c>
+      <c r="C448" s="11"/>
+      <c r="D448" s="11">
+        <v>3510</v>
+      </c>
+      <c r="E448" s="11">
+        <v>3760</v>
+      </c>
+      <c r="F448" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G448" s="8">
+        <v>19</v>
+      </c>
+      <c r="H448" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I448" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="449" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A449" t="s">
+        <v>52</v>
+      </c>
+      <c r="B449" t="s">
+        <v>15</v>
+      </c>
+      <c r="C449" s="11"/>
+      <c r="D449" s="11">
+        <v>3610</v>
+      </c>
+      <c r="E449" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F449" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G449" s="8">
+        <v>19</v>
+      </c>
+      <c r="H449" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I449" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="450" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A450" t="s">
+        <v>50</v>
+      </c>
+      <c r="B450" t="s">
+        <v>15</v>
+      </c>
+      <c r="C450" s="11"/>
+      <c r="D450" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E450" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F450" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G450" s="8">
+        <v>19</v>
+      </c>
+      <c r="H450" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I450" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="451" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A451" t="s">
+        <v>29</v>
+      </c>
+      <c r="B451" t="s">
+        <v>15</v>
+      </c>
+      <c r="C451" s="11"/>
+      <c r="D451" s="11">
+        <v>3760</v>
+      </c>
+      <c r="E451" s="11">
+        <v>4060</v>
+      </c>
+      <c r="F451" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G451" s="8">
+        <v>19</v>
+      </c>
+      <c r="H451" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I451" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="452" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A452" t="s">
+        <v>82</v>
+      </c>
+      <c r="B452" t="s">
+        <v>15</v>
+      </c>
+      <c r="C452" s="11"/>
+      <c r="D452" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E452" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F452" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G452" s="8">
+        <v>19</v>
+      </c>
+      <c r="H452" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I452" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="453" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A453" t="s">
+        <v>77</v>
+      </c>
+      <c r="B453" t="s">
+        <v>15</v>
+      </c>
+      <c r="C453" s="11"/>
+      <c r="D453" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E453" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F453" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G453" s="8">
+        <v>19</v>
+      </c>
+      <c r="H453" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I453" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="454" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A454" t="s">
+        <v>27</v>
+      </c>
+      <c r="B454" t="s">
+        <v>15</v>
+      </c>
+      <c r="C454" s="11"/>
+      <c r="D454" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E454" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F454" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G454" s="8">
+        <v>19</v>
+      </c>
+      <c r="H454" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I454" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="455" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A455" t="s">
+        <v>48</v>
+      </c>
+      <c r="B455" t="s">
+        <v>15</v>
+      </c>
+      <c r="C455" s="11"/>
+      <c r="D455" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E455" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F455" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G455" s="8">
+        <v>19</v>
+      </c>
+      <c r="H455" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I455" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="456" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A456" t="s">
+        <v>78</v>
+      </c>
+      <c r="B456" t="s">
+        <v>15</v>
+      </c>
+      <c r="C456" s="11"/>
+      <c r="D456" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E456" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F456" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G456" s="8">
+        <v>19</v>
+      </c>
+      <c r="H456" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I456" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="457" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A457" t="s">
+        <v>28</v>
+      </c>
+      <c r="B457" t="s">
+        <v>15</v>
+      </c>
+      <c r="C457" s="11"/>
+      <c r="D457" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E457" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F457" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G457" s="8">
+        <v>19</v>
+      </c>
+      <c r="H457" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I457" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="458" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A458" t="s">
+        <v>79</v>
+      </c>
+      <c r="B458" t="s">
+        <v>15</v>
+      </c>
+      <c r="C458" s="11"/>
+      <c r="D458" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E458" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F458" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G458" s="8">
+        <v>19</v>
+      </c>
+      <c r="H458" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I458" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="459" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A459" t="s">
+        <v>83</v>
+      </c>
+      <c r="B459" t="s">
+        <v>15</v>
+      </c>
+      <c r="C459" s="11"/>
+      <c r="D459" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E459" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F459" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G459" s="8">
+        <v>19</v>
+      </c>
+      <c r="H459" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I459" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="460" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A460" t="s">
+        <v>25</v>
+      </c>
+      <c r="B460" t="s">
+        <v>15</v>
+      </c>
+      <c r="C460" s="11"/>
+      <c r="D460" s="11">
+        <v>3610</v>
+      </c>
+      <c r="E460" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F460" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G460" s="8">
+        <v>19</v>
+      </c>
+      <c r="H460" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I460" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="461" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A461" t="s">
+        <v>19</v>
+      </c>
+      <c r="B461" t="s">
+        <v>15</v>
+      </c>
+      <c r="C461" s="11">
+        <v>3460</v>
+      </c>
+      <c r="D461" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E461" s="11">
+        <v>3660</v>
+      </c>
+      <c r="F461" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G461" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H461" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I461" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="462" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A462" t="s">
+        <v>21</v>
+      </c>
+      <c r="B462" t="s">
+        <v>15</v>
+      </c>
+      <c r="C462" s="11">
+        <v>3460</v>
+      </c>
+      <c r="D462" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E462" s="11">
+        <v>3660</v>
+      </c>
+      <c r="F462" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G462" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H462" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I462" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="463" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A463" t="s">
+        <v>51</v>
+      </c>
+      <c r="B463" t="s">
+        <v>15</v>
+      </c>
+      <c r="C463" s="11"/>
+      <c r="D463" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E463" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F463" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G463" s="8">
+        <v>19</v>
+      </c>
+      <c r="H463" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I463" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="464" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A464" t="s">
+        <v>80</v>
+      </c>
+      <c r="B464" t="s">
+        <v>15</v>
+      </c>
+      <c r="C464" s="11"/>
+      <c r="D464" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E464" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F464" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G464" s="8">
+        <v>19</v>
+      </c>
+      <c r="H464" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I464" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="465" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A465" t="s">
+        <v>16</v>
+      </c>
+      <c r="B465" t="s">
+        <v>15</v>
+      </c>
+      <c r="C465" s="11"/>
+      <c r="D465" s="11">
+        <v>3610</v>
+      </c>
+      <c r="E465" s="11">
+        <v>3960</v>
+      </c>
+      <c r="F465" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G465" s="8">
+        <v>19</v>
+      </c>
+      <c r="H465" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I465" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="466" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A466" t="s">
+        <v>26</v>
+      </c>
+      <c r="B466" t="s">
+        <v>15</v>
+      </c>
+      <c r="C466" s="11"/>
+      <c r="D466" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E466" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F466" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G466" s="8">
+        <v>19</v>
+      </c>
+      <c r="H466" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I466" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="467" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A467" t="s">
+        <v>49</v>
+      </c>
+      <c r="B467" t="s">
+        <v>15</v>
+      </c>
+      <c r="C467" s="11"/>
+      <c r="D467" s="11">
+        <v>3560</v>
+      </c>
+      <c r="E467" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F467" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G467" s="8">
+        <v>19</v>
+      </c>
+      <c r="H467" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I467" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="468" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A468" t="s">
+        <v>5</v>
+      </c>
+      <c r="B468" t="s">
+        <v>15</v>
+      </c>
+      <c r="C468" s="11"/>
+      <c r="D468" s="11">
+        <v>3500</v>
+      </c>
+      <c r="E468" s="11">
+        <v>3700</v>
+      </c>
+      <c r="F468" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G468" s="8">
+        <v>18</v>
+      </c>
+      <c r="H468" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I468" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="469" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A469" t="s">
+        <v>4</v>
+      </c>
+      <c r="B469" t="s">
+        <v>15</v>
+      </c>
+      <c r="C469" s="11"/>
+      <c r="D469" s="11">
+        <v>3500</v>
+      </c>
+      <c r="E469" s="11">
+        <v>3700</v>
+      </c>
+      <c r="F469" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G469" s="8">
+        <v>18</v>
+      </c>
+      <c r="H469" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I469" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="470" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A470" t="s">
+        <v>13</v>
+      </c>
+      <c r="B470" t="s">
+        <v>15</v>
+      </c>
+      <c r="C470" s="11"/>
+      <c r="D470" s="11">
+        <v>3550</v>
+      </c>
+      <c r="E470" s="11">
+        <v>3750</v>
+      </c>
+      <c r="F470" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G470" s="8">
+        <v>18</v>
+      </c>
+      <c r="H470" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I470" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="471" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A471" t="s">
+        <v>87</v>
+      </c>
+      <c r="B471" t="s">
+        <v>15</v>
+      </c>
+      <c r="C471" s="11"/>
+      <c r="D471" s="11">
+        <v>3500</v>
+      </c>
+      <c r="E471" s="11">
+        <v>3700</v>
+      </c>
+      <c r="F471" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G471" s="8">
+        <v>18</v>
+      </c>
+      <c r="H471" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I471" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="472" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A472" t="s">
+        <v>30</v>
+      </c>
+      <c r="B472" t="s">
+        <v>15</v>
+      </c>
+      <c r="C472" s="11"/>
+      <c r="D472" s="11">
+        <v>3600</v>
+      </c>
+      <c r="E472" s="11">
+        <v>3900</v>
+      </c>
+      <c r="F472" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G472" s="8">
+        <v>18</v>
+      </c>
+      <c r="H472" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I472" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="473" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A473" t="s">
+        <v>24</v>
+      </c>
+      <c r="B473" t="s">
+        <v>15</v>
+      </c>
+      <c r="C473" s="11"/>
+      <c r="D473" s="11">
+        <v>3600</v>
+      </c>
+      <c r="E473" s="11">
+        <v>3800</v>
+      </c>
+      <c r="F473" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="G473" s="8">
+        <v>18</v>
+      </c>
+      <c r="H473" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I473" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C474" s="11"/>
+      <c r="D474" s="11"/>
+      <c r="E474" s="11"/>
+      <c r="F474" s="7"/>
+      <c r="G474" s="8"/>
+      <c r="H474" s="7"/>
+      <c r="I474" s="7"/>
+    </row>
+    <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C475" s="11"/>
+      <c r="D475" s="11"/>
+      <c r="E475" s="11"/>
+      <c r="F475" s="7"/>
+      <c r="G475" s="8"/>
+      <c r="H475" s="7"/>
+      <c r="I475" s="7"/>
+    </row>
+    <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C476" s="11"/>
+      <c r="D476" s="11"/>
+      <c r="E476" s="11"/>
+      <c r="F476" s="7"/>
+      <c r="G476" s="8"/>
+      <c r="H476" s="7"/>
+      <c r="I476" s="7"/>
+    </row>
+    <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C477" s="11"/>
+      <c r="D477" s="11"/>
+      <c r="E477" s="11"/>
+      <c r="F477" s="7"/>
+      <c r="G477" s="8"/>
+      <c r="H477" s="7"/>
+      <c r="I477" s="7"/>
+    </row>
+    <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C478" s="11"/>
+      <c r="D478" s="11"/>
+      <c r="E478" s="11"/>
+      <c r="F478" s="7"/>
+      <c r="G478" s="8"/>
+      <c r="H478" s="7"/>
+      <c r="I478" s="7"/>
+    </row>
+    <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C479" s="11"/>
+      <c r="D479" s="11"/>
+      <c r="E479" s="11"/>
+      <c r="F479" s="7"/>
+      <c r="G479" s="8"/>
+      <c r="H479" s="7"/>
+      <c r="I479" s="7"/>
+    </row>
+    <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C480" s="11"/>
+      <c r="D480" s="11"/>
+      <c r="E480" s="11"/>
+      <c r="F480" s="7"/>
+      <c r="G480" s="8"/>
+      <c r="H480" s="7"/>
+      <c r="I480" s="7"/>
+    </row>
+    <row r="481" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C481" s="11"/>
+      <c r="D481" s="11"/>
+      <c r="E481" s="11"/>
+      <c r="F481" s="7"/>
+      <c r="G481" s="8"/>
+      <c r="H481" s="7"/>
+      <c r="I481" s="7"/>
+    </row>
+    <row r="482" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C482" s="11"/>
+      <c r="D482" s="11"/>
+      <c r="E482" s="11"/>
+      <c r="F482" s="7"/>
+      <c r="G482" s="8"/>
+      <c r="H482" s="7"/>
+      <c r="I482" s="7"/>
+    </row>
+    <row r="483" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C483" s="11"/>
+      <c r="D483" s="11"/>
+      <c r="E483" s="11"/>
+      <c r="F483" s="7"/>
+      <c r="G483" s="8"/>
+      <c r="H483" s="7"/>
+      <c r="I483" s="7"/>
+    </row>
+    <row r="484" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C484" s="11"/>
+      <c r="D484" s="11"/>
+      <c r="E484" s="11"/>
+      <c r="F484" s="7"/>
+      <c r="G484" s="8"/>
+      <c r="H484" s="7"/>
+      <c r="I484" s="7"/>
+    </row>
+    <row r="485" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C485" s="11"/>
+      <c r="D485" s="11"/>
+      <c r="E485" s="11"/>
+      <c r="F485" s="7"/>
+      <c r="G485" s="8"/>
+      <c r="H485" s="7"/>
+      <c r="I485" s="7"/>
+    </row>
+    <row r="486" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C486" s="11"/>
+      <c r="D486" s="11"/>
+      <c r="E486" s="11"/>
+      <c r="F486" s="7"/>
+      <c r="G486" s="8"/>
+      <c r="H486" s="7"/>
+      <c r="I486" s="7"/>
+    </row>
+    <row r="487" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C487" s="11"/>
+      <c r="D487" s="11"/>
+      <c r="E487" s="11"/>
+      <c r="F487" s="7"/>
+      <c r="G487" s="8"/>
+      <c r="H487" s="7"/>
+      <c r="I487" s="7"/>
+    </row>
+    <row r="488" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C488" s="11"/>
+      <c r="D488" s="11"/>
+      <c r="E488" s="11"/>
+      <c r="F488" s="7"/>
+      <c r="G488" s="8"/>
+      <c r="H488" s="7"/>
+      <c r="I488" s="7"/>
+    </row>
+    <row r="489" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C489" s="11"/>
+      <c r="D489" s="11"/>
+      <c r="E489" s="11"/>
+      <c r="F489" s="7"/>
+      <c r="G489" s="8"/>
+      <c r="H489" s="7"/>
+      <c r="I489" s="7"/>
+    </row>
+    <row r="490" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C490" s="11"/>
+      <c r="D490" s="11"/>
+      <c r="E490" s="11"/>
+      <c r="F490" s="7"/>
+      <c r="G490" s="8"/>
+      <c r="H490" s="7"/>
+      <c r="I490" s="7"/>
+    </row>
+    <row r="491" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C491" s="11"/>
+      <c r="D491" s="11"/>
+      <c r="E491" s="11"/>
+      <c r="F491" s="7"/>
+      <c r="G491" s="8"/>
+      <c r="H491" s="7"/>
+      <c r="I491" s="7"/>
+    </row>
+    <row r="492" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C492" s="11"/>
+      <c r="D492" s="11"/>
+      <c r="E492" s="11"/>
+      <c r="F492" s="7"/>
+      <c r="G492" s="8"/>
+      <c r="H492" s="7"/>
+      <c r="I492" s="7"/>
+    </row>
+    <row r="493" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C493" s="11"/>
+      <c r="D493" s="11"/>
+      <c r="E493" s="11"/>
+      <c r="F493" s="7"/>
+      <c r="G493" s="8"/>
+      <c r="H493" s="7"/>
+      <c r="I493" s="7"/>
+    </row>
+    <row r="494" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C494" s="11"/>
+      <c r="D494" s="11"/>
+      <c r="E494" s="11"/>
+      <c r="F494" s="7"/>
+      <c r="G494" s="8"/>
+      <c r="H494" s="7"/>
+      <c r="I494" s="7"/>
+    </row>
+    <row r="495" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C495" s="11"/>
+      <c r="D495" s="11"/>
+      <c r="E495" s="11"/>
+      <c r="F495" s="7"/>
+      <c r="G495" s="8"/>
+      <c r="H495" s="7"/>
+      <c r="I495" s="7"/>
+    </row>
+    <row r="496" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C496" s="11"/>
+      <c r="D496" s="11"/>
+      <c r="E496" s="11"/>
+      <c r="F496" s="7"/>
+      <c r="G496" s="8"/>
+      <c r="H496" s="7"/>
+      <c r="I496" s="7"/>
+    </row>
+    <row r="497" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C497" s="11"/>
+      <c r="D497" s="11"/>
+      <c r="E497" s="11"/>
+      <c r="F497" s="7"/>
+      <c r="G497" s="8"/>
+      <c r="H497" s="7"/>
+      <c r="I497" s="7"/>
+    </row>
+    <row r="498" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C498" s="11"/>
+      <c r="D498" s="11"/>
+      <c r="E498" s="11"/>
+      <c r="F498" s="7"/>
+      <c r="G498" s="8"/>
+      <c r="H498" s="7"/>
+      <c r="I498" s="7"/>
+    </row>
+    <row r="499" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C499" s="11"/>
+      <c r="D499" s="11"/>
+      <c r="E499" s="11"/>
+      <c r="F499" s="7"/>
+      <c r="G499" s="8"/>
+      <c r="H499" s="7"/>
+      <c r="I499" s="7"/>
+    </row>
+    <row r="500" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C500" s="11"/>
+      <c r="D500" s="11"/>
+      <c r="E500" s="11"/>
+      <c r="F500" s="7"/>
+      <c r="G500" s="8"/>
+      <c r="H500" s="7"/>
+      <c r="I500" s="7"/>
+    </row>
+    <row r="501" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C501" s="11"/>
+      <c r="D501" s="11"/>
+      <c r="E501" s="11"/>
+      <c r="F501" s="7"/>
+      <c r="G501" s="8"/>
+      <c r="H501" s="7"/>
+      <c r="I501" s="7"/>
+    </row>
+    <row r="502" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C502" s="11"/>
+      <c r="D502" s="11"/>
+      <c r="E502" s="11"/>
+      <c r="F502" s="7"/>
+      <c r="G502" s="8"/>
+      <c r="H502" s="7"/>
+      <c r="I502" s="7"/>
+    </row>
+    <row r="503" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C503" s="11"/>
+      <c r="D503" s="11"/>
+      <c r="E503" s="11"/>
+      <c r="F503" s="7"/>
+      <c r="G503" s="8"/>
+      <c r="H503" s="7"/>
+      <c r="I503" s="7"/>
+    </row>
+    <row r="504" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C504" s="11"/>
+      <c r="D504" s="11"/>
+      <c r="E504" s="11"/>
+      <c r="F504" s="7"/>
+      <c r="G504" s="8"/>
+      <c r="H504" s="7"/>
+      <c r="I504" s="7"/>
+    </row>
+    <row r="505" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C505" s="11"/>
+      <c r="D505" s="11"/>
+      <c r="E505" s="11"/>
+      <c r="F505" s="7"/>
+      <c r="G505" s="8"/>
+      <c r="H505" s="7"/>
+      <c r="I505" s="7"/>
+    </row>
+    <row r="506" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C506" s="11"/>
+      <c r="D506" s="11"/>
+      <c r="E506" s="11"/>
+      <c r="F506" s="7"/>
+      <c r="G506" s="8"/>
+      <c r="H506" s="7"/>
+      <c r="I506" s="7"/>
+    </row>
+    <row r="507" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C507" s="11"/>
+      <c r="D507" s="11"/>
+      <c r="E507" s="11"/>
+      <c r="F507" s="7"/>
+      <c r="G507" s="8"/>
+      <c r="H507" s="7"/>
+      <c r="I507" s="7"/>
+    </row>
+    <row r="508" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C508" s="11"/>
+      <c r="D508" s="11"/>
+      <c r="E508" s="11"/>
+      <c r="F508" s="7"/>
+      <c r="G508" s="8"/>
+      <c r="H508" s="7"/>
+      <c r="I508" s="7"/>
+    </row>
+    <row r="509" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C509" s="11"/>
+      <c r="D509" s="11"/>
+      <c r="E509" s="11"/>
+      <c r="F509" s="7"/>
+      <c r="G509" s="8"/>
+      <c r="H509" s="7"/>
+      <c r="I509" s="7"/>
+    </row>
+    <row r="510" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C510" s="11"/>
+      <c r="D510" s="11"/>
+      <c r="E510" s="11"/>
+      <c r="F510" s="7"/>
+      <c r="G510" s="8"/>
+      <c r="H510" s="7"/>
+      <c r="I510" s="7"/>
+    </row>
+    <row r="511" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C511" s="11"/>
+      <c r="D511" s="11"/>
+      <c r="E511" s="11"/>
+      <c r="F511" s="7"/>
+      <c r="G511" s="8"/>
+      <c r="H511" s="7"/>
+      <c r="I511" s="7"/>
+    </row>
+    <row r="512" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C512" s="11"/>
+      <c r="D512" s="11"/>
+      <c r="E512" s="11"/>
+      <c r="F512" s="7"/>
+      <c r="G512" s="8"/>
+      <c r="H512" s="7"/>
+      <c r="I512" s="7"/>
+    </row>
+    <row r="513" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C513" s="11"/>
+      <c r="D513" s="11"/>
+      <c r="E513" s="11"/>
+      <c r="F513" s="7"/>
+      <c r="G513" s="8"/>
+      <c r="H513" s="7"/>
+      <c r="I513" s="7"/>
+    </row>
+    <row r="514" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C514" s="11"/>
+      <c r="D514" s="11"/>
+      <c r="E514" s="11"/>
+      <c r="F514" s="7"/>
+      <c r="G514" s="8"/>
+      <c r="H514" s="7"/>
+      <c r="I514" s="7"/>
+    </row>
+    <row r="515" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C515" s="11"/>
+      <c r="D515" s="11"/>
+      <c r="E515" s="11"/>
+      <c r="F515" s="7"/>
+      <c r="G515" s="8"/>
+      <c r="H515" s="7"/>
+      <c r="I515" s="7"/>
+    </row>
+    <row r="516" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C516" s="11"/>
+      <c r="D516" s="11"/>
+      <c r="E516" s="11"/>
+      <c r="F516" s="7"/>
+      <c r="G516" s="8"/>
+      <c r="H516" s="7"/>
+      <c r="I516" s="7"/>
+    </row>
+    <row r="517" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C517" s="11"/>
+      <c r="D517" s="11"/>
+      <c r="E517" s="11"/>
+      <c r="F517" s="7"/>
+      <c r="G517" s="8"/>
+      <c r="H517" s="7"/>
+      <c r="I517" s="7"/>
+    </row>
+    <row r="518" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C518" s="11"/>
+      <c r="D518" s="11"/>
+      <c r="E518" s="11"/>
+      <c r="F518" s="7"/>
+      <c r="G518" s="8"/>
+      <c r="H518" s="7"/>
+      <c r="I518" s="7"/>
+    </row>
+    <row r="519" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C519" s="11"/>
+      <c r="D519" s="11"/>
+      <c r="E519" s="11"/>
+      <c r="F519" s="7"/>
+      <c r="G519" s="8"/>
+      <c r="H519" s="7"/>
+      <c r="I519" s="7"/>
+    </row>
+    <row r="520" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C520" s="11"/>
+      <c r="D520" s="11"/>
+      <c r="E520" s="11"/>
+      <c r="F520" s="7"/>
+      <c r="G520" s="8"/>
+      <c r="H520" s="7"/>
+      <c r="I520" s="7"/>
+    </row>
+    <row r="521" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C521" s="11"/>
+      <c r="D521" s="11"/>
+      <c r="E521" s="11"/>
+      <c r="F521" s="7"/>
+      <c r="G521" s="8"/>
+      <c r="H521" s="7"/>
+      <c r="I521" s="7"/>
+    </row>
+    <row r="522" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C522" s="11"/>
+      <c r="D522" s="11"/>
+      <c r="E522" s="11"/>
+      <c r="F522" s="7"/>
+      <c r="G522" s="8"/>
+      <c r="H522" s="7"/>
+      <c r="I522" s="7"/>
+    </row>
+    <row r="523" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C523" s="11"/>
+      <c r="D523" s="11"/>
+      <c r="E523" s="11"/>
+      <c r="F523" s="7"/>
+      <c r="G523" s="8"/>
+      <c r="H523" s="7"/>
+      <c r="I523" s="7"/>
+    </row>
+    <row r="524" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C524" s="11"/>
+      <c r="D524" s="11"/>
+      <c r="E524" s="11"/>
+      <c r="F524" s="7"/>
+      <c r="G524" s="8"/>
+      <c r="H524" s="7"/>
+      <c r="I524" s="7"/>
+    </row>
+    <row r="525" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C525" s="11"/>
+      <c r="D525" s="11"/>
+      <c r="E525" s="11"/>
+      <c r="F525" s="7"/>
+      <c r="G525" s="8"/>
+      <c r="H525" s="7"/>
+      <c r="I525" s="7"/>
+    </row>
+    <row r="526" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C526" s="11"/>
+      <c r="D526" s="11"/>
+      <c r="E526" s="11"/>
+      <c r="F526" s="7"/>
+      <c r="G526" s="8"/>
+      <c r="H526" s="7"/>
+      <c r="I526" s="7"/>
+    </row>
+    <row r="527" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C527" s="11"/>
+      <c r="D527" s="11"/>
+      <c r="E527" s="11"/>
+      <c r="F527" s="7"/>
+      <c r="G527" s="8"/>
+      <c r="H527" s="7"/>
+      <c r="I527" s="7"/>
+    </row>
+    <row r="528" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C528" s="11"/>
+      <c r="D528" s="11"/>
+      <c r="E528" s="11"/>
+      <c r="F528" s="7"/>
+      <c r="G528" s="8"/>
+      <c r="H528" s="7"/>
+      <c r="I528" s="7"/>
+    </row>
+    <row r="529" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C529" s="11"/>
+      <c r="D529" s="11"/>
+      <c r="E529" s="11"/>
+      <c r="F529" s="7"/>
+      <c r="G529" s="8"/>
+      <c r="H529" s="7"/>
+      <c r="I529" s="7"/>
+    </row>
+    <row r="530" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C530" s="11"/>
+      <c r="D530" s="11"/>
+      <c r="E530" s="11"/>
+      <c r="F530" s="7"/>
+      <c r="G530" s="8"/>
+      <c r="H530" s="7"/>
+      <c r="I530" s="7"/>
+    </row>
+    <row r="531" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C531" s="11"/>
+      <c r="D531" s="11"/>
+      <c r="E531" s="11"/>
+      <c r="F531" s="7"/>
+      <c r="G531" s="8"/>
+      <c r="H531" s="7"/>
+      <c r="I531" s="7"/>
+    </row>
+    <row r="532" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C532" s="11"/>
+      <c r="D532" s="11"/>
+      <c r="E532" s="11"/>
+      <c r="F532" s="7"/>
+      <c r="G532" s="8"/>
+      <c r="H532" s="7"/>
+      <c r="I532" s="7"/>
+    </row>
+    <row r="533" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C533" s="11"/>
+      <c r="D533" s="11"/>
+      <c r="E533" s="11"/>
+      <c r="F533" s="7"/>
+      <c r="G533" s="8"/>
+      <c r="H533" s="7"/>
+      <c r="I533" s="7"/>
+    </row>
+    <row r="534" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C534" s="11"/>
+      <c r="D534" s="11"/>
+      <c r="E534" s="11"/>
+      <c r="F534" s="7"/>
+      <c r="G534" s="8"/>
+      <c r="H534" s="7"/>
+      <c r="I534" s="7"/>
+    </row>
+    <row r="535" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C535" s="11"/>
+      <c r="D535" s="11"/>
+      <c r="E535" s="11"/>
+      <c r="F535" s="7"/>
+      <c r="G535" s="8"/>
+      <c r="H535" s="7"/>
+      <c r="I535" s="7"/>
+    </row>
+    <row r="536" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C536" s="11"/>
+      <c r="D536" s="11"/>
+      <c r="E536" s="11"/>
+      <c r="F536" s="7"/>
+      <c r="G536" s="8"/>
+      <c r="H536" s="7"/>
+      <c r="I536" s="7"/>
+    </row>
+    <row r="537" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C537" s="11"/>
+      <c r="D537" s="11"/>
+      <c r="E537" s="11"/>
+      <c r="F537" s="7"/>
+      <c r="G537" s="8"/>
+      <c r="H537" s="7"/>
+      <c r="I537" s="7"/>
+    </row>
+    <row r="538" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C538" s="11"/>
+      <c r="D538" s="11"/>
+      <c r="E538" s="11"/>
+      <c r="F538" s="7"/>
+      <c r="G538" s="8"/>
+      <c r="H538" s="7"/>
+      <c r="I538" s="7"/>
+    </row>
+    <row r="539" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C539" s="11"/>
+      <c r="D539" s="11"/>
+      <c r="E539" s="11"/>
+      <c r="F539" s="7"/>
+      <c r="G539" s="8"/>
+      <c r="H539" s="7"/>
+      <c r="I539" s="7"/>
+    </row>
+    <row r="540" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C540" s="11"/>
+      <c r="D540" s="11"/>
+      <c r="E540" s="11"/>
+      <c r="F540" s="7"/>
+      <c r="G540" s="8"/>
+      <c r="H540" s="7"/>
+      <c r="I540" s="7"/>
+    </row>
+    <row r="541" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C541" s="11"/>
+      <c r="D541" s="11"/>
+      <c r="E541" s="11"/>
+      <c r="F541" s="7"/>
+      <c r="G541" s="8"/>
+      <c r="H541" s="7"/>
+      <c r="I541" s="7"/>
+    </row>
+    <row r="542" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C542" s="11"/>
+      <c r="D542" s="11"/>
+      <c r="E542" s="11"/>
+      <c r="F542" s="7"/>
+      <c r="G542" s="8"/>
+      <c r="H542" s="7"/>
+      <c r="I542" s="7"/>
+    </row>
+    <row r="543" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C543" s="11"/>
+      <c r="D543" s="11"/>
+      <c r="E543" s="11"/>
+      <c r="F543" s="7"/>
+      <c r="G543" s="8"/>
+      <c r="H543" s="7"/>
+      <c r="I543" s="7"/>
+    </row>
+    <row r="544" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C544" s="11"/>
+      <c r="D544" s="11"/>
+      <c r="E544" s="11"/>
+      <c r="F544" s="7"/>
+      <c r="G544" s="8"/>
+      <c r="H544" s="7"/>
+      <c r="I544" s="7"/>
+    </row>
+    <row r="545" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C545" s="11"/>
+      <c r="D545" s="11"/>
+      <c r="E545" s="11"/>
+      <c r="F545" s="7"/>
+      <c r="G545" s="8"/>
+      <c r="H545" s="7"/>
+      <c r="I545" s="7"/>
+    </row>
+    <row r="546" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C546" s="11"/>
+      <c r="D546" s="11"/>
+      <c r="E546" s="11"/>
+      <c r="F546" s="7"/>
+      <c r="G546" s="8"/>
+      <c r="H546" s="7"/>
+      <c r="I546" s="7"/>
+    </row>
+    <row r="547" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C547" s="11"/>
+      <c r="D547" s="11"/>
+      <c r="E547" s="11"/>
+      <c r="F547" s="7"/>
+      <c r="G547" s="8"/>
+      <c r="H547" s="7"/>
+      <c r="I547" s="7"/>
+    </row>
+    <row r="548" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C548" s="11"/>
+      <c r="D548" s="11"/>
+      <c r="E548" s="11"/>
+      <c r="F548" s="7"/>
+      <c r="G548" s="8"/>
+      <c r="H548" s="7"/>
+      <c r="I548" s="7"/>
+    </row>
+    <row r="549" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C549" s="11"/>
+      <c r="D549" s="11"/>
+      <c r="E549" s="11"/>
+      <c r="F549" s="7"/>
+      <c r="G549" s="8"/>
+      <c r="H549" s="7"/>
+      <c r="I549" s="7"/>
+    </row>
+    <row r="550" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C550" s="11"/>
+      <c r="D550" s="11"/>
+      <c r="E550" s="11"/>
+      <c r="F550" s="7"/>
+      <c r="G550" s="8"/>
+      <c r="H550" s="7"/>
+      <c r="I550" s="7"/>
+    </row>
+    <row r="551" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C551" s="11"/>
+      <c r="D551" s="11"/>
+      <c r="E551" s="11"/>
+      <c r="F551" s="7"/>
+      <c r="G551" s="8"/>
+      <c r="H551" s="7"/>
+      <c r="I551" s="7"/>
+    </row>
+    <row r="552" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C552" s="11"/>
+      <c r="D552" s="11"/>
+      <c r="E552" s="11"/>
+      <c r="F552" s="7"/>
+      <c r="G552" s="8"/>
+      <c r="H552" s="7"/>
+      <c r="I552" s="7"/>
+    </row>
+    <row r="553" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C553" s="11"/>
+      <c r="D553" s="11"/>
+      <c r="E553" s="11"/>
+      <c r="F553" s="7"/>
+      <c r="G553" s="8"/>
+      <c r="H553" s="7"/>
+      <c r="I553" s="7"/>
+    </row>
+    <row r="554" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C554" s="11"/>
+      <c r="D554" s="11"/>
+      <c r="E554" s="11"/>
+      <c r="F554" s="7"/>
+      <c r="G554" s="8"/>
+      <c r="H554" s="7"/>
+      <c r="I554" s="7"/>
+    </row>
+    <row r="555" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C555" s="11"/>
+      <c r="D555" s="11"/>
+      <c r="E555" s="11"/>
+      <c r="F555" s="7"/>
+      <c r="G555" s="8"/>
+      <c r="H555" s="7"/>
+      <c r="I555" s="7"/>
+    </row>
+    <row r="556" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C556" s="11"/>
+      <c r="D556" s="11"/>
+      <c r="E556" s="11"/>
+      <c r="F556" s="7"/>
+      <c r="G556" s="8"/>
+      <c r="H556" s="7"/>
+      <c r="I556" s="7"/>
+    </row>
+    <row r="557" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C557" s="11"/>
+      <c r="D557" s="11"/>
+      <c r="E557" s="11"/>
+      <c r="F557" s="7"/>
+      <c r="G557" s="8"/>
+      <c r="H557" s="7"/>
+      <c r="I557" s="7"/>
+    </row>
+    <row r="558" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C558" s="11"/>
+      <c r="D558" s="11"/>
+      <c r="E558" s="11"/>
+      <c r="F558" s="7"/>
+      <c r="G558" s="8"/>
+      <c r="H558" s="7"/>
+      <c r="I558" s="7"/>
+    </row>
+    <row r="559" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C559" s="11"/>
+      <c r="D559" s="11"/>
+      <c r="E559" s="11"/>
+      <c r="F559" s="7"/>
+      <c r="G559" s="8"/>
+      <c r="H559" s="7"/>
+      <c r="I559" s="7"/>
+    </row>
+    <row r="560" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C560" s="11"/>
+      <c r="D560" s="11"/>
+      <c r="E560" s="11"/>
+      <c r="F560" s="7"/>
+      <c r="G560" s="8"/>
+      <c r="H560" s="7"/>
+      <c r="I560" s="7"/>
+    </row>
+    <row r="561" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C561" s="11"/>
+      <c r="D561" s="11"/>
+      <c r="E561" s="11"/>
+      <c r="F561" s="7"/>
+      <c r="G561" s="8"/>
+      <c r="H561" s="7"/>
+      <c r="I561" s="7"/>
+    </row>
+    <row r="562" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C562" s="11"/>
+      <c r="D562" s="11"/>
+      <c r="E562" s="11"/>
+      <c r="F562" s="7"/>
+      <c r="G562" s="8"/>
+      <c r="H562" s="7"/>
+      <c r="I562" s="7"/>
+    </row>
+    <row r="563" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C563" s="11"/>
+      <c r="D563" s="11"/>
+      <c r="E563" s="11"/>
+      <c r="F563" s="7"/>
+      <c r="G563" s="8"/>
+      <c r="H563" s="7"/>
+      <c r="I563" s="7"/>
+    </row>
+    <row r="564" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C564" s="11"/>
+      <c r="D564" s="11"/>
+      <c r="E564" s="11"/>
+      <c r="F564" s="7"/>
+      <c r="G564" s="8"/>
+      <c r="H564" s="7"/>
+      <c r="I564" s="7"/>
+    </row>
+    <row r="565" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C565" s="11"/>
+      <c r="D565" s="11"/>
+      <c r="E565" s="11"/>
+      <c r="F565" s="7"/>
+      <c r="G565" s="8"/>
+      <c r="H565" s="7"/>
+      <c r="I565" s="7"/>
+    </row>
+    <row r="566" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C566" s="11"/>
+      <c r="D566" s="11"/>
+      <c r="E566" s="11"/>
+      <c r="F566" s="7"/>
+      <c r="G566" s="8"/>
+      <c r="H566" s="7"/>
+      <c r="I566" s="7"/>
+    </row>
+    <row r="567" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C567" s="11"/>
+      <c r="D567" s="11"/>
+      <c r="E567" s="11"/>
+      <c r="F567" s="7"/>
+      <c r="G567" s="8"/>
+      <c r="H567" s="7"/>
+      <c r="I567" s="7"/>
+    </row>
+    <row r="568" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C568" s="11"/>
+      <c r="D568" s="11"/>
+      <c r="E568" s="11"/>
+      <c r="F568" s="7"/>
+      <c r="G568" s="8"/>
+      <c r="H568" s="7"/>
+      <c r="I568" s="7"/>
+    </row>
+    <row r="569" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C569" s="11"/>
+      <c r="D569" s="11"/>
+      <c r="E569" s="11"/>
+      <c r="F569" s="7"/>
+      <c r="G569" s="8"/>
+      <c r="H569" s="7"/>
+      <c r="I569" s="7"/>
+    </row>
+    <row r="570" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C570" s="11"/>
+      <c r="D570" s="11"/>
+      <c r="E570" s="11"/>
+      <c r="F570" s="7"/>
+      <c r="G570" s="8"/>
+      <c r="H570" s="7"/>
+      <c r="I570" s="7"/>
+    </row>
+    <row r="571" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C571" s="11"/>
+      <c r="D571" s="11"/>
+      <c r="E571" s="11"/>
+      <c r="F571" s="7"/>
+      <c r="G571" s="8"/>
+      <c r="H571" s="7"/>
+      <c r="I571" s="7"/>
+    </row>
+    <row r="572" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C572" s="11"/>
+      <c r="D572" s="11"/>
+      <c r="E572" s="11"/>
+      <c r="F572" s="7"/>
+      <c r="G572" s="8"/>
+      <c r="H572" s="7"/>
+      <c r="I572" s="7"/>
+    </row>
+    <row r="573" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C573" s="11"/>
+      <c r="D573" s="11"/>
+      <c r="E573" s="11"/>
+      <c r="F573" s="7"/>
+      <c r="G573" s="8"/>
+      <c r="H573" s="7"/>
+      <c r="I573" s="7"/>
+    </row>
+    <row r="574" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C574" s="11"/>
+      <c r="D574" s="11"/>
+      <c r="E574" s="11"/>
+      <c r="F574" s="7"/>
+      <c r="G574" s="8"/>
+      <c r="H574" s="7"/>
+      <c r="I574" s="7"/>
+    </row>
+    <row r="575" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C575" s="11"/>
+      <c r="D575" s="11"/>
+      <c r="E575" s="11"/>
+      <c r="F575" s="7"/>
+      <c r="G575" s="8"/>
+      <c r="H575" s="7"/>
+      <c r="I575" s="7"/>
+    </row>
+    <row r="576" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C576" s="11"/>
+      <c r="D576" s="11"/>
+      <c r="E576" s="11"/>
+      <c r="F576" s="7"/>
+      <c r="G576" s="8"/>
+      <c r="H576" s="7"/>
+      <c r="I576" s="7"/>
+    </row>
+    <row r="577" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C577" s="11"/>
+      <c r="D577" s="11"/>
+      <c r="E577" s="11"/>
+      <c r="F577" s="7"/>
+      <c r="G577" s="8"/>
+      <c r="H577" s="7"/>
+      <c r="I577" s="7"/>
+    </row>
+    <row r="578" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C578" s="11"/>
+      <c r="D578" s="11"/>
+      <c r="E578" s="11"/>
+      <c r="F578" s="7"/>
+      <c r="G578" s="8"/>
+      <c r="H578" s="7"/>
+      <c r="I578" s="7"/>
+    </row>
+    <row r="579" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C579" s="11"/>
+      <c r="D579" s="11"/>
+      <c r="E579" s="11"/>
+      <c r="F579" s="7"/>
+      <c r="G579" s="8"/>
+      <c r="H579" s="7"/>
+      <c r="I579" s="7"/>
+    </row>
+    <row r="580" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C580" s="11"/>
+      <c r="D580" s="11"/>
+      <c r="E580" s="11"/>
+      <c r="F580" s="7"/>
+      <c r="G580" s="8"/>
+      <c r="H580" s="7"/>
+      <c r="I580" s="7"/>
+    </row>
+    <row r="581" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C581" s="11"/>
+      <c r="D581" s="11"/>
+      <c r="E581" s="11"/>
+      <c r="F581" s="7"/>
+      <c r="G581" s="8"/>
+      <c r="H581" s="7"/>
+      <c r="I581" s="7"/>
+    </row>
+    <row r="582" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C582" s="11"/>
+      <c r="D582" s="11"/>
+      <c r="E582" s="11"/>
+      <c r="F582" s="7"/>
+      <c r="G582" s="8"/>
+      <c r="H582" s="7"/>
+      <c r="I582" s="7"/>
+    </row>
+    <row r="583" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C583" s="11"/>
+      <c r="D583" s="11"/>
+      <c r="E583" s="11"/>
+      <c r="F583" s="7"/>
+      <c r="G583" s="8"/>
+      <c r="H583" s="7"/>
+      <c r="I583" s="7"/>
+    </row>
+    <row r="584" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C584" s="11"/>
+      <c r="D584" s="11"/>
+      <c r="E584" s="11"/>
+      <c r="F584" s="7"/>
+      <c r="G584" s="8"/>
+      <c r="H584" s="7"/>
+      <c r="I584" s="7"/>
+    </row>
+    <row r="585" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C585" s="11"/>
+      <c r="D585" s="11"/>
+      <c r="E585" s="11"/>
+      <c r="F585" s="7"/>
+      <c r="G585" s="8"/>
+      <c r="H585" s="7"/>
+      <c r="I585" s="7"/>
+    </row>
+    <row r="586" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C586" s="11"/>
+      <c r="D586" s="11"/>
+      <c r="E586" s="11"/>
+      <c r="F586" s="7"/>
+      <c r="G586" s="8"/>
+      <c r="H586" s="7"/>
+      <c r="I586" s="7"/>
+    </row>
+    <row r="587" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C587" s="11"/>
+      <c r="D587" s="11"/>
+      <c r="E587" s="11"/>
+      <c r="F587" s="7"/>
+      <c r="G587" s="8"/>
+      <c r="H587" s="7"/>
+      <c r="I587" s="7"/>
+    </row>
+    <row r="588" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C588" s="11"/>
+      <c r="D588" s="11"/>
+      <c r="E588" s="11"/>
+      <c r="F588" s="7"/>
+      <c r="G588" s="8"/>
+      <c r="H588" s="7"/>
+      <c r="I588" s="7"/>
+    </row>
+    <row r="589" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C589" s="11"/>
+      <c r="D589" s="11"/>
+      <c r="E589" s="11"/>
+      <c r="F589" s="7"/>
+      <c r="G589" s="8"/>
+      <c r="H589" s="7"/>
+      <c r="I589" s="7"/>
+    </row>
+    <row r="590" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C590" s="11"/>
+      <c r="D590" s="11"/>
+      <c r="E590" s="11"/>
+      <c r="F590" s="7"/>
+      <c r="G590" s="8"/>
+      <c r="H590" s="7"/>
+      <c r="I590" s="7"/>
+    </row>
+    <row r="591" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C591" s="11"/>
+      <c r="D591" s="11"/>
+      <c r="E591" s="11"/>
+      <c r="F591" s="7"/>
+      <c r="G591" s="8"/>
+      <c r="H591" s="7"/>
+      <c r="I591" s="7"/>
+    </row>
+    <row r="592" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C592" s="11"/>
+      <c r="D592" s="11"/>
+      <c r="E592" s="11"/>
+      <c r="F592" s="7"/>
+      <c r="G592" s="8"/>
+      <c r="H592" s="7"/>
+      <c r="I592" s="7"/>
+    </row>
+    <row r="593" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C593" s="11"/>
+      <c r="D593" s="11"/>
+      <c r="E593" s="11"/>
+      <c r="F593" s="7"/>
+      <c r="G593" s="8"/>
+      <c r="H593" s="7"/>
+      <c r="I593" s="7"/>
+    </row>
+    <row r="594" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C594" s="11"/>
+      <c r="D594" s="11"/>
+      <c r="E594" s="11"/>
+      <c r="F594" s="7"/>
+      <c r="G594" s="8"/>
+      <c r="H594" s="7"/>
+      <c r="I594" s="7"/>
+    </row>
+    <row r="595" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C595" s="11"/>
+      <c r="D595" s="11"/>
+      <c r="E595" s="11"/>
+      <c r="F595" s="7"/>
+      <c r="G595" s="8"/>
+      <c r="H595" s="7"/>
+      <c r="I595" s="7"/>
+    </row>
+    <row r="596" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C596" s="11"/>
+      <c r="D596" s="11"/>
+      <c r="E596" s="11"/>
+      <c r="F596" s="7"/>
+      <c r="G596" s="8"/>
+      <c r="H596" s="7"/>
+      <c r="I596" s="7"/>
+    </row>
+    <row r="597" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C597" s="11"/>
+      <c r="D597" s="11"/>
+      <c r="E597" s="11"/>
+      <c r="F597" s="7"/>
+      <c r="G597" s="8"/>
+      <c r="H597" s="7"/>
+      <c r="I597" s="7"/>
+    </row>
+    <row r="598" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C598" s="11"/>
+      <c r="D598" s="11"/>
+      <c r="E598" s="11"/>
+      <c r="F598" s="7"/>
+      <c r="G598" s="8"/>
+      <c r="H598" s="7"/>
+      <c r="I598" s="7"/>
+    </row>
+    <row r="599" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C599" s="11"/>
+      <c r="D599" s="11"/>
+      <c r="E599" s="11"/>
+      <c r="F599" s="7"/>
+      <c r="G599" s="8"/>
+      <c r="H599" s="7"/>
+      <c r="I599" s="7"/>
+    </row>
+    <row r="600" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C600" s="11"/>
+      <c r="D600" s="11"/>
+      <c r="E600" s="11"/>
+      <c r="F600" s="7"/>
+      <c r="G600" s="8"/>
+      <c r="H600" s="7"/>
+      <c r="I600" s="7"/>
+    </row>
+    <row r="601" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C601" s="11"/>
+      <c r="D601" s="11"/>
+      <c r="E601" s="11"/>
+      <c r="F601" s="7"/>
+      <c r="G601" s="8"/>
+      <c r="H601" s="7"/>
+      <c r="I601" s="7"/>
+    </row>
+    <row r="602" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C602" s="11"/>
+      <c r="D602" s="11"/>
+      <c r="E602" s="11"/>
+      <c r="F602" s="7"/>
+      <c r="G602" s="8"/>
+      <c r="H602" s="7"/>
+      <c r="I602" s="7"/>
+    </row>
+    <row r="603" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C603" s="11"/>
+      <c r="D603" s="11"/>
+      <c r="E603" s="11"/>
+      <c r="F603" s="7"/>
+      <c r="G603" s="8"/>
+      <c r="H603" s="7"/>
+      <c r="I603" s="7"/>
+    </row>
+    <row r="604" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C604" s="11"/>
+      <c r="D604" s="11"/>
+      <c r="E604" s="11"/>
+      <c r="F604" s="7"/>
+      <c r="G604" s="8"/>
+      <c r="H604" s="7"/>
+      <c r="I604" s="7"/>
+    </row>
+    <row r="605" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C605" s="11"/>
+      <c r="D605" s="11"/>
+      <c r="E605" s="11"/>
+      <c r="F605" s="7"/>
+      <c r="G605" s="8"/>
+      <c r="H605" s="7"/>
+      <c r="I605" s="7"/>
+    </row>
+    <row r="606" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C606" s="11"/>
+      <c r="D606" s="11"/>
+      <c r="E606" s="11"/>
+      <c r="F606" s="7"/>
+      <c r="G606" s="8"/>
+      <c r="H606" s="7"/>
+      <c r="I606" s="7"/>
+    </row>
+    <row r="607" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C607" s="11"/>
+      <c r="D607" s="11"/>
+      <c r="E607" s="11"/>
+      <c r="F607" s="7"/>
+      <c r="G607" s="8"/>
+      <c r="H607" s="7"/>
+      <c r="I607" s="7"/>
+    </row>
+    <row r="608" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C608" s="11"/>
+      <c r="D608" s="11"/>
+      <c r="E608" s="11"/>
+      <c r="F608" s="7"/>
+      <c r="G608" s="8"/>
+      <c r="H608" s="7"/>
+      <c r="I608" s="7"/>
+    </row>
+    <row r="609" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C609" s="11"/>
+      <c r="D609" s="11"/>
+      <c r="E609" s="11"/>
+      <c r="F609" s="7"/>
+      <c r="G609" s="8"/>
+      <c r="H609" s="7"/>
+      <c r="I609" s="7"/>
+    </row>
+    <row r="610" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C610" s="11"/>
+      <c r="D610" s="11"/>
+      <c r="E610" s="11"/>
+      <c r="F610" s="7"/>
+      <c r="G610" s="8"/>
+      <c r="H610" s="7"/>
+      <c r="I610" s="7"/>
+    </row>
+    <row r="611" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C611" s="11"/>
+      <c r="D611" s="11"/>
+      <c r="E611" s="11"/>
+      <c r="F611" s="7"/>
+      <c r="G611" s="8"/>
+      <c r="H611" s="7"/>
+      <c r="I611" s="7"/>
+    </row>
+    <row r="612" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C612" s="11"/>
+      <c r="D612" s="11"/>
+      <c r="E612" s="11"/>
+      <c r="F612" s="7"/>
+      <c r="G612" s="8"/>
+      <c r="H612" s="7"/>
+      <c r="I612" s="7"/>
+    </row>
+    <row r="613" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C613" s="11"/>
+      <c r="D613" s="11"/>
+      <c r="E613" s="11"/>
+      <c r="F613" s="7"/>
+      <c r="G613" s="8"/>
+      <c r="H613" s="7"/>
+      <c r="I613" s="7"/>
+    </row>
+    <row r="614" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C614" s="11"/>
+      <c r="D614" s="11"/>
+      <c r="E614" s="11"/>
+      <c r="F614" s="7"/>
+      <c r="G614" s="8"/>
+      <c r="H614" s="7"/>
+      <c r="I614" s="7"/>
+    </row>
+    <row r="615" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C615" s="11"/>
+      <c r="D615" s="11"/>
+      <c r="E615" s="11"/>
+      <c r="F615" s="7"/>
+      <c r="G615" s="8"/>
+      <c r="H615" s="7"/>
+      <c r="I615" s="7"/>
+    </row>
+    <row r="616" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C616" s="11"/>
+      <c r="D616" s="11"/>
+      <c r="E616" s="11"/>
+      <c r="F616" s="7"/>
+      <c r="G616" s="8"/>
+      <c r="H616" s="7"/>
+      <c r="I616" s="7"/>
+    </row>
+    <row r="617" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C617" s="11"/>
+      <c r="D617" s="11"/>
+      <c r="E617" s="11"/>
+      <c r="F617" s="7"/>
+      <c r="G617" s="8"/>
+      <c r="H617" s="7"/>
+      <c r="I617" s="7"/>
+    </row>
+    <row r="618" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C618" s="11"/>
+      <c r="D618" s="11"/>
+      <c r="E618" s="11"/>
+      <c r="F618" s="7"/>
+      <c r="G618" s="8"/>
+      <c r="H618" s="7"/>
+      <c r="I618" s="7"/>
+    </row>
+    <row r="619" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C619" s="11"/>
+      <c r="D619" s="11"/>
+      <c r="E619" s="11"/>
+      <c r="F619" s="7"/>
+      <c r="G619" s="8"/>
+      <c r="H619" s="7"/>
+      <c r="I619" s="7"/>
+    </row>
+    <row r="620" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C620" s="11"/>
+      <c r="D620" s="11"/>
+      <c r="E620" s="11"/>
+      <c r="F620" s="7"/>
+      <c r="G620" s="8"/>
+      <c r="H620" s="7"/>
+      <c r="I620" s="7"/>
+    </row>
+    <row r="621" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C621" s="11"/>
+      <c r="D621" s="11"/>
+      <c r="E621" s="11"/>
+      <c r="F621" s="7"/>
+      <c r="G621" s="8"/>
+      <c r="H621" s="7"/>
+      <c r="I621" s="7"/>
+    </row>
+    <row r="622" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C622" s="11"/>
+      <c r="D622" s="11"/>
+      <c r="E622" s="11"/>
+      <c r="F622" s="7"/>
+      <c r="G622" s="8"/>
+      <c r="H622" s="7"/>
+      <c r="I622" s="7"/>
+    </row>
+    <row r="623" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C623" s="11"/>
+      <c r="D623" s="11"/>
+      <c r="E623" s="11"/>
+      <c r="F623" s="7"/>
+      <c r="G623" s="8"/>
+      <c r="H623" s="7"/>
+      <c r="I623" s="7"/>
+    </row>
+    <row r="624" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C624" s="11"/>
+      <c r="D624" s="11"/>
+      <c r="E624" s="11"/>
+      <c r="F624" s="7"/>
+      <c r="G624" s="8"/>
+      <c r="H624" s="7"/>
+      <c r="I624" s="7"/>
+    </row>
+    <row r="625" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C625" s="11"/>
+      <c r="D625" s="11"/>
+      <c r="E625" s="11"/>
+      <c r="F625" s="7"/>
+      <c r="G625" s="8"/>
+      <c r="H625" s="7"/>
+      <c r="I625" s="7"/>
+    </row>
+    <row r="626" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C626" s="11"/>
+      <c r="D626" s="11"/>
+      <c r="E626" s="11"/>
+      <c r="F626" s="7"/>
+      <c r="G626" s="8"/>
+      <c r="H626" s="7"/>
+      <c r="I626" s="7"/>
+    </row>
+    <row r="627" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C627" s="11"/>
+      <c r="D627" s="11"/>
+      <c r="E627" s="11"/>
+      <c r="F627" s="7"/>
+      <c r="G627" s="8"/>
+      <c r="H627" s="7"/>
+      <c r="I627" s="7"/>
+    </row>
+    <row r="628" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C628" s="11"/>
+      <c r="D628" s="11"/>
+      <c r="E628" s="11"/>
+      <c r="F628" s="7"/>
+      <c r="G628" s="8"/>
+      <c r="H628" s="7"/>
+      <c r="I628" s="7"/>
+    </row>
+    <row r="629" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C629" s="11"/>
+      <c r="D629" s="11"/>
+      <c r="E629" s="11"/>
+      <c r="F629" s="7"/>
+      <c r="G629" s="8"/>
+      <c r="H629" s="7"/>
+      <c r="I629" s="7"/>
+    </row>
+    <row r="630" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C630" s="11"/>
+      <c r="D630" s="11"/>
+      <c r="E630" s="11"/>
+      <c r="F630" s="7"/>
+      <c r="G630" s="8"/>
+      <c r="H630" s="7"/>
+      <c r="I630" s="7"/>
+    </row>
+    <row r="631" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C631" s="11"/>
+      <c r="D631" s="11"/>
+      <c r="E631" s="11"/>
+      <c r="F631" s="7"/>
+      <c r="G631" s="8"/>
+      <c r="H631" s="7"/>
+      <c r="I631" s="7"/>
+    </row>
+    <row r="632" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C632" s="11"/>
+      <c r="D632" s="11"/>
+      <c r="E632" s="11"/>
+      <c r="F632" s="7"/>
+      <c r="G632" s="8"/>
+      <c r="H632" s="7"/>
+      <c r="I632" s="7"/>
+    </row>
+    <row r="633" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C633" s="11"/>
+      <c r="D633" s="11"/>
+      <c r="E633" s="11"/>
+      <c r="F633" s="7"/>
+      <c r="G633" s="8"/>
+      <c r="H633" s="7"/>
+      <c r="I633" s="7"/>
+    </row>
+    <row r="634" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C634" s="11"/>
+      <c r="D634" s="11"/>
+      <c r="E634" s="11"/>
+      <c r="F634" s="7"/>
+      <c r="G634" s="8"/>
+      <c r="H634" s="7"/>
+      <c r="I634" s="7"/>
+    </row>
+    <row r="635" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C635" s="11"/>
+      <c r="D635" s="11"/>
+      <c r="E635" s="11"/>
+      <c r="F635" s="7"/>
+      <c r="G635" s="8"/>
+      <c r="H635" s="7"/>
+      <c r="I635" s="7"/>
+    </row>
+    <row r="636" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C636" s="11"/>
+      <c r="D636" s="11"/>
+      <c r="E636" s="11"/>
+      <c r="F636" s="7"/>
+      <c r="G636" s="8"/>
+      <c r="H636" s="7"/>
+      <c r="I636" s="7"/>
+    </row>
+    <row r="637" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C637" s="11"/>
+      <c r="D637" s="11"/>
+      <c r="E637" s="11"/>
+      <c r="F637" s="7"/>
+      <c r="G637" s="8"/>
+      <c r="H637" s="7"/>
+      <c r="I637" s="7"/>
+    </row>
+    <row r="638" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C638" s="11"/>
+      <c r="D638" s="11"/>
+      <c r="E638" s="11"/>
+      <c r="F638" s="7"/>
+      <c r="G638" s="8"/>
+      <c r="H638" s="7"/>
+      <c r="I638" s="7"/>
+    </row>
+    <row r="639" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C639" s="11"/>
+      <c r="D639" s="11"/>
+      <c r="E639" s="11"/>
+      <c r="F639" s="7"/>
+      <c r="G639" s="8"/>
+      <c r="H639" s="7"/>
+      <c r="I639" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I17" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{107D5F45-1308-45A8-A437-7AA2DB2D5694}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC0E2CC-0BFE-4CCD-ABE1-C3895D7EA212}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1032,10 +1032,10 @@
         <v>12</v>
       </c>
       <c r="D4" s="9">
-        <v>1885</v>
+        <v>2035</v>
       </c>
       <c r="E4" s="9">
-        <v>2990</v>
+        <v>3140</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>113</v>
@@ -1063,10 +1063,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="9">
-        <v>1885</v>
+        <v>2035</v>
       </c>
       <c r="E5" s="9">
-        <v>2990</v>
+        <v>3140</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>113</v>
@@ -1094,10 +1094,10 @@
         <v>12</v>
       </c>
       <c r="D6" s="9">
-        <v>1675</v>
+        <v>1825</v>
       </c>
       <c r="E6" s="9">
-        <v>3160</v>
+        <v>3310</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>113</v>
@@ -1125,10 +1125,10 @@
         <v>12</v>
       </c>
       <c r="D7" s="9">
-        <v>1675</v>
+        <v>1825</v>
       </c>
       <c r="E7" s="9">
-        <v>3160</v>
+        <v>3310</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>113</v>
@@ -1156,10 +1156,10 @@
         <v>12</v>
       </c>
       <c r="D8" s="9">
-        <v>2135</v>
+        <v>2285</v>
       </c>
       <c r="E8" s="9">
-        <v>3440</v>
+        <v>3590</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>113</v>
@@ -1187,10 +1187,10 @@
         <v>12</v>
       </c>
       <c r="D9" s="9">
-        <v>2135</v>
+        <v>2285</v>
       </c>
       <c r="E9" s="9">
-        <v>3440</v>
+        <v>3590</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>113</v>
@@ -1218,10 +1218,10 @@
         <v>12</v>
       </c>
       <c r="D10" s="9">
-        <v>2135</v>
+        <v>2285</v>
       </c>
       <c r="E10" s="9">
-        <v>3440</v>
+        <v>3590</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>113</v>
@@ -1249,10 +1249,10 @@
         <v>12</v>
       </c>
       <c r="D11" s="9">
-        <v>2635</v>
+        <v>2785</v>
       </c>
       <c r="E11" s="9">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>113</v>
@@ -1280,10 +1280,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="9">
-        <v>2135</v>
+        <v>2285</v>
       </c>
       <c r="E12" s="9">
-        <v>3440</v>
+        <v>3590</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>113</v>
@@ -1311,10 +1311,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="9">
-        <v>2415</v>
+        <v>2565</v>
       </c>
       <c r="E13" s="9">
-        <v>3760</v>
+        <v>3910</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>113</v>
@@ -1342,10 +1342,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="9">
-        <v>2635</v>
+        <v>2785</v>
       </c>
       <c r="E14" s="9">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>113</v>
@@ -1373,10 +1373,10 @@
         <v>12</v>
       </c>
       <c r="D15" s="9">
-        <v>2915</v>
+        <v>3065</v>
       </c>
       <c r="E15" s="9">
-        <v>4430</v>
+        <v>4580</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>113</v>
@@ -1404,10 +1404,10 @@
         <v>12</v>
       </c>
       <c r="D16" s="9">
-        <v>2635</v>
+        <v>2785</v>
       </c>
       <c r="E16" s="9">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>113</v>
@@ -1435,10 +1435,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="9">
-        <v>2635</v>
+        <v>2785</v>
       </c>
       <c r="E17" s="9">
-        <v>4110</v>
+        <v>4260</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>113</v>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEC0E2CC-0BFE-4CCD-ABE1-C3895D7EA212}"/>
+  <xr:revisionPtr revIDLastSave="134" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{921C11D0-B0D8-47FA-8EC6-28D397FB1ADF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2487" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="158">
   <si>
     <t>POD</t>
   </si>
@@ -388,6 +388,135 @@
   </si>
   <si>
     <t>15 al 21 de mayo</t>
+  </si>
+  <si>
+    <t>JAKARTA</t>
+  </si>
+  <si>
+    <t>PANJANG</t>
+  </si>
+  <si>
+    <t>SEMARANG</t>
+  </si>
+  <si>
+    <t>SURABAYA</t>
+  </si>
+  <si>
+    <t>CHENNAI</t>
+  </si>
+  <si>
+    <t>MUNDRA</t>
+  </si>
+  <si>
+    <t>NHAVA SHEVA</t>
+  </si>
+  <si>
+    <t>TUTICORIN (NEW TUTICORIN)</t>
+  </si>
+  <si>
+    <t>KOLKATA</t>
+  </si>
+  <si>
+    <t>GURGAON (GARHI HARSARU)</t>
+  </si>
+  <si>
+    <t>DELHI-TUGHLAKABAD</t>
+  </si>
+  <si>
+    <t>DELHI(ICD SONIPAT)</t>
+  </si>
+  <si>
+    <t>JAIPUR</t>
+  </si>
+  <si>
+    <t>KANPUR</t>
+  </si>
+  <si>
+    <t>BANGALORE</t>
+  </si>
+  <si>
+    <t>LUDHIANA</t>
+  </si>
+  <si>
+    <t>KWANGYANG</t>
+  </si>
+  <si>
+    <t>PENANG</t>
+  </si>
+  <si>
+    <t>PASIR GUDANG,JOHOR</t>
+  </si>
+  <si>
+    <t>PORT KLANG NORTH PORT</t>
+  </si>
+  <si>
+    <t>KOTA KINABALU</t>
+  </si>
+  <si>
+    <t>SINGAPORE</t>
+  </si>
+  <si>
+    <t>BANGKOK</t>
+  </si>
+  <si>
+    <t>LAEM CHABANG</t>
+  </si>
+  <si>
+    <t>LAT KRABANG</t>
+  </si>
+  <si>
+    <t>CAT LAI PORT HOCHIMINH</t>
+  </si>
+  <si>
+    <t>CAI MEP TCIT</t>
+  </si>
+  <si>
+    <t>HAIPHONG</t>
+  </si>
+  <si>
+    <t>MANILA NORTH PORT</t>
+  </si>
+  <si>
+    <t>DAVAO</t>
+  </si>
+  <si>
+    <t>COLOMBO</t>
+  </si>
+  <si>
+    <t>KARACHI</t>
+  </si>
+  <si>
+    <t>BELAWAN</t>
+  </si>
+  <si>
+    <t>JEBEL ALI</t>
+  </si>
+  <si>
+    <t>15 al 31 de mayo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGOYA </t>
+  </si>
+  <si>
+    <t>OSAKA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOKYO </t>
+  </si>
+  <si>
+    <t>KOBE</t>
+  </si>
+  <si>
+    <t>YOKOHAMA</t>
+  </si>
+  <si>
+    <t>SHIMIZU</t>
+  </si>
+  <si>
+    <t>HAKATA</t>
+  </si>
+  <si>
+    <t>DA NANG</t>
   </si>
 </sst>
 </file>
@@ -921,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:K639"/>
+  <dimension ref="A1:K637"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -13897,411 +14026,1221 @@
       </c>
     </row>
     <row r="474" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A474" t="s">
+        <v>115</v>
+      </c>
+      <c r="B474" t="s">
+        <v>15</v>
+      </c>
       <c r="C474" s="11"/>
-      <c r="D474" s="11"/>
-      <c r="E474" s="11"/>
-      <c r="F474" s="7"/>
-      <c r="G474" s="8"/>
-      <c r="H474" s="7"/>
-      <c r="I474" s="7"/>
+      <c r="D474" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E474" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F474" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G474" s="8">
+        <v>18</v>
+      </c>
+      <c r="H474" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I474" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="475" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A475" t="s">
+        <v>116</v>
+      </c>
+      <c r="B475" t="s">
+        <v>15</v>
+      </c>
       <c r="C475" s="11"/>
-      <c r="D475" s="11"/>
-      <c r="E475" s="11"/>
-      <c r="F475" s="7"/>
-      <c r="G475" s="8"/>
-      <c r="H475" s="7"/>
-      <c r="I475" s="7"/>
+      <c r="D475" s="11">
+        <v>3690</v>
+      </c>
+      <c r="E475" s="11">
+        <v>3890</v>
+      </c>
+      <c r="F475" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G475" s="8">
+        <v>18</v>
+      </c>
+      <c r="H475" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I475" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="476" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A476" t="s">
+        <v>117</v>
+      </c>
+      <c r="B476" t="s">
+        <v>15</v>
+      </c>
       <c r="C476" s="11"/>
-      <c r="D476" s="11"/>
-      <c r="E476" s="11"/>
-      <c r="F476" s="7"/>
-      <c r="G476" s="8"/>
-      <c r="H476" s="7"/>
-      <c r="I476" s="7"/>
+      <c r="D476" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E476" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F476" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G476" s="8">
+        <v>18</v>
+      </c>
+      <c r="H476" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I476" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="477" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A477" t="s">
+        <v>118</v>
+      </c>
+      <c r="B477" t="s">
+        <v>15</v>
+      </c>
       <c r="C477" s="11"/>
-      <c r="D477" s="11"/>
-      <c r="E477" s="11"/>
-      <c r="F477" s="7"/>
-      <c r="G477" s="8"/>
-      <c r="H477" s="7"/>
-      <c r="I477" s="7"/>
+      <c r="D477" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E477" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F477" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G477" s="8">
+        <v>18</v>
+      </c>
+      <c r="H477" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I477" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="478" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A478" t="s">
+        <v>119</v>
+      </c>
+      <c r="B478" t="s">
+        <v>15</v>
+      </c>
       <c r="C478" s="11"/>
-      <c r="D478" s="11"/>
-      <c r="E478" s="11"/>
-      <c r="F478" s="7"/>
-      <c r="G478" s="8"/>
-      <c r="H478" s="7"/>
-      <c r="I478" s="7"/>
+      <c r="D478" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E478" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F478" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G478" s="8">
+        <v>18</v>
+      </c>
+      <c r="H478" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I478" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A479" t="s">
+        <v>120</v>
+      </c>
+      <c r="B479" t="s">
+        <v>15</v>
+      </c>
       <c r="C479" s="11"/>
-      <c r="D479" s="11"/>
-      <c r="E479" s="11"/>
-      <c r="F479" s="7"/>
-      <c r="G479" s="8"/>
-      <c r="H479" s="7"/>
-      <c r="I479" s="7"/>
+      <c r="D479" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E479" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F479" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G479" s="8">
+        <v>18</v>
+      </c>
+      <c r="H479" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I479" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="480" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A480" t="s">
+        <v>121</v>
+      </c>
+      <c r="B480" t="s">
+        <v>15</v>
+      </c>
       <c r="C480" s="11"/>
-      <c r="D480" s="11"/>
-      <c r="E480" s="11"/>
-      <c r="F480" s="7"/>
-      <c r="G480" s="8"/>
-      <c r="H480" s="7"/>
-      <c r="I480" s="7"/>
-    </row>
-    <row r="481" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D480" s="11">
+        <v>3390</v>
+      </c>
+      <c r="E480" s="11">
+        <v>3690</v>
+      </c>
+      <c r="F480" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G480" s="8">
+        <v>18</v>
+      </c>
+      <c r="H480" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I480" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="481" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A481" t="s">
+        <v>122</v>
+      </c>
+      <c r="B481" t="s">
+        <v>15</v>
+      </c>
       <c r="C481" s="11"/>
-      <c r="D481" s="11"/>
-      <c r="E481" s="11"/>
-      <c r="F481" s="7"/>
-      <c r="G481" s="8"/>
-      <c r="H481" s="7"/>
-      <c r="I481" s="7"/>
-    </row>
-    <row r="482" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D481" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E481" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F481" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G481" s="8">
+        <v>18</v>
+      </c>
+      <c r="H481" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I481" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="482" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A482" t="s">
+        <v>123</v>
+      </c>
+      <c r="B482" t="s">
+        <v>15</v>
+      </c>
       <c r="C482" s="11"/>
-      <c r="D482" s="11"/>
-      <c r="E482" s="11"/>
-      <c r="F482" s="7"/>
-      <c r="G482" s="8"/>
-      <c r="H482" s="7"/>
-      <c r="I482" s="7"/>
-    </row>
-    <row r="483" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D482" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E482" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F482" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G482" s="8">
+        <v>18</v>
+      </c>
+      <c r="H482" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I482" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="483" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A483" t="s">
+        <v>124</v>
+      </c>
+      <c r="B483" t="s">
+        <v>15</v>
+      </c>
       <c r="C483" s="11"/>
-      <c r="D483" s="11"/>
-      <c r="E483" s="11"/>
-      <c r="F483" s="7"/>
-      <c r="G483" s="8"/>
-      <c r="H483" s="7"/>
-      <c r="I483" s="7"/>
-    </row>
-    <row r="484" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D483" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E483" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F483" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G483" s="8">
+        <v>18</v>
+      </c>
+      <c r="H483" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I483" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="484" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A484" t="s">
+        <v>125</v>
+      </c>
+      <c r="B484" t="s">
+        <v>15</v>
+      </c>
       <c r="C484" s="11"/>
-      <c r="D484" s="11"/>
-      <c r="E484" s="11"/>
-      <c r="F484" s="7"/>
-      <c r="G484" s="8"/>
-      <c r="H484" s="7"/>
-      <c r="I484" s="7"/>
-    </row>
-    <row r="485" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D484" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E484" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F484" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G484" s="8">
+        <v>18</v>
+      </c>
+      <c r="H484" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I484" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="485" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A485" t="s">
+        <v>126</v>
+      </c>
+      <c r="B485" t="s">
+        <v>15</v>
+      </c>
       <c r="C485" s="11"/>
-      <c r="D485" s="11"/>
-      <c r="E485" s="11"/>
-      <c r="F485" s="7"/>
-      <c r="G485" s="8"/>
-      <c r="H485" s="7"/>
-      <c r="I485" s="7"/>
-    </row>
-    <row r="486" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D485" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E485" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F485" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G485" s="8">
+        <v>18</v>
+      </c>
+      <c r="H485" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I485" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="486" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A486" t="s">
+        <v>127</v>
+      </c>
+      <c r="B486" t="s">
+        <v>15</v>
+      </c>
       <c r="C486" s="11"/>
-      <c r="D486" s="11"/>
-      <c r="E486" s="11"/>
-      <c r="F486" s="7"/>
-      <c r="G486" s="8"/>
-      <c r="H486" s="7"/>
-      <c r="I486" s="7"/>
-    </row>
-    <row r="487" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D486" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E486" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F486" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G486" s="8">
+        <v>18</v>
+      </c>
+      <c r="H486" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I486" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="487" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A487" t="s">
+        <v>128</v>
+      </c>
+      <c r="B487" t="s">
+        <v>15</v>
+      </c>
       <c r="C487" s="11"/>
-      <c r="D487" s="11"/>
-      <c r="E487" s="11"/>
-      <c r="F487" s="7"/>
-      <c r="G487" s="8"/>
-      <c r="H487" s="7"/>
-      <c r="I487" s="7"/>
-    </row>
-    <row r="488" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D487" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E487" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F487" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G487" s="8">
+        <v>18</v>
+      </c>
+      <c r="H487" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I487" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="488" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A488" t="s">
+        <v>129</v>
+      </c>
+      <c r="B488" t="s">
+        <v>15</v>
+      </c>
       <c r="C488" s="11"/>
-      <c r="D488" s="11"/>
-      <c r="E488" s="11"/>
-      <c r="F488" s="7"/>
-      <c r="G488" s="8"/>
-      <c r="H488" s="7"/>
-      <c r="I488" s="7"/>
-    </row>
-    <row r="489" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D488" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E488" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F488" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G488" s="8">
+        <v>18</v>
+      </c>
+      <c r="H488" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I488" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="489" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A489" t="s">
+        <v>130</v>
+      </c>
+      <c r="B489" t="s">
+        <v>15</v>
+      </c>
       <c r="C489" s="11"/>
-      <c r="D489" s="11"/>
-      <c r="E489" s="11"/>
-      <c r="F489" s="7"/>
-      <c r="G489" s="8"/>
-      <c r="H489" s="7"/>
-      <c r="I489" s="7"/>
-    </row>
-    <row r="490" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D489" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E489" s="11">
+        <v>3390</v>
+      </c>
+      <c r="F489" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G489" s="8">
+        <v>18</v>
+      </c>
+      <c r="H489" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I489" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="490" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A490" t="s">
+        <v>150</v>
+      </c>
+      <c r="B490" t="s">
+        <v>15</v>
+      </c>
       <c r="C490" s="11"/>
-      <c r="D490" s="11"/>
-      <c r="E490" s="11"/>
-      <c r="F490" s="7"/>
-      <c r="G490" s="8"/>
-      <c r="H490" s="7"/>
-      <c r="I490" s="7"/>
-    </row>
-    <row r="491" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D490" s="11">
+        <v>3340</v>
+      </c>
+      <c r="E490" s="11">
+        <v>3690</v>
+      </c>
+      <c r="F490" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G490" s="8">
+        <v>18</v>
+      </c>
+      <c r="H490" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I490" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="491" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A491" t="s">
+        <v>151</v>
+      </c>
+      <c r="B491" t="s">
+        <v>15</v>
+      </c>
       <c r="C491" s="11"/>
-      <c r="D491" s="11"/>
-      <c r="E491" s="11"/>
-      <c r="F491" s="7"/>
-      <c r="G491" s="8"/>
-      <c r="H491" s="7"/>
-      <c r="I491" s="7"/>
-    </row>
-    <row r="492" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D491" s="11">
+        <v>3340</v>
+      </c>
+      <c r="E491" s="11">
+        <v>3690</v>
+      </c>
+      <c r="F491" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G491" s="8">
+        <v>18</v>
+      </c>
+      <c r="H491" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I491" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="492" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A492" t="s">
+        <v>152</v>
+      </c>
+      <c r="B492" t="s">
+        <v>15</v>
+      </c>
       <c r="C492" s="11"/>
-      <c r="D492" s="11"/>
-      <c r="E492" s="11"/>
-      <c r="F492" s="7"/>
-      <c r="G492" s="8"/>
-      <c r="H492" s="7"/>
-      <c r="I492" s="7"/>
-    </row>
-    <row r="493" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D492" s="11">
+        <v>3340</v>
+      </c>
+      <c r="E492" s="11">
+        <v>3690</v>
+      </c>
+      <c r="F492" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G492" s="8">
+        <v>18</v>
+      </c>
+      <c r="H492" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I492" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="493" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A493" t="s">
+        <v>153</v>
+      </c>
+      <c r="B493" t="s">
+        <v>15</v>
+      </c>
       <c r="C493" s="11"/>
-      <c r="D493" s="11"/>
-      <c r="E493" s="11"/>
-      <c r="F493" s="7"/>
-      <c r="G493" s="8"/>
-      <c r="H493" s="7"/>
-      <c r="I493" s="7"/>
-    </row>
-    <row r="494" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D493" s="11">
+        <v>3340</v>
+      </c>
+      <c r="E493" s="11">
+        <v>3690</v>
+      </c>
+      <c r="F493" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G493" s="8">
+        <v>18</v>
+      </c>
+      <c r="H493" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I493" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="494" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A494" t="s">
+        <v>154</v>
+      </c>
+      <c r="B494" t="s">
+        <v>15</v>
+      </c>
       <c r="C494" s="11"/>
-      <c r="D494" s="11"/>
-      <c r="E494" s="11"/>
-      <c r="F494" s="7"/>
-      <c r="G494" s="8"/>
-      <c r="H494" s="7"/>
-      <c r="I494" s="7"/>
-    </row>
-    <row r="495" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D494" s="11">
+        <v>3340</v>
+      </c>
+      <c r="E494" s="11">
+        <v>3690</v>
+      </c>
+      <c r="F494" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G494" s="8">
+        <v>18</v>
+      </c>
+      <c r="H494" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I494" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="495" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A495" t="s">
+        <v>155</v>
+      </c>
+      <c r="B495" t="s">
+        <v>15</v>
+      </c>
       <c r="C495" s="11"/>
-      <c r="D495" s="11"/>
-      <c r="E495" s="11"/>
-      <c r="F495" s="7"/>
-      <c r="G495" s="8"/>
-      <c r="H495" s="7"/>
-      <c r="I495" s="7"/>
-    </row>
-    <row r="496" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D495" s="11">
+        <v>3540</v>
+      </c>
+      <c r="E495" s="11">
+        <v>3990</v>
+      </c>
+      <c r="F495" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G495" s="8">
+        <v>18</v>
+      </c>
+      <c r="H495" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I495" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="496" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A496" t="s">
+        <v>156</v>
+      </c>
+      <c r="B496" t="s">
+        <v>15</v>
+      </c>
       <c r="C496" s="11"/>
-      <c r="D496" s="11"/>
-      <c r="E496" s="11"/>
-      <c r="F496" s="7"/>
-      <c r="G496" s="8"/>
-      <c r="H496" s="7"/>
-      <c r="I496" s="7"/>
-    </row>
-    <row r="497" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D496" s="11">
+        <v>3540</v>
+      </c>
+      <c r="E496" s="11">
+        <v>3990</v>
+      </c>
+      <c r="F496" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G496" s="8">
+        <v>18</v>
+      </c>
+      <c r="H496" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I496" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="497" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A497" t="s">
+        <v>76</v>
+      </c>
+      <c r="B497" t="s">
+        <v>15</v>
+      </c>
       <c r="C497" s="11"/>
-      <c r="D497" s="11"/>
-      <c r="E497" s="11"/>
-      <c r="F497" s="7"/>
-      <c r="G497" s="8"/>
-      <c r="H497" s="7"/>
-      <c r="I497" s="7"/>
-    </row>
-    <row r="498" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D497" s="11">
+        <v>3090</v>
+      </c>
+      <c r="E497" s="11">
+        <v>3090</v>
+      </c>
+      <c r="F497" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G497" s="8">
+        <v>18</v>
+      </c>
+      <c r="H497" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I497" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="498" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A498" t="s">
+        <v>131</v>
+      </c>
+      <c r="B498" t="s">
+        <v>15</v>
+      </c>
       <c r="C498" s="11"/>
-      <c r="D498" s="11"/>
-      <c r="E498" s="11"/>
-      <c r="F498" s="7"/>
-      <c r="G498" s="8"/>
-      <c r="H498" s="7"/>
-      <c r="I498" s="7"/>
-    </row>
-    <row r="499" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D498" s="11">
+        <v>3190</v>
+      </c>
+      <c r="E498" s="11">
+        <v>3190</v>
+      </c>
+      <c r="F498" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G498" s="8">
+        <v>18</v>
+      </c>
+      <c r="H498" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I498" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="499" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A499" t="s">
+        <v>132</v>
+      </c>
+      <c r="B499" t="s">
+        <v>15</v>
+      </c>
       <c r="C499" s="11"/>
-      <c r="D499" s="11"/>
-      <c r="E499" s="11"/>
-      <c r="F499" s="7"/>
-      <c r="G499" s="8"/>
-      <c r="H499" s="7"/>
-      <c r="I499" s="7"/>
-    </row>
-    <row r="500" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D499" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E499" s="11">
+        <v>3590</v>
+      </c>
+      <c r="F499" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G499" s="8">
+        <v>18</v>
+      </c>
+      <c r="H499" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I499" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="500" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A500" t="s">
+        <v>133</v>
+      </c>
+      <c r="B500" t="s">
+        <v>15</v>
+      </c>
       <c r="C500" s="11"/>
-      <c r="D500" s="11"/>
-      <c r="E500" s="11"/>
-      <c r="F500" s="7"/>
-      <c r="G500" s="8"/>
-      <c r="H500" s="7"/>
-      <c r="I500" s="7"/>
-    </row>
-    <row r="501" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D500" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E500" s="11">
+        <v>3590</v>
+      </c>
+      <c r="F500" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G500" s="8">
+        <v>18</v>
+      </c>
+      <c r="H500" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I500" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="501" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A501" t="s">
+        <v>134</v>
+      </c>
+      <c r="B501" t="s">
+        <v>15</v>
+      </c>
       <c r="C501" s="11"/>
-      <c r="D501" s="11"/>
-      <c r="E501" s="11"/>
-      <c r="F501" s="7"/>
-      <c r="G501" s="8"/>
-      <c r="H501" s="7"/>
-      <c r="I501" s="7"/>
-    </row>
-    <row r="502" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D501" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E501" s="11">
+        <v>3590</v>
+      </c>
+      <c r="F501" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G501" s="8">
+        <v>18</v>
+      </c>
+      <c r="H501" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I501" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="502" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A502" t="s">
+        <v>135</v>
+      </c>
+      <c r="B502" t="s">
+        <v>15</v>
+      </c>
       <c r="C502" s="11"/>
-      <c r="D502" s="11"/>
-      <c r="E502" s="11"/>
-      <c r="F502" s="7"/>
-      <c r="G502" s="8"/>
-      <c r="H502" s="7"/>
-      <c r="I502" s="7"/>
-    </row>
-    <row r="503" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D502" s="11">
+        <v>3740</v>
+      </c>
+      <c r="E502" s="11">
+        <v>4040</v>
+      </c>
+      <c r="F502" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G502" s="8">
+        <v>18</v>
+      </c>
+      <c r="H502" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I502" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="503" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A503" t="s">
+        <v>136</v>
+      </c>
+      <c r="B503" t="s">
+        <v>15</v>
+      </c>
       <c r="C503" s="11"/>
-      <c r="D503" s="11"/>
-      <c r="E503" s="11"/>
-      <c r="F503" s="7"/>
-      <c r="G503" s="8"/>
-      <c r="H503" s="7"/>
-      <c r="I503" s="7"/>
-    </row>
-    <row r="504" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D503" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E503" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F503" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G503" s="8">
+        <v>18</v>
+      </c>
+      <c r="H503" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I503" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="504" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A504" t="s">
+        <v>137</v>
+      </c>
+      <c r="B504" t="s">
+        <v>15</v>
+      </c>
       <c r="C504" s="11"/>
-      <c r="D504" s="11"/>
-      <c r="E504" s="11"/>
-      <c r="F504" s="7"/>
-      <c r="G504" s="8"/>
-      <c r="H504" s="7"/>
-      <c r="I504" s="7"/>
-    </row>
-    <row r="505" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D504" s="11">
+        <v>3290</v>
+      </c>
+      <c r="E504" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F504" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G504" s="8">
+        <v>18</v>
+      </c>
+      <c r="H504" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I504" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="505" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A505" t="s">
+        <v>138</v>
+      </c>
+      <c r="B505" t="s">
+        <v>15</v>
+      </c>
       <c r="C505" s="11"/>
-      <c r="D505" s="11"/>
-      <c r="E505" s="11"/>
-      <c r="F505" s="7"/>
-      <c r="G505" s="8"/>
-      <c r="H505" s="7"/>
-      <c r="I505" s="7"/>
-    </row>
-    <row r="506" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D505" s="11">
+        <v>3290</v>
+      </c>
+      <c r="E505" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F505" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G505" s="8">
+        <v>18</v>
+      </c>
+      <c r="H505" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I505" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="506" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A506" t="s">
+        <v>139</v>
+      </c>
+      <c r="B506" t="s">
+        <v>15</v>
+      </c>
       <c r="C506" s="11"/>
-      <c r="D506" s="11"/>
-      <c r="E506" s="11"/>
-      <c r="F506" s="7"/>
-      <c r="G506" s="8"/>
-      <c r="H506" s="7"/>
-      <c r="I506" s="7"/>
-    </row>
-    <row r="507" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D506" s="11">
+        <v>3410</v>
+      </c>
+      <c r="E506" s="11">
+        <v>3610</v>
+      </c>
+      <c r="F506" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G506" s="8">
+        <v>18</v>
+      </c>
+      <c r="H506" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I506" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="507" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A507" t="s">
+        <v>140</v>
+      </c>
+      <c r="B507" t="s">
+        <v>15</v>
+      </c>
       <c r="C507" s="11"/>
-      <c r="D507" s="11"/>
-      <c r="E507" s="11"/>
-      <c r="F507" s="7"/>
-      <c r="G507" s="8"/>
-      <c r="H507" s="7"/>
-      <c r="I507" s="7"/>
-    </row>
-    <row r="508" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D507" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E507" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F507" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G507" s="8">
+        <v>18</v>
+      </c>
+      <c r="H507" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I507" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="508" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A508" t="s">
+        <v>141</v>
+      </c>
+      <c r="B508" t="s">
+        <v>15</v>
+      </c>
       <c r="C508" s="11"/>
-      <c r="D508" s="11"/>
-      <c r="E508" s="11"/>
-      <c r="F508" s="7"/>
-      <c r="G508" s="8"/>
-      <c r="H508" s="7"/>
-      <c r="I508" s="7"/>
-    </row>
-    <row r="509" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D508" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E508" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F508" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G508" s="8">
+        <v>18</v>
+      </c>
+      <c r="H508" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I508" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="509" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A509" t="s">
+        <v>157</v>
+      </c>
+      <c r="B509" t="s">
+        <v>15</v>
+      </c>
       <c r="C509" s="11"/>
-      <c r="D509" s="11"/>
-      <c r="E509" s="11"/>
-      <c r="F509" s="7"/>
-      <c r="G509" s="8"/>
-      <c r="H509" s="7"/>
-      <c r="I509" s="7"/>
-    </row>
-    <row r="510" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D509" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E509" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F509" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G509" s="8">
+        <v>18</v>
+      </c>
+      <c r="H509" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I509" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="510" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A510" t="s">
+        <v>142</v>
+      </c>
+      <c r="B510" t="s">
+        <v>15</v>
+      </c>
       <c r="C510" s="11"/>
-      <c r="D510" s="11"/>
-      <c r="E510" s="11"/>
-      <c r="F510" s="7"/>
-      <c r="G510" s="8"/>
-      <c r="H510" s="7"/>
-      <c r="I510" s="7"/>
-    </row>
-    <row r="511" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D510" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E510" s="11">
+        <v>3540</v>
+      </c>
+      <c r="F510" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G510" s="8">
+        <v>18</v>
+      </c>
+      <c r="H510" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I510" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="511" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A511" t="s">
+        <v>143</v>
+      </c>
+      <c r="B511" t="s">
+        <v>15</v>
+      </c>
       <c r="C511" s="11"/>
-      <c r="D511" s="11"/>
-      <c r="E511" s="11"/>
-      <c r="F511" s="7"/>
-      <c r="G511" s="8"/>
-      <c r="H511" s="7"/>
-      <c r="I511" s="7"/>
-    </row>
-    <row r="512" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D511" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E511" s="11">
+        <v>3590</v>
+      </c>
+      <c r="F511" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G511" s="8">
+        <v>18</v>
+      </c>
+      <c r="H511" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I511" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="512" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A512" t="s">
+        <v>144</v>
+      </c>
+      <c r="B512" t="s">
+        <v>15</v>
+      </c>
       <c r="C512" s="11"/>
-      <c r="D512" s="11"/>
-      <c r="E512" s="11"/>
-      <c r="F512" s="7"/>
-      <c r="G512" s="8"/>
-      <c r="H512" s="7"/>
-      <c r="I512" s="7"/>
-    </row>
-    <row r="513" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D512" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E512" s="11">
+        <v>3590</v>
+      </c>
+      <c r="F512" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G512" s="8">
+        <v>18</v>
+      </c>
+      <c r="H512" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I512" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="513" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A513" t="s">
+        <v>127</v>
+      </c>
+      <c r="B513" t="s">
+        <v>15</v>
+      </c>
       <c r="C513" s="11"/>
-      <c r="D513" s="11"/>
-      <c r="E513" s="11"/>
-      <c r="F513" s="7"/>
-      <c r="G513" s="8"/>
-      <c r="H513" s="7"/>
-      <c r="I513" s="7"/>
-    </row>
-    <row r="514" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D513" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E513" s="11">
+        <v>3190</v>
+      </c>
+      <c r="F513" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G513" s="8">
+        <v>18</v>
+      </c>
+      <c r="H513" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I513" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="514" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A514" t="s">
+        <v>145</v>
+      </c>
+      <c r="B514" t="s">
+        <v>15</v>
+      </c>
       <c r="C514" s="11"/>
-      <c r="D514" s="11"/>
-      <c r="E514" s="11"/>
-      <c r="F514" s="7"/>
-      <c r="G514" s="8"/>
-      <c r="H514" s="7"/>
-      <c r="I514" s="7"/>
-    </row>
-    <row r="515" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D514" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E514" s="11">
+        <v>3190</v>
+      </c>
+      <c r="F514" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G514" s="8">
+        <v>18</v>
+      </c>
+      <c r="H514" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I514" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="515" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A515" t="s">
+        <v>146</v>
+      </c>
+      <c r="B515" t="s">
+        <v>15</v>
+      </c>
       <c r="C515" s="11"/>
-      <c r="D515" s="11"/>
-      <c r="E515" s="11"/>
-      <c r="F515" s="7"/>
-      <c r="G515" s="8"/>
-      <c r="H515" s="7"/>
-      <c r="I515" s="7"/>
-    </row>
-    <row r="516" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D515" s="11">
+        <v>3890</v>
+      </c>
+      <c r="E515" s="11">
+        <v>4090</v>
+      </c>
+      <c r="F515" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G515" s="8">
+        <v>18</v>
+      </c>
+      <c r="H515" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I515" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="516" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A516" t="s">
+        <v>147</v>
+      </c>
+      <c r="B516" t="s">
+        <v>15</v>
+      </c>
       <c r="C516" s="11"/>
-      <c r="D516" s="11"/>
-      <c r="E516" s="11"/>
-      <c r="F516" s="7"/>
-      <c r="G516" s="8"/>
-      <c r="H516" s="7"/>
-      <c r="I516" s="7"/>
-    </row>
-    <row r="517" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D516" s="11">
+        <v>3490</v>
+      </c>
+      <c r="E516" s="11">
+        <v>3490</v>
+      </c>
+      <c r="F516" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G516" s="8">
+        <v>18</v>
+      </c>
+      <c r="H516" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I516" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="517" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A517" t="s">
+        <v>130</v>
+      </c>
+      <c r="B517" t="s">
+        <v>15</v>
+      </c>
       <c r="C517" s="11"/>
-      <c r="D517" s="11"/>
-      <c r="E517" s="11"/>
-      <c r="F517" s="7"/>
-      <c r="G517" s="8"/>
-      <c r="H517" s="7"/>
-      <c r="I517" s="7"/>
-    </row>
-    <row r="518" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D517" s="11">
+        <v>2990</v>
+      </c>
+      <c r="E517" s="11">
+        <v>3190</v>
+      </c>
+      <c r="F517" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G517" s="8">
+        <v>18</v>
+      </c>
+      <c r="H517" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I517" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="518" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A518" t="s">
+        <v>148</v>
+      </c>
+      <c r="B518" t="s">
+        <v>15</v>
+      </c>
       <c r="C518" s="11"/>
-      <c r="D518" s="11"/>
-      <c r="E518" s="11"/>
-      <c r="F518" s="7"/>
-      <c r="G518" s="8"/>
-      <c r="H518" s="7"/>
-      <c r="I518" s="7"/>
-    </row>
-    <row r="519" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="D518" s="11">
+        <v>3590</v>
+      </c>
+      <c r="E518" s="11">
+        <v>3790</v>
+      </c>
+      <c r="F518" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="G518" s="8">
+        <v>18</v>
+      </c>
+      <c r="H518" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I518" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C519" s="11"/>
       <c r="D519" s="11"/>
       <c r="E519" s="11"/>
@@ -14310,7 +15249,7 @@
       <c r="H519" s="7"/>
       <c r="I519" s="7"/>
     </row>
-    <row r="520" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C520" s="11"/>
       <c r="D520" s="11"/>
       <c r="E520" s="11"/>
@@ -14319,7 +15258,7 @@
       <c r="H520" s="7"/>
       <c r="I520" s="7"/>
     </row>
-    <row r="521" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C521" s="11"/>
       <c r="D521" s="11"/>
       <c r="E521" s="11"/>
@@ -14328,7 +15267,7 @@
       <c r="H521" s="7"/>
       <c r="I521" s="7"/>
     </row>
-    <row r="522" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C522" s="11"/>
       <c r="D522" s="11"/>
       <c r="E522" s="11"/>
@@ -14337,7 +15276,7 @@
       <c r="H522" s="7"/>
       <c r="I522" s="7"/>
     </row>
-    <row r="523" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C523" s="11"/>
       <c r="D523" s="11"/>
       <c r="E523" s="11"/>
@@ -14346,7 +15285,7 @@
       <c r="H523" s="7"/>
       <c r="I523" s="7"/>
     </row>
-    <row r="524" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C524" s="11"/>
       <c r="D524" s="11"/>
       <c r="E524" s="11"/>
@@ -14355,7 +15294,7 @@
       <c r="H524" s="7"/>
       <c r="I524" s="7"/>
     </row>
-    <row r="525" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C525" s="11"/>
       <c r="D525" s="11"/>
       <c r="E525" s="11"/>
@@ -14364,7 +15303,7 @@
       <c r="H525" s="7"/>
       <c r="I525" s="7"/>
     </row>
-    <row r="526" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C526" s="11"/>
       <c r="D526" s="11"/>
       <c r="E526" s="11"/>
@@ -14373,7 +15312,7 @@
       <c r="H526" s="7"/>
       <c r="I526" s="7"/>
     </row>
-    <row r="527" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C527" s="11"/>
       <c r="D527" s="11"/>
       <c r="E527" s="11"/>
@@ -14382,7 +15321,7 @@
       <c r="H527" s="7"/>
       <c r="I527" s="7"/>
     </row>
-    <row r="528" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C528" s="11"/>
       <c r="D528" s="11"/>
       <c r="E528" s="11"/>
@@ -15371,24 +16310,6 @@
       <c r="G637" s="8"/>
       <c r="H637" s="7"/>
       <c r="I637" s="7"/>
-    </row>
-    <row r="638" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C638" s="11"/>
-      <c r="D638" s="11"/>
-      <c r="E638" s="11"/>
-      <c r="F638" s="7"/>
-      <c r="G638" s="8"/>
-      <c r="H638" s="7"/>
-      <c r="I638" s="7"/>
-    </row>
-    <row r="639" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C639" s="11"/>
-      <c r="D639" s="11"/>
-      <c r="E639" s="11"/>
-      <c r="F639" s="7"/>
-      <c r="G639" s="8"/>
-      <c r="H639" s="7"/>
-      <c r="I639" s="7"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I17" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B23BF1CD-9FBB-4E80-847D-B2E425CB0556}"/>
+  <xr:revisionPtr revIDLastSave="182" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82CD0857-AF21-4B8C-93EF-F371BFAF262B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,29 +21,20 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$428</definedName>
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2303" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="170">
   <si>
     <t>POD</t>
   </si>
@@ -520,6 +511,39 @@
   </si>
   <si>
     <t>1 al 15 de junio</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>RIO DE JANEIRO</t>
+  </si>
+  <si>
+    <t>ITAPOÁ</t>
+  </si>
+  <si>
+    <t>RIO GRANDE</t>
+  </si>
+  <si>
+    <t>PARANAGUÁ</t>
+  </si>
+  <si>
+    <t>ITAJAI</t>
+  </si>
+  <si>
+    <t>SUAPE</t>
+  </si>
+  <si>
+    <t>PECEM</t>
+  </si>
+  <si>
+    <t>1 al30 de junio</t>
+  </si>
+  <si>
+    <t>HPL</t>
+  </si>
+  <si>
+    <t>DFX</t>
   </si>
 </sst>
 </file>
@@ -12880,101 +12904,277 @@
       </c>
     </row>
     <row r="429" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A429" t="s">
+        <v>159</v>
+      </c>
+      <c r="B429" t="s">
+        <v>15</v>
+      </c>
       <c r="C429" s="11"/>
-      <c r="D429" s="11"/>
-      <c r="E429" s="11"/>
+      <c r="D429" s="11">
+        <v>2500</v>
+      </c>
+      <c r="E429" s="11">
+        <v>2580</v>
+      </c>
+      <c r="F429" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G429" s="8">
+        <v>15</v>
+      </c>
+      <c r="H429" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I429" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A430" t="s">
+        <v>160</v>
+      </c>
+      <c r="B430" t="s">
+        <v>15</v>
+      </c>
       <c r="C430" s="11"/>
-      <c r="D430" s="11"/>
-      <c r="E430" s="11"/>
+      <c r="D430" s="11">
+        <v>2500</v>
+      </c>
+      <c r="E430" s="11">
+        <v>2580</v>
+      </c>
+      <c r="F430" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G430" s="8">
+        <v>15</v>
+      </c>
+      <c r="H430" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I430" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A431" t="s">
+        <v>161</v>
+      </c>
+      <c r="B431" t="s">
+        <v>15</v>
+      </c>
       <c r="C431" s="11"/>
-      <c r="D431" s="11"/>
-      <c r="E431" s="11"/>
+      <c r="D431" s="11">
+        <v>2500</v>
+      </c>
+      <c r="E431" s="11">
+        <v>2580</v>
+      </c>
+      <c r="F431" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G431" s="8">
+        <v>15</v>
+      </c>
+      <c r="H431" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I431" s="7" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A432" t="s">
+        <v>162</v>
+      </c>
+      <c r="B432" t="s">
+        <v>15</v>
+      </c>
       <c r="C432" s="11"/>
-      <c r="D432" s="11"/>
-      <c r="E432" s="11"/>
-    </row>
-    <row r="433" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D432" s="11">
+        <v>2500</v>
+      </c>
+      <c r="E432" s="11">
+        <v>2580</v>
+      </c>
+      <c r="F432" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G432" s="8">
+        <v>15</v>
+      </c>
+      <c r="H432" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I432" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="433" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A433" t="s">
+        <v>163</v>
+      </c>
+      <c r="B433" t="s">
+        <v>15</v>
+      </c>
       <c r="C433" s="11"/>
-      <c r="D433" s="11"/>
-      <c r="E433" s="11"/>
-    </row>
-    <row r="434" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D433" s="11">
+        <v>2850</v>
+      </c>
+      <c r="E433" s="11">
+        <v>3060</v>
+      </c>
+      <c r="F433" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G433" s="8">
+        <v>15</v>
+      </c>
+      <c r="H433" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I433" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="434" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A434" t="s">
+        <v>164</v>
+      </c>
+      <c r="B434" t="s">
+        <v>15</v>
+      </c>
       <c r="C434" s="11"/>
-      <c r="D434" s="11"/>
-      <c r="E434" s="11"/>
-    </row>
-    <row r="435" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D434" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E434" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F434" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G434" s="8">
+        <v>15</v>
+      </c>
+      <c r="H434" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="435" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A435" t="s">
+        <v>165</v>
+      </c>
+      <c r="B435" t="s">
+        <v>15</v>
+      </c>
       <c r="C435" s="11"/>
-      <c r="D435" s="11"/>
-      <c r="E435" s="11"/>
-    </row>
-    <row r="436" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D435" s="11">
+        <v>3370</v>
+      </c>
+      <c r="E435" s="11">
+        <v>3580</v>
+      </c>
+      <c r="F435" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G435" s="8">
+        <v>15</v>
+      </c>
+      <c r="H435" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I435" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="436" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A436" t="s">
+        <v>166</v>
+      </c>
+      <c r="B436" t="s">
+        <v>15</v>
+      </c>
       <c r="C436" s="11"/>
-      <c r="D436" s="11"/>
-      <c r="E436" s="11"/>
-    </row>
-    <row r="437" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D436" s="11">
+        <v>3460</v>
+      </c>
+      <c r="E436" s="11">
+        <v>3860</v>
+      </c>
+      <c r="F436" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="G436" s="8">
+        <v>15</v>
+      </c>
+      <c r="H436" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="437" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C437" s="11"/>
       <c r="D437" s="11"/>
       <c r="E437" s="11"/>
     </row>
-    <row r="438" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C438" s="11"/>
       <c r="D438" s="11"/>
       <c r="E438" s="11"/>
     </row>
-    <row r="439" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C439" s="11"/>
       <c r="D439" s="11"/>
       <c r="E439" s="11"/>
     </row>
-    <row r="440" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C440" s="11"/>
       <c r="D440" s="11"/>
       <c r="E440" s="11"/>
     </row>
-    <row r="441" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C441" s="11"/>
       <c r="D441" s="11"/>
       <c r="E441" s="11"/>
     </row>
-    <row r="442" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C442" s="11"/>
       <c r="D442" s="11"/>
       <c r="E442" s="11"/>
     </row>
-    <row r="443" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C443" s="11"/>
       <c r="D443" s="11"/>
       <c r="E443" s="11"/>
     </row>
-    <row r="444" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C444" s="11"/>
       <c r="D444" s="11"/>
       <c r="E444" s="11"/>
     </row>
-    <row r="445" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C445" s="11"/>
       <c r="D445" s="11"/>
       <c r="E445" s="11"/>
     </row>
-    <row r="446" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C446" s="11"/>
       <c r="D446" s="11"/>
       <c r="E446" s="11"/>
     </row>
-    <row r="447" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C447" s="11"/>
       <c r="D447" s="11"/>
       <c r="E447" s="11"/>
     </row>
-    <row r="448" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C448" s="11"/>
       <c r="D448" s="11"/>
       <c r="E448" s="11"/>
@@ -17120,7 +17320,7 @@
       <c r="E1276" s="11"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I17" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
+  <autoFilter ref="A1:I428" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}"/>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/data/tarifas.xlsx
+++ b/data/tarifas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ecuworldwide-my.sharepoint.com/personal/daniel_calle_am_eculine_net/Documents/Documentos/ASIAPAC/COTIZADOR GITHUB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="185" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4931216D-407B-4A5A-AEE2-3B7B67CBB99C}"/>
+  <xr:revisionPtr revIDLastSave="191" documentId="8_{06DB657C-D116-4D70-A1A8-ADA8965C387F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CEDFFB5-7B80-454F-A8D3-53F9ABA633E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="512" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,20 +21,29 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$199</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RATES!$A$1:$I$414</definedName>
     <definedName name="Dgroup">OFFSET([1]Tariff!$J$136, 0, 0, COUNTA([1]Tariff!$J$136:$J$140),1)</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1461" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2382" uniqueCount="181">
   <si>
     <t>POD</t>
   </si>
@@ -559,6 +568,24 @@
   </si>
   <si>
     <t>15 al 21 de junio</t>
+  </si>
+  <si>
+    <t>TUTICORIN (NEW TUTICORIN)</t>
+  </si>
+  <si>
+    <t>NAGOYA</t>
+  </si>
+  <si>
+    <t>OSAKA</t>
+  </si>
+  <si>
+    <t>BUSAN NEW PORT</t>
+  </si>
+  <si>
+    <t>VUNG TAU</t>
+  </si>
+  <si>
+    <t>16 al 31 de junio</t>
   </si>
 </sst>
 </file>
@@ -1070,7 +1097,7 @@
 
 <file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
 <wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="1">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="2">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -1092,7 +1119,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4725C15-4070-400E-AEB7-BEAF299F75D6}">
-  <dimension ref="A1:K1044"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:K994"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" bestFit="1" customWidth="1"/>
@@ -1130,7 +1158,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>59</v>
       </c>
@@ -1161,7 +1189,7 @@
       <c r="J2" s="12"/>
       <c r="K2" s="12"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -1192,7 +1220,7 @@
       <c r="J3" s="12"/>
       <c r="K3" s="12"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>61</v>
       </c>
@@ -1223,7 +1251,7 @@
       <c r="J4" s="12"/>
       <c r="K4" s="12"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>65</v>
       </c>
@@ -1254,7 +1282,7 @@
       <c r="J5" s="12"/>
       <c r="K5" s="12"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>66</v>
       </c>
@@ -1285,7 +1313,7 @@
       <c r="J6" s="12"/>
       <c r="K6" s="12"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1316,7 +1344,7 @@
       <c r="J7" s="12"/>
       <c r="K7" s="12"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -1347,7 +1375,7 @@
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>69</v>
       </c>
@@ -1378,7 +1406,7 @@
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>70</v>
       </c>
@@ -1409,7 +1437,7 @@
       <c r="J10" s="12"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>68</v>
       </c>
@@ -1440,7 +1468,7 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1471,7 +1499,7 @@
       <c r="J12" s="12"/>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>71</v>
       </c>
@@ -1502,7 +1530,7 @@
       <c r="J13" s="12"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>70</v>
       </c>
@@ -1533,7 +1561,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>71</v>
       </c>
@@ -1564,7 +1592,7 @@
       <c r="J15" s="12"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>72</v>
       </c>
@@ -1595,7 +1623,7 @@
       <c r="J16" s="12"/>
       <c r="K16" s="12"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -1626,7 +1654,7 @@
       <c r="J17" s="12"/>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -1654,7 +1682,7 @@
       </c>
       <c r="J18" s="7"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -1682,7 +1710,7 @@
       </c>
       <c r="J19" s="7"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
@@ -1710,7 +1738,7 @@
       </c>
       <c r="J20" s="7"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>75</v>
       </c>
@@ -1738,7 +1766,7 @@
       </c>
       <c r="J21" s="7"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>76</v>
       </c>
@@ -1766,7 +1794,7 @@
       </c>
       <c r="J22" s="7"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>52</v>
       </c>
@@ -1794,7 +1822,7 @@
       </c>
       <c r="J23" s="7"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -1822,7 +1850,7 @@
       </c>
       <c r="J24" s="7"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1850,7 +1878,7 @@
       </c>
       <c r="J25" s="7"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -1878,7 +1906,7 @@
       </c>
       <c r="J26" s="7"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -1906,7 +1934,7 @@
       </c>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -1934,7 +1962,7 @@
       </c>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -1962,7 +1990,7 @@
       </c>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -1990,7 +2018,7 @@
       </c>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>30</v>
       </c>
@@ -2018,7 +2046,7 @@
       </c>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>56</v>
       </c>
@@ -2046,7 +2074,7 @@
       </c>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -2074,7 +2102,7 @@
       </c>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>28</v>
       </c>
@@ -2102,7 +2130,7 @@
       </c>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>57</v>
       </c>
@@ -2130,7 +2158,7 @@
       </c>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -2158,7 +2186,7 @@
       </c>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -2186,7 +2214,7 @@
       </c>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>25</v>
       </c>
@@ -2214,7 +2242,7 @@
       </c>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -2242,7 +2270,7 @@
       </c>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -2270,7 +2298,7 @@
       </c>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -2298,7 +2326,7 @@
       </c>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>32</v>
       </c>
@@ -2326,7 +2354,7 @@
       </c>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -2354,7 +2382,7 @@
       </c>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>87</v>
       </c>
@@ -2382,7 +2410,7 @@
       </c>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>20</v>
       </c>
@@ -2410,7 +2438,7 @@
       </c>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>81</v>
       </c>
@@ -2438,7 +2466,7 @@
       </c>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -2466,7 +2494,7 @@
       </c>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>31</v>
       </c>
@@ -2494,7 +2522,7 @@
       </c>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -2522,7 +2550,7 @@
       </c>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>26</v>
       </c>
@@ -2550,7 +2578,7 @@
       </c>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>49</v>
       </c>
@@ -2577,7 +2605,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2634,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>4</v>
       </c>
@@ -2633,7 +2661,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>74</v>
       </c>
@@ -2660,7 +2688,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>52</v>
       </c>
@@ -2687,7 +2715,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>35</v>
       </c>
@@ -2714,7 +2742,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>24</v>
       </c>
@@ -2741,7 +2769,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>50</v>
       </c>
@@ -2768,7 +2796,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>29</v>
       </c>
@@ -2795,7 +2823,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>82</v>
       </c>
@@ -2822,7 +2850,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>77</v>
       </c>
@@ -2849,7 +2877,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -2876,7 +2904,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>48</v>
       </c>
@@ -2903,7 +2931,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>33</v>
       </c>
@@ -2930,7 +2958,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>30</v>
       </c>
@@ -2957,7 +2985,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>94</v>
       </c>
@@ -2984,7 +3012,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>56</v>
       </c>
@@ -3011,7 +3039,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>34</v>
       </c>
@@ -3038,7 +3066,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>28</v>
       </c>
@@ -3065,7 +3093,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>57</v>
       </c>
@@ -3092,7 +3120,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -3119,7 +3147,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -3146,7 +3174,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>83</v>
       </c>
@@ -3173,7 +3201,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>25</v>
       </c>
@@ -3200,7 +3228,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>19</v>
       </c>
@@ -3227,7 +3255,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>21</v>
       </c>
@@ -3254,7 +3282,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>51</v>
       </c>
@@ -3281,7 +3309,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>53</v>
       </c>
@@ -3308,7 +3336,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>32</v>
       </c>
@@ -3335,7 +3363,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>16</v>
       </c>
@@ -3362,7 +3390,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>87</v>
       </c>
@@ -3391,7 +3419,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>95</v>
       </c>
@@ -3418,7 +3446,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>20</v>
       </c>
@@ -3445,7 +3473,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>81</v>
       </c>
@@ -3472,7 +3500,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>55</v>
       </c>
@@ -3499,7 +3527,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -3526,7 +3554,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>54</v>
       </c>
@@ -3553,7 +3581,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>26</v>
       </c>
@@ -3580,7 +3608,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>49</v>
       </c>
@@ -3607,7 +3635,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>5</v>
       </c>
@@ -3634,7 +3662,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>4</v>
       </c>
@@ -3661,7 +3689,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>74</v>
       </c>
@@ -3688,7 +3716,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>75</v>
       </c>
@@ -3715,7 +3743,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>76</v>
       </c>
@@ -3742,7 +3770,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>52</v>
       </c>
@@ -3769,7 +3797,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>35</v>
       </c>
@@ -3796,7 +3824,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>24</v>
       </c>
@@ -3823,7 +3851,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>50</v>
       </c>
@@ -3850,7 +3878,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>29</v>
       </c>
@@ -3877,7 +3905,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>27</v>
       </c>
@@ -3904,7 +3932,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>48</v>
       </c>
@@ -3931,7 +3959,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>33</v>
       </c>
@@ -3958,7 +3986,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>78</v>
       </c>
@@ -3985,7 +4013,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>30</v>
       </c>
@@ -4012,7 +4040,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>56</v>
       </c>
@@ -4039,7 +4067,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>28</v>
       </c>
@@ -4066,7 +4094,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>57</v>
       </c>
@@ -4093,7 +4121,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -4120,7 +4148,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>79</v>
       </c>
@@ -4147,7 +4175,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>25</v>
       </c>
@@ -4174,7 +4202,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>19</v>
       </c>
@@ -4201,7 +4229,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>21</v>
       </c>
@@ -4228,7 +4256,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>51</v>
       </c>
@@ -4255,7 +4283,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>53</v>
       </c>
@@ -4282,7 +4310,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>80</v>
       </c>
@@ -4309,7 +4337,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>16</v>
       </c>
@@ -4336,7 +4364,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>87</v>
       </c>
@@ -4363,7 +4391,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>20</v>
       </c>
@@ -4390,7 +4418,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>55</v>
       </c>
@@ -4417,7 +4445,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>31</v>
       </c>
@@ -4444,7 +4472,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>54</v>
       </c>
@@ -4471,7 +4499,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>26</v>
       </c>
@@ -4498,7 +4526,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>49</v>
       </c>
@@ -4525,7 +4553,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>5</v>
       </c>
@@ -4554,7 +4582,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>4</v>
       </c>
@@ -4583,7 +4611,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>74</v>
       </c>
@@ -4610,7 +4638,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>75</v>
       </c>
@@ -4637,7 +4665,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>76</v>
       </c>
@@ -4664,7 +4692,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>52</v>
       </c>
@@ -4691,7 +4719,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>50</v>
       </c>
@@ -4718,7 +4746,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>29</v>
       </c>
@@ -4745,7 +4773,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>82</v>
       </c>
@@ -4772,7 +4800,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>77</v>
       </c>
@@ -4799,7 +4827,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>27</v>
       </c>
@@ -4826,7 +4854,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>48</v>
       </c>
@@ -4853,7 +4881,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>78</v>
       </c>
@@ -4880,7 +4908,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>28</v>
       </c>
@@ -4907,7 +4935,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>79</v>
       </c>
@@ -4934,7 +4962,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>83</v>
       </c>
@@ -4961,7 +4989,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>25</v>
       </c>
@@ -4988,7 +5016,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>19</v>
       </c>
@@ -5017,7 +5045,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>21</v>
       </c>
@@ -5046,7 +5074,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>51</v>
       </c>
@@ -5073,7 +5101,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>80</v>
       </c>
@@ -5100,7 +5128,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -5127,7 +5155,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>26</v>
       </c>
@@ -5154,7 +5182,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>49</v>
       </c>
@@ -5181,7 +5209,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>5</v>
       </c>
@@ -5208,7 +5236,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>4</v>
       </c>
@@ -5235,7 +5263,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>13</v>
       </c>
@@ -5262,7 +5290,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>87</v>
       </c>
@@ -5289,7 +5317,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>30</v>
       </c>
@@ -5316,7 +5344,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>24</v>
       </c>
@@ -5343,7 +5371,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>99</v>
       </c>
@@ -5370,7 +5398,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>100</v>
       </c>
@@ -5397,7 +5425,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>101</v>
       </c>
@@ -5424,7 +5452,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>102</v>
       </c>
@@ -5451,7 +5479,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>103</v>
       </c>
@@ -5478,7 +5506,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>104</v>
       </c>
@@ -5505,7 +5533,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>105</v>
       </c>
@@ -5532,7 +5560,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>142</v>
       </c>
@@ -5559,7 +5587,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>106</v>
       </c>
@@ -5586,7 +5614,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>107</v>
       </c>
@@ -5613,7 +5641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>108</v>
       </c>
@@ -5640,7 +5668,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>109</v>
       </c>
@@ -5667,7 +5695,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>110</v>
       </c>
@@ -5694,7 +5722,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>111</v>
       </c>
@@ -5721,7 +5749,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>112</v>
       </c>
@@ -5748,7 +5776,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>113</v>
       </c>
@@ -5775,7 +5803,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>132</v>
       </c>
@@ -5802,7 +5830,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>133</v>
       </c>
@@ -5829,7 +5857,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>139</v>
       </c>
@@ -5856,7 +5884,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>134</v>
       </c>
@@ -5883,7 +5911,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>135</v>
       </c>
@@ -5910,7 +5938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>136</v>
       </c>
@@ -5937,7 +5965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>137</v>
       </c>
@@ -5964,7 +5992,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>76</v>
       </c>
@@ -5991,7 +6019,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>114</v>
       </c>
@@ -6018,7 +6046,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>140</v>
       </c>
@@ -6045,7 +6073,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>115</v>
       </c>
@@ -6072,7 +6100,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>116</v>
       </c>
@@ -6099,7 +6127,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>117</v>
       </c>
@@ -6126,7 +6154,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>118</v>
       </c>
@@ -6153,7 +6181,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>119</v>
       </c>
@@ -6180,7 +6208,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>120</v>
       </c>
@@ -6207,7 +6235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>121</v>
       </c>
@@ -6234,7 +6262,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>122</v>
       </c>
@@ -6261,7 +6289,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>123</v>
       </c>
@@ -6288,7 +6316,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>124</v>
       </c>
@@ -6315,7 +6343,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>141</v>
       </c>
@@ -6342,7 +6370,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>125</v>
       </c>
@@ -6369,7 +6397,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>126</v>
       </c>
@@ -6396,7 +6424,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>127</v>
       </c>
@@ -6423,7 +6451,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>110</v>
       </c>
@@ -6450,7 +6478,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>128</v>
       </c>
@@ -6477,7 +6505,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>129</v>
       </c>
@@ -6504,7 +6532,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>130</v>
       </c>
@@ -6531,7 +6559,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>113</v>
       </c>
@@ -6558,7 +6586,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>131</v>
       </c>
@@ -6585,7 +6613,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>144</v>
       </c>
@@ -6612,7 +6640,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>145</v>
       </c>
@@ -6639,7 +6667,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>146</v>
       </c>
@@ -6666,7 +6694,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>147</v>
       </c>
@@ -6693,7 +6721,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>148</v>
       </c>
@@ -6720,7 +6748,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>149</v>
       </c>
@@ -6747,7 +6775,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>150</v>
       </c>
@@ -6774,7 +6802,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>151</v>
       </c>
@@ -8719,931 +8747,4969 @@
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>5</v>
+      </c>
+      <c r="B279" t="s">
+        <v>62</v>
+      </c>
       <c r="C279" s="11"/>
-      <c r="D279" s="11"/>
-      <c r="E279" s="11"/>
+      <c r="D279" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E279" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G279" s="8">
+        <v>14</v>
+      </c>
+      <c r="H279" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="I279" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>4</v>
+      </c>
+      <c r="B280" t="s">
+        <v>62</v>
+      </c>
       <c r="C280" s="11"/>
-      <c r="D280" s="11"/>
-      <c r="E280" s="11"/>
+      <c r="D280" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E280" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G280" s="8">
+        <v>14</v>
+      </c>
+      <c r="H280" t="s">
+        <v>63</v>
+      </c>
+      <c r="I280" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>74</v>
+      </c>
+      <c r="B281" t="s">
+        <v>62</v>
+      </c>
       <c r="C281" s="11"/>
-      <c r="D281" s="11"/>
-      <c r="E281" s="11"/>
+      <c r="D281" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E281" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G281" s="8">
+        <v>14</v>
+      </c>
+      <c r="H281" t="s">
+        <v>63</v>
+      </c>
+      <c r="I281" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>75</v>
+      </c>
+      <c r="B282" t="s">
+        <v>62</v>
+      </c>
       <c r="C282" s="11"/>
-      <c r="D282" s="11"/>
-      <c r="E282" s="11"/>
+      <c r="D282" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E282" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G282" s="8">
+        <v>14</v>
+      </c>
+      <c r="H282" t="s">
+        <v>63</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>76</v>
+      </c>
+      <c r="B283" t="s">
+        <v>62</v>
+      </c>
       <c r="C283" s="11"/>
-      <c r="D283" s="11"/>
-      <c r="E283" s="11"/>
+      <c r="D283" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E283" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F283" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G283" s="8">
+        <v>14</v>
+      </c>
+      <c r="H283" t="s">
+        <v>63</v>
+      </c>
+      <c r="I283" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>52</v>
+      </c>
+      <c r="B284" t="s">
+        <v>62</v>
+      </c>
       <c r="C284" s="11"/>
-      <c r="D284" s="11"/>
-      <c r="E284" s="11"/>
+      <c r="D284" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E284" s="11">
+        <v>6810</v>
+      </c>
+      <c r="F284" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G284" s="8">
+        <v>14</v>
+      </c>
+      <c r="H284" t="s">
+        <v>63</v>
+      </c>
+      <c r="I284" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>35</v>
+      </c>
+      <c r="B285" t="s">
+        <v>62</v>
+      </c>
       <c r="C285" s="11"/>
-      <c r="D285" s="11"/>
-      <c r="E285" s="11"/>
+      <c r="D285" s="11">
+        <v>6610</v>
+      </c>
+      <c r="E285" s="11">
+        <v>7310</v>
+      </c>
+      <c r="F285" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G285" s="8">
+        <v>14</v>
+      </c>
+      <c r="H285" t="s">
+        <v>63</v>
+      </c>
+      <c r="I285" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>24</v>
+      </c>
+      <c r="B286" t="s">
+        <v>62</v>
+      </c>
       <c r="C286" s="11"/>
-      <c r="D286" s="11"/>
-      <c r="E286" s="11"/>
+      <c r="D286" s="11">
+        <v>6510</v>
+      </c>
+      <c r="E286" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F286" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G286" s="8">
+        <v>14</v>
+      </c>
+      <c r="H286" t="s">
+        <v>63</v>
+      </c>
+      <c r="I286" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>50</v>
+      </c>
+      <c r="B287" t="s">
+        <v>62</v>
+      </c>
       <c r="C287" s="11"/>
-      <c r="D287" s="11"/>
-      <c r="E287" s="11"/>
+      <c r="D287" s="11">
+        <v>6560</v>
+      </c>
+      <c r="E287" s="11">
+        <v>7010</v>
+      </c>
+      <c r="F287" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G287" s="8">
+        <v>14</v>
+      </c>
+      <c r="H287" t="s">
+        <v>63</v>
+      </c>
+      <c r="I287" s="7" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>29</v>
+      </c>
+      <c r="B288" t="s">
+        <v>62</v>
+      </c>
       <c r="C288" s="11"/>
-      <c r="D288" s="11"/>
-      <c r="E288" s="11"/>
-    </row>
-    <row r="289" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D288" s="11">
+        <v>6660</v>
+      </c>
+      <c r="E288" s="11">
+        <v>7210</v>
+      </c>
+      <c r="F288" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G288" s="8">
+        <v>14</v>
+      </c>
+      <c r="H288" t="s">
+        <v>63</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>27</v>
+      </c>
+      <c r="B289" t="s">
+        <v>62</v>
+      </c>
       <c r="C289" s="11"/>
-      <c r="D289" s="11"/>
-      <c r="E289" s="11"/>
-    </row>
-    <row r="290" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D289" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E289" s="11">
+        <v>6810</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G289" s="8">
+        <v>14</v>
+      </c>
+      <c r="H289" t="s">
+        <v>63</v>
+      </c>
+      <c r="I289" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>48</v>
+      </c>
+      <c r="B290" t="s">
+        <v>62</v>
+      </c>
       <c r="C290" s="11"/>
-      <c r="D290" s="11"/>
-      <c r="E290" s="11"/>
-    </row>
-    <row r="291" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D290" s="11">
+        <v>6610</v>
+      </c>
+      <c r="E290" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G290" s="8">
+        <v>14</v>
+      </c>
+      <c r="H290" t="s">
+        <v>63</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>33</v>
+      </c>
+      <c r="B291" t="s">
+        <v>62</v>
+      </c>
       <c r="C291" s="11"/>
-      <c r="D291" s="11"/>
-      <c r="E291" s="11"/>
-    </row>
-    <row r="292" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D291" s="11">
+        <v>6410</v>
+      </c>
+      <c r="E291" s="11">
+        <v>6910</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G291" s="8">
+        <v>14</v>
+      </c>
+      <c r="H291" t="s">
+        <v>63</v>
+      </c>
+      <c r="I291" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>30</v>
+      </c>
+      <c r="B292" t="s">
+        <v>62</v>
+      </c>
       <c r="C292" s="11"/>
-      <c r="D292" s="11"/>
-      <c r="E292" s="11"/>
-    </row>
-    <row r="293" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D292" s="11">
+        <v>6560</v>
+      </c>
+      <c r="E292" s="11">
+        <v>7110</v>
+      </c>
+      <c r="F292" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G292" s="8">
+        <v>14</v>
+      </c>
+      <c r="H292" t="s">
+        <v>63</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>56</v>
+      </c>
+      <c r="B293" t="s">
+        <v>62</v>
+      </c>
       <c r="C293" s="11"/>
-      <c r="D293" s="11"/>
-      <c r="E293" s="11"/>
-    </row>
-    <row r="294" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D293" s="11">
+        <v>6510</v>
+      </c>
+      <c r="E293" s="11">
+        <v>6860</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G293" s="8">
+        <v>14</v>
+      </c>
+      <c r="H293" t="s">
+        <v>63</v>
+      </c>
+      <c r="I293" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>34</v>
+      </c>
+      <c r="B294" t="s">
+        <v>62</v>
+      </c>
       <c r="C294" s="11"/>
-      <c r="D294" s="11"/>
-      <c r="E294" s="11"/>
-    </row>
-    <row r="295" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D294" s="11">
+        <v>6610</v>
+      </c>
+      <c r="E294" s="11">
+        <v>7060</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G294" s="8">
+        <v>14</v>
+      </c>
+      <c r="H294" t="s">
+        <v>63</v>
+      </c>
+      <c r="I294" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>28</v>
+      </c>
+      <c r="B295" t="s">
+        <v>62</v>
+      </c>
       <c r="C295" s="11"/>
-      <c r="D295" s="11"/>
-      <c r="E295" s="11"/>
-    </row>
-    <row r="296" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D295" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E295" s="11">
+        <v>6860</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G295" s="8">
+        <v>14</v>
+      </c>
+      <c r="H295" t="s">
+        <v>63</v>
+      </c>
+      <c r="I295" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>57</v>
+      </c>
+      <c r="B296" t="s">
+        <v>62</v>
+      </c>
       <c r="C296" s="11"/>
-      <c r="D296" s="11"/>
-      <c r="E296" s="11"/>
-    </row>
-    <row r="297" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D296" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E296" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G296" s="8">
+        <v>14</v>
+      </c>
+      <c r="H296" t="s">
+        <v>63</v>
+      </c>
+      <c r="I296" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>13</v>
+      </c>
+      <c r="B297" t="s">
+        <v>62</v>
+      </c>
       <c r="C297" s="11"/>
-      <c r="D297" s="11"/>
-      <c r="E297" s="11"/>
-    </row>
-    <row r="298" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D297" s="11">
+        <v>6260</v>
+      </c>
+      <c r="E297" s="11">
+        <v>6610</v>
+      </c>
+      <c r="F297" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G297" s="8">
+        <v>14</v>
+      </c>
+      <c r="H297" t="s">
+        <v>63</v>
+      </c>
+      <c r="I297" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>79</v>
+      </c>
+      <c r="B298" t="s">
+        <v>62</v>
+      </c>
       <c r="C298" s="11"/>
-      <c r="D298" s="11"/>
-      <c r="E298" s="11"/>
-    </row>
-    <row r="299" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D298" s="11">
+        <v>6510</v>
+      </c>
+      <c r="E298" s="11">
+        <v>6910</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G298" s="8">
+        <v>14</v>
+      </c>
+      <c r="H298" t="s">
+        <v>63</v>
+      </c>
+      <c r="I298" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>25</v>
+      </c>
+      <c r="B299" t="s">
+        <v>62</v>
+      </c>
       <c r="C299" s="11"/>
-      <c r="D299" s="11"/>
-      <c r="E299" s="11"/>
-    </row>
-    <row r="300" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D299" s="11">
+        <v>6510</v>
+      </c>
+      <c r="E299" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G299" s="8">
+        <v>14</v>
+      </c>
+      <c r="H299" t="s">
+        <v>63</v>
+      </c>
+      <c r="I299" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>21</v>
+      </c>
+      <c r="B300" t="s">
+        <v>62</v>
+      </c>
       <c r="C300" s="11"/>
-      <c r="D300" s="11"/>
-      <c r="E300" s="11"/>
-    </row>
-    <row r="301" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D300" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E300" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G300" s="8">
+        <v>14</v>
+      </c>
+      <c r="H300" t="s">
+        <v>63</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>51</v>
+      </c>
+      <c r="B301" t="s">
+        <v>62</v>
+      </c>
       <c r="C301" s="11"/>
-      <c r="D301" s="11"/>
-      <c r="E301" s="11"/>
-    </row>
-    <row r="302" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D301" s="11">
+        <v>6610</v>
+      </c>
+      <c r="E301" s="11">
+        <v>7010</v>
+      </c>
+      <c r="F301" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G301" s="8">
+        <v>14</v>
+      </c>
+      <c r="H301" t="s">
+        <v>63</v>
+      </c>
+      <c r="I301" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>53</v>
+      </c>
+      <c r="B302" t="s">
+        <v>62</v>
+      </c>
       <c r="C302" s="11"/>
-      <c r="D302" s="11"/>
-      <c r="E302" s="11"/>
-    </row>
-    <row r="303" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D302" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E302" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G302" s="8">
+        <v>14</v>
+      </c>
+      <c r="H302" t="s">
+        <v>63</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>32</v>
+      </c>
+      <c r="B303" t="s">
+        <v>62</v>
+      </c>
       <c r="C303" s="11"/>
-      <c r="D303" s="11"/>
-      <c r="E303" s="11"/>
-    </row>
-    <row r="304" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D303" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E303" s="11">
+        <v>6860</v>
+      </c>
+      <c r="F303" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G303" s="8">
+        <v>14</v>
+      </c>
+      <c r="H303" t="s">
+        <v>63</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>16</v>
+      </c>
+      <c r="B304" t="s">
+        <v>62</v>
+      </c>
       <c r="C304" s="11"/>
-      <c r="D304" s="11"/>
-      <c r="E304" s="11"/>
-    </row>
-    <row r="305" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D304" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E304" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G304" s="8">
+        <v>14</v>
+      </c>
+      <c r="H304" t="s">
+        <v>63</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>87</v>
+      </c>
+      <c r="B305" t="s">
+        <v>62</v>
+      </c>
       <c r="C305" s="11"/>
-      <c r="D305" s="11"/>
-      <c r="E305" s="11"/>
-    </row>
-    <row r="306" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D305" s="11">
+        <v>6560</v>
+      </c>
+      <c r="E305" s="11">
+        <v>7110</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G305" s="8">
+        <v>14</v>
+      </c>
+      <c r="H305" t="s">
+        <v>63</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>20</v>
+      </c>
+      <c r="B306" t="s">
+        <v>62</v>
+      </c>
       <c r="C306" s="11"/>
-      <c r="D306" s="11"/>
-      <c r="E306" s="11"/>
-    </row>
-    <row r="307" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D306" s="11">
+        <v>6210</v>
+      </c>
+      <c r="E306" s="11">
+        <v>6510</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G306" s="8">
+        <v>14</v>
+      </c>
+      <c r="H306" t="s">
+        <v>63</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>81</v>
+      </c>
+      <c r="B307" t="s">
+        <v>62</v>
+      </c>
       <c r="C307" s="11"/>
-      <c r="D307" s="11"/>
-      <c r="E307" s="11"/>
-    </row>
-    <row r="308" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D307" s="11">
+        <v>6610</v>
+      </c>
+      <c r="E307" s="11">
+        <v>7110</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G307" s="8">
+        <v>14</v>
+      </c>
+      <c r="H307" t="s">
+        <v>63</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>55</v>
+      </c>
+      <c r="B308" t="s">
+        <v>62</v>
+      </c>
       <c r="C308" s="11"/>
-      <c r="D308" s="11"/>
-      <c r="E308" s="11"/>
-    </row>
-    <row r="309" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D308" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E308" s="11">
+        <v>6810</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G308" s="8">
+        <v>14</v>
+      </c>
+      <c r="H308" t="s">
+        <v>63</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>31</v>
+      </c>
+      <c r="B309" t="s">
+        <v>62</v>
+      </c>
       <c r="C309" s="11"/>
-      <c r="D309" s="11"/>
-      <c r="E309" s="11"/>
-    </row>
-    <row r="310" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D309" s="11">
+        <v>6610</v>
+      </c>
+      <c r="E309" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G309" s="8">
+        <v>14</v>
+      </c>
+      <c r="H309" t="s">
+        <v>63</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>54</v>
+      </c>
+      <c r="B310" t="s">
+        <v>62</v>
+      </c>
       <c r="C310" s="11"/>
-      <c r="D310" s="11"/>
-      <c r="E310" s="11"/>
-    </row>
-    <row r="311" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D310" s="11">
+        <v>6460</v>
+      </c>
+      <c r="E310" s="11">
+        <v>6860</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G310" s="8">
+        <v>14</v>
+      </c>
+      <c r="H310" t="s">
+        <v>63</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>26</v>
+      </c>
+      <c r="B311" t="s">
+        <v>62</v>
+      </c>
       <c r="C311" s="11"/>
-      <c r="D311" s="11"/>
-      <c r="E311" s="11"/>
-    </row>
-    <row r="312" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D311" s="11">
+        <v>6560</v>
+      </c>
+      <c r="E311" s="11">
+        <v>6960</v>
+      </c>
+      <c r="F311" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G311" s="8">
+        <v>14</v>
+      </c>
+      <c r="H311" t="s">
+        <v>63</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>49</v>
+      </c>
+      <c r="B312" t="s">
+        <v>62</v>
+      </c>
       <c r="C312" s="11"/>
-      <c r="D312" s="11"/>
-      <c r="E312" s="11"/>
-    </row>
-    <row r="313" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C313" s="11"/>
-      <c r="D313" s="11"/>
-      <c r="E313" s="11"/>
-    </row>
-    <row r="314" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D312" s="11">
+        <v>6560</v>
+      </c>
+      <c r="E312" s="11">
+        <v>7010</v>
+      </c>
+      <c r="F312" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G312" s="8">
+        <v>14</v>
+      </c>
+      <c r="H312" t="s">
+        <v>63</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>5</v>
+      </c>
+      <c r="B313" t="s">
+        <v>15</v>
+      </c>
+      <c r="C313" s="11">
+        <v>5470</v>
+      </c>
+      <c r="D313" s="11">
+        <v>6170</v>
+      </c>
+      <c r="E313" s="11">
+        <v>6370</v>
+      </c>
+      <c r="F313" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="H313" t="s">
+        <v>93</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>4</v>
+      </c>
+      <c r="B314" t="s">
+        <v>15</v>
+      </c>
       <c r="C314" s="11"/>
-      <c r="D314" s="11"/>
-      <c r="E314" s="11"/>
-    </row>
-    <row r="315" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D314" s="11">
+        <v>6170</v>
+      </c>
+      <c r="E314" s="11">
+        <v>6370</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G314" s="8">
+        <v>17</v>
+      </c>
+      <c r="H314" t="s">
+        <v>93</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>74</v>
+      </c>
+      <c r="B315" t="s">
+        <v>15</v>
+      </c>
       <c r="C315" s="11"/>
-      <c r="D315" s="11"/>
-      <c r="E315" s="11"/>
-    </row>
-    <row r="316" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D315" s="11">
+        <v>6170</v>
+      </c>
+      <c r="E315" s="11">
+        <v>6370</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G315" s="8">
+        <v>17</v>
+      </c>
+      <c r="H315" t="s">
+        <v>93</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>52</v>
+      </c>
+      <c r="B316" t="s">
+        <v>15</v>
+      </c>
       <c r="C316" s="11"/>
-      <c r="D316" s="11"/>
-      <c r="E316" s="11"/>
-    </row>
-    <row r="317" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D316" s="11">
+        <v>6280</v>
+      </c>
+      <c r="E316" s="11">
+        <v>6530</v>
+      </c>
+      <c r="F316" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G316" s="8">
+        <v>17</v>
+      </c>
+      <c r="H316" t="s">
+        <v>93</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>35</v>
+      </c>
+      <c r="B317" t="s">
+        <v>15</v>
+      </c>
       <c r="C317" s="11"/>
-      <c r="D317" s="11"/>
-      <c r="E317" s="11"/>
-    </row>
-    <row r="318" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D317" s="11">
+        <v>6430</v>
+      </c>
+      <c r="E317" s="11">
+        <v>6910</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G317" s="8">
+        <v>17</v>
+      </c>
+      <c r="H317" t="s">
+        <v>93</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>24</v>
+      </c>
+      <c r="B318" t="s">
+        <v>15</v>
+      </c>
       <c r="C318" s="11"/>
-      <c r="D318" s="11"/>
-      <c r="E318" s="11"/>
-    </row>
-    <row r="319" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D318" s="11">
+        <v>6220</v>
+      </c>
+      <c r="E318" s="11">
+        <v>6470</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G318" s="8">
+        <v>17</v>
+      </c>
+      <c r="H318" t="s">
+        <v>93</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>50</v>
+      </c>
+      <c r="B319" t="s">
+        <v>15</v>
+      </c>
       <c r="C319" s="11"/>
-      <c r="D319" s="11"/>
-      <c r="E319" s="11"/>
-    </row>
-    <row r="320" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D319" s="11">
+        <v>6280</v>
+      </c>
+      <c r="E319" s="11">
+        <v>6540</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G319" s="8">
+        <v>17</v>
+      </c>
+      <c r="H319" t="s">
+        <v>93</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>29</v>
+      </c>
+      <c r="B320" t="s">
+        <v>15</v>
+      </c>
       <c r="C320" s="11"/>
-      <c r="D320" s="11"/>
-      <c r="E320" s="11"/>
-    </row>
-    <row r="321" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D320" s="11">
+        <v>6220</v>
+      </c>
+      <c r="E320" s="11">
+        <v>6470</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G320" s="8">
+        <v>17</v>
+      </c>
+      <c r="H320" t="s">
+        <v>93</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>82</v>
+      </c>
+      <c r="B321" t="s">
+        <v>15</v>
+      </c>
       <c r="C321" s="11"/>
-      <c r="D321" s="11"/>
-      <c r="E321" s="11"/>
-    </row>
-    <row r="322" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D321" s="11">
+        <v>6320</v>
+      </c>
+      <c r="E321" s="11">
+        <v>6570</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G321" s="8">
+        <v>17</v>
+      </c>
+      <c r="H321" t="s">
+        <v>93</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>77</v>
+      </c>
+      <c r="B322" t="s">
+        <v>15</v>
+      </c>
       <c r="C322" s="11"/>
-      <c r="D322" s="11"/>
-      <c r="E322" s="11"/>
-    </row>
-    <row r="323" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D322" s="11">
+        <v>6270</v>
+      </c>
+      <c r="E322" s="11">
+        <v>6550</v>
+      </c>
+      <c r="F322" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G322" s="8">
+        <v>17</v>
+      </c>
+      <c r="H322" t="s">
+        <v>93</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>27</v>
+      </c>
+      <c r="B323" t="s">
+        <v>15</v>
+      </c>
       <c r="C323" s="11"/>
-      <c r="D323" s="11"/>
-      <c r="E323" s="11"/>
-    </row>
-    <row r="324" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="D323" s="11">
+        <v>6270</v>
+      </c>
+      <c r="E323" s="11">
+        <v>6570</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G323" s="8">
+        <v>17</v>
+      </c>
+      <c r="H323" t="s">
+        <v>93</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>85</v>
+      </